--- a/2027届秋招投递信息_2026-07-24.xlsx
+++ b/2027届秋招投递信息_2026-07-24.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R3195183b3c0a4cf8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="R7b14e7fafe6949de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="R0b9c3c4537e1477e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R1fd41a20ef1546d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="Rd22248b77c5446b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="R39cb9e3f4a6f45f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -83,6 +83,11 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4CCCC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
@@ -99,11 +104,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE6EBEE"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF4CCCC"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -195,7 +195,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -235,10 +235,13 @@
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -247,20 +250,14 @@
     <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -304,8 +301,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q93" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:Q93"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q107" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:Q107"/>
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="开放投递时间"/>
     <x:tableColumn id="2" name="企业名称"/>
@@ -571,7 +568,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>2027届秋招投递信息（截至2026-07-30）</x:v>
+        <x:v>2027届秋招投递信息（截至2026-08-03）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -592,7 +589,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>每日更新：按开放时间倒序；新增卓越教育集团、极客未来；京东TET截止日按官网更正为11月30日；鹰角与字节AI早鸟进入短期截止窗口；米哈游继续保留为已截止。</x:v>
+        <x:v>每日更新：按开放时间倒序；本轮新增2项官方核验项目，关闭4项；第三方汇总入口不作为立即投递链接。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -665,85 +662,85 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
-      <x:c r="A4" s="4" t="str">
-        <x:v>2026-07-28</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="str">
-        <x:v>广州市卓越教育集团</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="str">
-        <x:v>教育科技</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="str">
-        <x:v>广州等，以职位页为准</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G4" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="str">
-        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
-      </x:c>
-      <x:c r="I4" s="15" t="str">
-        <x:v>https://zyjob.hotjob.cn/</x:v>
-      </x:c>
-      <x:c r="J4" s="4" t="str">
-        <x:v>2026-10-26</x:v>
-      </x:c>
-      <x:c r="K4" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L4" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
-      </x:c>
-      <x:c r="M4" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
-      </x:c>
-      <x:c r="N4" s="4" t="str">
-        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
-      </x:c>
-      <x:c r="O4" s="15" t="str">
-        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
-      </x:c>
-      <x:c r="P4" s="14" t="str">
-        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
-      </x:c>
-      <x:c r="Q4" s="4" t="n">
-        <x:v>46233</x:v>
+      <x:c r="A4" s="14" t="str">
+        <x:v>不晚于2026-07-30</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="str">
+        <x:v>恒丰银行总行-雏鹰计划</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="str">
+        <x:v>银行/金融</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>股份制商业银行</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>总行及相关机构，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F4" s="14" t="str">
+        <x:v>暑期实习/秋招储备</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="str">
+        <x:v>2027届硕士及以上，以公告要求为准</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="str">
+        <x:v>总行实习生，具体专业和方向以官方公告为准</x:v>
+      </x:c>
+      <x:c r="I4" s="16" t="str">
+        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
+      </x:c>
+      <x:c r="J4" s="14" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K4" s="14" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L4" s="14" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M4" s="14" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N4" s="14" t="str">
+        <x:v>官方公告显示7月31日24:00截止，实习期安排和具体岗位以恒丰银行招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O4" s="16" t="str">
+        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
+      </x:c>
+      <x:c r="P4" s="15" t="str">
+        <x:v>A-企业官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q4" s="14" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>我乐家居</x:v>
+        <x:v>四方股份</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
-        <x:v>家居/消费品/智能制造</x:v>
+        <x:v>电力系统/工业自动化</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
-        <x:v>提前批/校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G5" s="4" t="str">
-        <x:v>2027届本科及以上，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H5" s="4" t="str">
-        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
-      </x:c>
-      <x:c r="I5" s="15" t="str">
-        <x:v>https://olo-home.zhiye.com/Campus</x:v>
+        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
+      </x:c>
+      <x:c r="I5" s="17" t="str">
+        <x:v>https://www.sf-auto.com/campus</x:v>
       </x:c>
       <x:c r="J5" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -752,51 +749,51 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L5" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
+        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="M5" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N5" s="4" t="str">
-        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
-      </x:c>
-      <x:c r="O5" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P5" s="16" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
-      </x:c>
-      <x:c r="Q5" s="4" t="n">
-        <x:v>46232</x:v>
+        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O5" s="17" t="str">
+        <x:v>https://www.sf-auto.com/campus</x:v>
+      </x:c>
+      <x:c r="P5" s="15" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q5" s="4" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="4" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>轩宇信息</x:v>
+        <x:v>苏纳光电</x:v>
       </x:c>
       <x:c r="C6" s="4" t="str">
-        <x:v>航天/军工信息化/软件</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>央企子公司/高新技术企业</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
-        <x:v>北京、杭州、西安</x:v>
+        <x:v>苏州、上海</x:v>
       </x:c>
       <x:c r="F6" s="4" t="str">
-        <x:v>AI专项/提前批</x:v>
+        <x:v>提前批/Open Day</x:v>
       </x:c>
       <x:c r="G6" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H6" s="4" t="str">
-        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
-      </x:c>
-      <x:c r="I6" s="15" t="str">
-        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
+        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
+      </x:c>
+      <x:c r="I6" s="17" t="str">
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="J6" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -805,51 +802,51 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L6" s="4" t="str">
-        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
+        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
       </x:c>
       <x:c r="M6" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N6" s="4" t="str">
-        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
-      </x:c>
-      <x:c r="O6" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P6" s="14" t="str">
-        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
-      </x:c>
-      <x:c r="Q6" s="4" t="n">
-        <x:v>46232</x:v>
+        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
+      </x:c>
+      <x:c r="O6" s="17" t="str">
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+      </x:c>
+      <x:c r="P6" s="15" t="str">
+        <x:v>A-企业官方校园招聘系统已核验</x:v>
+      </x:c>
+      <x:c r="Q6" s="4" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>卡尔动力</x:v>
+        <x:v>特斯拉中国</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
-        <x:v>自动驾驶/智能汽车</x:v>
+        <x:v>新能源汽车/智能制造</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>外资/上市</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>北京、上海、天津等</x:v>
+        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
-      </x:c>
-      <x:c r="I7" s="15" t="str">
-        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
+        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
+      </x:c>
+      <x:c r="I7" s="17" t="str">
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -858,104 +855,104 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L7" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
+        <x:v>本轮新确认；企业官方职位页已核验</x:v>
       </x:c>
       <x:c r="M7" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N7" s="4" t="str">
-        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
-      </x:c>
-      <x:c r="O7" s="15" t="str">
-        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
-      </x:c>
-      <x:c r="P7" s="16" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
-      </x:c>
-      <x:c r="Q7" s="4" t="n">
-        <x:v>46230</x:v>
+        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
+      </x:c>
+      <x:c r="O7" s="17" t="str">
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
+      </x:c>
+      <x:c r="P7" s="15" t="str">
+        <x:v>A-企业官方职位页已核验</x:v>
+      </x:c>
+      <x:c r="Q7" s="4" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="4" t="str">
-        <x:v>2026-07-25</x:v>
-      </x:c>
-      <x:c r="B8" s="4" t="str">
-        <x:v>深信服-X-STAR顶尖人才计划</x:v>
-      </x:c>
-      <x:c r="C8" s="4" t="str">
-        <x:v>网络安全/云计算/软件</x:v>
-      </x:c>
-      <x:c r="D8" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E8" s="4" t="str">
-        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F8" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
-      </x:c>
-      <x:c r="G8" s="4" t="str">
-        <x:v>顶尖人才，本硕博按岗位要求</x:v>
-      </x:c>
-      <x:c r="H8" s="4" t="str">
-        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
-      </x:c>
-      <x:c r="I8" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
-      </x:c>
-      <x:c r="J8" s="4" t="str">
-        <x:v>2026-09-25</x:v>
-      </x:c>
-      <x:c r="K8" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L8" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M8" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
-      </x:c>
-      <x:c r="N8" s="4" t="str">
-        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
-      </x:c>
-      <x:c r="O8" s="15" t="str">
-        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
-      </x:c>
-      <x:c r="P8" s="14" t="str">
-        <x:v>A-高校就业网含官方投递链接</x:v>
-      </x:c>
-      <x:c r="Q8" s="4" t="n">
-        <x:v>46230</x:v>
+      <x:c r="A8" s="14" t="str">
+        <x:v>不晚于2026-07-30</x:v>
+      </x:c>
+      <x:c r="B8" s="14" t="str">
+        <x:v>天健会计师事务所-暑期实习培训生</x:v>
+      </x:c>
+      <x:c r="C8" s="14" t="str">
+        <x:v>会计审计/专业服务</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="str">
+        <x:v>会计师事务所</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="str">
+        <x:v>上海等，以职位页为准</x:v>
+      </x:c>
+      <x:c r="F8" s="14" t="str">
+        <x:v>暑期实习/培训生</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str">
+        <x:v>财务审计暑期实习培训生</x:v>
+      </x:c>
+      <x:c r="I8" s="16" t="str">
+        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
+      </x:c>
+      <x:c r="J8" s="14" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K8" s="14" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L8" s="14" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M8" s="14" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N8" s="14" t="str">
+        <x:v>公开公告显示7月31日截止；具体办公地点、专业要求和实习安排以天健招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O8" s="16" t="str">
+        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
+      </x:c>
+      <x:c r="P8" s="15" t="str">
+        <x:v>A-企业官方招聘入口已核验</x:v>
+      </x:c>
+      <x:c r="Q8" s="14" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>希夕智能</x:v>
+        <x:v>西安紫光国芯半导体</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
-        <x:v>机器人/智能制造</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
         <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>西安、上海、成都</x:v>
       </x:c>
       <x:c r="F9" s="4" t="str">
         <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
-        <x:v>2027届本科及以上</x:v>
+        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
-      </x:c>
-      <x:c r="I9" s="15" t="str">
-        <x:v>https://sunseed.zhiye.com/jobs</x:v>
+        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
+      </x:c>
+      <x:c r="I9" s="17" t="str">
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
       </x:c>
       <x:c r="J9" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -964,157 +961,157 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L9" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
+        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
       </x:c>
       <x:c r="M9" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N9" s="4" t="str">
-        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
-      </x:c>
-      <x:c r="O9" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
-      </x:c>
-      <x:c r="P9" s="16" t="str">
-        <x:v>B-高校就业平台转载企业来源</x:v>
-      </x:c>
-      <x:c r="Q9" s="4" t="n">
-        <x:v>46230</x:v>
+        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
+      </x:c>
+      <x:c r="O9" s="17" t="str">
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
+      </x:c>
+      <x:c r="P9" s="15" t="str">
+        <x:v>A-企业官方招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q9" s="4" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="4" t="str">
-        <x:v>不晚于2026-07-24</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B10" s="4" t="str">
-        <x:v>中国兵器工业集团</x:v>
+        <x:v>新大陆自动识别</x:v>
       </x:c>
       <x:c r="C10" s="4" t="str">
-        <x:v>军工/高端装备</x:v>
+        <x:v>计算机视觉/智能硬件</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/上市公司子公司</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
+        <x:v>福州总部及全国/海外岗位</x:v>
       </x:c>
       <x:c r="F10" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
-      </x:c>
-      <x:c r="I10" s="15" t="str">
-        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
+        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
+      </x:c>
+      <x:c r="I10" s="17" t="str">
+        <x:v>https://nlscan.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J10" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K10" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L10" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
       </x:c>
       <x:c r="M10" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N10" s="4" t="str">
-        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
-      </x:c>
-      <x:c r="O10" s="15" t="str">
-        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
-      </x:c>
-      <x:c r="P10" s="16" t="str">
-        <x:v>B-公开招聘公告/集团入口</x:v>
-      </x:c>
-      <x:c r="Q10" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
+      </x:c>
+      <x:c r="O10" s="17" t="str">
+        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
+      </x:c>
+      <x:c r="P10" s="15" t="str">
+        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
+      </x:c>
+      <x:c r="Q10" s="4" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="4" t="str">
-        <x:v>2026-07-23</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B11" s="4" t="str">
-        <x:v>禾迈股份</x:v>
+        <x:v>影石Insta360</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
-        <x:v>光伏/电力电子</x:v>
+        <x:v>消费电子/智能影像</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>杭州等，以岗位页为准</x:v>
+        <x:v>深圳、上海、珠海</x:v>
       </x:c>
       <x:c r="F11" s="4" t="str">
-        <x:v>研发类提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
-      </x:c>
-      <x:c r="I11" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
+        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+      </x:c>
+      <x:c r="I11" s="17" t="str">
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-31</x:v>
       </x:c>
       <x:c r="K11" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L11" s="4" t="str">
-        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
+        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="M11" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N11" s="4" t="str">
-        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
-      </x:c>
-      <x:c r="O11" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
-      </x:c>
-      <x:c r="P11" s="16" t="str">
-        <x:v>B-高校就业网转载企业公告</x:v>
-      </x:c>
-      <x:c r="Q11" s="4" t="n">
-        <x:v>46230</x:v>
+        <x:v>岗位城市和具体职位以影石Insta360官方招聘页为准；公开信息标注10月31日，投递前再次确认职位状态。</x:v>
+      </x:c>
+      <x:c r="O11" s="17" t="str">
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
+      </x:c>
+      <x:c r="P11" s="15" t="str">
+        <x:v>A-企业官方招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q11" s="4" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="4" t="str">
-        <x:v>2026-07-23</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>极客未来</x:v>
+        <x:v>兆易创新</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>四川、重庆、广东</x:v>
+        <x:v>北京、上海、武汉、合肥等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F12" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
-      </x:c>
-      <x:c r="I12" s="15" t="str">
-        <x:v>https://geek3.zhiye.com/campus/</x:v>
+        <x:v>芯片设计、验证、嵌入式、软件、应用、测试及职能岗位</x:v>
+      </x:c>
+      <x:c r="I12" s="17" t="str">
+        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
       </x:c>
       <x:c r="J12" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1123,261 +1120,263 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L12" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
+        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="M12" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N12" s="4" t="str">
-        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
-      </x:c>
-      <x:c r="O12" s="15" t="str">
-        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
-      </x:c>
-      <x:c r="P12" s="16" t="str">
-        <x:v>B-高校就业网公告+公开招聘页面</x:v>
-      </x:c>
-      <x:c r="Q12" s="4" t="n">
-        <x:v>46233</x:v>
+        <x:v>提前批岗位和城市以兆易创新官方加入我们页面为准，投递前确认职位仍开放。</x:v>
+      </x:c>
+      <x:c r="O12" s="17" t="str">
+        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
+      </x:c>
+      <x:c r="P12" s="15" t="str">
+        <x:v>A-企业官方招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q12" s="4" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B13" s="4" t="str">
-        <x:v>网易游戏雷火</x:v>
+        <x:v>中国航空发动机集团</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>航空发动机/军工</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>杭州、上海等，以岗位页为准</x:v>
+        <x:v>全国各院所及下属单位</x:v>
       </x:c>
       <x:c r="F13" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
-      </x:c>
-      <x:c r="I13" s="15" t="str">
-        <x:v>https://leihuo.163.com/campus/#/full</x:v>
+        <x:v>研发设计、工艺、试验、制造、材料、控制、软件及管理岗位</x:v>
+      </x:c>
+      <x:c r="I13" s="17" t="str">
+        <x:v>https://aecc.iguopin.com/notice2</x:v>
       </x:c>
       <x:c r="J13" s="4" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K13" s="4" t="str">
-        <x:v>部分岗位免笔试；部分可直通面试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L13" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>本轮新确认；集团官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="M13" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N13" s="4" t="str">
-        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
-      </x:c>
-      <x:c r="O13" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P13" s="14" t="str">
-        <x:v>A-官方招聘官网已核验</x:v>
-      </x:c>
-      <x:c r="Q13" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>各单位岗位和截止时间不同，需在中国航发招聘平台按单位和专业筛选。</x:v>
+      </x:c>
+      <x:c r="O13" s="17" t="str">
+        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/n2588350/c35693219/content.html</x:v>
+      </x:c>
+      <x:c r="P13" s="15" t="str">
+        <x:v>A-国资委公告与集团招聘平台交叉核验</x:v>
+      </x:c>
+      <x:c r="Q13" s="4" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B14" s="4" t="str">
-        <x:v>芯迈半导体</x:v>
+        <x:v>中粮资本-粮曦计划</x:v>
       </x:c>
       <x:c r="C14" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>金融/投资/资管</x:v>
       </x:c>
       <x:c r="D14" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企/金融控股</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>杭州、上海、深圳、成都</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F14" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>培养计划/实习</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027-2029届硕士及以上，以公告要求为准</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
-      </x:c>
-      <x:c r="I14" s="15" t="str">
-        <x:v>https://www.silicon-magic.com/joinus</x:v>
+        <x:v>金融、投资、风险、运营、人力资源及综合管理方向</x:v>
+      </x:c>
+      <x:c r="I14" s="17" t="str">
+        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
       </x:c>
       <x:c r="J14" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K14" s="4" t="str">
-        <x:v>官方未说明；公开流程未列笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L14" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
       </x:c>
       <x:c r="M14" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N14" s="4" t="str">
-        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
-      </x:c>
-      <x:c r="O14" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P14" s="14" t="str">
-        <x:v>A-企业官网与公开公告已核验</x:v>
-      </x:c>
-      <x:c r="Q14" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>粮曦计划具体批次、面向人群和岗位以中粮资本官方加入我们页面及公告为准。</x:v>
+      </x:c>
+      <x:c r="O14" s="17" t="str">
+        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+      </x:c>
+      <x:c r="P14" s="15" t="str">
+        <x:v>A-企业官方招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q14" s="4" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B15" s="4" t="str">
-        <x:v>阿里巴巴-阿里星计划</x:v>
+        <x:v>中移九天人工智能科技</x:v>
       </x:c>
       <x:c r="C15" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>AI/软件/云计算</x:v>
       </x:c>
       <x:c r="D15" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企子公司</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>杭州、北京、上海、深圳等</x:v>
+        <x:v>北京、西安、广州、深圳</x:v>
       </x:c>
       <x:c r="F15" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批/超级实习生</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
-      </x:c>
-      <x:c r="I15" s="15" t="str">
-        <x:v>https://talent.alibaba.com/campus/</x:v>
+        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
+      </x:c>
+      <x:c r="I15" s="17" t="str">
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="J15" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-09-27</x:v>
       </x:c>
       <x:c r="K15" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L15" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
       </x:c>
       <x:c r="M15" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N15" s="4" t="str">
-        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
-      </x:c>
-      <x:c r="O15" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P15" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q15" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
+      </x:c>
+      <x:c r="O15" s="17" t="str">
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
+      </x:c>
+      <x:c r="P15" s="15" t="str">
+        <x:v>A-中国移动官方招聘平台已核验</x:v>
+      </x:c>
+      <x:c r="Q15" s="4" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
-        <x:v>贝恩公司</x:v>
+        <x:v>广州市卓越教育集团</x:v>
       </x:c>
       <x:c r="C16" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>北京、上海、香港等</x:v>
+        <x:v>广州等，以职位页为准</x:v>
       </x:c>
       <x:c r="F16" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>助理咨询顾问等</x:v>
-      </x:c>
-      <x:c r="I16" s="15" t="str">
-        <x:v>https://www.bain.com/careers/</x:v>
+        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+      </x:c>
+      <x:c r="I16" s="17" t="str">
+        <x:v>https://zyjob.hotjob.cn/</x:v>
       </x:c>
       <x:c r="J16" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-26</x:v>
       </x:c>
       <x:c r="K16" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L16" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
       </x:c>
       <x:c r="M16" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N16" s="4"/>
-      <x:c r="O16" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P16" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q16" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N16" s="4" t="str">
+        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
+      </x:c>
+      <x:c r="O16" s="17" t="str">
+        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
+      </x:c>
+      <x:c r="P16" s="15" t="str">
+        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
+      </x:c>
+      <x:c r="Q16" s="4" t="str">
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
+        <x:v>我乐家居</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>家居/消费品/智能制造</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>上海、北京等</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F17" s="4" t="str">
-        <x:v>顶尖技术专项/提前批</x:v>
+        <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
-      </x:c>
-      <x:c r="I17" s="15" t="str">
-        <x:v>https://jobs.bilibili.com/</x:v>
+        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
+      </x:c>
+      <x:c r="I17" s="17" t="str">
+        <x:v>https://olo-home.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J17" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1386,51 +1385,51 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L17" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
       </x:c>
       <x:c r="M17" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N17" s="4" t="str">
-        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
-      </x:c>
-      <x:c r="O17" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P17" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q17" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
+      </x:c>
+      <x:c r="O17" s="17" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P17" s="18" t="str">
+        <x:v>B-高校就业网转载企业来源</x:v>
+      </x:c>
+      <x:c r="Q17" s="4" t="str">
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="B18" s="4" t="str">
-        <x:v>东风汽车-全球博士人才</x:v>
+        <x:v>轩宇信息</x:v>
       </x:c>
       <x:c r="C18" s="4" t="str">
-        <x:v>汽车/央企</x:v>
+        <x:v>航天/军工信息化/软件</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>央企子公司/高新技术企业</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>武汉、广州、十堰及全国研发基地</x:v>
+        <x:v>北京、杭州、西安</x:v>
       </x:c>
       <x:c r="F18" s="4" t="str">
-        <x:v>博士专项</x:v>
+        <x:v>AI专项/提前批</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>2026届及以后博士</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
-      </x:c>
-      <x:c r="I18" s="15" t="str">
-        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
+        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
+      </x:c>
+      <x:c r="I18" s="17" t="str">
+        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
       </x:c>
       <x:c r="J18" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1439,51 +1438,51 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L18" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
       </x:c>
       <x:c r="M18" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N18" s="4" t="str">
-        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
-      </x:c>
-      <x:c r="O18" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P18" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q18" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
+      </x:c>
+      <x:c r="O18" s="17" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P18" s="15" t="str">
+        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
+      </x:c>
+      <x:c r="Q18" s="4" t="str">
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>度小满-博士后人才招聘</x:v>
+        <x:v>卡尔动力</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>金融科技</x:v>
+        <x:v>自动驾驶/智能汽车</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>北京、上海、天津等</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>博士后专项</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>2025/2026/2027届博士</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
-      </x:c>
-      <x:c r="I19" s="15" t="str">
-        <x:v>https://campus.duxiaoman.com/</x:v>
+        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
+      </x:c>
+      <x:c r="I19" s="17" t="str">
+        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1492,104 +1491,104 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L19" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
       </x:c>
       <x:c r="M19" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N19" s="4" t="str">
-        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
-      </x:c>
-      <x:c r="O19" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P19" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q19" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
+      </x:c>
+      <x:c r="O19" s="17" t="str">
+        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
+      </x:c>
+      <x:c r="P19" s="18" t="str">
+        <x:v>B-高校就业网转载企业来源</x:v>
+      </x:c>
+      <x:c r="Q19" s="4" t="str">
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
-        <x:v>多益网络</x:v>
+        <x:v>深信服-X-STAR顶尖人才计划</x:v>
       </x:c>
       <x:c r="C20" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>网络安全/云计算/软件</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>广州、武汉、成都等</x:v>
+        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>顶尖人才，本硕博按岗位要求</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>程序、策划、美术、运营、市场及职能</x:v>
-      </x:c>
-      <x:c r="I20" s="15" t="str">
-        <x:v>https://www.duoyi.com/job/</x:v>
+        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
+      </x:c>
+      <x:c r="I20" s="17" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-09-25</x:v>
       </x:c>
       <x:c r="K20" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L20" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M20" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N20" s="4" t="str">
-        <x:v>岗位可能按城市提前关闭。</x:v>
-      </x:c>
-      <x:c r="O20" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P20" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q20" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
+      </x:c>
+      <x:c r="O20" s="17" t="str">
+        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
+      </x:c>
+      <x:c r="P20" s="15" t="str">
+        <x:v>A-高校就业网含官方投递链接</x:v>
+      </x:c>
+      <x:c r="Q20" s="4" t="str">
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B21" s="4" t="str">
-        <x:v>海天集团-高潜专项</x:v>
+        <x:v>希夕智能</x:v>
       </x:c>
       <x:c r="C21" s="4" t="str">
-        <x:v>工业制造</x:v>
+        <x:v>机器人/智能制造</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>宁波及全国基地</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F21" s="4" t="str">
-        <x:v>高潜人才专项/提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科及以上</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
-      </x:c>
-      <x:c r="I21" s="15" t="str">
-        <x:v>https://www.haitian.com/careers/</x:v>
+        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
+      </x:c>
+      <x:c r="I21" s="17" t="str">
+        <x:v>https://sunseed.zhiye.com/jobs</x:v>
       </x:c>
       <x:c r="J21" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1598,228 +1597,234 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L21" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
       </x:c>
       <x:c r="M21" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N21" s="4" t="str">
-        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
-      </x:c>
-      <x:c r="O21" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P21" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q21" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
+      </x:c>
+      <x:c r="O21" s="17" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
+      </x:c>
+      <x:c r="P21" s="18" t="str">
+        <x:v>B-高校就业平台转载企业来源</x:v>
+      </x:c>
+      <x:c r="Q21" s="4" t="str">
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>不晚于2026-07-24</x:v>
       </x:c>
       <x:c r="B22" s="4" t="str">
-        <x:v>赫力昂-销售先锋计划</x:v>
+        <x:v>中国兵器工业集团</x:v>
       </x:c>
       <x:c r="C22" s="4" t="str">
-        <x:v>消费健康/医药</x:v>
+        <x:v>军工/高端装备</x:v>
       </x:c>
       <x:c r="D22" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>全国重点城市</x:v>
+        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
       </x:c>
       <x:c r="F22" s="4" t="str">
-        <x:v>管培/销售专项</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>医药及消费健康销售、商业运营方向</x:v>
-      </x:c>
-      <x:c r="I22" s="15" t="str">
-        <x:v>https://careers.haleon.com/</x:v>
+        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
+      </x:c>
+      <x:c r="I22" s="17" t="str">
+        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
       </x:c>
       <x:c r="J22" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K22" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L22" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M22" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N22" s="4"/>
-      <x:c r="O22" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P22" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q22" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="N22" s="4" t="str">
+        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
+      </x:c>
+      <x:c r="O22" s="17" t="str">
+        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
+      </x:c>
+      <x:c r="P22" s="18" t="str">
+        <x:v>B-公开招聘公告/集团入口</x:v>
+      </x:c>
+      <x:c r="Q22" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B23" s="4" t="str">
-        <x:v>虹软科技</x:v>
+        <x:v>禾迈股份</x:v>
       </x:c>
       <x:c r="C23" s="4" t="str">
-        <x:v>计算机视觉/软件</x:v>
+        <x:v>光伏/电力电子</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>杭州、上海、南京等</x:v>
+        <x:v>杭州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F23" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>研发类提前批</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
-      </x:c>
-      <x:c r="I23" s="15" t="str">
-        <x:v>https://hr.arcsoft.com.cn/</x:v>
+        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
+      </x:c>
+      <x:c r="I23" s="17" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
       </x:c>
       <x:c r="J23" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K23" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L23" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
       </x:c>
       <x:c r="M23" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N23" s="4"/>
-      <x:c r="O23" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P23" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q23" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N23" s="4" t="str">
+        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
+      </x:c>
+      <x:c r="O23" s="17" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
+      </x:c>
+      <x:c r="P23" s="18" t="str">
+        <x:v>B-高校就业网转载企业公告</x:v>
+      </x:c>
+      <x:c r="Q23" s="4" t="str">
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B24" s="4" t="str">
-        <x:v>汇川技术</x:v>
+        <x:v>极客未来</x:v>
       </x:c>
       <x:c r="C24" s="4" t="str">
-        <x:v>工业自动化/新能源</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D24" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
+        <x:v>四川、重庆、广东</x:v>
       </x:c>
       <x:c r="F24" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
-      </x:c>
-      <x:c r="I24" s="15" t="str">
-        <x:v>https://career.inovance.com/</x:v>
+        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+      </x:c>
+      <x:c r="I24" s="17" t="str">
+        <x:v>https://geek3.zhiye.com/campus/</x:v>
       </x:c>
       <x:c r="J24" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K24" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L24" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
       </x:c>
       <x:c r="M24" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N24" s="4"/>
-      <x:c r="O24" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P24" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q24" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="N24" s="4" t="str">
+        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
+      </x:c>
+      <x:c r="O24" s="17" t="str">
+        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
+      </x:c>
+      <x:c r="P24" s="18" t="str">
+        <x:v>B-高校就业网公告+公开招聘页面</x:v>
+      </x:c>
+      <x:c r="Q24" s="4" t="str">
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
       <x:c r="A25" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="B25" s="4" t="str">
-        <x:v>伽利略-星途星锐计划</x:v>
+        <x:v>安永EY</x:v>
       </x:c>
       <x:c r="C25" s="4" t="str">
-        <x:v>科技/综合</x:v>
+        <x:v>会计审计/咨询/专业服务</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>外资/专业服务机构</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>以项目职位页为准</x:v>
+        <x:v>中国内地多地，以职位页为准</x:v>
       </x:c>
       <x:c r="F25" s="4" t="str">
-        <x:v>人才专项</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>以官方项目页为准</x:v>
-      </x:c>
-      <x:c r="I25" s="20" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
+      </x:c>
+      <x:c r="I25" s="17" t="str">
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
       </x:c>
       <x:c r="J25" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026年10月（具体日期未公布）</x:v>
       </x:c>
       <x:c r="K25" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；官方流程包含在线测评</x:v>
       </x:c>
       <x:c r="L25" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
       </x:c>
       <x:c r="M25" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N25" s="4" t="str">
-        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
-      </x:c>
-      <x:c r="O25" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P25" s="17" t="str">
-        <x:v>C-主体与入口需二次确认</x:v>
-      </x:c>
-      <x:c r="Q25" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
+      </x:c>
+      <x:c r="O25" s="17" t="str">
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
+      </x:c>
+      <x:c r="P25" s="15" t="str">
+        <x:v>A-企业官方校招网站与职位页已核验</x:v>
+      </x:c>
+      <x:c r="Q25" s="4" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="54" customHeight="1">
@@ -1827,52 +1832,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B26" s="4" t="str">
-        <x:v>京东-TET管理培训生</x:v>
+        <x:v>阿里巴巴-阿里星计划</x:v>
       </x:c>
       <x:c r="C26" s="4" t="str">
-        <x:v>互联网/零售</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D26" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>北京及业务所在城市</x:v>
+        <x:v>杭州、北京、上海、深圳等</x:v>
       </x:c>
       <x:c r="F26" s="4" t="str">
-        <x:v>管培生专项/提前批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
-      </x:c>
-      <x:c r="I26" s="15" t="str">
-        <x:v>https://campus.jd.com/</x:v>
+        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
+      </x:c>
+      <x:c r="I26" s="17" t="str">
+        <x:v>https://talent.alibaba.com/campus/</x:v>
       </x:c>
       <x:c r="J26" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K26" s="4" t="str">
-        <x:v>含测评，笔试以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L26" s="4" t="str">
-        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M26" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N26" s="4" t="str">
-        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
-      </x:c>
-      <x:c r="O26" s="15" t="str">
-        <x:v>https://campus.jd.com/#/</x:v>
-      </x:c>
-      <x:c r="P26" s="14" t="str">
-        <x:v>A-企业官网校招页面已核验</x:v>
-      </x:c>
-      <x:c r="Q26" s="4" t="n">
-        <x:v>46233</x:v>
+        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
+      </x:c>
+      <x:c r="O26" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P26" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q26" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="54" customHeight="1">
@@ -1880,34 +1885,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B27" s="4" t="str">
-        <x:v>科大讯飞-飞凡计划</x:v>
+        <x:v>贝恩公司</x:v>
       </x:c>
       <x:c r="C27" s="4" t="str">
-        <x:v>AI/软件</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D27" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
+        <x:v>北京、上海、香港等</x:v>
       </x:c>
       <x:c r="F27" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>2026/2027届</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
-      </x:c>
-      <x:c r="I27" s="15" t="str">
-        <x:v>https://campus.iflytek.com/</x:v>
+        <x:v>助理咨询顾问等</x:v>
+      </x:c>
+      <x:c r="I27" s="17" t="str">
+        <x:v>https://www.bain.com/careers/</x:v>
       </x:c>
       <x:c r="J27" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K27" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L27" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -1915,17 +1920,15 @@
       <x:c r="M27" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N27" s="4" t="str">
-        <x:v>专项岗位与常规校招可能并行。</x:v>
-      </x:c>
-      <x:c r="O27" s="15" t="str">
+      <x:c r="N27" s="4" t="str"/>
+      <x:c r="O27" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P27" s="17" t="str">
+      <x:c r="P27" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q27" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q27" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="54" customHeight="1">
@@ -1933,28 +1936,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B28" s="4" t="str">
-        <x:v>理想汽车</x:v>
+        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
       </x:c>
       <x:c r="C28" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="D28" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>北京、上海、常州等</x:v>
+        <x:v>上海、北京等</x:v>
       </x:c>
       <x:c r="F28" s="4" t="str">
-        <x:v>暑期实习转正通道</x:v>
+        <x:v>顶尖技术专项/提前批</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
-      </x:c>
-      <x:c r="I28" s="15" t="str">
-        <x:v>https://career.lixiang.com/campus</x:v>
+        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
+      </x:c>
+      <x:c r="I28" s="17" t="str">
+        <x:v>https://jobs.bilibili.com/</x:v>
       </x:c>
       <x:c r="J28" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1969,16 +1972,16 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N28" s="4" t="str">
-        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
-      </x:c>
-      <x:c r="O28" s="15" t="str">
+        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
+      </x:c>
+      <x:c r="O28" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P28" s="17" t="str">
+      <x:c r="P28" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q28" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q28" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="54" customHeight="1">
@@ -1986,50 +1989,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B29" s="4" t="str">
-        <x:v>莉莉丝游戏</x:v>
+        <x:v>东风汽车-全球博士人才</x:v>
       </x:c>
       <x:c r="C29" s="4" t="str">
-        <x:v>游戏</x:v>
+        <x:v>汽车/央企</x:v>
       </x:c>
       <x:c r="D29" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>武汉、广州、十堰及全国研发基地</x:v>
       </x:c>
       <x:c r="F29" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>博士专项</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026届及以后博士</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
-      </x:c>
-      <x:c r="I29" s="15" t="str">
-        <x:v>https://campus.lilith.com/</x:v>
+        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
+      </x:c>
+      <x:c r="I29" s="17" t="str">
+        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
       </x:c>
       <x:c r="J29" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K29" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L29" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M29" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N29" s="4"/>
-      <x:c r="O29" s="15" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N29" s="4" t="str">
+        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
+      </x:c>
+      <x:c r="O29" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P29" s="17" t="str">
+      <x:c r="P29" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q29" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q29" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="54" customHeight="1">
@@ -2037,34 +2042,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B30" s="4" t="str">
-        <x:v>麦肯锡</x:v>
+        <x:v>度小满-博士后人才招聘</x:v>
       </x:c>
       <x:c r="C30" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>金融科技</x:v>
       </x:c>
       <x:c r="D30" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F30" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>博士后专项</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2025/2026/2027届博士</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>商业分析师、咨询及专业岗位</x:v>
-      </x:c>
-      <x:c r="I30" s="15" t="str">
-        <x:v>https://www.mckinsey.com/careers</x:v>
+        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
+      </x:c>
+      <x:c r="I30" s="17" t="str">
+        <x:v>https://campus.duxiaoman.com/</x:v>
       </x:c>
       <x:c r="J30" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K30" s="4" t="str">
-        <x:v>通常含测评/案例面试；以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L30" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2072,15 +2077,17 @@
       <x:c r="M30" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N30" s="4"/>
-      <x:c r="O30" s="15" t="str">
+      <x:c r="N30" s="4" t="str">
+        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
+      </x:c>
+      <x:c r="O30" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P30" s="17" t="str">
+      <x:c r="P30" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q30" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q30" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="54" customHeight="1">
@@ -2088,16 +2095,16 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B31" s="4" t="str">
-        <x:v>拼多多</x:v>
+        <x:v>多益网络</x:v>
       </x:c>
       <x:c r="C31" s="4" t="str">
-        <x:v>互联网/电商</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D31" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>上海、广州等，以岗位页为准</x:v>
+        <x:v>广州、武汉、成都等</x:v>
       </x:c>
       <x:c r="F31" s="4" t="str">
         <x:v>提前批</x:v>
@@ -2106,16 +2113,16 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>技术、算法、产品、运营、商业分析等</x:v>
-      </x:c>
-      <x:c r="I31" s="15" t="str">
-        <x:v>https://careers.pinduoduo.com/campus/</x:v>
+        <x:v>程序、策划、美术、运营、市场及职能</x:v>
+      </x:c>
+      <x:c r="I31" s="17" t="str">
+        <x:v>https://www.duoyi.com/job/</x:v>
       </x:c>
       <x:c r="J31" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K31" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L31" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2124,16 +2131,16 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N31" s="4" t="str">
-        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
-      </x:c>
-      <x:c r="O31" s="15" t="str">
+        <x:v>岗位可能按城市提前关闭。</x:v>
+      </x:c>
+      <x:c r="O31" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P31" s="17" t="str">
+      <x:c r="P31" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q31" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q31" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="54" customHeight="1">
@@ -2141,34 +2148,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B32" s="4" t="str">
-        <x:v>启林投资</x:v>
+        <x:v>海天集团-高潜专项</x:v>
       </x:c>
       <x:c r="C32" s="4" t="str">
-        <x:v>量化金融/资管</x:v>
+        <x:v>工业制造</x:v>
       </x:c>
       <x:c r="D32" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>宁波及全国基地</x:v>
       </x:c>
       <x:c r="F32" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>高潜人才专项/提前批</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
-        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
-      </x:c>
-      <x:c r="I32" s="15" t="str">
-        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
+        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
+      </x:c>
+      <x:c r="I32" s="17" t="str">
+        <x:v>https://www.haitian.com/careers/</x:v>
       </x:c>
       <x:c r="J32" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K32" s="4" t="str">
-        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L32" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2177,16 +2184,16 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N32" s="4" t="str">
-        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
-      </x:c>
-      <x:c r="O32" s="15" t="str">
+        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
+      </x:c>
+      <x:c r="O32" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P32" s="17" t="str">
+      <x:c r="P32" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q32" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q32" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="54" customHeight="1">
@@ -2194,28 +2201,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B33" s="4" t="str">
-        <x:v>商汤科技-无限原力计划</x:v>
+        <x:v>赫力昂-销售先锋计划</x:v>
       </x:c>
       <x:c r="C33" s="4" t="str">
-        <x:v>AI/计算机视觉</x:v>
+        <x:v>消费健康/医药</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
-        <x:v>上海、北京、深圳、杭州等</x:v>
+        <x:v>全国重点城市</x:v>
       </x:c>
       <x:c r="F33" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>管培/销售专项</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
-        <x:v>2027/2028届</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H33" s="4" t="str">
-        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
-      </x:c>
-      <x:c r="I33" s="15" t="str">
-        <x:v>https://joinus.sensetime.com/</x:v>
+        <x:v>医药及消费健康销售、商业运营方向</x:v>
+      </x:c>
+      <x:c r="I33" s="17" t="str">
+        <x:v>https://careers.haleon.com/</x:v>
       </x:c>
       <x:c r="J33" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2229,17 +2236,15 @@
       <x:c r="M33" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N33" s="4" t="str">
-        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
-      </x:c>
-      <x:c r="O33" s="15" t="str">
+      <x:c r="N33" s="4" t="str"/>
+      <x:c r="O33" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P33" s="17" t="str">
+      <x:c r="P33" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q33" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q33" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="54" customHeight="1">
@@ -2247,52 +2252,50 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B34" s="4" t="str">
-        <x:v>腾讯-青云计划</x:v>
+        <x:v>虹软科技</x:v>
       </x:c>
       <x:c r="C34" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>计算机视觉/软件</x:v>
       </x:c>
       <x:c r="D34" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
-        <x:v>深圳、北京、上海等</x:v>
+        <x:v>杭州、上海、南京等</x:v>
       </x:c>
       <x:c r="F34" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G34" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H34" s="4" t="str">
-        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
-      </x:c>
-      <x:c r="I34" s="15" t="str">
-        <x:v>https://join.qq.com/</x:v>
+        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
+      </x:c>
+      <x:c r="I34" s="17" t="str">
+        <x:v>https://hr.arcsoft.com.cn/</x:v>
       </x:c>
       <x:c r="J34" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K34" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L34" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M34" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N34" s="4" t="str">
-        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
-      </x:c>
-      <x:c r="O34" s="15" t="str">
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N34" s="4" t="str"/>
+      <x:c r="O34" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P34" s="17" t="str">
+      <x:c r="P34" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q34" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q34" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="54" customHeight="1">
@@ -2300,34 +2303,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B35" s="4" t="str">
-        <x:v>天锐星通</x:v>
+        <x:v>汇川技术</x:v>
       </x:c>
       <x:c r="C35" s="4" t="str">
-        <x:v>卫星通信/相控阵</x:v>
+        <x:v>工业自动化/新能源</x:v>
       </x:c>
       <x:c r="D35" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E35" s="4" t="str">
-        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
+        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
       </x:c>
       <x:c r="F35" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H35" s="4" t="str">
-        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
-      </x:c>
-      <x:c r="I35" s="15" t="str">
-        <x:v>https://www.tianruixing.com/</x:v>
+        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
+      </x:c>
+      <x:c r="I35" s="17" t="str">
+        <x:v>https://career.inovance.com/</x:v>
       </x:c>
       <x:c r="J35" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K35" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L35" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2335,17 +2338,15 @@
       <x:c r="M35" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N35" s="4" t="str">
-        <x:v>官网入口与具体岗位需投前复核。</x:v>
-      </x:c>
-      <x:c r="O35" s="15" t="str">
+      <x:c r="N35" s="4" t="str"/>
+      <x:c r="O35" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P35" s="17" t="str">
+      <x:c r="P35" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q35" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q35" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="54" customHeight="1">
@@ -2353,28 +2354,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B36" s="4" t="str">
-        <x:v>小鹏集团</x:v>
+        <x:v>伽利略-星途星锐计划</x:v>
       </x:c>
       <x:c r="C36" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>科技/综合</x:v>
       </x:c>
       <x:c r="D36" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
-        <x:v>广州、北京、上海、深圳、武汉等</x:v>
+        <x:v>以项目职位页为准</x:v>
       </x:c>
       <x:c r="F36" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
+        <x:v>人才专项</x:v>
       </x:c>
       <x:c r="G36" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H36" s="4" t="str">
-        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
-      </x:c>
-      <x:c r="I36" s="15" t="str">
-        <x:v>https://join.xiaopeng.com/campus</x:v>
+        <x:v>以官方项目页为准</x:v>
+      </x:c>
+      <x:c r="I36" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J36" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2389,16 +2390,16 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N36" s="4" t="str">
-        <x:v>营销服与技术岗位可能分项目发布。</x:v>
-      </x:c>
-      <x:c r="O36" s="15" t="str">
+        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
+      </x:c>
+      <x:c r="O36" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P36" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q36" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P36" s="19" t="str">
+        <x:v>C-主体与入口需二次确认</x:v>
+      </x:c>
+      <x:c r="Q36" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="54" customHeight="1">
@@ -2406,50 +2407,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B37" s="4" t="str">
-        <x:v>芯动科技</x:v>
+        <x:v>京东-TET管理培训生</x:v>
       </x:c>
       <x:c r="C37" s="4" t="str">
-        <x:v>半导体/IP设计</x:v>
+        <x:v>互联网/零售</x:v>
       </x:c>
       <x:c r="D37" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E37" s="4" t="str">
-        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
+        <x:v>北京及业务所在城市</x:v>
       </x:c>
       <x:c r="F37" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>管培生专项/提前批</x:v>
       </x:c>
       <x:c r="G37" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
-        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
-      </x:c>
-      <x:c r="I37" s="15" t="str">
-        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
+        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
+      </x:c>
+      <x:c r="I37" s="17" t="str">
+        <x:v>https://campus.jd.com/</x:v>
       </x:c>
       <x:c r="J37" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K37" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>含测评，笔试以通知为准</x:v>
       </x:c>
       <x:c r="L37" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
       </x:c>
       <x:c r="M37" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N37" s="4"/>
-      <x:c r="O37" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P37" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q37" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N37" s="4" t="str">
+        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
+      </x:c>
+      <x:c r="O37" s="17" t="str">
+        <x:v>https://campus.jd.com/#/</x:v>
+      </x:c>
+      <x:c r="P37" s="15" t="str">
+        <x:v>A-企业官网校招页面已核验</x:v>
+      </x:c>
+      <x:c r="Q37" s="4" t="str">
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="54" customHeight="1">
@@ -2457,52 +2460,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B38" s="4" t="str">
-        <x:v>新易盛</x:v>
+        <x:v>科大讯飞-飞凡计划</x:v>
       </x:c>
       <x:c r="C38" s="4" t="str">
-        <x:v>光通信/半导体</x:v>
+        <x:v>AI/软件</x:v>
       </x:c>
       <x:c r="D38" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E38" s="4" t="str">
-        <x:v>成都、苏州等，以岗位页为准</x:v>
+        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
       </x:c>
       <x:c r="F38" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026/2027届</x:v>
       </x:c>
       <x:c r="H38" s="4" t="str">
-        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
-      </x:c>
-      <x:c r="I38" s="15" t="str">
-        <x:v>https://www.eoptolink.com/</x:v>
+        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
+      </x:c>
+      <x:c r="I38" s="17" t="str">
+        <x:v>https://campus.iflytek.com/</x:v>
       </x:c>
       <x:c r="J38" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K38" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L38" s="4" t="str">
-        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M38" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N38" s="4" t="str">
-        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
-      </x:c>
-      <x:c r="O38" s="15" t="str">
+        <x:v>专项岗位与常规校招可能并行。</x:v>
+      </x:c>
+      <x:c r="O38" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P38" s="16" t="str">
-        <x:v>B-高校/招聘平台转载，投前复核</x:v>
-      </x:c>
-      <x:c r="Q38" s="4" t="n">
-        <x:v>46230</x:v>
+      <x:c r="P38" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q38" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="54" customHeight="1">
@@ -2510,34 +2513,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B39" s="4" t="str">
-        <x:v>元戎启行</x:v>
+        <x:v>理想汽车</x:v>
       </x:c>
       <x:c r="C39" s="4" t="str">
-        <x:v>自动驾驶</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D39" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
-        <x:v>深圳、北京等</x:v>
+        <x:v>北京、上海、常州等</x:v>
       </x:c>
       <x:c r="F39" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>暑期实习转正通道</x:v>
       </x:c>
       <x:c r="G39" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H39" s="4" t="str">
-        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
-      </x:c>
-      <x:c r="I39" s="15" t="str">
-        <x:v>https://www.deeproute.ai/join-us</x:v>
+        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
+      </x:c>
+      <x:c r="I39" s="17" t="str">
+        <x:v>https://career.lixiang.com/campus</x:v>
       </x:c>
       <x:c r="J39" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K39" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L39" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2545,15 +2548,17 @@
       <x:c r="M39" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N39" s="4"/>
-      <x:c r="O39" s="15" t="str">
+      <x:c r="N39" s="4" t="str">
+        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
+      </x:c>
+      <x:c r="O39" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P39" s="17" t="str">
+      <x:c r="P39" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q39" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q39" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="54" customHeight="1">
@@ -2561,50 +2566,50 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B40" s="4" t="str">
-        <x:v>圆通速递</x:v>
+        <x:v>莉莉丝游戏</x:v>
       </x:c>
       <x:c r="C40" s="4" t="str">
-        <x:v>物流/供应链</x:v>
+        <x:v>游戏</x:v>
       </x:c>
       <x:c r="D40" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E40" s="4" t="str">
-        <x:v>上海及全国网络</x:v>
+        <x:v>上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F40" s="4" t="str">
-        <x:v>正式批/校招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G40" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H40" s="4" t="str">
-        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
-      </x:c>
-      <x:c r="I40" s="15" t="str">
-        <x:v>https://hr.yto.net.cn/</x:v>
+        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
+      </x:c>
+      <x:c r="I40" s="17" t="str">
+        <x:v>https://campus.lilith.com/</x:v>
       </x:c>
       <x:c r="J40" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="K40" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L40" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M40" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N40" s="4"/>
-      <x:c r="O40" s="15" t="str">
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N40" s="4" t="str"/>
+      <x:c r="O40" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P40" s="17" t="str">
+      <x:c r="P40" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q40" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q40" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="54" customHeight="1">
@@ -2612,16 +2617,16 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B41" s="4" t="str">
-        <x:v>长亭科技</x:v>
+        <x:v>麦肯锡</x:v>
       </x:c>
       <x:c r="C41" s="4" t="str">
-        <x:v>网络安全</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D41" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E41" s="4" t="str">
-        <x:v>北京、上海等，以岗位页为准</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F41" s="4" t="str">
         <x:v>正式批/秋招</x:v>
@@ -2630,16 +2635,16 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H41" s="4" t="str">
-        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
-      </x:c>
-      <x:c r="I41" s="15" t="str">
-        <x:v>https://job.chaitin.cn/</x:v>
+        <x:v>商业分析师、咨询及专业岗位</x:v>
+      </x:c>
+      <x:c r="I41" s="17" t="str">
+        <x:v>https://www.mckinsey.com/careers</x:v>
       </x:c>
       <x:c r="J41" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K41" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>通常含测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L41" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2647,15 +2652,15 @@
       <x:c r="M41" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N41" s="4"/>
-      <x:c r="O41" s="15" t="str">
+      <x:c r="N41" s="4" t="str"/>
+      <x:c r="O41" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P41" s="17" t="str">
+      <x:c r="P41" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q41" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q41" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="54" customHeight="1">
@@ -2663,28 +2668,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B42" s="4" t="str">
-        <x:v>智元机器人-优才计划</x:v>
+        <x:v>拼多多</x:v>
       </x:c>
       <x:c r="C42" s="4" t="str">
-        <x:v>具身智能/机器人</x:v>
+        <x:v>互联网/电商</x:v>
       </x:c>
       <x:c r="D42" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E42" s="4" t="str">
-        <x:v>上海、北京、深圳等</x:v>
+        <x:v>上海、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F42" s="4" t="str">
-        <x:v>优才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G42" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H42" s="4" t="str">
-        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
-      </x:c>
-      <x:c r="I42" s="15" t="str">
-        <x:v>https://www.agibot.com/recruit</x:v>
+        <x:v>技术、算法、产品、运营、商业分析等</x:v>
+      </x:c>
+      <x:c r="I42" s="17" t="str">
+        <x:v>https://careers.pinduoduo.com/campus/</x:v>
       </x:c>
       <x:c r="J42" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2698,15 +2703,17 @@
       <x:c r="M42" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N42" s="4"/>
-      <x:c r="O42" s="15" t="str">
+      <x:c r="N42" s="4" t="str">
+        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
+      </x:c>
+      <x:c r="O42" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P42" s="17" t="str">
+      <x:c r="P42" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q42" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q42" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="54" customHeight="1">
@@ -2714,34 +2721,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B43" s="4" t="str">
-        <x:v>中国电信天翼云-超级优才</x:v>
+        <x:v>启林投资</x:v>
       </x:c>
       <x:c r="C43" s="4" t="str">
-        <x:v>云计算/央企</x:v>
+        <x:v>量化金融/资管</x:v>
       </x:c>
       <x:c r="D43" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E43" s="4" t="str">
-        <x:v>北京、上海、广州、成都及全国机构</x:v>
+        <x:v>上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F43" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G43" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H43" s="4" t="str">
-        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
-      </x:c>
-      <x:c r="I43" s="15" t="str">
-        <x:v>https://www.ctyun.cn/about/recruit</x:v>
+        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
+      </x:c>
+      <x:c r="I43" s="17" t="str">
+        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
       </x:c>
       <x:c r="J43" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K43" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
       </x:c>
       <x:c r="L43" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2750,16 +2757,16 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N43" s="4" t="str">
-        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
-      </x:c>
-      <x:c r="O43" s="15" t="str">
+        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
+      </x:c>
+      <x:c r="O43" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P43" s="17" t="str">
+      <x:c r="P43" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q43" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q43" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="54" customHeight="1">
@@ -2767,31 +2774,31 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B44" s="4" t="str">
-        <x:v>中科光电</x:v>
+        <x:v>商汤科技-无限原力计划</x:v>
       </x:c>
       <x:c r="C44" s="4" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>AI/计算机视觉</x:v>
       </x:c>
       <x:c r="D44" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E44" s="4" t="str">
-        <x:v>以职位公告为准</x:v>
+        <x:v>上海、北京、深圳、杭州等</x:v>
       </x:c>
       <x:c r="F44" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G44" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027/2028届</x:v>
       </x:c>
       <x:c r="H44" s="4" t="str">
-        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
-      </x:c>
-      <x:c r="I44" s="15" t="str">
-        <x:v>https://job.cn-amd.com/</x:v>
+        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
+      </x:c>
+      <x:c r="I44" s="17" t="str">
+        <x:v>https://joinus.sensetime.com/</x:v>
       </x:c>
       <x:c r="J44" s="4" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K44" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -2800,19 +2807,19 @@
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M44" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N44" s="4" t="str">
-        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
-      </x:c>
-      <x:c r="O44" s="15" t="str">
+        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
+      </x:c>
+      <x:c r="O44" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P44" s="17" t="str">
-        <x:v>C-名称需二次确认</x:v>
-      </x:c>
-      <x:c r="Q44" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P44" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q44" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="54" customHeight="1">
@@ -2820,16 +2827,16 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B45" s="4" t="str">
-        <x:v>中兴微电子-未来领军计划</x:v>
+        <x:v>腾讯-青云计划</x:v>
       </x:c>
       <x:c r="C45" s="4" t="str">
-        <x:v>半导体/通信</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D45" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E45" s="4" t="str">
-        <x:v>深圳、西安、南京、上海等</x:v>
+        <x:v>深圳、北京、上海等</x:v>
       </x:c>
       <x:c r="F45" s="4" t="str">
         <x:v>顶尖人才专项/提前批</x:v>
@@ -2838,10 +2845,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H45" s="4" t="str">
-        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
-      </x:c>
-      <x:c r="I45" s="15" t="str">
-        <x:v>https://job.zte.com.cn/</x:v>
+        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
+      </x:c>
+      <x:c r="I45" s="17" t="str">
+        <x:v>https://join.qq.com/</x:v>
       </x:c>
       <x:c r="J45" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2856,120 +2863,122 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N45" s="4" t="str">
-        <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
-      </x:c>
-      <x:c r="O45" s="15" t="str">
+        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
+      </x:c>
+      <x:c r="O45" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P45" s="17" t="str">
+      <x:c r="P45" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q45" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q45" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="54" customHeight="1">
-      <x:c r="A46" s="16" t="str">
+      <x:c r="A46" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B46" s="16" t="str">
-        <x:v>字节跳动-AI产品经理早鸟通道</x:v>
-      </x:c>
-      <x:c r="C46" s="16" t="str">
-        <x:v>互联网/AI</x:v>
-      </x:c>
-      <x:c r="D46" s="16" t="str">
+      <x:c r="B46" s="4" t="str">
+        <x:v>天锐星通</x:v>
+      </x:c>
+      <x:c r="C46" s="4" t="str">
+        <x:v>卫星通信/相控阵</x:v>
+      </x:c>
+      <x:c r="D46" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E46" s="16" t="str">
-        <x:v>北京、上海、深圳</x:v>
-      </x:c>
-      <x:c r="F46" s="16" t="str">
-        <x:v>早鸟专项/提前批</x:v>
-      </x:c>
-      <x:c r="G46" s="16" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H46" s="16" t="str">
-        <x:v>AI产品经理、智能体及大模型产品方向</x:v>
-      </x:c>
-      <x:c r="I46" s="21" t="str">
-        <x:v>https://jobs.bytedance.com/campus/</x:v>
-      </x:c>
-      <x:c r="J46" s="16" t="str">
-        <x:v>2026-08-02</x:v>
-      </x:c>
-      <x:c r="K46" s="16" t="str">
-        <x:v>按岗位，未统一公布</x:v>
-      </x:c>
-      <x:c r="L46" s="16" t="str">
-        <x:v>3天内截止（2026-08-02）</x:v>
-      </x:c>
-      <x:c r="M46" s="16" t="str">
-        <x:v>P0-7天内截止</x:v>
-      </x:c>
-      <x:c r="N46" s="16" t="str">
-        <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
-      </x:c>
-      <x:c r="O46" s="21" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P46" s="16" t="str">
-        <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q46" s="16" t="n">
-        <x:v>46233</x:v>
+      <x:c r="E46" s="4" t="str">
+        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F46" s="4" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G46" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H46" s="4" t="str">
+        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
+      </x:c>
+      <x:c r="I46" s="17" t="str">
+        <x:v>https://www.tianruixing.com/</x:v>
+      </x:c>
+      <x:c r="J46" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K46" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L46" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M46" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N46" s="4" t="str">
+        <x:v>官网入口与具体岗位需投前复核。</x:v>
+      </x:c>
+      <x:c r="O46" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P46" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q46" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="54" customHeight="1">
       <x:c r="A47" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B47" s="4" t="str">
-        <x:v>BCG波士顿咨询</x:v>
+        <x:v>网易游戏雷火</x:v>
       </x:c>
       <x:c r="C47" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D47" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E47" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>杭州、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F47" s="4" t="str">
-        <x:v>正式批/中国区校招</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G47" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H47" s="4" t="str">
-        <x:v>咨询顾问及相关专业岗位</x:v>
-      </x:c>
-      <x:c r="I47" s="15" t="str">
-        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
+        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
+      </x:c>
+      <x:c r="I47" s="17" t="str">
+        <x:v>https://leihuo.163.com/campus/#/full</x:v>
       </x:c>
       <x:c r="J47" s="4" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="K47" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>部分岗位免笔试；部分可直通面试</x:v>
       </x:c>
       <x:c r="L47" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M47" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N47" s="4"/>
-      <x:c r="O47" s="15" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N47" s="4" t="str">
+        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
+      </x:c>
+      <x:c r="O47" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P47" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q47" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P47" s="15" t="str">
+        <x:v>A-官方招聘官网已核验</x:v>
+      </x:c>
+      <x:c r="Q47" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="54" customHeight="1">
@@ -2977,16 +2986,16 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B48" s="4" t="str">
-        <x:v>OPPO</x:v>
+        <x:v>小鹏集团</x:v>
       </x:c>
       <x:c r="C48" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D48" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E48" s="4" t="str">
-        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
+        <x:v>广州、北京、上海、深圳、武汉等</x:v>
       </x:c>
       <x:c r="F48" s="4" t="str">
         <x:v>全球校园招聘/正式批</x:v>
@@ -2995,10 +3004,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H48" s="4" t="str">
-        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
-      </x:c>
-      <x:c r="I48" s="15" t="str">
-        <x:v>https://careers.oppo.com/campus</x:v>
+        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
+      </x:c>
+      <x:c r="I48" s="17" t="str">
+        <x:v>https://join.xiaopeng.com/campus</x:v>
       </x:c>
       <x:c r="J48" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3013,16 +3022,16 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N48" s="4" t="str">
-        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
-      </x:c>
-      <x:c r="O48" s="15" t="str">
+        <x:v>营销服与技术岗位可能分项目发布。</x:v>
+      </x:c>
+      <x:c r="O48" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P48" s="17" t="str">
+      <x:c r="P48" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q48" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q48" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="54" customHeight="1">
@@ -3030,34 +3039,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B49" s="4" t="str">
-        <x:v>Tap4Fun</x:v>
+        <x:v>芯动科技</x:v>
       </x:c>
       <x:c r="C49" s="4" t="str">
-        <x:v>游戏</x:v>
+        <x:v>半导体/IP设计</x:v>
       </x:c>
       <x:c r="D49" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E49" s="4" t="str">
-        <x:v>成都等</x:v>
+        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
       </x:c>
       <x:c r="F49" s="4" t="str">
-        <x:v>实习转正通道</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G49" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H49" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
-      </x:c>
-      <x:c r="I49" s="15" t="str">
-        <x:v>https://www.tap4fun.com/careers</x:v>
+        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
+      </x:c>
+      <x:c r="I49" s="17" t="str">
+        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
       </x:c>
       <x:c r="J49" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K49" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L49" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3065,470 +3074,460 @@
       <x:c r="M49" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N49" s="4" t="str">
-        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
-      </x:c>
-      <x:c r="O49" s="15" t="str">
+      <x:c r="N49" s="4" t="str"/>
+      <x:c r="O49" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P49" s="17" t="str">
+      <x:c r="P49" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q49" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q49" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="54" customHeight="1">
       <x:c r="A50" s="4" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B50" s="4" t="str">
-        <x:v>航天科技集团五院502所</x:v>
+        <x:v>芯迈半导体</x:v>
       </x:c>
       <x:c r="C50" s="4" t="str">
-        <x:v>航天/自动控制</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D50" s="4" t="str">
-        <x:v>事业单位/央企院所</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E50" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>杭州、上海、深圳、成都</x:v>
       </x:c>
       <x:c r="F50" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G50" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H50" s="4" t="str">
+        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
+      </x:c>
+      <x:c r="I50" s="17" t="str">
+        <x:v>https://www.silicon-magic.com/joinus</x:v>
+      </x:c>
+      <x:c r="J50" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K50" s="4" t="str">
+        <x:v>官方未说明；公开流程未列笔试</x:v>
+      </x:c>
+      <x:c r="L50" s="4" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M50" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N50" s="4" t="str">
+        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
+      </x:c>
+      <x:c r="O50" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P50" s="15" t="str">
+        <x:v>A-企业官网与公开公告已核验</x:v>
+      </x:c>
+      <x:c r="Q50" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="54" customHeight="1">
+      <x:c r="A51" s="4" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B51" s="4" t="str">
+        <x:v>新易盛</x:v>
+      </x:c>
+      <x:c r="C51" s="4" t="str">
+        <x:v>光通信/半导体</x:v>
+      </x:c>
+      <x:c r="D51" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E51" s="4" t="str">
+        <x:v>成都、苏州等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F51" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G50" s="4" t="str">
-        <x:v>硕士/博士为主，以岗位为准</x:v>
-      </x:c>
-      <x:c r="H50" s="4" t="str">
-        <x:v>导航制导与控制、自动化、电子、通信、计算机、软件、机械等</x:v>
-      </x:c>
-      <x:c r="I50" s="15" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
-      </x:c>
-      <x:c r="J50" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K50" s="4" t="str">
-        <x:v>未统一公布</x:v>
-      </x:c>
-      <x:c r="L50" s="4" t="str">
-        <x:v>公开公告显示开放；投前确认</x:v>
-      </x:c>
-      <x:c r="M50" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N50" s="4" t="str">
-        <x:v>研究所岗位通常有专业、学历、政审及保密要求。</x:v>
-      </x:c>
-      <x:c r="O50" s="15" t="str">
-        <x:v>https://www.baidu.com/s?wd=%E4%BA%94%E9%99%A2502%E6%89%802027%E5%B1%8A%E6%A0%A1%E6%8B%9B</x:v>
-      </x:c>
-      <x:c r="P50" s="16" t="str">
-        <x:v>B-高校就业网公开公告</x:v>
-      </x:c>
-      <x:c r="Q50" s="4" t="n">
-        <x:v>46227</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="54" customHeight="1">
-      <x:c r="A51" s="16" t="str">
-        <x:v>2026-07-17</x:v>
-      </x:c>
-      <x:c r="B51" s="16" t="str">
-        <x:v>鹰角网络</x:v>
-      </x:c>
-      <x:c r="C51" s="16" t="str">
-        <x:v>游戏</x:v>
-      </x:c>
-      <x:c r="D51" s="16" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E51" s="16" t="str">
-        <x:v>上海</x:v>
-      </x:c>
-      <x:c r="F51" s="16" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G51" s="16" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H51" s="16" t="str">
-        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
-      </x:c>
-      <x:c r="I51" s="21" t="str">
-        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
-      </x:c>
-      <x:c r="J51" s="16" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K51" s="16" t="str">
-        <x:v>否；安排笔试/面试</x:v>
-      </x:c>
-      <x:c r="L51" s="16" t="str">
-        <x:v>1天内截止（2026-07-31）</x:v>
-      </x:c>
-      <x:c r="M51" s="16" t="str">
-        <x:v>P0-7天内截止</x:v>
-      </x:c>
-      <x:c r="N51" s="16" t="str">
-        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
-      </x:c>
-      <x:c r="O51" s="21" t="str">
-        <x:v>https://campus.hypergryph.com/</x:v>
-      </x:c>
-      <x:c r="P51" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q51" s="16" t="n">
-        <x:v>46233</x:v>
+      <x:c r="G51" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H51" s="4" t="str">
+        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
+      </x:c>
+      <x:c r="I51" s="17" t="str">
+        <x:v>https://www.eoptolink.com/</x:v>
+      </x:c>
+      <x:c r="J51" s="4" t="str">
+        <x:v>2026-08-20</x:v>
+      </x:c>
+      <x:c r="K51" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L51" s="4" t="str">
+        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
+      </x:c>
+      <x:c r="M51" s="4" t="str">
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N51" s="4" t="str">
+        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+      </x:c>
+      <x:c r="O51" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P51" s="18" t="str">
+        <x:v>B-高校/招聘平台转载，投前复核</x:v>
+      </x:c>
+      <x:c r="Q51" s="4" t="str">
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="54" customHeight="1">
       <x:c r="A52" s="4" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B52" s="4" t="str">
-        <x:v>联发科技</x:v>
+        <x:v>元戎启行</x:v>
       </x:c>
       <x:c r="C52" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>自动驾驶</x:v>
       </x:c>
       <x:c r="D52" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E52" s="4" t="str">
-        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
+        <x:v>深圳、北京等</x:v>
       </x:c>
       <x:c r="F52" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G52" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H52" s="4" t="str">
-        <x:v>软件类、通信类、IC类</x:v>
-      </x:c>
-      <x:c r="I52" s="15" t="str">
-        <x:v>https://mediatek.zhiye.com/</x:v>
+        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
+      </x:c>
+      <x:c r="I52" s="17" t="str">
+        <x:v>https://www.deeproute.ai/join-us</x:v>
       </x:c>
       <x:c r="J52" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K52" s="4" t="str">
-        <x:v>否；明确安排7-8月笔试</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L52" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M52" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N52" s="4" t="str">
-        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
-      </x:c>
-      <x:c r="O52" s="15" t="str">
+      <x:c r="N52" s="4" t="str"/>
+      <x:c r="O52" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P52" s="14" t="str">
-        <x:v>A-官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q52" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P52" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q52" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="54" customHeight="1">
       <x:c r="A53" s="4" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B53" s="4" t="str">
-        <x:v>DJI大疆</x:v>
+        <x:v>圆通速递</x:v>
       </x:c>
       <x:c r="C53" s="4" t="str">
-        <x:v>无人机/智能硬件</x:v>
+        <x:v>物流/供应链</x:v>
       </x:c>
       <x:c r="D53" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E53" s="4" t="str">
-        <x:v>深圳、东莞、上海、北京、西安等</x:v>
+        <x:v>上海及全国网络</x:v>
       </x:c>
       <x:c r="F53" s="4" t="str">
-        <x:v>正式批-拓疆者计划</x:v>
+        <x:v>正式批/校招</x:v>
       </x:c>
       <x:c r="G53" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H53" s="4" t="str">
-        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
-      </x:c>
-      <x:c r="I53" s="15" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
+        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
+      </x:c>
+      <x:c r="I53" s="17" t="str">
+        <x:v>https://hr.yto.net.cn/</x:v>
       </x:c>
       <x:c r="J53" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K53" s="4" t="str">
-        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L53" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M53" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N53" s="4" t="str">
-        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
-      </x:c>
-      <x:c r="O53" s="15" t="str">
+      <x:c r="N53" s="4" t="str"/>
+      <x:c r="O53" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P53" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q53" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P53" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q53" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="54" customHeight="1">
       <x:c r="A54" s="4" t="str">
-        <x:v>2026-07-15</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B54" s="4" t="str">
-        <x:v>蔚来</x:v>
+        <x:v>长亭科技</x:v>
       </x:c>
       <x:c r="C54" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>网络安全</x:v>
       </x:c>
       <x:c r="D54" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E54" s="4" t="str">
-        <x:v>上海、合肥、北京、武汉、南京等</x:v>
+        <x:v>北京、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F54" s="4" t="str">
-        <x:v>技术提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G54" s="4" t="str">
-        <x:v>2024年9月-2027年8月毕业</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H54" s="4" t="str">
-        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
-      </x:c>
-      <x:c r="I54" s="15" t="str">
-        <x:v>https://campus.nio.com/</x:v>
+        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
+      </x:c>
+      <x:c r="I54" s="17" t="str">
+        <x:v>https://job.chaitin.cn/</x:v>
       </x:c>
       <x:c r="J54" s="4" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K54" s="4" t="str">
-        <x:v>否；有笔试/测评</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L54" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M54" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N54" s="4" t="str">
-        <x:v>最多同时申请3个岗位。</x:v>
-      </x:c>
-      <x:c r="O54" s="15" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N54" s="4" t="str"/>
+      <x:c r="O54" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P54" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q54" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P54" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q54" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="54" customHeight="1">
       <x:c r="A55" s="4" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B55" s="4" t="str">
-        <x:v>北方华创</x:v>
+        <x:v>智元机器人-优才计划</x:v>
       </x:c>
       <x:c r="C55" s="4" t="str">
-        <x:v>半导体设备</x:v>
+        <x:v>具身智能/机器人</x:v>
       </x:c>
       <x:c r="D55" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E55" s="4" t="str">
-        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
+        <x:v>上海、北京、深圳等</x:v>
       </x:c>
       <x:c r="F55" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>优才专项/提前批</x:v>
       </x:c>
       <x:c r="G55" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H55" s="4" t="str">
-        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
-      </x:c>
-      <x:c r="I55" s="15" t="str">
-        <x:v>https://career.naura.com/campus</x:v>
+        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
+      </x:c>
+      <x:c r="I55" s="17" t="str">
+        <x:v>https://www.agibot.com/recruit</x:v>
       </x:c>
       <x:c r="J55" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K55" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L55" s="4" t="str">
-        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M55" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N55" s="4" t="str">
-        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
-      </x:c>
-      <x:c r="O55" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P55" s="14" t="str">
-        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
-      </x:c>
-      <x:c r="Q55" s="4" t="n">
-        <x:v>46233</x:v>
+      <x:c r="N55" s="4" t="str"/>
+      <x:c r="O55" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P55" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q55" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="54" customHeight="1">
       <x:c r="A56" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B56" s="4" t="str">
-        <x:v>百度</x:v>
+        <x:v>中国电信天翼云-超级优才</x:v>
       </x:c>
       <x:c r="C56" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>云计算/央企</x:v>
       </x:c>
       <x:c r="D56" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E56" s="4" t="str">
-        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+        <x:v>北京、上海、广州、成都及全国机构</x:v>
       </x:c>
       <x:c r="F56" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G56" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H56" s="4" t="str">
-        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
-      </x:c>
-      <x:c r="I56" s="15" t="str">
-        <x:v>https://talent.baidu.com/jobs</x:v>
+        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
+      </x:c>
+      <x:c r="I56" s="17" t="str">
+        <x:v>https://www.ctyun.cn/about/recruit</x:v>
       </x:c>
       <x:c r="J56" s="4" t="str">
-        <x:v>2027-06-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K56" s="4" t="str">
-        <x:v>部分免；并非所有候选人参加笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L56" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M56" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N56" s="4" t="str">
-        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
-      </x:c>
-      <x:c r="O56" s="15" t="str">
+        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
+      </x:c>
+      <x:c r="O56" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P56" s="14" t="str">
-        <x:v>A-官方招聘日历/官方来源已核验</x:v>
-      </x:c>
-      <x:c r="Q56" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P56" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q56" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="54" customHeight="1">
       <x:c r="A57" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B57" s="4" t="str">
-        <x:v>中国航天科工集团第六研究院</x:v>
+        <x:v>中科光电</x:v>
       </x:c>
       <x:c r="C57" s="4" t="str">
-        <x:v>航天/军工/动力系统</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D57" s="4" t="str">
-        <x:v>央企院所</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E57" s="4" t="str">
-        <x:v>呼和浩特及所属单位</x:v>
+        <x:v>以职位公告为准</x:v>
       </x:c>
       <x:c r="F57" s="4" t="str">
-        <x:v>提前批+暑期开放日</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G57" s="4" t="str">
-        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H57" s="4" t="str">
-        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
-      </x:c>
-      <x:c r="I57" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
+        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
+      </x:c>
+      <x:c r="I57" s="17" t="str">
+        <x:v>https://job.cn-amd.com/</x:v>
       </x:c>
       <x:c r="J57" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K57" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L57" s="4" t="str">
-        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M57" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N57" s="4" t="str">
-        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
-      </x:c>
-      <x:c r="O57" s="15" t="str">
-        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
-      </x:c>
-      <x:c r="P57" s="16" t="str">
-        <x:v>B-高校就业网公开公告</x:v>
-      </x:c>
-      <x:c r="Q57" s="4" t="n">
-        <x:v>46230</x:v>
+        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
+      </x:c>
+      <x:c r="O57" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P57" s="19" t="str">
+        <x:v>C-名称需二次确认</x:v>
+      </x:c>
+      <x:c r="Q57" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="54" customHeight="1">
       <x:c r="A58" s="4" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B58" s="4" t="str">
-        <x:v>思瑞浦</x:v>
+        <x:v>中兴微电子-未来领军计划</x:v>
       </x:c>
       <x:c r="C58" s="4" t="str">
-        <x:v>半导体/模拟IC</x:v>
+        <x:v>半导体/通信</x:v>
       </x:c>
       <x:c r="D58" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E58" s="4" t="str">
-        <x:v>上海、深圳等，以岗位页为准</x:v>
+        <x:v>深圳、西安、南京、上海等</x:v>
       </x:c>
       <x:c r="F58" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G58" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H58" s="4" t="str">
-        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
-      </x:c>
-      <x:c r="I58" s="15" t="str">
-        <x:v>https://www.3peak.cn/careers</x:v>
+        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
+      </x:c>
+      <x:c r="I58" s="17" t="str">
+        <x:v>https://job.zte.com.cn/</x:v>
       </x:c>
       <x:c r="J58" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3537,357 +3536,355 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L58" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M58" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N58" s="4" t="str">
-        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
-      </x:c>
-      <x:c r="O58" s="15" t="str">
-        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
-      </x:c>
-      <x:c r="P58" s="16" t="str">
-        <x:v>B-招聘平台/高校就业转载</x:v>
-      </x:c>
-      <x:c r="Q58" s="4" t="n">
-        <x:v>46230</x:v>
+        <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
+      </x:c>
+      <x:c r="O58" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P58" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q58" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="54" customHeight="1">
-      <x:c r="A59" s="22" t="str">
-        <x:v>2026-07-06</x:v>
-      </x:c>
-      <x:c r="B59" s="22" t="str">
-        <x:v>米哈游</x:v>
-      </x:c>
-      <x:c r="C59" s="22" t="str">
-        <x:v>游戏/互联网</x:v>
-      </x:c>
-      <x:c r="D59" s="22" t="str">
+      <x:c r="A59" s="14" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B59" s="14" t="str">
+        <x:v>字节跳动-AI产品经理早鸟通道</x:v>
+      </x:c>
+      <x:c r="C59" s="14" t="str">
+        <x:v>互联网/AI</x:v>
+      </x:c>
+      <x:c r="D59" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E59" s="22" t="str">
-        <x:v>上海、北京</x:v>
-      </x:c>
-      <x:c r="F59" s="22" t="str">
-        <x:v>技术提前批</x:v>
-      </x:c>
-      <x:c r="G59" s="22" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H59" s="22" t="str">
-        <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
-      </x:c>
-      <x:c r="I59" s="23" t="str">
-        <x:v>https://campus.mihoyo.com/</x:v>
-      </x:c>
-      <x:c r="J59" s="22" t="str">
-        <x:v>2026-07-27</x:v>
-      </x:c>
-      <x:c r="K59" s="22" t="str">
-        <x:v>有免笔试直通面试机会</x:v>
-      </x:c>
-      <x:c r="L59" s="22" t="str">
-        <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
-      </x:c>
-      <x:c r="M59" s="22" t="str">
+      <x:c r="E59" s="14" t="str">
+        <x:v>北京、上海、深圳</x:v>
+      </x:c>
+      <x:c r="F59" s="14" t="str">
+        <x:v>早鸟专项/提前批</x:v>
+      </x:c>
+      <x:c r="G59" s="14" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H59" s="14" t="str">
+        <x:v>AI产品经理、智能体及大模型产品方向</x:v>
+      </x:c>
+      <x:c r="I59" s="16" t="str">
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
+      </x:c>
+      <x:c r="J59" s="14" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+      <x:c r="K59" s="14" t="str">
+        <x:v>按岗位，未统一公布</x:v>
+      </x:c>
+      <x:c r="L59" s="14" t="str">
+        <x:v>已截止（2026-08-02）；原公告与官方投递入口保留</x:v>
+      </x:c>
+      <x:c r="M59" s="14" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N59" s="22" t="str">
-        <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
-      </x:c>
-      <x:c r="O59" s="23" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P59" s="14" t="str">
-        <x:v>A-官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q59" s="22" t="n">
-        <x:v>46233</x:v>
+      <x:c r="N59" s="14" t="str">
+        <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
+      </x:c>
+      <x:c r="O59" s="16" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P59" s="18" t="str">
+        <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q59" s="14" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="54" customHeight="1">
       <x:c r="A60" s="4" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B60" s="4" t="str">
-        <x:v>京东方-先锋京英计划</x:v>
+        <x:v>BCG波士顿咨询</x:v>
       </x:c>
       <x:c r="C60" s="4" t="str">
-        <x:v>显示技术/半导体/物联网</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D60" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E60" s="4" t="str">
-        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F60" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/中国区校招</x:v>
       </x:c>
       <x:c r="G60" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H60" s="4" t="str">
-        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
-      </x:c>
-      <x:c r="I60" s="15" t="str">
-        <x:v>https://campus.boe.com/</x:v>
+        <x:v>咨询顾问及相关专业岗位</x:v>
+      </x:c>
+      <x:c r="I60" s="17" t="str">
+        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
       </x:c>
       <x:c r="J60" s="4" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K60" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L60" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M60" s="4" t="str">
         <x:v>P1-30天内截止</x:v>
       </x:c>
-      <x:c r="N60" s="4" t="str">
-        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
-      </x:c>
-      <x:c r="O60" s="15" t="str">
+      <x:c r="N60" s="4" t="str"/>
+      <x:c r="O60" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P60" s="14" t="str">
-        <x:v>A-国家大学生就业平台公告已核验</x:v>
-      </x:c>
-      <x:c r="Q60" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P60" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q60" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="54" customHeight="1">
       <x:c r="A61" s="4" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B61" s="4" t="str">
-        <x:v>中国航天科技集团</x:v>
+        <x:v>OPPO</x:v>
       </x:c>
       <x:c r="C61" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D61" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E61" s="4" t="str">
-        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
+        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
       </x:c>
       <x:c r="F61" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G61" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H61" s="4" t="str">
-        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
-      </x:c>
-      <x:c r="I61" s="15" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
+        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
+      </x:c>
+      <x:c r="I61" s="17" t="str">
+        <x:v>https://careers.oppo.com/campus</x:v>
       </x:c>
       <x:c r="J61" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K61" s="4" t="str">
-        <x:v>各院所自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L61" s="4" t="str">
-        <x:v>官方公告已确认启动</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M61" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N61" s="4" t="str">
-        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
-      </x:c>
-      <x:c r="O61" s="15" t="str">
-        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
-      </x:c>
-      <x:c r="P61" s="14" t="str">
-        <x:v>A-国务院国资委/集团官方来源</x:v>
-      </x:c>
-      <x:c r="Q61" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
+      </x:c>
+      <x:c r="O61" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P61" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q61" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="54" customHeight="1">
       <x:c r="A62" s="4" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B62" s="4" t="str">
-        <x:v>高途</x:v>
+        <x:v>Tap4Fun</x:v>
       </x:c>
       <x:c r="C62" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>游戏</x:v>
       </x:c>
       <x:c r="D62" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E62" s="4" t="str">
-        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
+        <x:v>成都等</x:v>
       </x:c>
       <x:c r="F62" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>实习转正通道</x:v>
       </x:c>
       <x:c r="G62" s="4" t="str">
-        <x:v>27届为主，优秀28届也可投</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H62" s="4" t="str">
-        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
-      </x:c>
-      <x:c r="I62" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
+        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
+      </x:c>
+      <x:c r="I62" s="17" t="str">
+        <x:v>https://www.tap4fun.com/careers</x:v>
       </x:c>
       <x:c r="J62" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K62" s="4" t="str">
-        <x:v>否；流程包含笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L62" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M62" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N62" s="4" t="str">
-        <x:v>滚动发放Offer，截止时间未公布。</x:v>
-      </x:c>
-      <x:c r="O62" s="15" t="str">
+        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
+      </x:c>
+      <x:c r="O62" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P62" s="14" t="str">
-        <x:v>A-官方投递平台已核验</x:v>
-      </x:c>
-      <x:c r="Q62" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P62" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q62" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="54" customHeight="1">
       <x:c r="A63" s="4" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="B63" s="4" t="str">
-        <x:v>中汽中心</x:v>
+        <x:v>航天科技集团五院502所</x:v>
       </x:c>
       <x:c r="C63" s="4" t="str">
-        <x:v>汽车检测/科研</x:v>
+        <x:v>航天/自动控制</x:v>
       </x:c>
       <x:c r="D63" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>事业单位/央企院所</x:v>
       </x:c>
       <x:c r="E63" s="4" t="str">
-        <x:v>天津、武汉、北京、上海等</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F63" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G63" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>硕士/博士为主，以岗位为准</x:v>
       </x:c>
       <x:c r="H63" s="4" t="str">
-        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
-      </x:c>
-      <x:c r="I63" s="15" t="str">
-        <x:v>https://www.catarc.ac.cn/</x:v>
+        <x:v>导航制导与控制、自动化、电子、通信、计算机、软件、机械等</x:v>
+      </x:c>
+      <x:c r="I63" s="17" t="str">
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J63" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K63" s="4" t="str">
-        <x:v>官方未统一说明</x:v>
+        <x:v>未统一公布</x:v>
       </x:c>
       <x:c r="L63" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>公开公告显示开放；投前确认</x:v>
       </x:c>
       <x:c r="M63" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N63" s="4" t="str">
-        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
-      </x:c>
-      <x:c r="O63" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
-      </x:c>
-      <x:c r="P63" s="16" t="str">
-        <x:v>B-公开招聘公告</x:v>
-      </x:c>
-      <x:c r="Q63" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>研究所岗位通常有专业、学历、政审及保密要求。</x:v>
+      </x:c>
+      <x:c r="O63" s="17" t="str">
+        <x:v>https://www.baidu.com/s?wd=%E4%BA%94%E9%99%A2502%E6%89%802027%E5%B1%8A%E6%A0%A1%E6%8B%9B</x:v>
+      </x:c>
+      <x:c r="P63" s="18" t="str">
+        <x:v>B-高校就业网公开公告</x:v>
+      </x:c>
+      <x:c r="Q63" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="54" customHeight="1">
-      <x:c r="A64" s="4" t="str">
-        <x:v>2026-06-24</x:v>
-      </x:c>
-      <x:c r="B64" s="4" t="str">
-        <x:v>中国航天科工集团</x:v>
-      </x:c>
-      <x:c r="C64" s="4" t="str">
-        <x:v>航天/军工</x:v>
-      </x:c>
-      <x:c r="D64" s="4" t="str">
-        <x:v>央企</x:v>
-      </x:c>
-      <x:c r="E64" s="4" t="str">
-        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
-      </x:c>
-      <x:c r="F64" s="4" t="str">
-        <x:v>正式批/提前批</x:v>
-      </x:c>
-      <x:c r="G64" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H64" s="4" t="str">
-        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
-      </x:c>
-      <x:c r="I64" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
-      </x:c>
-      <x:c r="J64" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K64" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
-      </x:c>
-      <x:c r="L64" s="4" t="str">
-        <x:v>官网公告已确认启动</x:v>
-      </x:c>
-      <x:c r="M64" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N64" s="4" t="str">
-        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
-      </x:c>
-      <x:c r="O64" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
-      </x:c>
-      <x:c r="P64" s="14" t="str">
-        <x:v>A-集团官网公告已核验</x:v>
-      </x:c>
-      <x:c r="Q64" s="4" t="n">
-        <x:v>46230</x:v>
+      <x:c r="A64" s="14" t="str">
+        <x:v>2026-07-17</x:v>
+      </x:c>
+      <x:c r="B64" s="14" t="str">
+        <x:v>鹰角网络</x:v>
+      </x:c>
+      <x:c r="C64" s="14" t="str">
+        <x:v>游戏</x:v>
+      </x:c>
+      <x:c r="D64" s="14" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E64" s="14" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F64" s="14" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G64" s="14" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H64" s="14" t="str">
+        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
+      </x:c>
+      <x:c r="I64" s="16" t="str">
+        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
+      </x:c>
+      <x:c r="J64" s="14" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K64" s="14" t="str">
+        <x:v>否；安排笔试/面试</x:v>
+      </x:c>
+      <x:c r="L64" s="14" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M64" s="14" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N64" s="14" t="str">
+        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
+      </x:c>
+      <x:c r="O64" s="16" t="str">
+        <x:v>https://campus.hypergryph.com/</x:v>
+      </x:c>
+      <x:c r="P64" s="15" t="str">
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q64" s="14" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="54" customHeight="1">
       <x:c r="A65" s="4" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B65" s="4" t="str">
-        <x:v>禾赛科技</x:v>
+        <x:v>联发科技</x:v>
       </x:c>
       <x:c r="C65" s="4" t="str">
-        <x:v>激光雷达/机器人</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D65" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E65" s="4" t="str">
-        <x:v>上海、杭州</x:v>
+        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
       </x:c>
       <x:c r="F65" s="4" t="str">
         <x:v>提前批</x:v>
@@ -3896,157 +3893,157 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H65" s="4" t="str">
-        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
-      </x:c>
-      <x:c r="I65" s="15" t="str">
-        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
+        <x:v>软件类、通信类、IC类</x:v>
+      </x:c>
+      <x:c r="I65" s="17" t="str">
+        <x:v>https://mediatek.zhiye.com/</x:v>
       </x:c>
       <x:c r="J65" s="4" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K65" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；明确安排7-8月笔试</x:v>
       </x:c>
       <x:c r="L65" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M65" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N65" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O65" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P65" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q65" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
+      </x:c>
+      <x:c r="O65" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P65" s="15" t="str">
+        <x:v>A-官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q65" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="54" customHeight="1">
       <x:c r="A66" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B66" s="4" t="str">
-        <x:v>北京国望光学科技有限公司</x:v>
+        <x:v>DJI大疆</x:v>
       </x:c>
       <x:c r="C66" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>无人机/智能硬件</x:v>
       </x:c>
       <x:c r="D66" s="4" t="str">
-        <x:v>央国企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E66" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>深圳、东莞、上海、北京、西安等</x:v>
       </x:c>
       <x:c r="F66" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批-拓疆者计划</x:v>
       </x:c>
       <x:c r="G66" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H66" s="4" t="str">
-        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
-      </x:c>
-      <x:c r="I66" s="20" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
+      </x:c>
+      <x:c r="I66" s="17" t="str">
+        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
       </x:c>
       <x:c r="J66" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K66" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
       </x:c>
       <x:c r="L66" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M66" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N66" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O66" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P66" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q66" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
+      </x:c>
+      <x:c r="O66" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P66" s="15" t="str">
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q66" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="54" customHeight="1">
       <x:c r="A67" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="B67" s="4" t="str">
-        <x:v>乐读</x:v>
+        <x:v>蔚来</x:v>
       </x:c>
       <x:c r="C67" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D67" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E67" s="4" t="str">
-        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
+        <x:v>上海、合肥、北京、武汉、南京等</x:v>
       </x:c>
       <x:c r="F67" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>技术提前批</x:v>
       </x:c>
       <x:c r="G67" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2024年9月-2027年8月毕业</x:v>
       </x:c>
       <x:c r="H67" s="4" t="str">
-        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
-      </x:c>
-      <x:c r="I67" s="20" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
+      </x:c>
+      <x:c r="I67" s="17" t="str">
+        <x:v>https://campus.nio.com/</x:v>
       </x:c>
       <x:c r="J67" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K67" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；有笔试/测评</x:v>
       </x:c>
       <x:c r="L67" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M67" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N67" s="4" t="str">
-        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
-      </x:c>
-      <x:c r="O67" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P67" s="16" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
-      </x:c>
-      <x:c r="Q67" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>最多同时申请3个岗位。</x:v>
+      </x:c>
+      <x:c r="O67" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P67" s="15" t="str">
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q67" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="54" customHeight="1">
       <x:c r="A68" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="B68" s="4" t="str">
-        <x:v>龙蟠科技</x:v>
+        <x:v>北方华创</x:v>
       </x:c>
       <x:c r="C68" s="4" t="str">
-        <x:v>新能源材料/化工</x:v>
+        <x:v>半导体设备</x:v>
       </x:c>
       <x:c r="D68" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E68" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F68" s="4" t="str">
         <x:v>提前批</x:v>
@@ -4055,169 +4052,169 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H68" s="4" t="str">
-        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
-      </x:c>
-      <x:c r="I68" s="15" t="str">
-        <x:v>https://www.lopal.com.cn/join</x:v>
+        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
+      </x:c>
+      <x:c r="I68" s="17" t="str">
+        <x:v>https://career.naura.com/campus</x:v>
       </x:c>
       <x:c r="J68" s="4" t="str">
-        <x:v>2027-06-01</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K68" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L68" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
       </x:c>
       <x:c r="M68" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N68" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O68" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P68" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q68" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
+      </x:c>
+      <x:c r="O68" s="17" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P68" s="15" t="str">
+        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
+      </x:c>
+      <x:c r="Q68" s="4" t="str">
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="54" customHeight="1">
       <x:c r="A69" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B69" s="4" t="str">
-        <x:v>牧原</x:v>
+        <x:v>百度</x:v>
       </x:c>
       <x:c r="C69" s="4" t="str">
-        <x:v>农业/食品/智能养殖</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D69" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E69" s="4" t="str">
-        <x:v>河南南阳及全国</x:v>
+        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
       </x:c>
       <x:c r="F69" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G69" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H69" s="4" t="str">
-        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
-      </x:c>
-      <x:c r="I69" s="15" t="str">
-        <x:v>https://job.muyuanfoods.com/</x:v>
+        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+      </x:c>
+      <x:c r="I69" s="17" t="str">
+        <x:v>https://talent.baidu.com/jobs</x:v>
       </x:c>
       <x:c r="J69" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-30</x:v>
       </x:c>
       <x:c r="K69" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>部分免；并非所有候选人参加笔试</x:v>
       </x:c>
       <x:c r="L69" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M69" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N69" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O69" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P69" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q69" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
+      </x:c>
+      <x:c r="O69" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P69" s="15" t="str">
+        <x:v>A-官方招聘日历/官方来源已核验</x:v>
+      </x:c>
+      <x:c r="Q69" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="54" customHeight="1">
       <x:c r="A70" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B70" s="4" t="str">
-        <x:v>三一集团-小语种校招</x:v>
+        <x:v>中国航天科工集团第六研究院</x:v>
       </x:c>
       <x:c r="C70" s="4" t="str">
-        <x:v>工程机械/制造</x:v>
+        <x:v>航天/军工/动力系统</x:v>
       </x:c>
       <x:c r="D70" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企院所</x:v>
       </x:c>
       <x:c r="E70" s="4" t="str">
-        <x:v>海外多国</x:v>
+        <x:v>呼和浩特及所属单位</x:v>
       </x:c>
       <x:c r="F70" s="4" t="str">
-        <x:v>小语种专项/正式批</x:v>
+        <x:v>提前批+暑期开放日</x:v>
       </x:c>
       <x:c r="G70" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
       </x:c>
       <x:c r="H70" s="4" t="str">
-        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
-      </x:c>
-      <x:c r="I70" s="15" t="str">
-        <x:v>https://sanycampus.zhiye.com/</x:v>
+        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
+      </x:c>
+      <x:c r="I70" s="17" t="str">
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
       <x:c r="J70" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K70" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L70" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
       </x:c>
       <x:c r="M70" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N70" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O70" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P70" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q70" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
+      </x:c>
+      <x:c r="O70" s="17" t="str">
+        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
+      </x:c>
+      <x:c r="P70" s="18" t="str">
+        <x:v>B-高校就业网公开公告</x:v>
+      </x:c>
+      <x:c r="Q70" s="4" t="str">
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="54" customHeight="1">
       <x:c r="A71" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="B71" s="4" t="str">
-        <x:v>上海电气-暑期精英训练营</x:v>
+        <x:v>思瑞浦</x:v>
       </x:c>
       <x:c r="C71" s="4" t="str">
-        <x:v>高端装备/能源</x:v>
+        <x:v>半导体/模拟IC</x:v>
       </x:c>
       <x:c r="D71" s="4" t="str">
-        <x:v>地方国企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E71" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>上海、深圳等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F71" s="4" t="str">
-        <x:v>训练营/秋招直通</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G71" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H71" s="4" t="str">
-        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
-      </x:c>
-      <x:c r="I71" s="15" t="str">
-        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
+        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
+      </x:c>
+      <x:c r="I71" s="17" t="str">
+        <x:v>https://www.3peak.cn/careers</x:v>
       </x:c>
       <x:c r="J71" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4226,425 +4223,425 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L71" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
       </x:c>
       <x:c r="M71" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N71" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O71" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P71" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q71" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
+      </x:c>
+      <x:c r="O71" s="17" t="str">
+        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
+      </x:c>
+      <x:c r="P71" s="18" t="str">
+        <x:v>B-招聘平台/高校就业转载</x:v>
+      </x:c>
+      <x:c r="Q71" s="4" t="str">
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="54" customHeight="1">
       <x:c r="A72" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>不晚于2026-07-07</x:v>
       </x:c>
       <x:c r="B72" s="4" t="str">
-        <x:v>vivo-蓝极星计划</x:v>
+        <x:v>文远知行WeRide</x:v>
       </x:c>
       <x:c r="C72" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>自动驾驶/人工智能</x:v>
       </x:c>
       <x:c r="D72" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E72" s="4" t="str">
+        <x:v>广州、深圳、武汉等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F72" s="4" t="str">
+        <x:v>正式批/校招/可转正实习</x:v>
+      </x:c>
+      <x:c r="G72" s="4" t="str">
+        <x:v>2027届应届毕业生及可转正实习生，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H72" s="4" t="str">
+        <x:v>感知/预测/规划控制算法、算法测试、测试开发、SRE、云与车端安全、AI Infra、仿真平台等</x:v>
+      </x:c>
+      <x:c r="I72" s="17" t="str">
+        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
+      </x:c>
+      <x:c r="J72" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K72" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L72" s="4" t="str">
+        <x:v>企业官方校招系统在招；已核验137个职位</x:v>
+      </x:c>
+      <x:c r="M72" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N72" s="4" t="str">
+        <x:v>官方列表显示2027届校招职位最早发布于7月7日；部分岗位为可转正实习，城市和岗位随招聘系统实时调整。</x:v>
+      </x:c>
+      <x:c r="O72" s="17" t="str">
+        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
+      </x:c>
+      <x:c r="P72" s="15" t="str">
+        <x:v>A-企业官方校招系统与职位列表已核验</x:v>
+      </x:c>
+      <x:c r="Q72" s="4" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="54" customHeight="1">
+      <x:c r="A73" s="14" t="str">
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="B73" s="14" t="str">
+        <x:v>米哈游</x:v>
+      </x:c>
+      <x:c r="C73" s="14" t="str">
+        <x:v>游戏/互联网</x:v>
+      </x:c>
+      <x:c r="D73" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E72" s="4" t="str">
-        <x:v>深圳、杭州、东莞、上海</x:v>
-      </x:c>
-      <x:c r="F72" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
-      </x:c>
-      <x:c r="G72" s="4" t="str">
-        <x:v>博士为主</x:v>
-      </x:c>
-      <x:c r="H72" s="4" t="str">
-        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
-      </x:c>
-      <x:c r="I72" s="15" t="str">
-        <x:v>https://hr.vivo.com/</x:v>
-      </x:c>
-      <x:c r="J72" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K72" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L72" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
-      </x:c>
-      <x:c r="M72" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N72" s="4" t="str">
-        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
-      </x:c>
-      <x:c r="O72" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P72" s="16" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
-      </x:c>
-      <x:c r="Q72" s="4" t="n">
-        <x:v>46227</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" ht="54" customHeight="1">
-      <x:c r="A73" s="4" t="str">
-        <x:v>2026-06-16</x:v>
-      </x:c>
-      <x:c r="B73" s="4" t="str">
-        <x:v>澜起科技</x:v>
-      </x:c>
-      <x:c r="C73" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
-      </x:c>
-      <x:c r="D73" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E73" s="4" t="str">
-        <x:v>昆山、西安、南京</x:v>
-      </x:c>
-      <x:c r="F73" s="4" t="str">
-        <x:v>正式批</x:v>
-      </x:c>
-      <x:c r="G73" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H73" s="4" t="str">
-        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
-      </x:c>
-      <x:c r="I73" s="15" t="str">
-        <x:v>https://www.montage-tech.com/cn/careers</x:v>
-      </x:c>
-      <x:c r="J73" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K73" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L73" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
-      </x:c>
-      <x:c r="M73" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N73" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O73" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P73" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q73" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="E73" s="14" t="str">
+        <x:v>上海、北京</x:v>
+      </x:c>
+      <x:c r="F73" s="14" t="str">
+        <x:v>技术提前批</x:v>
+      </x:c>
+      <x:c r="G73" s="14" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H73" s="14" t="str">
+        <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
+      </x:c>
+      <x:c r="I73" s="16" t="str">
+        <x:v>https://campus.mihoyo.com/</x:v>
+      </x:c>
+      <x:c r="J73" s="14" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+      <x:c r="K73" s="14" t="str">
+        <x:v>有免笔试直通面试机会</x:v>
+      </x:c>
+      <x:c r="L73" s="14" t="str">
+        <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
+      </x:c>
+      <x:c r="M73" s="14" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N73" s="14" t="str">
+        <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
+      </x:c>
+      <x:c r="O73" s="16" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P73" s="15" t="str">
+        <x:v>A-官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q73" s="14" t="str">
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="54" customHeight="1">
       <x:c r="A74" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="B74" s="4" t="str">
-        <x:v>上海宇量昇</x:v>
+        <x:v>京东方-先锋京英计划</x:v>
       </x:c>
       <x:c r="C74" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>显示技术/半导体/物联网</x:v>
       </x:c>
       <x:c r="D74" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E74" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
       </x:c>
       <x:c r="F74" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G74" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H74" s="4" t="str">
-        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
-      </x:c>
-      <x:c r="I74" s="15" t="str">
-        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
+        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
+      </x:c>
+      <x:c r="I74" s="17" t="str">
+        <x:v>https://campus.boe.com/</x:v>
       </x:c>
       <x:c r="J74" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K74" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L74" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M74" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N74" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O74" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P74" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q74" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
+      </x:c>
+      <x:c r="O74" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P74" s="15" t="str">
+        <x:v>A-国家大学生就业平台公告已核验</x:v>
+      </x:c>
+      <x:c r="Q74" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="54" customHeight="1">
       <x:c r="A75" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="B75" s="4" t="str">
-        <x:v>是为科技</x:v>
+        <x:v>中国航天科技集团</x:v>
       </x:c>
       <x:c r="C75" s="4" t="str">
-        <x:v>新能源/智能制造</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D75" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E75" s="4" t="str">
-        <x:v>南京、上海、常州</x:v>
+        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
       </x:c>
       <x:c r="F75" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G75" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H75" s="4" t="str">
-        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
-      </x:c>
-      <x:c r="I75" s="15" t="str">
-        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
+        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
+      </x:c>
+      <x:c r="I75" s="17" t="str">
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J75" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K75" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各院所自行组织，未统一</x:v>
       </x:c>
       <x:c r="L75" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>官方公告已确认启动</x:v>
       </x:c>
       <x:c r="M75" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N75" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O75" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P75" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q75" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
+      </x:c>
+      <x:c r="O75" s="17" t="str">
+        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
+      </x:c>
+      <x:c r="P75" s="15" t="str">
+        <x:v>A-国务院国资委/集团官方来源</x:v>
+      </x:c>
+      <x:c r="Q75" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="54" customHeight="1">
       <x:c r="A76" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="B76" s="4" t="str">
-        <x:v>游族网络</x:v>
+        <x:v>高途</x:v>
       </x:c>
       <x:c r="C76" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D76" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E76" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
       </x:c>
       <x:c r="F76" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G76" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>27届为主，优秀28届也可投</x:v>
       </x:c>
       <x:c r="H76" s="4" t="str">
-        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
-      </x:c>
-      <x:c r="I76" s="15" t="str">
-        <x:v>https://job.youzu.com/</x:v>
+        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
+      </x:c>
+      <x:c r="I76" s="17" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
       </x:c>
       <x:c r="J76" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K76" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；流程包含笔试</x:v>
       </x:c>
       <x:c r="L76" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M76" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N76" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O76" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P76" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q76" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>滚动发放Offer，截止时间未公布。</x:v>
+      </x:c>
+      <x:c r="O76" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P76" s="15" t="str">
+        <x:v>A-官方投递平台已核验</x:v>
+      </x:c>
+      <x:c r="Q76" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="54" customHeight="1">
       <x:c r="A77" s="4" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="B77" s="4" t="str">
-        <x:v>中铁设计</x:v>
+        <x:v>中汽中心</x:v>
       </x:c>
       <x:c r="C77" s="4" t="str">
-        <x:v>轨道交通/工程设计</x:v>
+        <x:v>汽车检测/科研</x:v>
       </x:c>
       <x:c r="D77" s="4" t="str">
         <x:v>央企</x:v>
       </x:c>
       <x:c r="E77" s="4" t="str">
-        <x:v>北京、济南、郑州、太原</x:v>
+        <x:v>天津、武汉、北京、上海等</x:v>
       </x:c>
       <x:c r="F77" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G77" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H77" s="4" t="str">
-        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
-      </x:c>
-      <x:c r="I77" s="15" t="str">
-        <x:v>https://www.crdc.com/</x:v>
+        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
+      </x:c>
+      <x:c r="I77" s="17" t="str">
+        <x:v>https://www.catarc.ac.cn/</x:v>
       </x:c>
       <x:c r="J77" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K77" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L77" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M77" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N77" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O77" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P77" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q77" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
+      </x:c>
+      <x:c r="O77" s="17" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
+      </x:c>
+      <x:c r="P77" s="18" t="str">
+        <x:v>B-公开招聘公告</x:v>
+      </x:c>
+      <x:c r="Q77" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="54" customHeight="1">
       <x:c r="A78" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="B78" s="4" t="str">
-        <x:v>迈安德集团-校园大使</x:v>
+        <x:v>中国航天科工集团</x:v>
       </x:c>
       <x:c r="C78" s="4" t="str">
-        <x:v>粮油工程/装备</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D78" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E78" s="4" t="str">
-        <x:v>扬州/高校</x:v>
+        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
       </x:c>
       <x:c r="F78" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>正式批/提前批</x:v>
       </x:c>
       <x:c r="G78" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H78" s="4" t="str">
-        <x:v>校园大使</x:v>
-      </x:c>
-      <x:c r="I78" s="15" t="str">
-        <x:v>https://www.myande.com/</x:v>
+        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
+      </x:c>
+      <x:c r="I78" s="17" t="str">
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
       <x:c r="J78" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K78" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L78" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>官网公告已确认启动</x:v>
       </x:c>
       <x:c r="M78" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N78" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O78" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P78" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q78" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
+      </x:c>
+      <x:c r="O78" s="17" t="str">
+        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
+      </x:c>
+      <x:c r="P78" s="15" t="str">
+        <x:v>A-集团官网公告已核验</x:v>
+      </x:c>
+      <x:c r="Q78" s="4" t="str">
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="54" customHeight="1">
       <x:c r="A79" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="B79" s="4" t="str">
-        <x:v>迅仿科技</x:v>
+        <x:v>禾赛科技</x:v>
       </x:c>
       <x:c r="C79" s="4" t="str">
-        <x:v>工业软件/仿真</x:v>
+        <x:v>激光雷达/机器人</x:v>
       </x:c>
       <x:c r="D79" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E79" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>上海、杭州</x:v>
       </x:c>
       <x:c r="F79" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G79" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H79" s="4" t="str">
-        <x:v>仿真工程师</x:v>
-      </x:c>
-      <x:c r="I79" s="20" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
+      </x:c>
+      <x:c r="I79" s="17" t="str">
+        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
       </x:c>
       <x:c r="J79" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="K79" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -4653,51 +4650,51 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M79" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N79" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O79" s="15" t="str">
+      <x:c r="O79" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P79" s="16" t="str">
+      <x:c r="P79" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q79" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q79" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="54" customHeight="1">
       <x:c r="A80" s="4" t="str">
-        <x:v>2026-06-12</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B80" s="4" t="str">
-        <x:v>MOVA</x:v>
+        <x:v>北京国望光学科技有限公司</x:v>
       </x:c>
       <x:c r="C80" s="4" t="str">
-        <x:v>智能家电/机器人</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D80" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>央国企</x:v>
       </x:c>
       <x:c r="E80" s="4" t="str">
-        <x:v>苏州及全国</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F80" s="4" t="str">
-        <x:v>全球校招/正式批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G80" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H80" s="4" t="str">
-        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
-      </x:c>
-      <x:c r="I80" s="15" t="str">
-        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
+      </x:c>
+      <x:c r="I80" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J80" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K80" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -4706,48 +4703,48 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M80" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N80" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O80" s="15" t="str">
+      <x:c r="O80" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P80" s="16" t="str">
+      <x:c r="P80" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q80" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q80" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="54" customHeight="1">
       <x:c r="A81" s="4" t="str">
-        <x:v>2026-06-11</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B81" s="4" t="str">
-        <x:v>财通证券</x:v>
+        <x:v>乐读</x:v>
       </x:c>
       <x:c r="C81" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D81" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E81" s="4" t="str">
-        <x:v>杭州、上海、深圳、北京</x:v>
+        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
       </x:c>
       <x:c r="F81" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G81" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H81" s="4" t="str">
-        <x:v>总部、参股公司、分公司岗位</x:v>
-      </x:c>
-      <x:c r="I81" s="15" t="str">
-        <x:v>https://www.ctsec.com/joinUs</x:v>
+        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
+      </x:c>
+      <x:c r="I81" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J81" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4756,54 +4753,54 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L81" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M81" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N81" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O81" s="15" t="str">
+        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
+      </x:c>
+      <x:c r="O81" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P81" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q81" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P81" s="18" t="str">
+        <x:v>B-招聘平台公开汇总</x:v>
+      </x:c>
+      <x:c r="Q81" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="54" customHeight="1">
       <x:c r="A82" s="4" t="str">
-        <x:v>2026-06-10</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B82" s="4" t="str">
-        <x:v>歌尔股份</x:v>
+        <x:v>龙蟠科技</x:v>
       </x:c>
       <x:c r="C82" s="4" t="str">
-        <x:v>消费电子/智能硬件</x:v>
+        <x:v>新能源材料/化工</x:v>
       </x:c>
       <x:c r="D82" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E82" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F82" s="4" t="str">
-        <x:v>实习/校招储备</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G82" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H82" s="4" t="str">
-        <x:v>法务助理</x:v>
-      </x:c>
-      <x:c r="I82" s="15" t="str">
-        <x:v>https://career.goertek.com/</x:v>
+        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
+      </x:c>
+      <x:c r="I82" s="17" t="str">
+        <x:v>https://www.lopal.com.cn/join</x:v>
       </x:c>
       <x:c r="J82" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-01</x:v>
       </x:c>
       <x:c r="K82" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -4812,48 +4809,48 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M82" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N82" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O82" s="15" t="str">
+      <x:c r="O82" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P82" s="16" t="str">
+      <x:c r="P82" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q82" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q82" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="54" customHeight="1">
       <x:c r="A83" s="4" t="str">
-        <x:v>2026-06-09</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B83" s="4" t="str">
-        <x:v>深信服-校园大使</x:v>
+        <x:v>牧原</x:v>
       </x:c>
       <x:c r="C83" s="4" t="str">
-        <x:v>网络安全/云计算</x:v>
+        <x:v>农业/食品/智能养殖</x:v>
       </x:c>
       <x:c r="D83" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E83" s="4" t="str">
-        <x:v>西安</x:v>
+        <x:v>河南南阳及全国</x:v>
       </x:c>
       <x:c r="F83" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G83" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H83" s="4" t="str">
-        <x:v>校园大使</x:v>
-      </x:c>
-      <x:c r="I83" s="15" t="str">
-        <x:v>https://hr.sangfor.com/</x:v>
+        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
+      </x:c>
+      <x:c r="I83" s="17" t="str">
+        <x:v>https://job.muyuanfoods.com/</x:v>
       </x:c>
       <x:c r="J83" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4870,43 +4867,43 @@
       <x:c r="N83" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O83" s="15" t="str">
+      <x:c r="O83" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P83" s="16" t="str">
+      <x:c r="P83" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q83" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q83" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="54" customHeight="1">
       <x:c r="A84" s="4" t="str">
-        <x:v>2026-06-08</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B84" s="4" t="str">
-        <x:v>晓禾教育</x:v>
+        <x:v>三一集团-小语种校招</x:v>
       </x:c>
       <x:c r="C84" s="4" t="str">
-        <x:v>教育</x:v>
+        <x:v>工程机械/制造</x:v>
       </x:c>
       <x:c r="D84" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E84" s="4" t="str">
-        <x:v>武汉、郑州、襄阳、宜昌</x:v>
+        <x:v>海外多国</x:v>
       </x:c>
       <x:c r="F84" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>小语种专项/正式批</x:v>
       </x:c>
       <x:c r="G84" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H84" s="4" t="str">
-        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
-      </x:c>
-      <x:c r="I84" s="20" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
+      </x:c>
+      <x:c r="I84" s="17" t="str">
+        <x:v>https://sanycampus.zhiye.com/</x:v>
       </x:c>
       <x:c r="J84" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4923,43 +4920,43 @@
       <x:c r="N84" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O84" s="15" t="str">
+      <x:c r="O84" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P84" s="16" t="str">
+      <x:c r="P84" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q84" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q84" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="54" customHeight="1">
       <x:c r="A85" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B85" s="4" t="str">
-        <x:v>晖致医药</x:v>
+        <x:v>上海电气-暑期精英训练营</x:v>
       </x:c>
       <x:c r="C85" s="4" t="str">
-        <x:v>医药</x:v>
+        <x:v>高端装备/能源</x:v>
       </x:c>
       <x:c r="D85" s="4" t="str">
-        <x:v>外资</x:v>
+        <x:v>地方国企</x:v>
       </x:c>
       <x:c r="E85" s="4" t="str">
         <x:v>上海</x:v>
       </x:c>
       <x:c r="F85" s="4" t="str">
-        <x:v>实习储备正式岗</x:v>
+        <x:v>训练营/秋招直通</x:v>
       </x:c>
       <x:c r="G85" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H85" s="4" t="str">
-        <x:v>医学信息沟通实习生</x:v>
-      </x:c>
-      <x:c r="I85" s="15" t="str">
-        <x:v>https://careers.viatris.com/</x:v>
+        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
+      </x:c>
+      <x:c r="I85" s="17" t="str">
+        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
       </x:c>
       <x:c r="J85" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4976,43 +4973,43 @@
       <x:c r="N85" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O85" s="15" t="str">
+      <x:c r="O85" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P85" s="16" t="str">
+      <x:c r="P85" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q85" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q85" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="54" customHeight="1">
       <x:c r="A86" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B86" s="4" t="str">
-        <x:v>苏州鸿凌达电子</x:v>
+        <x:v>vivo-蓝极星计划</x:v>
       </x:c>
       <x:c r="C86" s="4" t="str">
-        <x:v>电子制造</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D86" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E86" s="4" t="str">
-        <x:v>苏州</x:v>
+        <x:v>深圳、杭州、东莞、上海</x:v>
       </x:c>
       <x:c r="F86" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G86" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>博士为主</x:v>
       </x:c>
       <x:c r="H86" s="4" t="str">
-        <x:v>财务助理</x:v>
-      </x:c>
-      <x:c r="I86" s="15" t="str">
-        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
+        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
+      </x:c>
+      <x:c r="I86" s="17" t="str">
+        <x:v>https://hr.vivo.com/</x:v>
       </x:c>
       <x:c r="J86" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5021,39 +5018,39 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L86" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M86" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N86" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O86" s="15" t="str">
+        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
+      </x:c>
+      <x:c r="O86" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P86" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q86" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P86" s="18" t="str">
+        <x:v>B-招聘平台公开汇总</x:v>
+      </x:c>
+      <x:c r="Q86" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="54" customHeight="1">
       <x:c r="A87" s="4" t="str">
-        <x:v>2026-06-02</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B87" s="4" t="str">
-        <x:v>万得信息</x:v>
+        <x:v>澜起科技</x:v>
       </x:c>
       <x:c r="C87" s="4" t="str">
-        <x:v>金融数据/软件</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D87" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E87" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>昆山、西安、南京</x:v>
       </x:c>
       <x:c r="F87" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5062,10 +5059,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H87" s="4" t="str">
-        <x:v>AI算法工程师等</x:v>
-      </x:c>
-      <x:c r="I87" s="15" t="str">
-        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
+        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
+      </x:c>
+      <x:c r="I87" s="17" t="str">
+        <x:v>https://www.montage-tech.com/cn/careers</x:v>
       </x:c>
       <x:c r="J87" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5082,43 +5079,43 @@
       <x:c r="N87" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O87" s="15" t="str">
+      <x:c r="O87" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P87" s="16" t="str">
+      <x:c r="P87" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q87" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q87" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="54" customHeight="1">
       <x:c r="A88" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B88" s="4" t="str">
-        <x:v>淘大集供应链</x:v>
+        <x:v>上海宇量昇</x:v>
       </x:c>
       <x:c r="C88" s="4" t="str">
-        <x:v>零售/供应链</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D88" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E88" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F88" s="4" t="str">
-        <x:v>管培/实习</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G88" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H88" s="4" t="str">
-        <x:v>巡店管培生、实习生</x:v>
-      </x:c>
-      <x:c r="I88" s="20" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
+      </x:c>
+      <x:c r="I88" s="17" t="str">
+        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
       </x:c>
       <x:c r="J88" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5135,43 +5132,43 @@
       <x:c r="N88" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O88" s="15" t="str">
+      <x:c r="O88" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P88" s="16" t="str">
+      <x:c r="P88" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q88" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q88" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="54" customHeight="1">
       <x:c r="A89" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B89" s="4" t="str">
-        <x:v>友芝友实业集团</x:v>
+        <x:v>是为科技</x:v>
       </x:c>
       <x:c r="C89" s="4" t="str">
-        <x:v>综合实业</x:v>
+        <x:v>新能源/智能制造</x:v>
       </x:c>
       <x:c r="D89" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E89" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>南京、上海、常州</x:v>
       </x:c>
       <x:c r="F89" s="4" t="str">
-        <x:v>管培生</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G89" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H89" s="4" t="str">
-        <x:v>青年领军人才管培生</x:v>
-      </x:c>
-      <x:c r="I89" s="15" t="str">
-        <x:v>https://www.yzyqh.com/jrwm</x:v>
+        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
+      </x:c>
+      <x:c r="I89" s="17" t="str">
+        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
       </x:c>
       <x:c r="J89" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5188,31 +5185,31 @@
       <x:c r="N89" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O89" s="15" t="str">
+      <x:c r="O89" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P89" s="16" t="str">
+      <x:c r="P89" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q89" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q89" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="54" customHeight="1">
       <x:c r="A90" s="4" t="str">
-        <x:v>2026-05-29</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B90" s="4" t="str">
-        <x:v>银雁科技</x:v>
+        <x:v>游族网络</x:v>
       </x:c>
       <x:c r="C90" s="4" t="str">
-        <x:v>金融科技服务</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D90" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E90" s="4" t="str">
-        <x:v>成都</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F90" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5221,10 +5218,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H90" s="4" t="str">
-        <x:v>人伤理赔</x:v>
-      </x:c>
-      <x:c r="I90" s="15" t="str">
-        <x:v>https://www.cfss.net.cn/</x:v>
+        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
+      </x:c>
+      <x:c r="I90" s="17" t="str">
+        <x:v>https://job.youzu.com/</x:v>
       </x:c>
       <x:c r="J90" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5241,31 +5238,31 @@
       <x:c r="N90" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O90" s="15" t="str">
+      <x:c r="O90" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P90" s="16" t="str">
+      <x:c r="P90" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q90" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q90" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="54" customHeight="1">
       <x:c r="A91" s="4" t="str">
-        <x:v>2026-05-15</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="B91" s="4" t="str">
-        <x:v>知乎</x:v>
+        <x:v>中铁设计</x:v>
       </x:c>
       <x:c r="C91" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>轨道交通/工程设计</x:v>
       </x:c>
       <x:c r="D91" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E91" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>北京、济南、郑州、太原</x:v>
       </x:c>
       <x:c r="F91" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5274,10 +5271,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H91" s="4" t="str">
-        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
-      </x:c>
-      <x:c r="I91" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
+        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
+      </x:c>
+      <x:c r="I91" s="17" t="str">
+        <x:v>https://www.crdc.com/</x:v>
       </x:c>
       <x:c r="J91" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5294,43 +5291,43 @@
       <x:c r="N91" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O91" s="15" t="str">
+      <x:c r="O91" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P91" s="16" t="str">
+      <x:c r="P91" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q91" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q91" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="54" customHeight="1">
       <x:c r="A92" s="4" t="str">
-        <x:v>2026-05-08</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B92" s="4" t="str">
-        <x:v>招商银行长沙分行</x:v>
+        <x:v>迈安德集团-校园大使</x:v>
       </x:c>
       <x:c r="C92" s="4" t="str">
-        <x:v>银行/金融</x:v>
+        <x:v>粮油工程/装备</x:v>
       </x:c>
       <x:c r="D92" s="4" t="str">
-        <x:v>股份制银行</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E92" s="4" t="str">
-        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+        <x:v>扬州/高校</x:v>
       </x:c>
       <x:c r="F92" s="4" t="str">
-        <x:v>暑期实习/秋招直通</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G92" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H92" s="4" t="str">
-        <x:v>2027暑期实习生</x:v>
-      </x:c>
-      <x:c r="I92" s="15" t="str">
-        <x:v>https://career.cmbchina.com/</x:v>
+        <x:v>校园大使</x:v>
+      </x:c>
+      <x:c r="I92" s="17" t="str">
+        <x:v>https://www.myande.com/</x:v>
       </x:c>
       <x:c r="J92" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5347,28 +5344,28 @@
       <x:c r="N92" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O92" s="15" t="str">
+      <x:c r="O92" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P92" s="16" t="str">
+      <x:c r="P92" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q92" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q92" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="54" customHeight="1">
       <x:c r="A93" s="4" t="str">
-        <x:v>2026-04-22</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B93" s="4" t="str">
-        <x:v>华金证券</x:v>
+        <x:v>迅仿科技</x:v>
       </x:c>
       <x:c r="C93" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>工业软件/仿真</x:v>
       </x:c>
       <x:c r="D93" s="4" t="str">
-        <x:v>国企</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E93" s="4" t="str">
         <x:v>上海</x:v>
@@ -5380,10 +5377,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H93" s="4" t="str">
-        <x:v>战略发展类</x:v>
-      </x:c>
-      <x:c r="I93" s="15" t="str">
-        <x:v>https://www.huajinsc.cn/</x:v>
+        <x:v>仿真工程师</x:v>
+      </x:c>
+      <x:c r="I93" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J93" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5400,14 +5397,756 @@
       <x:c r="N93" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O93" s="15" t="str">
+      <x:c r="O93" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P93" s="16" t="str">
+      <x:c r="P93" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q93" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q93" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="54" customHeight="1">
+      <x:c r="A94" s="4" t="str">
+        <x:v>2026-06-12</x:v>
+      </x:c>
+      <x:c r="B94" s="4" t="str">
+        <x:v>MOVA</x:v>
+      </x:c>
+      <x:c r="C94" s="4" t="str">
+        <x:v>智能家电/机器人</x:v>
+      </x:c>
+      <x:c r="D94" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E94" s="4" t="str">
+        <x:v>苏州及全国</x:v>
+      </x:c>
+      <x:c r="F94" s="4" t="str">
+        <x:v>全球校招/正式批</x:v>
+      </x:c>
+      <x:c r="G94" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H94" s="4" t="str">
+        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+      </x:c>
+      <x:c r="I94" s="17" t="str">
+        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+      </x:c>
+      <x:c r="J94" s="4" t="str">
+        <x:v>2026-11-30</x:v>
+      </x:c>
+      <x:c r="K94" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L94" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M94" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N94" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O94" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P94" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q94" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="54" customHeight="1">
+      <x:c r="A95" s="4" t="str">
+        <x:v>2026-06-11</x:v>
+      </x:c>
+      <x:c r="B95" s="4" t="str">
+        <x:v>财通证券</x:v>
+      </x:c>
+      <x:c r="C95" s="4" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="D95" s="4" t="str">
+        <x:v>国企/上市</x:v>
+      </x:c>
+      <x:c r="E95" s="4" t="str">
+        <x:v>杭州、上海、深圳、北京</x:v>
+      </x:c>
+      <x:c r="F95" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G95" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H95" s="4" t="str">
+        <x:v>总部、参股公司、分公司岗位</x:v>
+      </x:c>
+      <x:c r="I95" s="17" t="str">
+        <x:v>https://www.ctsec.com/joinUs</x:v>
+      </x:c>
+      <x:c r="J95" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K95" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L95" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M95" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N95" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O95" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P95" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q95" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="54" customHeight="1">
+      <x:c r="A96" s="4" t="str">
+        <x:v>2026-06-10</x:v>
+      </x:c>
+      <x:c r="B96" s="4" t="str">
+        <x:v>歌尔股份</x:v>
+      </x:c>
+      <x:c r="C96" s="4" t="str">
+        <x:v>消费电子/智能硬件</x:v>
+      </x:c>
+      <x:c r="D96" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E96" s="4" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F96" s="4" t="str">
+        <x:v>实习/校招储备</x:v>
+      </x:c>
+      <x:c r="G96" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H96" s="4" t="str">
+        <x:v>法务助理</x:v>
+      </x:c>
+      <x:c r="I96" s="17" t="str">
+        <x:v>https://career.goertek.com/</x:v>
+      </x:c>
+      <x:c r="J96" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K96" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L96" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M96" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N96" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O96" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P96" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q96" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="54" customHeight="1">
+      <x:c r="A97" s="4" t="str">
+        <x:v>2026-06-09</x:v>
+      </x:c>
+      <x:c r="B97" s="4" t="str">
+        <x:v>深信服-校园大使</x:v>
+      </x:c>
+      <x:c r="C97" s="4" t="str">
+        <x:v>网络安全/云计算</x:v>
+      </x:c>
+      <x:c r="D97" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E97" s="4" t="str">
+        <x:v>西安</x:v>
+      </x:c>
+      <x:c r="F97" s="4" t="str">
+        <x:v>校园大使/非正式全职</x:v>
+      </x:c>
+      <x:c r="G97" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H97" s="4" t="str">
+        <x:v>校园大使</x:v>
+      </x:c>
+      <x:c r="I97" s="17" t="str">
+        <x:v>https://hr.sangfor.com/</x:v>
+      </x:c>
+      <x:c r="J97" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K97" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L97" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M97" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N97" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O97" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P97" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q97" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="54" customHeight="1">
+      <x:c r="A98" s="4" t="str">
+        <x:v>2026-06-08</x:v>
+      </x:c>
+      <x:c r="B98" s="4" t="str">
+        <x:v>晓禾教育</x:v>
+      </x:c>
+      <x:c r="C98" s="4" t="str">
+        <x:v>教育</x:v>
+      </x:c>
+      <x:c r="D98" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E98" s="4" t="str">
+        <x:v>武汉、郑州、襄阳、宜昌</x:v>
+      </x:c>
+      <x:c r="F98" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G98" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H98" s="4" t="str">
+        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
+      </x:c>
+      <x:c r="I98" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
+      </x:c>
+      <x:c r="J98" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K98" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L98" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M98" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N98" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O98" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P98" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q98" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="54" customHeight="1">
+      <x:c r="A99" s="4" t="str">
+        <x:v>2026-06-04</x:v>
+      </x:c>
+      <x:c r="B99" s="4" t="str">
+        <x:v>晖致医药</x:v>
+      </x:c>
+      <x:c r="C99" s="4" t="str">
+        <x:v>医药</x:v>
+      </x:c>
+      <x:c r="D99" s="4" t="str">
+        <x:v>外资</x:v>
+      </x:c>
+      <x:c r="E99" s="4" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F99" s="4" t="str">
+        <x:v>实习储备正式岗</x:v>
+      </x:c>
+      <x:c r="G99" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H99" s="4" t="str">
+        <x:v>医学信息沟通实习生</x:v>
+      </x:c>
+      <x:c r="I99" s="17" t="str">
+        <x:v>https://careers.viatris.com/</x:v>
+      </x:c>
+      <x:c r="J99" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K99" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L99" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M99" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N99" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O99" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P99" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q99" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="54" customHeight="1">
+      <x:c r="A100" s="4" t="str">
+        <x:v>2026-06-04</x:v>
+      </x:c>
+      <x:c r="B100" s="4" t="str">
+        <x:v>苏州鸿凌达电子</x:v>
+      </x:c>
+      <x:c r="C100" s="4" t="str">
+        <x:v>电子制造</x:v>
+      </x:c>
+      <x:c r="D100" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E100" s="4" t="str">
+        <x:v>苏州</x:v>
+      </x:c>
+      <x:c r="F100" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G100" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H100" s="4" t="str">
+        <x:v>财务助理</x:v>
+      </x:c>
+      <x:c r="I100" s="17" t="str">
+        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
+      </x:c>
+      <x:c r="J100" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K100" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L100" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M100" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N100" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O100" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P100" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q100" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="54" customHeight="1">
+      <x:c r="A101" s="4" t="str">
+        <x:v>2026-06-02</x:v>
+      </x:c>
+      <x:c r="B101" s="4" t="str">
+        <x:v>万得信息</x:v>
+      </x:c>
+      <x:c r="C101" s="4" t="str">
+        <x:v>金融数据/软件</x:v>
+      </x:c>
+      <x:c r="D101" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E101" s="4" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F101" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G101" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H101" s="4" t="str">
+        <x:v>AI算法工程师等</x:v>
+      </x:c>
+      <x:c r="I101" s="17" t="str">
+        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
+      </x:c>
+      <x:c r="J101" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K101" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L101" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M101" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N101" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O101" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P101" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q101" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" ht="54" customHeight="1">
+      <x:c r="A102" s="4" t="str">
+        <x:v>2026-06-01</x:v>
+      </x:c>
+      <x:c r="B102" s="4" t="str">
+        <x:v>淘大集供应链</x:v>
+      </x:c>
+      <x:c r="C102" s="4" t="str">
+        <x:v>零售/供应链</x:v>
+      </x:c>
+      <x:c r="D102" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E102" s="4" t="str">
+        <x:v>武汉</x:v>
+      </x:c>
+      <x:c r="F102" s="4" t="str">
+        <x:v>管培/实习</x:v>
+      </x:c>
+      <x:c r="G102" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H102" s="4" t="str">
+        <x:v>巡店管培生、实习生</x:v>
+      </x:c>
+      <x:c r="I102" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
+      </x:c>
+      <x:c r="J102" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K102" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L102" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M102" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N102" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O102" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P102" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q102" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="54" customHeight="1">
+      <x:c r="A103" s="4" t="str">
+        <x:v>2026-06-01</x:v>
+      </x:c>
+      <x:c r="B103" s="4" t="str">
+        <x:v>友芝友实业集团</x:v>
+      </x:c>
+      <x:c r="C103" s="4" t="str">
+        <x:v>综合实业</x:v>
+      </x:c>
+      <x:c r="D103" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E103" s="4" t="str">
+        <x:v>武汉</x:v>
+      </x:c>
+      <x:c r="F103" s="4" t="str">
+        <x:v>管培生</x:v>
+      </x:c>
+      <x:c r="G103" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H103" s="4" t="str">
+        <x:v>青年领军人才管培生</x:v>
+      </x:c>
+      <x:c r="I103" s="17" t="str">
+        <x:v>https://www.yzyqh.com/jrwm</x:v>
+      </x:c>
+      <x:c r="J103" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K103" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L103" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M103" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N103" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O103" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P103" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q103" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" ht="54" customHeight="1">
+      <x:c r="A104" s="4" t="str">
+        <x:v>2026-05-29</x:v>
+      </x:c>
+      <x:c r="B104" s="4" t="str">
+        <x:v>银雁科技</x:v>
+      </x:c>
+      <x:c r="C104" s="4" t="str">
+        <x:v>金融科技服务</x:v>
+      </x:c>
+      <x:c r="D104" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E104" s="4" t="str">
+        <x:v>成都</x:v>
+      </x:c>
+      <x:c r="F104" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G104" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H104" s="4" t="str">
+        <x:v>人伤理赔</x:v>
+      </x:c>
+      <x:c r="I104" s="17" t="str">
+        <x:v>https://www.cfss.net.cn/</x:v>
+      </x:c>
+      <x:c r="J104" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K104" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L104" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M104" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N104" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O104" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P104" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q104" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="54" customHeight="1">
+      <x:c r="A105" s="4" t="str">
+        <x:v>2026-05-15</x:v>
+      </x:c>
+      <x:c r="B105" s="4" t="str">
+        <x:v>知乎</x:v>
+      </x:c>
+      <x:c r="C105" s="4" t="str">
+        <x:v>互联网/内容平台</x:v>
+      </x:c>
+      <x:c r="D105" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E105" s="4" t="str">
+        <x:v>北京</x:v>
+      </x:c>
+      <x:c r="F105" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G105" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H105" s="4" t="str">
+        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
+      </x:c>
+      <x:c r="I105" s="17" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
+      </x:c>
+      <x:c r="J105" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K105" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L105" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M105" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N105" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O105" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P105" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q105" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" ht="54" customHeight="1">
+      <x:c r="A106" s="4" t="str">
+        <x:v>2026-05-08</x:v>
+      </x:c>
+      <x:c r="B106" s="4" t="str">
+        <x:v>招商银行长沙分行</x:v>
+      </x:c>
+      <x:c r="C106" s="4" t="str">
+        <x:v>银行/金融</x:v>
+      </x:c>
+      <x:c r="D106" s="4" t="str">
+        <x:v>股份制银行</x:v>
+      </x:c>
+      <x:c r="E106" s="4" t="str">
+        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+      </x:c>
+      <x:c r="F106" s="4" t="str">
+        <x:v>暑期实习/秋招直通</x:v>
+      </x:c>
+      <x:c r="G106" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H106" s="4" t="str">
+        <x:v>2027暑期实习生</x:v>
+      </x:c>
+      <x:c r="I106" s="17" t="str">
+        <x:v>https://career.cmbchina.com/</x:v>
+      </x:c>
+      <x:c r="J106" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K106" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L106" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M106" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N106" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O106" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P106" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q106" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" ht="54" customHeight="1">
+      <x:c r="A107" s="4" t="str">
+        <x:v>2026-04-22</x:v>
+      </x:c>
+      <x:c r="B107" s="4" t="str">
+        <x:v>华金证券</x:v>
+      </x:c>
+      <x:c r="C107" s="4" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="D107" s="4" t="str">
+        <x:v>国企</x:v>
+      </x:c>
+      <x:c r="E107" s="4" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F107" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G107" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H107" s="4" t="str">
+        <x:v>战略发展类</x:v>
+      </x:c>
+      <x:c r="I107" s="17" t="str">
+        <x:v>https://www.huajinsc.cn/</x:v>
+      </x:c>
+      <x:c r="J107" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K107" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L107" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M107" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N107" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O107" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P107" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q107" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5417,7 +6156,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13a17ef8f54747ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa96992addae4765"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5447,7 +6186,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>近期有明确截止时间的项目（截至2026-07-30）</x:v>
+        <x:v>近期有明确截止时间的项目（截至2026-08-03）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -5541,126 +6280,124 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
-      <x:c r="A4" s="16" t="str">
-        <x:v>2026-07-17</x:v>
-      </x:c>
-      <x:c r="B4" s="16" t="str">
-        <x:v>鹰角网络</x:v>
-      </x:c>
-      <x:c r="C4" s="16" t="str">
+      <x:c r="A4" s="4" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="str">
+        <x:v>莉莉丝游戏</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="str">
         <x:v>游戏</x:v>
       </x:c>
-      <x:c r="D4" s="16" t="str">
+      <x:c r="D4" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E4" s="16" t="str">
-        <x:v>上海</x:v>
-      </x:c>
-      <x:c r="F4" s="16" t="str">
+      <x:c r="E4" s="4" t="str">
+        <x:v>上海等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G4" s="16" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H4" s="16" t="str">
-        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
-      </x:c>
-      <x:c r="I4" s="21" t="str">
-        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
-      </x:c>
-      <x:c r="J4" s="16" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K4" s="16" t="str">
-        <x:v>否；安排笔试/面试</x:v>
-      </x:c>
-      <x:c r="L4" s="16" t="str">
-        <x:v>1天内截止（2026-07-31）</x:v>
-      </x:c>
-      <x:c r="M4" s="16" t="str">
-        <x:v>P0-7天内截止</x:v>
-      </x:c>
-      <x:c r="N4" s="16" t="str">
-        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
-      </x:c>
-      <x:c r="O4" s="21" t="str">
-        <x:v>https://campus.hypergryph.com/</x:v>
-      </x:c>
-      <x:c r="P4" s="14" t="str">
+      <x:c r="G4" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H4" s="4" t="str">
+        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
+      </x:c>
+      <x:c r="I4" s="17" t="str">
+        <x:v>https://campus.lilith.com/</x:v>
+      </x:c>
+      <x:c r="J4" s="4" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+      <x:c r="K4" s="4" t="str">
+        <x:v>按岗位，官方未统一说明</x:v>
+      </x:c>
+      <x:c r="L4" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M4" s="4" t="str">
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N4" s="4" t="str"/>
+      <x:c r="O4" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P4" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q4" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="4" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="str">
+        <x:v>蔚来</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="str">
+        <x:v>新能源汽车/智能汽车</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="str">
+        <x:v>上海、合肥、北京、武汉、南京等</x:v>
+      </x:c>
+      <x:c r="F5" s="4" t="str">
+        <x:v>技术提前批</x:v>
+      </x:c>
+      <x:c r="G5" s="4" t="str">
+        <x:v>2024年9月-2027年8月毕业</x:v>
+      </x:c>
+      <x:c r="H5" s="4" t="str">
+        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
+      </x:c>
+      <x:c r="I5" s="17" t="str">
+        <x:v>https://campus.nio.com/</x:v>
+      </x:c>
+      <x:c r="J5" s="4" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="K5" s="4" t="str">
+        <x:v>否；有笔试/测评</x:v>
+      </x:c>
+      <x:c r="L5" s="4" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M5" s="4" t="str">
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N5" s="4" t="str">
+        <x:v>最多同时申请3个岗位。</x:v>
+      </x:c>
+      <x:c r="O5" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P5" s="15" t="str">
         <x:v>A-官方来源公告已核验</x:v>
       </x:c>
-      <x:c r="Q4" s="16" t="n">
-        <x:v>46233</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="54" customHeight="1">
-      <x:c r="A5" s="16" t="str">
-        <x:v>不晚于2026-07-21</x:v>
-      </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>字节跳动-AI产品经理早鸟通道</x:v>
-      </x:c>
-      <x:c r="C5" s="16" t="str">
-        <x:v>互联网/AI</x:v>
-      </x:c>
-      <x:c r="D5" s="16" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E5" s="16" t="str">
-        <x:v>北京、上海、深圳</x:v>
-      </x:c>
-      <x:c r="F5" s="16" t="str">
-        <x:v>早鸟专项/提前批</x:v>
-      </x:c>
-      <x:c r="G5" s="16" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H5" s="16" t="str">
-        <x:v>AI产品经理、智能体及大模型产品方向</x:v>
-      </x:c>
-      <x:c r="I5" s="21" t="str">
-        <x:v>https://jobs.bytedance.com/campus/</x:v>
-      </x:c>
-      <x:c r="J5" s="16" t="str">
-        <x:v>2026-08-02</x:v>
-      </x:c>
-      <x:c r="K5" s="16" t="str">
-        <x:v>按岗位，未统一公布</x:v>
-      </x:c>
-      <x:c r="L5" s="16" t="str">
-        <x:v>3天内截止（2026-08-02）</x:v>
-      </x:c>
-      <x:c r="M5" s="16" t="str">
-        <x:v>P0-7天内截止</x:v>
-      </x:c>
-      <x:c r="N5" s="16" t="str">
-        <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
-      </x:c>
-      <x:c r="O5" s="21" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P5" s="16" t="str">
-        <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q5" s="16" t="n">
-        <x:v>46233</x:v>
+      <x:c r="Q5" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>莉莉丝游戏</x:v>
+        <x:v>京东方-先锋京英计划</x:v>
       </x:c>
       <x:c r="C6" s="4" t="str">
-        <x:v>游戏</x:v>
+        <x:v>显示技术/半导体/物联网</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
       </x:c>
       <x:c r="F6" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5669,49 +6406,51 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H6" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
-      </x:c>
-      <x:c r="I6" s="15" t="str">
-        <x:v>https://campus.lilith.com/</x:v>
+        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
+      </x:c>
+      <x:c r="I6" s="17" t="str">
+        <x:v>https://campus.boe.com/</x:v>
       </x:c>
       <x:c r="J6" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K6" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L6" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M6" s="4" t="str">
         <x:v>P1-30天内截止</x:v>
       </x:c>
-      <x:c r="N6" s="4"/>
-      <x:c r="O6" s="15" t="str">
+      <x:c r="N6" s="4" t="str">
+        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
+      </x:c>
+      <x:c r="O6" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P6" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q6" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P6" s="15" t="str">
+        <x:v>A-国家大学生就业平台公告已核验</x:v>
+      </x:c>
+      <x:c r="Q6" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="4" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>京东方-先锋京英计划</x:v>
+        <x:v>中科光电</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
-        <x:v>显示技术/半导体/物联网</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
+        <x:v>以职位公告为准</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5720,87 +6459,85 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
-      </x:c>
-      <x:c r="I7" s="15" t="str">
-        <x:v>https://campus.boe.com/</x:v>
+        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
+      </x:c>
+      <x:c r="I7" s="17" t="str">
+        <x:v>https://job.cn-amd.com/</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K7" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L7" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M7" s="4" t="str">
         <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N7" s="4" t="str">
-        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
-      </x:c>
-      <x:c r="O7" s="15" t="str">
+        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
+      </x:c>
+      <x:c r="O7" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P7" s="14" t="str">
-        <x:v>A-国家大学生就业平台公告已核验</x:v>
-      </x:c>
-      <x:c r="Q7" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P7" s="19" t="str">
+        <x:v>C-名称需二次确认</x:v>
+      </x:c>
+      <x:c r="Q7" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="4" t="str">
-        <x:v>2026-07-15</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>蔚来</x:v>
+        <x:v>BCG波士顿咨询</x:v>
       </x:c>
       <x:c r="C8" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>上海、合肥、北京、武汉、南京等</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F8" s="4" t="str">
-        <x:v>技术提前批</x:v>
+        <x:v>正式批/中国区校招</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
-        <x:v>2024年9月-2027年8月毕业</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
-        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
-      </x:c>
-      <x:c r="I8" s="15" t="str">
-        <x:v>https://campus.nio.com/</x:v>
+        <x:v>咨询顾问及相关专业岗位</x:v>
+      </x:c>
+      <x:c r="I8" s="17" t="str">
+        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
       </x:c>
       <x:c r="J8" s="4" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K8" s="4" t="str">
-        <x:v>否；有笔试/测评</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L8" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M8" s="4" t="str">
         <x:v>P1-30天内截止</x:v>
       </x:c>
-      <x:c r="N8" s="4" t="str">
-        <x:v>最多同时申请3个岗位。</x:v>
-      </x:c>
-      <x:c r="O8" s="15" t="str">
+      <x:c r="N8" s="4" t="str"/>
+      <x:c r="O8" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P8" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q8" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P8" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q8" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
@@ -5808,16 +6545,16 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>中科光电</x:v>
+        <x:v>虹软科技</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>计算机视觉/软件</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>以职位公告为准</x:v>
+        <x:v>杭州、上海、南京等</x:v>
       </x:c>
       <x:c r="F9" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5826,16 +6563,16 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
-      </x:c>
-      <x:c r="I9" s="15" t="str">
-        <x:v>https://job.cn-amd.com/</x:v>
+        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
+      </x:c>
+      <x:c r="I9" s="17" t="str">
+        <x:v>https://hr.arcsoft.com.cn/</x:v>
       </x:c>
       <x:c r="J9" s="4" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K9" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L9" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -5843,17 +6580,15 @@
       <x:c r="M9" s="4" t="str">
         <x:v>P1-30天内截止</x:v>
       </x:c>
-      <x:c r="N9" s="4" t="str">
-        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
-      </x:c>
-      <x:c r="O9" s="15" t="str">
+      <x:c r="N9" s="4" t="str"/>
+      <x:c r="O9" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P9" s="17" t="str">
-        <x:v>C-名称需二次确认</x:v>
-      </x:c>
-      <x:c r="Q9" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P9" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q9" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
@@ -5861,67 +6596,69 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B10" s="4" t="str">
-        <x:v>BCG波士顿咨询</x:v>
+        <x:v>新易盛</x:v>
       </x:c>
       <x:c r="C10" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>光通信/半导体</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>成都、苏州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F10" s="4" t="str">
-        <x:v>正式批/中国区校招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>咨询顾问及相关专业岗位</x:v>
-      </x:c>
-      <x:c r="I10" s="15" t="str">
-        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
+        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
+      </x:c>
+      <x:c r="I10" s="17" t="str">
+        <x:v>https://www.eoptolink.com/</x:v>
       </x:c>
       <x:c r="J10" s="4" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K10" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L10" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
       </x:c>
       <x:c r="M10" s="4" t="str">
         <x:v>P1-30天内截止</x:v>
       </x:c>
-      <x:c r="N10" s="4"/>
-      <x:c r="O10" s="15" t="str">
+      <x:c r="N10" s="4" t="str">
+        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+      </x:c>
+      <x:c r="O10" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P10" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q10" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="P10" s="18" t="str">
+        <x:v>B-高校/招聘平台转载，投前复核</x:v>
+      </x:c>
+      <x:c r="Q10" s="4" t="str">
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="B11" s="4" t="str">
-        <x:v>虹软科技</x:v>
+        <x:v>禾赛科技</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
-        <x:v>计算机视觉/软件</x:v>
+        <x:v>激光雷达/机器人</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>杭州、上海、南京等</x:v>
+        <x:v>上海、杭州</x:v>
       </x:c>
       <x:c r="F11" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5930,173 +6667,175 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
-      </x:c>
-      <x:c r="I11" s="15" t="str">
-        <x:v>https://hr.arcsoft.com.cn/</x:v>
+        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
+      </x:c>
+      <x:c r="I11" s="17" t="str">
+        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="K11" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L11" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M11" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N11" s="4"/>
-      <x:c r="O11" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P11" s="17" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q11" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N11" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O11" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P11" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q11" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>新易盛</x:v>
+        <x:v>深信服-X-STAR顶尖人才计划</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
-        <x:v>光通信/半导体</x:v>
+        <x:v>网络安全/云计算/软件</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>成都、苏州等，以岗位页为准</x:v>
+        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F12" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>顶尖人才，本硕博按岗位要求</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
-      </x:c>
-      <x:c r="I12" s="15" t="str">
-        <x:v>https://www.eoptolink.com/</x:v>
+        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
+      </x:c>
+      <x:c r="I12" s="17" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
       </x:c>
       <x:c r="J12" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-09-25</x:v>
       </x:c>
       <x:c r="K12" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L12" s="4" t="str">
-        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M12" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N12" s="4" t="str">
-        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
-      </x:c>
-      <x:c r="O12" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P12" s="16" t="str">
-        <x:v>B-高校/招聘平台转载，投前复核</x:v>
-      </x:c>
-      <x:c r="Q12" s="4" t="n">
-        <x:v>46230</x:v>
+        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
+      </x:c>
+      <x:c r="O12" s="17" t="str">
+        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
+      </x:c>
+      <x:c r="P12" s="15" t="str">
+        <x:v>A-高校就业网含官方投递链接</x:v>
+      </x:c>
+      <x:c r="Q12" s="4" t="str">
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="4" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B13" s="4" t="str">
-        <x:v>禾赛科技</x:v>
+        <x:v>中移九天人工智能科技</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
-        <x:v>激光雷达/机器人</x:v>
+        <x:v>AI/软件/云计算</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企子公司</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>上海、杭州</x:v>
+        <x:v>北京、西安、广州、深圳</x:v>
       </x:c>
       <x:c r="F13" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/超级实习生</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
-      </x:c>
-      <x:c r="I13" s="15" t="str">
-        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
+        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
+      </x:c>
+      <x:c r="I13" s="17" t="str">
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="J13" s="4" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-09-27</x:v>
       </x:c>
       <x:c r="K13" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L13" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
       </x:c>
       <x:c r="M13" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N13" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O13" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P13" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q13" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
+      </x:c>
+      <x:c r="O13" s="17" t="str">
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
+      </x:c>
+      <x:c r="P13" s="15" t="str">
+        <x:v>A-中国移动官方招聘平台已核验</x:v>
+      </x:c>
+      <x:c r="Q13" s="4" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B14" s="4" t="str">
-        <x:v>深信服-X-STAR顶尖人才计划</x:v>
+        <x:v>网易游戏雷火</x:v>
       </x:c>
       <x:c r="C14" s="4" t="str">
-        <x:v>网络安全/云计算/软件</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D14" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
+        <x:v>杭州、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F14" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>顶尖人才，本硕博按岗位要求</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
-      </x:c>
-      <x:c r="I14" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
+        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
+      </x:c>
+      <x:c r="I14" s="17" t="str">
+        <x:v>https://leihuo.163.com/campus/#/full</x:v>
       </x:c>
       <x:c r="J14" s="4" t="str">
-        <x:v>2026-09-25</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="K14" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>部分岗位免笔试；部分可直通面试</x:v>
       </x:c>
       <x:c r="L14" s="4" t="str">
         <x:v>已核验开放</x:v>
@@ -6105,122 +6844,122 @@
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N14" s="4" t="str">
-        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
-      </x:c>
-      <x:c r="O14" s="15" t="str">
-        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
-      </x:c>
-      <x:c r="P14" s="14" t="str">
-        <x:v>A-高校就业网含官方投递链接</x:v>
-      </x:c>
-      <x:c r="Q14" s="4" t="n">
-        <x:v>46230</x:v>
+        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
+      </x:c>
+      <x:c r="O14" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P14" s="15" t="str">
+        <x:v>A-官方招聘官网已核验</x:v>
+      </x:c>
+      <x:c r="Q14" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B15" s="4" t="str">
-        <x:v>网易游戏雷火</x:v>
+        <x:v>广州市卓越教育集团</x:v>
       </x:c>
       <x:c r="C15" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D15" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>杭州、上海等，以岗位页为准</x:v>
+        <x:v>广州等，以职位页为准</x:v>
       </x:c>
       <x:c r="F15" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
-      </x:c>
-      <x:c r="I15" s="15" t="str">
-        <x:v>https://leihuo.163.com/campus/#/full</x:v>
+        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+      </x:c>
+      <x:c r="I15" s="17" t="str">
+        <x:v>https://zyjob.hotjob.cn/</x:v>
       </x:c>
       <x:c r="J15" s="4" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>2026-10-26</x:v>
       </x:c>
       <x:c r="K15" s="4" t="str">
-        <x:v>部分岗位免笔试；部分可直通面试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L15" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
       </x:c>
       <x:c r="M15" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N15" s="4" t="str">
-        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
-      </x:c>
-      <x:c r="O15" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P15" s="14" t="str">
-        <x:v>A-官方招聘官网已核验</x:v>
-      </x:c>
-      <x:c r="Q15" s="4" t="n">
-        <x:v>46227</x:v>
+        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
+      </x:c>
+      <x:c r="O15" s="17" t="str">
+        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
+      </x:c>
+      <x:c r="P15" s="15" t="str">
+        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
+      </x:c>
+      <x:c r="Q15" s="4" t="str">
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="4" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
-        <x:v>广州市卓越教育集团</x:v>
+        <x:v>影石Insta360</x:v>
       </x:c>
       <x:c r="C16" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>消费电子/智能影像</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>广州等，以职位页为准</x:v>
+        <x:v>深圳、上海、珠海</x:v>
       </x:c>
       <x:c r="F16" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
-      </x:c>
-      <x:c r="I16" s="15" t="str">
-        <x:v>https://zyjob.hotjob.cn/</x:v>
+        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+      </x:c>
+      <x:c r="I16" s="17" t="str">
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
       </x:c>
       <x:c r="J16" s="4" t="str">
-        <x:v>2026-10-26</x:v>
+        <x:v>2026-10-31</x:v>
       </x:c>
       <x:c r="K16" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L16" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
+        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="M16" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N16" s="4" t="str">
-        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
-      </x:c>
-      <x:c r="O16" s="15" t="str">
-        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
-      </x:c>
-      <x:c r="P16" s="14" t="str">
-        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
-      </x:c>
-      <x:c r="Q16" s="4" t="n">
-        <x:v>46233</x:v>
+        <x:v>岗位城市和具体职位以影石Insta360官方招聘页为准；公开信息标注10月31日，投递前再次确认职位状态。</x:v>
+      </x:c>
+      <x:c r="O16" s="17" t="str">
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
+      </x:c>
+      <x:c r="P16" s="15" t="str">
+        <x:v>A-企业官方招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q16" s="4" t="str">
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
@@ -6248,7 +6987,7 @@
       <x:c r="H17" s="4" t="str">
         <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
       </x:c>
-      <x:c r="I17" s="15" t="str">
+      <x:c r="I17" s="17" t="str">
         <x:v>https://campus.jd.com/</x:v>
       </x:c>
       <x:c r="J17" s="4" t="str">
@@ -6266,14 +7005,14 @@
       <x:c r="N17" s="4" t="str">
         <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
       </x:c>
-      <x:c r="O17" s="15" t="str">
+      <x:c r="O17" s="17" t="str">
         <x:v>https://campus.jd.com/#/</x:v>
       </x:c>
-      <x:c r="P17" s="14" t="str">
+      <x:c r="P17" s="15" t="str">
         <x:v>A-企业官网校招页面已核验</x:v>
       </x:c>
-      <x:c r="Q17" s="4" t="n">
-        <x:v>46233</x:v>
+      <x:c r="Q17" s="4" t="str">
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
@@ -6301,7 +7040,7 @@
       <x:c r="H18" s="4" t="str">
         <x:v>研产、全球营销、设计、职能、制造供应</x:v>
       </x:c>
-      <x:c r="I18" s="15" t="str">
+      <x:c r="I18" s="17" t="str">
         <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
       </x:c>
       <x:c r="J18" s="4" t="str">
@@ -6319,14 +7058,14 @@
       <x:c r="N18" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O18" s="15" t="str">
+      <x:c r="O18" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P18" s="16" t="str">
+      <x:c r="P18" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q18" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q18" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
@@ -6354,7 +7093,7 @@
       <x:c r="H19" s="4" t="str">
         <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
       </x:c>
-      <x:c r="I19" s="15" t="str">
+      <x:c r="I19" s="17" t="str">
         <x:v>https://www.lopal.com.cn/join</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
@@ -6372,14 +7111,14 @@
       <x:c r="N19" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O19" s="15" t="str">
+      <x:c r="O19" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P19" s="16" t="str">
+      <x:c r="P19" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q19" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q19" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
@@ -6407,7 +7146,7 @@
       <x:c r="H20" s="4" t="str">
         <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
       </x:c>
-      <x:c r="I20" s="15" t="str">
+      <x:c r="I20" s="17" t="str">
         <x:v>https://talent.baidu.com/jobs</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
@@ -6425,14 +7164,14 @@
       <x:c r="N20" s="4" t="str">
         <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
       </x:c>
-      <x:c r="O20" s="15" t="str">
+      <x:c r="O20" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P20" s="14" t="str">
+      <x:c r="P20" s="15" t="str">
         <x:v>A-官方招聘日历/官方来源已核验</x:v>
       </x:c>
-      <x:c r="Q20" s="4" t="n">
-        <x:v>46227</x:v>
+      <x:c r="Q20" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6442,7 +7181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5ecc1fec1d6460a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf05e1a7641e6467b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6459,295 +7198,295 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="28" t="str">
-        <x:v>使用说明与统计（截至2026-07-30）</x:v>
-      </x:c>
-      <x:c r="B1" s="28"/>
-      <x:c r="C1" s="28"/>
-      <x:c r="D1" s="28"/>
-      <x:c r="E1" s="28"/>
+      <x:c r="A1" s="27" t="str">
+        <x:v>使用说明与统计（截至2026-08-03）</x:v>
+      </x:c>
+      <x:c r="B1" s="27"/>
+      <x:c r="C1" s="27"/>
+      <x:c r="D1" s="27"/>
+      <x:c r="E1" s="27"/>
       <x:c r="F1"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="26"/>
-      <x:c r="B2" s="26"/>
-      <x:c r="C2" s="26"/>
-      <x:c r="D2" s="26"/>
-      <x:c r="E2" s="26"/>
+      <x:c r="A2" s="25"/>
+      <x:c r="B2" s="25"/>
+      <x:c r="C2" s="25"/>
+      <x:c r="D2" s="25"/>
+      <x:c r="E2" s="25"/>
       <x:c r="F2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="29" t="str">
+      <x:c r="A3" s="28" t="str">
         <x:v>核验等级</x:v>
       </x:c>
-      <x:c r="B3" s="29" t="str">
+      <x:c r="B3" s="28" t="str">
         <x:v>含义</x:v>
       </x:c>
-      <x:c r="C3" s="29"/>
-      <x:c r="D3" s="30" t="str">
+      <x:c r="C3" s="28"/>
+      <x:c r="D3" s="29" t="str">
         <x:v>行业分布（前15）</x:v>
       </x:c>
-      <x:c r="E3" s="31"/>
+      <x:c r="E3" s="30"/>
       <x:c r="F3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="26" t="str">
+      <x:c r="A4" s="25" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="B4" s="26" t="str">
+      <x:c r="B4" s="25" t="str">
         <x:v>已打开企业官网、官方招聘页、官方来源公告或国资委页面核验。</x:v>
       </x:c>
-      <x:c r="C4" s="26"/>
-      <x:c r="D4" s="32" t="str">
+      <x:c r="C4" s="25"/>
+      <x:c r="D4" s="31" t="str">
+        <x:v>半导体/IC设计</x:v>
+      </x:c>
+      <x:c r="E4" s="32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F4"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="25" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="B5" s="25" t="str">
+        <x:v>来自高校就业网、51job校园或官方来源转载；投递前仍需确认岗位是否静默关闭。</x:v>
+      </x:c>
+      <x:c r="C5" s="25"/>
+      <x:c r="D5" s="31" t="str">
         <x:v>互联网/AI</x:v>
       </x:c>
-      <x:c r="E4" s="33" t="n">
+      <x:c r="E5" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F4"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="26" t="str">
-        <x:v>B</x:v>
-      </x:c>
-      <x:c r="B5" s="26" t="str">
-        <x:v>来自高校就业网、51job校园或官方来源转载；投递前仍需确认岗位是否静默关闭。</x:v>
-      </x:c>
-      <x:c r="C5" s="26"/>
-      <x:c r="D5" s="32" t="str">
+      <x:c r="F5"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="25" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="B6" s="25" t="str">
+        <x:v>来自2026-07-21公开汇总；用于扩大覆盖面，必须通过企业官网二次确认。</x:v>
+      </x:c>
+      <x:c r="C6" s="25"/>
+      <x:c r="D6" s="31" t="str">
         <x:v>教育科技</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E6" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F5"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="26" t="str">
-        <x:v>C</x:v>
-      </x:c>
-      <x:c r="B6" s="26" t="str">
-        <x:v>来自2026-07-21公开汇总；用于扩大覆盖面，必须通过企业官网二次确认。</x:v>
-      </x:c>
-      <x:c r="C6" s="26"/>
-      <x:c r="D6" s="32" t="str">
+      <x:c r="F6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="25"/>
+      <x:c r="B7" s="25"/>
+      <x:c r="C7" s="25"/>
+      <x:c r="D7" s="31" t="str">
         <x:v>游戏/互联网</x:v>
       </x:c>
-      <x:c r="E6" s="33" t="n">
+      <x:c r="E7" s="32" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="F6"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="26"/>
-      <x:c r="B7" s="26"/>
-      <x:c r="C7" s="26"/>
-      <x:c r="D7" s="32" t="str">
-        <x:v>半导体/IC设计</x:v>
-      </x:c>
-      <x:c r="E7" s="33" t="n">
+      <x:c r="F7"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="28" t="str">
+        <x:v>重要说明</x:v>
+      </x:c>
+      <x:c r="B8" s="28"/>
+      <x:c r="C8" s="25"/>
+      <x:c r="D8" s="31" t="str">
+        <x:v>管理咨询</x:v>
+      </x:c>
+      <x:c r="E8" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F7"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="29" t="str">
-        <x:v>重要说明</x:v>
-      </x:c>
-      <x:c r="B8" s="29"/>
-      <x:c r="C8" s="26"/>
-      <x:c r="D8" s="32" t="str">
-        <x:v>管理咨询</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="n">
+      <x:c r="F8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="25" t="str">
+        <x:v>1. ‘官方未说明’不等于免笔试；只有公告明确写明免笔试/部分免笔试时才作肯定标注。</x:v>
+      </x:c>
+      <x:c r="B9" s="25"/>
+      <x:c r="C9" s="25"/>
+      <x:c r="D9" s="31" t="str">
+        <x:v>新能源汽车/智能汽车</x:v>
+      </x:c>
+      <x:c r="E9" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F8"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="26" t="str">
-        <x:v>1. ‘官方未说明’不等于免笔试；只有公告明确写明免笔试/部分免笔试时才作肯定标注。</x:v>
-      </x:c>
-      <x:c r="B9" s="26"/>
-      <x:c r="C9" s="26"/>
-      <x:c r="D9" s="32" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
-      </x:c>
-      <x:c r="E9" s="33" t="n">
+      <x:c r="F9"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="25" t="str">
+        <x:v>2. ‘招满即止’岗位可能没有公开截止日，并可能在无通知的情况下关闭。</x:v>
+      </x:c>
+      <x:c r="B10" s="25"/>
+      <x:c r="C10" s="25"/>
+      <x:c r="D10" s="31" t="str">
+        <x:v>游戏</x:v>
+      </x:c>
+      <x:c r="E10" s="32" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F9"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="26" t="str">
-        <x:v>2. ‘招满即止’岗位可能没有公开截止日，并可能在无通知的情况下关闭。</x:v>
-      </x:c>
-      <x:c r="B10" s="26"/>
-      <x:c r="C10" s="26"/>
-      <x:c r="D10" s="32" t="str">
-        <x:v>游戏</x:v>
-      </x:c>
-      <x:c r="E10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="F10"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="26" t="str">
+      <x:c r="A11" s="25" t="str">
         <x:v>3. 实习转正、训练营、校园大使、博士后/博士专项已在招聘类型和注意事项中单独标明。</x:v>
       </x:c>
-      <x:c r="B11" s="26"/>
-      <x:c r="C11" s="26"/>
-      <x:c r="D11" s="32" t="str">
+      <x:c r="B11" s="25"/>
+      <x:c r="C11" s="25"/>
+      <x:c r="D11" s="31" t="str">
+        <x:v>光电/科研</x:v>
+      </x:c>
+      <x:c r="E11" s="32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="25" t="str">
+        <x:v>4. 当前银行和大型央企正式秋招尚未全面启动，本表不使用上一届时间预测冒充已开放信息。</x:v>
+      </x:c>
+      <x:c r="B12" s="25"/>
+      <x:c r="C12" s="25"/>
+      <x:c r="D12" s="31" t="str">
         <x:v>光学/高端装备</x:v>
       </x:c>
-      <x:c r="E11" s="33" t="n">
+      <x:c r="E12" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F11"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="26" t="str">
-        <x:v>4. 当前银行和大型央企正式秋招尚未全面启动，本表不使用上一届时间预测冒充已开放信息。</x:v>
-      </x:c>
-      <x:c r="B12" s="26"/>
-      <x:c r="C12" s="26"/>
-      <x:c r="D12" s="32" t="str">
+      <x:c r="F12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="25" t="str">
+        <x:v>5. 工作地点与岗位汇总按项目级归纳，最终以具体职位JD为准。</x:v>
+      </x:c>
+      <x:c r="B13" s="25"/>
+      <x:c r="C13" s="25"/>
+      <x:c r="D13" s="31" t="str">
         <x:v>航天/军工</x:v>
       </x:c>
-      <x:c r="E12" s="33" t="n">
+      <x:c r="E13" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F12"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="26" t="str">
-        <x:v>5. 工作地点与岗位汇总按项目级归纳，最终以具体职位JD为准。</x:v>
-      </x:c>
-      <x:c r="B13" s="26"/>
-      <x:c r="C13" s="26"/>
-      <x:c r="D13" s="32" t="str">
+      <x:c r="F13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="25"/>
+      <x:c r="B14" s="25"/>
+      <x:c r="C14" s="25"/>
+      <x:c r="D14" s="31" t="str">
         <x:v>互联网/内容平台</x:v>
       </x:c>
-      <x:c r="E13" s="33" t="n">
+      <x:c r="E14" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F13"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="26"/>
-      <x:c r="B14" s="26"/>
-      <x:c r="C14" s="26"/>
-      <x:c r="D14" s="32" t="str">
+      <x:c r="F14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="25"/>
+      <x:c r="B15" s="25"/>
+      <x:c r="C15" s="25"/>
+      <x:c r="D15" s="31" t="str">
         <x:v>消费电子/智能终端</x:v>
       </x:c>
-      <x:c r="E14" s="33" t="n">
+      <x:c r="E15" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F14"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="26"/>
-      <x:c r="B15" s="26"/>
-      <x:c r="C15" s="26"/>
-      <x:c r="D15" s="32" t="str">
+      <x:c r="F15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="28" t="str">
+        <x:v>项目总数</x:v>
+      </x:c>
+      <x:c r="B16" s="28" t="n">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="C16" s="25"/>
+      <x:c r="D16" s="31" t="str">
+        <x:v>银行/金融</x:v>
+      </x:c>
+      <x:c r="E16" s="32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="28" t="str">
+        <x:v>有明确截止时间（未截止）</x:v>
+      </x:c>
+      <x:c r="B17" s="28" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C17" s="25"/>
+      <x:c r="D17" s="31" t="str">
         <x:v>证券/金融</x:v>
       </x:c>
-      <x:c r="E15" s="33" t="n">
+      <x:c r="E17" s="32" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F15"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="29" t="str">
-        <x:v>项目总数</x:v>
-      </x:c>
-      <x:c r="B16" s="29" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C16" s="26"/>
-      <x:c r="D16" s="32" t="str">
+      <x:c r="F17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="28" t="str">
+        <x:v>A等级</x:v>
+      </x:c>
+      <x:c r="B18" s="28" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C18" s="25"/>
+      <x:c r="D18" s="31" t="str">
         <x:v>半导体/模拟IC</x:v>
       </x:c>
-      <x:c r="E16" s="33" t="n">
+      <x:c r="E18" s="32" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F16"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="29" t="str">
-        <x:v>有明确截止时间（未截止）</x:v>
-      </x:c>
-      <x:c r="B17" s="29" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C17" s="26"/>
-      <x:c r="D17" s="32" t="str">
-        <x:v>半导体/通信</x:v>
-      </x:c>
-      <x:c r="E17" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F17"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="29" t="str">
-        <x:v>A等级</x:v>
-      </x:c>
-      <x:c r="B18" s="29" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C18" s="26"/>
-      <x:c r="D18" s="32" t="str">
-        <x:v>半导体/IP设计</x:v>
-      </x:c>
-      <x:c r="E18" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="F18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="29" t="str">
+      <x:c r="A19" s="28" t="str">
         <x:v>B等级</x:v>
       </x:c>
-      <x:c r="B19" s="29" t="n">
+      <x:c r="B19" s="28" t="n">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C19" s="26"/>
-      <x:c r="D19" s="32"/>
-      <x:c r="E19" s="33"/>
+      <x:c r="C19" s="25"/>
+      <x:c r="D19" s="31"/>
+      <x:c r="E19" s="32"/>
       <x:c r="F19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="29" t="str">
+      <x:c r="A20" s="28" t="str">
         <x:v>C等级</x:v>
       </x:c>
-      <x:c r="B20" s="29" t="n">
+      <x:c r="B20" s="28" t="n">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="C20" s="26"/>
-      <x:c r="D20" s="34"/>
-      <x:c r="E20" s="35"/>
+      <x:c r="C20" s="25"/>
+      <x:c r="D20" s="33"/>
+      <x:c r="E20" s="34"/>
       <x:c r="F20"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="26"/>
-      <x:c r="B21" s="26"/>
-      <x:c r="C21" s="26"/>
-      <x:c r="D21" s="26"/>
-      <x:c r="E21" s="26"/>
+      <x:c r="A21" s="25"/>
+      <x:c r="B21" s="25"/>
+      <x:c r="C21" s="25"/>
+      <x:c r="D21" s="25"/>
+      <x:c r="E21" s="25"/>
       <x:c r="F21"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="26" t="str">
+      <x:c r="A22" s="25" t="str">
         <x:v>本次更新</x:v>
       </x:c>
-      <x:c r="B22" s="26" t="str">
-        <x:v>2项新增；更新3项截止/来源/状态；关闭0项；未来7天内明确截止2项；京东TET截止日按官网更正为2026-11-30。</x:v>
-      </x:c>
-      <x:c r="C22" s="26"/>
-      <x:c r="D22" s="26"/>
-      <x:c r="E22" s="26"/>
+      <x:c r="B22" s="25" t="str">
+        <x:v>新增2项；关闭4项；未来7天内明确截止1项；新增项目均已打开企业官方招聘系统核验，未核验到开放职位的候选未纳入。</x:v>
+      </x:c>
+      <x:c r="C22" s="25"/>
+      <x:c r="D22" s="25"/>
+      <x:c r="E22" s="25"/>
       <x:c r="F22"/>
     </x:row>
   </x:sheetData>

--- a/2027届秋招投递信息_2026-07-24.xlsx
+++ b/2027届秋招投递信息_2026-07-24.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R1fd41a20ef1546d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="Rd22248b77c5446b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="R39cb9e3f4a6f45f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R749d57a1ba014186"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="R7f0c4d5993cd48f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="Rc853f8092b164847"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -83,12 +83,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF4CCCC"/>
+        <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE2F0D9"/>
+        <x:fgColor rgb="FFF4CCCC"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -235,13 +235,13 @@
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -301,8 +301,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q107" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:Q107"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q108" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:Q108"/>
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="开放投递时间"/>
     <x:tableColumn id="2" name="企业名称"/>
@@ -568,7 +568,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>2027届秋招投递信息（截至2026-08-03）</x:v>
+        <x:v>2027届秋招投递信息（截至2026-08-04）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -589,7 +589,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>每日更新：按开放时间倒序；本轮新增2项官方核验项目，关闭4项；第三方汇总入口不作为立即投递链接。</x:v>
+        <x:v>每日更新：按开放时间倒序；本轮新增1项官方核验项目，关闭0项；第三方汇总入口不作为立即投递链接。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -662,109 +662,109 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
-      <x:c r="A4" s="14" t="str">
+      <x:c r="A4" s="4" t="str">
+        <x:v>2026-08-01</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="str">
+        <x:v>影石Insta360</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="str">
+        <x:v>消费电子/智能影像</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="str">
+        <x:v>深圳、上海、珠海</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="str">
+        <x:v>正式批/秋招</x:v>
+      </x:c>
+      <x:c r="G4" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H4" s="4" t="str">
+        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+      </x:c>
+      <x:c r="I4" s="15" t="str">
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
+      </x:c>
+      <x:c r="J4" s="4" t="str">
+        <x:v>2026-10-31</x:v>
+      </x:c>
+      <x:c r="K4" s="4" t="str">
+        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
+      </x:c>
+      <x:c r="L4" s="4" t="str">
+        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
+      </x:c>
+      <x:c r="M4" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N4" s="4" t="str">
+        <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
+      </x:c>
+      <x:c r="O4" s="15" t="str">
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
+      </x:c>
+      <x:c r="P4" s="14" t="str">
+        <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
+      </x:c>
+      <x:c r="Q4" s="4" t="str">
+        <x:v>2026-08-04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="16" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
-      <x:c r="B4" s="14" t="str">
+      <x:c r="B5" s="16" t="str">
         <x:v>恒丰银行总行-雏鹰计划</x:v>
       </x:c>
-      <x:c r="C4" s="14" t="str">
+      <x:c r="C5" s="16" t="str">
         <x:v>银行/金融</x:v>
       </x:c>
-      <x:c r="D4" s="14" t="str">
+      <x:c r="D5" s="16" t="str">
         <x:v>股份制商业银行</x:v>
       </x:c>
-      <x:c r="E4" s="14" t="str">
+      <x:c r="E5" s="16" t="str">
         <x:v>总行及相关机构，以岗位页为准</x:v>
       </x:c>
-      <x:c r="F4" s="14" t="str">
+      <x:c r="F5" s="16" t="str">
         <x:v>暑期实习/秋招储备</x:v>
       </x:c>
-      <x:c r="G4" s="14" t="str">
+      <x:c r="G5" s="16" t="str">
         <x:v>2027届硕士及以上，以公告要求为准</x:v>
       </x:c>
-      <x:c r="H4" s="14" t="str">
+      <x:c r="H5" s="16" t="str">
         <x:v>总行实习生，具体专业和方向以官方公告为准</x:v>
       </x:c>
-      <x:c r="I4" s="16" t="str">
+      <x:c r="I5" s="17" t="str">
         <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
       </x:c>
-      <x:c r="J4" s="14" t="str">
+      <x:c r="J5" s="16" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
-      <x:c r="K4" s="14" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L4" s="14" t="str">
+      <x:c r="K5" s="16" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L5" s="16" t="str">
         <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
       </x:c>
-      <x:c r="M4" s="14" t="str">
+      <x:c r="M5" s="16" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N4" s="14" t="str">
+      <x:c r="N5" s="16" t="str">
         <x:v>官方公告显示7月31日24:00截止，实习期安排和具体岗位以恒丰银行招聘官网为准。</x:v>
       </x:c>
-      <x:c r="O4" s="16" t="str">
+      <x:c r="O5" s="17" t="str">
         <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
       </x:c>
-      <x:c r="P4" s="15" t="str">
+      <x:c r="P5" s="14" t="str">
         <x:v>A-企业官方招聘公告已核验</x:v>
       </x:c>
-      <x:c r="Q4" s="14" t="str">
+      <x:c r="Q5" s="16" t="str">
         <x:v>2026-08-03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="54" customHeight="1">
-      <x:c r="A5" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B5" s="4" t="str">
-        <x:v>四方股份</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="str">
-        <x:v>电力系统/工业自动化</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="str">
-        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
-      </x:c>
-      <x:c r="F5" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G5" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H5" s="4" t="str">
-        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
-      </x:c>
-      <x:c r="I5" s="17" t="str">
-        <x:v>https://www.sf-auto.com/campus</x:v>
-      </x:c>
-      <x:c r="J5" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K5" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L5" s="4" t="str">
-        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="M5" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N5" s="4" t="str">
-        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
-      </x:c>
-      <x:c r="O5" s="17" t="str">
-        <x:v>https://www.sf-auto.com/campus</x:v>
-      </x:c>
-      <x:c r="P5" s="15" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="Q5" s="4" t="str">
-        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
@@ -772,28 +772,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>苏纳光电</x:v>
+        <x:v>四方股份</x:v>
       </x:c>
       <x:c r="C6" s="4" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>电力系统/工业自动化</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
-        <x:v>苏州、上海</x:v>
+        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
       </x:c>
       <x:c r="F6" s="4" t="str">
-        <x:v>提前批/Open Day</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G6" s="4" t="str">
-        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H6" s="4" t="str">
-        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
-      </x:c>
-      <x:c r="I6" s="17" t="str">
-        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
+      </x:c>
+      <x:c r="I6" s="15" t="str">
+        <x:v>https://www.sf-auto.com/campus</x:v>
       </x:c>
       <x:c r="J6" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -802,19 +802,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L6" s="4" t="str">
-        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
+        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="M6" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N6" s="4" t="str">
-        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
-      </x:c>
-      <x:c r="O6" s="17" t="str">
-        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
-      </x:c>
-      <x:c r="P6" s="15" t="str">
-        <x:v>A-企业官方校园招聘系统已核验</x:v>
+        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O6" s="15" t="str">
+        <x:v>https://www.sf-auto.com/campus</x:v>
+      </x:c>
+      <x:c r="P6" s="14" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="Q6" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -825,28 +825,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>特斯拉中国</x:v>
+        <x:v>苏纳光电</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
-        <x:v>新能源汽车/智能制造</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>外资/上市</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
+        <x:v>苏州、上海</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批/Open Day</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
-        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
+        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
-      </x:c>
-      <x:c r="I7" s="17" t="str">
-        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
+        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
+      </x:c>
+      <x:c r="I7" s="15" t="str">
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -855,128 +855,128 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L7" s="4" t="str">
-        <x:v>本轮新确认；企业官方职位页已核验</x:v>
+        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
       </x:c>
       <x:c r="M7" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N7" s="4" t="str">
-        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
-      </x:c>
-      <x:c r="O7" s="17" t="str">
-        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
-      </x:c>
-      <x:c r="P7" s="15" t="str">
-        <x:v>A-企业官方职位页已核验</x:v>
+        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
+      </x:c>
+      <x:c r="O7" s="15" t="str">
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+      </x:c>
+      <x:c r="P7" s="14" t="str">
+        <x:v>A-企业官方校园招聘系统已核验</x:v>
       </x:c>
       <x:c r="Q7" s="4" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="14" t="str">
+      <x:c r="A8" s="4" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
-      <x:c r="B8" s="14" t="str">
+      <x:c r="B8" s="4" t="str">
+        <x:v>特斯拉中国</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="str">
+        <x:v>新能源汽车/智能制造</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="str">
+        <x:v>外资/上市</x:v>
+      </x:c>
+      <x:c r="E8" s="4" t="str">
+        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
+      </x:c>
+      <x:c r="F8" s="4" t="str">
+        <x:v>正式批/校园招聘</x:v>
+      </x:c>
+      <x:c r="G8" s="4" t="str">
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H8" s="4" t="str">
+        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
+      </x:c>
+      <x:c r="I8" s="15" t="str">
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
+      </x:c>
+      <x:c r="J8" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K8" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L8" s="4" t="str">
+        <x:v>本轮新确认；企业官方职位页已核验</x:v>
+      </x:c>
+      <x:c r="M8" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N8" s="4" t="str">
+        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
+      </x:c>
+      <x:c r="O8" s="15" t="str">
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
+      </x:c>
+      <x:c r="P8" s="14" t="str">
+        <x:v>A-企业官方职位页已核验</x:v>
+      </x:c>
+      <x:c r="Q8" s="4" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="16" t="str">
+        <x:v>不晚于2026-07-30</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="str">
         <x:v>天健会计师事务所-暑期实习培训生</x:v>
       </x:c>
-      <x:c r="C8" s="14" t="str">
+      <x:c r="C9" s="16" t="str">
         <x:v>会计审计/专业服务</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="str">
+      <x:c r="D9" s="16" t="str">
         <x:v>会计师事务所</x:v>
       </x:c>
-      <x:c r="E8" s="14" t="str">
+      <x:c r="E9" s="16" t="str">
         <x:v>上海等，以职位页为准</x:v>
       </x:c>
-      <x:c r="F8" s="14" t="str">
+      <x:c r="F9" s="16" t="str">
         <x:v>暑期实习/培训生</x:v>
       </x:c>
-      <x:c r="G8" s="14" t="str">
+      <x:c r="G9" s="16" t="str">
         <x:v>2027届应届毕业生，以岗位要求为准</x:v>
       </x:c>
-      <x:c r="H8" s="14" t="str">
+      <x:c r="H9" s="16" t="str">
         <x:v>财务审计暑期实习培训生</x:v>
       </x:c>
-      <x:c r="I8" s="16" t="str">
+      <x:c r="I9" s="17" t="str">
         <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="str">
+      <x:c r="J9" s="16" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
-      <x:c r="K8" s="14" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L8" s="14" t="str">
+      <x:c r="K9" s="16" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L9" s="16" t="str">
         <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
       </x:c>
-      <x:c r="M8" s="14" t="str">
+      <x:c r="M9" s="16" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N8" s="14" t="str">
+      <x:c r="N9" s="16" t="str">
         <x:v>公开公告显示7月31日截止；具体办公地点、专业要求和实习安排以天健招聘官网为准。</x:v>
       </x:c>
-      <x:c r="O8" s="16" t="str">
+      <x:c r="O9" s="17" t="str">
         <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
       </x:c>
-      <x:c r="P8" s="15" t="str">
+      <x:c r="P9" s="14" t="str">
         <x:v>A-企业官方招聘入口已核验</x:v>
       </x:c>
-      <x:c r="Q8" s="14" t="str">
+      <x:c r="Q9" s="16" t="str">
         <x:v>2026-08-03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="54" customHeight="1">
-      <x:c r="A9" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B9" s="4" t="str">
-        <x:v>西安紫光国芯半导体</x:v>
-      </x:c>
-      <x:c r="C9" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
-      </x:c>
-      <x:c r="E9" s="4" t="str">
-        <x:v>西安、上海、成都</x:v>
-      </x:c>
-      <x:c r="F9" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
-      </x:c>
-      <x:c r="G9" s="4" t="str">
-        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H9" s="4" t="str">
-        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
-      </x:c>
-      <x:c r="I9" s="17" t="str">
-        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
-      </x:c>
-      <x:c r="J9" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K9" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="str">
-        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
-      </x:c>
-      <x:c r="M9" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N9" s="4" t="str">
-        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
-      </x:c>
-      <x:c r="O9" s="17" t="str">
-        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
-      </x:c>
-      <x:c r="P9" s="15" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
-      </x:c>
-      <x:c r="Q9" s="4" t="str">
-        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
@@ -984,28 +984,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B10" s="4" t="str">
-        <x:v>新大陆自动识别</x:v>
+        <x:v>西安紫光国芯半导体</x:v>
       </x:c>
       <x:c r="C10" s="4" t="str">
-        <x:v>计算机视觉/智能硬件</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
-        <x:v>民营/上市公司子公司</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>福州总部及全国/海外岗位</x:v>
+        <x:v>西安、上海、成都</x:v>
       </x:c>
       <x:c r="F10" s="4" t="str">
         <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
+        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
-      </x:c>
-      <x:c r="I10" s="17" t="str">
-        <x:v>https://nlscan.zhiye.com/Campus</x:v>
+        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
+      </x:c>
+      <x:c r="I10" s="15" t="str">
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
       </x:c>
       <x:c r="J10" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1014,19 +1014,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L10" s="4" t="str">
-        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
+        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
       </x:c>
       <x:c r="M10" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N10" s="4" t="str">
-        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
-      </x:c>
-      <x:c r="O10" s="17" t="str">
-        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
-      </x:c>
-      <x:c r="P10" s="15" t="str">
-        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
+        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
+      </x:c>
+      <x:c r="O10" s="15" t="str">
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
+      </x:c>
+      <x:c r="P10" s="14" t="str">
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q10" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1037,49 +1037,49 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B11" s="4" t="str">
-        <x:v>影石Insta360</x:v>
+        <x:v>新大陆自动识别</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
-        <x:v>消费电子/智能影像</x:v>
+        <x:v>计算机视觉/智能硬件</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/上市公司子公司</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>深圳、上海、珠海</x:v>
+        <x:v>福州总部及全国/海外岗位</x:v>
       </x:c>
       <x:c r="F11" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
-      </x:c>
-      <x:c r="I11" s="17" t="str">
-        <x:v>https://www.insta360.com/cn/jobs</x:v>
+        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
+      </x:c>
+      <x:c r="I11" s="15" t="str">
+        <x:v>https://nlscan.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
-        <x:v>2026-10-31</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K11" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L11" s="4" t="str">
-        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
+        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
       </x:c>
       <x:c r="M11" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N11" s="4" t="str">
-        <x:v>岗位城市和具体职位以影石Insta360官方招聘页为准；公开信息标注10月31日，投递前再次确认职位状态。</x:v>
-      </x:c>
-      <x:c r="O11" s="17" t="str">
-        <x:v>https://www.insta360.com/cn/jobs</x:v>
-      </x:c>
-      <x:c r="P11" s="15" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
+        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
+      </x:c>
+      <x:c r="O11" s="15" t="str">
+        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
+      </x:c>
+      <x:c r="P11" s="14" t="str">
+        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
       </x:c>
       <x:c r="Q11" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1110,7 +1110,7 @@
       <x:c r="H12" s="4" t="str">
         <x:v>芯片设计、验证、嵌入式、软件、应用、测试及职能岗位</x:v>
       </x:c>
-      <x:c r="I12" s="17" t="str">
+      <x:c r="I12" s="15" t="str">
         <x:v>https://www.gigadevice.com.cn/about/career</x:v>
       </x:c>
       <x:c r="J12" s="4" t="str">
@@ -1128,10 +1128,10 @@
       <x:c r="N12" s="4" t="str">
         <x:v>提前批岗位和城市以兆易创新官方加入我们页面为准，投递前确认职位仍开放。</x:v>
       </x:c>
-      <x:c r="O12" s="17" t="str">
+      <x:c r="O12" s="15" t="str">
         <x:v>https://www.gigadevice.com.cn/about/career</x:v>
       </x:c>
-      <x:c r="P12" s="15" t="str">
+      <x:c r="P12" s="14" t="str">
         <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q12" s="4" t="str">
@@ -1163,7 +1163,7 @@
       <x:c r="H13" s="4" t="str">
         <x:v>研发设计、工艺、试验、制造、材料、控制、软件及管理岗位</x:v>
       </x:c>
-      <x:c r="I13" s="17" t="str">
+      <x:c r="I13" s="15" t="str">
         <x:v>https://aecc.iguopin.com/notice2</x:v>
       </x:c>
       <x:c r="J13" s="4" t="str">
@@ -1181,10 +1181,10 @@
       <x:c r="N13" s="4" t="str">
         <x:v>各单位岗位和截止时间不同，需在中国航发招聘平台按单位和专业筛选。</x:v>
       </x:c>
-      <x:c r="O13" s="17" t="str">
+      <x:c r="O13" s="15" t="str">
         <x:v>http://www.sasac.gov.cn/n2588035/n2588325/n2588350/c35693219/content.html</x:v>
       </x:c>
-      <x:c r="P13" s="15" t="str">
+      <x:c r="P13" s="14" t="str">
         <x:v>A-国资委公告与集团招聘平台交叉核验</x:v>
       </x:c>
       <x:c r="Q13" s="4" t="str">
@@ -1216,7 +1216,7 @@
       <x:c r="H14" s="4" t="str">
         <x:v>金融、投资、风险、运营、人力资源及综合管理方向</x:v>
       </x:c>
-      <x:c r="I14" s="17" t="str">
+      <x:c r="I14" s="15" t="str">
         <x:v>http://www.cofco-capital.com/join_us.html</x:v>
       </x:c>
       <x:c r="J14" s="4" t="str">
@@ -1234,10 +1234,10 @@
       <x:c r="N14" s="4" t="str">
         <x:v>粮曦计划具体批次、面向人群和岗位以中粮资本官方加入我们页面及公告为准。</x:v>
       </x:c>
-      <x:c r="O14" s="17" t="str">
+      <x:c r="O14" s="15" t="str">
         <x:v>http://www.cofco-capital.com/join_us.html</x:v>
       </x:c>
-      <x:c r="P14" s="15" t="str">
+      <x:c r="P14" s="14" t="str">
         <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q14" s="4" t="str">
@@ -1269,7 +1269,7 @@
       <x:c r="H15" s="4" t="str">
         <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
       </x:c>
-      <x:c r="I15" s="17" t="str">
+      <x:c r="I15" s="15" t="str">
         <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="J15" s="4" t="str">
@@ -1287,10 +1287,10 @@
       <x:c r="N15" s="4" t="str">
         <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
       </x:c>
-      <x:c r="O15" s="17" t="str">
+      <x:c r="O15" s="15" t="str">
         <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
-      <x:c r="P15" s="15" t="str">
+      <x:c r="P15" s="14" t="str">
         <x:v>A-中国移动官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="Q15" s="4" t="str">
@@ -1322,7 +1322,7 @@
       <x:c r="H16" s="4" t="str">
         <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
-      <x:c r="I16" s="17" t="str">
+      <x:c r="I16" s="15" t="str">
         <x:v>https://zyjob.hotjob.cn/</x:v>
       </x:c>
       <x:c r="J16" s="4" t="str">
@@ -1340,10 +1340,10 @@
       <x:c r="N16" s="4" t="str">
         <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
       </x:c>
-      <x:c r="O16" s="17" t="str">
+      <x:c r="O16" s="15" t="str">
         <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
       </x:c>
-      <x:c r="P16" s="15" t="str">
+      <x:c r="P16" s="14" t="str">
         <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
       </x:c>
       <x:c r="Q16" s="4" t="str">
@@ -1352,84 +1352,84 @@
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>我乐家居</x:v>
+        <x:v>搜狐畅游</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
-        <x:v>家居/消费品/智能制造</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/互联网</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>以岗位页面为准</x:v>
       </x:c>
       <x:c r="F17" s="4" t="str">
         <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>2027届本科及以上，以岗位要求为准</x:v>
+        <x:v>2027届毕业生（部分岗位兼收2026届）</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
-      </x:c>
-      <x:c r="I17" s="17" t="str">
-        <x:v>https://olo-home.zhiye.com/Campus</x:v>
+        <x:v>游戏策划、游戏开发、游戏美术、游戏运营、业务支持、平台开发、平台职能、游戏测试8大类岗位</x:v>
+      </x:c>
+      <x:c r="I17" s="15" t="str">
+        <x:v>https://app.mokahr.com/m/campus_apply/cyou-inc/42233?recommendCode=DSRgNQU7#/jobs</x:v>
       </x:c>
       <x:c r="J17" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K17" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>非免笔试；提前批未录取可参加后续统一笔试</x:v>
       </x:c>
       <x:c r="L17" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
+        <x:v>可信高校就业网公告显示开放；官方投递入口已核验</x:v>
       </x:c>
       <x:c r="M17" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N17" s="4" t="str">
-        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
-      </x:c>
-      <x:c r="O17" s="17" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
+        <x:v>深圳北理莫斯科大学就业网公告《搜狐畅游2027届秋季校园招聘提前批正式启动！》发布于2026-07-28；提前批流程快、部分岗位有直通面试机会，未被录取者可参与后续统一笔试，部分热招岗位招满即停。</x:v>
+      </x:c>
+      <x:c r="O17" s="15" t="str">
+        <x:v>https://career.smbu.edu.cn/detail/online?id=3535355</x:v>
       </x:c>
       <x:c r="P17" s="18" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
+        <x:v>B-可信高校就业网公告含官方投递链接</x:v>
       </x:c>
       <x:c r="Q17" s="4" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="4" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="B18" s="4" t="str">
-        <x:v>轩宇信息</x:v>
+        <x:v>我乐家居</x:v>
       </x:c>
       <x:c r="C18" s="4" t="str">
-        <x:v>航天/军工信息化/软件</x:v>
+        <x:v>家居/消费品/智能制造</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
-        <x:v>央企子公司/高新技术企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>北京、杭州、西安</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F18" s="4" t="str">
-        <x:v>AI专项/提前批</x:v>
+        <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届本科及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
-      </x:c>
-      <x:c r="I18" s="17" t="str">
-        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
+        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
+      </x:c>
+      <x:c r="I18" s="15" t="str">
+        <x:v>https://olo-home.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J18" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1438,19 +1438,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L18" s="4" t="str">
-        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
       </x:c>
       <x:c r="M18" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N18" s="4" t="str">
-        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
-      </x:c>
-      <x:c r="O18" s="17" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P18" s="15" t="str">
-        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
+        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
+      </x:c>
+      <x:c r="O18" s="15" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P18" s="18" t="str">
+        <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
       <x:c r="Q18" s="4" t="str">
         <x:v>2026-07-29</x:v>
@@ -1458,31 +1458,31 @@
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>卡尔动力</x:v>
+        <x:v>轩宇信息</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>自动驾驶/智能汽车</x:v>
+        <x:v>航天/军工信息化/软件</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>央企子公司/高新技术企业</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>北京、上海、天津等</x:v>
+        <x:v>北京、杭州、西安</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>AI专项/提前批</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
         <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
-      </x:c>
-      <x:c r="I19" s="17" t="str">
-        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
+        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
+      </x:c>
+      <x:c r="I19" s="15" t="str">
+        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1491,22 +1491,22 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L19" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
+        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
       </x:c>
       <x:c r="M19" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N19" s="4" t="str">
-        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
-      </x:c>
-      <x:c r="O19" s="17" t="str">
-        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
-      </x:c>
-      <x:c r="P19" s="18" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
+        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
+      </x:c>
+      <x:c r="O19" s="15" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P19" s="14" t="str">
+        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
       </x:c>
       <x:c r="Q19" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
@@ -1514,49 +1514,49 @@
         <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
-        <x:v>深信服-X-STAR顶尖人才计划</x:v>
+        <x:v>卡尔动力</x:v>
       </x:c>
       <x:c r="C20" s="4" t="str">
-        <x:v>网络安全/云计算/软件</x:v>
+        <x:v>自动驾驶/智能汽车</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
+        <x:v>北京、上海、天津等</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>顶尖人才，本硕博按岗位要求</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
-      </x:c>
-      <x:c r="I20" s="17" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
+        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
+      </x:c>
+      <x:c r="I20" s="15" t="str">
+        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
-        <x:v>2026-09-25</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K20" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L20" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
       </x:c>
       <x:c r="M20" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N20" s="4" t="str">
-        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
-      </x:c>
-      <x:c r="O20" s="17" t="str">
-        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
-      </x:c>
-      <x:c r="P20" s="15" t="str">
-        <x:v>A-高校就业网含官方投递链接</x:v>
+        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
+      </x:c>
+      <x:c r="O20" s="15" t="str">
+        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
+      </x:c>
+      <x:c r="P20" s="18" t="str">
+        <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
       <x:c r="Q20" s="4" t="str">
         <x:v>2026-07-27</x:v>
@@ -1567,49 +1567,49 @@
         <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B21" s="4" t="str">
-        <x:v>希夕智能</x:v>
+        <x:v>深信服-X-STAR顶尖人才计划</x:v>
       </x:c>
       <x:c r="C21" s="4" t="str">
-        <x:v>机器人/智能制造</x:v>
+        <x:v>网络安全/云计算/软件</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F21" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>2027届本科及以上</x:v>
+        <x:v>顶尖人才，本硕博按岗位要求</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
-      </x:c>
-      <x:c r="I21" s="17" t="str">
-        <x:v>https://sunseed.zhiye.com/jobs</x:v>
+        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
+      </x:c>
+      <x:c r="I21" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
       </x:c>
       <x:c r="J21" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-09-25</x:v>
       </x:c>
       <x:c r="K21" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L21" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M21" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N21" s="4" t="str">
-        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
-      </x:c>
-      <x:c r="O21" s="17" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
-      </x:c>
-      <x:c r="P21" s="18" t="str">
-        <x:v>B-高校就业平台转载企业来源</x:v>
+        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
+      </x:c>
+      <x:c r="O21" s="15" t="str">
+        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
+      </x:c>
+      <x:c r="P21" s="14" t="str">
+        <x:v>A-高校就业网含官方投递链接</x:v>
       </x:c>
       <x:c r="Q21" s="4" t="str">
         <x:v>2026-07-27</x:v>
@@ -1617,108 +1617,108 @@
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="4" t="str">
-        <x:v>不晚于2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B22" s="4" t="str">
-        <x:v>中国兵器工业集团</x:v>
+        <x:v>希夕智能</x:v>
       </x:c>
       <x:c r="C22" s="4" t="str">
-        <x:v>军工/高端装备</x:v>
+        <x:v>机器人/智能制造</x:v>
       </x:c>
       <x:c r="D22" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F22" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科及以上</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
-      </x:c>
-      <x:c r="I22" s="17" t="str">
-        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
+        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
+      </x:c>
+      <x:c r="I22" s="15" t="str">
+        <x:v>https://sunseed.zhiye.com/jobs</x:v>
       </x:c>
       <x:c r="J22" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K22" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L22" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
       </x:c>
       <x:c r="M22" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N22" s="4" t="str">
-        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
-      </x:c>
-      <x:c r="O22" s="17" t="str">
-        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
+        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
+      </x:c>
+      <x:c r="O22" s="15" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
       </x:c>
       <x:c r="P22" s="18" t="str">
-        <x:v>B-公开招聘公告/集团入口</x:v>
+        <x:v>B-高校就业平台转载企业来源</x:v>
       </x:c>
       <x:c r="Q22" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="4" t="str">
-        <x:v>2026-07-23</x:v>
+        <x:v>不晚于2026-07-24</x:v>
       </x:c>
       <x:c r="B23" s="4" t="str">
-        <x:v>禾迈股份</x:v>
+        <x:v>中国兵器工业集团</x:v>
       </x:c>
       <x:c r="C23" s="4" t="str">
-        <x:v>光伏/电力电子</x:v>
+        <x:v>军工/高端装备</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>杭州等，以岗位页为准</x:v>
+        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
       </x:c>
       <x:c r="F23" s="4" t="str">
-        <x:v>研发类提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
-      </x:c>
-      <x:c r="I23" s="17" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
+        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
+      </x:c>
+      <x:c r="I23" s="15" t="str">
+        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
       </x:c>
       <x:c r="J23" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K23" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L23" s="4" t="str">
-        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M23" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N23" s="4" t="str">
-        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
-      </x:c>
-      <x:c r="O23" s="17" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
+        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
+      </x:c>
+      <x:c r="O23" s="15" t="str">
+        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
       </x:c>
       <x:c r="P23" s="18" t="str">
-        <x:v>B-高校就业网转载企业公告</x:v>
+        <x:v>B-公开招聘公告/集团入口</x:v>
       </x:c>
       <x:c r="Q23" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
@@ -1726,28 +1726,28 @@
         <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B24" s="4" t="str">
-        <x:v>极客未来</x:v>
+        <x:v>禾迈股份</x:v>
       </x:c>
       <x:c r="C24" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>光伏/电力电子</x:v>
       </x:c>
       <x:c r="D24" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>四川、重庆、广东</x:v>
+        <x:v>杭州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F24" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>研发类提前批</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
-      </x:c>
-      <x:c r="I24" s="17" t="str">
-        <x:v>https://geek3.zhiye.com/campus/</x:v>
+        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
+      </x:c>
+      <x:c r="I24" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
       </x:c>
       <x:c r="J24" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1756,128 +1756,128 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L24" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
+        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
       </x:c>
       <x:c r="M24" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N24" s="4" t="str">
-        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
-      </x:c>
-      <x:c r="O24" s="17" t="str">
-        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
+        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
+      </x:c>
+      <x:c r="O24" s="15" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
       </x:c>
       <x:c r="P24" s="18" t="str">
-        <x:v>B-高校就业网公告+公开招聘页面</x:v>
+        <x:v>B-高校就业网转载企业公告</x:v>
       </x:c>
       <x:c r="Q24" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
       <x:c r="A25" s="4" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B25" s="4" t="str">
-        <x:v>安永EY</x:v>
+        <x:v>极客未来</x:v>
       </x:c>
       <x:c r="C25" s="4" t="str">
-        <x:v>会计审计/咨询/专业服务</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
-        <x:v>外资/专业服务机构</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>中国内地多地，以职位页为准</x:v>
+        <x:v>四川、重庆、广东</x:v>
       </x:c>
       <x:c r="F25" s="4" t="str">
-        <x:v>正式批/秋季校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
-      </x:c>
-      <x:c r="I25" s="17" t="str">
-        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
+        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+      </x:c>
+      <x:c r="I25" s="15" t="str">
+        <x:v>https://geek3.zhiye.com/campus/</x:v>
       </x:c>
       <x:c r="J25" s="4" t="str">
-        <x:v>2026年10月（具体日期未公布）</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K25" s="4" t="str">
-        <x:v>否；官方流程包含在线测评</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L25" s="4" t="str">
-        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
+        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
       </x:c>
       <x:c r="M25" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N25" s="4" t="str">
-        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
-      </x:c>
-      <x:c r="O25" s="17" t="str">
-        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
-      </x:c>
-      <x:c r="P25" s="15" t="str">
-        <x:v>A-企业官方校招网站与职位页已核验</x:v>
+        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
+      </x:c>
+      <x:c r="O25" s="15" t="str">
+        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
+      </x:c>
+      <x:c r="P25" s="18" t="str">
+        <x:v>B-高校就业网公告+公开招聘页面</x:v>
       </x:c>
       <x:c r="Q25" s="4" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="54" customHeight="1">
       <x:c r="A26" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="B26" s="4" t="str">
-        <x:v>阿里巴巴-阿里星计划</x:v>
+        <x:v>安永EY</x:v>
       </x:c>
       <x:c r="C26" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>会计审计/咨询/专业服务</x:v>
       </x:c>
       <x:c r="D26" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>外资/专业服务机构</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>杭州、北京、上海、深圳等</x:v>
+        <x:v>中国内地多地，以职位页为准</x:v>
       </x:c>
       <x:c r="F26" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
-      </x:c>
-      <x:c r="I26" s="17" t="str">
-        <x:v>https://talent.alibaba.com/campus/</x:v>
+        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
+      </x:c>
+      <x:c r="I26" s="15" t="str">
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
       </x:c>
       <x:c r="J26" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026年10月（具体日期未公布）</x:v>
       </x:c>
       <x:c r="K26" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；官方流程包含在线测评</x:v>
       </x:c>
       <x:c r="L26" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
       </x:c>
       <x:c r="M26" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N26" s="4" t="str">
-        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
-      </x:c>
-      <x:c r="O26" s="17" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P26" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
+      </x:c>
+      <x:c r="O26" s="15" t="str">
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
+      </x:c>
+      <x:c r="P26" s="14" t="str">
+        <x:v>A-企业官方校招网站与职位页已核验</x:v>
       </x:c>
       <x:c r="Q26" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="54" customHeight="1">
@@ -1885,34 +1885,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B27" s="4" t="str">
-        <x:v>贝恩公司</x:v>
+        <x:v>阿里巴巴-阿里星计划</x:v>
       </x:c>
       <x:c r="C27" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D27" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>北京、上海、香港等</x:v>
+        <x:v>杭州、北京、上海、深圳等</x:v>
       </x:c>
       <x:c r="F27" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>助理咨询顾问等</x:v>
-      </x:c>
-      <x:c r="I27" s="17" t="str">
-        <x:v>https://www.bain.com/careers/</x:v>
+        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
+      </x:c>
+      <x:c r="I27" s="15" t="str">
+        <x:v>https://talent.alibaba.com/campus/</x:v>
       </x:c>
       <x:c r="J27" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K27" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L27" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -1920,8 +1920,10 @@
       <x:c r="M27" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N27" s="4" t="str"/>
-      <x:c r="O27" s="17" t="str">
+      <x:c r="N27" s="4" t="str">
+        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
+      </x:c>
+      <x:c r="O27" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P27" s="19" t="str">
@@ -1936,34 +1938,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B28" s="4" t="str">
-        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
+        <x:v>贝恩公司</x:v>
       </x:c>
       <x:c r="C28" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D28" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>上海、北京等</x:v>
+        <x:v>北京、上海、香港等</x:v>
       </x:c>
       <x:c r="F28" s="4" t="str">
-        <x:v>顶尖技术专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
-      </x:c>
-      <x:c r="I28" s="17" t="str">
-        <x:v>https://jobs.bilibili.com/</x:v>
+        <x:v>助理咨询顾问等</x:v>
+      </x:c>
+      <x:c r="I28" s="15" t="str">
+        <x:v>https://www.bain.com/careers/</x:v>
       </x:c>
       <x:c r="J28" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K28" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L28" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -1971,10 +1973,8 @@
       <x:c r="M28" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N28" s="4" t="str">
-        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
-      </x:c>
-      <x:c r="O28" s="17" t="str">
+      <x:c r="N28" s="4" t="str"/>
+      <x:c r="O28" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P28" s="19" t="str">
@@ -1989,28 +1989,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B29" s="4" t="str">
-        <x:v>东风汽车-全球博士人才</x:v>
+        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
       </x:c>
       <x:c r="C29" s="4" t="str">
-        <x:v>汽车/央企</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="D29" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>武汉、广州、十堰及全国研发基地</x:v>
+        <x:v>上海、北京等</x:v>
       </x:c>
       <x:c r="F29" s="4" t="str">
-        <x:v>博士专项</x:v>
+        <x:v>顶尖技术专项/提前批</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>2026届及以后博士</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
-      </x:c>
-      <x:c r="I29" s="17" t="str">
-        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
+        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
+      </x:c>
+      <x:c r="I29" s="15" t="str">
+        <x:v>https://jobs.bilibili.com/</x:v>
       </x:c>
       <x:c r="J29" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2025,9 +2025,9 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N29" s="4" t="str">
-        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
-      </x:c>
-      <x:c r="O29" s="17" t="str">
+        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
+      </x:c>
+      <x:c r="O29" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P29" s="19" t="str">
@@ -2042,28 +2042,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B30" s="4" t="str">
-        <x:v>度小满-博士后人才招聘</x:v>
+        <x:v>东风汽车-全球博士人才</x:v>
       </x:c>
       <x:c r="C30" s="4" t="str">
-        <x:v>金融科技</x:v>
+        <x:v>汽车/央企</x:v>
       </x:c>
       <x:c r="D30" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>武汉、广州、十堰及全国研发基地</x:v>
       </x:c>
       <x:c r="F30" s="4" t="str">
-        <x:v>博士后专项</x:v>
+        <x:v>博士专项</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>2025/2026/2027届博士</x:v>
+        <x:v>2026届及以后博士</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
-      </x:c>
-      <x:c r="I30" s="17" t="str">
-        <x:v>https://campus.duxiaoman.com/</x:v>
+        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
+      </x:c>
+      <x:c r="I30" s="15" t="str">
+        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
       </x:c>
       <x:c r="J30" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2078,9 +2078,9 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N30" s="4" t="str">
-        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
-      </x:c>
-      <x:c r="O30" s="17" t="str">
+        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
+      </x:c>
+      <x:c r="O30" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P30" s="19" t="str">
@@ -2095,28 +2095,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B31" s="4" t="str">
-        <x:v>多益网络</x:v>
+        <x:v>度小满-博士后人才招聘</x:v>
       </x:c>
       <x:c r="C31" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>金融科技</x:v>
       </x:c>
       <x:c r="D31" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>广州、武汉、成都等</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F31" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>博士后专项</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2025/2026/2027届博士</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>程序、策划、美术、运营、市场及职能</x:v>
-      </x:c>
-      <x:c r="I31" s="17" t="str">
-        <x:v>https://www.duoyi.com/job/</x:v>
+        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
+      </x:c>
+      <x:c r="I31" s="15" t="str">
+        <x:v>https://campus.duxiaoman.com/</x:v>
       </x:c>
       <x:c r="J31" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2131,9 +2131,9 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N31" s="4" t="str">
-        <x:v>岗位可能按城市提前关闭。</x:v>
-      </x:c>
-      <x:c r="O31" s="17" t="str">
+        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
+      </x:c>
+      <x:c r="O31" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P31" s="19" t="str">
@@ -2148,28 +2148,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B32" s="4" t="str">
-        <x:v>海天集团-高潜专项</x:v>
+        <x:v>多益网络</x:v>
       </x:c>
       <x:c r="C32" s="4" t="str">
-        <x:v>工业制造</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D32" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
-        <x:v>宁波及全国基地</x:v>
+        <x:v>广州、武汉、成都等</x:v>
       </x:c>
       <x:c r="F32" s="4" t="str">
-        <x:v>高潜人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
-        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
-      </x:c>
-      <x:c r="I32" s="17" t="str">
-        <x:v>https://www.haitian.com/careers/</x:v>
+        <x:v>程序、策划、美术、运营、市场及职能</x:v>
+      </x:c>
+      <x:c r="I32" s="15" t="str">
+        <x:v>https://www.duoyi.com/job/</x:v>
       </x:c>
       <x:c r="J32" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2184,9 +2184,9 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N32" s="4" t="str">
-        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
-      </x:c>
-      <x:c r="O32" s="17" t="str">
+        <x:v>岗位可能按城市提前关闭。</x:v>
+      </x:c>
+      <x:c r="O32" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P32" s="19" t="str">
@@ -2201,28 +2201,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B33" s="4" t="str">
-        <x:v>赫力昂-销售先锋计划</x:v>
+        <x:v>海天集团-高潜专项</x:v>
       </x:c>
       <x:c r="C33" s="4" t="str">
-        <x:v>消费健康/医药</x:v>
+        <x:v>工业制造</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
-        <x:v>全国重点城市</x:v>
+        <x:v>宁波及全国基地</x:v>
       </x:c>
       <x:c r="F33" s="4" t="str">
-        <x:v>管培/销售专项</x:v>
+        <x:v>高潜人才专项/提前批</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H33" s="4" t="str">
-        <x:v>医药及消费健康销售、商业运营方向</x:v>
-      </x:c>
-      <x:c r="I33" s="17" t="str">
-        <x:v>https://careers.haleon.com/</x:v>
+        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
+      </x:c>
+      <x:c r="I33" s="15" t="str">
+        <x:v>https://www.haitian.com/careers/</x:v>
       </x:c>
       <x:c r="J33" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2236,8 +2236,10 @@
       <x:c r="M33" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N33" s="4" t="str"/>
-      <x:c r="O33" s="17" t="str">
+      <x:c r="N33" s="4" t="str">
+        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
+      </x:c>
+      <x:c r="O33" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P33" s="19" t="str">
@@ -2252,43 +2254,43 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B34" s="4" t="str">
-        <x:v>虹软科技</x:v>
+        <x:v>赫力昂-销售先锋计划</x:v>
       </x:c>
       <x:c r="C34" s="4" t="str">
-        <x:v>计算机视觉/软件</x:v>
+        <x:v>消费健康/医药</x:v>
       </x:c>
       <x:c r="D34" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
-        <x:v>杭州、上海、南京等</x:v>
+        <x:v>全国重点城市</x:v>
       </x:c>
       <x:c r="F34" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>管培/销售专项</x:v>
       </x:c>
       <x:c r="G34" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H34" s="4" t="str">
-        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
-      </x:c>
-      <x:c r="I34" s="17" t="str">
-        <x:v>https://hr.arcsoft.com.cn/</x:v>
+        <x:v>医药及消费健康销售、商业运营方向</x:v>
+      </x:c>
+      <x:c r="I34" s="15" t="str">
+        <x:v>https://careers.haleon.com/</x:v>
       </x:c>
       <x:c r="J34" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K34" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L34" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M34" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N34" s="4" t="str"/>
-      <x:c r="O34" s="17" t="str">
+      <x:c r="O34" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P34" s="19" t="str">
@@ -2303,31 +2305,31 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B35" s="4" t="str">
-        <x:v>汇川技术</x:v>
+        <x:v>虹软科技</x:v>
       </x:c>
       <x:c r="C35" s="4" t="str">
-        <x:v>工业自动化/新能源</x:v>
+        <x:v>计算机视觉/软件</x:v>
       </x:c>
       <x:c r="D35" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E35" s="4" t="str">
-        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
+        <x:v>杭州、上海、南京等</x:v>
       </x:c>
       <x:c r="F35" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H35" s="4" t="str">
-        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
-      </x:c>
-      <x:c r="I35" s="17" t="str">
-        <x:v>https://career.inovance.com/</x:v>
+        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
+      </x:c>
+      <x:c r="I35" s="15" t="str">
+        <x:v>https://hr.arcsoft.com.cn/</x:v>
       </x:c>
       <x:c r="J35" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K35" s="4" t="str">
         <x:v>按岗位，官方未统一说明</x:v>
@@ -2336,10 +2338,10 @@
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M35" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N35" s="4" t="str"/>
-      <x:c r="O35" s="17" t="str">
+      <x:c r="O35" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P35" s="19" t="str">
@@ -2354,34 +2356,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B36" s="4" t="str">
-        <x:v>伽利略-星途星锐计划</x:v>
+        <x:v>汇川技术</x:v>
       </x:c>
       <x:c r="C36" s="4" t="str">
-        <x:v>科技/综合</x:v>
+        <x:v>工业自动化/新能源</x:v>
       </x:c>
       <x:c r="D36" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
-        <x:v>以项目职位页为准</x:v>
+        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
       </x:c>
       <x:c r="F36" s="4" t="str">
-        <x:v>人才专项</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G36" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H36" s="4" t="str">
-        <x:v>以官方项目页为准</x:v>
-      </x:c>
-      <x:c r="I36" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
+      </x:c>
+      <x:c r="I36" s="15" t="str">
+        <x:v>https://career.inovance.com/</x:v>
       </x:c>
       <x:c r="J36" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K36" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L36" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2389,14 +2391,12 @@
       <x:c r="M36" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N36" s="4" t="str">
-        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
-      </x:c>
-      <x:c r="O36" s="17" t="str">
+      <x:c r="N36" s="4" t="str"/>
+      <x:c r="O36" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P36" s="19" t="str">
-        <x:v>C-主体与入口需二次确认</x:v>
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q36" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -2407,52 +2407,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B37" s="4" t="str">
-        <x:v>京东-TET管理培训生</x:v>
+        <x:v>伽利略-星途星锐计划</x:v>
       </x:c>
       <x:c r="C37" s="4" t="str">
-        <x:v>互联网/零售</x:v>
+        <x:v>科技/综合</x:v>
       </x:c>
       <x:c r="D37" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E37" s="4" t="str">
-        <x:v>北京及业务所在城市</x:v>
+        <x:v>以项目职位页为准</x:v>
       </x:c>
       <x:c r="F37" s="4" t="str">
-        <x:v>管培生专项/提前批</x:v>
+        <x:v>人才专项</x:v>
       </x:c>
       <x:c r="G37" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
-        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
-      </x:c>
-      <x:c r="I37" s="17" t="str">
-        <x:v>https://campus.jd.com/</x:v>
+        <x:v>以官方项目页为准</x:v>
+      </x:c>
+      <x:c r="I37" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J37" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K37" s="4" t="str">
-        <x:v>含测评，笔试以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L37" s="4" t="str">
-        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M37" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N37" s="4" t="str">
-        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
-      </x:c>
-      <x:c r="O37" s="17" t="str">
-        <x:v>https://campus.jd.com/#/</x:v>
-      </x:c>
-      <x:c r="P37" s="15" t="str">
-        <x:v>A-企业官网校招页面已核验</x:v>
+        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
+      </x:c>
+      <x:c r="O37" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P37" s="19" t="str">
+        <x:v>C-主体与入口需二次确认</x:v>
       </x:c>
       <x:c r="Q37" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="54" customHeight="1">
@@ -2460,52 +2460,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B38" s="4" t="str">
-        <x:v>科大讯飞-飞凡计划</x:v>
+        <x:v>京东-TET管理培训生</x:v>
       </x:c>
       <x:c r="C38" s="4" t="str">
-        <x:v>AI/软件</x:v>
+        <x:v>互联网/零售</x:v>
       </x:c>
       <x:c r="D38" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E38" s="4" t="str">
-        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
+        <x:v>北京及业务所在城市</x:v>
       </x:c>
       <x:c r="F38" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>管培生专项/提前批</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
-        <x:v>2026/2027届</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H38" s="4" t="str">
-        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
-      </x:c>
-      <x:c r="I38" s="17" t="str">
-        <x:v>https://campus.iflytek.com/</x:v>
+        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
+      </x:c>
+      <x:c r="I38" s="15" t="str">
+        <x:v>https://campus.jd.com/</x:v>
       </x:c>
       <x:c r="J38" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K38" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>含测评，笔试以通知为准</x:v>
       </x:c>
       <x:c r="L38" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
       </x:c>
       <x:c r="M38" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N38" s="4" t="str">
-        <x:v>专项岗位与常规校招可能并行。</x:v>
-      </x:c>
-      <x:c r="O38" s="17" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P38" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
+      </x:c>
+      <x:c r="O38" s="15" t="str">
+        <x:v>https://campus.jd.com/#/</x:v>
+      </x:c>
+      <x:c r="P38" s="14" t="str">
+        <x:v>A-企业官网校招页面已核验</x:v>
       </x:c>
       <x:c r="Q38" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="54" customHeight="1">
@@ -2513,28 +2513,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B39" s="4" t="str">
-        <x:v>理想汽车</x:v>
+        <x:v>科大讯飞-飞凡计划</x:v>
       </x:c>
       <x:c r="C39" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>AI/软件</x:v>
       </x:c>
       <x:c r="D39" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
-        <x:v>北京、上海、常州等</x:v>
+        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
       </x:c>
       <x:c r="F39" s="4" t="str">
-        <x:v>暑期实习转正通道</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G39" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026/2027届</x:v>
       </x:c>
       <x:c r="H39" s="4" t="str">
-        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
-      </x:c>
-      <x:c r="I39" s="17" t="str">
-        <x:v>https://career.lixiang.com/campus</x:v>
+        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
+      </x:c>
+      <x:c r="I39" s="15" t="str">
+        <x:v>https://campus.iflytek.com/</x:v>
       </x:c>
       <x:c r="J39" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2549,9 +2549,9 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N39" s="4" t="str">
-        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
-      </x:c>
-      <x:c r="O39" s="17" t="str">
+        <x:v>专项岗位与常规校招可能并行。</x:v>
+      </x:c>
+      <x:c r="O39" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P39" s="19" t="str">
@@ -2566,43 +2566,45 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B40" s="4" t="str">
-        <x:v>莉莉丝游戏</x:v>
+        <x:v>理想汽车</x:v>
       </x:c>
       <x:c r="C40" s="4" t="str">
-        <x:v>游戏</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D40" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E40" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>北京、上海、常州等</x:v>
       </x:c>
       <x:c r="F40" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>暑期实习转正通道</x:v>
       </x:c>
       <x:c r="G40" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H40" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
-      </x:c>
-      <x:c r="I40" s="17" t="str">
-        <x:v>https://campus.lilith.com/</x:v>
+        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
+      </x:c>
+      <x:c r="I40" s="15" t="str">
+        <x:v>https://career.lixiang.com/campus</x:v>
       </x:c>
       <x:c r="J40" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K40" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L40" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M40" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N40" s="4" t="str"/>
-      <x:c r="O40" s="17" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N40" s="4" t="str">
+        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
+      </x:c>
+      <x:c r="O40" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P40" s="19" t="str">
@@ -2617,43 +2619,43 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B41" s="4" t="str">
-        <x:v>麦肯锡</x:v>
+        <x:v>莉莉丝游戏</x:v>
       </x:c>
       <x:c r="C41" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>游戏</x:v>
       </x:c>
       <x:c r="D41" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E41" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F41" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G41" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H41" s="4" t="str">
-        <x:v>商业分析师、咨询及专业岗位</x:v>
-      </x:c>
-      <x:c r="I41" s="17" t="str">
-        <x:v>https://www.mckinsey.com/careers</x:v>
+        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
+      </x:c>
+      <x:c r="I41" s="15" t="str">
+        <x:v>https://campus.lilith.com/</x:v>
       </x:c>
       <x:c r="J41" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="K41" s="4" t="str">
-        <x:v>通常含测评/案例面试；以通知为准</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L41" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M41" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N41" s="4" t="str"/>
-      <x:c r="O41" s="17" t="str">
+      <x:c r="O41" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P41" s="19" t="str">
@@ -2668,34 +2670,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B42" s="4" t="str">
-        <x:v>拼多多</x:v>
+        <x:v>麦肯锡</x:v>
       </x:c>
       <x:c r="C42" s="4" t="str">
-        <x:v>互联网/电商</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D42" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E42" s="4" t="str">
-        <x:v>上海、广州等，以岗位页为准</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F42" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G42" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H42" s="4" t="str">
-        <x:v>技术、算法、产品、运营、商业分析等</x:v>
-      </x:c>
-      <x:c r="I42" s="17" t="str">
-        <x:v>https://careers.pinduoduo.com/campus/</x:v>
+        <x:v>商业分析师、咨询及专业岗位</x:v>
+      </x:c>
+      <x:c r="I42" s="15" t="str">
+        <x:v>https://www.mckinsey.com/careers</x:v>
       </x:c>
       <x:c r="J42" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K42" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>通常含测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L42" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2703,10 +2705,8 @@
       <x:c r="M42" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N42" s="4" t="str">
-        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
-      </x:c>
-      <x:c r="O42" s="17" t="str">
+      <x:c r="N42" s="4" t="str"/>
+      <x:c r="O42" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P42" s="19" t="str">
@@ -2721,34 +2721,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B43" s="4" t="str">
-        <x:v>启林投资</x:v>
+        <x:v>拼多多</x:v>
       </x:c>
       <x:c r="C43" s="4" t="str">
-        <x:v>量化金融/资管</x:v>
+        <x:v>互联网/电商</x:v>
       </x:c>
       <x:c r="D43" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E43" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>上海、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F43" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G43" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H43" s="4" t="str">
-        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
-      </x:c>
-      <x:c r="I43" s="17" t="str">
-        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
+        <x:v>技术、算法、产品、运营、商业分析等</x:v>
+      </x:c>
+      <x:c r="I43" s="15" t="str">
+        <x:v>https://careers.pinduoduo.com/campus/</x:v>
       </x:c>
       <x:c r="J43" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K43" s="4" t="str">
-        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L43" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2757,9 +2757,9 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N43" s="4" t="str">
-        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
-      </x:c>
-      <x:c r="O43" s="17" t="str">
+        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
+      </x:c>
+      <x:c r="O43" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P43" s="19" t="str">
@@ -2774,34 +2774,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B44" s="4" t="str">
-        <x:v>商汤科技-无限原力计划</x:v>
+        <x:v>启林投资</x:v>
       </x:c>
       <x:c r="C44" s="4" t="str">
-        <x:v>AI/计算机视觉</x:v>
+        <x:v>量化金融/资管</x:v>
       </x:c>
       <x:c r="D44" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E44" s="4" t="str">
-        <x:v>上海、北京、深圳、杭州等</x:v>
+        <x:v>上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F44" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G44" s="4" t="str">
-        <x:v>2027/2028届</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H44" s="4" t="str">
-        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
-      </x:c>
-      <x:c r="I44" s="17" t="str">
-        <x:v>https://joinus.sensetime.com/</x:v>
+        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
+      </x:c>
+      <x:c r="I44" s="15" t="str">
+        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
       </x:c>
       <x:c r="J44" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K44" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
       </x:c>
       <x:c r="L44" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2810,9 +2810,9 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N44" s="4" t="str">
-        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
-      </x:c>
-      <x:c r="O44" s="17" t="str">
+        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
+      </x:c>
+      <x:c r="O44" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P44" s="19" t="str">
@@ -2827,28 +2827,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B45" s="4" t="str">
-        <x:v>腾讯-青云计划</x:v>
+        <x:v>商汤科技-无限原力计划</x:v>
       </x:c>
       <x:c r="C45" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>AI/计算机视觉</x:v>
       </x:c>
       <x:c r="D45" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E45" s="4" t="str">
-        <x:v>深圳、北京、上海等</x:v>
+        <x:v>上海、北京、深圳、杭州等</x:v>
       </x:c>
       <x:c r="F45" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G45" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027/2028届</x:v>
       </x:c>
       <x:c r="H45" s="4" t="str">
-        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
-      </x:c>
-      <x:c r="I45" s="17" t="str">
-        <x:v>https://join.qq.com/</x:v>
+        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
+      </x:c>
+      <x:c r="I45" s="15" t="str">
+        <x:v>https://joinus.sensetime.com/</x:v>
       </x:c>
       <x:c r="J45" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2863,9 +2863,9 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N45" s="4" t="str">
-        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
-      </x:c>
-      <x:c r="O45" s="17" t="str">
+        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
+      </x:c>
+      <x:c r="O45" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P45" s="19" t="str">
@@ -2880,28 +2880,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B46" s="4" t="str">
-        <x:v>天锐星通</x:v>
+        <x:v>腾讯-青云计划</x:v>
       </x:c>
       <x:c r="C46" s="4" t="str">
-        <x:v>卫星通信/相控阵</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D46" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E46" s="4" t="str">
-        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
+        <x:v>深圳、北京、上海等</x:v>
       </x:c>
       <x:c r="F46" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G46" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H46" s="4" t="str">
-        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
-      </x:c>
-      <x:c r="I46" s="17" t="str">
-        <x:v>https://www.tianruixing.com/</x:v>
+        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
+      </x:c>
+      <x:c r="I46" s="15" t="str">
+        <x:v>https://join.qq.com/</x:v>
       </x:c>
       <x:c r="J46" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2916,9 +2916,9 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N46" s="4" t="str">
-        <x:v>官网入口与具体岗位需投前复核。</x:v>
-      </x:c>
-      <x:c r="O46" s="17" t="str">
+        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
+      </x:c>
+      <x:c r="O46" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P46" s="19" t="str">
@@ -2930,52 +2930,52 @@
     </x:row>
     <x:row r="47" ht="54" customHeight="1">
       <x:c r="A47" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B47" s="4" t="str">
-        <x:v>网易游戏雷火</x:v>
+        <x:v>天锐星通</x:v>
       </x:c>
       <x:c r="C47" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>卫星通信/相控阵</x:v>
       </x:c>
       <x:c r="D47" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E47" s="4" t="str">
-        <x:v>杭州、上海等，以岗位页为准</x:v>
+        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F47" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G47" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H47" s="4" t="str">
-        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
-      </x:c>
-      <x:c r="I47" s="17" t="str">
-        <x:v>https://leihuo.163.com/campus/#/full</x:v>
+        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
+      </x:c>
+      <x:c r="I47" s="15" t="str">
+        <x:v>https://www.tianruixing.com/</x:v>
       </x:c>
       <x:c r="J47" s="4" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K47" s="4" t="str">
-        <x:v>部分岗位免笔试；部分可直通面试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L47" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M47" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N47" s="4" t="str">
-        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
-      </x:c>
-      <x:c r="O47" s="17" t="str">
+        <x:v>官网入口与具体岗位需投前复核。</x:v>
+      </x:c>
+      <x:c r="O47" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P47" s="15" t="str">
-        <x:v>A-官方招聘官网已核验</x:v>
+      <x:c r="P47" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q47" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -2983,52 +2983,52 @@
     </x:row>
     <x:row r="48" ht="54" customHeight="1">
       <x:c r="A48" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B48" s="4" t="str">
-        <x:v>小鹏集团</x:v>
+        <x:v>网易游戏雷火</x:v>
       </x:c>
       <x:c r="C48" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D48" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E48" s="4" t="str">
-        <x:v>广州、北京、上海、深圳、武汉等</x:v>
+        <x:v>杭州、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F48" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G48" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H48" s="4" t="str">
-        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
-      </x:c>
-      <x:c r="I48" s="17" t="str">
-        <x:v>https://join.xiaopeng.com/campus</x:v>
+        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
+      </x:c>
+      <x:c r="I48" s="15" t="str">
+        <x:v>https://leihuo.163.com/campus/#/full</x:v>
       </x:c>
       <x:c r="J48" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="K48" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>部分岗位免笔试；部分可直通面试</x:v>
       </x:c>
       <x:c r="L48" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M48" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N48" s="4" t="str">
-        <x:v>营销服与技术岗位可能分项目发布。</x:v>
-      </x:c>
-      <x:c r="O48" s="17" t="str">
+        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
+      </x:c>
+      <x:c r="O48" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P48" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P48" s="14" t="str">
+        <x:v>A-官方招聘官网已核验</x:v>
       </x:c>
       <x:c r="Q48" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3039,34 +3039,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B49" s="4" t="str">
-        <x:v>芯动科技</x:v>
+        <x:v>小鹏集团</x:v>
       </x:c>
       <x:c r="C49" s="4" t="str">
-        <x:v>半导体/IP设计</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D49" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E49" s="4" t="str">
-        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
+        <x:v>广州、北京、上海、深圳、武汉等</x:v>
       </x:c>
       <x:c r="F49" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G49" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H49" s="4" t="str">
-        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
-      </x:c>
-      <x:c r="I49" s="17" t="str">
-        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
+        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
+      </x:c>
+      <x:c r="I49" s="15" t="str">
+        <x:v>https://join.xiaopeng.com/campus</x:v>
       </x:c>
       <x:c r="J49" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K49" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L49" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3074,8 +3074,10 @@
       <x:c r="M49" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N49" s="4" t="str"/>
-      <x:c r="O49" s="17" t="str">
+      <x:c r="N49" s="4" t="str">
+        <x:v>营销服与技术岗位可能分项目发布。</x:v>
+      </x:c>
+      <x:c r="O49" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P49" s="19" t="str">
@@ -3087,52 +3089,50 @@
     </x:row>
     <x:row r="50" ht="54" customHeight="1">
       <x:c r="A50" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B50" s="4" t="str">
-        <x:v>芯迈半导体</x:v>
+        <x:v>芯动科技</x:v>
       </x:c>
       <x:c r="C50" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>半导体/IP设计</x:v>
       </x:c>
       <x:c r="D50" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E50" s="4" t="str">
-        <x:v>杭州、上海、深圳、成都</x:v>
+        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
       </x:c>
       <x:c r="F50" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G50" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H50" s="4" t="str">
-        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
-      </x:c>
-      <x:c r="I50" s="17" t="str">
-        <x:v>https://www.silicon-magic.com/joinus</x:v>
+        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
+      </x:c>
+      <x:c r="I50" s="15" t="str">
+        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
       </x:c>
       <x:c r="J50" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K50" s="4" t="str">
-        <x:v>官方未说明；公开流程未列笔试</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L50" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M50" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N50" s="4" t="str">
-        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
-      </x:c>
-      <x:c r="O50" s="17" t="str">
+      <x:c r="N50" s="4" t="str"/>
+      <x:c r="O50" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P50" s="15" t="str">
-        <x:v>A-企业官网与公开公告已核验</x:v>
+      <x:c r="P50" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q50" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3140,55 +3140,55 @@
     </x:row>
     <x:row r="51" ht="54" customHeight="1">
       <x:c r="A51" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B51" s="4" t="str">
-        <x:v>新易盛</x:v>
+        <x:v>芯迈半导体</x:v>
       </x:c>
       <x:c r="C51" s="4" t="str">
-        <x:v>光通信/半导体</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D51" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E51" s="4" t="str">
-        <x:v>成都、苏州等，以岗位页为准</x:v>
+        <x:v>杭州、上海、深圳、成都</x:v>
       </x:c>
       <x:c r="F51" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G51" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H51" s="4" t="str">
-        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
-      </x:c>
-      <x:c r="I51" s="17" t="str">
-        <x:v>https://www.eoptolink.com/</x:v>
+        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
+      </x:c>
+      <x:c r="I51" s="15" t="str">
+        <x:v>https://www.silicon-magic.com/joinus</x:v>
       </x:c>
       <x:c r="J51" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K51" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未说明；公开流程未列笔试</x:v>
       </x:c>
       <x:c r="L51" s="4" t="str">
-        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M51" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N51" s="4" t="str">
-        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
-      </x:c>
-      <x:c r="O51" s="17" t="str">
+        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
+      </x:c>
+      <x:c r="O51" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P51" s="18" t="str">
-        <x:v>B-高校/招聘平台转载，投前复核</x:v>
+      <x:c r="P51" s="14" t="str">
+        <x:v>A-企业官网与公开公告已核验</x:v>
       </x:c>
       <x:c r="Q51" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="54" customHeight="1">
@@ -3196,50 +3196,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B52" s="4" t="str">
-        <x:v>元戎启行</x:v>
+        <x:v>新易盛</x:v>
       </x:c>
       <x:c r="C52" s="4" t="str">
-        <x:v>自动驾驶</x:v>
+        <x:v>光通信/半导体</x:v>
       </x:c>
       <x:c r="D52" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E52" s="4" t="str">
-        <x:v>深圳、北京等</x:v>
+        <x:v>成都、苏州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F52" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G52" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H52" s="4" t="str">
-        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
-      </x:c>
-      <x:c r="I52" s="17" t="str">
-        <x:v>https://www.deeproute.ai/join-us</x:v>
+        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
+      </x:c>
+      <x:c r="I52" s="15" t="str">
+        <x:v>https://www.eoptolink.com/</x:v>
       </x:c>
       <x:c r="J52" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K52" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L52" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
       </x:c>
       <x:c r="M52" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N52" s="4" t="str"/>
-      <x:c r="O52" s="17" t="str">
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N52" s="4" t="str">
+        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+      </x:c>
+      <x:c r="O52" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P52" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P52" s="18" t="str">
+        <x:v>B-高校/招聘平台转载，投前复核</x:v>
       </x:c>
       <x:c r="Q52" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="54" customHeight="1">
@@ -3247,34 +3249,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B53" s="4" t="str">
-        <x:v>圆通速递</x:v>
+        <x:v>元戎启行</x:v>
       </x:c>
       <x:c r="C53" s="4" t="str">
-        <x:v>物流/供应链</x:v>
+        <x:v>自动驾驶</x:v>
       </x:c>
       <x:c r="D53" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E53" s="4" t="str">
-        <x:v>上海及全国网络</x:v>
+        <x:v>深圳、北京等</x:v>
       </x:c>
       <x:c r="F53" s="4" t="str">
-        <x:v>正式批/校招</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G53" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H53" s="4" t="str">
-        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
-      </x:c>
-      <x:c r="I53" s="17" t="str">
-        <x:v>https://hr.yto.net.cn/</x:v>
+        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
+      </x:c>
+      <x:c r="I53" s="15" t="str">
+        <x:v>https://www.deeproute.ai/join-us</x:v>
       </x:c>
       <x:c r="J53" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K53" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L53" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3283,7 +3285,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N53" s="4" t="str"/>
-      <x:c r="O53" s="17" t="str">
+      <x:c r="O53" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P53" s="19" t="str">
@@ -3298,34 +3300,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B54" s="4" t="str">
-        <x:v>长亭科技</x:v>
+        <x:v>圆通速递</x:v>
       </x:c>
       <x:c r="C54" s="4" t="str">
-        <x:v>网络安全</x:v>
+        <x:v>物流/供应链</x:v>
       </x:c>
       <x:c r="D54" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E54" s="4" t="str">
-        <x:v>北京、上海等，以岗位页为准</x:v>
+        <x:v>上海及全国网络</x:v>
       </x:c>
       <x:c r="F54" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批/校招</x:v>
       </x:c>
       <x:c r="G54" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H54" s="4" t="str">
-        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
-      </x:c>
-      <x:c r="I54" s="17" t="str">
-        <x:v>https://job.chaitin.cn/</x:v>
+        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
+      </x:c>
+      <x:c r="I54" s="15" t="str">
+        <x:v>https://hr.yto.net.cn/</x:v>
       </x:c>
       <x:c r="J54" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K54" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L54" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3334,7 +3336,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N54" s="4" t="str"/>
-      <x:c r="O54" s="17" t="str">
+      <x:c r="O54" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P54" s="19" t="str">
@@ -3349,28 +3351,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B55" s="4" t="str">
-        <x:v>智元机器人-优才计划</x:v>
+        <x:v>长亭科技</x:v>
       </x:c>
       <x:c r="C55" s="4" t="str">
-        <x:v>具身智能/机器人</x:v>
+        <x:v>网络安全</x:v>
       </x:c>
       <x:c r="D55" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E55" s="4" t="str">
-        <x:v>上海、北京、深圳等</x:v>
+        <x:v>北京、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F55" s="4" t="str">
-        <x:v>优才专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G55" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H55" s="4" t="str">
-        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
-      </x:c>
-      <x:c r="I55" s="17" t="str">
-        <x:v>https://www.agibot.com/recruit</x:v>
+        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
+      </x:c>
+      <x:c r="I55" s="15" t="str">
+        <x:v>https://job.chaitin.cn/</x:v>
       </x:c>
       <x:c r="J55" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3385,7 +3387,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N55" s="4" t="str"/>
-      <x:c r="O55" s="17" t="str">
+      <x:c r="O55" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P55" s="19" t="str">
@@ -3400,34 +3402,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B56" s="4" t="str">
-        <x:v>中国电信天翼云-超级优才</x:v>
+        <x:v>智元机器人-优才计划</x:v>
       </x:c>
       <x:c r="C56" s="4" t="str">
-        <x:v>云计算/央企</x:v>
+        <x:v>具身智能/机器人</x:v>
       </x:c>
       <x:c r="D56" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E56" s="4" t="str">
-        <x:v>北京、上海、广州、成都及全国机构</x:v>
+        <x:v>上海、北京、深圳等</x:v>
       </x:c>
       <x:c r="F56" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>优才专项/提前批</x:v>
       </x:c>
       <x:c r="G56" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H56" s="4" t="str">
-        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
-      </x:c>
-      <x:c r="I56" s="17" t="str">
-        <x:v>https://www.ctyun.cn/about/recruit</x:v>
+        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
+      </x:c>
+      <x:c r="I56" s="15" t="str">
+        <x:v>https://www.agibot.com/recruit</x:v>
       </x:c>
       <x:c r="J56" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K56" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L56" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3435,10 +3437,8 @@
       <x:c r="M56" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N56" s="4" t="str">
-        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
-      </x:c>
-      <x:c r="O56" s="17" t="str">
+      <x:c r="N56" s="4" t="str"/>
+      <x:c r="O56" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P56" s="19" t="str">
@@ -3453,31 +3453,31 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B57" s="4" t="str">
-        <x:v>中科光电</x:v>
+        <x:v>中国电信天翼云-超级优才</x:v>
       </x:c>
       <x:c r="C57" s="4" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>云计算/央企</x:v>
       </x:c>
       <x:c r="D57" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E57" s="4" t="str">
-        <x:v>以职位公告为准</x:v>
+        <x:v>北京、上海、广州、成都及全国机构</x:v>
       </x:c>
       <x:c r="F57" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G57" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H57" s="4" t="str">
-        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
-      </x:c>
-      <x:c r="I57" s="17" t="str">
-        <x:v>https://job.cn-amd.com/</x:v>
+        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
+      </x:c>
+      <x:c r="I57" s="15" t="str">
+        <x:v>https://www.ctyun.cn/about/recruit</x:v>
       </x:c>
       <x:c r="J57" s="4" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K57" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -3486,16 +3486,16 @@
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M57" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N57" s="4" t="str">
-        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
-      </x:c>
-      <x:c r="O57" s="17" t="str">
+        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
+      </x:c>
+      <x:c r="O57" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P57" s="19" t="str">
-        <x:v>C-名称需二次确认</x:v>
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q57" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3506,31 +3506,31 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B58" s="4" t="str">
-        <x:v>中兴微电子-未来领军计划</x:v>
+        <x:v>中科光电</x:v>
       </x:c>
       <x:c r="C58" s="4" t="str">
-        <x:v>半导体/通信</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D58" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E58" s="4" t="str">
-        <x:v>深圳、西安、南京、上海等</x:v>
+        <x:v>以职位公告为准</x:v>
       </x:c>
       <x:c r="F58" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G58" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H58" s="4" t="str">
-        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
-      </x:c>
-      <x:c r="I58" s="17" t="str">
-        <x:v>https://job.zte.com.cn/</x:v>
+        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
+      </x:c>
+      <x:c r="I58" s="15" t="str">
+        <x:v>https://job.cn-amd.com/</x:v>
       </x:c>
       <x:c r="J58" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K58" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -3539,123 +3539,125 @@
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M58" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N58" s="4" t="str">
+        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
+      </x:c>
+      <x:c r="O58" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P58" s="19" t="str">
+        <x:v>C-名称需二次确认</x:v>
+      </x:c>
+      <x:c r="Q58" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="54" customHeight="1">
+      <x:c r="A59" s="4" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B59" s="4" t="str">
+        <x:v>中兴微电子-未来领军计划</x:v>
+      </x:c>
+      <x:c r="C59" s="4" t="str">
+        <x:v>半导体/通信</x:v>
+      </x:c>
+      <x:c r="D59" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E59" s="4" t="str">
+        <x:v>深圳、西安、南京、上海等</x:v>
+      </x:c>
+      <x:c r="F59" s="4" t="str">
+        <x:v>顶尖人才专项/提前批</x:v>
+      </x:c>
+      <x:c r="G59" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H59" s="4" t="str">
+        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
+      </x:c>
+      <x:c r="I59" s="15" t="str">
+        <x:v>https://job.zte.com.cn/</x:v>
+      </x:c>
+      <x:c r="J59" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K59" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L59" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M59" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N59" s="4" t="str">
         <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
       </x:c>
-      <x:c r="O58" s="17" t="str">
+      <x:c r="O59" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P58" s="19" t="str">
+      <x:c r="P59" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q58" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="54" customHeight="1">
-      <x:c r="A59" s="14" t="str">
+      <x:c r="Q59" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="54" customHeight="1">
+      <x:c r="A60" s="16" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B59" s="14" t="str">
+      <x:c r="B60" s="16" t="str">
         <x:v>字节跳动-AI产品经理早鸟通道</x:v>
       </x:c>
-      <x:c r="C59" s="14" t="str">
+      <x:c r="C60" s="16" t="str">
         <x:v>互联网/AI</x:v>
       </x:c>
-      <x:c r="D59" s="14" t="str">
+      <x:c r="D60" s="16" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E59" s="14" t="str">
+      <x:c r="E60" s="16" t="str">
         <x:v>北京、上海、深圳</x:v>
       </x:c>
-      <x:c r="F59" s="14" t="str">
+      <x:c r="F60" s="16" t="str">
         <x:v>早鸟专项/提前批</x:v>
       </x:c>
-      <x:c r="G59" s="14" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H59" s="14" t="str">
+      <x:c r="G60" s="16" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H60" s="16" t="str">
         <x:v>AI产品经理、智能体及大模型产品方向</x:v>
       </x:c>
-      <x:c r="I59" s="16" t="str">
+      <x:c r="I60" s="17" t="str">
         <x:v>https://jobs.bytedance.com/campus/</x:v>
       </x:c>
-      <x:c r="J59" s="14" t="str">
+      <x:c r="J60" s="16" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
-      <x:c r="K59" s="14" t="str">
+      <x:c r="K60" s="16" t="str">
         <x:v>按岗位，未统一公布</x:v>
       </x:c>
-      <x:c r="L59" s="14" t="str">
+      <x:c r="L60" s="16" t="str">
         <x:v>已截止（2026-08-02）；原公告与官方投递入口保留</x:v>
       </x:c>
-      <x:c r="M59" s="14" t="str">
+      <x:c r="M60" s="16" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N59" s="14" t="str">
+      <x:c r="N60" s="16" t="str">
         <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
       </x:c>
-      <x:c r="O59" s="16" t="str">
+      <x:c r="O60" s="17" t="str">
         <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
       </x:c>
-      <x:c r="P59" s="18" t="str">
+      <x:c r="P60" s="18" t="str">
         <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q59" s="14" t="str">
+      <x:c r="Q60" s="16" t="str">
         <x:v>2026-08-03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" ht="54" customHeight="1">
-      <x:c r="A60" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
-      </x:c>
-      <x:c r="B60" s="4" t="str">
-        <x:v>BCG波士顿咨询</x:v>
-      </x:c>
-      <x:c r="C60" s="4" t="str">
-        <x:v>管理咨询</x:v>
-      </x:c>
-      <x:c r="D60" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E60" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
-      </x:c>
-      <x:c r="F60" s="4" t="str">
-        <x:v>正式批/中国区校招</x:v>
-      </x:c>
-      <x:c r="G60" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H60" s="4" t="str">
-        <x:v>咨询顾问及相关专业岗位</x:v>
-      </x:c>
-      <x:c r="I60" s="17" t="str">
-        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
-      </x:c>
-      <x:c r="J60" s="4" t="str">
-        <x:v>2026-08-16</x:v>
-      </x:c>
-      <x:c r="K60" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
-      </x:c>
-      <x:c r="L60" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
-      </x:c>
-      <x:c r="M60" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N60" s="4" t="str"/>
-      <x:c r="O60" s="17" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P60" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q60" s="4" t="str">
-        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="54" customHeight="1">
@@ -3663,45 +3665,43 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B61" s="4" t="str">
-        <x:v>OPPO</x:v>
+        <x:v>BCG波士顿咨询</x:v>
       </x:c>
       <x:c r="C61" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D61" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E61" s="4" t="str">
-        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F61" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
+        <x:v>正式批/中国区校招</x:v>
       </x:c>
       <x:c r="G61" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H61" s="4" t="str">
-        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
-      </x:c>
-      <x:c r="I61" s="17" t="str">
-        <x:v>https://careers.oppo.com/campus</x:v>
+        <x:v>咨询顾问及相关专业岗位</x:v>
+      </x:c>
+      <x:c r="I61" s="15" t="str">
+        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
       </x:c>
       <x:c r="J61" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K61" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L61" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M61" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N61" s="4" t="str">
-        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
-      </x:c>
-      <x:c r="O61" s="17" t="str">
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N61" s="4" t="str"/>
+      <x:c r="O61" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P61" s="19" t="str">
@@ -3716,28 +3716,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B62" s="4" t="str">
-        <x:v>Tap4Fun</x:v>
+        <x:v>OPPO</x:v>
       </x:c>
       <x:c r="C62" s="4" t="str">
-        <x:v>游戏</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D62" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E62" s="4" t="str">
-        <x:v>成都等</x:v>
+        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
       </x:c>
       <x:c r="F62" s="4" t="str">
-        <x:v>实习转正通道</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G62" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H62" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
-      </x:c>
-      <x:c r="I62" s="17" t="str">
-        <x:v>https://www.tap4fun.com/careers</x:v>
+        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
+      </x:c>
+      <x:c r="I62" s="15" t="str">
+        <x:v>https://careers.oppo.com/campus</x:v>
       </x:c>
       <x:c r="J62" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3752,9 +3752,9 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N62" s="4" t="str">
-        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
-      </x:c>
-      <x:c r="O62" s="17" t="str">
+        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
+      </x:c>
+      <x:c r="O62" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P62" s="19" t="str">
@@ -3766,161 +3766,161 @@
     </x:row>
     <x:row r="63" ht="54" customHeight="1">
       <x:c r="A63" s="4" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B63" s="4" t="str">
+        <x:v>Tap4Fun</x:v>
+      </x:c>
+      <x:c r="C63" s="4" t="str">
+        <x:v>游戏</x:v>
+      </x:c>
+      <x:c r="D63" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E63" s="4" t="str">
+        <x:v>成都等</x:v>
+      </x:c>
+      <x:c r="F63" s="4" t="str">
+        <x:v>实习转正通道</x:v>
+      </x:c>
+      <x:c r="G63" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H63" s="4" t="str">
+        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
+      </x:c>
+      <x:c r="I63" s="15" t="str">
+        <x:v>https://www.tap4fun.com/careers</x:v>
+      </x:c>
+      <x:c r="J63" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K63" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L63" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M63" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N63" s="4" t="str">
+        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
+      </x:c>
+      <x:c r="O63" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P63" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q63" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="54" customHeight="1">
+      <x:c r="A64" s="4" t="str">
         <x:v>2026-07-20</x:v>
       </x:c>
-      <x:c r="B63" s="4" t="str">
+      <x:c r="B64" s="4" t="str">
         <x:v>航天科技集团五院502所</x:v>
       </x:c>
-      <x:c r="C63" s="4" t="str">
+      <x:c r="C64" s="4" t="str">
         <x:v>航天/自动控制</x:v>
       </x:c>
-      <x:c r="D63" s="4" t="str">
+      <x:c r="D64" s="4" t="str">
         <x:v>事业单位/央企院所</x:v>
       </x:c>
-      <x:c r="E63" s="4" t="str">
+      <x:c r="E64" s="4" t="str">
         <x:v>北京</x:v>
       </x:c>
-      <x:c r="F63" s="4" t="str">
+      <x:c r="F64" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G63" s="4" t="str">
+      <x:c r="G64" s="4" t="str">
         <x:v>硕士/博士为主，以岗位为准</x:v>
       </x:c>
-      <x:c r="H63" s="4" t="str">
+      <x:c r="H64" s="4" t="str">
         <x:v>导航制导与控制、自动化、电子、通信、计算机、软件、机械等</x:v>
       </x:c>
-      <x:c r="I63" s="17" t="str">
+      <x:c r="I64" s="15" t="str">
         <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
-      <x:c r="J63" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K63" s="4" t="str">
+      <x:c r="J64" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K64" s="4" t="str">
         <x:v>未统一公布</x:v>
       </x:c>
-      <x:c r="L63" s="4" t="str">
+      <x:c r="L64" s="4" t="str">
         <x:v>公开公告显示开放；投前确认</x:v>
       </x:c>
-      <x:c r="M63" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N63" s="4" t="str">
+      <x:c r="M64" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N64" s="4" t="str">
         <x:v>研究所岗位通常有专业、学历、政审及保密要求。</x:v>
       </x:c>
-      <x:c r="O63" s="17" t="str">
+      <x:c r="O64" s="15" t="str">
         <x:v>https://www.baidu.com/s?wd=%E4%BA%94%E9%99%A2502%E6%89%802027%E5%B1%8A%E6%A0%A1%E6%8B%9B</x:v>
       </x:c>
-      <x:c r="P63" s="18" t="str">
+      <x:c r="P64" s="18" t="str">
         <x:v>B-高校就业网公开公告</x:v>
       </x:c>
-      <x:c r="Q63" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="54" customHeight="1">
-      <x:c r="A64" s="14" t="str">
+      <x:c r="Q64" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="54" customHeight="1">
+      <x:c r="A65" s="16" t="str">
         <x:v>2026-07-17</x:v>
       </x:c>
-      <x:c r="B64" s="14" t="str">
+      <x:c r="B65" s="16" t="str">
         <x:v>鹰角网络</x:v>
       </x:c>
-      <x:c r="C64" s="14" t="str">
+      <x:c r="C65" s="16" t="str">
         <x:v>游戏</x:v>
       </x:c>
-      <x:c r="D64" s="14" t="str">
+      <x:c r="D65" s="16" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E64" s="14" t="str">
+      <x:c r="E65" s="16" t="str">
         <x:v>上海</x:v>
       </x:c>
-      <x:c r="F64" s="14" t="str">
+      <x:c r="F65" s="16" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G64" s="14" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H64" s="14" t="str">
+      <x:c r="G65" s="16" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H65" s="16" t="str">
         <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
       </x:c>
-      <x:c r="I64" s="16" t="str">
+      <x:c r="I65" s="17" t="str">
         <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
       </x:c>
-      <x:c r="J64" s="14" t="str">
+      <x:c r="J65" s="16" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
-      <x:c r="K64" s="14" t="str">
+      <x:c r="K65" s="16" t="str">
         <x:v>否；安排笔试/面试</x:v>
       </x:c>
-      <x:c r="L64" s="14" t="str">
+      <x:c r="L65" s="16" t="str">
         <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
       </x:c>
-      <x:c r="M64" s="14" t="str">
+      <x:c r="M65" s="16" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N64" s="14" t="str">
+      <x:c r="N65" s="16" t="str">
         <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
       </x:c>
-      <x:c r="O64" s="16" t="str">
+      <x:c r="O65" s="17" t="str">
         <x:v>https://campus.hypergryph.com/</x:v>
       </x:c>
-      <x:c r="P64" s="15" t="str">
+      <x:c r="P65" s="14" t="str">
         <x:v>A-官方来源公告已核验</x:v>
       </x:c>
-      <x:c r="Q64" s="14" t="str">
+      <x:c r="Q65" s="16" t="str">
         <x:v>2026-08-03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="54" customHeight="1">
-      <x:c r="A65" s="4" t="str">
-        <x:v>2026-07-16</x:v>
-      </x:c>
-      <x:c r="B65" s="4" t="str">
-        <x:v>联发科技</x:v>
-      </x:c>
-      <x:c r="C65" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
-      </x:c>
-      <x:c r="D65" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E65" s="4" t="str">
-        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
-      </x:c>
-      <x:c r="F65" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G65" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H65" s="4" t="str">
-        <x:v>软件类、通信类、IC类</x:v>
-      </x:c>
-      <x:c r="I65" s="17" t="str">
-        <x:v>https://mediatek.zhiye.com/</x:v>
-      </x:c>
-      <x:c r="J65" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K65" s="4" t="str">
-        <x:v>否；明确安排7-8月笔试</x:v>
-      </x:c>
-      <x:c r="L65" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M65" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N65" s="4" t="str">
-        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
-      </x:c>
-      <x:c r="O65" s="17" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P65" s="15" t="str">
-        <x:v>A-官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q65" s="4" t="str">
-        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="54" customHeight="1">
@@ -3928,34 +3928,34 @@
         <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B66" s="4" t="str">
-        <x:v>DJI大疆</x:v>
+        <x:v>联发科技</x:v>
       </x:c>
       <x:c r="C66" s="4" t="str">
-        <x:v>无人机/智能硬件</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D66" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E66" s="4" t="str">
-        <x:v>深圳、东莞、上海、北京、西安等</x:v>
+        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
       </x:c>
       <x:c r="F66" s="4" t="str">
-        <x:v>正式批-拓疆者计划</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G66" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H66" s="4" t="str">
-        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
-      </x:c>
-      <x:c r="I66" s="17" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
+        <x:v>软件类、通信类、IC类</x:v>
+      </x:c>
+      <x:c r="I66" s="15" t="str">
+        <x:v>https://mediatek.zhiye.com/</x:v>
       </x:c>
       <x:c r="J66" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K66" s="4" t="str">
-        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
+        <x:v>否；明确安排7-8月笔试</x:v>
       </x:c>
       <x:c r="L66" s="4" t="str">
         <x:v>已核验开放</x:v>
@@ -3964,13 +3964,13 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N66" s="4" t="str">
-        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
-      </x:c>
-      <x:c r="O66" s="17" t="str">
+        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
+      </x:c>
+      <x:c r="O66" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P66" s="15" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
+      <x:c r="P66" s="14" t="str">
+        <x:v>A-官方招聘公告已核验</x:v>
       </x:c>
       <x:c r="Q66" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3978,51 +3978,51 @@
     </x:row>
     <x:row r="67" ht="54" customHeight="1">
       <x:c r="A67" s="4" t="str">
-        <x:v>2026-07-15</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B67" s="4" t="str">
-        <x:v>蔚来</x:v>
+        <x:v>DJI大疆</x:v>
       </x:c>
       <x:c r="C67" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>无人机/智能硬件</x:v>
       </x:c>
       <x:c r="D67" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E67" s="4" t="str">
-        <x:v>上海、合肥、北京、武汉、南京等</x:v>
+        <x:v>深圳、东莞、上海、北京、西安等</x:v>
       </x:c>
       <x:c r="F67" s="4" t="str">
-        <x:v>技术提前批</x:v>
+        <x:v>正式批-拓疆者计划</x:v>
       </x:c>
       <x:c r="G67" s="4" t="str">
-        <x:v>2024年9月-2027年8月毕业</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H67" s="4" t="str">
-        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
-      </x:c>
-      <x:c r="I67" s="17" t="str">
-        <x:v>https://campus.nio.com/</x:v>
+        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
+      </x:c>
+      <x:c r="I67" s="15" t="str">
+        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
       </x:c>
       <x:c r="J67" s="4" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K67" s="4" t="str">
-        <x:v>否；有笔试/测评</x:v>
+        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
       </x:c>
       <x:c r="L67" s="4" t="str">
         <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M67" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N67" s="4" t="str">
-        <x:v>最多同时申请3个岗位。</x:v>
-      </x:c>
-      <x:c r="O67" s="17" t="str">
+        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
+      </x:c>
+      <x:c r="O67" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P67" s="15" t="str">
+      <x:c r="P67" s="14" t="str">
         <x:v>A-官方来源公告已核验</x:v>
       </x:c>
       <x:c r="Q67" s="4" t="str">
@@ -4031,108 +4031,108 @@
     </x:row>
     <x:row r="68" ht="54" customHeight="1">
       <x:c r="A68" s="4" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="B68" s="4" t="str">
-        <x:v>北方华创</x:v>
+        <x:v>蔚来</x:v>
       </x:c>
       <x:c r="C68" s="4" t="str">
-        <x:v>半导体设备</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D68" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E68" s="4" t="str">
-        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
+        <x:v>上海、合肥、北京、武汉、南京等</x:v>
       </x:c>
       <x:c r="F68" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>技术提前批</x:v>
       </x:c>
       <x:c r="G68" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2024年9月-2027年8月毕业</x:v>
       </x:c>
       <x:c r="H68" s="4" t="str">
-        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
-      </x:c>
-      <x:c r="I68" s="17" t="str">
-        <x:v>https://career.naura.com/campus</x:v>
+        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
+      </x:c>
+      <x:c r="I68" s="15" t="str">
+        <x:v>https://campus.nio.com/</x:v>
       </x:c>
       <x:c r="J68" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K68" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；有笔试/测评</x:v>
       </x:c>
       <x:c r="L68" s="4" t="str">
-        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M68" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N68" s="4" t="str">
-        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
-      </x:c>
-      <x:c r="O68" s="17" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P68" s="15" t="str">
-        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
+        <x:v>最多同时申请3个岗位。</x:v>
+      </x:c>
+      <x:c r="O68" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P68" s="14" t="str">
+        <x:v>A-官方来源公告已核验</x:v>
       </x:c>
       <x:c r="Q68" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="54" customHeight="1">
       <x:c r="A69" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="B69" s="4" t="str">
-        <x:v>百度</x:v>
+        <x:v>北方华创</x:v>
       </x:c>
       <x:c r="C69" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>半导体设备</x:v>
       </x:c>
       <x:c r="D69" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E69" s="4" t="str">
-        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F69" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G69" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H69" s="4" t="str">
-        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
-      </x:c>
-      <x:c r="I69" s="17" t="str">
-        <x:v>https://talent.baidu.com/jobs</x:v>
+        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
+      </x:c>
+      <x:c r="I69" s="15" t="str">
+        <x:v>https://career.naura.com/campus</x:v>
       </x:c>
       <x:c r="J69" s="4" t="str">
-        <x:v>2027-06-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K69" s="4" t="str">
-        <x:v>部分免；并非所有候选人参加笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L69" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
       </x:c>
       <x:c r="M69" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N69" s="4" t="str">
-        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
-      </x:c>
-      <x:c r="O69" s="17" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P69" s="15" t="str">
-        <x:v>A-官方招聘日历/官方来源已核验</x:v>
+        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
+      </x:c>
+      <x:c r="O69" s="15" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P69" s="14" t="str">
+        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
       </x:c>
       <x:c r="Q69" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="54" customHeight="1">
@@ -4140,102 +4140,102 @@
         <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B70" s="4" t="str">
-        <x:v>中国航天科工集团第六研究院</x:v>
+        <x:v>百度</x:v>
       </x:c>
       <x:c r="C70" s="4" t="str">
-        <x:v>航天/军工/动力系统</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D70" s="4" t="str">
-        <x:v>央企院所</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E70" s="4" t="str">
-        <x:v>呼和浩特及所属单位</x:v>
+        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
       </x:c>
       <x:c r="F70" s="4" t="str">
-        <x:v>提前批+暑期开放日</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G70" s="4" t="str">
-        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H70" s="4" t="str">
-        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
-      </x:c>
-      <x:c r="I70" s="17" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
+        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+      </x:c>
+      <x:c r="I70" s="15" t="str">
+        <x:v>https://talent.baidu.com/jobs</x:v>
       </x:c>
       <x:c r="J70" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-30</x:v>
       </x:c>
       <x:c r="K70" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>部分免；并非所有候选人参加笔试</x:v>
       </x:c>
       <x:c r="L70" s="4" t="str">
-        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M70" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N70" s="4" t="str">
-        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
-      </x:c>
-      <x:c r="O70" s="17" t="str">
-        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
-      </x:c>
-      <x:c r="P70" s="18" t="str">
-        <x:v>B-高校就业网公开公告</x:v>
+        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
+      </x:c>
+      <x:c r="O70" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P70" s="14" t="str">
+        <x:v>A-官方招聘日历/官方来源已核验</x:v>
       </x:c>
       <x:c r="Q70" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="54" customHeight="1">
       <x:c r="A71" s="4" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B71" s="4" t="str">
-        <x:v>思瑞浦</x:v>
+        <x:v>中国航天科工集团第六研究院</x:v>
       </x:c>
       <x:c r="C71" s="4" t="str">
-        <x:v>半导体/模拟IC</x:v>
+        <x:v>航天/军工/动力系统</x:v>
       </x:c>
       <x:c r="D71" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企院所</x:v>
       </x:c>
       <x:c r="E71" s="4" t="str">
-        <x:v>上海、深圳等，以岗位页为准</x:v>
+        <x:v>呼和浩特及所属单位</x:v>
       </x:c>
       <x:c r="F71" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批+暑期开放日</x:v>
       </x:c>
       <x:c r="G71" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
       </x:c>
       <x:c r="H71" s="4" t="str">
-        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
-      </x:c>
-      <x:c r="I71" s="17" t="str">
-        <x:v>https://www.3peak.cn/careers</x:v>
+        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
+      </x:c>
+      <x:c r="I71" s="15" t="str">
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
       <x:c r="J71" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K71" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L71" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
+        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
       </x:c>
       <x:c r="M71" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N71" s="4" t="str">
-        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
-      </x:c>
-      <x:c r="O71" s="17" t="str">
-        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
+        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
+      </x:c>
+      <x:c r="O71" s="15" t="str">
+        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
       </x:c>
       <x:c r="P71" s="18" t="str">
-        <x:v>B-招聘平台/高校就业转载</x:v>
+        <x:v>B-高校就业网公开公告</x:v>
       </x:c>
       <x:c r="Q71" s="4" t="str">
         <x:v>2026-07-27</x:v>
@@ -4243,178 +4243,178 @@
     </x:row>
     <x:row r="72" ht="54" customHeight="1">
       <x:c r="A72" s="4" t="str">
-        <x:v>不晚于2026-07-07</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="B72" s="4" t="str">
-        <x:v>文远知行WeRide</x:v>
+        <x:v>思瑞浦</x:v>
       </x:c>
       <x:c r="C72" s="4" t="str">
-        <x:v>自动驾驶/人工智能</x:v>
+        <x:v>半导体/模拟IC</x:v>
       </x:c>
       <x:c r="D72" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E72" s="4" t="str">
+        <x:v>上海、深圳等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F72" s="4" t="str">
+        <x:v>正式批/校园招聘</x:v>
+      </x:c>
+      <x:c r="G72" s="4" t="str">
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H72" s="4" t="str">
+        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
+      </x:c>
+      <x:c r="I72" s="15" t="str">
+        <x:v>https://www.3peak.cn/careers</x:v>
+      </x:c>
+      <x:c r="J72" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K72" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L72" s="4" t="str">
+        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
+      </x:c>
+      <x:c r="M72" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N72" s="4" t="str">
+        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
+      </x:c>
+      <x:c r="O72" s="15" t="str">
+        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
+      </x:c>
+      <x:c r="P72" s="18" t="str">
+        <x:v>B-招聘平台/高校就业转载</x:v>
+      </x:c>
+      <x:c r="Q72" s="4" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="54" customHeight="1">
+      <x:c r="A73" s="4" t="str">
+        <x:v>不晚于2026-07-07</x:v>
+      </x:c>
+      <x:c r="B73" s="4" t="str">
+        <x:v>文远知行WeRide</x:v>
+      </x:c>
+      <x:c r="C73" s="4" t="str">
+        <x:v>自动驾驶/人工智能</x:v>
+      </x:c>
+      <x:c r="D73" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E73" s="4" t="str">
         <x:v>广州、深圳、武汉等，以岗位页为准</x:v>
       </x:c>
-      <x:c r="F72" s="4" t="str">
+      <x:c r="F73" s="4" t="str">
         <x:v>正式批/校招/可转正实习</x:v>
       </x:c>
-      <x:c r="G72" s="4" t="str">
+      <x:c r="G73" s="4" t="str">
         <x:v>2027届应届毕业生及可转正实习生，以岗位要求为准</x:v>
       </x:c>
-      <x:c r="H72" s="4" t="str">
+      <x:c r="H73" s="4" t="str">
         <x:v>感知/预测/规划控制算法、算法测试、测试开发、SRE、云与车端安全、AI Infra、仿真平台等</x:v>
       </x:c>
-      <x:c r="I72" s="17" t="str">
+      <x:c r="I73" s="15" t="str">
         <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
       </x:c>
-      <x:c r="J72" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K72" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L72" s="4" t="str">
+      <x:c r="J73" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K73" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L73" s="4" t="str">
         <x:v>企业官方校招系统在招；已核验137个职位</x:v>
       </x:c>
-      <x:c r="M72" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N72" s="4" t="str">
+      <x:c r="M73" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N73" s="4" t="str">
         <x:v>官方列表显示2027届校招职位最早发布于7月7日；部分岗位为可转正实习，城市和岗位随招聘系统实时调整。</x:v>
       </x:c>
-      <x:c r="O72" s="17" t="str">
+      <x:c r="O73" s="15" t="str">
         <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
       </x:c>
-      <x:c r="P72" s="15" t="str">
+      <x:c r="P73" s="14" t="str">
         <x:v>A-企业官方校招系统与职位列表已核验</x:v>
       </x:c>
-      <x:c r="Q72" s="4" t="str">
+      <x:c r="Q73" s="4" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="54" customHeight="1">
-      <x:c r="A73" s="14" t="str">
+    <x:row r="74" ht="54" customHeight="1">
+      <x:c r="A74" s="16" t="str">
         <x:v>2026-07-06</x:v>
       </x:c>
-      <x:c r="B73" s="14" t="str">
+      <x:c r="B74" s="16" t="str">
         <x:v>米哈游</x:v>
       </x:c>
-      <x:c r="C73" s="14" t="str">
+      <x:c r="C74" s="16" t="str">
         <x:v>游戏/互联网</x:v>
       </x:c>
-      <x:c r="D73" s="14" t="str">
+      <x:c r="D74" s="16" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E73" s="14" t="str">
+      <x:c r="E74" s="16" t="str">
         <x:v>上海、北京</x:v>
       </x:c>
-      <x:c r="F73" s="14" t="str">
+      <x:c r="F74" s="16" t="str">
         <x:v>技术提前批</x:v>
       </x:c>
-      <x:c r="G73" s="14" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H73" s="14" t="str">
+      <x:c r="G74" s="16" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H74" s="16" t="str">
         <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
       </x:c>
-      <x:c r="I73" s="16" t="str">
+      <x:c r="I74" s="17" t="str">
         <x:v>https://campus.mihoyo.com/</x:v>
       </x:c>
-      <x:c r="J73" s="14" t="str">
+      <x:c r="J74" s="16" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
-      <x:c r="K73" s="14" t="str">
+      <x:c r="K74" s="16" t="str">
         <x:v>有免笔试直通面试机会</x:v>
       </x:c>
-      <x:c r="L73" s="14" t="str">
+      <x:c r="L74" s="16" t="str">
         <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
       </x:c>
-      <x:c r="M73" s="14" t="str">
+      <x:c r="M74" s="16" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N73" s="14" t="str">
+      <x:c r="N74" s="16" t="str">
         <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
-      </x:c>
-      <x:c r="O73" s="16" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P73" s="15" t="str">
-        <x:v>A-官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q73" s="14" t="str">
-        <x:v>2026-07-30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" ht="54" customHeight="1">
-      <x:c r="A74" s="4" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="B74" s="4" t="str">
-        <x:v>京东方-先锋京英计划</x:v>
-      </x:c>
-      <x:c r="C74" s="4" t="str">
-        <x:v>显示技术/半导体/物联网</x:v>
-      </x:c>
-      <x:c r="D74" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E74" s="4" t="str">
-        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
-      </x:c>
-      <x:c r="F74" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G74" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H74" s="4" t="str">
-        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
-      </x:c>
-      <x:c r="I74" s="17" t="str">
-        <x:v>https://campus.boe.com/</x:v>
-      </x:c>
-      <x:c r="J74" s="4" t="str">
-        <x:v>2026-08-14</x:v>
-      </x:c>
-      <x:c r="K74" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L74" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M74" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N74" s="4" t="str">
-        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
       </x:c>
       <x:c r="O74" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P74" s="15" t="str">
-        <x:v>A-国家大学生就业平台公告已核验</x:v>
-      </x:c>
-      <x:c r="Q74" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+      <x:c r="P74" s="14" t="str">
+        <x:v>A-官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q74" s="16" t="str">
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="54" customHeight="1">
       <x:c r="A75" s="4" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="B75" s="4" t="str">
-        <x:v>中国航天科技集团</x:v>
+        <x:v>京东方-先锋京英计划</x:v>
       </x:c>
       <x:c r="C75" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>显示技术/半导体/物联网</x:v>
       </x:c>
       <x:c r="D75" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E75" s="4" t="str">
-        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
+        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
       </x:c>
       <x:c r="F75" s="4" t="str">
         <x:v>提前批</x:v>
@@ -4423,31 +4423,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H75" s="4" t="str">
-        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
-      </x:c>
-      <x:c r="I75" s="17" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
+        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
+      </x:c>
+      <x:c r="I75" s="15" t="str">
+        <x:v>https://campus.boe.com/</x:v>
       </x:c>
       <x:c r="J75" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K75" s="4" t="str">
-        <x:v>各院所自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L75" s="4" t="str">
-        <x:v>官方公告已确认启动</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M75" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N75" s="4" t="str">
-        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
-      </x:c>
-      <x:c r="O75" s="17" t="str">
-        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
-      </x:c>
-      <x:c r="P75" s="15" t="str">
-        <x:v>A-国务院国资委/集团官方来源</x:v>
+        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
+      </x:c>
+      <x:c r="O75" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P75" s="14" t="str">
+        <x:v>A-国家大学生就业平台公告已核验</x:v>
       </x:c>
       <x:c r="Q75" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4455,52 +4455,52 @@
     </x:row>
     <x:row r="76" ht="54" customHeight="1">
       <x:c r="A76" s="4" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="B76" s="4" t="str">
-        <x:v>高途</x:v>
+        <x:v>中国航天科技集团</x:v>
       </x:c>
       <x:c r="C76" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D76" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E76" s="4" t="str">
-        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
+        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
       </x:c>
       <x:c r="F76" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G76" s="4" t="str">
-        <x:v>27届为主，优秀28届也可投</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H76" s="4" t="str">
-        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
-      </x:c>
-      <x:c r="I76" s="17" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
+        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
+      </x:c>
+      <x:c r="I76" s="15" t="str">
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J76" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K76" s="4" t="str">
-        <x:v>否；流程包含笔试</x:v>
+        <x:v>各院所自行组织，未统一</x:v>
       </x:c>
       <x:c r="L76" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>官方公告已确认启动</x:v>
       </x:c>
       <x:c r="M76" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N76" s="4" t="str">
-        <x:v>滚动发放Offer，截止时间未公布。</x:v>
-      </x:c>
-      <x:c r="O76" s="17" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P76" s="15" t="str">
-        <x:v>A-官方投递平台已核验</x:v>
+        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
+      </x:c>
+      <x:c r="O76" s="15" t="str">
+        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
+      </x:c>
+      <x:c r="P76" s="14" t="str">
+        <x:v>A-国务院国资委/集团官方来源</x:v>
       </x:c>
       <x:c r="Q76" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4508,52 +4508,52 @@
     </x:row>
     <x:row r="77" ht="54" customHeight="1">
       <x:c r="A77" s="4" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="B77" s="4" t="str">
-        <x:v>中汽中心</x:v>
+        <x:v>高途</x:v>
       </x:c>
       <x:c r="C77" s="4" t="str">
-        <x:v>汽车检测/科研</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D77" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E77" s="4" t="str">
-        <x:v>天津、武汉、北京、上海等</x:v>
+        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
       </x:c>
       <x:c r="F77" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G77" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>27届为主，优秀28届也可投</x:v>
       </x:c>
       <x:c r="H77" s="4" t="str">
-        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
-      </x:c>
-      <x:c r="I77" s="17" t="str">
-        <x:v>https://www.catarc.ac.cn/</x:v>
+        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
+      </x:c>
+      <x:c r="I77" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
       </x:c>
       <x:c r="J77" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K77" s="4" t="str">
-        <x:v>官方未统一说明</x:v>
+        <x:v>否；流程包含笔试</x:v>
       </x:c>
       <x:c r="L77" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M77" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N77" s="4" t="str">
-        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
-      </x:c>
-      <x:c r="O77" s="17" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
-      </x:c>
-      <x:c r="P77" s="18" t="str">
-        <x:v>B-公开招聘公告</x:v>
+        <x:v>滚动发放Offer，截止时间未公布。</x:v>
+      </x:c>
+      <x:c r="O77" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P77" s="14" t="str">
+        <x:v>A-官方投递平台已核验</x:v>
       </x:c>
       <x:c r="Q77" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4561,140 +4561,140 @@
     </x:row>
     <x:row r="78" ht="54" customHeight="1">
       <x:c r="A78" s="4" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="B78" s="4" t="str">
-        <x:v>中国航天科工集团</x:v>
+        <x:v>中汽中心</x:v>
       </x:c>
       <x:c r="C78" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>汽车检测/科研</x:v>
       </x:c>
       <x:c r="D78" s="4" t="str">
         <x:v>央企</x:v>
       </x:c>
       <x:c r="E78" s="4" t="str">
-        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
+        <x:v>天津、武汉、北京、上海等</x:v>
       </x:c>
       <x:c r="F78" s="4" t="str">
-        <x:v>正式批/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G78" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H78" s="4" t="str">
-        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
-      </x:c>
-      <x:c r="I78" s="17" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
+        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
+      </x:c>
+      <x:c r="I78" s="15" t="str">
+        <x:v>https://www.catarc.ac.cn/</x:v>
       </x:c>
       <x:c r="J78" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K78" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L78" s="4" t="str">
-        <x:v>官网公告已确认启动</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M78" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N78" s="4" t="str">
-        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
-      </x:c>
-      <x:c r="O78" s="17" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
-      </x:c>
-      <x:c r="P78" s="15" t="str">
-        <x:v>A-集团官网公告已核验</x:v>
+        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
+      </x:c>
+      <x:c r="O78" s="15" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
+      </x:c>
+      <x:c r="P78" s="18" t="str">
+        <x:v>B-公开招聘公告</x:v>
       </x:c>
       <x:c r="Q78" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="54" customHeight="1">
       <x:c r="A79" s="4" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="B79" s="4" t="str">
-        <x:v>禾赛科技</x:v>
+        <x:v>中国航天科工集团</x:v>
       </x:c>
       <x:c r="C79" s="4" t="str">
-        <x:v>激光雷达/机器人</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D79" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E79" s="4" t="str">
-        <x:v>上海、杭州</x:v>
+        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
       </x:c>
       <x:c r="F79" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/提前批</x:v>
       </x:c>
       <x:c r="G79" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H79" s="4" t="str">
-        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
-      </x:c>
-      <x:c r="I79" s="17" t="str">
-        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
+        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
+      </x:c>
+      <x:c r="I79" s="15" t="str">
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
       <x:c r="J79" s="4" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K79" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L79" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>官网公告已确认启动</x:v>
       </x:c>
       <x:c r="M79" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N79" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O79" s="17" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P79" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
+      </x:c>
+      <x:c r="O79" s="15" t="str">
+        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
+      </x:c>
+      <x:c r="P79" s="14" t="str">
+        <x:v>A-集团官网公告已核验</x:v>
       </x:c>
       <x:c r="Q79" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="54" customHeight="1">
       <x:c r="A80" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="B80" s="4" t="str">
-        <x:v>北京国望光学科技有限公司</x:v>
+        <x:v>禾赛科技</x:v>
       </x:c>
       <x:c r="C80" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>激光雷达/机器人</x:v>
       </x:c>
       <x:c r="D80" s="4" t="str">
-        <x:v>央国企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E80" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>上海、杭州</x:v>
       </x:c>
       <x:c r="F80" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G80" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H80" s="4" t="str">
-        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
-      </x:c>
-      <x:c r="I80" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
+      </x:c>
+      <x:c r="I80" s="15" t="str">
+        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
       </x:c>
       <x:c r="J80" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="K80" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -4703,12 +4703,12 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M80" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N80" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O80" s="17" t="str">
+      <x:c r="O80" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P80" s="18" t="str">
@@ -4723,25 +4723,25 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B81" s="4" t="str">
-        <x:v>乐读</x:v>
+        <x:v>北京国望光学科技有限公司</x:v>
       </x:c>
       <x:c r="C81" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D81" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央国企</x:v>
       </x:c>
       <x:c r="E81" s="4" t="str">
-        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F81" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G81" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H81" s="4" t="str">
-        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
+        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
       </x:c>
       <x:c r="I81" s="22" t="str">
         <x:v>官方入口待核验</x:v>
@@ -4753,19 +4753,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L81" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M81" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N81" s="4" t="str">
-        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
-      </x:c>
-      <x:c r="O81" s="17" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O81" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P81" s="18" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q81" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4776,16 +4776,16 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B82" s="4" t="str">
-        <x:v>龙蟠科技</x:v>
+        <x:v>乐读</x:v>
       </x:c>
       <x:c r="C82" s="4" t="str">
-        <x:v>新能源材料/化工</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D82" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E82" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
       </x:c>
       <x:c r="F82" s="4" t="str">
         <x:v>提前批</x:v>
@@ -4794,31 +4794,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H82" s="4" t="str">
-        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
-      </x:c>
-      <x:c r="I82" s="17" t="str">
-        <x:v>https://www.lopal.com.cn/join</x:v>
+        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
+      </x:c>
+      <x:c r="I82" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J82" s="4" t="str">
-        <x:v>2027-06-01</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K82" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L82" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M82" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N82" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O82" s="17" t="str">
+        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
+      </x:c>
+      <x:c r="O82" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P82" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>B-招聘平台公开汇总</x:v>
       </x:c>
       <x:c r="Q82" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4829,16 +4829,16 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B83" s="4" t="str">
-        <x:v>牧原</x:v>
+        <x:v>龙蟠科技</x:v>
       </x:c>
       <x:c r="C83" s="4" t="str">
-        <x:v>农业/食品/智能养殖</x:v>
+        <x:v>新能源材料/化工</x:v>
       </x:c>
       <x:c r="D83" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E83" s="4" t="str">
-        <x:v>河南南阳及全国</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F83" s="4" t="str">
         <x:v>提前批</x:v>
@@ -4847,13 +4847,13 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H83" s="4" t="str">
-        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
-      </x:c>
-      <x:c r="I83" s="17" t="str">
-        <x:v>https://job.muyuanfoods.com/</x:v>
+        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
+      </x:c>
+      <x:c r="I83" s="15" t="str">
+        <x:v>https://www.lopal.com.cn/join</x:v>
       </x:c>
       <x:c r="J83" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-01</x:v>
       </x:c>
       <x:c r="K83" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -4862,12 +4862,12 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M83" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N83" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O83" s="17" t="str">
+      <x:c r="O83" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P83" s="18" t="str">
@@ -4882,28 +4882,28 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B84" s="4" t="str">
-        <x:v>三一集团-小语种校招</x:v>
+        <x:v>牧原</x:v>
       </x:c>
       <x:c r="C84" s="4" t="str">
-        <x:v>工程机械/制造</x:v>
+        <x:v>农业/食品/智能养殖</x:v>
       </x:c>
       <x:c r="D84" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E84" s="4" t="str">
-        <x:v>海外多国</x:v>
+        <x:v>河南南阳及全国</x:v>
       </x:c>
       <x:c r="F84" s="4" t="str">
-        <x:v>小语种专项/正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G84" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H84" s="4" t="str">
-        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
-      </x:c>
-      <x:c r="I84" s="17" t="str">
-        <x:v>https://sanycampus.zhiye.com/</x:v>
+        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
+      </x:c>
+      <x:c r="I84" s="15" t="str">
+        <x:v>https://job.muyuanfoods.com/</x:v>
       </x:c>
       <x:c r="J84" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4920,7 +4920,7 @@
       <x:c r="N84" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O84" s="17" t="str">
+      <x:c r="O84" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P84" s="18" t="str">
@@ -4935,28 +4935,28 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B85" s="4" t="str">
-        <x:v>上海电气-暑期精英训练营</x:v>
+        <x:v>三一集团-小语种校招</x:v>
       </x:c>
       <x:c r="C85" s="4" t="str">
-        <x:v>高端装备/能源</x:v>
+        <x:v>工程机械/制造</x:v>
       </x:c>
       <x:c r="D85" s="4" t="str">
-        <x:v>地方国企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E85" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>海外多国</x:v>
       </x:c>
       <x:c r="F85" s="4" t="str">
-        <x:v>训练营/秋招直通</x:v>
+        <x:v>小语种专项/正式批</x:v>
       </x:c>
       <x:c r="G85" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H85" s="4" t="str">
-        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
-      </x:c>
-      <x:c r="I85" s="17" t="str">
-        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
+        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
+      </x:c>
+      <x:c r="I85" s="15" t="str">
+        <x:v>https://sanycampus.zhiye.com/</x:v>
       </x:c>
       <x:c r="J85" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4973,7 +4973,7 @@
       <x:c r="N85" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O85" s="17" t="str">
+      <x:c r="O85" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P85" s="18" t="str">
@@ -4988,28 +4988,28 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B86" s="4" t="str">
-        <x:v>vivo-蓝极星计划</x:v>
+        <x:v>上海电气-暑期精英训练营</x:v>
       </x:c>
       <x:c r="C86" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>高端装备/能源</x:v>
       </x:c>
       <x:c r="D86" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>地方国企</x:v>
       </x:c>
       <x:c r="E86" s="4" t="str">
-        <x:v>深圳、杭州、东莞、上海</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F86" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>训练营/秋招直通</x:v>
       </x:c>
       <x:c r="G86" s="4" t="str">
-        <x:v>博士为主</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H86" s="4" t="str">
-        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
-      </x:c>
-      <x:c r="I86" s="17" t="str">
-        <x:v>https://hr.vivo.com/</x:v>
+        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
+      </x:c>
+      <x:c r="I86" s="15" t="str">
+        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
       </x:c>
       <x:c r="J86" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5018,19 +5018,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L86" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M86" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N86" s="4" t="str">
-        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
-      </x:c>
-      <x:c r="O86" s="17" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O86" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P86" s="18" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q86" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5038,31 +5038,31 @@
     </x:row>
     <x:row r="87" ht="54" customHeight="1">
       <x:c r="A87" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B87" s="4" t="str">
-        <x:v>澜起科技</x:v>
+        <x:v>vivo-蓝极星计划</x:v>
       </x:c>
       <x:c r="C87" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D87" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E87" s="4" t="str">
-        <x:v>昆山、西安、南京</x:v>
+        <x:v>深圳、杭州、东莞、上海</x:v>
       </x:c>
       <x:c r="F87" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G87" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>博士为主</x:v>
       </x:c>
       <x:c r="H87" s="4" t="str">
-        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
-      </x:c>
-      <x:c r="I87" s="17" t="str">
-        <x:v>https://www.montage-tech.com/cn/careers</x:v>
+        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
+      </x:c>
+      <x:c r="I87" s="15" t="str">
+        <x:v>https://hr.vivo.com/</x:v>
       </x:c>
       <x:c r="J87" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5071,19 +5071,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L87" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M87" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N87" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O87" s="17" t="str">
+        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
+      </x:c>
+      <x:c r="O87" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P87" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>B-招聘平台公开汇总</x:v>
       </x:c>
       <x:c r="Q87" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5094,16 +5094,16 @@
         <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B88" s="4" t="str">
-        <x:v>上海宇量昇</x:v>
+        <x:v>澜起科技</x:v>
       </x:c>
       <x:c r="C88" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D88" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E88" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>昆山、西安、南京</x:v>
       </x:c>
       <x:c r="F88" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5112,10 +5112,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H88" s="4" t="str">
-        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
-      </x:c>
-      <x:c r="I88" s="17" t="str">
-        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
+        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
+      </x:c>
+      <x:c r="I88" s="15" t="str">
+        <x:v>https://www.montage-tech.com/cn/careers</x:v>
       </x:c>
       <x:c r="J88" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5132,7 +5132,7 @@
       <x:c r="N88" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O88" s="17" t="str">
+      <x:c r="O88" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P88" s="18" t="str">
@@ -5147,16 +5147,16 @@
         <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B89" s="4" t="str">
-        <x:v>是为科技</x:v>
+        <x:v>上海宇量昇</x:v>
       </x:c>
       <x:c r="C89" s="4" t="str">
-        <x:v>新能源/智能制造</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D89" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E89" s="4" t="str">
-        <x:v>南京、上海、常州</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F89" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5165,10 +5165,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H89" s="4" t="str">
-        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
-      </x:c>
-      <x:c r="I89" s="17" t="str">
-        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
+        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
+      </x:c>
+      <x:c r="I89" s="15" t="str">
+        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
       </x:c>
       <x:c r="J89" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5185,7 +5185,7 @@
       <x:c r="N89" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O89" s="17" t="str">
+      <x:c r="O89" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P89" s="18" t="str">
@@ -5200,16 +5200,16 @@
         <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B90" s="4" t="str">
-        <x:v>游族网络</x:v>
+        <x:v>是为科技</x:v>
       </x:c>
       <x:c r="C90" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>新能源/智能制造</x:v>
       </x:c>
       <x:c r="D90" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E90" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>南京、上海、常州</x:v>
       </x:c>
       <x:c r="F90" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5218,10 +5218,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H90" s="4" t="str">
-        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
-      </x:c>
-      <x:c r="I90" s="17" t="str">
-        <x:v>https://job.youzu.com/</x:v>
+        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
+      </x:c>
+      <x:c r="I90" s="15" t="str">
+        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
       </x:c>
       <x:c r="J90" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5238,7 +5238,7 @@
       <x:c r="N90" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O90" s="17" t="str">
+      <x:c r="O90" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P90" s="18" t="str">
@@ -5250,19 +5250,19 @@
     </x:row>
     <x:row r="91" ht="54" customHeight="1">
       <x:c r="A91" s="4" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B91" s="4" t="str">
-        <x:v>中铁设计</x:v>
+        <x:v>游族网络</x:v>
       </x:c>
       <x:c r="C91" s="4" t="str">
-        <x:v>轨道交通/工程设计</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D91" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E91" s="4" t="str">
-        <x:v>北京、济南、郑州、太原</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F91" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5271,10 +5271,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H91" s="4" t="str">
-        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
-      </x:c>
-      <x:c r="I91" s="17" t="str">
-        <x:v>https://www.crdc.com/</x:v>
+        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
+      </x:c>
+      <x:c r="I91" s="15" t="str">
+        <x:v>https://job.youzu.com/</x:v>
       </x:c>
       <x:c r="J91" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5291,7 +5291,7 @@
       <x:c r="N91" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O91" s="17" t="str">
+      <x:c r="O91" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P91" s="18" t="str">
@@ -5303,31 +5303,31 @@
     </x:row>
     <x:row r="92" ht="54" customHeight="1">
       <x:c r="A92" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="B92" s="4" t="str">
-        <x:v>迈安德集团-校园大使</x:v>
+        <x:v>中铁设计</x:v>
       </x:c>
       <x:c r="C92" s="4" t="str">
-        <x:v>粮油工程/装备</x:v>
+        <x:v>轨道交通/工程设计</x:v>
       </x:c>
       <x:c r="D92" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E92" s="4" t="str">
-        <x:v>扬州/高校</x:v>
+        <x:v>北京、济南、郑州、太原</x:v>
       </x:c>
       <x:c r="F92" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G92" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H92" s="4" t="str">
-        <x:v>校园大使</x:v>
-      </x:c>
-      <x:c r="I92" s="17" t="str">
-        <x:v>https://www.myande.com/</x:v>
+        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
+      </x:c>
+      <x:c r="I92" s="15" t="str">
+        <x:v>https://www.crdc.com/</x:v>
       </x:c>
       <x:c r="J92" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5344,7 +5344,7 @@
       <x:c r="N92" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O92" s="17" t="str">
+      <x:c r="O92" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P92" s="18" t="str">
@@ -5359,28 +5359,28 @@
         <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B93" s="4" t="str">
-        <x:v>迅仿科技</x:v>
+        <x:v>迈安德集团-校园大使</x:v>
       </x:c>
       <x:c r="C93" s="4" t="str">
-        <x:v>工业软件/仿真</x:v>
+        <x:v>粮油工程/装备</x:v>
       </x:c>
       <x:c r="D93" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E93" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>扬州/高校</x:v>
       </x:c>
       <x:c r="F93" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G93" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H93" s="4" t="str">
-        <x:v>仿真工程师</x:v>
-      </x:c>
-      <x:c r="I93" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>校园大使</x:v>
+      </x:c>
+      <x:c r="I93" s="15" t="str">
+        <x:v>https://www.myande.com/</x:v>
       </x:c>
       <x:c r="J93" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5397,7 +5397,7 @@
       <x:c r="N93" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O93" s="17" t="str">
+      <x:c r="O93" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P93" s="18" t="str">
@@ -5409,34 +5409,34 @@
     </x:row>
     <x:row r="94" ht="54" customHeight="1">
       <x:c r="A94" s="4" t="str">
-        <x:v>2026-06-12</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B94" s="4" t="str">
-        <x:v>MOVA</x:v>
+        <x:v>迅仿科技</x:v>
       </x:c>
       <x:c r="C94" s="4" t="str">
-        <x:v>智能家电/机器人</x:v>
+        <x:v>工业软件/仿真</x:v>
       </x:c>
       <x:c r="D94" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E94" s="4" t="str">
-        <x:v>苏州及全国</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F94" s="4" t="str">
-        <x:v>全球校招/正式批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G94" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H94" s="4" t="str">
-        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
-      </x:c>
-      <x:c r="I94" s="17" t="str">
-        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+        <x:v>仿真工程师</x:v>
+      </x:c>
+      <x:c r="I94" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J94" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K94" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -5445,12 +5445,12 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M94" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N94" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O94" s="17" t="str">
+      <x:c r="O94" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P94" s="18" t="str">
@@ -5462,34 +5462,34 @@
     </x:row>
     <x:row r="95" ht="54" customHeight="1">
       <x:c r="A95" s="4" t="str">
-        <x:v>2026-06-11</x:v>
+        <x:v>2026-06-12</x:v>
       </x:c>
       <x:c r="B95" s="4" t="str">
-        <x:v>财通证券</x:v>
+        <x:v>MOVA</x:v>
       </x:c>
       <x:c r="C95" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>智能家电/机器人</x:v>
       </x:c>
       <x:c r="D95" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E95" s="4" t="str">
-        <x:v>杭州、上海、深圳、北京</x:v>
+        <x:v>苏州及全国</x:v>
       </x:c>
       <x:c r="F95" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>全球校招/正式批</x:v>
       </x:c>
       <x:c r="G95" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H95" s="4" t="str">
-        <x:v>总部、参股公司、分公司岗位</x:v>
-      </x:c>
-      <x:c r="I95" s="17" t="str">
-        <x:v>https://www.ctsec.com/joinUs</x:v>
+        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+      </x:c>
+      <x:c r="I95" s="15" t="str">
+        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
       </x:c>
       <x:c r="J95" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K95" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -5498,12 +5498,12 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M95" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N95" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O95" s="17" t="str">
+      <x:c r="O95" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P95" s="18" t="str">
@@ -5515,31 +5515,31 @@
     </x:row>
     <x:row r="96" ht="54" customHeight="1">
       <x:c r="A96" s="4" t="str">
-        <x:v>2026-06-10</x:v>
+        <x:v>2026-06-11</x:v>
       </x:c>
       <x:c r="B96" s="4" t="str">
-        <x:v>歌尔股份</x:v>
+        <x:v>财通证券</x:v>
       </x:c>
       <x:c r="C96" s="4" t="str">
-        <x:v>消费电子/智能硬件</x:v>
+        <x:v>证券/金融</x:v>
       </x:c>
       <x:c r="D96" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E96" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>杭州、上海、深圳、北京</x:v>
       </x:c>
       <x:c r="F96" s="4" t="str">
-        <x:v>实习/校招储备</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G96" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H96" s="4" t="str">
-        <x:v>法务助理</x:v>
-      </x:c>
-      <x:c r="I96" s="17" t="str">
-        <x:v>https://career.goertek.com/</x:v>
+        <x:v>总部、参股公司、分公司岗位</x:v>
+      </x:c>
+      <x:c r="I96" s="15" t="str">
+        <x:v>https://www.ctsec.com/joinUs</x:v>
       </x:c>
       <x:c r="J96" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5556,7 +5556,7 @@
       <x:c r="N96" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O96" s="17" t="str">
+      <x:c r="O96" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P96" s="18" t="str">
@@ -5568,31 +5568,31 @@
     </x:row>
     <x:row r="97" ht="54" customHeight="1">
       <x:c r="A97" s="4" t="str">
-        <x:v>2026-06-09</x:v>
+        <x:v>2026-06-10</x:v>
       </x:c>
       <x:c r="B97" s="4" t="str">
-        <x:v>深信服-校园大使</x:v>
+        <x:v>歌尔股份</x:v>
       </x:c>
       <x:c r="C97" s="4" t="str">
-        <x:v>网络安全/云计算</x:v>
+        <x:v>消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D97" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E97" s="4" t="str">
-        <x:v>西安</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F97" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>实习/校招储备</x:v>
       </x:c>
       <x:c r="G97" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H97" s="4" t="str">
-        <x:v>校园大使</x:v>
-      </x:c>
-      <x:c r="I97" s="17" t="str">
-        <x:v>https://hr.sangfor.com/</x:v>
+        <x:v>法务助理</x:v>
+      </x:c>
+      <x:c r="I97" s="15" t="str">
+        <x:v>https://career.goertek.com/</x:v>
       </x:c>
       <x:c r="J97" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5609,7 +5609,7 @@
       <x:c r="N97" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O97" s="17" t="str">
+      <x:c r="O97" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P97" s="18" t="str">
@@ -5621,31 +5621,31 @@
     </x:row>
     <x:row r="98" ht="54" customHeight="1">
       <x:c r="A98" s="4" t="str">
-        <x:v>2026-06-08</x:v>
+        <x:v>2026-06-09</x:v>
       </x:c>
       <x:c r="B98" s="4" t="str">
-        <x:v>晓禾教育</x:v>
+        <x:v>深信服-校园大使</x:v>
       </x:c>
       <x:c r="C98" s="4" t="str">
-        <x:v>教育</x:v>
+        <x:v>网络安全/云计算</x:v>
       </x:c>
       <x:c r="D98" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E98" s="4" t="str">
-        <x:v>武汉、郑州、襄阳、宜昌</x:v>
+        <x:v>西安</x:v>
       </x:c>
       <x:c r="F98" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G98" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H98" s="4" t="str">
-        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
-      </x:c>
-      <x:c r="I98" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>校园大使</x:v>
+      </x:c>
+      <x:c r="I98" s="15" t="str">
+        <x:v>https://hr.sangfor.com/</x:v>
       </x:c>
       <x:c r="J98" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5662,7 +5662,7 @@
       <x:c r="N98" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O98" s="17" t="str">
+      <x:c r="O98" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P98" s="18" t="str">
@@ -5674,31 +5674,31 @@
     </x:row>
     <x:row r="99" ht="54" customHeight="1">
       <x:c r="A99" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-08</x:v>
       </x:c>
       <x:c r="B99" s="4" t="str">
-        <x:v>晖致医药</x:v>
+        <x:v>晓禾教育</x:v>
       </x:c>
       <x:c r="C99" s="4" t="str">
-        <x:v>医药</x:v>
+        <x:v>教育</x:v>
       </x:c>
       <x:c r="D99" s="4" t="str">
-        <x:v>外资</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E99" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>武汉、郑州、襄阳、宜昌</x:v>
       </x:c>
       <x:c r="F99" s="4" t="str">
-        <x:v>实习储备正式岗</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G99" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H99" s="4" t="str">
-        <x:v>医学信息沟通实习生</x:v>
-      </x:c>
-      <x:c r="I99" s="17" t="str">
-        <x:v>https://careers.viatris.com/</x:v>
+        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
+      </x:c>
+      <x:c r="I99" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J99" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5715,7 +5715,7 @@
       <x:c r="N99" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O99" s="17" t="str">
+      <x:c r="O99" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P99" s="18" t="str">
@@ -5730,28 +5730,28 @@
         <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="B100" s="4" t="str">
-        <x:v>苏州鸿凌达电子</x:v>
+        <x:v>晖致医药</x:v>
       </x:c>
       <x:c r="C100" s="4" t="str">
-        <x:v>电子制造</x:v>
+        <x:v>医药</x:v>
       </x:c>
       <x:c r="D100" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>外资</x:v>
       </x:c>
       <x:c r="E100" s="4" t="str">
-        <x:v>苏州</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F100" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>实习储备正式岗</x:v>
       </x:c>
       <x:c r="G100" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H100" s="4" t="str">
-        <x:v>财务助理</x:v>
-      </x:c>
-      <x:c r="I100" s="17" t="str">
-        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
+        <x:v>医学信息沟通实习生</x:v>
+      </x:c>
+      <x:c r="I100" s="15" t="str">
+        <x:v>https://careers.viatris.com/</x:v>
       </x:c>
       <x:c r="J100" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5768,7 +5768,7 @@
       <x:c r="N100" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O100" s="17" t="str">
+      <x:c r="O100" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P100" s="18" t="str">
@@ -5780,19 +5780,19 @@
     </x:row>
     <x:row r="101" ht="54" customHeight="1">
       <x:c r="A101" s="4" t="str">
-        <x:v>2026-06-02</x:v>
+        <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="B101" s="4" t="str">
-        <x:v>万得信息</x:v>
+        <x:v>苏州鸿凌达电子</x:v>
       </x:c>
       <x:c r="C101" s="4" t="str">
-        <x:v>金融数据/软件</x:v>
+        <x:v>电子制造</x:v>
       </x:c>
       <x:c r="D101" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E101" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>苏州</x:v>
       </x:c>
       <x:c r="F101" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5801,10 +5801,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H101" s="4" t="str">
-        <x:v>AI算法工程师等</x:v>
-      </x:c>
-      <x:c r="I101" s="17" t="str">
-        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
+        <x:v>财务助理</x:v>
+      </x:c>
+      <x:c r="I101" s="15" t="str">
+        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
       </x:c>
       <x:c r="J101" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5821,7 +5821,7 @@
       <x:c r="N101" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O101" s="17" t="str">
+      <x:c r="O101" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P101" s="18" t="str">
@@ -5833,31 +5833,31 @@
     </x:row>
     <x:row r="102" ht="54" customHeight="1">
       <x:c r="A102" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-02</x:v>
       </x:c>
       <x:c r="B102" s="4" t="str">
-        <x:v>淘大集供应链</x:v>
+        <x:v>万得信息</x:v>
       </x:c>
       <x:c r="C102" s="4" t="str">
-        <x:v>零售/供应链</x:v>
+        <x:v>金融数据/软件</x:v>
       </x:c>
       <x:c r="D102" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E102" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F102" s="4" t="str">
-        <x:v>管培/实习</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G102" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H102" s="4" t="str">
-        <x:v>巡店管培生、实习生</x:v>
-      </x:c>
-      <x:c r="I102" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>AI算法工程师等</x:v>
+      </x:c>
+      <x:c r="I102" s="15" t="str">
+        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
       </x:c>
       <x:c r="J102" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5874,7 +5874,7 @@
       <x:c r="N102" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O102" s="17" t="str">
+      <x:c r="O102" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P102" s="18" t="str">
@@ -5889,10 +5889,10 @@
         <x:v>2026-06-01</x:v>
       </x:c>
       <x:c r="B103" s="4" t="str">
-        <x:v>友芝友实业集团</x:v>
+        <x:v>淘大集供应链</x:v>
       </x:c>
       <x:c r="C103" s="4" t="str">
-        <x:v>综合实业</x:v>
+        <x:v>零售/供应链</x:v>
       </x:c>
       <x:c r="D103" s="4" t="str">
         <x:v>民营</x:v>
@@ -5901,16 +5901,16 @@
         <x:v>武汉</x:v>
       </x:c>
       <x:c r="F103" s="4" t="str">
-        <x:v>管培生</x:v>
+        <x:v>管培/实习</x:v>
       </x:c>
       <x:c r="G103" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H103" s="4" t="str">
-        <x:v>青年领军人才管培生</x:v>
-      </x:c>
-      <x:c r="I103" s="17" t="str">
-        <x:v>https://www.yzyqh.com/jrwm</x:v>
+        <x:v>巡店管培生、实习生</x:v>
+      </x:c>
+      <x:c r="I103" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J103" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5927,7 +5927,7 @@
       <x:c r="N103" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O103" s="17" t="str">
+      <x:c r="O103" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P103" s="18" t="str">
@@ -5939,31 +5939,31 @@
     </x:row>
     <x:row r="104" ht="54" customHeight="1">
       <x:c r="A104" s="4" t="str">
-        <x:v>2026-05-29</x:v>
+        <x:v>2026-06-01</x:v>
       </x:c>
       <x:c r="B104" s="4" t="str">
-        <x:v>银雁科技</x:v>
+        <x:v>友芝友实业集团</x:v>
       </x:c>
       <x:c r="C104" s="4" t="str">
-        <x:v>金融科技服务</x:v>
+        <x:v>综合实业</x:v>
       </x:c>
       <x:c r="D104" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E104" s="4" t="str">
-        <x:v>成都</x:v>
+        <x:v>武汉</x:v>
       </x:c>
       <x:c r="F104" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>管培生</x:v>
       </x:c>
       <x:c r="G104" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H104" s="4" t="str">
-        <x:v>人伤理赔</x:v>
-      </x:c>
-      <x:c r="I104" s="17" t="str">
-        <x:v>https://www.cfss.net.cn/</x:v>
+        <x:v>青年领军人才管培生</x:v>
+      </x:c>
+      <x:c r="I104" s="15" t="str">
+        <x:v>https://www.yzyqh.com/jrwm</x:v>
       </x:c>
       <x:c r="J104" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5980,7 +5980,7 @@
       <x:c r="N104" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O104" s="17" t="str">
+      <x:c r="O104" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P104" s="18" t="str">
@@ -5992,19 +5992,19 @@
     </x:row>
     <x:row r="105" ht="54" customHeight="1">
       <x:c r="A105" s="4" t="str">
-        <x:v>2026-05-15</x:v>
+        <x:v>2026-05-29</x:v>
       </x:c>
       <x:c r="B105" s="4" t="str">
-        <x:v>知乎</x:v>
+        <x:v>银雁科技</x:v>
       </x:c>
       <x:c r="C105" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>金融科技服务</x:v>
       </x:c>
       <x:c r="D105" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E105" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>成都</x:v>
       </x:c>
       <x:c r="F105" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6013,10 +6013,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H105" s="4" t="str">
-        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
-      </x:c>
-      <x:c r="I105" s="17" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
+        <x:v>人伤理赔</x:v>
+      </x:c>
+      <x:c r="I105" s="15" t="str">
+        <x:v>https://www.cfss.net.cn/</x:v>
       </x:c>
       <x:c r="J105" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6033,7 +6033,7 @@
       <x:c r="N105" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O105" s="17" t="str">
+      <x:c r="O105" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P105" s="18" t="str">
@@ -6045,31 +6045,31 @@
     </x:row>
     <x:row r="106" ht="54" customHeight="1">
       <x:c r="A106" s="4" t="str">
-        <x:v>2026-05-08</x:v>
+        <x:v>2026-05-15</x:v>
       </x:c>
       <x:c r="B106" s="4" t="str">
-        <x:v>招商银行长沙分行</x:v>
+        <x:v>知乎</x:v>
       </x:c>
       <x:c r="C106" s="4" t="str">
-        <x:v>银行/金融</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="D106" s="4" t="str">
-        <x:v>股份制银行</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E106" s="4" t="str">
-        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F106" s="4" t="str">
-        <x:v>暑期实习/秋招直通</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G106" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H106" s="4" t="str">
-        <x:v>2027暑期实习生</x:v>
-      </x:c>
-      <x:c r="I106" s="17" t="str">
-        <x:v>https://career.cmbchina.com/</x:v>
+        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
+      </x:c>
+      <x:c r="I106" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
       </x:c>
       <x:c r="J106" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6086,7 +6086,7 @@
       <x:c r="N106" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O106" s="17" t="str">
+      <x:c r="O106" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P106" s="18" t="str">
@@ -6098,31 +6098,31 @@
     </x:row>
     <x:row r="107" ht="54" customHeight="1">
       <x:c r="A107" s="4" t="str">
-        <x:v>2026-04-22</x:v>
+        <x:v>2026-05-08</x:v>
       </x:c>
       <x:c r="B107" s="4" t="str">
-        <x:v>华金证券</x:v>
+        <x:v>招商银行长沙分行</x:v>
       </x:c>
       <x:c r="C107" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>银行/金融</x:v>
       </x:c>
       <x:c r="D107" s="4" t="str">
-        <x:v>国企</x:v>
+        <x:v>股份制银行</x:v>
       </x:c>
       <x:c r="E107" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
       </x:c>
       <x:c r="F107" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>暑期实习/秋招直通</x:v>
       </x:c>
       <x:c r="G107" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H107" s="4" t="str">
-        <x:v>战略发展类</x:v>
-      </x:c>
-      <x:c r="I107" s="17" t="str">
-        <x:v>https://www.huajinsc.cn/</x:v>
+        <x:v>2027暑期实习生</x:v>
+      </x:c>
+      <x:c r="I107" s="15" t="str">
+        <x:v>https://career.cmbchina.com/</x:v>
       </x:c>
       <x:c r="J107" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6139,13 +6139,66 @@
       <x:c r="N107" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O107" s="17" t="str">
+      <x:c r="O107" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P107" s="18" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q107" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" ht="54" customHeight="1">
+      <x:c r="A108" s="4" t="str">
+        <x:v>2026-04-22</x:v>
+      </x:c>
+      <x:c r="B108" s="4" t="str">
+        <x:v>华金证券</x:v>
+      </x:c>
+      <x:c r="C108" s="4" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="D108" s="4" t="str">
+        <x:v>国企</x:v>
+      </x:c>
+      <x:c r="E108" s="4" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F108" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G108" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H108" s="4" t="str">
+        <x:v>战略发展类</x:v>
+      </x:c>
+      <x:c r="I108" s="15" t="str">
+        <x:v>https://www.huajinsc.cn/</x:v>
+      </x:c>
+      <x:c r="J108" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K108" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L108" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M108" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N108" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O108" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P108" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q108" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -6156,7 +6209,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa96992addae4765"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35b243dc075e4fec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6186,7 +6239,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>近期有明确截止时间的项目（截至2026-08-03）</x:v>
+        <x:v>近期有明确截止时间的项目（截至2026-08-04）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -6304,7 +6357,7 @@
       <x:c r="H4" s="4" t="str">
         <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
       </x:c>
-      <x:c r="I4" s="17" t="str">
+      <x:c r="I4" s="15" t="str">
         <x:v>https://campus.lilith.com/</x:v>
       </x:c>
       <x:c r="J4" s="4" t="str">
@@ -6320,7 +6373,7 @@
         <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N4" s="4" t="str"/>
-      <x:c r="O4" s="17" t="str">
+      <x:c r="O4" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P4" s="19" t="str">
@@ -6355,7 +6408,7 @@
       <x:c r="H5" s="4" t="str">
         <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
       </x:c>
-      <x:c r="I5" s="17" t="str">
+      <x:c r="I5" s="15" t="str">
         <x:v>https://campus.nio.com/</x:v>
       </x:c>
       <x:c r="J5" s="4" t="str">
@@ -6373,10 +6426,10 @@
       <x:c r="N5" s="4" t="str">
         <x:v>最多同时申请3个岗位。</x:v>
       </x:c>
-      <x:c r="O5" s="17" t="str">
+      <x:c r="O5" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P5" s="15" t="str">
+      <x:c r="P5" s="14" t="str">
         <x:v>A-官方来源公告已核验</x:v>
       </x:c>
       <x:c r="Q5" s="4" t="str">
@@ -6408,7 +6461,7 @@
       <x:c r="H6" s="4" t="str">
         <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
       </x:c>
-      <x:c r="I6" s="17" t="str">
+      <x:c r="I6" s="15" t="str">
         <x:v>https://campus.boe.com/</x:v>
       </x:c>
       <x:c r="J6" s="4" t="str">
@@ -6426,10 +6479,10 @@
       <x:c r="N6" s="4" t="str">
         <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
       </x:c>
-      <x:c r="O6" s="17" t="str">
+      <x:c r="O6" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P6" s="15" t="str">
+      <x:c r="P6" s="14" t="str">
         <x:v>A-国家大学生就业平台公告已核验</x:v>
       </x:c>
       <x:c r="Q6" s="4" t="str">
@@ -6461,7 +6514,7 @@
       <x:c r="H7" s="4" t="str">
         <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
       </x:c>
-      <x:c r="I7" s="17" t="str">
+      <x:c r="I7" s="15" t="str">
         <x:v>https://job.cn-amd.com/</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
@@ -6479,7 +6532,7 @@
       <x:c r="N7" s="4" t="str">
         <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
       </x:c>
-      <x:c r="O7" s="17" t="str">
+      <x:c r="O7" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P7" s="19" t="str">
@@ -6514,7 +6567,7 @@
       <x:c r="H8" s="4" t="str">
         <x:v>咨询顾问及相关专业岗位</x:v>
       </x:c>
-      <x:c r="I8" s="17" t="str">
+      <x:c r="I8" s="15" t="str">
         <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
       </x:c>
       <x:c r="J8" s="4" t="str">
@@ -6530,7 +6583,7 @@
         <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N8" s="4" t="str"/>
-      <x:c r="O8" s="17" t="str">
+      <x:c r="O8" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P8" s="19" t="str">
@@ -6565,7 +6618,7 @@
       <x:c r="H9" s="4" t="str">
         <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
       </x:c>
-      <x:c r="I9" s="17" t="str">
+      <x:c r="I9" s="15" t="str">
         <x:v>https://hr.arcsoft.com.cn/</x:v>
       </x:c>
       <x:c r="J9" s="4" t="str">
@@ -6581,7 +6634,7 @@
         <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N9" s="4" t="str"/>
-      <x:c r="O9" s="17" t="str">
+      <x:c r="O9" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P9" s="19" t="str">
@@ -6616,7 +6669,7 @@
       <x:c r="H10" s="4" t="str">
         <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
       </x:c>
-      <x:c r="I10" s="17" t="str">
+      <x:c r="I10" s="15" t="str">
         <x:v>https://www.eoptolink.com/</x:v>
       </x:c>
       <x:c r="J10" s="4" t="str">
@@ -6634,7 +6687,7 @@
       <x:c r="N10" s="4" t="str">
         <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
       </x:c>
-      <x:c r="O10" s="17" t="str">
+      <x:c r="O10" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P10" s="18" t="str">
@@ -6669,7 +6722,7 @@
       <x:c r="H11" s="4" t="str">
         <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
       </x:c>
-      <x:c r="I11" s="17" t="str">
+      <x:c r="I11" s="15" t="str">
         <x:v>https://www.hesaitech.com/cn/careers/</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
@@ -6687,7 +6740,7 @@
       <x:c r="N11" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O11" s="17" t="str">
+      <x:c r="O11" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P11" s="18" t="str">
@@ -6722,7 +6775,7 @@
       <x:c r="H12" s="4" t="str">
         <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
       </x:c>
-      <x:c r="I12" s="17" t="str">
+      <x:c r="I12" s="15" t="str">
         <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
       </x:c>
       <x:c r="J12" s="4" t="str">
@@ -6740,10 +6793,10 @@
       <x:c r="N12" s="4" t="str">
         <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
       </x:c>
-      <x:c r="O12" s="17" t="str">
+      <x:c r="O12" s="15" t="str">
         <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
       </x:c>
-      <x:c r="P12" s="15" t="str">
+      <x:c r="P12" s="14" t="str">
         <x:v>A-高校就业网含官方投递链接</x:v>
       </x:c>
       <x:c r="Q12" s="4" t="str">
@@ -6775,7 +6828,7 @@
       <x:c r="H13" s="4" t="str">
         <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
       </x:c>
-      <x:c r="I13" s="17" t="str">
+      <x:c r="I13" s="15" t="str">
         <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="J13" s="4" t="str">
@@ -6793,10 +6846,10 @@
       <x:c r="N13" s="4" t="str">
         <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
       </x:c>
-      <x:c r="O13" s="17" t="str">
+      <x:c r="O13" s="15" t="str">
         <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
-      <x:c r="P13" s="15" t="str">
+      <x:c r="P13" s="14" t="str">
         <x:v>A-中国移动官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="Q13" s="4" t="str">
@@ -6828,7 +6881,7 @@
       <x:c r="H14" s="4" t="str">
         <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
       </x:c>
-      <x:c r="I14" s="17" t="str">
+      <x:c r="I14" s="15" t="str">
         <x:v>https://leihuo.163.com/campus/#/full</x:v>
       </x:c>
       <x:c r="J14" s="4" t="str">
@@ -6846,10 +6899,10 @@
       <x:c r="N14" s="4" t="str">
         <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
       </x:c>
-      <x:c r="O14" s="17" t="str">
+      <x:c r="O14" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P14" s="15" t="str">
+      <x:c r="P14" s="14" t="str">
         <x:v>A-官方招聘官网已核验</x:v>
       </x:c>
       <x:c r="Q14" s="4" t="str">
@@ -6881,7 +6934,7 @@
       <x:c r="H15" s="4" t="str">
         <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
-      <x:c r="I15" s="17" t="str">
+      <x:c r="I15" s="15" t="str">
         <x:v>https://zyjob.hotjob.cn/</x:v>
       </x:c>
       <x:c r="J15" s="4" t="str">
@@ -6899,10 +6952,10 @@
       <x:c r="N15" s="4" t="str">
         <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
       </x:c>
-      <x:c r="O15" s="17" t="str">
+      <x:c r="O15" s="15" t="str">
         <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
       </x:c>
-      <x:c r="P15" s="15" t="str">
+      <x:c r="P15" s="14" t="str">
         <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
       </x:c>
       <x:c r="Q15" s="4" t="str">
@@ -6911,7 +6964,7 @@
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>2026-08-01</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
         <x:v>影石Insta360</x:v>
@@ -6934,32 +6987,32 @@
       <x:c r="H16" s="4" t="str">
         <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
       </x:c>
-      <x:c r="I16" s="17" t="str">
+      <x:c r="I16" s="15" t="str">
         <x:v>https://www.insta360.com/cn/jobs</x:v>
       </x:c>
       <x:c r="J16" s="4" t="str">
         <x:v>2026-10-31</x:v>
       </x:c>
       <x:c r="K16" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
       </x:c>
       <x:c r="L16" s="4" t="str">
-        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
+        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
       </x:c>
       <x:c r="M16" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N16" s="4" t="str">
-        <x:v>岗位城市和具体职位以影石Insta360官方招聘页为准；公开信息标注10月31日，投递前再次确认职位状态。</x:v>
-      </x:c>
-      <x:c r="O16" s="17" t="str">
+        <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
+      </x:c>
+      <x:c r="O16" s="15" t="str">
         <x:v>https://www.insta360.com/cn/jobs</x:v>
       </x:c>
-      <x:c r="P16" s="15" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
+      <x:c r="P16" s="14" t="str">
+        <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
       </x:c>
       <x:c r="Q16" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
@@ -6987,7 +7040,7 @@
       <x:c r="H17" s="4" t="str">
         <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
       </x:c>
-      <x:c r="I17" s="17" t="str">
+      <x:c r="I17" s="15" t="str">
         <x:v>https://campus.jd.com/</x:v>
       </x:c>
       <x:c r="J17" s="4" t="str">
@@ -7005,10 +7058,10 @@
       <x:c r="N17" s="4" t="str">
         <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
       </x:c>
-      <x:c r="O17" s="17" t="str">
+      <x:c r="O17" s="15" t="str">
         <x:v>https://campus.jd.com/#/</x:v>
       </x:c>
-      <x:c r="P17" s="15" t="str">
+      <x:c r="P17" s="14" t="str">
         <x:v>A-企业官网校招页面已核验</x:v>
       </x:c>
       <x:c r="Q17" s="4" t="str">
@@ -7040,7 +7093,7 @@
       <x:c r="H18" s="4" t="str">
         <x:v>研产、全球营销、设计、职能、制造供应</x:v>
       </x:c>
-      <x:c r="I18" s="17" t="str">
+      <x:c r="I18" s="15" t="str">
         <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
       </x:c>
       <x:c r="J18" s="4" t="str">
@@ -7058,7 +7111,7 @@
       <x:c r="N18" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O18" s="17" t="str">
+      <x:c r="O18" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P18" s="18" t="str">
@@ -7093,7 +7146,7 @@
       <x:c r="H19" s="4" t="str">
         <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
       </x:c>
-      <x:c r="I19" s="17" t="str">
+      <x:c r="I19" s="15" t="str">
         <x:v>https://www.lopal.com.cn/join</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
@@ -7111,7 +7164,7 @@
       <x:c r="N19" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
-      <x:c r="O19" s="17" t="str">
+      <x:c r="O19" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P19" s="18" t="str">
@@ -7146,7 +7199,7 @@
       <x:c r="H20" s="4" t="str">
         <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
       </x:c>
-      <x:c r="I20" s="17" t="str">
+      <x:c r="I20" s="15" t="str">
         <x:v>https://talent.baidu.com/jobs</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
@@ -7164,10 +7217,10 @@
       <x:c r="N20" s="4" t="str">
         <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
       </x:c>
-      <x:c r="O20" s="17" t="str">
+      <x:c r="O20" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P20" s="15" t="str">
+      <x:c r="P20" s="14" t="str">
         <x:v>A-官方招聘日历/官方来源已核验</x:v>
       </x:c>
       <x:c r="Q20" s="4" t="str">
@@ -7181,7 +7234,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf05e1a7641e6467b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R949de6a5a1fa4261"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7199,7 +7252,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="27" t="str">
-        <x:v>使用说明与统计（截至2026-08-03）</x:v>
+        <x:v>使用说明与统计（截至2026-08-04）</x:v>
       </x:c>
       <x:c r="B1" s="27"/>
       <x:c r="C1" s="27"/>
@@ -7254,10 +7307,10 @@
       </x:c>
       <x:c r="C5" s="25"/>
       <x:c r="D5" s="31" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="E5" s="32" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F5"/>
     </x:row>
@@ -7270,7 +7323,7 @@
       </x:c>
       <x:c r="C6" s="25"/>
       <x:c r="D6" s="31" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="E6" s="32" t="n">
         <x:v>4</x:v>
@@ -7282,7 +7335,7 @@
       <x:c r="B7" s="25"/>
       <x:c r="C7" s="25"/>
       <x:c r="D7" s="31" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="E7" s="32" t="n">
         <x:v>4</x:v>
@@ -7402,7 +7455,7 @@
         <x:v>项目总数</x:v>
       </x:c>
       <x:c r="B16" s="28" t="n">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C16" s="25"/>
       <x:c r="D16" s="31" t="str">
@@ -7450,7 +7503,7 @@
         <x:v>B等级</x:v>
       </x:c>
       <x:c r="B19" s="28" t="n">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C19" s="25"/>
       <x:c r="D19" s="31"/>
@@ -7482,7 +7535,7 @@
         <x:v>本次更新</x:v>
       </x:c>
       <x:c r="B22" s="25" t="str">
-        <x:v>新增2项；关闭4项；未来7天内明确截止1项；新增项目均已打开企业官方招聘系统核验，未核验到开放职位的候选未纳入。</x:v>
+        <x:v>新增1项；关闭0项；未来7天内明确截止1项；新增项目来自可信高校就业网公告并核验官方投递入口，免笔试政策以公告为准。</x:v>
       </x:c>
       <x:c r="C22" s="25"/>
       <x:c r="D22" s="25"/>

--- a/2027届秋招投递信息_2026-07-24.xlsx
+++ b/2027届秋招投递信息_2026-07-24.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R749d57a1ba014186"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="R7f0c4d5993cd48f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="Rc853f8092b164847"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="Rd3b867ef39d04225"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="R8f9b3003bfa1476d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="R011f61f9abfc4d52"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -705,7 +705,7 @@
         <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
       </x:c>
       <x:c r="O4" s="15" t="str">
-        <x:v>https://www.insta360.com/cn/jobs</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
       </x:c>
       <x:c r="P4" s="14" t="str">
         <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
@@ -6209,7 +6209,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35b243dc075e4fec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54cd0616e22f43a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7006,7 +7006,7 @@
         <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
       </x:c>
       <x:c r="O16" s="15" t="str">
-        <x:v>https://www.insta360.com/cn/jobs</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
       </x:c>
       <x:c r="P16" s="14" t="str">
         <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
@@ -7234,7 +7234,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R949de6a5a1fa4261"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26a1d8c8a7414a7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>

--- a/2027届秋招投递信息_2026-07-24.xlsx
+++ b/2027届秋招投递信息_2026-07-24.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="Rd3b867ef39d04225"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="R8f9b3003bfa1476d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="R011f61f9abfc4d52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R7058580a4e864a38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="Rf992459e2bd04eb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="R81ddd37a8cee4980"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -301,8 +301,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q108" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:Q108"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q109" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:Q109"/>
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="开放投递时间"/>
     <x:tableColumn id="2" name="企业名称"/>
@@ -327,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DeadlineProjectsTable" displayName="DeadlineProjectsTable" ref="A3:Q20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:Q20"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DeadlineProjectsTable" displayName="DeadlineProjectsTable" ref="A3:Q21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:Q21"/>
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="开放投递时间"/>
     <x:tableColumn id="2" name="企业名称"/>
@@ -568,7 +568,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>2027届秋招投递信息（截至2026-08-04）</x:v>
+        <x:v>2027届秋招投递信息（截至2026-08-05）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -663,161 +663,161 @@
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="4" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="B4" s="4" t="str">
-        <x:v>影石Insta360</x:v>
+        <x:v>联想集团</x:v>
       </x:c>
       <x:c r="C4" s="4" t="str">
-        <x:v>消费电子/智能影像</x:v>
+        <x:v>计算机/消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
-        <x:v>深圳、上海、珠海</x:v>
+        <x:v>北京、上海、天津、成都、南京、武汉、深圳、厦门等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F4" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批/应届生招聘</x:v>
       </x:c>
       <x:c r="G4" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届海内外毕业生（中国大陆毕业时间为2026年9月1日至2027年8月31日）</x:v>
       </x:c>
       <x:c r="H4" s="4" t="str">
-        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+        <x:v>AI开发、软件开发、嵌入式、硬件、产品与项目、设计、市场与销售、供应链及职能岗位</x:v>
       </x:c>
       <x:c r="I4" s="15" t="str">
-        <x:v>https://www.insta360.com/cn/jobs</x:v>
+        <x:v>https://talent.lenovo.com.cn/campus</x:v>
       </x:c>
       <x:c r="J4" s="4" t="str">
-        <x:v>2026-10-31</x:v>
+        <x:v>2026-11-13</x:v>
       </x:c>
       <x:c r="K4" s="4" t="str">
-        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
+        <x:v>否（官方校招日历含在线测评&amp;技术笔试，简历筛选通过发放笔试通知）</x:v>
       </x:c>
       <x:c r="L4" s="4" t="str">
-        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
+        <x:v>本轮新增；联想官方应届生招聘页显示热招中</x:v>
       </x:c>
       <x:c r="M4" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N4" s="4" t="str">
+        <x:v>联想官方应届生招聘页当前显示“联想2027应届生招聘”，面向2027届海内外毕业生；网申自2026年8月5日开启，官网公布网申截止2026年11月13日。简历完整度需达到100%才能投递，每个校招项目只能投一个岗位（管培生项目和其他项目可各投一个），部分岗位可能因投递人数较多下线；投递时可选择接受岗位调剂，测评通知以邮件、短信和系统提醒为准。</x:v>
+      </x:c>
+      <x:c r="O4" s="15" t="str">
+        <x:v>https://talent.lenovo.com.cn/campus</x:v>
+      </x:c>
+      <x:c r="P4" s="14" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q4" s="4" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="4" t="str">
+        <x:v>2026-08-01</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="str">
+        <x:v>影石Insta360</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="str">
+        <x:v>消费电子/智能影像</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="str">
+        <x:v>深圳、上海、珠海</x:v>
+      </x:c>
+      <x:c r="F5" s="4" t="str">
+        <x:v>正式批/秋招</x:v>
+      </x:c>
+      <x:c r="G5" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H5" s="4" t="str">
+        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+      </x:c>
+      <x:c r="I5" s="15" t="str">
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
+      </x:c>
+      <x:c r="J5" s="4" t="str">
+        <x:v>2026-10-31</x:v>
+      </x:c>
+      <x:c r="K5" s="4" t="str">
+        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
+      </x:c>
+      <x:c r="L5" s="4" t="str">
+        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
+      </x:c>
+      <x:c r="M5" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N5" s="4" t="str">
         <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
       </x:c>
-      <x:c r="O4" s="15" t="str">
+      <x:c r="O5" s="15" t="str">
         <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
       </x:c>
-      <x:c r="P4" s="14" t="str">
+      <x:c r="P5" s="14" t="str">
         <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
       </x:c>
-      <x:c r="Q4" s="4" t="str">
+      <x:c r="Q5" s="4" t="str">
         <x:v>2026-08-04</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="54" customHeight="1">
-      <x:c r="A5" s="16" t="str">
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="16" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
+      <x:c r="B6" s="16" t="str">
         <x:v>恒丰银行总行-雏鹰计划</x:v>
       </x:c>
-      <x:c r="C5" s="16" t="str">
+      <x:c r="C6" s="16" t="str">
         <x:v>银行/金融</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="str">
+      <x:c r="D6" s="16" t="str">
         <x:v>股份制商业银行</x:v>
       </x:c>
-      <x:c r="E5" s="16" t="str">
+      <x:c r="E6" s="16" t="str">
         <x:v>总行及相关机构，以岗位页为准</x:v>
       </x:c>
-      <x:c r="F5" s="16" t="str">
+      <x:c r="F6" s="16" t="str">
         <x:v>暑期实习/秋招储备</x:v>
       </x:c>
-      <x:c r="G5" s="16" t="str">
+      <x:c r="G6" s="16" t="str">
         <x:v>2027届硕士及以上，以公告要求为准</x:v>
       </x:c>
-      <x:c r="H5" s="16" t="str">
+      <x:c r="H6" s="16" t="str">
         <x:v>总行实习生，具体专业和方向以官方公告为准</x:v>
       </x:c>
-      <x:c r="I5" s="17" t="str">
+      <x:c r="I6" s="17" t="str">
         <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
       </x:c>
-      <x:c r="J5" s="16" t="str">
+      <x:c r="J6" s="16" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
-      <x:c r="K5" s="16" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L5" s="16" t="str">
+      <x:c r="K6" s="16" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L6" s="16" t="str">
         <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
       </x:c>
-      <x:c r="M5" s="16" t="str">
+      <x:c r="M6" s="16" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N5" s="16" t="str">
+      <x:c r="N6" s="16" t="str">
         <x:v>官方公告显示7月31日24:00截止，实习期安排和具体岗位以恒丰银行招聘官网为准。</x:v>
       </x:c>
-      <x:c r="O5" s="17" t="str">
+      <x:c r="O6" s="17" t="str">
         <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
       </x:c>
-      <x:c r="P5" s="14" t="str">
+      <x:c r="P6" s="14" t="str">
         <x:v>A-企业官方招聘公告已核验</x:v>
       </x:c>
-      <x:c r="Q5" s="16" t="str">
+      <x:c r="Q6" s="16" t="str">
         <x:v>2026-08-03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="54" customHeight="1">
-      <x:c r="A6" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="str">
-        <x:v>四方股份</x:v>
-      </x:c>
-      <x:c r="C6" s="4" t="str">
-        <x:v>电力系统/工业自动化</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E6" s="4" t="str">
-        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
-      </x:c>
-      <x:c r="F6" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G6" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H6" s="4" t="str">
-        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
-      </x:c>
-      <x:c r="I6" s="15" t="str">
-        <x:v>https://www.sf-auto.com/campus</x:v>
-      </x:c>
-      <x:c r="J6" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K6" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L6" s="4" t="str">
-        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="M6" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N6" s="4" t="str">
-        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
-      </x:c>
-      <x:c r="O6" s="15" t="str">
-        <x:v>https://www.sf-auto.com/campus</x:v>
-      </x:c>
-      <x:c r="P6" s="14" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="Q6" s="4" t="str">
-        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
@@ -825,28 +825,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>苏纳光电</x:v>
+        <x:v>四方股份</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>电力系统/工业自动化</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>苏州、上海</x:v>
+        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
-        <x:v>提前批/Open Day</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
-        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
+        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
       </x:c>
       <x:c r="I7" s="15" t="str">
-        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+        <x:v>https://www.sf-auto.com/campus</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -855,19 +855,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L7" s="4" t="str">
-        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
+        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="M7" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N7" s="4" t="str">
-        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
+        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
       </x:c>
       <x:c r="O7" s="15" t="str">
-        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+        <x:v>https://www.sf-auto.com/campus</x:v>
       </x:c>
       <x:c r="P7" s="14" t="str">
-        <x:v>A-企业官方校园招聘系统已核验</x:v>
+        <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="Q7" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -878,28 +878,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>特斯拉中国</x:v>
+        <x:v>苏纳光电</x:v>
       </x:c>
       <x:c r="C8" s="4" t="str">
-        <x:v>新能源汽车/智能制造</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
-        <x:v>外资/上市</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
+        <x:v>苏州、上海</x:v>
       </x:c>
       <x:c r="F8" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批/Open Day</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
-        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
+        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
-        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
+        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
       </x:c>
       <x:c r="I8" s="15" t="str">
-        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="J8" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -908,128 +908,128 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L8" s="4" t="str">
-        <x:v>本轮新确认；企业官方职位页已核验</x:v>
+        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
       </x:c>
       <x:c r="M8" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N8" s="4" t="str">
-        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
+        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
       </x:c>
       <x:c r="O8" s="15" t="str">
-        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="P8" s="14" t="str">
-        <x:v>A-企业官方职位页已核验</x:v>
+        <x:v>A-企业官方校园招聘系统已核验</x:v>
       </x:c>
       <x:c r="Q8" s="4" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
-      <x:c r="A9" s="16" t="str">
+      <x:c r="A9" s="4" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="str">
+      <x:c r="B9" s="4" t="str">
+        <x:v>特斯拉中国</x:v>
+      </x:c>
+      <x:c r="C9" s="4" t="str">
+        <x:v>新能源汽车/智能制造</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="str">
+        <x:v>外资/上市</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="str">
+        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="str">
+        <x:v>正式批/校园招聘</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="str">
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="str">
+        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
+      </x:c>
+      <x:c r="I9" s="15" t="str">
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
+      </x:c>
+      <x:c r="J9" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="str">
+        <x:v>本轮新确认；企业官方职位页已核验</x:v>
+      </x:c>
+      <x:c r="M9" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N9" s="4" t="str">
+        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
+      </x:c>
+      <x:c r="O9" s="15" t="str">
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
+      </x:c>
+      <x:c r="P9" s="14" t="str">
+        <x:v>A-企业官方职位页已核验</x:v>
+      </x:c>
+      <x:c r="Q9" s="4" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="16" t="str">
+        <x:v>不晚于2026-07-30</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="str">
         <x:v>天健会计师事务所-暑期实习培训生</x:v>
       </x:c>
-      <x:c r="C9" s="16" t="str">
+      <x:c r="C10" s="16" t="str">
         <x:v>会计审计/专业服务</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="str">
+      <x:c r="D10" s="16" t="str">
         <x:v>会计师事务所</x:v>
       </x:c>
-      <x:c r="E9" s="16" t="str">
+      <x:c r="E10" s="16" t="str">
         <x:v>上海等，以职位页为准</x:v>
       </x:c>
-      <x:c r="F9" s="16" t="str">
+      <x:c r="F10" s="16" t="str">
         <x:v>暑期实习/培训生</x:v>
       </x:c>
-      <x:c r="G9" s="16" t="str">
+      <x:c r="G10" s="16" t="str">
         <x:v>2027届应届毕业生，以岗位要求为准</x:v>
       </x:c>
-      <x:c r="H9" s="16" t="str">
+      <x:c r="H10" s="16" t="str">
         <x:v>财务审计暑期实习培训生</x:v>
       </x:c>
-      <x:c r="I9" s="17" t="str">
+      <x:c r="I10" s="17" t="str">
         <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
       </x:c>
-      <x:c r="J9" s="16" t="str">
+      <x:c r="J10" s="16" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
-      <x:c r="K9" s="16" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L9" s="16" t="str">
+      <x:c r="K10" s="16" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L10" s="16" t="str">
         <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
       </x:c>
-      <x:c r="M9" s="16" t="str">
+      <x:c r="M10" s="16" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N9" s="16" t="str">
+      <x:c r="N10" s="16" t="str">
         <x:v>公开公告显示7月31日截止；具体办公地点、专业要求和实习安排以天健招聘官网为准。</x:v>
       </x:c>
-      <x:c r="O9" s="17" t="str">
+      <x:c r="O10" s="17" t="str">
         <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
       </x:c>
-      <x:c r="P9" s="14" t="str">
+      <x:c r="P10" s="14" t="str">
         <x:v>A-企业官方招聘入口已核验</x:v>
       </x:c>
-      <x:c r="Q9" s="16" t="str">
+      <x:c r="Q10" s="16" t="str">
         <x:v>2026-08-03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="54" customHeight="1">
-      <x:c r="A10" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B10" s="4" t="str">
-        <x:v>西安紫光国芯半导体</x:v>
-      </x:c>
-      <x:c r="C10" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
-      </x:c>
-      <x:c r="D10" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
-      </x:c>
-      <x:c r="E10" s="4" t="str">
-        <x:v>西安、上海、成都</x:v>
-      </x:c>
-      <x:c r="F10" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
-      </x:c>
-      <x:c r="G10" s="4" t="str">
-        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H10" s="4" t="str">
-        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
-      </x:c>
-      <x:c r="I10" s="15" t="str">
-        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
-      </x:c>
-      <x:c r="J10" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K10" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L10" s="4" t="str">
-        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
-      </x:c>
-      <x:c r="M10" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N10" s="4" t="str">
-        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
-      </x:c>
-      <x:c r="O10" s="15" t="str">
-        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
-      </x:c>
-      <x:c r="P10" s="14" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
-      </x:c>
-      <x:c r="Q10" s="4" t="str">
-        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
@@ -1037,28 +1037,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B11" s="4" t="str">
-        <x:v>新大陆自动识别</x:v>
+        <x:v>西安紫光国芯半导体</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
-        <x:v>计算机视觉/智能硬件</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>民营/上市公司子公司</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>福州总部及全国/海外岗位</x:v>
+        <x:v>西安、上海、成都</x:v>
       </x:c>
       <x:c r="F11" s="4" t="str">
         <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
+        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
+        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
       </x:c>
       <x:c r="I11" s="15" t="str">
-        <x:v>https://nlscan.zhiye.com/Campus</x:v>
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1067,19 +1067,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L11" s="4" t="str">
-        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
+        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
       </x:c>
       <x:c r="M11" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N11" s="4" t="str">
-        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
+        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
       </x:c>
       <x:c r="O11" s="15" t="str">
-        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
       </x:c>
       <x:c r="P11" s="14" t="str">
-        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q11" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1090,28 +1090,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>兆易创新</x:v>
+        <x:v>新大陆自动识别</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>计算机视觉/智能硬件</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/上市公司子公司</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>北京、上海、武汉、合肥等，以岗位页为准</x:v>
+        <x:v>福州总部及全国/海外岗位</x:v>
       </x:c>
       <x:c r="F12" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>芯片设计、验证、嵌入式、软件、应用、测试及职能岗位</x:v>
+        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
       </x:c>
       <x:c r="I12" s="15" t="str">
-        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
+        <x:v>https://nlscan.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J12" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1120,19 +1120,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L12" s="4" t="str">
-        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
+        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
       </x:c>
       <x:c r="M12" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N12" s="4" t="str">
-        <x:v>提前批岗位和城市以兆易创新官方加入我们页面为准，投递前确认职位仍开放。</x:v>
+        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
       </x:c>
       <x:c r="O12" s="15" t="str">
-        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
+        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
       </x:c>
       <x:c r="P12" s="14" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
+        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
       </x:c>
       <x:c r="Q12" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1143,28 +1143,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B13" s="4" t="str">
-        <x:v>中国航空发动机集团</x:v>
+        <x:v>兆易创新</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
-        <x:v>航空发动机/军工</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>全国各院所及下属单位</x:v>
+        <x:v>北京、上海、武汉、合肥等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F13" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
         <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>研发设计、工艺、试验、制造、材料、控制、软件及管理岗位</x:v>
+        <x:v>芯片设计、验证、嵌入式、软件、应用、测试及职能岗位</x:v>
       </x:c>
       <x:c r="I13" s="15" t="str">
-        <x:v>https://aecc.iguopin.com/notice2</x:v>
+        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
       </x:c>
       <x:c r="J13" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1173,19 +1173,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L13" s="4" t="str">
-        <x:v>本轮新确认；集团官方招聘平台已核验</x:v>
+        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="M13" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N13" s="4" t="str">
-        <x:v>各单位岗位和截止时间不同，需在中国航发招聘平台按单位和专业筛选。</x:v>
+        <x:v>提前批岗位和城市以兆易创新官方加入我们页面为准，投递前确认职位仍开放。</x:v>
       </x:c>
       <x:c r="O13" s="15" t="str">
-        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/n2588350/c35693219/content.html</x:v>
+        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
       </x:c>
       <x:c r="P13" s="14" t="str">
-        <x:v>A-国资委公告与集团招聘平台交叉核验</x:v>
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q13" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1196,28 +1196,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B14" s="4" t="str">
-        <x:v>中粮资本-粮曦计划</x:v>
+        <x:v>中国航空发动机集团</x:v>
       </x:c>
       <x:c r="C14" s="4" t="str">
-        <x:v>金融/投资/资管</x:v>
+        <x:v>航空发动机/军工</x:v>
       </x:c>
       <x:c r="D14" s="4" t="str">
-        <x:v>央企/金融控股</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>全国各院所及下属单位</x:v>
       </x:c>
       <x:c r="F14" s="4" t="str">
-        <x:v>培养计划/实习</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
-        <x:v>2027-2029届硕士及以上，以公告要求为准</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>金融、投资、风险、运营、人力资源及综合管理方向</x:v>
+        <x:v>研发设计、工艺、试验、制造、材料、控制、软件及管理岗位</x:v>
       </x:c>
       <x:c r="I14" s="15" t="str">
-        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+        <x:v>https://aecc.iguopin.com/notice2</x:v>
       </x:c>
       <x:c r="J14" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1226,19 +1226,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L14" s="4" t="str">
-        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
+        <x:v>本轮新确认；集团官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="M14" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N14" s="4" t="str">
-        <x:v>粮曦计划具体批次、面向人群和岗位以中粮资本官方加入我们页面及公告为准。</x:v>
+        <x:v>各单位岗位和截止时间不同，需在中国航发招聘平台按单位和专业筛选。</x:v>
       </x:c>
       <x:c r="O14" s="15" t="str">
-        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/n2588350/c35693219/content.html</x:v>
       </x:c>
       <x:c r="P14" s="14" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
+        <x:v>A-国资委公告与集团招聘平台交叉核验</x:v>
       </x:c>
       <x:c r="Q14" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1249,49 +1249,49 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B15" s="4" t="str">
-        <x:v>中移九天人工智能科技</x:v>
+        <x:v>中粮资本-粮曦计划</x:v>
       </x:c>
       <x:c r="C15" s="4" t="str">
-        <x:v>AI/软件/云计算</x:v>
+        <x:v>金融/投资/资管</x:v>
       </x:c>
       <x:c r="D15" s="4" t="str">
-        <x:v>央企子公司</x:v>
+        <x:v>央企/金融控股</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>北京、西安、广州、深圳</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F15" s="4" t="str">
-        <x:v>正式批/超级实习生</x:v>
+        <x:v>培养计划/实习</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
+        <x:v>2027-2029届硕士及以上，以公告要求为准</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
+        <x:v>金融、投资、风险、运营、人力资源及综合管理方向</x:v>
       </x:c>
       <x:c r="I15" s="15" t="str">
-        <x:v>https://job.10086.cn/personal/campus/</x:v>
+        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
       </x:c>
       <x:c r="J15" s="4" t="str">
-        <x:v>2026-09-27</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K15" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L15" s="4" t="str">
-        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
+        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
       </x:c>
       <x:c r="M15" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N15" s="4" t="str">
-        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
+        <x:v>粮曦计划具体批次、面向人群和岗位以中粮资本官方加入我们页面及公告为准。</x:v>
       </x:c>
       <x:c r="O15" s="15" t="str">
-        <x:v>https://job.10086.cn/personal/campus/</x:v>
+        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
       </x:c>
       <x:c r="P15" s="14" t="str">
-        <x:v>A-中国移动官方招聘平台已核验</x:v>
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q15" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1299,55 +1299,55 @@
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="4" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
-        <x:v>广州市卓越教育集团</x:v>
+        <x:v>中移九天人工智能科技</x:v>
       </x:c>
       <x:c r="C16" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>AI/软件/云计算</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企子公司</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>广州等，以职位页为准</x:v>
+        <x:v>北京、西安、广州、深圳</x:v>
       </x:c>
       <x:c r="F16" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/超级实习生</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
       </x:c>
       <x:c r="I16" s="15" t="str">
-        <x:v>https://zyjob.hotjob.cn/</x:v>
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="J16" s="4" t="str">
-        <x:v>2026-10-26</x:v>
+        <x:v>2026-09-27</x:v>
       </x:c>
       <x:c r="K16" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L16" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
+        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
       </x:c>
       <x:c r="M16" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N16" s="4" t="str">
-        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
+        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
       </x:c>
       <x:c r="O16" s="15" t="str">
-        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="P16" s="14" t="str">
-        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
+        <x:v>A-中国移动官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="Q16" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
@@ -1355,134 +1355,134 @@
         <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>搜狐畅游</x:v>
+        <x:v>广州市卓越教育集团</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>民营/互联网</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>以岗位页面为准</x:v>
+        <x:v>广州等，以职位页为准</x:v>
       </x:c>
       <x:c r="F17" s="4" t="str">
-        <x:v>提前批/校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>2027届毕业生（部分岗位兼收2026届）</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>游戏策划、游戏开发、游戏美术、游戏运营、业务支持、平台开发、平台职能、游戏测试8大类岗位</x:v>
+        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
       <x:c r="I17" s="15" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/cyou-inc/42233?recommendCode=DSRgNQU7#/jobs</x:v>
+        <x:v>https://zyjob.hotjob.cn/</x:v>
       </x:c>
       <x:c r="J17" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-26</x:v>
       </x:c>
       <x:c r="K17" s="4" t="str">
-        <x:v>非免笔试；提前批未录取可参加后续统一笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L17" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；官方投递入口已核验</x:v>
+        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
       </x:c>
       <x:c r="M17" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N17" s="4" t="str">
-        <x:v>深圳北理莫斯科大学就业网公告《搜狐畅游2027届秋季校园招聘提前批正式启动！》发布于2026-07-28；提前批流程快、部分岗位有直通面试机会，未被录取者可参与后续统一笔试，部分热招岗位招满即停。</x:v>
+        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
       </x:c>
       <x:c r="O17" s="15" t="str">
-        <x:v>https://career.smbu.edu.cn/detail/online?id=3535355</x:v>
-      </x:c>
-      <x:c r="P17" s="18" t="str">
-        <x:v>B-可信高校就业网公告含官方投递链接</x:v>
+        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
+      </x:c>
+      <x:c r="P17" s="14" t="str">
+        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
       </x:c>
       <x:c r="Q17" s="4" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B18" s="4" t="str">
-        <x:v>我乐家居</x:v>
+        <x:v>搜狐畅游</x:v>
       </x:c>
       <x:c r="C18" s="4" t="str">
-        <x:v>家居/消费品/智能制造</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/互联网</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>以岗位页面为准</x:v>
       </x:c>
       <x:c r="F18" s="4" t="str">
         <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>2027届本科及以上，以岗位要求为准</x:v>
+        <x:v>2027届毕业生（部分岗位兼收2026届）</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
+        <x:v>游戏策划、游戏开发、游戏美术、游戏运营、业务支持、平台开发、平台职能、游戏测试8大类岗位</x:v>
       </x:c>
       <x:c r="I18" s="15" t="str">
-        <x:v>https://olo-home.zhiye.com/Campus</x:v>
+        <x:v>https://app.mokahr.com/m/campus_apply/cyou-inc/42233?recommendCode=DSRgNQU7#/jobs</x:v>
       </x:c>
       <x:c r="J18" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K18" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>非免笔试；提前批未录取可参加后续统一笔试</x:v>
       </x:c>
       <x:c r="L18" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
+        <x:v>可信高校就业网公告显示开放；官方投递入口已核验</x:v>
       </x:c>
       <x:c r="M18" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N18" s="4" t="str">
-        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
+        <x:v>深圳北理莫斯科大学就业网公告《搜狐畅游2027届秋季校园招聘提前批正式启动！》发布于2026-07-28；提前批流程快、部分岗位有直通面试机会，未被录取者可参与后续统一笔试，部分热招岗位招满即停。</x:v>
       </x:c>
       <x:c r="O18" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
+        <x:v>https://career.smbu.edu.cn/detail/online?id=3535355</x:v>
       </x:c>
       <x:c r="P18" s="18" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
+        <x:v>B-可信高校就业网公告含官方投递链接</x:v>
       </x:c>
       <x:c r="Q18" s="4" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="4" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>轩宇信息</x:v>
+        <x:v>我乐家居</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>航天/军工信息化/软件</x:v>
+        <x:v>家居/消费品/智能制造</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>央企子公司/高新技术企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>北京、杭州、西安</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>AI专项/提前批</x:v>
+        <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届本科及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
+        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
       </x:c>
       <x:c r="I19" s="15" t="str">
-        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
+        <x:v>https://olo-home.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1491,19 +1491,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L19" s="4" t="str">
-        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
       </x:c>
       <x:c r="M19" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N19" s="4" t="str">
-        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
+        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
       </x:c>
       <x:c r="O19" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P19" s="14" t="str">
-        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P19" s="18" t="str">
+        <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
       <x:c r="Q19" s="4" t="str">
         <x:v>2026-07-29</x:v>
@@ -1511,31 +1511,31 @@
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
-        <x:v>卡尔动力</x:v>
+        <x:v>轩宇信息</x:v>
       </x:c>
       <x:c r="C20" s="4" t="str">
-        <x:v>自动驾驶/智能汽车</x:v>
+        <x:v>航天/军工信息化/软件</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>央企子公司/高新技术企业</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>北京、上海、天津等</x:v>
+        <x:v>北京、杭州、西安</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>AI专项/提前批</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
         <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
+        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
       </x:c>
       <x:c r="I20" s="15" t="str">
-        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
+        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1544,22 +1544,22 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L20" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
+        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
       </x:c>
       <x:c r="M20" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N20" s="4" t="str">
-        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
+        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
       </x:c>
       <x:c r="O20" s="15" t="str">
-        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
-      </x:c>
-      <x:c r="P20" s="18" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P20" s="14" t="str">
+        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
       </x:c>
       <x:c r="Q20" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
@@ -1567,49 +1567,49 @@
         <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B21" s="4" t="str">
-        <x:v>深信服-X-STAR顶尖人才计划</x:v>
+        <x:v>卡尔动力</x:v>
       </x:c>
       <x:c r="C21" s="4" t="str">
-        <x:v>网络安全/云计算/软件</x:v>
+        <x:v>自动驾驶/智能汽车</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
+        <x:v>北京、上海、天津等</x:v>
       </x:c>
       <x:c r="F21" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>顶尖人才，本硕博按岗位要求</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
+        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
       </x:c>
       <x:c r="I21" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
+        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
       </x:c>
       <x:c r="J21" s="4" t="str">
-        <x:v>2026-09-25</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K21" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L21" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
       </x:c>
       <x:c r="M21" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N21" s="4" t="str">
-        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
+        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
       </x:c>
       <x:c r="O21" s="15" t="str">
-        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
-      </x:c>
-      <x:c r="P21" s="14" t="str">
-        <x:v>A-高校就业网含官方投递链接</x:v>
+        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
+      </x:c>
+      <x:c r="P21" s="18" t="str">
+        <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
       <x:c r="Q21" s="4" t="str">
         <x:v>2026-07-27</x:v>
@@ -1620,49 +1620,49 @@
         <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B22" s="4" t="str">
-        <x:v>希夕智能</x:v>
+        <x:v>深信服-X-STAR顶尖人才计划</x:v>
       </x:c>
       <x:c r="C22" s="4" t="str">
-        <x:v>机器人/智能制造</x:v>
+        <x:v>网络安全/云计算/软件</x:v>
       </x:c>
       <x:c r="D22" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F22" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>2027届本科及以上</x:v>
+        <x:v>顶尖人才，本硕博按岗位要求</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
+        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
       </x:c>
       <x:c r="I22" s="15" t="str">
-        <x:v>https://sunseed.zhiye.com/jobs</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
       </x:c>
       <x:c r="J22" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-09-25</x:v>
       </x:c>
       <x:c r="K22" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L22" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M22" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N22" s="4" t="str">
-        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
+        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
       </x:c>
       <x:c r="O22" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
-      </x:c>
-      <x:c r="P22" s="18" t="str">
-        <x:v>B-高校就业平台转载企业来源</x:v>
+        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
+      </x:c>
+      <x:c r="P22" s="14" t="str">
+        <x:v>A-高校就业网含官方投递链接</x:v>
       </x:c>
       <x:c r="Q22" s="4" t="str">
         <x:v>2026-07-27</x:v>
@@ -1670,108 +1670,108 @@
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="4" t="str">
-        <x:v>不晚于2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B23" s="4" t="str">
-        <x:v>中国兵器工业集团</x:v>
+        <x:v>希夕智能</x:v>
       </x:c>
       <x:c r="C23" s="4" t="str">
-        <x:v>军工/高端装备</x:v>
+        <x:v>机器人/智能制造</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F23" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科及以上</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
+        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
       </x:c>
       <x:c r="I23" s="15" t="str">
-        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
+        <x:v>https://sunseed.zhiye.com/jobs</x:v>
       </x:c>
       <x:c r="J23" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K23" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L23" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
       </x:c>
       <x:c r="M23" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N23" s="4" t="str">
-        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
+        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
       </x:c>
       <x:c r="O23" s="15" t="str">
-        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
       </x:c>
       <x:c r="P23" s="18" t="str">
-        <x:v>B-公开招聘公告/集团入口</x:v>
+        <x:v>B-高校就业平台转载企业来源</x:v>
       </x:c>
       <x:c r="Q23" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="4" t="str">
-        <x:v>2026-07-23</x:v>
+        <x:v>不晚于2026-07-24</x:v>
       </x:c>
       <x:c r="B24" s="4" t="str">
-        <x:v>禾迈股份</x:v>
+        <x:v>中国兵器工业集团</x:v>
       </x:c>
       <x:c r="C24" s="4" t="str">
-        <x:v>光伏/电力电子</x:v>
+        <x:v>军工/高端装备</x:v>
       </x:c>
       <x:c r="D24" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>杭州等，以岗位页为准</x:v>
+        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
       </x:c>
       <x:c r="F24" s="4" t="str">
-        <x:v>研发类提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
+        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
       </x:c>
       <x:c r="I24" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
+        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
       </x:c>
       <x:c r="J24" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K24" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L24" s="4" t="str">
-        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M24" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N24" s="4" t="str">
-        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
+        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
       </x:c>
       <x:c r="O24" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
+        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
       </x:c>
       <x:c r="P24" s="18" t="str">
-        <x:v>B-高校就业网转载企业公告</x:v>
+        <x:v>B-公开招聘公告/集团入口</x:v>
       </x:c>
       <x:c r="Q24" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
@@ -1779,28 +1779,28 @@
         <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B25" s="4" t="str">
-        <x:v>极客未来</x:v>
+        <x:v>禾迈股份</x:v>
       </x:c>
       <x:c r="C25" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>光伏/电力电子</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>四川、重庆、广东</x:v>
+        <x:v>杭州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F25" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>研发类提前批</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
       </x:c>
       <x:c r="I25" s="15" t="str">
-        <x:v>https://geek3.zhiye.com/campus/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
       </x:c>
       <x:c r="J25" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1809,128 +1809,128 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L25" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
+        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
       </x:c>
       <x:c r="M25" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N25" s="4" t="str">
-        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
+        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
       </x:c>
       <x:c r="O25" s="15" t="str">
-        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
       </x:c>
       <x:c r="P25" s="18" t="str">
-        <x:v>B-高校就业网公告+公开招聘页面</x:v>
+        <x:v>B-高校就业网转载企业公告</x:v>
       </x:c>
       <x:c r="Q25" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="54" customHeight="1">
       <x:c r="A26" s="4" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B26" s="4" t="str">
-        <x:v>安永EY</x:v>
+        <x:v>极客未来</x:v>
       </x:c>
       <x:c r="C26" s="4" t="str">
-        <x:v>会计审计/咨询/专业服务</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D26" s="4" t="str">
-        <x:v>外资/专业服务机构</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>中国内地多地，以职位页为准</x:v>
+        <x:v>四川、重庆、广东</x:v>
       </x:c>
       <x:c r="F26" s="4" t="str">
-        <x:v>正式批/秋季校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
+        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
       <x:c r="I26" s="15" t="str">
-        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
+        <x:v>https://geek3.zhiye.com/campus/</x:v>
       </x:c>
       <x:c r="J26" s="4" t="str">
-        <x:v>2026年10月（具体日期未公布）</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K26" s="4" t="str">
-        <x:v>否；官方流程包含在线测评</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L26" s="4" t="str">
-        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
+        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
       </x:c>
       <x:c r="M26" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N26" s="4" t="str">
-        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
+        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
       </x:c>
       <x:c r="O26" s="15" t="str">
-        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
-      </x:c>
-      <x:c r="P26" s="14" t="str">
-        <x:v>A-企业官方校招网站与职位页已核验</x:v>
+        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
+      </x:c>
+      <x:c r="P26" s="18" t="str">
+        <x:v>B-高校就业网公告+公开招聘页面</x:v>
       </x:c>
       <x:c r="Q26" s="4" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="54" customHeight="1">
       <x:c r="A27" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="B27" s="4" t="str">
-        <x:v>阿里巴巴-阿里星计划</x:v>
+        <x:v>安永EY</x:v>
       </x:c>
       <x:c r="C27" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>会计审计/咨询/专业服务</x:v>
       </x:c>
       <x:c r="D27" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>外资/专业服务机构</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>杭州、北京、上海、深圳等</x:v>
+        <x:v>中国内地多地，以职位页为准</x:v>
       </x:c>
       <x:c r="F27" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
+        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
       </x:c>
       <x:c r="I27" s="15" t="str">
-        <x:v>https://talent.alibaba.com/campus/</x:v>
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
       </x:c>
       <x:c r="J27" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026年10月（具体日期未公布）</x:v>
       </x:c>
       <x:c r="K27" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；官方流程包含在线测评</x:v>
       </x:c>
       <x:c r="L27" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
       </x:c>
       <x:c r="M27" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N27" s="4" t="str">
-        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
+        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
       </x:c>
       <x:c r="O27" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P27" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
+      </x:c>
+      <x:c r="P27" s="14" t="str">
+        <x:v>A-企业官方校招网站与职位页已核验</x:v>
       </x:c>
       <x:c r="Q27" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="54" customHeight="1">
@@ -1938,34 +1938,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B28" s="4" t="str">
-        <x:v>贝恩公司</x:v>
+        <x:v>阿里巴巴-阿里星计划</x:v>
       </x:c>
       <x:c r="C28" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D28" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>北京、上海、香港等</x:v>
+        <x:v>杭州、北京、上海、深圳等</x:v>
       </x:c>
       <x:c r="F28" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>助理咨询顾问等</x:v>
+        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
       </x:c>
       <x:c r="I28" s="15" t="str">
-        <x:v>https://www.bain.com/careers/</x:v>
+        <x:v>https://talent.alibaba.com/campus/</x:v>
       </x:c>
       <x:c r="J28" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K28" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L28" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -1973,7 +1973,9 @@
       <x:c r="M28" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N28" s="4" t="str"/>
+      <x:c r="N28" s="4" t="str">
+        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
+      </x:c>
       <x:c r="O28" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -1989,34 +1991,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B29" s="4" t="str">
-        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
+        <x:v>贝恩公司</x:v>
       </x:c>
       <x:c r="C29" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D29" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>上海、北京等</x:v>
+        <x:v>北京、上海、香港等</x:v>
       </x:c>
       <x:c r="F29" s="4" t="str">
-        <x:v>顶尖技术专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
+        <x:v>助理咨询顾问等</x:v>
       </x:c>
       <x:c r="I29" s="15" t="str">
-        <x:v>https://jobs.bilibili.com/</x:v>
+        <x:v>https://www.bain.com/careers/</x:v>
       </x:c>
       <x:c r="J29" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K29" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L29" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2024,9 +2026,7 @@
       <x:c r="M29" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N29" s="4" t="str">
-        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
-      </x:c>
+      <x:c r="N29" s="4" t="str"/>
       <x:c r="O29" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -2042,28 +2042,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B30" s="4" t="str">
-        <x:v>东风汽车-全球博士人才</x:v>
+        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
       </x:c>
       <x:c r="C30" s="4" t="str">
-        <x:v>汽车/央企</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="D30" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>武汉、广州、十堰及全国研发基地</x:v>
+        <x:v>上海、北京等</x:v>
       </x:c>
       <x:c r="F30" s="4" t="str">
-        <x:v>博士专项</x:v>
+        <x:v>顶尖技术专项/提前批</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>2026届及以后博士</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
+        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
       </x:c>
       <x:c r="I30" s="15" t="str">
-        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
+        <x:v>https://jobs.bilibili.com/</x:v>
       </x:c>
       <x:c r="J30" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2078,7 +2078,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N30" s="4" t="str">
-        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
+        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
       </x:c>
       <x:c r="O30" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -2095,28 +2095,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B31" s="4" t="str">
-        <x:v>度小满-博士后人才招聘</x:v>
+        <x:v>东风汽车-全球博士人才</x:v>
       </x:c>
       <x:c r="C31" s="4" t="str">
-        <x:v>金融科技</x:v>
+        <x:v>汽车/央企</x:v>
       </x:c>
       <x:c r="D31" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>武汉、广州、十堰及全国研发基地</x:v>
       </x:c>
       <x:c r="F31" s="4" t="str">
-        <x:v>博士后专项</x:v>
+        <x:v>博士专项</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>2025/2026/2027届博士</x:v>
+        <x:v>2026届及以后博士</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
+        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
       </x:c>
       <x:c r="I31" s="15" t="str">
-        <x:v>https://campus.duxiaoman.com/</x:v>
+        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
       </x:c>
       <x:c r="J31" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2131,7 +2131,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N31" s="4" t="str">
-        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
+        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
       </x:c>
       <x:c r="O31" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -2148,28 +2148,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B32" s="4" t="str">
-        <x:v>多益网络</x:v>
+        <x:v>度小满-博士后人才招聘</x:v>
       </x:c>
       <x:c r="C32" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>金融科技</x:v>
       </x:c>
       <x:c r="D32" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
-        <x:v>广州、武汉、成都等</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F32" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>博士后专项</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2025/2026/2027届博士</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
-        <x:v>程序、策划、美术、运营、市场及职能</x:v>
+        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
       </x:c>
       <x:c r="I32" s="15" t="str">
-        <x:v>https://www.duoyi.com/job/</x:v>
+        <x:v>https://campus.duxiaoman.com/</x:v>
       </x:c>
       <x:c r="J32" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2184,7 +2184,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N32" s="4" t="str">
-        <x:v>岗位可能按城市提前关闭。</x:v>
+        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
       </x:c>
       <x:c r="O32" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -2201,28 +2201,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B33" s="4" t="str">
-        <x:v>海天集团-高潜专项</x:v>
+        <x:v>多益网络</x:v>
       </x:c>
       <x:c r="C33" s="4" t="str">
-        <x:v>工业制造</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
-        <x:v>宁波及全国基地</x:v>
+        <x:v>广州、武汉、成都等</x:v>
       </x:c>
       <x:c r="F33" s="4" t="str">
-        <x:v>高潜人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H33" s="4" t="str">
-        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
+        <x:v>程序、策划、美术、运营、市场及职能</x:v>
       </x:c>
       <x:c r="I33" s="15" t="str">
-        <x:v>https://www.haitian.com/careers/</x:v>
+        <x:v>https://www.duoyi.com/job/</x:v>
       </x:c>
       <x:c r="J33" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2237,7 +2237,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N33" s="4" t="str">
-        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
+        <x:v>岗位可能按城市提前关闭。</x:v>
       </x:c>
       <x:c r="O33" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -2254,28 +2254,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B34" s="4" t="str">
-        <x:v>赫力昂-销售先锋计划</x:v>
+        <x:v>海天集团-高潜专项</x:v>
       </x:c>
       <x:c r="C34" s="4" t="str">
-        <x:v>消费健康/医药</x:v>
+        <x:v>工业制造</x:v>
       </x:c>
       <x:c r="D34" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
-        <x:v>全国重点城市</x:v>
+        <x:v>宁波及全国基地</x:v>
       </x:c>
       <x:c r="F34" s="4" t="str">
-        <x:v>管培/销售专项</x:v>
+        <x:v>高潜人才专项/提前批</x:v>
       </x:c>
       <x:c r="G34" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H34" s="4" t="str">
-        <x:v>医药及消费健康销售、商业运营方向</x:v>
+        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
       </x:c>
       <x:c r="I34" s="15" t="str">
-        <x:v>https://careers.haleon.com/</x:v>
+        <x:v>https://www.haitian.com/careers/</x:v>
       </x:c>
       <x:c r="J34" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2289,7 +2289,9 @@
       <x:c r="M34" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N34" s="4" t="str"/>
+      <x:c r="N34" s="4" t="str">
+        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
+      </x:c>
       <x:c r="O34" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -2305,40 +2307,40 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B35" s="4" t="str">
-        <x:v>虹软科技</x:v>
+        <x:v>赫力昂-销售先锋计划</x:v>
       </x:c>
       <x:c r="C35" s="4" t="str">
-        <x:v>计算机视觉/软件</x:v>
+        <x:v>消费健康/医药</x:v>
       </x:c>
       <x:c r="D35" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E35" s="4" t="str">
-        <x:v>杭州、上海、南京等</x:v>
+        <x:v>全国重点城市</x:v>
       </x:c>
       <x:c r="F35" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>管培/销售专项</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H35" s="4" t="str">
-        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
+        <x:v>医药及消费健康销售、商业运营方向</x:v>
       </x:c>
       <x:c r="I35" s="15" t="str">
-        <x:v>https://hr.arcsoft.com.cn/</x:v>
+        <x:v>https://careers.haleon.com/</x:v>
       </x:c>
       <x:c r="J35" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K35" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L35" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M35" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N35" s="4" t="str"/>
       <x:c r="O35" s="15" t="str">
@@ -2356,31 +2358,31 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B36" s="4" t="str">
-        <x:v>汇川技术</x:v>
+        <x:v>虹软科技</x:v>
       </x:c>
       <x:c r="C36" s="4" t="str">
-        <x:v>工业自动化/新能源</x:v>
+        <x:v>计算机视觉/软件</x:v>
       </x:c>
       <x:c r="D36" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
-        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
+        <x:v>杭州、上海、南京等</x:v>
       </x:c>
       <x:c r="F36" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G36" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H36" s="4" t="str">
-        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
+        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
       </x:c>
       <x:c r="I36" s="15" t="str">
-        <x:v>https://career.inovance.com/</x:v>
+        <x:v>https://hr.arcsoft.com.cn/</x:v>
       </x:c>
       <x:c r="J36" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K36" s="4" t="str">
         <x:v>按岗位，官方未统一说明</x:v>
@@ -2389,7 +2391,7 @@
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M36" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N36" s="4" t="str"/>
       <x:c r="O36" s="15" t="str">
@@ -2407,34 +2409,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B37" s="4" t="str">
-        <x:v>伽利略-星途星锐计划</x:v>
+        <x:v>汇川技术</x:v>
       </x:c>
       <x:c r="C37" s="4" t="str">
-        <x:v>科技/综合</x:v>
+        <x:v>工业自动化/新能源</x:v>
       </x:c>
       <x:c r="D37" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E37" s="4" t="str">
-        <x:v>以项目职位页为准</x:v>
+        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
       </x:c>
       <x:c r="F37" s="4" t="str">
-        <x:v>人才专项</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G37" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
-        <x:v>以官方项目页为准</x:v>
-      </x:c>
-      <x:c r="I37" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
+      </x:c>
+      <x:c r="I37" s="15" t="str">
+        <x:v>https://career.inovance.com/</x:v>
       </x:c>
       <x:c r="J37" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K37" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L37" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2442,14 +2444,12 @@
       <x:c r="M37" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N37" s="4" t="str">
-        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
-      </x:c>
+      <x:c r="N37" s="4" t="str"/>
       <x:c r="O37" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P37" s="19" t="str">
-        <x:v>C-主体与入口需二次确认</x:v>
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q37" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -2460,52 +2460,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B38" s="4" t="str">
-        <x:v>京东-TET管理培训生</x:v>
+        <x:v>伽利略-星途星锐计划</x:v>
       </x:c>
       <x:c r="C38" s="4" t="str">
-        <x:v>互联网/零售</x:v>
+        <x:v>科技/综合</x:v>
       </x:c>
       <x:c r="D38" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E38" s="4" t="str">
-        <x:v>北京及业务所在城市</x:v>
+        <x:v>以项目职位页为准</x:v>
       </x:c>
       <x:c r="F38" s="4" t="str">
-        <x:v>管培生专项/提前批</x:v>
+        <x:v>人才专项</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H38" s="4" t="str">
-        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
-      </x:c>
-      <x:c r="I38" s="15" t="str">
-        <x:v>https://campus.jd.com/</x:v>
+        <x:v>以官方项目页为准</x:v>
+      </x:c>
+      <x:c r="I38" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J38" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K38" s="4" t="str">
-        <x:v>含测评，笔试以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L38" s="4" t="str">
-        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M38" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N38" s="4" t="str">
-        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
+        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
       </x:c>
       <x:c r="O38" s="15" t="str">
-        <x:v>https://campus.jd.com/#/</x:v>
-      </x:c>
-      <x:c r="P38" s="14" t="str">
-        <x:v>A-企业官网校招页面已核验</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P38" s="19" t="str">
+        <x:v>C-主体与入口需二次确认</x:v>
       </x:c>
       <x:c r="Q38" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="54" customHeight="1">
@@ -2513,52 +2513,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B39" s="4" t="str">
-        <x:v>科大讯飞-飞凡计划</x:v>
+        <x:v>京东-TET管理培训生</x:v>
       </x:c>
       <x:c r="C39" s="4" t="str">
-        <x:v>AI/软件</x:v>
+        <x:v>互联网/零售</x:v>
       </x:c>
       <x:c r="D39" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
-        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
+        <x:v>北京及业务所在城市</x:v>
       </x:c>
       <x:c r="F39" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>管培生专项/提前批</x:v>
       </x:c>
       <x:c r="G39" s="4" t="str">
-        <x:v>2026/2027届</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H39" s="4" t="str">
-        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
+        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
       </x:c>
       <x:c r="I39" s="15" t="str">
-        <x:v>https://campus.iflytek.com/</x:v>
+        <x:v>https://campus.jd.com/</x:v>
       </x:c>
       <x:c r="J39" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K39" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>含测评，笔试以通知为准</x:v>
       </x:c>
       <x:c r="L39" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
       </x:c>
       <x:c r="M39" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N39" s="4" t="str">
-        <x:v>专项岗位与常规校招可能并行。</x:v>
+        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
       </x:c>
       <x:c r="O39" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P39" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://campus.jd.com/#/</x:v>
+      </x:c>
+      <x:c r="P39" s="14" t="str">
+        <x:v>A-企业官网校招页面已核验</x:v>
       </x:c>
       <x:c r="Q39" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="54" customHeight="1">
@@ -2566,28 +2566,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B40" s="4" t="str">
-        <x:v>理想汽车</x:v>
+        <x:v>科大讯飞-飞凡计划</x:v>
       </x:c>
       <x:c r="C40" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>AI/软件</x:v>
       </x:c>
       <x:c r="D40" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E40" s="4" t="str">
-        <x:v>北京、上海、常州等</x:v>
+        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
       </x:c>
       <x:c r="F40" s="4" t="str">
-        <x:v>暑期实习转正通道</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G40" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026/2027届</x:v>
       </x:c>
       <x:c r="H40" s="4" t="str">
-        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
+        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
       </x:c>
       <x:c r="I40" s="15" t="str">
-        <x:v>https://career.lixiang.com/campus</x:v>
+        <x:v>https://campus.iflytek.com/</x:v>
       </x:c>
       <x:c r="J40" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2602,7 +2602,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N40" s="4" t="str">
-        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
+        <x:v>专项岗位与常规校招可能并行。</x:v>
       </x:c>
       <x:c r="O40" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -2619,42 +2619,44 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B41" s="4" t="str">
-        <x:v>莉莉丝游戏</x:v>
+        <x:v>理想汽车</x:v>
       </x:c>
       <x:c r="C41" s="4" t="str">
-        <x:v>游戏</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D41" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E41" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>北京、上海、常州等</x:v>
       </x:c>
       <x:c r="F41" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>暑期实习转正通道</x:v>
       </x:c>
       <x:c r="G41" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H41" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
+        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
       </x:c>
       <x:c r="I41" s="15" t="str">
-        <x:v>https://campus.lilith.com/</x:v>
+        <x:v>https://career.lixiang.com/campus</x:v>
       </x:c>
       <x:c r="J41" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K41" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L41" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M41" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N41" s="4" t="str"/>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N41" s="4" t="str">
+        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
+      </x:c>
       <x:c r="O41" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -2670,40 +2672,40 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B42" s="4" t="str">
-        <x:v>麦肯锡</x:v>
+        <x:v>莉莉丝游戏</x:v>
       </x:c>
       <x:c r="C42" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>游戏</x:v>
       </x:c>
       <x:c r="D42" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E42" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F42" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G42" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H42" s="4" t="str">
-        <x:v>商业分析师、咨询及专业岗位</x:v>
+        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
       </x:c>
       <x:c r="I42" s="15" t="str">
-        <x:v>https://www.mckinsey.com/careers</x:v>
+        <x:v>https://campus.lilith.com/</x:v>
       </x:c>
       <x:c r="J42" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="K42" s="4" t="str">
-        <x:v>通常含测评/案例面试；以通知为准</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L42" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M42" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N42" s="4" t="str"/>
       <x:c r="O42" s="15" t="str">
@@ -2721,34 +2723,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B43" s="4" t="str">
-        <x:v>拼多多</x:v>
+        <x:v>麦肯锡</x:v>
       </x:c>
       <x:c r="C43" s="4" t="str">
-        <x:v>互联网/电商</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D43" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E43" s="4" t="str">
-        <x:v>上海、广州等，以岗位页为准</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F43" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G43" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H43" s="4" t="str">
-        <x:v>技术、算法、产品、运营、商业分析等</x:v>
+        <x:v>商业分析师、咨询及专业岗位</x:v>
       </x:c>
       <x:c r="I43" s="15" t="str">
-        <x:v>https://careers.pinduoduo.com/campus/</x:v>
+        <x:v>https://www.mckinsey.com/careers</x:v>
       </x:c>
       <x:c r="J43" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K43" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>通常含测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L43" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2756,9 +2758,7 @@
       <x:c r="M43" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N43" s="4" t="str">
-        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
-      </x:c>
+      <x:c r="N43" s="4" t="str"/>
       <x:c r="O43" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -2774,34 +2774,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B44" s="4" t="str">
-        <x:v>启林投资</x:v>
+        <x:v>拼多多</x:v>
       </x:c>
       <x:c r="C44" s="4" t="str">
-        <x:v>量化金融/资管</x:v>
+        <x:v>互联网/电商</x:v>
       </x:c>
       <x:c r="D44" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E44" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>上海、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F44" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G44" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H44" s="4" t="str">
-        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
+        <x:v>技术、算法、产品、运营、商业分析等</x:v>
       </x:c>
       <x:c r="I44" s="15" t="str">
-        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
+        <x:v>https://careers.pinduoduo.com/campus/</x:v>
       </x:c>
       <x:c r="J44" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K44" s="4" t="str">
-        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L44" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2810,7 +2810,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N44" s="4" t="str">
-        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
+        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
       </x:c>
       <x:c r="O44" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -2827,34 +2827,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B45" s="4" t="str">
-        <x:v>商汤科技-无限原力计划</x:v>
+        <x:v>启林投资</x:v>
       </x:c>
       <x:c r="C45" s="4" t="str">
-        <x:v>AI/计算机视觉</x:v>
+        <x:v>量化金融/资管</x:v>
       </x:c>
       <x:c r="D45" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E45" s="4" t="str">
-        <x:v>上海、北京、深圳、杭州等</x:v>
+        <x:v>上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F45" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G45" s="4" t="str">
-        <x:v>2027/2028届</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H45" s="4" t="str">
-        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
+        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
       </x:c>
       <x:c r="I45" s="15" t="str">
-        <x:v>https://joinus.sensetime.com/</x:v>
+        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
       </x:c>
       <x:c r="J45" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K45" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
       </x:c>
       <x:c r="L45" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2863,7 +2863,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N45" s="4" t="str">
-        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
+        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
       </x:c>
       <x:c r="O45" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -2880,28 +2880,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B46" s="4" t="str">
-        <x:v>腾讯-青云计划</x:v>
+        <x:v>商汤科技-无限原力计划</x:v>
       </x:c>
       <x:c r="C46" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>AI/计算机视觉</x:v>
       </x:c>
       <x:c r="D46" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E46" s="4" t="str">
-        <x:v>深圳、北京、上海等</x:v>
+        <x:v>上海、北京、深圳、杭州等</x:v>
       </x:c>
       <x:c r="F46" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G46" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027/2028届</x:v>
       </x:c>
       <x:c r="H46" s="4" t="str">
-        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
+        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
       </x:c>
       <x:c r="I46" s="15" t="str">
-        <x:v>https://join.qq.com/</x:v>
+        <x:v>https://joinus.sensetime.com/</x:v>
       </x:c>
       <x:c r="J46" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2916,7 +2916,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N46" s="4" t="str">
-        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
+        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
       </x:c>
       <x:c r="O46" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -2933,28 +2933,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B47" s="4" t="str">
-        <x:v>天锐星通</x:v>
+        <x:v>腾讯-青云计划</x:v>
       </x:c>
       <x:c r="C47" s="4" t="str">
-        <x:v>卫星通信/相控阵</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D47" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E47" s="4" t="str">
-        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
+        <x:v>深圳、北京、上海等</x:v>
       </x:c>
       <x:c r="F47" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G47" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H47" s="4" t="str">
-        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
+        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
       </x:c>
       <x:c r="I47" s="15" t="str">
-        <x:v>https://www.tianruixing.com/</x:v>
+        <x:v>https://join.qq.com/</x:v>
       </x:c>
       <x:c r="J47" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2969,7 +2969,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N47" s="4" t="str">
-        <x:v>官网入口与具体岗位需投前复核。</x:v>
+        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
       </x:c>
       <x:c r="O47" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -2983,52 +2983,52 @@
     </x:row>
     <x:row r="48" ht="54" customHeight="1">
       <x:c r="A48" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B48" s="4" t="str">
-        <x:v>网易游戏雷火</x:v>
+        <x:v>天锐星通</x:v>
       </x:c>
       <x:c r="C48" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>卫星通信/相控阵</x:v>
       </x:c>
       <x:c r="D48" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E48" s="4" t="str">
-        <x:v>杭州、上海等，以岗位页为准</x:v>
+        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F48" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G48" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H48" s="4" t="str">
-        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
+        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
       </x:c>
       <x:c r="I48" s="15" t="str">
-        <x:v>https://leihuo.163.com/campus/#/full</x:v>
+        <x:v>https://www.tianruixing.com/</x:v>
       </x:c>
       <x:c r="J48" s="4" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K48" s="4" t="str">
-        <x:v>部分岗位免笔试；部分可直通面试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L48" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M48" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N48" s="4" t="str">
-        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
+        <x:v>官网入口与具体岗位需投前复核。</x:v>
       </x:c>
       <x:c r="O48" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P48" s="14" t="str">
-        <x:v>A-官方招聘官网已核验</x:v>
+      <x:c r="P48" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q48" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3036,52 +3036,52 @@
     </x:row>
     <x:row r="49" ht="54" customHeight="1">
       <x:c r="A49" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B49" s="4" t="str">
-        <x:v>小鹏集团</x:v>
+        <x:v>网易游戏雷火</x:v>
       </x:c>
       <x:c r="C49" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D49" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E49" s="4" t="str">
-        <x:v>广州、北京、上海、深圳、武汉等</x:v>
+        <x:v>杭州、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F49" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G49" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H49" s="4" t="str">
-        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
+        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
       </x:c>
       <x:c r="I49" s="15" t="str">
-        <x:v>https://join.xiaopeng.com/campus</x:v>
+        <x:v>https://leihuo.163.com/campus/#/full</x:v>
       </x:c>
       <x:c r="J49" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="K49" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>部分岗位免笔试；部分可直通面试</x:v>
       </x:c>
       <x:c r="L49" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M49" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N49" s="4" t="str">
-        <x:v>营销服与技术岗位可能分项目发布。</x:v>
+        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
       </x:c>
       <x:c r="O49" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P49" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P49" s="14" t="str">
+        <x:v>A-官方招聘官网已核验</x:v>
       </x:c>
       <x:c r="Q49" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3092,34 +3092,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B50" s="4" t="str">
-        <x:v>芯动科技</x:v>
+        <x:v>小鹏集团</x:v>
       </x:c>
       <x:c r="C50" s="4" t="str">
-        <x:v>半导体/IP设计</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D50" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E50" s="4" t="str">
-        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
+        <x:v>广州、北京、上海、深圳、武汉等</x:v>
       </x:c>
       <x:c r="F50" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G50" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H50" s="4" t="str">
-        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
+        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
       </x:c>
       <x:c r="I50" s="15" t="str">
-        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
+        <x:v>https://join.xiaopeng.com/campus</x:v>
       </x:c>
       <x:c r="J50" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K50" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L50" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3127,7 +3127,9 @@
       <x:c r="M50" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N50" s="4" t="str"/>
+      <x:c r="N50" s="4" t="str">
+        <x:v>营销服与技术岗位可能分项目发布。</x:v>
+      </x:c>
       <x:c r="O50" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3140,52 +3142,50 @@
     </x:row>
     <x:row r="51" ht="54" customHeight="1">
       <x:c r="A51" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B51" s="4" t="str">
-        <x:v>芯迈半导体</x:v>
+        <x:v>芯动科技</x:v>
       </x:c>
       <x:c r="C51" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>半导体/IP设计</x:v>
       </x:c>
       <x:c r="D51" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E51" s="4" t="str">
-        <x:v>杭州、上海、深圳、成都</x:v>
+        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
       </x:c>
       <x:c r="F51" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G51" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H51" s="4" t="str">
-        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
+        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
       </x:c>
       <x:c r="I51" s="15" t="str">
-        <x:v>https://www.silicon-magic.com/joinus</x:v>
+        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
       </x:c>
       <x:c r="J51" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K51" s="4" t="str">
-        <x:v>官方未说明；公开流程未列笔试</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L51" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M51" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N51" s="4" t="str">
-        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
-      </x:c>
+      <x:c r="N51" s="4" t="str"/>
       <x:c r="O51" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P51" s="14" t="str">
-        <x:v>A-企业官网与公开公告已核验</x:v>
+      <x:c r="P51" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q51" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3193,55 +3193,55 @@
     </x:row>
     <x:row r="52" ht="54" customHeight="1">
       <x:c r="A52" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B52" s="4" t="str">
-        <x:v>新易盛</x:v>
+        <x:v>芯迈半导体</x:v>
       </x:c>
       <x:c r="C52" s="4" t="str">
-        <x:v>光通信/半导体</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D52" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E52" s="4" t="str">
-        <x:v>成都、苏州等，以岗位页为准</x:v>
+        <x:v>杭州、上海、深圳、成都</x:v>
       </x:c>
       <x:c r="F52" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G52" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H52" s="4" t="str">
-        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
+        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
       </x:c>
       <x:c r="I52" s="15" t="str">
-        <x:v>https://www.eoptolink.com/</x:v>
+        <x:v>https://www.silicon-magic.com/joinus</x:v>
       </x:c>
       <x:c r="J52" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K52" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未说明；公开流程未列笔试</x:v>
       </x:c>
       <x:c r="L52" s="4" t="str">
-        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M52" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N52" s="4" t="str">
-        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
       </x:c>
       <x:c r="O52" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P52" s="18" t="str">
-        <x:v>B-高校/招聘平台转载，投前复核</x:v>
+      <x:c r="P52" s="14" t="str">
+        <x:v>A-企业官网与公开公告已核验</x:v>
       </x:c>
       <x:c r="Q52" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="54" customHeight="1">
@@ -3249,50 +3249,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B53" s="4" t="str">
-        <x:v>元戎启行</x:v>
+        <x:v>新易盛</x:v>
       </x:c>
       <x:c r="C53" s="4" t="str">
-        <x:v>自动驾驶</x:v>
+        <x:v>光通信/半导体</x:v>
       </x:c>
       <x:c r="D53" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E53" s="4" t="str">
-        <x:v>深圳、北京等</x:v>
+        <x:v>成都、苏州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F53" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G53" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H53" s="4" t="str">
-        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
+        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
       </x:c>
       <x:c r="I53" s="15" t="str">
-        <x:v>https://www.deeproute.ai/join-us</x:v>
+        <x:v>https://www.eoptolink.com/</x:v>
       </x:c>
       <x:c r="J53" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K53" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L53" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
       </x:c>
       <x:c r="M53" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N53" s="4" t="str"/>
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N53" s="4" t="str">
+        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+      </x:c>
       <x:c r="O53" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P53" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P53" s="18" t="str">
+        <x:v>B-高校/招聘平台转载，投前复核</x:v>
       </x:c>
       <x:c r="Q53" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="54" customHeight="1">
@@ -3300,34 +3302,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B54" s="4" t="str">
-        <x:v>圆通速递</x:v>
+        <x:v>元戎启行</x:v>
       </x:c>
       <x:c r="C54" s="4" t="str">
-        <x:v>物流/供应链</x:v>
+        <x:v>自动驾驶</x:v>
       </x:c>
       <x:c r="D54" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E54" s="4" t="str">
-        <x:v>上海及全国网络</x:v>
+        <x:v>深圳、北京等</x:v>
       </x:c>
       <x:c r="F54" s="4" t="str">
-        <x:v>正式批/校招</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G54" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H54" s="4" t="str">
-        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
+        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
       </x:c>
       <x:c r="I54" s="15" t="str">
-        <x:v>https://hr.yto.net.cn/</x:v>
+        <x:v>https://www.deeproute.ai/join-us</x:v>
       </x:c>
       <x:c r="J54" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K54" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L54" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3351,34 +3353,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B55" s="4" t="str">
-        <x:v>长亭科技</x:v>
+        <x:v>圆通速递</x:v>
       </x:c>
       <x:c r="C55" s="4" t="str">
-        <x:v>网络安全</x:v>
+        <x:v>物流/供应链</x:v>
       </x:c>
       <x:c r="D55" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E55" s="4" t="str">
-        <x:v>北京、上海等，以岗位页为准</x:v>
+        <x:v>上海及全国网络</x:v>
       </x:c>
       <x:c r="F55" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批/校招</x:v>
       </x:c>
       <x:c r="G55" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H55" s="4" t="str">
-        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
+        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
       </x:c>
       <x:c r="I55" s="15" t="str">
-        <x:v>https://job.chaitin.cn/</x:v>
+        <x:v>https://hr.yto.net.cn/</x:v>
       </x:c>
       <x:c r="J55" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K55" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L55" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3402,28 +3404,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B56" s="4" t="str">
-        <x:v>智元机器人-优才计划</x:v>
+        <x:v>长亭科技</x:v>
       </x:c>
       <x:c r="C56" s="4" t="str">
-        <x:v>具身智能/机器人</x:v>
+        <x:v>网络安全</x:v>
       </x:c>
       <x:c r="D56" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E56" s="4" t="str">
-        <x:v>上海、北京、深圳等</x:v>
+        <x:v>北京、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F56" s="4" t="str">
-        <x:v>优才专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G56" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H56" s="4" t="str">
-        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
+        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
       </x:c>
       <x:c r="I56" s="15" t="str">
-        <x:v>https://www.agibot.com/recruit</x:v>
+        <x:v>https://job.chaitin.cn/</x:v>
       </x:c>
       <x:c r="J56" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3453,34 +3455,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B57" s="4" t="str">
-        <x:v>中国电信天翼云-超级优才</x:v>
+        <x:v>智元机器人-优才计划</x:v>
       </x:c>
       <x:c r="C57" s="4" t="str">
-        <x:v>云计算/央企</x:v>
+        <x:v>具身智能/机器人</x:v>
       </x:c>
       <x:c r="D57" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E57" s="4" t="str">
-        <x:v>北京、上海、广州、成都及全国机构</x:v>
+        <x:v>上海、北京、深圳等</x:v>
       </x:c>
       <x:c r="F57" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>优才专项/提前批</x:v>
       </x:c>
       <x:c r="G57" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H57" s="4" t="str">
-        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
+        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
       </x:c>
       <x:c r="I57" s="15" t="str">
-        <x:v>https://www.ctyun.cn/about/recruit</x:v>
+        <x:v>https://www.agibot.com/recruit</x:v>
       </x:c>
       <x:c r="J57" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K57" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L57" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3488,9 +3490,7 @@
       <x:c r="M57" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N57" s="4" t="str">
-        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
-      </x:c>
+      <x:c r="N57" s="4" t="str"/>
       <x:c r="O57" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3506,31 +3506,31 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B58" s="4" t="str">
-        <x:v>中科光电</x:v>
+        <x:v>中国电信天翼云-超级优才</x:v>
       </x:c>
       <x:c r="C58" s="4" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>云计算/央企</x:v>
       </x:c>
       <x:c r="D58" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E58" s="4" t="str">
-        <x:v>以职位公告为准</x:v>
+        <x:v>北京、上海、广州、成都及全国机构</x:v>
       </x:c>
       <x:c r="F58" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G58" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H58" s="4" t="str">
-        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
+        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
       </x:c>
       <x:c r="I58" s="15" t="str">
-        <x:v>https://job.cn-amd.com/</x:v>
+        <x:v>https://www.ctyun.cn/about/recruit</x:v>
       </x:c>
       <x:c r="J58" s="4" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K58" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -3539,16 +3539,16 @@
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M58" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N58" s="4" t="str">
-        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
+        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
       </x:c>
       <x:c r="O58" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P58" s="19" t="str">
-        <x:v>C-名称需二次确认</x:v>
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q58" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3559,31 +3559,31 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B59" s="4" t="str">
-        <x:v>中兴微电子-未来领军计划</x:v>
+        <x:v>中科光电</x:v>
       </x:c>
       <x:c r="C59" s="4" t="str">
-        <x:v>半导体/通信</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D59" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E59" s="4" t="str">
-        <x:v>深圳、西安、南京、上海等</x:v>
+        <x:v>以职位公告为准</x:v>
       </x:c>
       <x:c r="F59" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G59" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H59" s="4" t="str">
-        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
+        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
       </x:c>
       <x:c r="I59" s="15" t="str">
-        <x:v>https://job.zte.com.cn/</x:v>
+        <x:v>https://job.cn-amd.com/</x:v>
       </x:c>
       <x:c r="J59" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K59" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -3592,123 +3592,125 @@
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M59" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N59" s="4" t="str">
-        <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
+        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
       </x:c>
       <x:c r="O59" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P59" s="19" t="str">
+        <x:v>C-名称需二次确认</x:v>
+      </x:c>
+      <x:c r="Q59" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="54" customHeight="1">
+      <x:c r="A60" s="4" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B60" s="4" t="str">
+        <x:v>中兴微电子-未来领军计划</x:v>
+      </x:c>
+      <x:c r="C60" s="4" t="str">
+        <x:v>半导体/通信</x:v>
+      </x:c>
+      <x:c r="D60" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E60" s="4" t="str">
+        <x:v>深圳、西安、南京、上海等</x:v>
+      </x:c>
+      <x:c r="F60" s="4" t="str">
+        <x:v>顶尖人才专项/提前批</x:v>
+      </x:c>
+      <x:c r="G60" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H60" s="4" t="str">
+        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
+      </x:c>
+      <x:c r="I60" s="15" t="str">
+        <x:v>https://job.zte.com.cn/</x:v>
+      </x:c>
+      <x:c r="J60" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K60" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L60" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M60" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N60" s="4" t="str">
+        <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
+      </x:c>
+      <x:c r="O60" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P60" s="19" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q59" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" ht="54" customHeight="1">
-      <x:c r="A60" s="16" t="str">
+      <x:c r="Q60" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="54" customHeight="1">
+      <x:c r="A61" s="16" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B60" s="16" t="str">
+      <x:c r="B61" s="16" t="str">
         <x:v>字节跳动-AI产品经理早鸟通道</x:v>
       </x:c>
-      <x:c r="C60" s="16" t="str">
+      <x:c r="C61" s="16" t="str">
         <x:v>互联网/AI</x:v>
       </x:c>
-      <x:c r="D60" s="16" t="str">
+      <x:c r="D61" s="16" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E60" s="16" t="str">
+      <x:c r="E61" s="16" t="str">
         <x:v>北京、上海、深圳</x:v>
       </x:c>
-      <x:c r="F60" s="16" t="str">
+      <x:c r="F61" s="16" t="str">
         <x:v>早鸟专项/提前批</x:v>
       </x:c>
-      <x:c r="G60" s="16" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H60" s="16" t="str">
+      <x:c r="G61" s="16" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H61" s="16" t="str">
         <x:v>AI产品经理、智能体及大模型产品方向</x:v>
       </x:c>
-      <x:c r="I60" s="17" t="str">
+      <x:c r="I61" s="17" t="str">
         <x:v>https://jobs.bytedance.com/campus/</x:v>
       </x:c>
-      <x:c r="J60" s="16" t="str">
+      <x:c r="J61" s="16" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
-      <x:c r="K60" s="16" t="str">
+      <x:c r="K61" s="16" t="str">
         <x:v>按岗位，未统一公布</x:v>
       </x:c>
-      <x:c r="L60" s="16" t="str">
+      <x:c r="L61" s="16" t="str">
         <x:v>已截止（2026-08-02）；原公告与官方投递入口保留</x:v>
       </x:c>
-      <x:c r="M60" s="16" t="str">
+      <x:c r="M61" s="16" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N60" s="16" t="str">
+      <x:c r="N61" s="16" t="str">
         <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
       </x:c>
-      <x:c r="O60" s="17" t="str">
+      <x:c r="O61" s="17" t="str">
         <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
       </x:c>
-      <x:c r="P60" s="18" t="str">
+      <x:c r="P61" s="18" t="str">
         <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q60" s="16" t="str">
+      <x:c r="Q61" s="16" t="str">
         <x:v>2026-08-03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" ht="54" customHeight="1">
-      <x:c r="A61" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
-      </x:c>
-      <x:c r="B61" s="4" t="str">
-        <x:v>BCG波士顿咨询</x:v>
-      </x:c>
-      <x:c r="C61" s="4" t="str">
-        <x:v>管理咨询</x:v>
-      </x:c>
-      <x:c r="D61" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E61" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
-      </x:c>
-      <x:c r="F61" s="4" t="str">
-        <x:v>正式批/中国区校招</x:v>
-      </x:c>
-      <x:c r="G61" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H61" s="4" t="str">
-        <x:v>咨询顾问及相关专业岗位</x:v>
-      </x:c>
-      <x:c r="I61" s="15" t="str">
-        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
-      </x:c>
-      <x:c r="J61" s="4" t="str">
-        <x:v>2026-08-16</x:v>
-      </x:c>
-      <x:c r="K61" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
-      </x:c>
-      <x:c r="L61" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
-      </x:c>
-      <x:c r="M61" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N61" s="4" t="str"/>
-      <x:c r="O61" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P61" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q61" s="4" t="str">
-        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="54" customHeight="1">
@@ -3716,44 +3718,42 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B62" s="4" t="str">
-        <x:v>OPPO</x:v>
+        <x:v>BCG波士顿咨询</x:v>
       </x:c>
       <x:c r="C62" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D62" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E62" s="4" t="str">
-        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F62" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
+        <x:v>正式批/中国区校招</x:v>
       </x:c>
       <x:c r="G62" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H62" s="4" t="str">
-        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
+        <x:v>咨询顾问及相关专业岗位</x:v>
       </x:c>
       <x:c r="I62" s="15" t="str">
-        <x:v>https://careers.oppo.com/campus</x:v>
+        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
       </x:c>
       <x:c r="J62" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K62" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L62" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M62" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N62" s="4" t="str">
-        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
-      </x:c>
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N62" s="4" t="str"/>
       <x:c r="O62" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3769,28 +3769,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B63" s="4" t="str">
-        <x:v>Tap4Fun</x:v>
+        <x:v>OPPO</x:v>
       </x:c>
       <x:c r="C63" s="4" t="str">
-        <x:v>游戏</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D63" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E63" s="4" t="str">
-        <x:v>成都等</x:v>
+        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
       </x:c>
       <x:c r="F63" s="4" t="str">
-        <x:v>实习转正通道</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G63" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H63" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
+        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
       </x:c>
       <x:c r="I63" s="15" t="str">
-        <x:v>https://www.tap4fun.com/careers</x:v>
+        <x:v>https://careers.oppo.com/campus</x:v>
       </x:c>
       <x:c r="J63" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3805,7 +3805,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N63" s="4" t="str">
-        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
+        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
       </x:c>
       <x:c r="O63" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3819,161 +3819,161 @@
     </x:row>
     <x:row r="64" ht="54" customHeight="1">
       <x:c r="A64" s="4" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B64" s="4" t="str">
+        <x:v>Tap4Fun</x:v>
+      </x:c>
+      <x:c r="C64" s="4" t="str">
+        <x:v>游戏</x:v>
+      </x:c>
+      <x:c r="D64" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E64" s="4" t="str">
+        <x:v>成都等</x:v>
+      </x:c>
+      <x:c r="F64" s="4" t="str">
+        <x:v>实习转正通道</x:v>
+      </x:c>
+      <x:c r="G64" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H64" s="4" t="str">
+        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
+      </x:c>
+      <x:c r="I64" s="15" t="str">
+        <x:v>https://www.tap4fun.com/careers</x:v>
+      </x:c>
+      <x:c r="J64" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K64" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L64" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M64" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N64" s="4" t="str">
+        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
+      </x:c>
+      <x:c r="O64" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P64" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q64" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="54" customHeight="1">
+      <x:c r="A65" s="4" t="str">
         <x:v>2026-07-20</x:v>
       </x:c>
-      <x:c r="B64" s="4" t="str">
+      <x:c r="B65" s="4" t="str">
         <x:v>航天科技集团五院502所</x:v>
       </x:c>
-      <x:c r="C64" s="4" t="str">
+      <x:c r="C65" s="4" t="str">
         <x:v>航天/自动控制</x:v>
       </x:c>
-      <x:c r="D64" s="4" t="str">
+      <x:c r="D65" s="4" t="str">
         <x:v>事业单位/央企院所</x:v>
       </x:c>
-      <x:c r="E64" s="4" t="str">
+      <x:c r="E65" s="4" t="str">
         <x:v>北京</x:v>
       </x:c>
-      <x:c r="F64" s="4" t="str">
+      <x:c r="F65" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G64" s="4" t="str">
+      <x:c r="G65" s="4" t="str">
         <x:v>硕士/博士为主，以岗位为准</x:v>
       </x:c>
-      <x:c r="H64" s="4" t="str">
+      <x:c r="H65" s="4" t="str">
         <x:v>导航制导与控制、自动化、电子、通信、计算机、软件、机械等</x:v>
       </x:c>
-      <x:c r="I64" s="15" t="str">
+      <x:c r="I65" s="15" t="str">
         <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
-      <x:c r="J64" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K64" s="4" t="str">
+      <x:c r="J65" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K65" s="4" t="str">
         <x:v>未统一公布</x:v>
       </x:c>
-      <x:c r="L64" s="4" t="str">
+      <x:c r="L65" s="4" t="str">
         <x:v>公开公告显示开放；投前确认</x:v>
       </x:c>
-      <x:c r="M64" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N64" s="4" t="str">
+      <x:c r="M65" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N65" s="4" t="str">
         <x:v>研究所岗位通常有专业、学历、政审及保密要求。</x:v>
       </x:c>
-      <x:c r="O64" s="15" t="str">
+      <x:c r="O65" s="15" t="str">
         <x:v>https://www.baidu.com/s?wd=%E4%BA%94%E9%99%A2502%E6%89%802027%E5%B1%8A%E6%A0%A1%E6%8B%9B</x:v>
       </x:c>
-      <x:c r="P64" s="18" t="str">
+      <x:c r="P65" s="18" t="str">
         <x:v>B-高校就业网公开公告</x:v>
       </x:c>
-      <x:c r="Q64" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="54" customHeight="1">
-      <x:c r="A65" s="16" t="str">
+      <x:c r="Q65" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="54" customHeight="1">
+      <x:c r="A66" s="16" t="str">
         <x:v>2026-07-17</x:v>
       </x:c>
-      <x:c r="B65" s="16" t="str">
+      <x:c r="B66" s="16" t="str">
         <x:v>鹰角网络</x:v>
       </x:c>
-      <x:c r="C65" s="16" t="str">
+      <x:c r="C66" s="16" t="str">
         <x:v>游戏</x:v>
       </x:c>
-      <x:c r="D65" s="16" t="str">
+      <x:c r="D66" s="16" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E65" s="16" t="str">
+      <x:c r="E66" s="16" t="str">
         <x:v>上海</x:v>
       </x:c>
-      <x:c r="F65" s="16" t="str">
+      <x:c r="F66" s="16" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G65" s="16" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H65" s="16" t="str">
+      <x:c r="G66" s="16" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H66" s="16" t="str">
         <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
       </x:c>
-      <x:c r="I65" s="17" t="str">
+      <x:c r="I66" s="17" t="str">
         <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
       </x:c>
-      <x:c r="J65" s="16" t="str">
+      <x:c r="J66" s="16" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
-      <x:c r="K65" s="16" t="str">
+      <x:c r="K66" s="16" t="str">
         <x:v>否；安排笔试/面试</x:v>
       </x:c>
-      <x:c r="L65" s="16" t="str">
+      <x:c r="L66" s="16" t="str">
         <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
       </x:c>
-      <x:c r="M65" s="16" t="str">
+      <x:c r="M66" s="16" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N65" s="16" t="str">
+      <x:c r="N66" s="16" t="str">
         <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
       </x:c>
-      <x:c r="O65" s="17" t="str">
+      <x:c r="O66" s="17" t="str">
         <x:v>https://campus.hypergryph.com/</x:v>
       </x:c>
-      <x:c r="P65" s="14" t="str">
+      <x:c r="P66" s="14" t="str">
         <x:v>A-官方来源公告已核验</x:v>
       </x:c>
-      <x:c r="Q65" s="16" t="str">
+      <x:c r="Q66" s="16" t="str">
         <x:v>2026-08-03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" ht="54" customHeight="1">
-      <x:c r="A66" s="4" t="str">
-        <x:v>2026-07-16</x:v>
-      </x:c>
-      <x:c r="B66" s="4" t="str">
-        <x:v>联发科技</x:v>
-      </x:c>
-      <x:c r="C66" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
-      </x:c>
-      <x:c r="D66" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E66" s="4" t="str">
-        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
-      </x:c>
-      <x:c r="F66" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G66" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H66" s="4" t="str">
-        <x:v>软件类、通信类、IC类</x:v>
-      </x:c>
-      <x:c r="I66" s="15" t="str">
-        <x:v>https://mediatek.zhiye.com/</x:v>
-      </x:c>
-      <x:c r="J66" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K66" s="4" t="str">
-        <x:v>否；明确安排7-8月笔试</x:v>
-      </x:c>
-      <x:c r="L66" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M66" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N66" s="4" t="str">
-        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
-      </x:c>
-      <x:c r="O66" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P66" s="14" t="str">
-        <x:v>A-官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q66" s="4" t="str">
-        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="54" customHeight="1">
@@ -3981,34 +3981,34 @@
         <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B67" s="4" t="str">
-        <x:v>DJI大疆</x:v>
+        <x:v>联发科技</x:v>
       </x:c>
       <x:c r="C67" s="4" t="str">
-        <x:v>无人机/智能硬件</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D67" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E67" s="4" t="str">
-        <x:v>深圳、东莞、上海、北京、西安等</x:v>
+        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
       </x:c>
       <x:c r="F67" s="4" t="str">
-        <x:v>正式批-拓疆者计划</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G67" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H67" s="4" t="str">
-        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
+        <x:v>软件类、通信类、IC类</x:v>
       </x:c>
       <x:c r="I67" s="15" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
+        <x:v>https://mediatek.zhiye.com/</x:v>
       </x:c>
       <x:c r="J67" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K67" s="4" t="str">
-        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
+        <x:v>否；明确安排7-8月笔试</x:v>
       </x:c>
       <x:c r="L67" s="4" t="str">
         <x:v>已核验开放</x:v>
@@ -4017,13 +4017,13 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N67" s="4" t="str">
-        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
+        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
       </x:c>
       <x:c r="O67" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P67" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
+        <x:v>A-官方招聘公告已核验</x:v>
       </x:c>
       <x:c r="Q67" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4031,46 +4031,46 @@
     </x:row>
     <x:row r="68" ht="54" customHeight="1">
       <x:c r="A68" s="4" t="str">
-        <x:v>2026-07-15</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B68" s="4" t="str">
-        <x:v>蔚来</x:v>
+        <x:v>DJI大疆</x:v>
       </x:c>
       <x:c r="C68" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>无人机/智能硬件</x:v>
       </x:c>
       <x:c r="D68" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E68" s="4" t="str">
-        <x:v>上海、合肥、北京、武汉、南京等</x:v>
+        <x:v>深圳、东莞、上海、北京、西安等</x:v>
       </x:c>
       <x:c r="F68" s="4" t="str">
-        <x:v>技术提前批</x:v>
+        <x:v>正式批-拓疆者计划</x:v>
       </x:c>
       <x:c r="G68" s="4" t="str">
-        <x:v>2024年9月-2027年8月毕业</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H68" s="4" t="str">
-        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
+        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
       </x:c>
       <x:c r="I68" s="15" t="str">
-        <x:v>https://campus.nio.com/</x:v>
+        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
       </x:c>
       <x:c r="J68" s="4" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K68" s="4" t="str">
-        <x:v>否；有笔试/测评</x:v>
+        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
       </x:c>
       <x:c r="L68" s="4" t="str">
         <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M68" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N68" s="4" t="str">
-        <x:v>最多同时申请3个岗位。</x:v>
+        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
       </x:c>
       <x:c r="O68" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -4084,108 +4084,108 @@
     </x:row>
     <x:row r="69" ht="54" customHeight="1">
       <x:c r="A69" s="4" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="B69" s="4" t="str">
-        <x:v>北方华创</x:v>
+        <x:v>蔚来</x:v>
       </x:c>
       <x:c r="C69" s="4" t="str">
-        <x:v>半导体设备</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D69" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E69" s="4" t="str">
-        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
+        <x:v>上海、合肥、北京、武汉、南京等</x:v>
       </x:c>
       <x:c r="F69" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>技术提前批</x:v>
       </x:c>
       <x:c r="G69" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2024年9月-2027年8月毕业</x:v>
       </x:c>
       <x:c r="H69" s="4" t="str">
-        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
+        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
       </x:c>
       <x:c r="I69" s="15" t="str">
-        <x:v>https://career.naura.com/campus</x:v>
+        <x:v>https://campus.nio.com/</x:v>
       </x:c>
       <x:c r="J69" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K69" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；有笔试/测评</x:v>
       </x:c>
       <x:c r="L69" s="4" t="str">
-        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M69" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N69" s="4" t="str">
-        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
+        <x:v>最多同时申请3个岗位。</x:v>
       </x:c>
       <x:c r="O69" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P69" s="14" t="str">
-        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
+        <x:v>A-官方来源公告已核验</x:v>
       </x:c>
       <x:c r="Q69" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="54" customHeight="1">
       <x:c r="A70" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="B70" s="4" t="str">
-        <x:v>百度</x:v>
+        <x:v>北方华创</x:v>
       </x:c>
       <x:c r="C70" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>半导体设备</x:v>
       </x:c>
       <x:c r="D70" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E70" s="4" t="str">
-        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F70" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G70" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H70" s="4" t="str">
-        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
       </x:c>
       <x:c r="I70" s="15" t="str">
-        <x:v>https://talent.baidu.com/jobs</x:v>
+        <x:v>https://career.naura.com/campus</x:v>
       </x:c>
       <x:c r="J70" s="4" t="str">
-        <x:v>2027-06-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K70" s="4" t="str">
-        <x:v>部分免；并非所有候选人参加笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L70" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
       </x:c>
       <x:c r="M70" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N70" s="4" t="str">
-        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
+        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
       </x:c>
       <x:c r="O70" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
       </x:c>
       <x:c r="P70" s="14" t="str">
-        <x:v>A-官方招聘日历/官方来源已核验</x:v>
+        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
       </x:c>
       <x:c r="Q70" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="54" customHeight="1">
@@ -4193,102 +4193,102 @@
         <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B71" s="4" t="str">
-        <x:v>中国航天科工集团第六研究院</x:v>
+        <x:v>百度</x:v>
       </x:c>
       <x:c r="C71" s="4" t="str">
-        <x:v>航天/军工/动力系统</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D71" s="4" t="str">
-        <x:v>央企院所</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E71" s="4" t="str">
-        <x:v>呼和浩特及所属单位</x:v>
+        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
       </x:c>
       <x:c r="F71" s="4" t="str">
-        <x:v>提前批+暑期开放日</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G71" s="4" t="str">
-        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H71" s="4" t="str">
-        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
+        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
       </x:c>
       <x:c r="I71" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
+        <x:v>https://talent.baidu.com/jobs</x:v>
       </x:c>
       <x:c r="J71" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-30</x:v>
       </x:c>
       <x:c r="K71" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>部分免；并非所有候选人参加笔试</x:v>
       </x:c>
       <x:c r="L71" s="4" t="str">
-        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M71" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N71" s="4" t="str">
-        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
+        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
       </x:c>
       <x:c r="O71" s="15" t="str">
-        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
-      </x:c>
-      <x:c r="P71" s="18" t="str">
-        <x:v>B-高校就业网公开公告</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P71" s="14" t="str">
+        <x:v>A-官方招聘日历/官方来源已核验</x:v>
       </x:c>
       <x:c r="Q71" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="54" customHeight="1">
       <x:c r="A72" s="4" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B72" s="4" t="str">
-        <x:v>思瑞浦</x:v>
+        <x:v>中国航天科工集团第六研究院</x:v>
       </x:c>
       <x:c r="C72" s="4" t="str">
-        <x:v>半导体/模拟IC</x:v>
+        <x:v>航天/军工/动力系统</x:v>
       </x:c>
       <x:c r="D72" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企院所</x:v>
       </x:c>
       <x:c r="E72" s="4" t="str">
-        <x:v>上海、深圳等，以岗位页为准</x:v>
+        <x:v>呼和浩特及所属单位</x:v>
       </x:c>
       <x:c r="F72" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批+暑期开放日</x:v>
       </x:c>
       <x:c r="G72" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
       </x:c>
       <x:c r="H72" s="4" t="str">
-        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
+        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
       </x:c>
       <x:c r="I72" s="15" t="str">
-        <x:v>https://www.3peak.cn/careers</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
       <x:c r="J72" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K72" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L72" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
+        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
       </x:c>
       <x:c r="M72" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N72" s="4" t="str">
-        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
+        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
       </x:c>
       <x:c r="O72" s="15" t="str">
-        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
+        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
       </x:c>
       <x:c r="P72" s="18" t="str">
-        <x:v>B-招聘平台/高校就业转载</x:v>
+        <x:v>B-高校就业网公开公告</x:v>
       </x:c>
       <x:c r="Q72" s="4" t="str">
         <x:v>2026-07-27</x:v>
@@ -4296,178 +4296,178 @@
     </x:row>
     <x:row r="73" ht="54" customHeight="1">
       <x:c r="A73" s="4" t="str">
-        <x:v>不晚于2026-07-07</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="B73" s="4" t="str">
-        <x:v>文远知行WeRide</x:v>
+        <x:v>思瑞浦</x:v>
       </x:c>
       <x:c r="C73" s="4" t="str">
-        <x:v>自动驾驶/人工智能</x:v>
+        <x:v>半导体/模拟IC</x:v>
       </x:c>
       <x:c r="D73" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E73" s="4" t="str">
+        <x:v>上海、深圳等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F73" s="4" t="str">
+        <x:v>正式批/校园招聘</x:v>
+      </x:c>
+      <x:c r="G73" s="4" t="str">
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H73" s="4" t="str">
+        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
+      </x:c>
+      <x:c r="I73" s="15" t="str">
+        <x:v>https://www.3peak.cn/careers</x:v>
+      </x:c>
+      <x:c r="J73" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K73" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L73" s="4" t="str">
+        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
+      </x:c>
+      <x:c r="M73" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N73" s="4" t="str">
+        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
+      </x:c>
+      <x:c r="O73" s="15" t="str">
+        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
+      </x:c>
+      <x:c r="P73" s="18" t="str">
+        <x:v>B-招聘平台/高校就业转载</x:v>
+      </x:c>
+      <x:c r="Q73" s="4" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="54" customHeight="1">
+      <x:c r="A74" s="4" t="str">
+        <x:v>不晚于2026-07-07</x:v>
+      </x:c>
+      <x:c r="B74" s="4" t="str">
+        <x:v>文远知行WeRide</x:v>
+      </x:c>
+      <x:c r="C74" s="4" t="str">
+        <x:v>自动驾驶/人工智能</x:v>
+      </x:c>
+      <x:c r="D74" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E74" s="4" t="str">
         <x:v>广州、深圳、武汉等，以岗位页为准</x:v>
       </x:c>
-      <x:c r="F73" s="4" t="str">
+      <x:c r="F74" s="4" t="str">
         <x:v>正式批/校招/可转正实习</x:v>
       </x:c>
-      <x:c r="G73" s="4" t="str">
+      <x:c r="G74" s="4" t="str">
         <x:v>2027届应届毕业生及可转正实习生，以岗位要求为准</x:v>
       </x:c>
-      <x:c r="H73" s="4" t="str">
+      <x:c r="H74" s="4" t="str">
         <x:v>感知/预测/规划控制算法、算法测试、测试开发、SRE、云与车端安全、AI Infra、仿真平台等</x:v>
       </x:c>
-      <x:c r="I73" s="15" t="str">
+      <x:c r="I74" s="15" t="str">
         <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
       </x:c>
-      <x:c r="J73" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K73" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L73" s="4" t="str">
+      <x:c r="J74" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K74" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L74" s="4" t="str">
         <x:v>企业官方校招系统在招；已核验137个职位</x:v>
       </x:c>
-      <x:c r="M73" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N73" s="4" t="str">
+      <x:c r="M74" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N74" s="4" t="str">
         <x:v>官方列表显示2027届校招职位最早发布于7月7日；部分岗位为可转正实习，城市和岗位随招聘系统实时调整。</x:v>
       </x:c>
-      <x:c r="O73" s="15" t="str">
+      <x:c r="O74" s="15" t="str">
         <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
       </x:c>
-      <x:c r="P73" s="14" t="str">
+      <x:c r="P74" s="14" t="str">
         <x:v>A-企业官方校招系统与职位列表已核验</x:v>
       </x:c>
-      <x:c r="Q73" s="4" t="str">
+      <x:c r="Q74" s="4" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="54" customHeight="1">
-      <x:c r="A74" s="16" t="str">
+    <x:row r="75" ht="54" customHeight="1">
+      <x:c r="A75" s="16" t="str">
         <x:v>2026-07-06</x:v>
       </x:c>
-      <x:c r="B74" s="16" t="str">
+      <x:c r="B75" s="16" t="str">
         <x:v>米哈游</x:v>
       </x:c>
-      <x:c r="C74" s="16" t="str">
+      <x:c r="C75" s="16" t="str">
         <x:v>游戏/互联网</x:v>
       </x:c>
-      <x:c r="D74" s="16" t="str">
+      <x:c r="D75" s="16" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E74" s="16" t="str">
+      <x:c r="E75" s="16" t="str">
         <x:v>上海、北京</x:v>
       </x:c>
-      <x:c r="F74" s="16" t="str">
+      <x:c r="F75" s="16" t="str">
         <x:v>技术提前批</x:v>
       </x:c>
-      <x:c r="G74" s="16" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H74" s="16" t="str">
+      <x:c r="G75" s="16" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H75" s="16" t="str">
         <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
       </x:c>
-      <x:c r="I74" s="17" t="str">
+      <x:c r="I75" s="17" t="str">
         <x:v>https://campus.mihoyo.com/</x:v>
       </x:c>
-      <x:c r="J74" s="16" t="str">
+      <x:c r="J75" s="16" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
-      <x:c r="K74" s="16" t="str">
+      <x:c r="K75" s="16" t="str">
         <x:v>有免笔试直通面试机会</x:v>
       </x:c>
-      <x:c r="L74" s="16" t="str">
+      <x:c r="L75" s="16" t="str">
         <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
       </x:c>
-      <x:c r="M74" s="16" t="str">
+      <x:c r="M75" s="16" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N74" s="16" t="str">
+      <x:c r="N75" s="16" t="str">
         <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
       </x:c>
-      <x:c r="O74" s="17" t="str">
+      <x:c r="O75" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P74" s="14" t="str">
+      <x:c r="P75" s="14" t="str">
         <x:v>A-官方招聘公告已核验</x:v>
       </x:c>
-      <x:c r="Q74" s="16" t="str">
+      <x:c r="Q75" s="16" t="str">
         <x:v>2026-07-30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" ht="54" customHeight="1">
-      <x:c r="A75" s="4" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="B75" s="4" t="str">
-        <x:v>京东方-先锋京英计划</x:v>
-      </x:c>
-      <x:c r="C75" s="4" t="str">
-        <x:v>显示技术/半导体/物联网</x:v>
-      </x:c>
-      <x:c r="D75" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E75" s="4" t="str">
-        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
-      </x:c>
-      <x:c r="F75" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G75" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H75" s="4" t="str">
-        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
-      </x:c>
-      <x:c r="I75" s="15" t="str">
-        <x:v>https://campus.boe.com/</x:v>
-      </x:c>
-      <x:c r="J75" s="4" t="str">
-        <x:v>2026-08-14</x:v>
-      </x:c>
-      <x:c r="K75" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L75" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M75" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N75" s="4" t="str">
-        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
-      </x:c>
-      <x:c r="O75" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P75" s="14" t="str">
-        <x:v>A-国家大学生就业平台公告已核验</x:v>
-      </x:c>
-      <x:c r="Q75" s="4" t="str">
-        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="54" customHeight="1">
       <x:c r="A76" s="4" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="B76" s="4" t="str">
-        <x:v>中国航天科技集团</x:v>
+        <x:v>京东方-先锋京英计划</x:v>
       </x:c>
       <x:c r="C76" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>显示技术/半导体/物联网</x:v>
       </x:c>
       <x:c r="D76" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E76" s="4" t="str">
-        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
+        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
       </x:c>
       <x:c r="F76" s="4" t="str">
         <x:v>提前批</x:v>
@@ -4476,31 +4476,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H76" s="4" t="str">
-        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
+        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
       </x:c>
       <x:c r="I76" s="15" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
+        <x:v>https://campus.boe.com/</x:v>
       </x:c>
       <x:c r="J76" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K76" s="4" t="str">
-        <x:v>各院所自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L76" s="4" t="str">
-        <x:v>官方公告已确认启动</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M76" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N76" s="4" t="str">
-        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
+        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
       </x:c>
       <x:c r="O76" s="15" t="str">
-        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P76" s="14" t="str">
-        <x:v>A-国务院国资委/集团官方来源</x:v>
+        <x:v>A-国家大学生就业平台公告已核验</x:v>
       </x:c>
       <x:c r="Q76" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4508,52 +4508,52 @@
     </x:row>
     <x:row r="77" ht="54" customHeight="1">
       <x:c r="A77" s="4" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="B77" s="4" t="str">
-        <x:v>高途</x:v>
+        <x:v>中国航天科技集团</x:v>
       </x:c>
       <x:c r="C77" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D77" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E77" s="4" t="str">
-        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
+        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
       </x:c>
       <x:c r="F77" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G77" s="4" t="str">
-        <x:v>27届为主，优秀28届也可投</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H77" s="4" t="str">
-        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
+        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
       </x:c>
       <x:c r="I77" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J77" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K77" s="4" t="str">
-        <x:v>否；流程包含笔试</x:v>
+        <x:v>各院所自行组织，未统一</x:v>
       </x:c>
       <x:c r="L77" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>官方公告已确认启动</x:v>
       </x:c>
       <x:c r="M77" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N77" s="4" t="str">
-        <x:v>滚动发放Offer，截止时间未公布。</x:v>
+        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
       </x:c>
       <x:c r="O77" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
       </x:c>
       <x:c r="P77" s="14" t="str">
-        <x:v>A-官方投递平台已核验</x:v>
+        <x:v>A-国务院国资委/集团官方来源</x:v>
       </x:c>
       <x:c r="Q77" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4561,52 +4561,52 @@
     </x:row>
     <x:row r="78" ht="54" customHeight="1">
       <x:c r="A78" s="4" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="B78" s="4" t="str">
-        <x:v>中汽中心</x:v>
+        <x:v>高途</x:v>
       </x:c>
       <x:c r="C78" s="4" t="str">
-        <x:v>汽车检测/科研</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D78" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E78" s="4" t="str">
-        <x:v>天津、武汉、北京、上海等</x:v>
+        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
       </x:c>
       <x:c r="F78" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G78" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>27届为主，优秀28届也可投</x:v>
       </x:c>
       <x:c r="H78" s="4" t="str">
-        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
+        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
       </x:c>
       <x:c r="I78" s="15" t="str">
-        <x:v>https://www.catarc.ac.cn/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
       </x:c>
       <x:c r="J78" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K78" s="4" t="str">
-        <x:v>官方未统一说明</x:v>
+        <x:v>否；流程包含笔试</x:v>
       </x:c>
       <x:c r="L78" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M78" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N78" s="4" t="str">
-        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
+        <x:v>滚动发放Offer，截止时间未公布。</x:v>
       </x:c>
       <x:c r="O78" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
-      </x:c>
-      <x:c r="P78" s="18" t="str">
-        <x:v>B-公开招聘公告</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P78" s="14" t="str">
+        <x:v>A-官方投递平台已核验</x:v>
       </x:c>
       <x:c r="Q78" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4614,140 +4614,140 @@
     </x:row>
     <x:row r="79" ht="54" customHeight="1">
       <x:c r="A79" s="4" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="B79" s="4" t="str">
-        <x:v>中国航天科工集团</x:v>
+        <x:v>中汽中心</x:v>
       </x:c>
       <x:c r="C79" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>汽车检测/科研</x:v>
       </x:c>
       <x:c r="D79" s="4" t="str">
         <x:v>央企</x:v>
       </x:c>
       <x:c r="E79" s="4" t="str">
-        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
+        <x:v>天津、武汉、北京、上海等</x:v>
       </x:c>
       <x:c r="F79" s="4" t="str">
-        <x:v>正式批/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G79" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H79" s="4" t="str">
-        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
+        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
       </x:c>
       <x:c r="I79" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
+        <x:v>https://www.catarc.ac.cn/</x:v>
       </x:c>
       <x:c r="J79" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K79" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L79" s="4" t="str">
-        <x:v>官网公告已确认启动</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M79" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N79" s="4" t="str">
-        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
+        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
       </x:c>
       <x:c r="O79" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
-      </x:c>
-      <x:c r="P79" s="14" t="str">
-        <x:v>A-集团官网公告已核验</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
+      </x:c>
+      <x:c r="P79" s="18" t="str">
+        <x:v>B-公开招聘公告</x:v>
       </x:c>
       <x:c r="Q79" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="54" customHeight="1">
       <x:c r="A80" s="4" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="B80" s="4" t="str">
-        <x:v>禾赛科技</x:v>
+        <x:v>中国航天科工集团</x:v>
       </x:c>
       <x:c r="C80" s="4" t="str">
-        <x:v>激光雷达/机器人</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D80" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E80" s="4" t="str">
-        <x:v>上海、杭州</x:v>
+        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
       </x:c>
       <x:c r="F80" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/提前批</x:v>
       </x:c>
       <x:c r="G80" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H80" s="4" t="str">
-        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
+        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
       </x:c>
       <x:c r="I80" s="15" t="str">
-        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
       <x:c r="J80" s="4" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K80" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L80" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>官网公告已确认启动</x:v>
       </x:c>
       <x:c r="M80" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N80" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
       </x:c>
       <x:c r="O80" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P80" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
+      </x:c>
+      <x:c r="P80" s="14" t="str">
+        <x:v>A-集团官网公告已核验</x:v>
       </x:c>
       <x:c r="Q80" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="54" customHeight="1">
       <x:c r="A81" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="B81" s="4" t="str">
-        <x:v>北京国望光学科技有限公司</x:v>
+        <x:v>禾赛科技</x:v>
       </x:c>
       <x:c r="C81" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>激光雷达/机器人</x:v>
       </x:c>
       <x:c r="D81" s="4" t="str">
-        <x:v>央国企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E81" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>上海、杭州</x:v>
       </x:c>
       <x:c r="F81" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G81" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H81" s="4" t="str">
-        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
-      </x:c>
-      <x:c r="I81" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
+      </x:c>
+      <x:c r="I81" s="15" t="str">
+        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
       </x:c>
       <x:c r="J81" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="K81" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -4756,7 +4756,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M81" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N81" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -4776,25 +4776,25 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B82" s="4" t="str">
-        <x:v>乐读</x:v>
+        <x:v>北京国望光学科技有限公司</x:v>
       </x:c>
       <x:c r="C82" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D82" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央国企</x:v>
       </x:c>
       <x:c r="E82" s="4" t="str">
-        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F82" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G82" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H82" s="4" t="str">
-        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
+        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
       </x:c>
       <x:c r="I82" s="22" t="str">
         <x:v>官方入口待核验</x:v>
@@ -4806,19 +4806,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L82" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M82" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N82" s="4" t="str">
-        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O82" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P82" s="18" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q82" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4829,16 +4829,16 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B83" s="4" t="str">
-        <x:v>龙蟠科技</x:v>
+        <x:v>乐读</x:v>
       </x:c>
       <x:c r="C83" s="4" t="str">
-        <x:v>新能源材料/化工</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D83" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E83" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
       </x:c>
       <x:c r="F83" s="4" t="str">
         <x:v>提前批</x:v>
@@ -4847,31 +4847,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H83" s="4" t="str">
-        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
-      </x:c>
-      <x:c r="I83" s="15" t="str">
-        <x:v>https://www.lopal.com.cn/join</x:v>
+        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
+      </x:c>
+      <x:c r="I83" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J83" s="4" t="str">
-        <x:v>2027-06-01</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K83" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L83" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M83" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N83" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
       </x:c>
       <x:c r="O83" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P83" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>B-招聘平台公开汇总</x:v>
       </x:c>
       <x:c r="Q83" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4882,16 +4882,16 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B84" s="4" t="str">
-        <x:v>牧原</x:v>
+        <x:v>龙蟠科技</x:v>
       </x:c>
       <x:c r="C84" s="4" t="str">
-        <x:v>农业/食品/智能养殖</x:v>
+        <x:v>新能源材料/化工</x:v>
       </x:c>
       <x:c r="D84" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E84" s="4" t="str">
-        <x:v>河南南阳及全国</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F84" s="4" t="str">
         <x:v>提前批</x:v>
@@ -4900,13 +4900,13 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H84" s="4" t="str">
-        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
+        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
       </x:c>
       <x:c r="I84" s="15" t="str">
-        <x:v>https://job.muyuanfoods.com/</x:v>
+        <x:v>https://www.lopal.com.cn/join</x:v>
       </x:c>
       <x:c r="J84" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-01</x:v>
       </x:c>
       <x:c r="K84" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -4915,7 +4915,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M84" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N84" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -4935,28 +4935,28 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B85" s="4" t="str">
-        <x:v>三一集团-小语种校招</x:v>
+        <x:v>牧原</x:v>
       </x:c>
       <x:c r="C85" s="4" t="str">
-        <x:v>工程机械/制造</x:v>
+        <x:v>农业/食品/智能养殖</x:v>
       </x:c>
       <x:c r="D85" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E85" s="4" t="str">
-        <x:v>海外多国</x:v>
+        <x:v>河南南阳及全国</x:v>
       </x:c>
       <x:c r="F85" s="4" t="str">
-        <x:v>小语种专项/正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G85" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H85" s="4" t="str">
-        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
+        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
       </x:c>
       <x:c r="I85" s="15" t="str">
-        <x:v>https://sanycampus.zhiye.com/</x:v>
+        <x:v>https://job.muyuanfoods.com/</x:v>
       </x:c>
       <x:c r="J85" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4988,28 +4988,28 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B86" s="4" t="str">
-        <x:v>上海电气-暑期精英训练营</x:v>
+        <x:v>三一集团-小语种校招</x:v>
       </x:c>
       <x:c r="C86" s="4" t="str">
-        <x:v>高端装备/能源</x:v>
+        <x:v>工程机械/制造</x:v>
       </x:c>
       <x:c r="D86" s="4" t="str">
-        <x:v>地方国企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E86" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>海外多国</x:v>
       </x:c>
       <x:c r="F86" s="4" t="str">
-        <x:v>训练营/秋招直通</x:v>
+        <x:v>小语种专项/正式批</x:v>
       </x:c>
       <x:c r="G86" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H86" s="4" t="str">
-        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
+        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
       </x:c>
       <x:c r="I86" s="15" t="str">
-        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
+        <x:v>https://sanycampus.zhiye.com/</x:v>
       </x:c>
       <x:c r="J86" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5041,28 +5041,28 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B87" s="4" t="str">
-        <x:v>vivo-蓝极星计划</x:v>
+        <x:v>上海电气-暑期精英训练营</x:v>
       </x:c>
       <x:c r="C87" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>高端装备/能源</x:v>
       </x:c>
       <x:c r="D87" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>地方国企</x:v>
       </x:c>
       <x:c r="E87" s="4" t="str">
-        <x:v>深圳、杭州、东莞、上海</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F87" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>训练营/秋招直通</x:v>
       </x:c>
       <x:c r="G87" s="4" t="str">
-        <x:v>博士为主</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H87" s="4" t="str">
-        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
+        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
       </x:c>
       <x:c r="I87" s="15" t="str">
-        <x:v>https://hr.vivo.com/</x:v>
+        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
       </x:c>
       <x:c r="J87" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5071,19 +5071,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L87" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M87" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N87" s="4" t="str">
-        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O87" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P87" s="18" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q87" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5091,31 +5091,31 @@
     </x:row>
     <x:row r="88" ht="54" customHeight="1">
       <x:c r="A88" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B88" s="4" t="str">
-        <x:v>澜起科技</x:v>
+        <x:v>vivo-蓝极星计划</x:v>
       </x:c>
       <x:c r="C88" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D88" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E88" s="4" t="str">
-        <x:v>昆山、西安、南京</x:v>
+        <x:v>深圳、杭州、东莞、上海</x:v>
       </x:c>
       <x:c r="F88" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G88" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>博士为主</x:v>
       </x:c>
       <x:c r="H88" s="4" t="str">
-        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
+        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
       </x:c>
       <x:c r="I88" s="15" t="str">
-        <x:v>https://www.montage-tech.com/cn/careers</x:v>
+        <x:v>https://hr.vivo.com/</x:v>
       </x:c>
       <x:c r="J88" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5124,19 +5124,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L88" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M88" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N88" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
       </x:c>
       <x:c r="O88" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P88" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>B-招聘平台公开汇总</x:v>
       </x:c>
       <x:c r="Q88" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5147,16 +5147,16 @@
         <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B89" s="4" t="str">
-        <x:v>上海宇量昇</x:v>
+        <x:v>澜起科技</x:v>
       </x:c>
       <x:c r="C89" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D89" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E89" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>昆山、西安、南京</x:v>
       </x:c>
       <x:c r="F89" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5165,10 +5165,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H89" s="4" t="str">
-        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
+        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
       </x:c>
       <x:c r="I89" s="15" t="str">
-        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
+        <x:v>https://www.montage-tech.com/cn/careers</x:v>
       </x:c>
       <x:c r="J89" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5200,16 +5200,16 @@
         <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B90" s="4" t="str">
-        <x:v>是为科技</x:v>
+        <x:v>上海宇量昇</x:v>
       </x:c>
       <x:c r="C90" s="4" t="str">
-        <x:v>新能源/智能制造</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D90" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E90" s="4" t="str">
-        <x:v>南京、上海、常州</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F90" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5218,10 +5218,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H90" s="4" t="str">
-        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
+        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
       </x:c>
       <x:c r="I90" s="15" t="str">
-        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
+        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
       </x:c>
       <x:c r="J90" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5253,16 +5253,16 @@
         <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B91" s="4" t="str">
-        <x:v>游族网络</x:v>
+        <x:v>是为科技</x:v>
       </x:c>
       <x:c r="C91" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>新能源/智能制造</x:v>
       </x:c>
       <x:c r="D91" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E91" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>南京、上海、常州</x:v>
       </x:c>
       <x:c r="F91" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5271,10 +5271,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H91" s="4" t="str">
-        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
+        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
       </x:c>
       <x:c r="I91" s="15" t="str">
-        <x:v>https://job.youzu.com/</x:v>
+        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
       </x:c>
       <x:c r="J91" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5303,19 +5303,19 @@
     </x:row>
     <x:row r="92" ht="54" customHeight="1">
       <x:c r="A92" s="4" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B92" s="4" t="str">
-        <x:v>中铁设计</x:v>
+        <x:v>游族网络</x:v>
       </x:c>
       <x:c r="C92" s="4" t="str">
-        <x:v>轨道交通/工程设计</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D92" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E92" s="4" t="str">
-        <x:v>北京、济南、郑州、太原</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F92" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5324,10 +5324,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H92" s="4" t="str">
-        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
+        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
       </x:c>
       <x:c r="I92" s="15" t="str">
-        <x:v>https://www.crdc.com/</x:v>
+        <x:v>https://job.youzu.com/</x:v>
       </x:c>
       <x:c r="J92" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5356,31 +5356,31 @@
     </x:row>
     <x:row r="93" ht="54" customHeight="1">
       <x:c r="A93" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="B93" s="4" t="str">
-        <x:v>迈安德集团-校园大使</x:v>
+        <x:v>中铁设计</x:v>
       </x:c>
       <x:c r="C93" s="4" t="str">
-        <x:v>粮油工程/装备</x:v>
+        <x:v>轨道交通/工程设计</x:v>
       </x:c>
       <x:c r="D93" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E93" s="4" t="str">
-        <x:v>扬州/高校</x:v>
+        <x:v>北京、济南、郑州、太原</x:v>
       </x:c>
       <x:c r="F93" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G93" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H93" s="4" t="str">
-        <x:v>校园大使</x:v>
+        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
       </x:c>
       <x:c r="I93" s="15" t="str">
-        <x:v>https://www.myande.com/</x:v>
+        <x:v>https://www.crdc.com/</x:v>
       </x:c>
       <x:c r="J93" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5412,28 +5412,28 @@
         <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B94" s="4" t="str">
-        <x:v>迅仿科技</x:v>
+        <x:v>迈安德集团-校园大使</x:v>
       </x:c>
       <x:c r="C94" s="4" t="str">
-        <x:v>工业软件/仿真</x:v>
+        <x:v>粮油工程/装备</x:v>
       </x:c>
       <x:c r="D94" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E94" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>扬州/高校</x:v>
       </x:c>
       <x:c r="F94" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G94" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H94" s="4" t="str">
-        <x:v>仿真工程师</x:v>
-      </x:c>
-      <x:c r="I94" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>校园大使</x:v>
+      </x:c>
+      <x:c r="I94" s="15" t="str">
+        <x:v>https://www.myande.com/</x:v>
       </x:c>
       <x:c r="J94" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5462,34 +5462,34 @@
     </x:row>
     <x:row r="95" ht="54" customHeight="1">
       <x:c r="A95" s="4" t="str">
-        <x:v>2026-06-12</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B95" s="4" t="str">
-        <x:v>MOVA</x:v>
+        <x:v>迅仿科技</x:v>
       </x:c>
       <x:c r="C95" s="4" t="str">
-        <x:v>智能家电/机器人</x:v>
+        <x:v>工业软件/仿真</x:v>
       </x:c>
       <x:c r="D95" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E95" s="4" t="str">
-        <x:v>苏州及全国</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F95" s="4" t="str">
-        <x:v>全球校招/正式批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G95" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H95" s="4" t="str">
-        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
-      </x:c>
-      <x:c r="I95" s="15" t="str">
-        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+        <x:v>仿真工程师</x:v>
+      </x:c>
+      <x:c r="I95" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J95" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K95" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -5498,7 +5498,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M95" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N95" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -5515,34 +5515,34 @@
     </x:row>
     <x:row r="96" ht="54" customHeight="1">
       <x:c r="A96" s="4" t="str">
-        <x:v>2026-06-11</x:v>
+        <x:v>2026-06-12</x:v>
       </x:c>
       <x:c r="B96" s="4" t="str">
-        <x:v>财通证券</x:v>
+        <x:v>MOVA</x:v>
       </x:c>
       <x:c r="C96" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>智能家电/机器人</x:v>
       </x:c>
       <x:c r="D96" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E96" s="4" t="str">
-        <x:v>杭州、上海、深圳、北京</x:v>
+        <x:v>苏州及全国</x:v>
       </x:c>
       <x:c r="F96" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>全球校招/正式批</x:v>
       </x:c>
       <x:c r="G96" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H96" s="4" t="str">
-        <x:v>总部、参股公司、分公司岗位</x:v>
+        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
       </x:c>
       <x:c r="I96" s="15" t="str">
-        <x:v>https://www.ctsec.com/joinUs</x:v>
+        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
       </x:c>
       <x:c r="J96" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K96" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -5551,7 +5551,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M96" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N96" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -5568,31 +5568,31 @@
     </x:row>
     <x:row r="97" ht="54" customHeight="1">
       <x:c r="A97" s="4" t="str">
-        <x:v>2026-06-10</x:v>
+        <x:v>2026-06-11</x:v>
       </x:c>
       <x:c r="B97" s="4" t="str">
-        <x:v>歌尔股份</x:v>
+        <x:v>财通证券</x:v>
       </x:c>
       <x:c r="C97" s="4" t="str">
-        <x:v>消费电子/智能硬件</x:v>
+        <x:v>证券/金融</x:v>
       </x:c>
       <x:c r="D97" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E97" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>杭州、上海、深圳、北京</x:v>
       </x:c>
       <x:c r="F97" s="4" t="str">
-        <x:v>实习/校招储备</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G97" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H97" s="4" t="str">
-        <x:v>法务助理</x:v>
+        <x:v>总部、参股公司、分公司岗位</x:v>
       </x:c>
       <x:c r="I97" s="15" t="str">
-        <x:v>https://career.goertek.com/</x:v>
+        <x:v>https://www.ctsec.com/joinUs</x:v>
       </x:c>
       <x:c r="J97" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5621,31 +5621,31 @@
     </x:row>
     <x:row r="98" ht="54" customHeight="1">
       <x:c r="A98" s="4" t="str">
-        <x:v>2026-06-09</x:v>
+        <x:v>2026-06-10</x:v>
       </x:c>
       <x:c r="B98" s="4" t="str">
-        <x:v>深信服-校园大使</x:v>
+        <x:v>歌尔股份</x:v>
       </x:c>
       <x:c r="C98" s="4" t="str">
-        <x:v>网络安全/云计算</x:v>
+        <x:v>消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D98" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E98" s="4" t="str">
-        <x:v>西安</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F98" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>实习/校招储备</x:v>
       </x:c>
       <x:c r="G98" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H98" s="4" t="str">
-        <x:v>校园大使</x:v>
+        <x:v>法务助理</x:v>
       </x:c>
       <x:c r="I98" s="15" t="str">
-        <x:v>https://hr.sangfor.com/</x:v>
+        <x:v>https://career.goertek.com/</x:v>
       </x:c>
       <x:c r="J98" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5674,31 +5674,31 @@
     </x:row>
     <x:row r="99" ht="54" customHeight="1">
       <x:c r="A99" s="4" t="str">
-        <x:v>2026-06-08</x:v>
+        <x:v>2026-06-09</x:v>
       </x:c>
       <x:c r="B99" s="4" t="str">
-        <x:v>晓禾教育</x:v>
+        <x:v>深信服-校园大使</x:v>
       </x:c>
       <x:c r="C99" s="4" t="str">
-        <x:v>教育</x:v>
+        <x:v>网络安全/云计算</x:v>
       </x:c>
       <x:c r="D99" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E99" s="4" t="str">
-        <x:v>武汉、郑州、襄阳、宜昌</x:v>
+        <x:v>西安</x:v>
       </x:c>
       <x:c r="F99" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G99" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H99" s="4" t="str">
-        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
-      </x:c>
-      <x:c r="I99" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>校园大使</x:v>
+      </x:c>
+      <x:c r="I99" s="15" t="str">
+        <x:v>https://hr.sangfor.com/</x:v>
       </x:c>
       <x:c r="J99" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5727,31 +5727,31 @@
     </x:row>
     <x:row r="100" ht="54" customHeight="1">
       <x:c r="A100" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-08</x:v>
       </x:c>
       <x:c r="B100" s="4" t="str">
-        <x:v>晖致医药</x:v>
+        <x:v>晓禾教育</x:v>
       </x:c>
       <x:c r="C100" s="4" t="str">
-        <x:v>医药</x:v>
+        <x:v>教育</x:v>
       </x:c>
       <x:c r="D100" s="4" t="str">
-        <x:v>外资</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E100" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>武汉、郑州、襄阳、宜昌</x:v>
       </x:c>
       <x:c r="F100" s="4" t="str">
-        <x:v>实习储备正式岗</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G100" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H100" s="4" t="str">
-        <x:v>医学信息沟通实习生</x:v>
-      </x:c>
-      <x:c r="I100" s="15" t="str">
-        <x:v>https://careers.viatris.com/</x:v>
+        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
+      </x:c>
+      <x:c r="I100" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J100" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5783,28 +5783,28 @@
         <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="B101" s="4" t="str">
-        <x:v>苏州鸿凌达电子</x:v>
+        <x:v>晖致医药</x:v>
       </x:c>
       <x:c r="C101" s="4" t="str">
-        <x:v>电子制造</x:v>
+        <x:v>医药</x:v>
       </x:c>
       <x:c r="D101" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>外资</x:v>
       </x:c>
       <x:c r="E101" s="4" t="str">
-        <x:v>苏州</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F101" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>实习储备正式岗</x:v>
       </x:c>
       <x:c r="G101" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H101" s="4" t="str">
-        <x:v>财务助理</x:v>
+        <x:v>医学信息沟通实习生</x:v>
       </x:c>
       <x:c r="I101" s="15" t="str">
-        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
+        <x:v>https://careers.viatris.com/</x:v>
       </x:c>
       <x:c r="J101" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5833,19 +5833,19 @@
     </x:row>
     <x:row r="102" ht="54" customHeight="1">
       <x:c r="A102" s="4" t="str">
-        <x:v>2026-06-02</x:v>
+        <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="B102" s="4" t="str">
-        <x:v>万得信息</x:v>
+        <x:v>苏州鸿凌达电子</x:v>
       </x:c>
       <x:c r="C102" s="4" t="str">
-        <x:v>金融数据/软件</x:v>
+        <x:v>电子制造</x:v>
       </x:c>
       <x:c r="D102" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E102" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>苏州</x:v>
       </x:c>
       <x:c r="F102" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5854,10 +5854,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H102" s="4" t="str">
-        <x:v>AI算法工程师等</x:v>
+        <x:v>财务助理</x:v>
       </x:c>
       <x:c r="I102" s="15" t="str">
-        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
+        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
       </x:c>
       <x:c r="J102" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5886,31 +5886,31 @@
     </x:row>
     <x:row r="103" ht="54" customHeight="1">
       <x:c r="A103" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-02</x:v>
       </x:c>
       <x:c r="B103" s="4" t="str">
-        <x:v>淘大集供应链</x:v>
+        <x:v>万得信息</x:v>
       </x:c>
       <x:c r="C103" s="4" t="str">
-        <x:v>零售/供应链</x:v>
+        <x:v>金融数据/软件</x:v>
       </x:c>
       <x:c r="D103" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E103" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F103" s="4" t="str">
-        <x:v>管培/实习</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G103" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H103" s="4" t="str">
-        <x:v>巡店管培生、实习生</x:v>
-      </x:c>
-      <x:c r="I103" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>AI算法工程师等</x:v>
+      </x:c>
+      <x:c r="I103" s="15" t="str">
+        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
       </x:c>
       <x:c r="J103" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5942,10 +5942,10 @@
         <x:v>2026-06-01</x:v>
       </x:c>
       <x:c r="B104" s="4" t="str">
-        <x:v>友芝友实业集团</x:v>
+        <x:v>淘大集供应链</x:v>
       </x:c>
       <x:c r="C104" s="4" t="str">
-        <x:v>综合实业</x:v>
+        <x:v>零售/供应链</x:v>
       </x:c>
       <x:c r="D104" s="4" t="str">
         <x:v>民营</x:v>
@@ -5954,16 +5954,16 @@
         <x:v>武汉</x:v>
       </x:c>
       <x:c r="F104" s="4" t="str">
-        <x:v>管培生</x:v>
+        <x:v>管培/实习</x:v>
       </x:c>
       <x:c r="G104" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H104" s="4" t="str">
-        <x:v>青年领军人才管培生</x:v>
-      </x:c>
-      <x:c r="I104" s="15" t="str">
-        <x:v>https://www.yzyqh.com/jrwm</x:v>
+        <x:v>巡店管培生、实习生</x:v>
+      </x:c>
+      <x:c r="I104" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J104" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5992,31 +5992,31 @@
     </x:row>
     <x:row r="105" ht="54" customHeight="1">
       <x:c r="A105" s="4" t="str">
-        <x:v>2026-05-29</x:v>
+        <x:v>2026-06-01</x:v>
       </x:c>
       <x:c r="B105" s="4" t="str">
-        <x:v>银雁科技</x:v>
+        <x:v>友芝友实业集团</x:v>
       </x:c>
       <x:c r="C105" s="4" t="str">
-        <x:v>金融科技服务</x:v>
+        <x:v>综合实业</x:v>
       </x:c>
       <x:c r="D105" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E105" s="4" t="str">
-        <x:v>成都</x:v>
+        <x:v>武汉</x:v>
       </x:c>
       <x:c r="F105" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>管培生</x:v>
       </x:c>
       <x:c r="G105" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H105" s="4" t="str">
-        <x:v>人伤理赔</x:v>
+        <x:v>青年领军人才管培生</x:v>
       </x:c>
       <x:c r="I105" s="15" t="str">
-        <x:v>https://www.cfss.net.cn/</x:v>
+        <x:v>https://www.yzyqh.com/jrwm</x:v>
       </x:c>
       <x:c r="J105" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6045,19 +6045,19 @@
     </x:row>
     <x:row r="106" ht="54" customHeight="1">
       <x:c r="A106" s="4" t="str">
-        <x:v>2026-05-15</x:v>
+        <x:v>2026-05-29</x:v>
       </x:c>
       <x:c r="B106" s="4" t="str">
-        <x:v>知乎</x:v>
+        <x:v>银雁科技</x:v>
       </x:c>
       <x:c r="C106" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>金融科技服务</x:v>
       </x:c>
       <x:c r="D106" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E106" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>成都</x:v>
       </x:c>
       <x:c r="F106" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6066,10 +6066,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H106" s="4" t="str">
-        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
+        <x:v>人伤理赔</x:v>
       </x:c>
       <x:c r="I106" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
+        <x:v>https://www.cfss.net.cn/</x:v>
       </x:c>
       <x:c r="J106" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6098,31 +6098,31 @@
     </x:row>
     <x:row r="107" ht="54" customHeight="1">
       <x:c r="A107" s="4" t="str">
-        <x:v>2026-05-08</x:v>
+        <x:v>2026-05-15</x:v>
       </x:c>
       <x:c r="B107" s="4" t="str">
-        <x:v>招商银行长沙分行</x:v>
+        <x:v>知乎</x:v>
       </x:c>
       <x:c r="C107" s="4" t="str">
-        <x:v>银行/金融</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="D107" s="4" t="str">
-        <x:v>股份制银行</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E107" s="4" t="str">
-        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F107" s="4" t="str">
-        <x:v>暑期实习/秋招直通</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G107" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H107" s="4" t="str">
-        <x:v>2027暑期实习生</x:v>
+        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
       </x:c>
       <x:c r="I107" s="15" t="str">
-        <x:v>https://career.cmbchina.com/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
       </x:c>
       <x:c r="J107" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6151,31 +6151,31 @@
     </x:row>
     <x:row r="108" ht="54" customHeight="1">
       <x:c r="A108" s="4" t="str">
-        <x:v>2026-04-22</x:v>
+        <x:v>2026-05-08</x:v>
       </x:c>
       <x:c r="B108" s="4" t="str">
-        <x:v>华金证券</x:v>
+        <x:v>招商银行长沙分行</x:v>
       </x:c>
       <x:c r="C108" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>银行/金融</x:v>
       </x:c>
       <x:c r="D108" s="4" t="str">
-        <x:v>国企</x:v>
+        <x:v>股份制银行</x:v>
       </x:c>
       <x:c r="E108" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
       </x:c>
       <x:c r="F108" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>暑期实习/秋招直通</x:v>
       </x:c>
       <x:c r="G108" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H108" s="4" t="str">
-        <x:v>战略发展类</x:v>
+        <x:v>2027暑期实习生</x:v>
       </x:c>
       <x:c r="I108" s="15" t="str">
-        <x:v>https://www.huajinsc.cn/</x:v>
+        <x:v>https://career.cmbchina.com/</x:v>
       </x:c>
       <x:c r="J108" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6199,6 +6199,59 @@
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q108" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" ht="54" customHeight="1">
+      <x:c r="A109" s="4" t="str">
+        <x:v>2026-04-22</x:v>
+      </x:c>
+      <x:c r="B109" s="4" t="str">
+        <x:v>华金证券</x:v>
+      </x:c>
+      <x:c r="C109" s="4" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="D109" s="4" t="str">
+        <x:v>国企</x:v>
+      </x:c>
+      <x:c r="E109" s="4" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F109" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G109" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H109" s="4" t="str">
+        <x:v>战略发展类</x:v>
+      </x:c>
+      <x:c r="I109" s="15" t="str">
+        <x:v>https://www.huajinsc.cn/</x:v>
+      </x:c>
+      <x:c r="J109" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K109" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L109" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M109" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N109" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O109" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P109" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q109" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -6209,7 +6262,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54cd0616e22f43a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf3f71d89fc34b0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6239,7 +6292,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>近期有明确截止时间的项目（截至2026-08-04）</x:v>
+        <x:v>近期有明确截止时间的项目（截至2026-08-05）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -7017,140 +7070,140 @@
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>京东-TET管理培训生</x:v>
+        <x:v>联想集团</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
-        <x:v>互联网/零售</x:v>
+        <x:v>计算机/消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>北京及业务所在城市</x:v>
+        <x:v>北京、上海、天津、成都、南京、武汉、深圳、厦门等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F17" s="4" t="str">
-        <x:v>管培生专项/提前批</x:v>
+        <x:v>正式批/应届生招聘</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届海内外毕业生（中国大陆毕业时间为2026年9月1日至2027年8月31日）</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
+        <x:v>AI开发、软件开发、嵌入式、硬件、产品与项目、设计、市场与销售、供应链及职能岗位</x:v>
       </x:c>
       <x:c r="I17" s="15" t="str">
-        <x:v>https://campus.jd.com/</x:v>
+        <x:v>https://talent.lenovo.com.cn/campus</x:v>
       </x:c>
       <x:c r="J17" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>2026-11-13</x:v>
       </x:c>
       <x:c r="K17" s="4" t="str">
-        <x:v>含测评，笔试以通知为准</x:v>
+        <x:v>否（官方校招日历含在线测评&amp;技术笔试，简历筛选通过发放笔试通知）</x:v>
       </x:c>
       <x:c r="L17" s="4" t="str">
-        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
+        <x:v>本轮新增；联想官方应届生招聘页显示热招中</x:v>
       </x:c>
       <x:c r="M17" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N17" s="4" t="str">
-        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
+        <x:v>联想官方应届生招聘页当前显示“联想2027应届生招聘”，面向2027届海内外毕业生；网申自2026年8月5日开启，官网公布网申截止2026年11月13日。简历完整度需达到100%才能投递，每个校招项目只能投一个岗位（管培生项目和其他项目可各投一个），部分岗位可能因投递人数较多下线；投递时可选择接受岗位调剂，测评通知以邮件、短信和系统提醒为准。</x:v>
       </x:c>
       <x:c r="O17" s="15" t="str">
-        <x:v>https://campus.jd.com/#/</x:v>
+        <x:v>https://talent.lenovo.com.cn/campus</x:v>
       </x:c>
       <x:c r="P17" s="14" t="str">
-        <x:v>A-企业官网校招页面已核验</x:v>
+        <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="Q17" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="4" t="str">
-        <x:v>2026-06-12</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B18" s="4" t="str">
-        <x:v>MOVA</x:v>
+        <x:v>京东-TET管理培训生</x:v>
       </x:c>
       <x:c r="C18" s="4" t="str">
-        <x:v>智能家电/机器人</x:v>
+        <x:v>互联网/零售</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>苏州及全国</x:v>
+        <x:v>北京及业务所在城市</x:v>
       </x:c>
       <x:c r="F18" s="4" t="str">
-        <x:v>全球校招/正式批</x:v>
+        <x:v>管培生专项/提前批</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
       </x:c>
       <x:c r="I18" s="15" t="str">
-        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+        <x:v>https://campus.jd.com/</x:v>
       </x:c>
       <x:c r="J18" s="4" t="str">
         <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K18" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>含测评，笔试以通知为准</x:v>
       </x:c>
       <x:c r="L18" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
       </x:c>
       <x:c r="M18" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N18" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
       </x:c>
       <x:c r="O18" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P18" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>https://campus.jd.com/#/</x:v>
+      </x:c>
+      <x:c r="P18" s="14" t="str">
+        <x:v>A-企业官网校招页面已核验</x:v>
       </x:c>
       <x:c r="Q18" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-12</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>龙蟠科技</x:v>
+        <x:v>MOVA</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>新能源材料/化工</x:v>
+        <x:v>智能家电/机器人</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>苏州及全国</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>全球校招/正式批</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
+        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
       </x:c>
       <x:c r="I19" s="15" t="str">
-        <x:v>https://www.lopal.com.cn/join</x:v>
+        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
-        <x:v>2027-06-01</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K19" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -7176,54 +7229,107 @@
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
-        <x:v>百度</x:v>
+        <x:v>龙蟠科技</x:v>
       </x:c>
       <x:c r="C20" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>新能源材料/化工</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
       </x:c>
       <x:c r="I20" s="15" t="str">
-        <x:v>https://talent.baidu.com/jobs</x:v>
+        <x:v>https://www.lopal.com.cn/join</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
-        <x:v>2027-06-30</x:v>
+        <x:v>2027-06-01</x:v>
       </x:c>
       <x:c r="K20" s="4" t="str">
-        <x:v>部分免；并非所有候选人参加笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L20" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M20" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N20" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O20" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P20" s="18" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q20" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="54" customHeight="1">
+      <x:c r="A21" s="4" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="str">
+        <x:v>百度</x:v>
+      </x:c>
+      <x:c r="C21" s="4" t="str">
+        <x:v>互联网/AI</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E21" s="4" t="str">
+        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+      </x:c>
+      <x:c r="F21" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G21" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H21" s="4" t="str">
+        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+      </x:c>
+      <x:c r="I21" s="15" t="str">
+        <x:v>https://talent.baidu.com/jobs</x:v>
+      </x:c>
+      <x:c r="J21" s="4" t="str">
+        <x:v>2027-06-30</x:v>
+      </x:c>
+      <x:c r="K21" s="4" t="str">
+        <x:v>部分免；并非所有候选人参加笔试</x:v>
+      </x:c>
+      <x:c r="L21" s="4" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M21" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N21" s="4" t="str">
         <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
       </x:c>
-      <x:c r="O20" s="15" t="str">
+      <x:c r="O21" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P20" s="14" t="str">
+      <x:c r="P21" s="14" t="str">
         <x:v>A-官方招聘日历/官方来源已核验</x:v>
       </x:c>
-      <x:c r="Q20" s="4" t="str">
+      <x:c r="Q21" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -7234,7 +7340,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26a1d8c8a7414a7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a447bf34539453a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7252,7 +7358,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="27" t="str">
-        <x:v>使用说明与统计（截至2026-08-04）</x:v>
+        <x:v>使用说明与统计（截至2026-08-05）</x:v>
       </x:c>
       <x:c r="B1" s="27"/>
       <x:c r="C1" s="27"/>
@@ -7455,7 +7561,7 @@
         <x:v>项目总数</x:v>
       </x:c>
       <x:c r="B16" s="28" t="n">
-        <x:v>105</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C16" s="25"/>
       <x:c r="D16" s="31" t="str">
@@ -7471,7 +7577,7 @@
         <x:v>有明确截止时间（未截止）</x:v>
       </x:c>
       <x:c r="B17" s="28" t="n">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C17" s="25"/>
       <x:c r="D17" s="31" t="str">
@@ -7487,7 +7593,7 @@
         <x:v>A等级</x:v>
       </x:c>
       <x:c r="B18" s="28" t="n">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C18" s="25"/>
       <x:c r="D18" s="31" t="str">
@@ -7535,7 +7641,7 @@
         <x:v>本次更新</x:v>
       </x:c>
       <x:c r="B22" s="25" t="str">
-        <x:v>新增1项；关闭0项；未来7天内明确截止1项；新增项目来自可信高校就业网公告并核验官方投递入口，免笔试政策以公告为准。</x:v>
+        <x:v>新增1项；关闭0项；未来7天内明确截止1项；新增项目来自企业官方校园招聘页，免笔试政策以公告为准。</x:v>
       </x:c>
       <x:c r="C22" s="25"/>
       <x:c r="D22" s="25"/>

--- a/2027届秋招投递信息_2026-07-24.xlsx
+++ b/2027届秋招投递信息_2026-07-24.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R7058580a4e864a38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="Rf992459e2bd04eb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="R81ddd37a8cee4980"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="Ra139c89b5f554056"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="R460d908b69be4f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="Rccd815b14df84a64"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -88,12 +88,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF4CCCC"/>
+        <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF2CC"/>
+        <x:fgColor rgb="FFF4CCCC"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -241,10 +241,10 @@
     <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -301,8 +301,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q109" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:Q109"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q117" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:Q117"/>
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="开放投递时间"/>
     <x:tableColumn id="2" name="企业名称"/>
@@ -568,7 +568,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>2027届秋招投递信息（截至2026-08-05）</x:v>
+        <x:v>2027届秋招投递信息（截至2026-08-06）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -589,7 +589,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>每日更新：按开放时间倒序；本轮新增1项官方核验项目，关闭0项；第三方汇总入口不作为立即投递链接。</x:v>
+        <x:v>每日更新：按开放时间倒序；本轮新增8项官方核验项目，关闭0项；第三方汇总入口不作为立即投递链接。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -663,455 +663,455 @@
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="4" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
       <x:c r="B4" s="4" t="str">
-        <x:v>联想集团</x:v>
+        <x:v>德邦快递</x:v>
       </x:c>
       <x:c r="C4" s="4" t="str">
-        <x:v>计算机/消费电子/智能硬件</x:v>
+        <x:v>物流/快递/供应链</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
-        <x:v>北京、上海、天津、成都、南京、武汉、深圳、厦门等，以岗位页为准</x:v>
+        <x:v>全国各战区，已核验山东、广东、西北、京津、浙沪等区域岗位</x:v>
       </x:c>
       <x:c r="F4" s="4" t="str">
-        <x:v>正式批/应届生招聘</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G4" s="4" t="str">
-        <x:v>2027届海内外毕业生（中国大陆毕业时间为2026年9月1日至2027年8月31日）</x:v>
+        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
       </x:c>
       <x:c r="H4" s="4" t="str">
-        <x:v>AI开发、软件开发、嵌入式、硬件、产品与项目、设计、市场与销售、供应链及职能岗位</x:v>
+        <x:v>经营方向、运营方向及总部校园岗位</x:v>
       </x:c>
       <x:c r="I4" s="15" t="str">
-        <x:v>https://talent.lenovo.com.cn/campus</x:v>
+        <x:v>http://zhaopin.deppon.com/campus</x:v>
       </x:c>
       <x:c r="J4" s="4" t="str">
-        <x:v>2026-11-13</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K4" s="4" t="str">
-        <x:v>否（官方校招日历含在线测评&amp;技术笔试，简历筛选通过发放笔试通知）</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L4" s="4" t="str">
-        <x:v>本轮新增；联想官方应届生招聘页显示热招中</x:v>
+        <x:v>本轮新增；官方校园岗位于2026-08-06集中发布</x:v>
       </x:c>
       <x:c r="M4" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N4" s="4" t="str">
-        <x:v>联想官方应届生招聘页当前显示“联想2027应届生招聘”，面向2027届海内外毕业生；网申自2026年8月5日开启，官网公布网申截止2026年11月13日。简历完整度需达到100%才能投递，每个校招项目只能投一个岗位（管培生项目和其他项目可各投一个），部分岗位可能因投递人数较多下线；投递时可选择接受岗位调剂，测评通知以邮件、短信和系统提醒为准。</x:v>
+        <x:v>官网分省区和总部两类入口；经营、运营岗位按战区发布，部分岗位可能随需求提前下线，投递前确认工作省份。</x:v>
       </x:c>
       <x:c r="O4" s="15" t="str">
-        <x:v>https://talent.lenovo.com.cn/campus</x:v>
+        <x:v>http://zhaopin.deppon.com/campus_post?p=3%5E21</x:v>
       </x:c>
       <x:c r="P4" s="14" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
+        <x:v>A-企业官方校园招聘岗位页已核验</x:v>
       </x:c>
       <x:c r="Q4" s="4" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="4" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>不晚于2026-08-06</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>影石Insta360</x:v>
+        <x:v>亿联网络</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
-        <x:v>消费电子/智能影像</x:v>
+        <x:v>通信设备/企业协作/软件</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
-        <x:v>深圳、上海、珠海</x:v>
+        <x:v>厦门为主；国内客户及售前岗位覆盖北京、上海、广州、深圳</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G5" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
       </x:c>
       <x:c r="H5" s="4" t="str">
-        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+        <x:v>大模型、图像算法、C/C++、Android、Web前端、SRE、硬件、射频、测试、产品、产品市场、客户经理、售前、技术支持、市场宣传及营销管理</x:v>
       </x:c>
       <x:c r="I5" s="15" t="str">
-        <x:v>https://www.insta360.com/cn/jobs</x:v>
+        <x:v>https://yealink.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="J5" s="4" t="str">
-        <x:v>2026-10-31</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K5" s="4" t="str">
-        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L5" s="4" t="str">
-        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
+        <x:v>本轮新增；官方校园招聘页当前开放23个岗位</x:v>
       </x:c>
       <x:c r="M5" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N5" s="4" t="str">
-        <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
+        <x:v>岗位分批开放，城市与专业要求差异较大；海外岗位通常有外语要求，以每个职位详情页为准。</x:v>
       </x:c>
       <x:c r="O5" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
+        <x:v>https://yealink.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="P5" s="14" t="str">
-        <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
+        <x:v>A-企业官方校园招聘岗位页已核验</x:v>
       </x:c>
       <x:c r="Q5" s="4" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
-      <x:c r="A6" s="16" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B6" s="16" t="str">
-        <x:v>恒丰银行总行-雏鹰计划</x:v>
-      </x:c>
-      <x:c r="C6" s="16" t="str">
-        <x:v>银行/金融</x:v>
-      </x:c>
-      <x:c r="D6" s="16" t="str">
-        <x:v>股份制商业银行</x:v>
-      </x:c>
-      <x:c r="E6" s="16" t="str">
-        <x:v>总行及相关机构，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F6" s="16" t="str">
-        <x:v>暑期实习/秋招储备</x:v>
-      </x:c>
-      <x:c r="G6" s="16" t="str">
-        <x:v>2027届硕士及以上，以公告要求为准</x:v>
-      </x:c>
-      <x:c r="H6" s="16" t="str">
-        <x:v>总行实习生，具体专业和方向以官方公告为准</x:v>
-      </x:c>
-      <x:c r="I6" s="17" t="str">
-        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
-      </x:c>
-      <x:c r="J6" s="16" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K6" s="16" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L6" s="16" t="str">
-        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M6" s="16" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N6" s="16" t="str">
-        <x:v>官方公告显示7月31日24:00截止，实习期安排和具体岗位以恒丰银行招聘官网为准。</x:v>
-      </x:c>
-      <x:c r="O6" s="17" t="str">
-        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
-      </x:c>
-      <x:c r="P6" s="14" t="str">
-        <x:v>A-企业官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q6" s="16" t="str">
-        <x:v>2026-08-03</x:v>
+      <x:c r="A6" s="4" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="str">
+        <x:v>菜鸟-2027应届生招聘</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="str">
+        <x:v>物流科技/供应链</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="str">
+        <x:v>民营/阿里巴巴业务</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="str">
+        <x:v>以阿里巴巴校园招聘官网岗位页为准</x:v>
+      </x:c>
+      <x:c r="F6" s="4" t="str">
+        <x:v>正式批/应届生招聘</x:v>
+      </x:c>
+      <x:c r="G6" s="4" t="str">
+        <x:v>海内外2027届应届生，毕业时间为2026年11月至2027年10月</x:v>
+      </x:c>
+      <x:c r="H6" s="4" t="str">
+        <x:v>算法、研发、产品、运营、数据、物流、职能及销售类</x:v>
+      </x:c>
+      <x:c r="I6" s="15" t="str">
+        <x:v>https://campus-talent.alibaba.com/</x:v>
+      </x:c>
+      <x:c r="J6" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K6" s="4" t="str">
+        <x:v>否（技术类岗位参加笔试，新增AI Coding题型）</x:v>
+      </x:c>
+      <x:c r="L6" s="4" t="str">
+        <x:v>本轮新增；可信高校就业网发布企业招聘海报，阿里巴巴官方校招入口已核验</x:v>
+      </x:c>
+      <x:c r="M6" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N6" s="4" t="str">
+        <x:v>进入阿里巴巴集团校招官网后选择27届应届生批次和菜鸟业务，最多选择两个意向岗位；技术类岗位笔试，8月中旬起面试，9月下旬起发放Offer。</x:v>
+      </x:c>
+      <x:c r="O6" s="15" t="str">
+        <x:v>https://wtu.91wllm.cn/news/view/aid/300685/tag/xxtz</x:v>
+      </x:c>
+      <x:c r="P6" s="16" t="str">
+        <x:v>B-可信高校就业网公告含企业官方投递入口</x:v>
+      </x:c>
+      <x:c r="Q6" s="4" t="str">
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>四方股份</x:v>
+        <x:v>电科芯片吉芯科技</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
-        <x:v>电力系统/工业自动化</x:v>
+        <x:v>半导体/模拟混合信号IC</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>国有控股</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
+        <x:v>重庆</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
+        <x:v>IC设计、IC测试、失效分析、IC应用、产品与质量、调测等岗位</x:v>
       </x:c>
       <x:c r="I7" s="15" t="str">
-        <x:v>https://www.sf-auto.com/campus</x:v>
+        <x:v>https://campus.51job.com/jxkj2026/</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K7" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否（官方招聘流程明确包含在线测评）</x:v>
       </x:c>
       <x:c r="L7" s="4" t="str">
-        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
+        <x:v>本轮新增；可信高校就业网发布企业招聘海报，官方投递站可访问</x:v>
       </x:c>
       <x:c r="M7" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N7" s="4" t="str">
-        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
+        <x:v>招聘流程为简历投递、简历筛选、在线测评、技术面试、综合面试、Offer发放；投递站路径虽含2026字样，但为本次2027届海报公布的电脑端入口。</x:v>
       </x:c>
       <x:c r="O7" s="15" t="str">
-        <x:v>https://www.sf-auto.com/campus</x:v>
-      </x:c>
-      <x:c r="P7" s="14" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
+        <x:v>https://wtu.91wllm.cn/news/view/aid/300682/tag/xxtz</x:v>
+      </x:c>
+      <x:c r="P7" s="16" t="str">
+        <x:v>B-可信高校就业网公告含企业官方投递入口</x:v>
       </x:c>
       <x:c r="Q7" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>苏纳光电</x:v>
+        <x:v>科大讯飞-2027秋季校园招聘</x:v>
       </x:c>
       <x:c r="C8" s="4" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>AI/软件/智能语音</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>苏州、上海</x:v>
+        <x:v>合肥、北京、上海、武汉、西安、广州、成都、苏州、石家庄、南京等</x:v>
       </x:c>
       <x:c r="F8" s="4" t="str">
-        <x:v>提前批/Open Day</x:v>
+        <x:v>正式批/大型秋季校园招聘</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
-        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
+        <x:v>毕业时间为2025年6月1日至2027年8月31日的学生（官网原文）</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
-        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
+        <x:v>研究算法、研发、AI研发、测试、大数据、产品、营销、设计、教育、医学、职能、资源、交付及工程类</x:v>
       </x:c>
       <x:c r="I8" s="15" t="str">
-        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+        <x:v>https://iflytek.zhiye.com/campus/jobs?sessionid=</x:v>
       </x:c>
       <x:c r="J8" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K8" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L8" s="4" t="str">
-        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
+        <x:v>本轮新增；与飞凡计划区分，官方常规大型秋季校招项目开放100个岗位</x:v>
       </x:c>
       <x:c r="M8" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N8" s="4" t="str">
-        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
+        <x:v>岗位持续上新；官网当前显示100个职位。正式秋招与库内的飞凡人才专项并行，投递时注意选择“常规大型秋季校园招聘项目-2027届”。</x:v>
       </x:c>
       <x:c r="O8" s="15" t="str">
-        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+        <x:v>https://wtu.91wllm.cn/news/view/aid/300681/tag/xxtz</x:v>
       </x:c>
       <x:c r="P8" s="14" t="str">
-        <x:v>A-企业官方校园招聘系统已核验</x:v>
+        <x:v>A-企业官方校招页与可信高校就业网公告交叉核验</x:v>
       </x:c>
       <x:c r="Q8" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>特斯拉中国</x:v>
+        <x:v>联想集团</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
-        <x:v>新能源汽车/智能制造</x:v>
+        <x:v>计算机/消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
-        <x:v>外资/上市</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
+        <x:v>北京、上海、天津、成都、南京、武汉、深圳、厦门等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F9" s="4" t="str">
+        <x:v>正式批/应届生招聘</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="str">
+        <x:v>2027届海内外毕业生（中国大陆毕业时间为2026年9月1日至2027年8月31日）</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="str">
+        <x:v>AI开发、软件开发、嵌入式、硬件、产品与项目、设计、市场与销售、供应链及职能岗位</x:v>
+      </x:c>
+      <x:c r="I9" s="15" t="str">
+        <x:v>https://talent.lenovo.com.cn/campus</x:v>
+      </x:c>
+      <x:c r="J9" s="4" t="str">
+        <x:v>2026-11-13</x:v>
+      </x:c>
+      <x:c r="K9" s="4" t="str">
+        <x:v>否（官方校招日历含在线测评&amp;技术笔试，简历筛选通过发放笔试通知）</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="str">
+        <x:v>本轮新增；联想官方应届生招聘页显示热招中</x:v>
+      </x:c>
+      <x:c r="M9" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N9" s="4" t="str">
+        <x:v>联想官方应届生招聘页当前显示“联想2027应届生招聘”，面向2027届海内外毕业生；网申自2026年8月5日开启，官网公布网申截止2026年11月13日。简历完整度需达到100%才能投递，每个校招项目只能投一个岗位（管培生项目和其他项目可各投一个），部分岗位可能因投递人数较多下线；投递时可选择接受岗位调剂，测评通知以邮件、短信和系统提醒为准。</x:v>
+      </x:c>
+      <x:c r="O9" s="15" t="str">
+        <x:v>https://talent.lenovo.com.cn/campus</x:v>
+      </x:c>
+      <x:c r="P9" s="14" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q9" s="4" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="4" t="str">
+        <x:v>不晚于2026-08-05</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="str">
+        <x:v>泉峰科技-2027校园招聘</x:v>
+      </x:c>
+      <x:c r="C10" s="4" t="str">
+        <x:v>电动工具/智能制造/消费科技</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="str">
+        <x:v>南京、上海及海外岗位，以职位页为准</x:v>
+      </x:c>
+      <x:c r="F10" s="4" t="str">
         <x:v>正式批/校园招聘</x:v>
       </x:c>
-      <x:c r="G9" s="4" t="str">
-        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H9" s="4" t="str">
-        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
-      </x:c>
-      <x:c r="I9" s="15" t="str">
-        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
-      </x:c>
-      <x:c r="J9" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K9" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L9" s="4" t="str">
-        <x:v>本轮新确认；企业官方职位页已核验</x:v>
-      </x:c>
-      <x:c r="M9" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N9" s="4" t="str">
-        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
-      </x:c>
-      <x:c r="O9" s="15" t="str">
-        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
-      </x:c>
-      <x:c r="P9" s="14" t="str">
-        <x:v>A-企业官方职位页已核验</x:v>
-      </x:c>
-      <x:c r="Q9" s="4" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="54" customHeight="1">
-      <x:c r="A10" s="16" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B10" s="16" t="str">
-        <x:v>天健会计师事务所-暑期实习培训生</x:v>
-      </x:c>
-      <x:c r="C10" s="16" t="str">
-        <x:v>会计审计/专业服务</x:v>
-      </x:c>
-      <x:c r="D10" s="16" t="str">
-        <x:v>会计师事务所</x:v>
-      </x:c>
-      <x:c r="E10" s="16" t="str">
-        <x:v>上海等，以职位页为准</x:v>
-      </x:c>
-      <x:c r="F10" s="16" t="str">
-        <x:v>暑期实习/培训生</x:v>
-      </x:c>
-      <x:c r="G10" s="16" t="str">
-        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H10" s="16" t="str">
-        <x:v>财务审计暑期实习培训生</x:v>
-      </x:c>
-      <x:c r="I10" s="17" t="str">
-        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
-      </x:c>
-      <x:c r="J10" s="16" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K10" s="16" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L10" s="16" t="str">
-        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M10" s="16" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N10" s="16" t="str">
-        <x:v>公开公告显示7月31日截止；具体办公地点、专业要求和实习安排以天健招聘官网为准。</x:v>
-      </x:c>
-      <x:c r="O10" s="17" t="str">
-        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
+      <x:c r="G10" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H10" s="4" t="str">
+        <x:v>产品研发、工程与制造、质量与供应链、销售与市场、行政与综合管理等30个岗位</x:v>
+      </x:c>
+      <x:c r="I10" s="15" t="str">
+        <x:v>https://wecruit.hotjob.cn/SU6396cdcc0dcad40b2a419d69/pb/school.html#/</x:v>
+      </x:c>
+      <x:c r="J10" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K10" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L10" s="4" t="str">
+        <x:v>本轮新增；官方校园招聘页显示30个在招岗位，多项2027届职位于2026-08-05更新</x:v>
+      </x:c>
+      <x:c r="M10" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N10" s="4" t="str">
+        <x:v>本次为当前正式校园招聘岗位，不沿用6月提前批的7月3日截止时间；岗位包含销售与市场管培、算法、BMS、系统研发、产品、海外服务、质量、IT及电机开发等。</x:v>
+      </x:c>
+      <x:c r="O10" s="15" t="str">
+        <x:v>https://wecruit.hotjob.cn/SU6396cdcc0dcad40b2a419d69/pb/school.html#/</x:v>
       </x:c>
       <x:c r="P10" s="14" t="str">
-        <x:v>A-企业官方招聘入口已核验</x:v>
-      </x:c>
-      <x:c r="Q10" s="16" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>A-企业官方校园招聘岗位页已核验</x:v>
+      </x:c>
+      <x:c r="Q10" s="4" t="str">
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="B11" s="4" t="str">
-        <x:v>西安紫光国芯半导体</x:v>
+        <x:v>淘宝闪购-2027应届生招聘</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>互联网/本地生活/即时零售</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/阿里巴巴业务</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>西安、上海、成都</x:v>
+        <x:v>以阿里巴巴校园招聘官网岗位页为准</x:v>
       </x:c>
       <x:c r="F11" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>正式批/应届生招聘</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
+        <x:v>AI应用研发、AI Infra、安全技术、算法、数据科学、AI视觉与体验设计、AI产品、产品运营、用户运营、商品运营、整合营销、风险策略运营及AI商业分析</x:v>
       </x:c>
       <x:c r="I11" s="15" t="str">
-        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
+        <x:v>https://campus-talent.alibaba.com/</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K11" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否（算法、工程、AI研发、数据研发、数据科学方向共安排11场笔试）</x:v>
       </x:c>
       <x:c r="L11" s="4" t="str">
-        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
+        <x:v>本轮新增；可信高校就业网发布企业招聘海报，阿里巴巴官方校招入口已核验</x:v>
       </x:c>
       <x:c r="M11" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N11" s="4" t="str">
-        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
+        <x:v>电脑端在阿里巴巴集团校园招聘官网选择淘宝闪购业务；手机端可关注“淘宝闪购招聘”公众号并进入校园招聘。具体岗位以淘宝闪购招聘官网发布为准。</x:v>
       </x:c>
       <x:c r="O11" s="15" t="str">
-        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
-      </x:c>
-      <x:c r="P11" s="14" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
+        <x:v>https://wtu.91wllm.cn/news/view/aid/300684/tag/xxtz</x:v>
+      </x:c>
+      <x:c r="P11" s="16" t="str">
+        <x:v>B-可信高校就业网公告含企业官方投递方式</x:v>
       </x:c>
       <x:c r="Q11" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>新大陆自动识别</x:v>
+        <x:v>德州仪器TI</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
-        <x:v>计算机视觉/智能硬件</x:v>
+        <x:v>半导体/模拟与嵌入式芯片</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>民营/上市公司子公司</x:v>
+        <x:v>外资/上市</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>福州总部及全国/海外岗位</x:v>
+        <x:v>上海及中国区岗位，以职位详情页为准</x:v>
       </x:c>
       <x:c r="F12" s="4" t="str">
         <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
+        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
+        <x:v>人力资源培训生、税务专员、会计专员、产品市场工程师（模拟/嵌入式方向）及品牌营销专员</x:v>
       </x:c>
       <x:c r="I12" s="15" t="str">
-        <x:v>https://nlscan.zhiye.com/Campus</x:v>
+        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
       </x:c>
       <x:c r="J12" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1120,128 +1120,128 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L12" s="4" t="str">
-        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
+        <x:v>本轮新增；官方职位页已发布多项中国区2027校园招聘岗位</x:v>
       </x:c>
       <x:c r="M12" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N12" s="4" t="str">
-        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
+        <x:v>岗位分批发布，当前核验到的2027校招岗位发布日期为2026-08-04；投递前按China地区和岗位关键词筛选。</x:v>
       </x:c>
       <x:c r="O12" s="15" t="str">
-        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
+        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
       </x:c>
       <x:c r="P12" s="14" t="str">
-        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
+        <x:v>A-企业官方职位页已核验</x:v>
       </x:c>
       <x:c r="Q12" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>2026-08-01</x:v>
       </x:c>
       <x:c r="B13" s="4" t="str">
-        <x:v>兆易创新</x:v>
+        <x:v>影石Insta360</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>消费电子/智能影像</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>北京、上海、武汉、合肥等，以岗位页为准</x:v>
+        <x:v>深圳、上海、珠海</x:v>
       </x:c>
       <x:c r="F13" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>芯片设计、验证、嵌入式、软件、应用、测试及职能岗位</x:v>
+        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
       </x:c>
       <x:c r="I13" s="15" t="str">
-        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
       </x:c>
       <x:c r="J13" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-31</x:v>
       </x:c>
       <x:c r="K13" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
       </x:c>
       <x:c r="L13" s="4" t="str">
-        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
+        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
       </x:c>
       <x:c r="M13" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N13" s="4" t="str">
-        <x:v>提前批岗位和城市以兆易创新官方加入我们页面为准，投递前确认职位仍开放。</x:v>
+        <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
       </x:c>
       <x:c r="O13" s="15" t="str">
-        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
       </x:c>
       <x:c r="P13" s="14" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
+        <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
       </x:c>
       <x:c r="Q13" s="4" t="str">
+        <x:v>2026-08-04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="17" t="str">
+        <x:v>不晚于2026-07-30</x:v>
+      </x:c>
+      <x:c r="B14" s="17" t="str">
+        <x:v>恒丰银行总行-雏鹰计划</x:v>
+      </x:c>
+      <x:c r="C14" s="17" t="str">
+        <x:v>银行/金融</x:v>
+      </x:c>
+      <x:c r="D14" s="17" t="str">
+        <x:v>股份制商业银行</x:v>
+      </x:c>
+      <x:c r="E14" s="17" t="str">
+        <x:v>总行及相关机构，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F14" s="17" t="str">
+        <x:v>暑期实习/秋招储备</x:v>
+      </x:c>
+      <x:c r="G14" s="17" t="str">
+        <x:v>2027届硕士及以上，以公告要求为准</x:v>
+      </x:c>
+      <x:c r="H14" s="17" t="str">
+        <x:v>总行实习生，具体专业和方向以官方公告为准</x:v>
+      </x:c>
+      <x:c r="I14" s="18" t="str">
+        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
+      </x:c>
+      <x:c r="J14" s="17" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" ht="54" customHeight="1">
-      <x:c r="A14" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B14" s="4" t="str">
-        <x:v>中国航空发动机集团</x:v>
-      </x:c>
-      <x:c r="C14" s="4" t="str">
-        <x:v>航空发动机/军工</x:v>
-      </x:c>
-      <x:c r="D14" s="4" t="str">
-        <x:v>央企</x:v>
-      </x:c>
-      <x:c r="E14" s="4" t="str">
-        <x:v>全国各院所及下属单位</x:v>
-      </x:c>
-      <x:c r="F14" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
-      </x:c>
-      <x:c r="G14" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H14" s="4" t="str">
-        <x:v>研发设计、工艺、试验、制造、材料、控制、软件及管理岗位</x:v>
-      </x:c>
-      <x:c r="I14" s="15" t="str">
-        <x:v>https://aecc.iguopin.com/notice2</x:v>
-      </x:c>
-      <x:c r="J14" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K14" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L14" s="4" t="str">
-        <x:v>本轮新确认；集团官方招聘平台已核验</x:v>
-      </x:c>
-      <x:c r="M14" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N14" s="4" t="str">
-        <x:v>各单位岗位和截止时间不同，需在中国航发招聘平台按单位和专业筛选。</x:v>
-      </x:c>
-      <x:c r="O14" s="15" t="str">
-        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/n2588350/c35693219/content.html</x:v>
+      <x:c r="K14" s="17" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L14" s="17" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M14" s="17" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N14" s="17" t="str">
+        <x:v>官方公告显示7月31日24:00截止，实习期安排和具体岗位以恒丰银行招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O14" s="18" t="str">
+        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
       </x:c>
       <x:c r="P14" s="14" t="str">
-        <x:v>A-国资委公告与集团招聘平台交叉核验</x:v>
-      </x:c>
-      <x:c r="Q14" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>A-企业官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q14" s="17" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
@@ -1249,28 +1249,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B15" s="4" t="str">
-        <x:v>中粮资本-粮曦计划</x:v>
+        <x:v>四方股份</x:v>
       </x:c>
       <x:c r="C15" s="4" t="str">
-        <x:v>金融/投资/资管</x:v>
+        <x:v>电力系统/工业自动化</x:v>
       </x:c>
       <x:c r="D15" s="4" t="str">
-        <x:v>央企/金融控股</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
       </x:c>
       <x:c r="F15" s="4" t="str">
-        <x:v>培养计划/实习</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G15" s="4" t="str">
-        <x:v>2027-2029届硕士及以上，以公告要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>金融、投资、风险、运营、人力资源及综合管理方向</x:v>
+        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
       </x:c>
       <x:c r="I15" s="15" t="str">
-        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+        <x:v>https://www.sf-auto.com/campus</x:v>
       </x:c>
       <x:c r="J15" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1279,19 +1279,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L15" s="4" t="str">
-        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
+        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="M15" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N15" s="4" t="str">
-        <x:v>粮曦计划具体批次、面向人群和岗位以中粮资本官方加入我们页面及公告为准。</x:v>
+        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
       </x:c>
       <x:c r="O15" s="15" t="str">
-        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+        <x:v>https://www.sf-auto.com/campus</x:v>
       </x:c>
       <x:c r="P15" s="14" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
+        <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="Q15" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1302,49 +1302,49 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
-        <x:v>中移九天人工智能科技</x:v>
+        <x:v>苏纳光电</x:v>
       </x:c>
       <x:c r="C16" s="4" t="str">
-        <x:v>AI/软件/云计算</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
-        <x:v>央企子公司</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>北京、西安、广州、深圳</x:v>
+        <x:v>苏州、上海</x:v>
       </x:c>
       <x:c r="F16" s="4" t="str">
-        <x:v>正式批/超级实习生</x:v>
+        <x:v>提前批/Open Day</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
+        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
+        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
       </x:c>
       <x:c r="I16" s="15" t="str">
-        <x:v>https://job.10086.cn/personal/campus/</x:v>
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="J16" s="4" t="str">
-        <x:v>2026-09-27</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K16" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L16" s="4" t="str">
-        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
+        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
       </x:c>
       <x:c r="M16" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N16" s="4" t="str">
-        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
+        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
       </x:c>
       <x:c r="O16" s="15" t="str">
-        <x:v>https://job.10086.cn/personal/campus/</x:v>
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="P16" s="14" t="str">
-        <x:v>A-中国移动官方招聘平台已核验</x:v>
+        <x:v>A-企业官方校园招聘系统已核验</x:v>
       </x:c>
       <x:c r="Q16" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1352,137 +1352,137 @@
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="4" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>广州市卓越教育集团</x:v>
+        <x:v>特斯拉中国</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>新能源汽车/智能制造</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>外资/上市</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>广州等，以职位页为准</x:v>
+        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
       </x:c>
       <x:c r="F17" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
       </x:c>
       <x:c r="I17" s="15" t="str">
-        <x:v>https://zyjob.hotjob.cn/</x:v>
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
       </x:c>
       <x:c r="J17" s="4" t="str">
-        <x:v>2026-10-26</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K17" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L17" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
+        <x:v>本轮新确认；企业官方职位页已核验</x:v>
       </x:c>
       <x:c r="M17" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N17" s="4" t="str">
-        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
+        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
       </x:c>
       <x:c r="O17" s="15" t="str">
-        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
       </x:c>
       <x:c r="P17" s="14" t="str">
-        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
+        <x:v>A-企业官方职位页已核验</x:v>
       </x:c>
       <x:c r="Q17" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
-      <x:c r="A18" s="4" t="str">
-        <x:v>2026-07-28</x:v>
-      </x:c>
-      <x:c r="B18" s="4" t="str">
-        <x:v>搜狐畅游</x:v>
-      </x:c>
-      <x:c r="C18" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
-      </x:c>
-      <x:c r="D18" s="4" t="str">
-        <x:v>民营/互联网</x:v>
-      </x:c>
-      <x:c r="E18" s="4" t="str">
-        <x:v>以岗位页面为准</x:v>
-      </x:c>
-      <x:c r="F18" s="4" t="str">
-        <x:v>提前批/校园招聘</x:v>
-      </x:c>
-      <x:c r="G18" s="4" t="str">
-        <x:v>2027届毕业生（部分岗位兼收2026届）</x:v>
-      </x:c>
-      <x:c r="H18" s="4" t="str">
-        <x:v>游戏策划、游戏开发、游戏美术、游戏运营、业务支持、平台开发、平台职能、游戏测试8大类岗位</x:v>
-      </x:c>
-      <x:c r="I18" s="15" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/cyou-inc/42233?recommendCode=DSRgNQU7#/jobs</x:v>
-      </x:c>
-      <x:c r="J18" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K18" s="4" t="str">
-        <x:v>非免笔试；提前批未录取可参加后续统一笔试</x:v>
-      </x:c>
-      <x:c r="L18" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；官方投递入口已核验</x:v>
-      </x:c>
-      <x:c r="M18" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N18" s="4" t="str">
-        <x:v>深圳北理莫斯科大学就业网公告《搜狐畅游2027届秋季校园招聘提前批正式启动！》发布于2026-07-28；提前批流程快、部分岗位有直通面试机会，未被录取者可参与后续统一笔试，部分热招岗位招满即停。</x:v>
-      </x:c>
-      <x:c r="O18" s="15" t="str">
-        <x:v>https://career.smbu.edu.cn/detail/online?id=3535355</x:v>
-      </x:c>
-      <x:c r="P18" s="18" t="str">
-        <x:v>B-可信高校就业网公告含官方投递链接</x:v>
-      </x:c>
-      <x:c r="Q18" s="4" t="str">
-        <x:v>2026-08-04</x:v>
+      <x:c r="A18" s="17" t="str">
+        <x:v>不晚于2026-07-30</x:v>
+      </x:c>
+      <x:c r="B18" s="17" t="str">
+        <x:v>天健会计师事务所-暑期实习培训生</x:v>
+      </x:c>
+      <x:c r="C18" s="17" t="str">
+        <x:v>会计审计/专业服务</x:v>
+      </x:c>
+      <x:c r="D18" s="17" t="str">
+        <x:v>会计师事务所</x:v>
+      </x:c>
+      <x:c r="E18" s="17" t="str">
+        <x:v>上海等，以职位页为准</x:v>
+      </x:c>
+      <x:c r="F18" s="17" t="str">
+        <x:v>暑期实习/培训生</x:v>
+      </x:c>
+      <x:c r="G18" s="17" t="str">
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H18" s="17" t="str">
+        <x:v>财务审计暑期实习培训生</x:v>
+      </x:c>
+      <x:c r="I18" s="18" t="str">
+        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
+      </x:c>
+      <x:c r="J18" s="17" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K18" s="17" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L18" s="17" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M18" s="17" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N18" s="17" t="str">
+        <x:v>公开公告显示7月31日截止；具体办公地点、专业要求和实习安排以天健招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O18" s="18" t="str">
+        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
+      </x:c>
+      <x:c r="P18" s="14" t="str">
+        <x:v>A-企业官方招聘入口已核验</x:v>
+      </x:c>
+      <x:c r="Q18" s="17" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>我乐家居</x:v>
+        <x:v>西安紫光国芯半导体</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>家居/消费品/智能制造</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>西安、上海、成都</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>提前批/校园招聘</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>2027届本科及以上，以岗位要求为准</x:v>
+        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
+        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
       </x:c>
       <x:c r="I19" s="15" t="str">
-        <x:v>https://olo-home.zhiye.com/Campus</x:v>
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1491,51 +1491,51 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L19" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
+        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
       </x:c>
       <x:c r="M19" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N19" s="4" t="str">
-        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
+        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
       </x:c>
       <x:c r="O19" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P19" s="18" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
+      </x:c>
+      <x:c r="P19" s="14" t="str">
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q19" s="4" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="4" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
-        <x:v>轩宇信息</x:v>
+        <x:v>新大陆自动识别</x:v>
       </x:c>
       <x:c r="C20" s="4" t="str">
-        <x:v>航天/军工信息化/软件</x:v>
+        <x:v>计算机视觉/智能硬件</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>央企子公司/高新技术企业</x:v>
+        <x:v>民营/上市公司子公司</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>北京、杭州、西安</x:v>
+        <x:v>福州总部及全国/海外岗位</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>AI专项/提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
+        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
       </x:c>
       <x:c r="I20" s="15" t="str">
-        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
+        <x:v>https://nlscan.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1544,39 +1544,39 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L20" s="4" t="str">
-        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
+        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
       </x:c>
       <x:c r="M20" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N20" s="4" t="str">
-        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
+        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
       </x:c>
       <x:c r="O20" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
+        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
       </x:c>
       <x:c r="P20" s="14" t="str">
-        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
+        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
       </x:c>
       <x:c r="Q20" s="4" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B21" s="4" t="str">
-        <x:v>卡尔动力</x:v>
+        <x:v>兆易创新</x:v>
       </x:c>
       <x:c r="C21" s="4" t="str">
-        <x:v>自动驾驶/智能汽车</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>北京、上海、天津等</x:v>
+        <x:v>北京、上海、武汉、合肥等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F21" s="4" t="str">
         <x:v>提前批</x:v>
@@ -1585,10 +1585,10 @@
         <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
+        <x:v>芯片设计、验证、嵌入式、软件、应用、测试及职能岗位</x:v>
       </x:c>
       <x:c r="I21" s="15" t="str">
-        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
+        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
       </x:c>
       <x:c r="J21" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1597,104 +1597,104 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L21" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
+        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="M21" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N21" s="4" t="str">
-        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
+        <x:v>提前批岗位和城市以兆易创新官方加入我们页面为准，投递前确认职位仍开放。</x:v>
       </x:c>
       <x:c r="O21" s="15" t="str">
-        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
-      </x:c>
-      <x:c r="P21" s="18" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
+        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
+      </x:c>
+      <x:c r="P21" s="14" t="str">
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q21" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B22" s="4" t="str">
-        <x:v>深信服-X-STAR顶尖人才计划</x:v>
+        <x:v>中国航空发动机集团</x:v>
       </x:c>
       <x:c r="C22" s="4" t="str">
-        <x:v>网络安全/云计算/软件</x:v>
+        <x:v>航空发动机/军工</x:v>
       </x:c>
       <x:c r="D22" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
+        <x:v>全国各院所及下属单位</x:v>
       </x:c>
       <x:c r="F22" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>顶尖人才，本硕博按岗位要求</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
+        <x:v>研发设计、工艺、试验、制造、材料、控制、软件及管理岗位</x:v>
       </x:c>
       <x:c r="I22" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
+        <x:v>https://aecc.iguopin.com/notice2</x:v>
       </x:c>
       <x:c r="J22" s="4" t="str">
-        <x:v>2026-09-25</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K22" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L22" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>本轮新确认；集团官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="M22" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N22" s="4" t="str">
-        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
+        <x:v>各单位岗位和截止时间不同，需在中国航发招聘平台按单位和专业筛选。</x:v>
       </x:c>
       <x:c r="O22" s="15" t="str">
-        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
+        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/n2588350/c35693219/content.html</x:v>
       </x:c>
       <x:c r="P22" s="14" t="str">
-        <x:v>A-高校就业网含官方投递链接</x:v>
+        <x:v>A-国资委公告与集团招聘平台交叉核验</x:v>
       </x:c>
       <x:c r="Q22" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B23" s="4" t="str">
-        <x:v>希夕智能</x:v>
+        <x:v>中粮资本-粮曦计划</x:v>
       </x:c>
       <x:c r="C23" s="4" t="str">
-        <x:v>机器人/智能制造</x:v>
+        <x:v>金融/投资/资管</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>央企/金融控股</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F23" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>培养计划/实习</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>2027届本科及以上</x:v>
+        <x:v>2027-2029届硕士及以上，以公告要求为准</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
+        <x:v>金融、投资、风险、运营、人力资源及综合管理方向</x:v>
       </x:c>
       <x:c r="I23" s="15" t="str">
-        <x:v>https://sunseed.zhiye.com/jobs</x:v>
+        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
       </x:c>
       <x:c r="J23" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1703,263 +1703,263 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L23" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
+        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
       </x:c>
       <x:c r="M23" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N23" s="4" t="str">
-        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
+        <x:v>粮曦计划具体批次、面向人群和岗位以中粮资本官方加入我们页面及公告为准。</x:v>
       </x:c>
       <x:c r="O23" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
-      </x:c>
-      <x:c r="P23" s="18" t="str">
-        <x:v>B-高校就业平台转载企业来源</x:v>
+        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+      </x:c>
+      <x:c r="P23" s="14" t="str">
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q23" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="4" t="str">
-        <x:v>不晚于2026-07-24</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B24" s="4" t="str">
-        <x:v>中国兵器工业集团</x:v>
+        <x:v>中移九天人工智能科技</x:v>
       </x:c>
       <x:c r="C24" s="4" t="str">
-        <x:v>军工/高端装备</x:v>
+        <x:v>AI/软件/云计算</x:v>
       </x:c>
       <x:c r="D24" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>央企子公司</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
+        <x:v>北京、西安、广州、深圳</x:v>
       </x:c>
       <x:c r="F24" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/超级实习生</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
+        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
       </x:c>
       <x:c r="I24" s="15" t="str">
-        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="J24" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-09-27</x:v>
       </x:c>
       <x:c r="K24" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L24" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
       </x:c>
       <x:c r="M24" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N24" s="4" t="str">
-        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
+        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
       </x:c>
       <x:c r="O24" s="15" t="str">
-        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
-      </x:c>
-      <x:c r="P24" s="18" t="str">
-        <x:v>B-公开招聘公告/集团入口</x:v>
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
+      </x:c>
+      <x:c r="P24" s="14" t="str">
+        <x:v>A-中国移动官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="Q24" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
       <x:c r="A25" s="4" t="str">
-        <x:v>2026-07-23</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B25" s="4" t="str">
-        <x:v>禾迈股份</x:v>
+        <x:v>广州市卓越教育集团</x:v>
       </x:c>
       <x:c r="C25" s="4" t="str">
-        <x:v>光伏/电力电子</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>杭州等，以岗位页为准</x:v>
+        <x:v>广州等，以职位页为准</x:v>
       </x:c>
       <x:c r="F25" s="4" t="str">
-        <x:v>研发类提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
+        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
       <x:c r="I25" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
+        <x:v>https://zyjob.hotjob.cn/</x:v>
       </x:c>
       <x:c r="J25" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-26</x:v>
       </x:c>
       <x:c r="K25" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L25" s="4" t="str">
-        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
+        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
       </x:c>
       <x:c r="M25" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N25" s="4" t="str">
-        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
+        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
       </x:c>
       <x:c r="O25" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
-      </x:c>
-      <x:c r="P25" s="18" t="str">
-        <x:v>B-高校就业网转载企业公告</x:v>
+        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
+      </x:c>
+      <x:c r="P25" s="14" t="str">
+        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
       </x:c>
       <x:c r="Q25" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="54" customHeight="1">
       <x:c r="A26" s="4" t="str">
-        <x:v>2026-07-23</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B26" s="4" t="str">
-        <x:v>极客未来</x:v>
+        <x:v>搜狐畅游</x:v>
       </x:c>
       <x:c r="C26" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D26" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/互联网</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>四川、重庆、广东</x:v>
+        <x:v>以岗位页面为准</x:v>
       </x:c>
       <x:c r="F26" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届毕业生（部分岗位兼收2026届）</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+        <x:v>游戏策划、游戏开发、游戏美术、游戏运营、业务支持、平台开发、平台职能、游戏测试8大类岗位</x:v>
       </x:c>
       <x:c r="I26" s="15" t="str">
-        <x:v>https://geek3.zhiye.com/campus/</x:v>
+        <x:v>https://app.mokahr.com/m/campus_apply/cyou-inc/42233?recommendCode=DSRgNQU7#/jobs</x:v>
       </x:c>
       <x:c r="J26" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K26" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>非免笔试；提前批未录取可参加后续统一笔试</x:v>
       </x:c>
       <x:c r="L26" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
+        <x:v>可信高校就业网公告显示开放；官方投递入口已核验</x:v>
       </x:c>
       <x:c r="M26" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N26" s="4" t="str">
-        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
+        <x:v>深圳北理莫斯科大学就业网公告《搜狐畅游2027届秋季校园招聘提前批正式启动！》发布于2026-07-28；提前批流程快、部分岗位有直通面试机会，未被录取者可参与后续统一笔试，部分热招岗位招满即停。</x:v>
       </x:c>
       <x:c r="O26" s="15" t="str">
-        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
-      </x:c>
-      <x:c r="P26" s="18" t="str">
-        <x:v>B-高校就业网公告+公开招聘页面</x:v>
+        <x:v>https://career.smbu.edu.cn/detail/online?id=3535355</x:v>
+      </x:c>
+      <x:c r="P26" s="16" t="str">
+        <x:v>B-可信高校就业网公告含官方投递链接</x:v>
       </x:c>
       <x:c r="Q26" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="54" customHeight="1">
       <x:c r="A27" s="4" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="B27" s="4" t="str">
-        <x:v>安永EY</x:v>
+        <x:v>我乐家居</x:v>
       </x:c>
       <x:c r="C27" s="4" t="str">
-        <x:v>会计审计/咨询/专业服务</x:v>
+        <x:v>家居/消费品/智能制造</x:v>
       </x:c>
       <x:c r="D27" s="4" t="str">
-        <x:v>外资/专业服务机构</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>中国内地多地，以职位页为准</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F27" s="4" t="str">
-        <x:v>正式批/秋季校园招聘</x:v>
+        <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
+        <x:v>2027届本科及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
+        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
       </x:c>
       <x:c r="I27" s="15" t="str">
-        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
+        <x:v>https://olo-home.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J27" s="4" t="str">
-        <x:v>2026年10月（具体日期未公布）</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K27" s="4" t="str">
-        <x:v>否；官方流程包含在线测评</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L27" s="4" t="str">
-        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
       </x:c>
       <x:c r="M27" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N27" s="4" t="str">
-        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
+        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
       </x:c>
       <x:c r="O27" s="15" t="str">
-        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
-      </x:c>
-      <x:c r="P27" s="14" t="str">
-        <x:v>A-企业官方校招网站与职位页已核验</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P27" s="16" t="str">
+        <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
       <x:c r="Q27" s="4" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="54" customHeight="1">
       <x:c r="A28" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="B28" s="4" t="str">
-        <x:v>阿里巴巴-阿里星计划</x:v>
+        <x:v>轩宇信息</x:v>
       </x:c>
       <x:c r="C28" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>航天/军工信息化/软件</x:v>
       </x:c>
       <x:c r="D28" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企子公司/高新技术企业</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>杭州、北京、上海、深圳等</x:v>
+        <x:v>北京、杭州、西安</x:v>
       </x:c>
       <x:c r="F28" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>AI专项/提前批</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
+        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
       </x:c>
       <x:c r="I28" s="15" t="str">
-        <x:v>https://talent.alibaba.com/campus/</x:v>
+        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
       </x:c>
       <x:c r="J28" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1968,155 +1968,157 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L28" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
       </x:c>
       <x:c r="M28" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N28" s="4" t="str">
-        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
+        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
       </x:c>
       <x:c r="O28" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P28" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P28" s="14" t="str">
+        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
       </x:c>
       <x:c r="Q28" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="54" customHeight="1">
       <x:c r="A29" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B29" s="4" t="str">
-        <x:v>贝恩公司</x:v>
+        <x:v>卡尔动力</x:v>
       </x:c>
       <x:c r="C29" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>自动驾驶/智能汽车</x:v>
       </x:c>
       <x:c r="D29" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>北京、上海、香港等</x:v>
+        <x:v>北京、上海、天津等</x:v>
       </x:c>
       <x:c r="F29" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>助理咨询顾问等</x:v>
+        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
       </x:c>
       <x:c r="I29" s="15" t="str">
-        <x:v>https://www.bain.com/careers/</x:v>
+        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
       </x:c>
       <x:c r="J29" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K29" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L29" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
       </x:c>
       <x:c r="M29" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N29" s="4" t="str"/>
+      <x:c r="N29" s="4" t="str">
+        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
+      </x:c>
       <x:c r="O29" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P29" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
+      </x:c>
+      <x:c r="P29" s="16" t="str">
+        <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
       <x:c r="Q29" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="54" customHeight="1">
       <x:c r="A30" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B30" s="4" t="str">
-        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
+        <x:v>深信服-X-STAR顶尖人才计划</x:v>
       </x:c>
       <x:c r="C30" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>网络安全/云计算/软件</x:v>
       </x:c>
       <x:c r="D30" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>上海、北京等</x:v>
+        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F30" s="4" t="str">
-        <x:v>顶尖技术专项/提前批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>顶尖人才，本硕博按岗位要求</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
+        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
       </x:c>
       <x:c r="I30" s="15" t="str">
-        <x:v>https://jobs.bilibili.com/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
       </x:c>
       <x:c r="J30" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-09-25</x:v>
       </x:c>
       <x:c r="K30" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L30" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M30" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N30" s="4" t="str">
-        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
+        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
       </x:c>
       <x:c r="O30" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P30" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
+      </x:c>
+      <x:c r="P30" s="14" t="str">
+        <x:v>A-高校就业网含官方投递链接</x:v>
       </x:c>
       <x:c r="Q30" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="54" customHeight="1">
       <x:c r="A31" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B31" s="4" t="str">
-        <x:v>东风汽车-全球博士人才</x:v>
+        <x:v>希夕智能</x:v>
       </x:c>
       <x:c r="C31" s="4" t="str">
-        <x:v>汽车/央企</x:v>
+        <x:v>机器人/智能制造</x:v>
       </x:c>
       <x:c r="D31" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>武汉、广州、十堰及全国研发基地</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F31" s="4" t="str">
-        <x:v>博士专项</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>2026届及以后博士</x:v>
+        <x:v>2027届本科及以上</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
+        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
       </x:c>
       <x:c r="I31" s="15" t="str">
-        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
+        <x:v>https://sunseed.zhiye.com/jobs</x:v>
       </x:c>
       <x:c r="J31" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2125,72 +2127,72 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L31" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
       </x:c>
       <x:c r="M31" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N31" s="4" t="str">
-        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
+        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
       </x:c>
       <x:c r="O31" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P31" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
+      </x:c>
+      <x:c r="P31" s="16" t="str">
+        <x:v>B-高校就业平台转载企业来源</x:v>
       </x:c>
       <x:c r="Q31" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="54" customHeight="1">
       <x:c r="A32" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>不晚于2026-07-24</x:v>
       </x:c>
       <x:c r="B32" s="4" t="str">
-        <x:v>度小满-博士后人才招聘</x:v>
+        <x:v>中国兵器工业集团</x:v>
       </x:c>
       <x:c r="C32" s="4" t="str">
-        <x:v>金融科技</x:v>
+        <x:v>军工/高端装备</x:v>
       </x:c>
       <x:c r="D32" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
       </x:c>
       <x:c r="F32" s="4" t="str">
-        <x:v>博士后专项</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
-        <x:v>2025/2026/2027届博士</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
-        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
+        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
       </x:c>
       <x:c r="I32" s="15" t="str">
-        <x:v>https://campus.duxiaoman.com/</x:v>
+        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
       </x:c>
       <x:c r="J32" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K32" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L32" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M32" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N32" s="4" t="str">
-        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
+        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
       </x:c>
       <x:c r="O32" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P32" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
+      </x:c>
+      <x:c r="P32" s="16" t="str">
+        <x:v>B-公开招聘公告/集团入口</x:v>
       </x:c>
       <x:c r="Q32" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -2198,31 +2200,31 @@
     </x:row>
     <x:row r="33" ht="54" customHeight="1">
       <x:c r="A33" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B33" s="4" t="str">
-        <x:v>多益网络</x:v>
+        <x:v>禾迈股份</x:v>
       </x:c>
       <x:c r="C33" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>光伏/电力电子</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
-        <x:v>广州、武汉、成都等</x:v>
+        <x:v>杭州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F33" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>研发类提前批</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H33" s="4" t="str">
-        <x:v>程序、策划、美术、运营、市场及职能</x:v>
+        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
       </x:c>
       <x:c r="I33" s="15" t="str">
-        <x:v>https://www.duoyi.com/job/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
       </x:c>
       <x:c r="J33" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2231,51 +2233,51 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L33" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
       </x:c>
       <x:c r="M33" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N33" s="4" t="str">
-        <x:v>岗位可能按城市提前关闭。</x:v>
+        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
       </x:c>
       <x:c r="O33" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P33" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
+      </x:c>
+      <x:c r="P33" s="16" t="str">
+        <x:v>B-高校就业网转载企业公告</x:v>
       </x:c>
       <x:c r="Q33" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="54" customHeight="1">
       <x:c r="A34" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B34" s="4" t="str">
-        <x:v>海天集团-高潜专项</x:v>
+        <x:v>极客未来</x:v>
       </x:c>
       <x:c r="C34" s="4" t="str">
-        <x:v>工业制造</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D34" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
-        <x:v>宁波及全国基地</x:v>
+        <x:v>四川、重庆、广东</x:v>
       </x:c>
       <x:c r="F34" s="4" t="str">
-        <x:v>高潜人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G34" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H34" s="4" t="str">
-        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
+        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
       <x:c r="I34" s="15" t="str">
-        <x:v>https://www.haitian.com/careers/</x:v>
+        <x:v>https://geek3.zhiye.com/campus/</x:v>
       </x:c>
       <x:c r="J34" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2284,73 +2286,75 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L34" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
       </x:c>
       <x:c r="M34" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N34" s="4" t="str">
-        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
+        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
       </x:c>
       <x:c r="O34" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P34" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
+      </x:c>
+      <x:c r="P34" s="16" t="str">
+        <x:v>B-高校就业网公告+公开招聘页面</x:v>
       </x:c>
       <x:c r="Q34" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="54" customHeight="1">
       <x:c r="A35" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="B35" s="4" t="str">
-        <x:v>赫力昂-销售先锋计划</x:v>
+        <x:v>安永EY</x:v>
       </x:c>
       <x:c r="C35" s="4" t="str">
-        <x:v>消费健康/医药</x:v>
+        <x:v>会计审计/咨询/专业服务</x:v>
       </x:c>
       <x:c r="D35" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>外资/专业服务机构</x:v>
       </x:c>
       <x:c r="E35" s="4" t="str">
-        <x:v>全国重点城市</x:v>
+        <x:v>中国内地多地，以职位页为准</x:v>
       </x:c>
       <x:c r="F35" s="4" t="str">
-        <x:v>管培/销售专项</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
       </x:c>
       <x:c r="H35" s="4" t="str">
-        <x:v>医药及消费健康销售、商业运营方向</x:v>
+        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
       </x:c>
       <x:c r="I35" s="15" t="str">
-        <x:v>https://careers.haleon.com/</x:v>
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
       </x:c>
       <x:c r="J35" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026年10月（具体日期未公布）</x:v>
       </x:c>
       <x:c r="K35" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；官方流程包含在线测评</x:v>
       </x:c>
       <x:c r="L35" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
       </x:c>
       <x:c r="M35" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N35" s="4" t="str"/>
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N35" s="4" t="str">
+        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
+      </x:c>
       <x:c r="O35" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P35" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
+      </x:c>
+      <x:c r="P35" s="14" t="str">
+        <x:v>A-企业官方校招网站与职位页已核验</x:v>
       </x:c>
       <x:c r="Q35" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="54" customHeight="1">
@@ -2358,42 +2362,44 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B36" s="4" t="str">
-        <x:v>虹软科技</x:v>
+        <x:v>阿里巴巴-阿里星计划</x:v>
       </x:c>
       <x:c r="C36" s="4" t="str">
-        <x:v>计算机视觉/软件</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D36" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
-        <x:v>杭州、上海、南京等</x:v>
+        <x:v>杭州、北京、上海、深圳等</x:v>
       </x:c>
       <x:c r="F36" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G36" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H36" s="4" t="str">
-        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
+        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
       </x:c>
       <x:c r="I36" s="15" t="str">
-        <x:v>https://hr.arcsoft.com.cn/</x:v>
+        <x:v>https://talent.alibaba.com/campus/</x:v>
       </x:c>
       <x:c r="J36" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K36" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L36" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M36" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N36" s="4" t="str"/>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N36" s="4" t="str">
+        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
+      </x:c>
       <x:c r="O36" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -2409,16 +2415,16 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B37" s="4" t="str">
-        <x:v>汇川技术</x:v>
+        <x:v>贝恩公司</x:v>
       </x:c>
       <x:c r="C37" s="4" t="str">
-        <x:v>工业自动化/新能源</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D37" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E37" s="4" t="str">
-        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
+        <x:v>北京、上海、香港等</x:v>
       </x:c>
       <x:c r="F37" s="4" t="str">
         <x:v>正式批/秋招</x:v>
@@ -2427,16 +2433,16 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
-        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
+        <x:v>助理咨询顾问等</x:v>
       </x:c>
       <x:c r="I37" s="15" t="str">
-        <x:v>https://career.inovance.com/</x:v>
+        <x:v>https://www.bain.com/careers/</x:v>
       </x:c>
       <x:c r="J37" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K37" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L37" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2460,28 +2466,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B38" s="4" t="str">
-        <x:v>伽利略-星途星锐计划</x:v>
+        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
       </x:c>
       <x:c r="C38" s="4" t="str">
-        <x:v>科技/综合</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="D38" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E38" s="4" t="str">
-        <x:v>以项目职位页为准</x:v>
+        <x:v>上海、北京等</x:v>
       </x:c>
       <x:c r="F38" s="4" t="str">
-        <x:v>人才专项</x:v>
+        <x:v>顶尖技术专项/提前批</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H38" s="4" t="str">
-        <x:v>以官方项目页为准</x:v>
-      </x:c>
-      <x:c r="I38" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
+      </x:c>
+      <x:c r="I38" s="15" t="str">
+        <x:v>https://jobs.bilibili.com/</x:v>
       </x:c>
       <x:c r="J38" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2496,13 +2502,13 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N38" s="4" t="str">
-        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
+        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
       </x:c>
       <x:c r="O38" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P38" s="19" t="str">
-        <x:v>C-主体与入口需二次确认</x:v>
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q38" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -2513,52 +2519,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B39" s="4" t="str">
-        <x:v>京东-TET管理培训生</x:v>
+        <x:v>东风汽车-全球博士人才</x:v>
       </x:c>
       <x:c r="C39" s="4" t="str">
-        <x:v>互联网/零售</x:v>
+        <x:v>汽车/央企</x:v>
       </x:c>
       <x:c r="D39" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
-        <x:v>北京及业务所在城市</x:v>
+        <x:v>武汉、广州、十堰及全国研发基地</x:v>
       </x:c>
       <x:c r="F39" s="4" t="str">
-        <x:v>管培生专项/提前批</x:v>
+        <x:v>博士专项</x:v>
       </x:c>
       <x:c r="G39" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026届及以后博士</x:v>
       </x:c>
       <x:c r="H39" s="4" t="str">
-        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
+        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
       </x:c>
       <x:c r="I39" s="15" t="str">
-        <x:v>https://campus.jd.com/</x:v>
+        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
       </x:c>
       <x:c r="J39" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K39" s="4" t="str">
-        <x:v>含测评，笔试以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L39" s="4" t="str">
-        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M39" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N39" s="4" t="str">
-        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
+        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
       </x:c>
       <x:c r="O39" s="15" t="str">
-        <x:v>https://campus.jd.com/#/</x:v>
-      </x:c>
-      <x:c r="P39" s="14" t="str">
-        <x:v>A-企业官网校招页面已核验</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P39" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q39" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="54" customHeight="1">
@@ -2566,28 +2572,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B40" s="4" t="str">
-        <x:v>科大讯飞-飞凡计划</x:v>
+        <x:v>度小满-博士后人才招聘</x:v>
       </x:c>
       <x:c r="C40" s="4" t="str">
-        <x:v>AI/软件</x:v>
+        <x:v>金融科技</x:v>
       </x:c>
       <x:c r="D40" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E40" s="4" t="str">
-        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F40" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>博士后专项</x:v>
       </x:c>
       <x:c r="G40" s="4" t="str">
-        <x:v>2026/2027届</x:v>
+        <x:v>2025/2026/2027届博士</x:v>
       </x:c>
       <x:c r="H40" s="4" t="str">
-        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
+        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
       </x:c>
       <x:c r="I40" s="15" t="str">
-        <x:v>https://campus.iflytek.com/</x:v>
+        <x:v>https://campus.duxiaoman.com/</x:v>
       </x:c>
       <x:c r="J40" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2602,7 +2608,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N40" s="4" t="str">
-        <x:v>专项岗位与常规校招可能并行。</x:v>
+        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
       </x:c>
       <x:c r="O40" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -2619,28 +2625,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B41" s="4" t="str">
-        <x:v>理想汽车</x:v>
+        <x:v>多益网络</x:v>
       </x:c>
       <x:c r="C41" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D41" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E41" s="4" t="str">
-        <x:v>北京、上海、常州等</x:v>
+        <x:v>广州、武汉、成都等</x:v>
       </x:c>
       <x:c r="F41" s="4" t="str">
-        <x:v>暑期实习转正通道</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G41" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H41" s="4" t="str">
-        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
+        <x:v>程序、策划、美术、运营、市场及职能</x:v>
       </x:c>
       <x:c r="I41" s="15" t="str">
-        <x:v>https://career.lixiang.com/campus</x:v>
+        <x:v>https://www.duoyi.com/job/</x:v>
       </x:c>
       <x:c r="J41" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2655,7 +2661,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N41" s="4" t="str">
-        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
+        <x:v>岗位可能按城市提前关闭。</x:v>
       </x:c>
       <x:c r="O41" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -2672,42 +2678,44 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B42" s="4" t="str">
-        <x:v>莉莉丝游戏</x:v>
+        <x:v>海天集团-高潜专项</x:v>
       </x:c>
       <x:c r="C42" s="4" t="str">
-        <x:v>游戏</x:v>
+        <x:v>工业制造</x:v>
       </x:c>
       <x:c r="D42" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E42" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>宁波及全国基地</x:v>
       </x:c>
       <x:c r="F42" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>高潜人才专项/提前批</x:v>
       </x:c>
       <x:c r="G42" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H42" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
+        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
       </x:c>
       <x:c r="I42" s="15" t="str">
-        <x:v>https://campus.lilith.com/</x:v>
+        <x:v>https://www.haitian.com/careers/</x:v>
       </x:c>
       <x:c r="J42" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K42" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L42" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M42" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N42" s="4" t="str"/>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N42" s="4" t="str">
+        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
+      </x:c>
       <x:c r="O42" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -2723,34 +2731,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B43" s="4" t="str">
-        <x:v>麦肯锡</x:v>
+        <x:v>赫力昂-销售先锋计划</x:v>
       </x:c>
       <x:c r="C43" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>消费健康/医药</x:v>
       </x:c>
       <x:c r="D43" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E43" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>全国重点城市</x:v>
       </x:c>
       <x:c r="F43" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>管培/销售专项</x:v>
       </x:c>
       <x:c r="G43" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H43" s="4" t="str">
-        <x:v>商业分析师、咨询及专业岗位</x:v>
+        <x:v>医药及消费健康销售、商业运营方向</x:v>
       </x:c>
       <x:c r="I43" s="15" t="str">
-        <x:v>https://www.mckinsey.com/careers</x:v>
+        <x:v>https://careers.haleon.com/</x:v>
       </x:c>
       <x:c r="J43" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K43" s="4" t="str">
-        <x:v>通常含测评/案例面试；以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L43" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2774,16 +2782,16 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B44" s="4" t="str">
-        <x:v>拼多多</x:v>
+        <x:v>虹软科技</x:v>
       </x:c>
       <x:c r="C44" s="4" t="str">
-        <x:v>互联网/电商</x:v>
+        <x:v>计算机视觉/软件</x:v>
       </x:c>
       <x:c r="D44" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E44" s="4" t="str">
-        <x:v>上海、广州等，以岗位页为准</x:v>
+        <x:v>杭州、上海、南京等</x:v>
       </x:c>
       <x:c r="F44" s="4" t="str">
         <x:v>提前批</x:v>
@@ -2792,13 +2800,13 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H44" s="4" t="str">
-        <x:v>技术、算法、产品、运营、商业分析等</x:v>
+        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
       </x:c>
       <x:c r="I44" s="15" t="str">
-        <x:v>https://careers.pinduoduo.com/campus/</x:v>
+        <x:v>https://hr.arcsoft.com.cn/</x:v>
       </x:c>
       <x:c r="J44" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K44" s="4" t="str">
         <x:v>按岗位，官方未统一说明</x:v>
@@ -2807,11 +2815,9 @@
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M44" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N44" s="4" t="str">
-        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
-      </x:c>
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N44" s="4" t="str"/>
       <x:c r="O44" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -2827,16 +2833,16 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B45" s="4" t="str">
-        <x:v>启林投资</x:v>
+        <x:v>汇川技术</x:v>
       </x:c>
       <x:c r="C45" s="4" t="str">
-        <x:v>量化金融/资管</x:v>
+        <x:v>工业自动化/新能源</x:v>
       </x:c>
       <x:c r="D45" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E45" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
       </x:c>
       <x:c r="F45" s="4" t="str">
         <x:v>正式批/秋招</x:v>
@@ -2845,16 +2851,16 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H45" s="4" t="str">
-        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
+        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
       </x:c>
       <x:c r="I45" s="15" t="str">
-        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
+        <x:v>https://career.inovance.com/</x:v>
       </x:c>
       <x:c r="J45" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K45" s="4" t="str">
-        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L45" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2862,9 +2868,7 @@
       <x:c r="M45" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N45" s="4" t="str">
-        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
-      </x:c>
+      <x:c r="N45" s="4" t="str"/>
       <x:c r="O45" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -2880,28 +2884,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B46" s="4" t="str">
-        <x:v>商汤科技-无限原力计划</x:v>
+        <x:v>伽利略-星途星锐计划</x:v>
       </x:c>
       <x:c r="C46" s="4" t="str">
-        <x:v>AI/计算机视觉</x:v>
+        <x:v>科技/综合</x:v>
       </x:c>
       <x:c r="D46" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E46" s="4" t="str">
-        <x:v>上海、北京、深圳、杭州等</x:v>
+        <x:v>以项目职位页为准</x:v>
       </x:c>
       <x:c r="F46" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>人才专项</x:v>
       </x:c>
       <x:c r="G46" s="4" t="str">
-        <x:v>2027/2028届</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H46" s="4" t="str">
-        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
-      </x:c>
-      <x:c r="I46" s="15" t="str">
-        <x:v>https://joinus.sensetime.com/</x:v>
+        <x:v>以官方项目页为准</x:v>
+      </x:c>
+      <x:c r="I46" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J46" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2916,13 +2920,13 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N46" s="4" t="str">
-        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
+        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
       </x:c>
       <x:c r="O46" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P46" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>C-主体与入口需二次确认</x:v>
       </x:c>
       <x:c r="Q46" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -2933,52 +2937,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B47" s="4" t="str">
-        <x:v>腾讯-青云计划</x:v>
+        <x:v>京东-TET管理培训生</x:v>
       </x:c>
       <x:c r="C47" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>互联网/零售</x:v>
       </x:c>
       <x:c r="D47" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E47" s="4" t="str">
-        <x:v>深圳、北京、上海等</x:v>
+        <x:v>北京及业务所在城市</x:v>
       </x:c>
       <x:c r="F47" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>管培生专项/提前批</x:v>
       </x:c>
       <x:c r="G47" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H47" s="4" t="str">
-        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
+        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
       </x:c>
       <x:c r="I47" s="15" t="str">
-        <x:v>https://join.qq.com/</x:v>
+        <x:v>https://campus.jd.com/</x:v>
       </x:c>
       <x:c r="J47" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K47" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>含测评，笔试以通知为准</x:v>
       </x:c>
       <x:c r="L47" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
       </x:c>
       <x:c r="M47" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N47" s="4" t="str">
-        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
+        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
       </x:c>
       <x:c r="O47" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P47" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://campus.jd.com/#/</x:v>
+      </x:c>
+      <x:c r="P47" s="14" t="str">
+        <x:v>A-企业官网校招页面已核验</x:v>
       </x:c>
       <x:c r="Q47" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="54" customHeight="1">
@@ -2986,28 +2990,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B48" s="4" t="str">
-        <x:v>天锐星通</x:v>
+        <x:v>科大讯飞-飞凡计划</x:v>
       </x:c>
       <x:c r="C48" s="4" t="str">
-        <x:v>卫星通信/相控阵</x:v>
+        <x:v>AI/软件</x:v>
       </x:c>
       <x:c r="D48" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E48" s="4" t="str">
-        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
+        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
       </x:c>
       <x:c r="F48" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G48" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026/2027届</x:v>
       </x:c>
       <x:c r="H48" s="4" t="str">
-        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
+        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
       </x:c>
       <x:c r="I48" s="15" t="str">
-        <x:v>https://www.tianruixing.com/</x:v>
+        <x:v>https://campus.iflytek.com/</x:v>
       </x:c>
       <x:c r="J48" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3022,7 +3026,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N48" s="4" t="str">
-        <x:v>官网入口与具体岗位需投前复核。</x:v>
+        <x:v>专项岗位与常规校招可能并行。</x:v>
       </x:c>
       <x:c r="O48" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3036,52 +3040,52 @@
     </x:row>
     <x:row r="49" ht="54" customHeight="1">
       <x:c r="A49" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B49" s="4" t="str">
-        <x:v>网易游戏雷火</x:v>
+        <x:v>理想汽车</x:v>
       </x:c>
       <x:c r="C49" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D49" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E49" s="4" t="str">
-        <x:v>杭州、上海等，以岗位页为准</x:v>
+        <x:v>北京、上海、常州等</x:v>
       </x:c>
       <x:c r="F49" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>暑期实习转正通道</x:v>
       </x:c>
       <x:c r="G49" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H49" s="4" t="str">
-        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
+        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
       </x:c>
       <x:c r="I49" s="15" t="str">
-        <x:v>https://leihuo.163.com/campus/#/full</x:v>
+        <x:v>https://career.lixiang.com/campus</x:v>
       </x:c>
       <x:c r="J49" s="4" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K49" s="4" t="str">
-        <x:v>部分岗位免笔试；部分可直通面试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L49" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M49" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N49" s="4" t="str">
-        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
+        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
       </x:c>
       <x:c r="O49" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P49" s="14" t="str">
-        <x:v>A-官方招聘官网已核验</x:v>
+      <x:c r="P49" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q49" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3092,44 +3096,42 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B50" s="4" t="str">
-        <x:v>小鹏集团</x:v>
+        <x:v>莉莉丝游戏</x:v>
       </x:c>
       <x:c r="C50" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>游戏</x:v>
       </x:c>
       <x:c r="D50" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E50" s="4" t="str">
-        <x:v>广州、北京、上海、深圳、武汉等</x:v>
+        <x:v>上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F50" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G50" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H50" s="4" t="str">
-        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
+        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
       </x:c>
       <x:c r="I50" s="15" t="str">
-        <x:v>https://join.xiaopeng.com/campus</x:v>
+        <x:v>https://campus.lilith.com/</x:v>
       </x:c>
       <x:c r="J50" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="K50" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L50" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M50" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N50" s="4" t="str">
-        <x:v>营销服与技术岗位可能分项目发布。</x:v>
-      </x:c>
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N50" s="4" t="str"/>
       <x:c r="O50" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3145,16 +3147,16 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B51" s="4" t="str">
-        <x:v>芯动科技</x:v>
+        <x:v>麦肯锡</x:v>
       </x:c>
       <x:c r="C51" s="4" t="str">
-        <x:v>半导体/IP设计</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D51" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E51" s="4" t="str">
-        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F51" s="4" t="str">
         <x:v>正式批/秋招</x:v>
@@ -3163,16 +3165,16 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H51" s="4" t="str">
-        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
+        <x:v>商业分析师、咨询及专业岗位</x:v>
       </x:c>
       <x:c r="I51" s="15" t="str">
-        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
+        <x:v>https://www.mckinsey.com/careers</x:v>
       </x:c>
       <x:c r="J51" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K51" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>通常含测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L51" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3193,52 +3195,52 @@
     </x:row>
     <x:row r="52" ht="54" customHeight="1">
       <x:c r="A52" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B52" s="4" t="str">
-        <x:v>芯迈半导体</x:v>
+        <x:v>拼多多</x:v>
       </x:c>
       <x:c r="C52" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>互联网/电商</x:v>
       </x:c>
       <x:c r="D52" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E52" s="4" t="str">
-        <x:v>杭州、上海、深圳、成都</x:v>
+        <x:v>上海、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F52" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G52" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H52" s="4" t="str">
-        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
+        <x:v>技术、算法、产品、运营、商业分析等</x:v>
       </x:c>
       <x:c r="I52" s="15" t="str">
-        <x:v>https://www.silicon-magic.com/joinus</x:v>
+        <x:v>https://careers.pinduoduo.com/campus/</x:v>
       </x:c>
       <x:c r="J52" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K52" s="4" t="str">
-        <x:v>官方未说明；公开流程未列笔试</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L52" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M52" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N52" s="4" t="str">
-        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
+        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
       </x:c>
       <x:c r="O52" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P52" s="14" t="str">
-        <x:v>A-企业官网与公开公告已核验</x:v>
+      <x:c r="P52" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q52" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3249,52 +3251,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B53" s="4" t="str">
-        <x:v>新易盛</x:v>
+        <x:v>启林投资</x:v>
       </x:c>
       <x:c r="C53" s="4" t="str">
-        <x:v>光通信/半导体</x:v>
+        <x:v>量化金融/资管</x:v>
       </x:c>
       <x:c r="D53" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E53" s="4" t="str">
-        <x:v>成都、苏州等，以岗位页为准</x:v>
+        <x:v>上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F53" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G53" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H53" s="4" t="str">
-        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
+        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
       </x:c>
       <x:c r="I53" s="15" t="str">
-        <x:v>https://www.eoptolink.com/</x:v>
+        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
       </x:c>
       <x:c r="J53" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K53" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
       </x:c>
       <x:c r="L53" s="4" t="str">
-        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M53" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N53" s="4" t="str">
-        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
       </x:c>
       <x:c r="O53" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P53" s="18" t="str">
-        <x:v>B-高校/招聘平台转载，投前复核</x:v>
+      <x:c r="P53" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q53" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="54" customHeight="1">
@@ -3302,34 +3304,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B54" s="4" t="str">
-        <x:v>元戎启行</x:v>
+        <x:v>商汤科技-无限原力计划</x:v>
       </x:c>
       <x:c r="C54" s="4" t="str">
-        <x:v>自动驾驶</x:v>
+        <x:v>AI/计算机视觉</x:v>
       </x:c>
       <x:c r="D54" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E54" s="4" t="str">
-        <x:v>深圳、北京等</x:v>
+        <x:v>上海、北京、深圳、杭州等</x:v>
       </x:c>
       <x:c r="F54" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G54" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027/2028届</x:v>
       </x:c>
       <x:c r="H54" s="4" t="str">
-        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
+        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
       </x:c>
       <x:c r="I54" s="15" t="str">
-        <x:v>https://www.deeproute.ai/join-us</x:v>
+        <x:v>https://joinus.sensetime.com/</x:v>
       </x:c>
       <x:c r="J54" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K54" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L54" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3337,7 +3339,9 @@
       <x:c r="M54" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N54" s="4" t="str"/>
+      <x:c r="N54" s="4" t="str">
+        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
+      </x:c>
       <x:c r="O54" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3353,28 +3357,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B55" s="4" t="str">
-        <x:v>圆通速递</x:v>
+        <x:v>腾讯-青云计划</x:v>
       </x:c>
       <x:c r="C55" s="4" t="str">
-        <x:v>物流/供应链</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D55" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E55" s="4" t="str">
-        <x:v>上海及全国网络</x:v>
+        <x:v>深圳、北京、上海等</x:v>
       </x:c>
       <x:c r="F55" s="4" t="str">
-        <x:v>正式批/校招</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G55" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H55" s="4" t="str">
-        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
+        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
       </x:c>
       <x:c r="I55" s="15" t="str">
-        <x:v>https://hr.yto.net.cn/</x:v>
+        <x:v>https://join.qq.com/</x:v>
       </x:c>
       <x:c r="J55" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3388,7 +3392,9 @@
       <x:c r="M55" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N55" s="4" t="str"/>
+      <x:c r="N55" s="4" t="str">
+        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
+      </x:c>
       <x:c r="O55" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3404,34 +3410,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B56" s="4" t="str">
-        <x:v>长亭科技</x:v>
+        <x:v>天锐星通</x:v>
       </x:c>
       <x:c r="C56" s="4" t="str">
-        <x:v>网络安全</x:v>
+        <x:v>卫星通信/相控阵</x:v>
       </x:c>
       <x:c r="D56" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E56" s="4" t="str">
-        <x:v>北京、上海等，以岗位页为准</x:v>
+        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F56" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G56" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H56" s="4" t="str">
-        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
+        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
       </x:c>
       <x:c r="I56" s="15" t="str">
-        <x:v>https://job.chaitin.cn/</x:v>
+        <x:v>https://www.tianruixing.com/</x:v>
       </x:c>
       <x:c r="J56" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K56" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L56" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3439,7 +3445,9 @@
       <x:c r="M56" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N56" s="4" t="str"/>
+      <x:c r="N56" s="4" t="str">
+        <x:v>官网入口与具体岗位需投前复核。</x:v>
+      </x:c>
       <x:c r="O56" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3452,50 +3460,52 @@
     </x:row>
     <x:row r="57" ht="54" customHeight="1">
       <x:c r="A57" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B57" s="4" t="str">
-        <x:v>智元机器人-优才计划</x:v>
+        <x:v>网易游戏雷火</x:v>
       </x:c>
       <x:c r="C57" s="4" t="str">
-        <x:v>具身智能/机器人</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D57" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E57" s="4" t="str">
-        <x:v>上海、北京、深圳等</x:v>
+        <x:v>杭州、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F57" s="4" t="str">
-        <x:v>优才专项/提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G57" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H57" s="4" t="str">
-        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
+        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
       </x:c>
       <x:c r="I57" s="15" t="str">
-        <x:v>https://www.agibot.com/recruit</x:v>
+        <x:v>https://leihuo.163.com/campus/#/full</x:v>
       </x:c>
       <x:c r="J57" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="K57" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>部分岗位免笔试；部分可直通面试</x:v>
       </x:c>
       <x:c r="L57" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M57" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N57" s="4" t="str"/>
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N57" s="4" t="str">
+        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
+      </x:c>
       <x:c r="O57" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P57" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P57" s="14" t="str">
+        <x:v>A-官方招聘官网已核验</x:v>
       </x:c>
       <x:c r="Q57" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3506,28 +3516,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B58" s="4" t="str">
-        <x:v>中国电信天翼云-超级优才</x:v>
+        <x:v>小鹏集团</x:v>
       </x:c>
       <x:c r="C58" s="4" t="str">
-        <x:v>云计算/央企</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D58" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E58" s="4" t="str">
-        <x:v>北京、上海、广州、成都及全国机构</x:v>
+        <x:v>广州、北京、上海、深圳、武汉等</x:v>
       </x:c>
       <x:c r="F58" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G58" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H58" s="4" t="str">
-        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
+        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
       </x:c>
       <x:c r="I58" s="15" t="str">
-        <x:v>https://www.ctyun.cn/about/recruit</x:v>
+        <x:v>https://join.xiaopeng.com/campus</x:v>
       </x:c>
       <x:c r="J58" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3542,7 +3552,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N58" s="4" t="str">
-        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
+        <x:v>营销服与技术岗位可能分项目发布。</x:v>
       </x:c>
       <x:c r="O58" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3559,49 +3569,47 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B59" s="4" t="str">
-        <x:v>中科光电</x:v>
+        <x:v>芯动科技</x:v>
       </x:c>
       <x:c r="C59" s="4" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>半导体/IP设计</x:v>
       </x:c>
       <x:c r="D59" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E59" s="4" t="str">
-        <x:v>以职位公告为准</x:v>
+        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
       </x:c>
       <x:c r="F59" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G59" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H59" s="4" t="str">
-        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
+        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
       </x:c>
       <x:c r="I59" s="15" t="str">
-        <x:v>https://job.cn-amd.com/</x:v>
+        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
       </x:c>
       <x:c r="J59" s="4" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K59" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L59" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M59" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N59" s="4" t="str">
-        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
-      </x:c>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N59" s="4" t="str"/>
       <x:c r="O59" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P59" s="19" t="str">
-        <x:v>C-名称需二次确认</x:v>
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q59" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3609,108 +3617,108 @@
     </x:row>
     <x:row r="60" ht="54" customHeight="1">
       <x:c r="A60" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B60" s="4" t="str">
-        <x:v>中兴微电子-未来领军计划</x:v>
+        <x:v>芯迈半导体</x:v>
       </x:c>
       <x:c r="C60" s="4" t="str">
-        <x:v>半导体/通信</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D60" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E60" s="4" t="str">
-        <x:v>深圳、西安、南京、上海等</x:v>
+        <x:v>杭州、上海、深圳、成都</x:v>
       </x:c>
       <x:c r="F60" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G60" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H60" s="4" t="str">
-        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
+        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
       </x:c>
       <x:c r="I60" s="15" t="str">
-        <x:v>https://job.zte.com.cn/</x:v>
+        <x:v>https://www.silicon-magic.com/joinus</x:v>
       </x:c>
       <x:c r="J60" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K60" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未说明；公开流程未列笔试</x:v>
       </x:c>
       <x:c r="L60" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M60" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N60" s="4" t="str">
-        <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
+        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
       </x:c>
       <x:c r="O60" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P60" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P60" s="14" t="str">
+        <x:v>A-企业官网与公开公告已核验</x:v>
       </x:c>
       <x:c r="Q60" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="54" customHeight="1">
-      <x:c r="A61" s="16" t="str">
+      <x:c r="A61" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B61" s="16" t="str">
-        <x:v>字节跳动-AI产品经理早鸟通道</x:v>
-      </x:c>
-      <x:c r="C61" s="16" t="str">
-        <x:v>互联网/AI</x:v>
-      </x:c>
-      <x:c r="D61" s="16" t="str">
+      <x:c r="B61" s="4" t="str">
+        <x:v>新易盛</x:v>
+      </x:c>
+      <x:c r="C61" s="4" t="str">
+        <x:v>光通信/半导体</x:v>
+      </x:c>
+      <x:c r="D61" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E61" s="16" t="str">
-        <x:v>北京、上海、深圳</x:v>
-      </x:c>
-      <x:c r="F61" s="16" t="str">
-        <x:v>早鸟专项/提前批</x:v>
-      </x:c>
-      <x:c r="G61" s="16" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H61" s="16" t="str">
-        <x:v>AI产品经理、智能体及大模型产品方向</x:v>
-      </x:c>
-      <x:c r="I61" s="17" t="str">
-        <x:v>https://jobs.bytedance.com/campus/</x:v>
-      </x:c>
-      <x:c r="J61" s="16" t="str">
-        <x:v>2026-08-02</x:v>
-      </x:c>
-      <x:c r="K61" s="16" t="str">
-        <x:v>按岗位，未统一公布</x:v>
-      </x:c>
-      <x:c r="L61" s="16" t="str">
-        <x:v>已截止（2026-08-02）；原公告与官方投递入口保留</x:v>
-      </x:c>
-      <x:c r="M61" s="16" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N61" s="16" t="str">
-        <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
-      </x:c>
-      <x:c r="O61" s="17" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P61" s="18" t="str">
-        <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q61" s="16" t="str">
-        <x:v>2026-08-03</x:v>
+      <x:c r="E61" s="4" t="str">
+        <x:v>成都、苏州等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F61" s="4" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G61" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H61" s="4" t="str">
+        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
+      </x:c>
+      <x:c r="I61" s="15" t="str">
+        <x:v>https://www.eoptolink.com/</x:v>
+      </x:c>
+      <x:c r="J61" s="4" t="str">
+        <x:v>2026-08-20</x:v>
+      </x:c>
+      <x:c r="K61" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L61" s="4" t="str">
+        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
+      </x:c>
+      <x:c r="M61" s="4" t="str">
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N61" s="4" t="str">
+        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+      </x:c>
+      <x:c r="O61" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P61" s="16" t="str">
+        <x:v>B-高校/招聘平台转载，投前复核</x:v>
+      </x:c>
+      <x:c r="Q61" s="4" t="str">
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="54" customHeight="1">
@@ -3718,40 +3726,40 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B62" s="4" t="str">
-        <x:v>BCG波士顿咨询</x:v>
+        <x:v>元戎启行</x:v>
       </x:c>
       <x:c r="C62" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>自动驾驶</x:v>
       </x:c>
       <x:c r="D62" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E62" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>深圳、北京等</x:v>
       </x:c>
       <x:c r="F62" s="4" t="str">
-        <x:v>正式批/中国区校招</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G62" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H62" s="4" t="str">
-        <x:v>咨询顾问及相关专业岗位</x:v>
+        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
       </x:c>
       <x:c r="I62" s="15" t="str">
-        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
+        <x:v>https://www.deeproute.ai/join-us</x:v>
       </x:c>
       <x:c r="J62" s="4" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K62" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L62" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M62" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N62" s="4" t="str"/>
       <x:c r="O62" s="15" t="str">
@@ -3769,28 +3777,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B63" s="4" t="str">
-        <x:v>OPPO</x:v>
+        <x:v>圆通速递</x:v>
       </x:c>
       <x:c r="C63" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>物流/供应链</x:v>
       </x:c>
       <x:c r="D63" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E63" s="4" t="str">
-        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
+        <x:v>上海及全国网络</x:v>
       </x:c>
       <x:c r="F63" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
+        <x:v>正式批/校招</x:v>
       </x:c>
       <x:c r="G63" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H63" s="4" t="str">
-        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
+        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
       </x:c>
       <x:c r="I63" s="15" t="str">
-        <x:v>https://careers.oppo.com/campus</x:v>
+        <x:v>https://hr.yto.net.cn/</x:v>
       </x:c>
       <x:c r="J63" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3804,9 +3812,7 @@
       <x:c r="M63" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N63" s="4" t="str">
-        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
-      </x:c>
+      <x:c r="N63" s="4" t="str"/>
       <x:c r="O63" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3822,34 +3828,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B64" s="4" t="str">
-        <x:v>Tap4Fun</x:v>
+        <x:v>长亭科技</x:v>
       </x:c>
       <x:c r="C64" s="4" t="str">
-        <x:v>游戏</x:v>
+        <x:v>网络安全</x:v>
       </x:c>
       <x:c r="D64" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E64" s="4" t="str">
-        <x:v>成都等</x:v>
+        <x:v>北京、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F64" s="4" t="str">
-        <x:v>实习转正通道</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G64" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H64" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
+        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
       </x:c>
       <x:c r="I64" s="15" t="str">
-        <x:v>https://www.tap4fun.com/careers</x:v>
+        <x:v>https://job.chaitin.cn/</x:v>
       </x:c>
       <x:c r="J64" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K64" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L64" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3857,9 +3863,7 @@
       <x:c r="M64" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N64" s="4" t="str">
-        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
-      </x:c>
+      <x:c r="N64" s="4" t="str"/>
       <x:c r="O64" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3872,125 +3876,123 @@
     </x:row>
     <x:row r="65" ht="54" customHeight="1">
       <x:c r="A65" s="4" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B65" s="4" t="str">
-        <x:v>航天科技集团五院502所</x:v>
+        <x:v>智元机器人-优才计划</x:v>
       </x:c>
       <x:c r="C65" s="4" t="str">
-        <x:v>航天/自动控制</x:v>
+        <x:v>具身智能/机器人</x:v>
       </x:c>
       <x:c r="D65" s="4" t="str">
-        <x:v>事业单位/央企院所</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E65" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>上海、北京、深圳等</x:v>
       </x:c>
       <x:c r="F65" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>优才专项/提前批</x:v>
       </x:c>
       <x:c r="G65" s="4" t="str">
-        <x:v>硕士/博士为主，以岗位为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H65" s="4" t="str">
-        <x:v>导航制导与控制、自动化、电子、通信、计算机、软件、机械等</x:v>
+        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
       </x:c>
       <x:c r="I65" s="15" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
+        <x:v>https://www.agibot.com/recruit</x:v>
       </x:c>
       <x:c r="J65" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K65" s="4" t="str">
-        <x:v>未统一公布</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L65" s="4" t="str">
-        <x:v>公开公告显示开放；投前确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M65" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N65" s="4" t="str">
-        <x:v>研究所岗位通常有专业、学历、政审及保密要求。</x:v>
-      </x:c>
+      <x:c r="N65" s="4" t="str"/>
       <x:c r="O65" s="15" t="str">
-        <x:v>https://www.baidu.com/s?wd=%E4%BA%94%E9%99%A2502%E6%89%802027%E5%B1%8A%E6%A0%A1%E6%8B%9B</x:v>
-      </x:c>
-      <x:c r="P65" s="18" t="str">
-        <x:v>B-高校就业网公开公告</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P65" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q65" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="54" customHeight="1">
-      <x:c r="A66" s="16" t="str">
-        <x:v>2026-07-17</x:v>
-      </x:c>
-      <x:c r="B66" s="16" t="str">
-        <x:v>鹰角网络</x:v>
-      </x:c>
-      <x:c r="C66" s="16" t="str">
-        <x:v>游戏</x:v>
-      </x:c>
-      <x:c r="D66" s="16" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E66" s="16" t="str">
-        <x:v>上海</x:v>
-      </x:c>
-      <x:c r="F66" s="16" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G66" s="16" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H66" s="16" t="str">
-        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
-      </x:c>
-      <x:c r="I66" s="17" t="str">
-        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
-      </x:c>
-      <x:c r="J66" s="16" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K66" s="16" t="str">
-        <x:v>否；安排笔试/面试</x:v>
-      </x:c>
-      <x:c r="L66" s="16" t="str">
-        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M66" s="16" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N66" s="16" t="str">
-        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
-      </x:c>
-      <x:c r="O66" s="17" t="str">
-        <x:v>https://campus.hypergryph.com/</x:v>
-      </x:c>
-      <x:c r="P66" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q66" s="16" t="str">
-        <x:v>2026-08-03</x:v>
+      <x:c r="A66" s="4" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B66" s="4" t="str">
+        <x:v>中国电信天翼云-超级优才</x:v>
+      </x:c>
+      <x:c r="C66" s="4" t="str">
+        <x:v>云计算/央企</x:v>
+      </x:c>
+      <x:c r="D66" s="4" t="str">
+        <x:v>央企</x:v>
+      </x:c>
+      <x:c r="E66" s="4" t="str">
+        <x:v>北京、上海、广州、成都及全国机构</x:v>
+      </x:c>
+      <x:c r="F66" s="4" t="str">
+        <x:v>人才专项/提前批</x:v>
+      </x:c>
+      <x:c r="G66" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H66" s="4" t="str">
+        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
+      </x:c>
+      <x:c r="I66" s="15" t="str">
+        <x:v>https://www.ctyun.cn/about/recruit</x:v>
+      </x:c>
+      <x:c r="J66" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K66" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L66" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M66" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N66" s="4" t="str">
+        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
+      </x:c>
+      <x:c r="O66" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P66" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q66" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="54" customHeight="1">
       <x:c r="A67" s="4" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B67" s="4" t="str">
-        <x:v>联发科技</x:v>
+        <x:v>中科光电</x:v>
       </x:c>
       <x:c r="C67" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D67" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E67" s="4" t="str">
-        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
+        <x:v>以职位公告为准</x:v>
       </x:c>
       <x:c r="F67" s="4" t="str">
         <x:v>提前批</x:v>
@@ -3999,31 +4001,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H67" s="4" t="str">
-        <x:v>软件类、通信类、IC类</x:v>
+        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
       </x:c>
       <x:c r="I67" s="15" t="str">
-        <x:v>https://mediatek.zhiye.com/</x:v>
+        <x:v>https://job.cn-amd.com/</x:v>
       </x:c>
       <x:c r="J67" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K67" s="4" t="str">
-        <x:v>否；明确安排7-8月笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L67" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M67" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N67" s="4" t="str">
-        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
+        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
       </x:c>
       <x:c r="O67" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P67" s="14" t="str">
-        <x:v>A-官方招聘公告已核验</x:v>
+      <x:c r="P67" s="19" t="str">
+        <x:v>C-名称需二次确认</x:v>
       </x:c>
       <x:c r="Q67" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4031,211 +4033,209 @@
     </x:row>
     <x:row r="68" ht="54" customHeight="1">
       <x:c r="A68" s="4" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B68" s="4" t="str">
-        <x:v>DJI大疆</x:v>
+        <x:v>中兴微电子-未来领军计划</x:v>
       </x:c>
       <x:c r="C68" s="4" t="str">
-        <x:v>无人机/智能硬件</x:v>
+        <x:v>半导体/通信</x:v>
       </x:c>
       <x:c r="D68" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E68" s="4" t="str">
-        <x:v>深圳、东莞、上海、北京、西安等</x:v>
+        <x:v>深圳、西安、南京、上海等</x:v>
       </x:c>
       <x:c r="F68" s="4" t="str">
-        <x:v>正式批-拓疆者计划</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G68" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H68" s="4" t="str">
-        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
+        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
       </x:c>
       <x:c r="I68" s="15" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
+        <x:v>https://job.zte.com.cn/</x:v>
       </x:c>
       <x:c r="J68" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K68" s="4" t="str">
-        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L68" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M68" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N68" s="4" t="str">
-        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
+        <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
       </x:c>
       <x:c r="O68" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P68" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
+      <x:c r="P68" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q68" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="54" customHeight="1">
-      <x:c r="A69" s="4" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="B69" s="4" t="str">
-        <x:v>蔚来</x:v>
-      </x:c>
-      <x:c r="C69" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
-      </x:c>
-      <x:c r="D69" s="4" t="str">
+      <x:c r="A69" s="17" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B69" s="17" t="str">
+        <x:v>字节跳动-AI产品经理早鸟通道</x:v>
+      </x:c>
+      <x:c r="C69" s="17" t="str">
+        <x:v>互联网/AI</x:v>
+      </x:c>
+      <x:c r="D69" s="17" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E69" s="4" t="str">
-        <x:v>上海、合肥、北京、武汉、南京等</x:v>
-      </x:c>
-      <x:c r="F69" s="4" t="str">
-        <x:v>技术提前批</x:v>
-      </x:c>
-      <x:c r="G69" s="4" t="str">
-        <x:v>2024年9月-2027年8月毕业</x:v>
-      </x:c>
-      <x:c r="H69" s="4" t="str">
-        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
-      </x:c>
-      <x:c r="I69" s="15" t="str">
-        <x:v>https://campus.nio.com/</x:v>
-      </x:c>
-      <x:c r="J69" s="4" t="str">
-        <x:v>2026-08-14</x:v>
-      </x:c>
-      <x:c r="K69" s="4" t="str">
-        <x:v>否；有笔试/测评</x:v>
-      </x:c>
-      <x:c r="L69" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M69" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N69" s="4" t="str">
-        <x:v>最多同时申请3个岗位。</x:v>
-      </x:c>
-      <x:c r="O69" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P69" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q69" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+      <x:c r="E69" s="17" t="str">
+        <x:v>北京、上海、深圳</x:v>
+      </x:c>
+      <x:c r="F69" s="17" t="str">
+        <x:v>早鸟专项/提前批</x:v>
+      </x:c>
+      <x:c r="G69" s="17" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H69" s="17" t="str">
+        <x:v>AI产品经理、智能体及大模型产品方向</x:v>
+      </x:c>
+      <x:c r="I69" s="18" t="str">
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
+      </x:c>
+      <x:c r="J69" s="17" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+      <x:c r="K69" s="17" t="str">
+        <x:v>按岗位，未统一公布</x:v>
+      </x:c>
+      <x:c r="L69" s="17" t="str">
+        <x:v>已截止（2026-08-02）；原公告与官方投递入口保留</x:v>
+      </x:c>
+      <x:c r="M69" s="17" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N69" s="17" t="str">
+        <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
+      </x:c>
+      <x:c r="O69" s="18" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P69" s="16" t="str">
+        <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q69" s="17" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="54" customHeight="1">
       <x:c r="A70" s="4" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B70" s="4" t="str">
-        <x:v>北方华创</x:v>
+        <x:v>BCG波士顿咨询</x:v>
       </x:c>
       <x:c r="C70" s="4" t="str">
-        <x:v>半导体设备</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D70" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E70" s="4" t="str">
-        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F70" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/中国区校招</x:v>
       </x:c>
       <x:c r="G70" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H70" s="4" t="str">
-        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
+        <x:v>咨询顾问及相关专业岗位</x:v>
       </x:c>
       <x:c r="I70" s="15" t="str">
-        <x:v>https://career.naura.com/campus</x:v>
+        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
       </x:c>
       <x:c r="J70" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K70" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L70" s="4" t="str">
-        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M70" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N70" s="4" t="str">
-        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
-      </x:c>
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N70" s="4" t="str"/>
       <x:c r="O70" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P70" s="14" t="str">
-        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P70" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q70" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="54" customHeight="1">
       <x:c r="A71" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B71" s="4" t="str">
-        <x:v>百度</x:v>
+        <x:v>OPPO</x:v>
       </x:c>
       <x:c r="C71" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D71" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E71" s="4" t="str">
-        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
       </x:c>
       <x:c r="F71" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G71" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H71" s="4" t="str">
-        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
       </x:c>
       <x:c r="I71" s="15" t="str">
-        <x:v>https://talent.baidu.com/jobs</x:v>
+        <x:v>https://careers.oppo.com/campus</x:v>
       </x:c>
       <x:c r="J71" s="4" t="str">
-        <x:v>2027-06-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K71" s="4" t="str">
-        <x:v>部分免；并非所有候选人参加笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L71" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M71" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N71" s="4" t="str">
-        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
+        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
       </x:c>
       <x:c r="O71" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P71" s="14" t="str">
-        <x:v>A-官方招聘日历/官方来源已核验</x:v>
+      <x:c r="P71" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q71" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4243,264 +4243,264 @@
     </x:row>
     <x:row r="72" ht="54" customHeight="1">
       <x:c r="A72" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B72" s="4" t="str">
-        <x:v>中国航天科工集团第六研究院</x:v>
+        <x:v>Tap4Fun</x:v>
       </x:c>
       <x:c r="C72" s="4" t="str">
-        <x:v>航天/军工/动力系统</x:v>
+        <x:v>游戏</x:v>
       </x:c>
       <x:c r="D72" s="4" t="str">
-        <x:v>央企院所</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E72" s="4" t="str">
-        <x:v>呼和浩特及所属单位</x:v>
+        <x:v>成都等</x:v>
       </x:c>
       <x:c r="F72" s="4" t="str">
-        <x:v>提前批+暑期开放日</x:v>
+        <x:v>实习转正通道</x:v>
       </x:c>
       <x:c r="G72" s="4" t="str">
-        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H72" s="4" t="str">
-        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
+        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
       </x:c>
       <x:c r="I72" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
+        <x:v>https://www.tap4fun.com/careers</x:v>
       </x:c>
       <x:c r="J72" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K72" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L72" s="4" t="str">
-        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M72" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N72" s="4" t="str">
-        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
+        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
       </x:c>
       <x:c r="O72" s="15" t="str">
-        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
-      </x:c>
-      <x:c r="P72" s="18" t="str">
-        <x:v>B-高校就业网公开公告</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P72" s="19" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q72" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="54" customHeight="1">
       <x:c r="A73" s="4" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="B73" s="4" t="str">
-        <x:v>思瑞浦</x:v>
+        <x:v>航天科技集团五院502所</x:v>
       </x:c>
       <x:c r="C73" s="4" t="str">
-        <x:v>半导体/模拟IC</x:v>
+        <x:v>航天/自动控制</x:v>
       </x:c>
       <x:c r="D73" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>事业单位/央企院所</x:v>
       </x:c>
       <x:c r="E73" s="4" t="str">
-        <x:v>上海、深圳等，以岗位页为准</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F73" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G73" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>硕士/博士为主，以岗位为准</x:v>
       </x:c>
       <x:c r="H73" s="4" t="str">
-        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
+        <x:v>导航制导与控制、自动化、电子、通信、计算机、软件、机械等</x:v>
       </x:c>
       <x:c r="I73" s="15" t="str">
-        <x:v>https://www.3peak.cn/careers</x:v>
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J73" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K73" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>未统一公布</x:v>
       </x:c>
       <x:c r="L73" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
+        <x:v>公开公告显示开放；投前确认</x:v>
       </x:c>
       <x:c r="M73" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N73" s="4" t="str">
-        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
+        <x:v>研究所岗位通常有专业、学历、政审及保密要求。</x:v>
       </x:c>
       <x:c r="O73" s="15" t="str">
-        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
-      </x:c>
-      <x:c r="P73" s="18" t="str">
-        <x:v>B-招聘平台/高校就业转载</x:v>
+        <x:v>https://www.baidu.com/s?wd=%E4%BA%94%E9%99%A2502%E6%89%802027%E5%B1%8A%E6%A0%A1%E6%8B%9B</x:v>
+      </x:c>
+      <x:c r="P73" s="16" t="str">
+        <x:v>B-高校就业网公开公告</x:v>
       </x:c>
       <x:c r="Q73" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="54" customHeight="1">
-      <x:c r="A74" s="4" t="str">
-        <x:v>不晚于2026-07-07</x:v>
-      </x:c>
-      <x:c r="B74" s="4" t="str">
-        <x:v>文远知行WeRide</x:v>
-      </x:c>
-      <x:c r="C74" s="4" t="str">
-        <x:v>自动驾驶/人工智能</x:v>
-      </x:c>
-      <x:c r="D74" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E74" s="4" t="str">
-        <x:v>广州、深圳、武汉等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F74" s="4" t="str">
-        <x:v>正式批/校招/可转正实习</x:v>
-      </x:c>
-      <x:c r="G74" s="4" t="str">
-        <x:v>2027届应届毕业生及可转正实习生，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H74" s="4" t="str">
-        <x:v>感知/预测/规划控制算法、算法测试、测试开发、SRE、云与车端安全、AI Infra、仿真平台等</x:v>
-      </x:c>
-      <x:c r="I74" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
-      </x:c>
-      <x:c r="J74" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K74" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L74" s="4" t="str">
-        <x:v>企业官方校招系统在招；已核验137个职位</x:v>
-      </x:c>
-      <x:c r="M74" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N74" s="4" t="str">
-        <x:v>官方列表显示2027届校招职位最早发布于7月7日；部分岗位为可转正实习，城市和岗位随招聘系统实时调整。</x:v>
-      </x:c>
-      <x:c r="O74" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
+      <x:c r="A74" s="17" t="str">
+        <x:v>2026-07-17</x:v>
+      </x:c>
+      <x:c r="B74" s="17" t="str">
+        <x:v>鹰角网络</x:v>
+      </x:c>
+      <x:c r="C74" s="17" t="str">
+        <x:v>游戏</x:v>
+      </x:c>
+      <x:c r="D74" s="17" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E74" s="17" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F74" s="17" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G74" s="17" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H74" s="17" t="str">
+        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
+      </x:c>
+      <x:c r="I74" s="18" t="str">
+        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
+      </x:c>
+      <x:c r="J74" s="17" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K74" s="17" t="str">
+        <x:v>否；安排笔试/面试</x:v>
+      </x:c>
+      <x:c r="L74" s="17" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M74" s="17" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N74" s="17" t="str">
+        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
+      </x:c>
+      <x:c r="O74" s="18" t="str">
+        <x:v>https://campus.hypergryph.com/</x:v>
       </x:c>
       <x:c r="P74" s="14" t="str">
-        <x:v>A-企业官方校招系统与职位列表已核验</x:v>
-      </x:c>
-      <x:c r="Q74" s="4" t="str">
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q74" s="17" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="54" customHeight="1">
-      <x:c r="A75" s="16" t="str">
-        <x:v>2026-07-06</x:v>
-      </x:c>
-      <x:c r="B75" s="16" t="str">
-        <x:v>米哈游</x:v>
-      </x:c>
-      <x:c r="C75" s="16" t="str">
-        <x:v>游戏/互联网</x:v>
-      </x:c>
-      <x:c r="D75" s="16" t="str">
+      <x:c r="A75" s="4" t="str">
+        <x:v>2026-07-16</x:v>
+      </x:c>
+      <x:c r="B75" s="4" t="str">
+        <x:v>联发科技</x:v>
+      </x:c>
+      <x:c r="C75" s="4" t="str">
+        <x:v>半导体/IC设计</x:v>
+      </x:c>
+      <x:c r="D75" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E75" s="16" t="str">
-        <x:v>上海、北京</x:v>
-      </x:c>
-      <x:c r="F75" s="16" t="str">
-        <x:v>技术提前批</x:v>
-      </x:c>
-      <x:c r="G75" s="16" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H75" s="16" t="str">
-        <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
-      </x:c>
-      <x:c r="I75" s="17" t="str">
-        <x:v>https://campus.mihoyo.com/</x:v>
-      </x:c>
-      <x:c r="J75" s="16" t="str">
-        <x:v>2026-07-27</x:v>
-      </x:c>
-      <x:c r="K75" s="16" t="str">
-        <x:v>有免笔试直通面试机会</x:v>
-      </x:c>
-      <x:c r="L75" s="16" t="str">
-        <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
-      </x:c>
-      <x:c r="M75" s="16" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N75" s="16" t="str">
-        <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
-      </x:c>
-      <x:c r="O75" s="17" t="str">
+      <x:c r="E75" s="4" t="str">
+        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
+      </x:c>
+      <x:c r="F75" s="4" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G75" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H75" s="4" t="str">
+        <x:v>软件类、通信类、IC类</x:v>
+      </x:c>
+      <x:c r="I75" s="15" t="str">
+        <x:v>https://mediatek.zhiye.com/</x:v>
+      </x:c>
+      <x:c r="J75" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K75" s="4" t="str">
+        <x:v>否；明确安排7-8月笔试</x:v>
+      </x:c>
+      <x:c r="L75" s="4" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M75" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N75" s="4" t="str">
+        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
+      </x:c>
+      <x:c r="O75" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P75" s="14" t="str">
         <x:v>A-官方招聘公告已核验</x:v>
       </x:c>
-      <x:c r="Q75" s="16" t="str">
-        <x:v>2026-07-30</x:v>
+      <x:c r="Q75" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="54" customHeight="1">
       <x:c r="A76" s="4" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B76" s="4" t="str">
-        <x:v>京东方-先锋京英计划</x:v>
+        <x:v>DJI大疆</x:v>
       </x:c>
       <x:c r="C76" s="4" t="str">
-        <x:v>显示技术/半导体/物联网</x:v>
+        <x:v>无人机/智能硬件</x:v>
       </x:c>
       <x:c r="D76" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E76" s="4" t="str">
-        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
+        <x:v>深圳、东莞、上海、北京、西安等</x:v>
       </x:c>
       <x:c r="F76" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批-拓疆者计划</x:v>
       </x:c>
       <x:c r="G76" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H76" s="4" t="str">
-        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
+        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
       </x:c>
       <x:c r="I76" s="15" t="str">
-        <x:v>https://campus.boe.com/</x:v>
+        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
       </x:c>
       <x:c r="J76" s="4" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K76" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
       </x:c>
       <x:c r="L76" s="4" t="str">
         <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M76" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N76" s="4" t="str">
-        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
+        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
       </x:c>
       <x:c r="O76" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P76" s="14" t="str">
-        <x:v>A-国家大学生就业平台公告已核验</x:v>
+        <x:v>A-官方来源公告已核验</x:v>
       </x:c>
       <x:c r="Q76" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4508,52 +4508,52 @@
     </x:row>
     <x:row r="77" ht="54" customHeight="1">
       <x:c r="A77" s="4" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="B77" s="4" t="str">
-        <x:v>中国航天科技集团</x:v>
+        <x:v>蔚来</x:v>
       </x:c>
       <x:c r="C77" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D77" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E77" s="4" t="str">
-        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
+        <x:v>上海、合肥、北京、武汉、南京等</x:v>
       </x:c>
       <x:c r="F77" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>技术提前批</x:v>
       </x:c>
       <x:c r="G77" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2024年9月-2027年8月毕业</x:v>
       </x:c>
       <x:c r="H77" s="4" t="str">
-        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
+        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
       </x:c>
       <x:c r="I77" s="15" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
+        <x:v>https://campus.nio.com/</x:v>
       </x:c>
       <x:c r="J77" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K77" s="4" t="str">
-        <x:v>各院所自行组织，未统一</x:v>
+        <x:v>否；有笔试/测评</x:v>
       </x:c>
       <x:c r="L77" s="4" t="str">
-        <x:v>官方公告已确认启动</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M77" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N77" s="4" t="str">
-        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
+        <x:v>最多同时申请3个岗位。</x:v>
       </x:c>
       <x:c r="O77" s="15" t="str">
-        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P77" s="14" t="str">
-        <x:v>A-国务院国资委/集团官方来源</x:v>
+        <x:v>A-官方来源公告已核验</x:v>
       </x:c>
       <x:c r="Q77" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4561,105 +4561,105 @@
     </x:row>
     <x:row r="78" ht="54" customHeight="1">
       <x:c r="A78" s="4" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="B78" s="4" t="str">
-        <x:v>高途</x:v>
+        <x:v>北方华创</x:v>
       </x:c>
       <x:c r="C78" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>半导体设备</x:v>
       </x:c>
       <x:c r="D78" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E78" s="4" t="str">
-        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
+        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F78" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G78" s="4" t="str">
-        <x:v>27届为主，优秀28届也可投</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H78" s="4" t="str">
-        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
+        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
       </x:c>
       <x:c r="I78" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
+        <x:v>https://career.naura.com/campus</x:v>
       </x:c>
       <x:c r="J78" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K78" s="4" t="str">
-        <x:v>否；流程包含笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L78" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
       </x:c>
       <x:c r="M78" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N78" s="4" t="str">
-        <x:v>滚动发放Offer，截止时间未公布。</x:v>
+        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
       </x:c>
       <x:c r="O78" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
       </x:c>
       <x:c r="P78" s="14" t="str">
-        <x:v>A-官方投递平台已核验</x:v>
+        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
       </x:c>
       <x:c r="Q78" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="54" customHeight="1">
       <x:c r="A79" s="4" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B79" s="4" t="str">
-        <x:v>中汽中心</x:v>
+        <x:v>百度</x:v>
       </x:c>
       <x:c r="C79" s="4" t="str">
-        <x:v>汽车检测/科研</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D79" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E79" s="4" t="str">
-        <x:v>天津、武汉、北京、上海等</x:v>
+        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
       </x:c>
       <x:c r="F79" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G79" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H79" s="4" t="str">
-        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
+        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
       </x:c>
       <x:c r="I79" s="15" t="str">
-        <x:v>https://www.catarc.ac.cn/</x:v>
+        <x:v>https://talent.baidu.com/jobs</x:v>
       </x:c>
       <x:c r="J79" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-30</x:v>
       </x:c>
       <x:c r="K79" s="4" t="str">
-        <x:v>官方未统一说明</x:v>
+        <x:v>部分免；并非所有候选人参加笔试</x:v>
       </x:c>
       <x:c r="L79" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M79" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N79" s="4" t="str">
-        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
+        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
       </x:c>
       <x:c r="O79" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
-      </x:c>
-      <x:c r="P79" s="18" t="str">
-        <x:v>B-公开招聘公告</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P79" s="14" t="str">
+        <x:v>A-官方招聘日历/官方来源已核验</x:v>
       </x:c>
       <x:c r="Q79" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4667,28 +4667,28 @@
     </x:row>
     <x:row r="80" ht="54" customHeight="1">
       <x:c r="A80" s="4" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B80" s="4" t="str">
-        <x:v>中国航天科工集团</x:v>
+        <x:v>中国航天科工集团第六研究院</x:v>
       </x:c>
       <x:c r="C80" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>航天/军工/动力系统</x:v>
       </x:c>
       <x:c r="D80" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>央企院所</x:v>
       </x:c>
       <x:c r="E80" s="4" t="str">
-        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
+        <x:v>呼和浩特及所属单位</x:v>
       </x:c>
       <x:c r="F80" s="4" t="str">
-        <x:v>正式批/提前批</x:v>
+        <x:v>提前批+暑期开放日</x:v>
       </x:c>
       <x:c r="G80" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
       </x:c>
       <x:c r="H80" s="4" t="str">
-        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
+        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
       </x:c>
       <x:c r="I80" s="15" t="str">
         <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
@@ -4700,19 +4700,19 @@
         <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L80" s="4" t="str">
-        <x:v>官网公告已确认启动</x:v>
+        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
       </x:c>
       <x:c r="M80" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N80" s="4" t="str">
-        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
+        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
       </x:c>
       <x:c r="O80" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
-      </x:c>
-      <x:c r="P80" s="14" t="str">
-        <x:v>A-集团官网公告已核验</x:v>
+        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
+      </x:c>
+      <x:c r="P80" s="16" t="str">
+        <x:v>B-高校就业网公开公告</x:v>
       </x:c>
       <x:c r="Q80" s="4" t="str">
         <x:v>2026-07-27</x:v>
@@ -4720,84 +4720,84 @@
     </x:row>
     <x:row r="81" ht="54" customHeight="1">
       <x:c r="A81" s="4" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="B81" s="4" t="str">
-        <x:v>禾赛科技</x:v>
+        <x:v>思瑞浦</x:v>
       </x:c>
       <x:c r="C81" s="4" t="str">
-        <x:v>激光雷达/机器人</x:v>
+        <x:v>半导体/模拟IC</x:v>
       </x:c>
       <x:c r="D81" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E81" s="4" t="str">
-        <x:v>上海、杭州</x:v>
+        <x:v>上海、深圳等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F81" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G81" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H81" s="4" t="str">
-        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
+        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
       </x:c>
       <x:c r="I81" s="15" t="str">
-        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
+        <x:v>https://www.3peak.cn/careers</x:v>
       </x:c>
       <x:c r="J81" s="4" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K81" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L81" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
       </x:c>
       <x:c r="M81" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N81" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
       </x:c>
       <x:c r="O81" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P81" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
+      </x:c>
+      <x:c r="P81" s="16" t="str">
+        <x:v>B-招聘平台/高校就业转载</x:v>
       </x:c>
       <x:c r="Q81" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="54" customHeight="1">
       <x:c r="A82" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>不晚于2026-07-07</x:v>
       </x:c>
       <x:c r="B82" s="4" t="str">
-        <x:v>北京国望光学科技有限公司</x:v>
+        <x:v>文远知行WeRide</x:v>
       </x:c>
       <x:c r="C82" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>自动驾驶/人工智能</x:v>
       </x:c>
       <x:c r="D82" s="4" t="str">
-        <x:v>央国企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E82" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>广州、深圳、武汉等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F82" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批/校招/可转正实习</x:v>
       </x:c>
       <x:c r="G82" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届毕业生及可转正实习生，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H82" s="4" t="str">
-        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
-      </x:c>
-      <x:c r="I82" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>感知/预测/规划控制算法、算法测试、测试开发、SRE、云与车端安全、AI Infra、仿真平台等</x:v>
+      </x:c>
+      <x:c r="I82" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
       </x:c>
       <x:c r="J82" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4806,92 +4806,92 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L82" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>企业官方校招系统在招；已核验137个职位</x:v>
       </x:c>
       <x:c r="M82" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N82" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>官方列表显示2027届校招职位最早发布于7月7日；部分岗位为可转正实习，城市和岗位随招聘系统实时调整。</x:v>
       </x:c>
       <x:c r="O82" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P82" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
+      </x:c>
+      <x:c r="P82" s="14" t="str">
+        <x:v>A-企业官方校招系统与职位列表已核验</x:v>
       </x:c>
       <x:c r="Q82" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="54" customHeight="1">
-      <x:c r="A83" s="4" t="str">
-        <x:v>2026-06-17</x:v>
-      </x:c>
-      <x:c r="B83" s="4" t="str">
-        <x:v>乐读</x:v>
-      </x:c>
-      <x:c r="C83" s="4" t="str">
-        <x:v>教育科技</x:v>
-      </x:c>
-      <x:c r="D83" s="4" t="str">
+      <x:c r="A83" s="17" t="str">
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="B83" s="17" t="str">
+        <x:v>米哈游</x:v>
+      </x:c>
+      <x:c r="C83" s="17" t="str">
+        <x:v>游戏/互联网</x:v>
+      </x:c>
+      <x:c r="D83" s="17" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E83" s="4" t="str">
-        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
-      </x:c>
-      <x:c r="F83" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G83" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H83" s="4" t="str">
-        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
-      </x:c>
-      <x:c r="I83" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
-      </x:c>
-      <x:c r="J83" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K83" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L83" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
-      </x:c>
-      <x:c r="M83" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N83" s="4" t="str">
-        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
-      </x:c>
-      <x:c r="O83" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P83" s="18" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
-      </x:c>
-      <x:c r="Q83" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+      <x:c r="E83" s="17" t="str">
+        <x:v>上海、北京</x:v>
+      </x:c>
+      <x:c r="F83" s="17" t="str">
+        <x:v>技术提前批</x:v>
+      </x:c>
+      <x:c r="G83" s="17" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H83" s="17" t="str">
+        <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
+      </x:c>
+      <x:c r="I83" s="18" t="str">
+        <x:v>https://campus.mihoyo.com/</x:v>
+      </x:c>
+      <x:c r="J83" s="17" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+      <x:c r="K83" s="17" t="str">
+        <x:v>有免笔试直通面试机会</x:v>
+      </x:c>
+      <x:c r="L83" s="17" t="str">
+        <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
+      </x:c>
+      <x:c r="M83" s="17" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N83" s="17" t="str">
+        <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
+      </x:c>
+      <x:c r="O83" s="18" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P83" s="14" t="str">
+        <x:v>A-官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q83" s="17" t="str">
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="54" customHeight="1">
       <x:c r="A84" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="B84" s="4" t="str">
-        <x:v>龙蟠科技</x:v>
+        <x:v>京东方-先锋京英计划</x:v>
       </x:c>
       <x:c r="C84" s="4" t="str">
-        <x:v>新能源材料/化工</x:v>
+        <x:v>显示技术/半导体/物联网</x:v>
       </x:c>
       <x:c r="D84" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E84" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
       </x:c>
       <x:c r="F84" s="4" t="str">
         <x:v>提前批</x:v>
@@ -4900,31 +4900,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H84" s="4" t="str">
-        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
+        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
       </x:c>
       <x:c r="I84" s="15" t="str">
-        <x:v>https://www.lopal.com.cn/join</x:v>
+        <x:v>https://campus.boe.com/</x:v>
       </x:c>
       <x:c r="J84" s="4" t="str">
-        <x:v>2027-06-01</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K84" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L84" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M84" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N84" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
       </x:c>
       <x:c r="O84" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P84" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P84" s="14" t="str">
+        <x:v>A-国家大学生就业平台公告已核验</x:v>
       </x:c>
       <x:c r="Q84" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4932,19 +4932,19 @@
     </x:row>
     <x:row r="85" ht="54" customHeight="1">
       <x:c r="A85" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="B85" s="4" t="str">
-        <x:v>牧原</x:v>
+        <x:v>中国航天科技集团</x:v>
       </x:c>
       <x:c r="C85" s="4" t="str">
-        <x:v>农业/食品/智能养殖</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D85" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E85" s="4" t="str">
-        <x:v>河南南阳及全国</x:v>
+        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
       </x:c>
       <x:c r="F85" s="4" t="str">
         <x:v>提前批</x:v>
@@ -4953,31 +4953,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H85" s="4" t="str">
-        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
+        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
       </x:c>
       <x:c r="I85" s="15" t="str">
-        <x:v>https://job.muyuanfoods.com/</x:v>
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J85" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K85" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各院所自行组织，未统一</x:v>
       </x:c>
       <x:c r="L85" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>官方公告已确认启动</x:v>
       </x:c>
       <x:c r="M85" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N85" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
       </x:c>
       <x:c r="O85" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P85" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
+      </x:c>
+      <x:c r="P85" s="14" t="str">
+        <x:v>A-国务院国资委/集团官方来源</x:v>
       </x:c>
       <x:c r="Q85" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4985,52 +4985,52 @@
     </x:row>
     <x:row r="86" ht="54" customHeight="1">
       <x:c r="A86" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="B86" s="4" t="str">
-        <x:v>三一集团-小语种校招</x:v>
+        <x:v>高途</x:v>
       </x:c>
       <x:c r="C86" s="4" t="str">
-        <x:v>工程机械/制造</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D86" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E86" s="4" t="str">
-        <x:v>海外多国</x:v>
+        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
       </x:c>
       <x:c r="F86" s="4" t="str">
-        <x:v>小语种专项/正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G86" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>27届为主，优秀28届也可投</x:v>
       </x:c>
       <x:c r="H86" s="4" t="str">
-        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
+        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
       </x:c>
       <x:c r="I86" s="15" t="str">
-        <x:v>https://sanycampus.zhiye.com/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
       </x:c>
       <x:c r="J86" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K86" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；流程包含笔试</x:v>
       </x:c>
       <x:c r="L86" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M86" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N86" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>滚动发放Offer，截止时间未公布。</x:v>
       </x:c>
       <x:c r="O86" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P86" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P86" s="14" t="str">
+        <x:v>A-官方投递平台已核验</x:v>
       </x:c>
       <x:c r="Q86" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5038,52 +5038,52 @@
     </x:row>
     <x:row r="87" ht="54" customHeight="1">
       <x:c r="A87" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="B87" s="4" t="str">
-        <x:v>上海电气-暑期精英训练营</x:v>
+        <x:v>中汽中心</x:v>
       </x:c>
       <x:c r="C87" s="4" t="str">
-        <x:v>高端装备/能源</x:v>
+        <x:v>汽车检测/科研</x:v>
       </x:c>
       <x:c r="D87" s="4" t="str">
-        <x:v>地方国企</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E87" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>天津、武汉、北京、上海等</x:v>
       </x:c>
       <x:c r="F87" s="4" t="str">
-        <x:v>训练营/秋招直通</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G87" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H87" s="4" t="str">
-        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
+        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
       </x:c>
       <x:c r="I87" s="15" t="str">
-        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
+        <x:v>https://www.catarc.ac.cn/</x:v>
       </x:c>
       <x:c r="J87" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K87" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L87" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M87" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N87" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
       </x:c>
       <x:c r="O87" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P87" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
+      </x:c>
+      <x:c r="P87" s="16" t="str">
+        <x:v>B-公开招聘公告</x:v>
       </x:c>
       <x:c r="Q87" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5091,87 +5091,87 @@
     </x:row>
     <x:row r="88" ht="54" customHeight="1">
       <x:c r="A88" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="B88" s="4" t="str">
-        <x:v>vivo-蓝极星计划</x:v>
+        <x:v>中国航天科工集团</x:v>
       </x:c>
       <x:c r="C88" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D88" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E88" s="4" t="str">
-        <x:v>深圳、杭州、东莞、上海</x:v>
+        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
       </x:c>
       <x:c r="F88" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批/提前批</x:v>
       </x:c>
       <x:c r="G88" s="4" t="str">
-        <x:v>博士为主</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H88" s="4" t="str">
-        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
+        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
       </x:c>
       <x:c r="I88" s="15" t="str">
-        <x:v>https://hr.vivo.com/</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
       <x:c r="J88" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K88" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L88" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>官网公告已确认启动</x:v>
       </x:c>
       <x:c r="M88" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N88" s="4" t="str">
-        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
+        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
       </x:c>
       <x:c r="O88" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P88" s="18" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
+      </x:c>
+      <x:c r="P88" s="14" t="str">
+        <x:v>A-集团官网公告已核验</x:v>
       </x:c>
       <x:c r="Q88" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="54" customHeight="1">
       <x:c r="A89" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="B89" s="4" t="str">
-        <x:v>澜起科技</x:v>
+        <x:v>禾赛科技</x:v>
       </x:c>
       <x:c r="C89" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>激光雷达/机器人</x:v>
       </x:c>
       <x:c r="D89" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E89" s="4" t="str">
-        <x:v>昆山、西安、南京</x:v>
+        <x:v>上海、杭州</x:v>
       </x:c>
       <x:c r="F89" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G89" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H89" s="4" t="str">
-        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
+        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
       </x:c>
       <x:c r="I89" s="15" t="str">
-        <x:v>https://www.montage-tech.com/cn/careers</x:v>
+        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
       </x:c>
       <x:c r="J89" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="K89" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -5180,7 +5180,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M89" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N89" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -5188,7 +5188,7 @@
       <x:c r="O89" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P89" s="18" t="str">
+      <x:c r="P89" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q89" s="4" t="str">
@@ -5197,19 +5197,19 @@
     </x:row>
     <x:row r="90" ht="54" customHeight="1">
       <x:c r="A90" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B90" s="4" t="str">
-        <x:v>上海宇量昇</x:v>
+        <x:v>北京国望光学科技有限公司</x:v>
       </x:c>
       <x:c r="C90" s="4" t="str">
         <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D90" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>央国企</x:v>
       </x:c>
       <x:c r="E90" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F90" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5218,10 +5218,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H90" s="4" t="str">
-        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
-      </x:c>
-      <x:c r="I90" s="15" t="str">
-        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
+        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
+      </x:c>
+      <x:c r="I90" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J90" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5241,7 +5241,7 @@
       <x:c r="O90" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P90" s="18" t="str">
+      <x:c r="P90" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q90" s="4" t="str">
@@ -5250,31 +5250,31 @@
     </x:row>
     <x:row r="91" ht="54" customHeight="1">
       <x:c r="A91" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B91" s="4" t="str">
-        <x:v>是为科技</x:v>
+        <x:v>乐读</x:v>
       </x:c>
       <x:c r="C91" s="4" t="str">
-        <x:v>新能源/智能制造</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D91" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E91" s="4" t="str">
-        <x:v>南京、上海、常州</x:v>
+        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
       </x:c>
       <x:c r="F91" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G91" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H91" s="4" t="str">
-        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
-      </x:c>
-      <x:c r="I91" s="15" t="str">
-        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
+        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
+      </x:c>
+      <x:c r="I91" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J91" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5283,19 +5283,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L91" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M91" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N91" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
       </x:c>
       <x:c r="O91" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P91" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      <x:c r="P91" s="16" t="str">
+        <x:v>B-招聘平台公开汇总</x:v>
       </x:c>
       <x:c r="Q91" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5303,34 +5303,34 @@
     </x:row>
     <x:row r="92" ht="54" customHeight="1">
       <x:c r="A92" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B92" s="4" t="str">
-        <x:v>游族网络</x:v>
+        <x:v>龙蟠科技</x:v>
       </x:c>
       <x:c r="C92" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>新能源材料/化工</x:v>
       </x:c>
       <x:c r="D92" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E92" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F92" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G92" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H92" s="4" t="str">
-        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
+        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
       </x:c>
       <x:c r="I92" s="15" t="str">
-        <x:v>https://job.youzu.com/</x:v>
+        <x:v>https://www.lopal.com.cn/join</x:v>
       </x:c>
       <x:c r="J92" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-01</x:v>
       </x:c>
       <x:c r="K92" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -5339,7 +5339,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M92" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N92" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -5347,7 +5347,7 @@
       <x:c r="O92" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P92" s="18" t="str">
+      <x:c r="P92" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q92" s="4" t="str">
@@ -5356,31 +5356,31 @@
     </x:row>
     <x:row r="93" ht="54" customHeight="1">
       <x:c r="A93" s="4" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B93" s="4" t="str">
-        <x:v>中铁设计</x:v>
+        <x:v>牧原</x:v>
       </x:c>
       <x:c r="C93" s="4" t="str">
-        <x:v>轨道交通/工程设计</x:v>
+        <x:v>农业/食品/智能养殖</x:v>
       </x:c>
       <x:c r="D93" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E93" s="4" t="str">
-        <x:v>北京、济南、郑州、太原</x:v>
+        <x:v>河南南阳及全国</x:v>
       </x:c>
       <x:c r="F93" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G93" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H93" s="4" t="str">
-        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
+        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
       </x:c>
       <x:c r="I93" s="15" t="str">
-        <x:v>https://www.crdc.com/</x:v>
+        <x:v>https://job.muyuanfoods.com/</x:v>
       </x:c>
       <x:c r="J93" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5400,7 +5400,7 @@
       <x:c r="O93" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P93" s="18" t="str">
+      <x:c r="P93" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q93" s="4" t="str">
@@ -5409,31 +5409,31 @@
     </x:row>
     <x:row r="94" ht="54" customHeight="1">
       <x:c r="A94" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B94" s="4" t="str">
-        <x:v>迈安德集团-校园大使</x:v>
+        <x:v>三一集团-小语种校招</x:v>
       </x:c>
       <x:c r="C94" s="4" t="str">
-        <x:v>粮油工程/装备</x:v>
+        <x:v>工程机械/制造</x:v>
       </x:c>
       <x:c r="D94" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E94" s="4" t="str">
-        <x:v>扬州/高校</x:v>
+        <x:v>海外多国</x:v>
       </x:c>
       <x:c r="F94" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>小语种专项/正式批</x:v>
       </x:c>
       <x:c r="G94" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H94" s="4" t="str">
-        <x:v>校园大使</x:v>
+        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
       </x:c>
       <x:c r="I94" s="15" t="str">
-        <x:v>https://www.myande.com/</x:v>
+        <x:v>https://sanycampus.zhiye.com/</x:v>
       </x:c>
       <x:c r="J94" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5453,7 +5453,7 @@
       <x:c r="O94" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P94" s="18" t="str">
+      <x:c r="P94" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q94" s="4" t="str">
@@ -5462,31 +5462,31 @@
     </x:row>
     <x:row r="95" ht="54" customHeight="1">
       <x:c r="A95" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B95" s="4" t="str">
-        <x:v>迅仿科技</x:v>
+        <x:v>上海电气-暑期精英训练营</x:v>
       </x:c>
       <x:c r="C95" s="4" t="str">
-        <x:v>工业软件/仿真</x:v>
+        <x:v>高端装备/能源</x:v>
       </x:c>
       <x:c r="D95" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>地方国企</x:v>
       </x:c>
       <x:c r="E95" s="4" t="str">
         <x:v>上海</x:v>
       </x:c>
       <x:c r="F95" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>训练营/秋招直通</x:v>
       </x:c>
       <x:c r="G95" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H95" s="4" t="str">
-        <x:v>仿真工程师</x:v>
-      </x:c>
-      <x:c r="I95" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
+      </x:c>
+      <x:c r="I95" s="15" t="str">
+        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
       </x:c>
       <x:c r="J95" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5506,7 +5506,7 @@
       <x:c r="O95" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P95" s="18" t="str">
+      <x:c r="P95" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q95" s="4" t="str">
@@ -5515,52 +5515,52 @@
     </x:row>
     <x:row r="96" ht="54" customHeight="1">
       <x:c r="A96" s="4" t="str">
-        <x:v>2026-06-12</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B96" s="4" t="str">
-        <x:v>MOVA</x:v>
+        <x:v>vivo-蓝极星计划</x:v>
       </x:c>
       <x:c r="C96" s="4" t="str">
-        <x:v>智能家电/机器人</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D96" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E96" s="4" t="str">
-        <x:v>苏州及全国</x:v>
+        <x:v>深圳、杭州、东莞、上海</x:v>
       </x:c>
       <x:c r="F96" s="4" t="str">
-        <x:v>全球校招/正式批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G96" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>博士为主</x:v>
       </x:c>
       <x:c r="H96" s="4" t="str">
-        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
       </x:c>
       <x:c r="I96" s="15" t="str">
-        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+        <x:v>https://hr.vivo.com/</x:v>
       </x:c>
       <x:c r="J96" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K96" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L96" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M96" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N96" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
       </x:c>
       <x:c r="O96" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P96" s="18" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      <x:c r="P96" s="16" t="str">
+        <x:v>B-招聘平台公开汇总</x:v>
       </x:c>
       <x:c r="Q96" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5568,19 +5568,19 @@
     </x:row>
     <x:row r="97" ht="54" customHeight="1">
       <x:c r="A97" s="4" t="str">
-        <x:v>2026-06-11</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B97" s="4" t="str">
-        <x:v>财通证券</x:v>
+        <x:v>澜起科技</x:v>
       </x:c>
       <x:c r="C97" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D97" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E97" s="4" t="str">
-        <x:v>杭州、上海、深圳、北京</x:v>
+        <x:v>昆山、西安、南京</x:v>
       </x:c>
       <x:c r="F97" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5589,10 +5589,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H97" s="4" t="str">
-        <x:v>总部、参股公司、分公司岗位</x:v>
+        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
       </x:c>
       <x:c r="I97" s="15" t="str">
-        <x:v>https://www.ctsec.com/joinUs</x:v>
+        <x:v>https://www.montage-tech.com/cn/careers</x:v>
       </x:c>
       <x:c r="J97" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5612,7 +5612,7 @@
       <x:c r="O97" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P97" s="18" t="str">
+      <x:c r="P97" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q97" s="4" t="str">
@@ -5621,31 +5621,31 @@
     </x:row>
     <x:row r="98" ht="54" customHeight="1">
       <x:c r="A98" s="4" t="str">
-        <x:v>2026-06-10</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B98" s="4" t="str">
-        <x:v>歌尔股份</x:v>
+        <x:v>上海宇量昇</x:v>
       </x:c>
       <x:c r="C98" s="4" t="str">
-        <x:v>消费电子/智能硬件</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D98" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E98" s="4" t="str">
         <x:v>上海</x:v>
       </x:c>
       <x:c r="F98" s="4" t="str">
-        <x:v>实习/校招储备</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G98" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H98" s="4" t="str">
-        <x:v>法务助理</x:v>
+        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
       </x:c>
       <x:c r="I98" s="15" t="str">
-        <x:v>https://career.goertek.com/</x:v>
+        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
       </x:c>
       <x:c r="J98" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5665,7 +5665,7 @@
       <x:c r="O98" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P98" s="18" t="str">
+      <x:c r="P98" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q98" s="4" t="str">
@@ -5674,31 +5674,31 @@
     </x:row>
     <x:row r="99" ht="54" customHeight="1">
       <x:c r="A99" s="4" t="str">
-        <x:v>2026-06-09</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B99" s="4" t="str">
-        <x:v>深信服-校园大使</x:v>
+        <x:v>是为科技</x:v>
       </x:c>
       <x:c r="C99" s="4" t="str">
-        <x:v>网络安全/云计算</x:v>
+        <x:v>新能源/智能制造</x:v>
       </x:c>
       <x:c r="D99" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E99" s="4" t="str">
-        <x:v>西安</x:v>
+        <x:v>南京、上海、常州</x:v>
       </x:c>
       <x:c r="F99" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G99" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H99" s="4" t="str">
-        <x:v>校园大使</x:v>
+        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
       </x:c>
       <x:c r="I99" s="15" t="str">
-        <x:v>https://hr.sangfor.com/</x:v>
+        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
       </x:c>
       <x:c r="J99" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5718,7 +5718,7 @@
       <x:c r="O99" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P99" s="18" t="str">
+      <x:c r="P99" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q99" s="4" t="str">
@@ -5727,19 +5727,19 @@
     </x:row>
     <x:row r="100" ht="54" customHeight="1">
       <x:c r="A100" s="4" t="str">
-        <x:v>2026-06-08</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B100" s="4" t="str">
-        <x:v>晓禾教育</x:v>
+        <x:v>游族网络</x:v>
       </x:c>
       <x:c r="C100" s="4" t="str">
-        <x:v>教育</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D100" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E100" s="4" t="str">
-        <x:v>武汉、郑州、襄阳、宜昌</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F100" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5748,10 +5748,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H100" s="4" t="str">
-        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
-      </x:c>
-      <x:c r="I100" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
+      </x:c>
+      <x:c r="I100" s="15" t="str">
+        <x:v>https://job.youzu.com/</x:v>
       </x:c>
       <x:c r="J100" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5771,7 +5771,7 @@
       <x:c r="O100" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P100" s="18" t="str">
+      <x:c r="P100" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q100" s="4" t="str">
@@ -5780,31 +5780,31 @@
     </x:row>
     <x:row r="101" ht="54" customHeight="1">
       <x:c r="A101" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="B101" s="4" t="str">
-        <x:v>晖致医药</x:v>
+        <x:v>中铁设计</x:v>
       </x:c>
       <x:c r="C101" s="4" t="str">
-        <x:v>医药</x:v>
+        <x:v>轨道交通/工程设计</x:v>
       </x:c>
       <x:c r="D101" s="4" t="str">
-        <x:v>外资</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E101" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京、济南、郑州、太原</x:v>
       </x:c>
       <x:c r="F101" s="4" t="str">
-        <x:v>实习储备正式岗</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G101" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H101" s="4" t="str">
-        <x:v>医学信息沟通实习生</x:v>
+        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
       </x:c>
       <x:c r="I101" s="15" t="str">
-        <x:v>https://careers.viatris.com/</x:v>
+        <x:v>https://www.crdc.com/</x:v>
       </x:c>
       <x:c r="J101" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5824,7 +5824,7 @@
       <x:c r="O101" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P101" s="18" t="str">
+      <x:c r="P101" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q101" s="4" t="str">
@@ -5833,31 +5833,31 @@
     </x:row>
     <x:row r="102" ht="54" customHeight="1">
       <x:c r="A102" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B102" s="4" t="str">
-        <x:v>苏州鸿凌达电子</x:v>
+        <x:v>迈安德集团-校园大使</x:v>
       </x:c>
       <x:c r="C102" s="4" t="str">
-        <x:v>电子制造</x:v>
+        <x:v>粮油工程/装备</x:v>
       </x:c>
       <x:c r="D102" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E102" s="4" t="str">
-        <x:v>苏州</x:v>
+        <x:v>扬州/高校</x:v>
       </x:c>
       <x:c r="F102" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G102" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H102" s="4" t="str">
-        <x:v>财务助理</x:v>
+        <x:v>校园大使</x:v>
       </x:c>
       <x:c r="I102" s="15" t="str">
-        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
+        <x:v>https://www.myande.com/</x:v>
       </x:c>
       <x:c r="J102" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5877,7 +5877,7 @@
       <x:c r="O102" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P102" s="18" t="str">
+      <x:c r="P102" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q102" s="4" t="str">
@@ -5886,13 +5886,13 @@
     </x:row>
     <x:row r="103" ht="54" customHeight="1">
       <x:c r="A103" s="4" t="str">
-        <x:v>2026-06-02</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B103" s="4" t="str">
-        <x:v>万得信息</x:v>
+        <x:v>迅仿科技</x:v>
       </x:c>
       <x:c r="C103" s="4" t="str">
-        <x:v>金融数据/软件</x:v>
+        <x:v>工业软件/仿真</x:v>
       </x:c>
       <x:c r="D103" s="4" t="str">
         <x:v>民营</x:v>
@@ -5907,10 +5907,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H103" s="4" t="str">
-        <x:v>AI算法工程师等</x:v>
-      </x:c>
-      <x:c r="I103" s="15" t="str">
-        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
+        <x:v>仿真工程师</x:v>
+      </x:c>
+      <x:c r="I103" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J103" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5930,7 +5930,7 @@
       <x:c r="O103" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P103" s="18" t="str">
+      <x:c r="P103" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q103" s="4" t="str">
@@ -5939,34 +5939,34 @@
     </x:row>
     <x:row r="104" ht="54" customHeight="1">
       <x:c r="A104" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-12</x:v>
       </x:c>
       <x:c r="B104" s="4" t="str">
-        <x:v>淘大集供应链</x:v>
+        <x:v>MOVA</x:v>
       </x:c>
       <x:c r="C104" s="4" t="str">
-        <x:v>零售/供应链</x:v>
+        <x:v>智能家电/机器人</x:v>
       </x:c>
       <x:c r="D104" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E104" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>苏州及全国</x:v>
       </x:c>
       <x:c r="F104" s="4" t="str">
-        <x:v>管培/实习</x:v>
+        <x:v>全球校招/正式批</x:v>
       </x:c>
       <x:c r="G104" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H104" s="4" t="str">
-        <x:v>巡店管培生、实习生</x:v>
-      </x:c>
-      <x:c r="I104" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+      </x:c>
+      <x:c r="I104" s="15" t="str">
+        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
       </x:c>
       <x:c r="J104" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K104" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -5975,7 +5975,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M104" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N104" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -5983,7 +5983,7 @@
       <x:c r="O104" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P104" s="18" t="str">
+      <x:c r="P104" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q104" s="4" t="str">
@@ -5992,31 +5992,31 @@
     </x:row>
     <x:row r="105" ht="54" customHeight="1">
       <x:c r="A105" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-11</x:v>
       </x:c>
       <x:c r="B105" s="4" t="str">
-        <x:v>友芝友实业集团</x:v>
+        <x:v>财通证券</x:v>
       </x:c>
       <x:c r="C105" s="4" t="str">
-        <x:v>综合实业</x:v>
+        <x:v>证券/金融</x:v>
       </x:c>
       <x:c r="D105" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E105" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>杭州、上海、深圳、北京</x:v>
       </x:c>
       <x:c r="F105" s="4" t="str">
-        <x:v>管培生</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G105" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H105" s="4" t="str">
-        <x:v>青年领军人才管培生</x:v>
+        <x:v>总部、参股公司、分公司岗位</x:v>
       </x:c>
       <x:c r="I105" s="15" t="str">
-        <x:v>https://www.yzyqh.com/jrwm</x:v>
+        <x:v>https://www.ctsec.com/joinUs</x:v>
       </x:c>
       <x:c r="J105" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6036,7 +6036,7 @@
       <x:c r="O105" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P105" s="18" t="str">
+      <x:c r="P105" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q105" s="4" t="str">
@@ -6045,31 +6045,31 @@
     </x:row>
     <x:row r="106" ht="54" customHeight="1">
       <x:c r="A106" s="4" t="str">
-        <x:v>2026-05-29</x:v>
+        <x:v>2026-06-10</x:v>
       </x:c>
       <x:c r="B106" s="4" t="str">
-        <x:v>银雁科技</x:v>
+        <x:v>歌尔股份</x:v>
       </x:c>
       <x:c r="C106" s="4" t="str">
-        <x:v>金融科技服务</x:v>
+        <x:v>消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D106" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E106" s="4" t="str">
-        <x:v>成都</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F106" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>实习/校招储备</x:v>
       </x:c>
       <x:c r="G106" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H106" s="4" t="str">
-        <x:v>人伤理赔</x:v>
+        <x:v>法务助理</x:v>
       </x:c>
       <x:c r="I106" s="15" t="str">
-        <x:v>https://www.cfss.net.cn/</x:v>
+        <x:v>https://career.goertek.com/</x:v>
       </x:c>
       <x:c r="J106" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6089,7 +6089,7 @@
       <x:c r="O106" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P106" s="18" t="str">
+      <x:c r="P106" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q106" s="4" t="str">
@@ -6098,31 +6098,31 @@
     </x:row>
     <x:row r="107" ht="54" customHeight="1">
       <x:c r="A107" s="4" t="str">
-        <x:v>2026-05-15</x:v>
+        <x:v>2026-06-09</x:v>
       </x:c>
       <x:c r="B107" s="4" t="str">
-        <x:v>知乎</x:v>
+        <x:v>深信服-校园大使</x:v>
       </x:c>
       <x:c r="C107" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>网络安全/云计算</x:v>
       </x:c>
       <x:c r="D107" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E107" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>西安</x:v>
       </x:c>
       <x:c r="F107" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G107" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H107" s="4" t="str">
-        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
+        <x:v>校园大使</x:v>
       </x:c>
       <x:c r="I107" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
+        <x:v>https://hr.sangfor.com/</x:v>
       </x:c>
       <x:c r="J107" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6142,7 +6142,7 @@
       <x:c r="O107" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P107" s="18" t="str">
+      <x:c r="P107" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q107" s="4" t="str">
@@ -6151,31 +6151,31 @@
     </x:row>
     <x:row r="108" ht="54" customHeight="1">
       <x:c r="A108" s="4" t="str">
-        <x:v>2026-05-08</x:v>
+        <x:v>2026-06-08</x:v>
       </x:c>
       <x:c r="B108" s="4" t="str">
-        <x:v>招商银行长沙分行</x:v>
+        <x:v>晓禾教育</x:v>
       </x:c>
       <x:c r="C108" s="4" t="str">
-        <x:v>银行/金融</x:v>
+        <x:v>教育</x:v>
       </x:c>
       <x:c r="D108" s="4" t="str">
-        <x:v>股份制银行</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E108" s="4" t="str">
-        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+        <x:v>武汉、郑州、襄阳、宜昌</x:v>
       </x:c>
       <x:c r="F108" s="4" t="str">
-        <x:v>暑期实习/秋招直通</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G108" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H108" s="4" t="str">
-        <x:v>2027暑期实习生</x:v>
-      </x:c>
-      <x:c r="I108" s="15" t="str">
-        <x:v>https://career.cmbchina.com/</x:v>
+        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
+      </x:c>
+      <x:c r="I108" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J108" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6195,7 +6195,7 @@
       <x:c r="O108" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P108" s="18" t="str">
+      <x:c r="P108" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q108" s="4" t="str">
@@ -6204,31 +6204,31 @@
     </x:row>
     <x:row r="109" ht="54" customHeight="1">
       <x:c r="A109" s="4" t="str">
-        <x:v>2026-04-22</x:v>
+        <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="B109" s="4" t="str">
-        <x:v>华金证券</x:v>
+        <x:v>晖致医药</x:v>
       </x:c>
       <x:c r="C109" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>医药</x:v>
       </x:c>
       <x:c r="D109" s="4" t="str">
-        <x:v>国企</x:v>
+        <x:v>外资</x:v>
       </x:c>
       <x:c r="E109" s="4" t="str">
         <x:v>上海</x:v>
       </x:c>
       <x:c r="F109" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>实习储备正式岗</x:v>
       </x:c>
       <x:c r="G109" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H109" s="4" t="str">
-        <x:v>战略发展类</x:v>
+        <x:v>医学信息沟通实习生</x:v>
       </x:c>
       <x:c r="I109" s="15" t="str">
-        <x:v>https://www.huajinsc.cn/</x:v>
+        <x:v>https://careers.viatris.com/</x:v>
       </x:c>
       <x:c r="J109" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6248,10 +6248,434 @@
       <x:c r="O109" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P109" s="18" t="str">
+      <x:c r="P109" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q109" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" ht="54" customHeight="1">
+      <x:c r="A110" s="4" t="str">
+        <x:v>2026-06-04</x:v>
+      </x:c>
+      <x:c r="B110" s="4" t="str">
+        <x:v>苏州鸿凌达电子</x:v>
+      </x:c>
+      <x:c r="C110" s="4" t="str">
+        <x:v>电子制造</x:v>
+      </x:c>
+      <x:c r="D110" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E110" s="4" t="str">
+        <x:v>苏州</x:v>
+      </x:c>
+      <x:c r="F110" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G110" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H110" s="4" t="str">
+        <x:v>财务助理</x:v>
+      </x:c>
+      <x:c r="I110" s="15" t="str">
+        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
+      </x:c>
+      <x:c r="J110" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K110" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L110" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M110" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N110" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O110" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P110" s="16" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q110" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" ht="54" customHeight="1">
+      <x:c r="A111" s="4" t="str">
+        <x:v>2026-06-02</x:v>
+      </x:c>
+      <x:c r="B111" s="4" t="str">
+        <x:v>万得信息</x:v>
+      </x:c>
+      <x:c r="C111" s="4" t="str">
+        <x:v>金融数据/软件</x:v>
+      </x:c>
+      <x:c r="D111" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E111" s="4" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F111" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G111" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H111" s="4" t="str">
+        <x:v>AI算法工程师等</x:v>
+      </x:c>
+      <x:c r="I111" s="15" t="str">
+        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
+      </x:c>
+      <x:c r="J111" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K111" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L111" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M111" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N111" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O111" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P111" s="16" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q111" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" ht="54" customHeight="1">
+      <x:c r="A112" s="4" t="str">
+        <x:v>2026-06-01</x:v>
+      </x:c>
+      <x:c r="B112" s="4" t="str">
+        <x:v>淘大集供应链</x:v>
+      </x:c>
+      <x:c r="C112" s="4" t="str">
+        <x:v>零售/供应链</x:v>
+      </x:c>
+      <x:c r="D112" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E112" s="4" t="str">
+        <x:v>武汉</x:v>
+      </x:c>
+      <x:c r="F112" s="4" t="str">
+        <x:v>管培/实习</x:v>
+      </x:c>
+      <x:c r="G112" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H112" s="4" t="str">
+        <x:v>巡店管培生、实习生</x:v>
+      </x:c>
+      <x:c r="I112" s="22" t="str">
+        <x:v>官方入口待核验</x:v>
+      </x:c>
+      <x:c r="J112" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K112" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L112" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M112" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N112" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O112" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P112" s="16" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q112" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" ht="54" customHeight="1">
+      <x:c r="A113" s="4" t="str">
+        <x:v>2026-06-01</x:v>
+      </x:c>
+      <x:c r="B113" s="4" t="str">
+        <x:v>友芝友实业集团</x:v>
+      </x:c>
+      <x:c r="C113" s="4" t="str">
+        <x:v>综合实业</x:v>
+      </x:c>
+      <x:c r="D113" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E113" s="4" t="str">
+        <x:v>武汉</x:v>
+      </x:c>
+      <x:c r="F113" s="4" t="str">
+        <x:v>管培生</x:v>
+      </x:c>
+      <x:c r="G113" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H113" s="4" t="str">
+        <x:v>青年领军人才管培生</x:v>
+      </x:c>
+      <x:c r="I113" s="15" t="str">
+        <x:v>https://www.yzyqh.com/jrwm</x:v>
+      </x:c>
+      <x:c r="J113" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K113" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L113" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M113" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N113" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O113" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P113" s="16" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q113" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" ht="54" customHeight="1">
+      <x:c r="A114" s="4" t="str">
+        <x:v>2026-05-29</x:v>
+      </x:c>
+      <x:c r="B114" s="4" t="str">
+        <x:v>银雁科技</x:v>
+      </x:c>
+      <x:c r="C114" s="4" t="str">
+        <x:v>金融科技服务</x:v>
+      </x:c>
+      <x:c r="D114" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E114" s="4" t="str">
+        <x:v>成都</x:v>
+      </x:c>
+      <x:c r="F114" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G114" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H114" s="4" t="str">
+        <x:v>人伤理赔</x:v>
+      </x:c>
+      <x:c r="I114" s="15" t="str">
+        <x:v>https://www.cfss.net.cn/</x:v>
+      </x:c>
+      <x:c r="J114" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K114" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L114" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M114" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N114" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O114" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P114" s="16" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q114" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" ht="54" customHeight="1">
+      <x:c r="A115" s="4" t="str">
+        <x:v>2026-05-15</x:v>
+      </x:c>
+      <x:c r="B115" s="4" t="str">
+        <x:v>知乎</x:v>
+      </x:c>
+      <x:c r="C115" s="4" t="str">
+        <x:v>互联网/内容平台</x:v>
+      </x:c>
+      <x:c r="D115" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E115" s="4" t="str">
+        <x:v>北京</x:v>
+      </x:c>
+      <x:c r="F115" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G115" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H115" s="4" t="str">
+        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
+      </x:c>
+      <x:c r="I115" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
+      </x:c>
+      <x:c r="J115" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K115" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L115" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M115" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N115" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O115" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P115" s="16" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q115" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" ht="54" customHeight="1">
+      <x:c r="A116" s="4" t="str">
+        <x:v>2026-05-08</x:v>
+      </x:c>
+      <x:c r="B116" s="4" t="str">
+        <x:v>招商银行长沙分行</x:v>
+      </x:c>
+      <x:c r="C116" s="4" t="str">
+        <x:v>银行/金融</x:v>
+      </x:c>
+      <x:c r="D116" s="4" t="str">
+        <x:v>股份制银行</x:v>
+      </x:c>
+      <x:c r="E116" s="4" t="str">
+        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+      </x:c>
+      <x:c r="F116" s="4" t="str">
+        <x:v>暑期实习/秋招直通</x:v>
+      </x:c>
+      <x:c r="G116" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H116" s="4" t="str">
+        <x:v>2027暑期实习生</x:v>
+      </x:c>
+      <x:c r="I116" s="15" t="str">
+        <x:v>https://career.cmbchina.com/</x:v>
+      </x:c>
+      <x:c r="J116" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K116" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L116" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M116" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N116" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O116" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P116" s="16" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q116" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" ht="54" customHeight="1">
+      <x:c r="A117" s="4" t="str">
+        <x:v>2026-04-22</x:v>
+      </x:c>
+      <x:c r="B117" s="4" t="str">
+        <x:v>华金证券</x:v>
+      </x:c>
+      <x:c r="C117" s="4" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="D117" s="4" t="str">
+        <x:v>国企</x:v>
+      </x:c>
+      <x:c r="E117" s="4" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F117" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G117" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H117" s="4" t="str">
+        <x:v>战略发展类</x:v>
+      </x:c>
+      <x:c r="I117" s="15" t="str">
+        <x:v>https://www.huajinsc.cn/</x:v>
+      </x:c>
+      <x:c r="J117" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K117" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L117" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M117" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N117" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O117" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P117" s="16" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q117" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -6262,7 +6686,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf3f71d89fc34b0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e1ab9c254a3487a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6292,7 +6716,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>近期有明确截止时间的项目（截至2026-08-05）</x:v>
+        <x:v>近期有明确截止时间的项目（截至2026-08-06）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -6743,7 +7167,7 @@
       <x:c r="O10" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P10" s="18" t="str">
+      <x:c r="P10" s="16" t="str">
         <x:v>B-高校/招聘平台转载，投前复核</x:v>
       </x:c>
       <x:c r="Q10" s="4" t="str">
@@ -6796,7 +7220,7 @@
       <x:c r="O11" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P11" s="18" t="str">
+      <x:c r="P11" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q11" s="4" t="str">
@@ -7220,7 +7644,7 @@
       <x:c r="O19" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P19" s="18" t="str">
+      <x:c r="P19" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q19" s="4" t="str">
@@ -7273,7 +7697,7 @@
       <x:c r="O20" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P20" s="18" t="str">
+      <x:c r="P20" s="16" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q20" s="4" t="str">
@@ -7340,7 +7764,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a447bf34539453a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R336494da190147f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7358,7 +7782,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="27" t="str">
-        <x:v>使用说明与统计（截至2026-08-05）</x:v>
+        <x:v>使用说明与统计（截至2026-08-06）</x:v>
       </x:c>
       <x:c r="B1" s="27"/>
       <x:c r="C1" s="27"/>
@@ -7561,7 +7985,7 @@
         <x:v>项目总数</x:v>
       </x:c>
       <x:c r="B16" s="28" t="n">
-        <x:v>106</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C16" s="25"/>
       <x:c r="D16" s="31" t="str">
@@ -7593,11 +8017,11 @@
         <x:v>A等级</x:v>
       </x:c>
       <x:c r="B18" s="28" t="n">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C18" s="25"/>
       <x:c r="D18" s="31" t="str">
-        <x:v>半导体/模拟IC</x:v>
+        <x:v>半导体/模拟混合信号IC</x:v>
       </x:c>
       <x:c r="E18" s="32" t="n">
         <x:v>1</x:v>
@@ -7609,7 +8033,7 @@
         <x:v>B等级</x:v>
       </x:c>
       <x:c r="B19" s="28" t="n">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C19" s="25"/>
       <x:c r="D19" s="31"/>
@@ -7641,7 +8065,7 @@
         <x:v>本次更新</x:v>
       </x:c>
       <x:c r="B22" s="25" t="str">
-        <x:v>新增1项；关闭0项；未来7天内明确截止1项；新增项目来自企业官方校园招聘页，免笔试政策以公告为准。</x:v>
+        <x:v>新增8项；关闭0项；未来7天内明确截止1项；新增项目来自企业官方校园招聘页，免笔试政策以公告为准。</x:v>
       </x:c>
       <x:c r="C22" s="25"/>
       <x:c r="D22" s="25"/>

--- a/2027届秋招投递信息_2026-07-24.xlsx
+++ b/2027届秋招投递信息_2026-07-24.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="Ra139c89b5f554056"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="R460d908b69be4f6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="Rccd815b14df84a64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R214d8c2d82f44384"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="R30a06d868c944cf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="Ra75e7e4526774c24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -195,7 +195,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="35">
+  <x:cellXfs count="36">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -239,6 +239,9 @@
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -301,8 +304,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q117" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:Q117"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q122" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:Q122"/>
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="开放投递时间"/>
     <x:tableColumn id="2" name="企业名称"/>
@@ -568,7 +571,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>2027届秋招投递信息（截至2026-08-06）</x:v>
+        <x:v>2027届秋招投递信息（截至2026-08-07）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -589,7 +592,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>每日更新：按开放时间倒序；本轮新增8项官方核验项目，关闭0项；第三方汇总入口不作为立即投递链接。</x:v>
+        <x:v>每日更新：按开放时间倒序；本轮新增5项官方核验项目，关闭0项；第三方汇总入口不作为立即投递链接。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -1090,369 +1093,369 @@
         <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>德州仪器TI</x:v>
+        <x:v>德勤-2027秋季校园招聘</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
-        <x:v>半导体/模拟与嵌入式芯片</x:v>
+        <x:v>会计审计/专业服务</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>外资/上市</x:v>
+        <x:v>外资/专业服务</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>上海及中国区岗位，以职位详情页为准</x:v>
+        <x:v>北京、上海、广州、深圳、重庆等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F12" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
+        <x:v>2027届应届毕业生；另有2027寒假实习生</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>人力资源培训生、税务专员、会计专员、产品市场工程师（模拟/嵌入式方向）及品牌营销专员</x:v>
+        <x:v>审计与鉴证、管理咨询、风险咨询、财务咨询、税务及法律、数字化等</x:v>
       </x:c>
       <x:c r="I12" s="15" t="str">
-        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
+        <x:v>https://www.deloitte.com/cn/zh/careers.html</x:v>
       </x:c>
       <x:c r="J12" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-31（部分岗位招满提前关闭）</x:v>
       </x:c>
       <x:c r="K12" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否（网申后通常安排在线笔试，具体以岗位流程为准）</x:v>
       </x:c>
       <x:c r="L12" s="4" t="str">
-        <x:v>本轮新增；官方职位页已发布多项中国区2027校园招聘岗位</x:v>
+        <x:v>本轮新增；可信高校就业公众号发布德勤2027校招信息，官方招聘入口已核验</x:v>
       </x:c>
       <x:c r="M12" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N12" s="4" t="str">
-        <x:v>岗位分批发布，当前核验到的2027校招岗位发布日期为2026-08-04；投递前按China地区和岗位关键词筛选。</x:v>
+        <x:v>秋季全职与寒假实习并行；网申完成后通常收到在线笔试邀请，部分岗位招满会提前结束网申；德勤中国不收取招聘费用，谨防第三方收费。</x:v>
       </x:c>
       <x:c r="O12" s="15" t="str">
-        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
-      </x:c>
-      <x:c r="P12" s="14" t="str">
-        <x:v>A-企业官方职位页已核验</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3ODQ3NTIzMA==&amp;mid=2651327099&amp;idx=4&amp;sn=465f2aa047b826709fa081aa25e633f5&amp;chksm=85d23ac1f4759b74460c0c675e988bc8434725c02e7a91d66890eb4795c8000b3dbe9fcf4a48&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P12" s="16" t="str">
+        <x:v>B-可信高校就业公众号公告含德勤官方招聘入口</x:v>
       </x:c>
       <x:c r="Q12" s="4" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="4" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="B13" s="4" t="str">
-        <x:v>影石Insta360</x:v>
+        <x:v>德州仪器TI</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
-        <x:v>消费电子/智能影像</x:v>
+        <x:v>半导体/模拟与嵌入式芯片</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
+        <x:v>外资/上市</x:v>
+      </x:c>
+      <x:c r="E13" s="4" t="str">
+        <x:v>上海及中国区岗位，以职位详情页为准</x:v>
+      </x:c>
+      <x:c r="F13" s="4" t="str">
+        <x:v>正式批/校园招聘</x:v>
+      </x:c>
+      <x:c r="G13" s="4" t="str">
+        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
+      </x:c>
+      <x:c r="H13" s="4" t="str">
+        <x:v>人力资源培训生、税务专员、会计专员、产品市场工程师（模拟/嵌入式方向）及品牌营销专员</x:v>
+      </x:c>
+      <x:c r="I13" s="15" t="str">
+        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
+      </x:c>
+      <x:c r="J13" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K13" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L13" s="4" t="str">
+        <x:v>本轮新增；官方职位页已发布多项中国区2027校园招聘岗位</x:v>
+      </x:c>
+      <x:c r="M13" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N13" s="4" t="str">
+        <x:v>岗位分批发布，当前核验到的2027校招岗位发布日期为2026-08-04；投递前按China地区和岗位关键词筛选。</x:v>
+      </x:c>
+      <x:c r="O13" s="15" t="str">
+        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
+      </x:c>
+      <x:c r="P13" s="14" t="str">
+        <x:v>A-企业官方职位页已核验</x:v>
+      </x:c>
+      <x:c r="Q13" s="4" t="str">
+        <x:v>2026-08-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="4" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+      <x:c r="B14" s="4" t="str">
+        <x:v>哔哩哔哩-2027秋季校园招聘</x:v>
+      </x:c>
+      <x:c r="C14" s="4" t="str">
+        <x:v>互联网/内容平台/游戏</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
-      <x:c r="E13" s="4" t="str">
-        <x:v>深圳、上海、珠海</x:v>
-      </x:c>
-      <x:c r="F13" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
-      </x:c>
-      <x:c r="G13" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H13" s="4" t="str">
-        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
-      </x:c>
-      <x:c r="I13" s="15" t="str">
-        <x:v>https://www.insta360.com/cn/jobs</x:v>
-      </x:c>
-      <x:c r="J13" s="4" t="str">
-        <x:v>2026-10-31</x:v>
-      </x:c>
-      <x:c r="K13" s="4" t="str">
-        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
-      </x:c>
-      <x:c r="L13" s="4" t="str">
-        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
-      </x:c>
-      <x:c r="M13" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
-      </x:c>
-      <x:c r="N13" s="4" t="str">
-        <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
-      </x:c>
-      <x:c r="O13" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P13" s="14" t="str">
-        <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
-      </x:c>
-      <x:c r="Q13" s="4" t="str">
-        <x:v>2026-08-04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="54" customHeight="1">
-      <x:c r="A14" s="17" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B14" s="17" t="str">
-        <x:v>恒丰银行总行-雏鹰计划</x:v>
-      </x:c>
-      <x:c r="C14" s="17" t="str">
-        <x:v>银行/金融</x:v>
-      </x:c>
-      <x:c r="D14" s="17" t="str">
-        <x:v>股份制商业银行</x:v>
-      </x:c>
-      <x:c r="E14" s="17" t="str">
-        <x:v>总行及相关机构，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F14" s="17" t="str">
-        <x:v>暑期实习/秋招储备</x:v>
-      </x:c>
-      <x:c r="G14" s="17" t="str">
-        <x:v>2027届硕士及以上，以公告要求为准</x:v>
-      </x:c>
-      <x:c r="H14" s="17" t="str">
-        <x:v>总行实习生，具体专业和方向以官方公告为准</x:v>
-      </x:c>
-      <x:c r="I14" s="18" t="str">
-        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
-      </x:c>
-      <x:c r="J14" s="17" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K14" s="17" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L14" s="17" t="str">
-        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M14" s="17" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N14" s="17" t="str">
-        <x:v>官方公告显示7月31日24:00截止，实习期安排和具体岗位以恒丰银行招聘官网为准。</x:v>
-      </x:c>
-      <x:c r="O14" s="18" t="str">
-        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
+      <x:c r="E14" s="4" t="str">
+        <x:v>上海、北京、广州、深圳、杭州等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="str">
+        <x:v>正式批/秋季校园招聘</x:v>
+      </x:c>
+      <x:c r="G14" s="4" t="str">
+        <x:v>毕业时间为2026年9月1日至2027年8月31日的海内外2027届应届生</x:v>
+      </x:c>
+      <x:c r="H14" s="4" t="str">
+        <x:v>技术、产品、运营、市场、设计、职能及游戏等全序列岗位；另有B-UP顶尖技术人才项目</x:v>
+      </x:c>
+      <x:c r="I14" s="15" t="str">
+        <x:v>https://jobs.bilibili.com/campus</x:v>
+      </x:c>
+      <x:c r="J14" s="4" t="str">
+        <x:v>未公布/岗位招满即止</x:v>
+      </x:c>
+      <x:c r="K14" s="4" t="str">
+        <x:v>官方未统一说明</x:v>
+      </x:c>
+      <x:c r="L14" s="4" t="str">
+        <x:v>本轮新增；哔哩哔哩官方校园招聘页显示2027届秋季校园招聘正式启动</x:v>
+      </x:c>
+      <x:c r="M14" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N14" s="4" t="str">
+        <x:v>每位同学最多投递2个志愿，按投递先后认定一、二志愿；可在校招官网投递记录或“哔哩哔哩招聘”公众号查询进度，岗位招满可能提前下架。</x:v>
+      </x:c>
+      <x:c r="O14" s="15" t="str">
+        <x:v>https://jobs.bilibili.com/campus</x:v>
       </x:c>
       <x:c r="P14" s="14" t="str">
-        <x:v>A-企业官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q14" s="17" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q14" s="4" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="54" customHeight="1">
+      <x:c r="A15" s="16" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15" ht="54" customHeight="1">
-      <x:c r="A15" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B15" s="4" t="str">
-        <x:v>四方股份</x:v>
-      </x:c>
-      <x:c r="C15" s="4" t="str">
-        <x:v>电力系统/工业自动化</x:v>
-      </x:c>
-      <x:c r="D15" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E15" s="4" t="str">
-        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
-      </x:c>
-      <x:c r="F15" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G15" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H15" s="4" t="str">
-        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
-      </x:c>
-      <x:c r="I15" s="15" t="str">
-        <x:v>https://www.sf-auto.com/campus</x:v>
-      </x:c>
-      <x:c r="J15" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K15" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L15" s="4" t="str">
-        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="M15" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N15" s="4" t="str">
-        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
-      </x:c>
-      <x:c r="O15" s="15" t="str">
-        <x:v>https://www.sf-auto.com/campus</x:v>
+      <x:c r="B15" s="16" t="str">
+        <x:v>中泰证券-2027秋季校园招聘</x:v>
+      </x:c>
+      <x:c r="C15" s="16" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="str">
+        <x:v>国有控股/上市</x:v>
+      </x:c>
+      <x:c r="E15" s="16" t="str">
+        <x:v>济南、北京、上海、深圳、青岛及全国分支机构</x:v>
+      </x:c>
+      <x:c r="F15" s="16" t="str">
+        <x:v>正式批/秋季校园招聘</x:v>
+      </x:c>
+      <x:c r="G15" s="16" t="str">
+        <x:v>2027届高校毕业生（择业期内高校毕业生亦可报名）</x:v>
+      </x:c>
+      <x:c r="H15" s="16" t="str">
+        <x:v>投行、投资、研究、机构、金融科技、总部中后台、分支机构及旗下金融子公司岗位，共86个岗位、拟招227人</x:v>
+      </x:c>
+      <x:c r="I15" s="17" t="str">
+        <x:v>https://zts.hotjob.cn/school.html</x:v>
+      </x:c>
+      <x:c r="J15" s="16" t="str">
+        <x:v>2026-08-16 24:00</x:v>
+      </x:c>
+      <x:c r="K15" s="16" t="str">
+        <x:v>否（招聘程序明确包含笔试、面试）</x:v>
+      </x:c>
+      <x:c r="L15" s="16" t="str">
+        <x:v>本轮新增；山东省国资委公告与中泰证券官方招聘网站已交叉核验</x:v>
+      </x:c>
+      <x:c r="M15" s="16" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N15" s="16" t="str">
+        <x:v>母公司业务条线、金融科技和总部中后台多要求硕士及以上，分支机构财富管理类岗位本科可报；统一网上报名，可通过中泰证券官方招聘网站或“中泰证券招聘”官方公众号投递，不收取任何费用。</x:v>
+      </x:c>
+      <x:c r="O15" s="17" t="str">
+        <x:v>https://www.selectshandong.com/recruit/company/833895033675845.html</x:v>
       </x:c>
       <x:c r="P15" s="14" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="Q15" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>A-山东省国资委公告与企业官方招聘网站交叉核验</x:v>
+      </x:c>
+      <x:c r="Q15" s="16" t="str">
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
-        <x:v>苏纳光电</x:v>
+        <x:v>字节跳动-2027校园招聘</x:v>
       </x:c>
       <x:c r="C16" s="4" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>互联网/AI/内容平台</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>苏州、上海</x:v>
+        <x:v>北京、上海、深圳、杭州等，具体以岗位页为准</x:v>
       </x:c>
       <x:c r="F16" s="4" t="str">
-        <x:v>提前批/Open Day</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
+        <x:v>毕业时间为2026年9月至2027年8月的应届生</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
+        <x:v>研发、产品、运营、设计、市场、职能/支持、销售、游戏策划八大类；新增AI全栈工程师、AI Agent开发等方向</x:v>
       </x:c>
       <x:c r="I16" s="15" t="str">
-        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
       </x:c>
       <x:c r="J16" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-12-31（岗位招满可能提前下架）</x:v>
       </x:c>
       <x:c r="K16" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L16" s="4" t="str">
-        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
+        <x:v>本轮新增；字节跳动官方校园招聘入口已核验，2027届校招于2026-08-03启动</x:v>
       </x:c>
       <x:c r="M16" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N16" s="4" t="str">
-        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
+        <x:v>普通校招投递机会按阶段刷新：2026-08-03至2026-12-31有两次机会，2027-01-01刷新两次；岗位招满会下架。AI产品早鸟通道、前沿技术人才校招、Seed大模型人才校招等专项不占用普通投递机会。</x:v>
       </x:c>
       <x:c r="O16" s="15" t="str">
-        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
       </x:c>
       <x:c r="P16" s="14" t="str">
-        <x:v>A-企业官方校园招聘系统已核验</x:v>
+        <x:v>A-企业官方校园招聘入口已核验</x:v>
       </x:c>
       <x:c r="Q16" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="4" t="str">
+        <x:v>2026-08-01</x:v>
+      </x:c>
+      <x:c r="B17" s="4" t="str">
+        <x:v>影石Insta360</x:v>
+      </x:c>
+      <x:c r="C17" s="4" t="str">
+        <x:v>消费电子/智能影像</x:v>
+      </x:c>
+      <x:c r="D17" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E17" s="4" t="str">
+        <x:v>深圳、上海、珠海</x:v>
+      </x:c>
+      <x:c r="F17" s="4" t="str">
+        <x:v>正式批/秋招</x:v>
+      </x:c>
+      <x:c r="G17" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H17" s="4" t="str">
+        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+      </x:c>
+      <x:c r="I17" s="15" t="str">
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
+      </x:c>
+      <x:c r="J17" s="4" t="str">
+        <x:v>2026-10-31</x:v>
+      </x:c>
+      <x:c r="K17" s="4" t="str">
+        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
+      </x:c>
+      <x:c r="L17" s="4" t="str">
+        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
+      </x:c>
+      <x:c r="M17" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N17" s="4" t="str">
+        <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
+      </x:c>
+      <x:c r="O17" s="15" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P17" s="14" t="str">
+        <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
+      </x:c>
+      <x:c r="Q17" s="4" t="str">
+        <x:v>2026-08-04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="54" customHeight="1">
+      <x:c r="A18" s="18" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
-      <x:c r="B17" s="4" t="str">
-        <x:v>特斯拉中国</x:v>
-      </x:c>
-      <x:c r="C17" s="4" t="str">
-        <x:v>新能源汽车/智能制造</x:v>
-      </x:c>
-      <x:c r="D17" s="4" t="str">
-        <x:v>外资/上市</x:v>
-      </x:c>
-      <x:c r="E17" s="4" t="str">
-        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
-      </x:c>
-      <x:c r="F17" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
-      </x:c>
-      <x:c r="G17" s="4" t="str">
-        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H17" s="4" t="str">
-        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
-      </x:c>
-      <x:c r="I17" s="15" t="str">
-        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
-      </x:c>
-      <x:c r="J17" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K17" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L17" s="4" t="str">
-        <x:v>本轮新确认；企业官方职位页已核验</x:v>
-      </x:c>
-      <x:c r="M17" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N17" s="4" t="str">
-        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
-      </x:c>
-      <x:c r="O17" s="15" t="str">
-        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
-      </x:c>
-      <x:c r="P17" s="14" t="str">
-        <x:v>A-企业官方职位页已核验</x:v>
-      </x:c>
-      <x:c r="Q17" s="4" t="str">
+      <x:c r="B18" s="18" t="str">
+        <x:v>恒丰银行总行-雏鹰计划</x:v>
+      </x:c>
+      <x:c r="C18" s="18" t="str">
+        <x:v>银行/金融</x:v>
+      </x:c>
+      <x:c r="D18" s="18" t="str">
+        <x:v>股份制商业银行</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="str">
+        <x:v>总行及相关机构，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F18" s="18" t="str">
+        <x:v>暑期实习/秋招储备</x:v>
+      </x:c>
+      <x:c r="G18" s="18" t="str">
+        <x:v>2027届硕士及以上，以公告要求为准</x:v>
+      </x:c>
+      <x:c r="H18" s="18" t="str">
+        <x:v>总行实习生，具体专业和方向以官方公告为准</x:v>
+      </x:c>
+      <x:c r="I18" s="19" t="str">
+        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18" ht="54" customHeight="1">
-      <x:c r="A18" s="17" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B18" s="17" t="str">
-        <x:v>天健会计师事务所-暑期实习培训生</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="str">
-        <x:v>会计审计/专业服务</x:v>
-      </x:c>
-      <x:c r="D18" s="17" t="str">
-        <x:v>会计师事务所</x:v>
-      </x:c>
-      <x:c r="E18" s="17" t="str">
-        <x:v>上海等，以职位页为准</x:v>
-      </x:c>
-      <x:c r="F18" s="17" t="str">
-        <x:v>暑期实习/培训生</x:v>
-      </x:c>
-      <x:c r="G18" s="17" t="str">
-        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H18" s="17" t="str">
-        <x:v>财务审计暑期实习培训生</x:v>
-      </x:c>
-      <x:c r="I18" s="18" t="str">
-        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
-      </x:c>
-      <x:c r="J18" s="17" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K18" s="17" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L18" s="17" t="str">
+      <x:c r="K18" s="18" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L18" s="18" t="str">
         <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
       </x:c>
-      <x:c r="M18" s="17" t="str">
+      <x:c r="M18" s="18" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N18" s="17" t="str">
-        <x:v>公开公告显示7月31日截止；具体办公地点、专业要求和实习安排以天健招聘官网为准。</x:v>
-      </x:c>
-      <x:c r="O18" s="18" t="str">
-        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
+      <x:c r="N18" s="18" t="str">
+        <x:v>官方公告显示7月31日24:00截止，实习期安排和具体岗位以恒丰银行招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O18" s="19" t="str">
+        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
       </x:c>
       <x:c r="P18" s="14" t="str">
-        <x:v>A-企业官方招聘入口已核验</x:v>
-      </x:c>
-      <x:c r="Q18" s="17" t="str">
+        <x:v>A-企业官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q18" s="18" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
@@ -1461,28 +1464,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>西安紫光国芯半导体</x:v>
+        <x:v>四方股份</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>电力系统/工业自动化</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>西安、上海、成都</x:v>
+        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
+        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
       </x:c>
       <x:c r="I19" s="15" t="str">
-        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
+        <x:v>https://www.sf-auto.com/campus</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1491,19 +1494,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L19" s="4" t="str">
-        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
+        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="M19" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N19" s="4" t="str">
-        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
+        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
       </x:c>
       <x:c r="O19" s="15" t="str">
-        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
+        <x:v>https://www.sf-auto.com/campus</x:v>
       </x:c>
       <x:c r="P19" s="14" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
+        <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="Q19" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1514,28 +1517,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
-        <x:v>新大陆自动识别</x:v>
+        <x:v>苏纳光电</x:v>
       </x:c>
       <x:c r="C20" s="4" t="str">
-        <x:v>计算机视觉/智能硬件</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>民营/上市公司子公司</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>福州总部及全国/海外岗位</x:v>
+        <x:v>苏州、上海</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批/Open Day</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
+        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
+        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
       </x:c>
       <x:c r="I20" s="15" t="str">
-        <x:v>https://nlscan.zhiye.com/Campus</x:v>
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1544,19 +1547,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L20" s="4" t="str">
-        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
+        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
       </x:c>
       <x:c r="M20" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N20" s="4" t="str">
-        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
+        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
       </x:c>
       <x:c r="O20" s="15" t="str">
-        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="P20" s="14" t="str">
-        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
+        <x:v>A-企业官方校园招聘系统已核验</x:v>
       </x:c>
       <x:c r="Q20" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1567,28 +1570,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B21" s="4" t="str">
-        <x:v>兆易创新</x:v>
+        <x:v>特斯拉中国</x:v>
       </x:c>
       <x:c r="C21" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>新能源汽车/智能制造</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>外资/上市</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>北京、上海、武汉、合肥等，以岗位页为准</x:v>
+        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
       </x:c>
       <x:c r="F21" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>芯片设计、验证、嵌入式、软件、应用、测试及职能岗位</x:v>
+        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
       </x:c>
       <x:c r="I21" s="15" t="str">
-        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
       </x:c>
       <x:c r="J21" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1597,75 +1600,75 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L21" s="4" t="str">
-        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
+        <x:v>本轮新确认；企业官方职位页已核验</x:v>
       </x:c>
       <x:c r="M21" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N21" s="4" t="str">
-        <x:v>提前批岗位和城市以兆易创新官方加入我们页面为准，投递前确认职位仍开放。</x:v>
+        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
       </x:c>
       <x:c r="O21" s="15" t="str">
-        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
       </x:c>
       <x:c r="P21" s="14" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
+        <x:v>A-企业官方职位页已核验</x:v>
       </x:c>
       <x:c r="Q21" s="4" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
-      <x:c r="A22" s="4" t="str">
+      <x:c r="A22" s="18" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
-      <x:c r="B22" s="4" t="str">
-        <x:v>中国航空发动机集团</x:v>
-      </x:c>
-      <x:c r="C22" s="4" t="str">
-        <x:v>航空发动机/军工</x:v>
-      </x:c>
-      <x:c r="D22" s="4" t="str">
-        <x:v>央企</x:v>
-      </x:c>
-      <x:c r="E22" s="4" t="str">
-        <x:v>全国各院所及下属单位</x:v>
-      </x:c>
-      <x:c r="F22" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
-      </x:c>
-      <x:c r="G22" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H22" s="4" t="str">
-        <x:v>研发设计、工艺、试验、制造、材料、控制、软件及管理岗位</x:v>
-      </x:c>
-      <x:c r="I22" s="15" t="str">
-        <x:v>https://aecc.iguopin.com/notice2</x:v>
-      </x:c>
-      <x:c r="J22" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K22" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L22" s="4" t="str">
-        <x:v>本轮新确认；集团官方招聘平台已核验</x:v>
-      </x:c>
-      <x:c r="M22" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N22" s="4" t="str">
-        <x:v>各单位岗位和截止时间不同，需在中国航发招聘平台按单位和专业筛选。</x:v>
-      </x:c>
-      <x:c r="O22" s="15" t="str">
-        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/n2588350/c35693219/content.html</x:v>
+      <x:c r="B22" s="18" t="str">
+        <x:v>天健会计师事务所-暑期实习培训生</x:v>
+      </x:c>
+      <x:c r="C22" s="18" t="str">
+        <x:v>会计审计/专业服务</x:v>
+      </x:c>
+      <x:c r="D22" s="18" t="str">
+        <x:v>会计师事务所</x:v>
+      </x:c>
+      <x:c r="E22" s="18" t="str">
+        <x:v>上海等，以职位页为准</x:v>
+      </x:c>
+      <x:c r="F22" s="18" t="str">
+        <x:v>暑期实习/培训生</x:v>
+      </x:c>
+      <x:c r="G22" s="18" t="str">
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H22" s="18" t="str">
+        <x:v>财务审计暑期实习培训生</x:v>
+      </x:c>
+      <x:c r="I22" s="19" t="str">
+        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K22" s="18" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L22" s="18" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M22" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N22" s="18" t="str">
+        <x:v>公开公告显示7月31日截止；具体办公地点、专业要求和实习安排以天健招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O22" s="19" t="str">
+        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
       </x:c>
       <x:c r="P22" s="14" t="str">
-        <x:v>A-国资委公告与集团招聘平台交叉核验</x:v>
-      </x:c>
-      <x:c r="Q22" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>A-企业官方招聘入口已核验</x:v>
+      </x:c>
+      <x:c r="Q22" s="18" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
@@ -1673,28 +1676,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B23" s="4" t="str">
-        <x:v>中粮资本-粮曦计划</x:v>
+        <x:v>西安紫光国芯半导体</x:v>
       </x:c>
       <x:c r="C23" s="4" t="str">
-        <x:v>金融/投资/资管</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>央企/金融控股</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>西安、上海、成都</x:v>
       </x:c>
       <x:c r="F23" s="4" t="str">
-        <x:v>培养计划/实习</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>2027-2029届硕士及以上，以公告要求为准</x:v>
+        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>金融、投资、风险、运营、人力资源及综合管理方向</x:v>
+        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
       </x:c>
       <x:c r="I23" s="15" t="str">
-        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
       </x:c>
       <x:c r="J23" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1709,10 +1712,10 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N23" s="4" t="str">
-        <x:v>粮曦计划具体批次、面向人群和岗位以中粮资本官方加入我们页面及公告为准。</x:v>
+        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
       </x:c>
       <x:c r="O23" s="15" t="str">
-        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
       </x:c>
       <x:c r="P23" s="14" t="str">
         <x:v>A-企业官方招聘页已核验</x:v>
@@ -1726,49 +1729,49 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B24" s="4" t="str">
-        <x:v>中移九天人工智能科技</x:v>
+        <x:v>新大陆自动识别</x:v>
       </x:c>
       <x:c r="C24" s="4" t="str">
-        <x:v>AI/软件/云计算</x:v>
+        <x:v>计算机视觉/智能硬件</x:v>
       </x:c>
       <x:c r="D24" s="4" t="str">
-        <x:v>央企子公司</x:v>
+        <x:v>民营/上市公司子公司</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>北京、西安、广州、深圳</x:v>
+        <x:v>福州总部及全国/海外岗位</x:v>
       </x:c>
       <x:c r="F24" s="4" t="str">
-        <x:v>正式批/超级实习生</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
+        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
+        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
       </x:c>
       <x:c r="I24" s="15" t="str">
-        <x:v>https://job.10086.cn/personal/campus/</x:v>
+        <x:v>https://nlscan.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J24" s="4" t="str">
-        <x:v>2026-09-27</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K24" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L24" s="4" t="str">
-        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
+        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
       </x:c>
       <x:c r="M24" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N24" s="4" t="str">
-        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
+        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
       </x:c>
       <x:c r="O24" s="15" t="str">
-        <x:v>https://job.10086.cn/personal/campus/</x:v>
+        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
       </x:c>
       <x:c r="P24" s="14" t="str">
-        <x:v>A-中国移动官方招聘平台已核验</x:v>
+        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
       </x:c>
       <x:c r="Q24" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1776,137 +1779,137 @@
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
       <x:c r="A25" s="4" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B25" s="4" t="str">
-        <x:v>广州市卓越教育集团</x:v>
+        <x:v>兆易创新</x:v>
       </x:c>
       <x:c r="C25" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D25" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E25" s="4" t="str">
-        <x:v>广州等，以职位页为准</x:v>
+        <x:v>北京、上海、武汉、合肥等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F25" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G25" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H25" s="4" t="str">
-        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+        <x:v>芯片设计、验证、嵌入式、软件、应用、测试及职能岗位</x:v>
       </x:c>
       <x:c r="I25" s="15" t="str">
-        <x:v>https://zyjob.hotjob.cn/</x:v>
+        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
       </x:c>
       <x:c r="J25" s="4" t="str">
-        <x:v>2026-10-26</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K25" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L25" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
+        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="M25" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N25" s="4" t="str">
-        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
+        <x:v>提前批岗位和城市以兆易创新官方加入我们页面为准，投递前确认职位仍开放。</x:v>
       </x:c>
       <x:c r="O25" s="15" t="str">
-        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
+        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
       </x:c>
       <x:c r="P25" s="14" t="str">
-        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q25" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="54" customHeight="1">
       <x:c r="A26" s="4" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B26" s="4" t="str">
-        <x:v>搜狐畅游</x:v>
+        <x:v>中国航空发动机集团</x:v>
       </x:c>
       <x:c r="C26" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>航空发动机/军工</x:v>
       </x:c>
       <x:c r="D26" s="4" t="str">
-        <x:v>民营/互联网</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>以岗位页面为准</x:v>
+        <x:v>全国各院所及下属单位</x:v>
       </x:c>
       <x:c r="F26" s="4" t="str">
-        <x:v>提前批/校园招聘</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>2027届毕业生（部分岗位兼收2026届）</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>游戏策划、游戏开发、游戏美术、游戏运营、业务支持、平台开发、平台职能、游戏测试8大类岗位</x:v>
+        <x:v>研发设计、工艺、试验、制造、材料、控制、软件及管理岗位</x:v>
       </x:c>
       <x:c r="I26" s="15" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/cyou-inc/42233?recommendCode=DSRgNQU7#/jobs</x:v>
+        <x:v>https://aecc.iguopin.com/notice2</x:v>
       </x:c>
       <x:c r="J26" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K26" s="4" t="str">
-        <x:v>非免笔试；提前批未录取可参加后续统一笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L26" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；官方投递入口已核验</x:v>
+        <x:v>本轮复核；中国航发官方招聘平台当前显示2027届校园招聘岗位持续开放</x:v>
       </x:c>
       <x:c r="M26" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N26" s="4" t="str">
-        <x:v>深圳北理莫斯科大学就业网公告《搜狐畅游2027届秋季校园招聘提前批正式启动！》发布于2026-07-28；提前批流程快、部分岗位有直通面试机会，未被录取者可参与后续统一笔试，部分热招岗位招满即停。</x:v>
+        <x:v>各单位岗位和截止时间不同，需在中国航发招聘平台按单位和专业筛选；本次复核到159家招聘单位及多项研发、工艺、制造、控制和软件岗位。</x:v>
       </x:c>
       <x:c r="O26" s="15" t="str">
-        <x:v>https://career.smbu.edu.cn/detail/online?id=3535355</x:v>
-      </x:c>
-      <x:c r="P26" s="16" t="str">
-        <x:v>B-可信高校就业网公告含官方投递链接</x:v>
+        <x:v>https://aecc.iguopin.com/job</x:v>
+      </x:c>
+      <x:c r="P26" s="14" t="str">
+        <x:v>A-中国航发官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="Q26" s="4" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="54" customHeight="1">
       <x:c r="A27" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B27" s="4" t="str">
-        <x:v>我乐家居</x:v>
+        <x:v>中粮资本-粮曦计划</x:v>
       </x:c>
       <x:c r="C27" s="4" t="str">
-        <x:v>家居/消费品/智能制造</x:v>
+        <x:v>金融/投资/资管</x:v>
       </x:c>
       <x:c r="D27" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企/金融控股</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F27" s="4" t="str">
-        <x:v>提前批/校园招聘</x:v>
+        <x:v>培养计划/实习</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>2027届本科及以上，以岗位要求为准</x:v>
+        <x:v>2027-2029届硕士及以上，以公告要求为准</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
+        <x:v>金融、投资、风险、运营、人力资源及综合管理方向</x:v>
       </x:c>
       <x:c r="I27" s="15" t="str">
-        <x:v>https://olo-home.zhiye.com/Campus</x:v>
+        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
       </x:c>
       <x:c r="J27" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1915,210 +1918,210 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L27" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
+        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
       </x:c>
       <x:c r="M27" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N27" s="4" t="str">
-        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
+        <x:v>粮曦计划具体批次、面向人群和岗位以中粮资本官方加入我们页面及公告为准。</x:v>
       </x:c>
       <x:c r="O27" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P27" s="16" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
+        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+      </x:c>
+      <x:c r="P27" s="14" t="str">
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q27" s="4" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="54" customHeight="1">
       <x:c r="A28" s="4" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B28" s="4" t="str">
-        <x:v>轩宇信息</x:v>
+        <x:v>中移九天人工智能科技</x:v>
       </x:c>
       <x:c r="C28" s="4" t="str">
-        <x:v>航天/军工信息化/软件</x:v>
+        <x:v>AI/软件/云计算</x:v>
       </x:c>
       <x:c r="D28" s="4" t="str">
-        <x:v>央企子公司/高新技术企业</x:v>
+        <x:v>央企子公司</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>北京、杭州、西安</x:v>
+        <x:v>北京、西安、广州、深圳</x:v>
       </x:c>
       <x:c r="F28" s="4" t="str">
-        <x:v>AI专项/提前批</x:v>
+        <x:v>正式批/超级实习生</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
+        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
       </x:c>
       <x:c r="I28" s="15" t="str">
-        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="J28" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-09-27</x:v>
       </x:c>
       <x:c r="K28" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L28" s="4" t="str">
-        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
+        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
       </x:c>
       <x:c r="M28" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N28" s="4" t="str">
-        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
+        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
       </x:c>
       <x:c r="O28" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="P28" s="14" t="str">
-        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
+        <x:v>A-中国移动官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="Q28" s="4" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="54" customHeight="1">
       <x:c r="A29" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B29" s="4" t="str">
-        <x:v>卡尔动力</x:v>
+        <x:v>广州市卓越教育集团</x:v>
       </x:c>
       <x:c r="C29" s="4" t="str">
-        <x:v>自动驾驶/智能汽车</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D29" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E29" s="4" t="str">
-        <x:v>北京、上海、天津等</x:v>
+        <x:v>广州等，以职位页为准</x:v>
       </x:c>
       <x:c r="F29" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G29" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H29" s="4" t="str">
-        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
+        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
       <x:c r="I29" s="15" t="str">
-        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
+        <x:v>https://zyjob.hotjob.cn/</x:v>
       </x:c>
       <x:c r="J29" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-26</x:v>
       </x:c>
       <x:c r="K29" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L29" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
+        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
       </x:c>
       <x:c r="M29" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N29" s="4" t="str">
-        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
+        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
       </x:c>
       <x:c r="O29" s="15" t="str">
-        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
-      </x:c>
-      <x:c r="P29" s="16" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
+        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
+      </x:c>
+      <x:c r="P29" s="14" t="str">
+        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
       </x:c>
       <x:c r="Q29" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="54" customHeight="1">
       <x:c r="A30" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B30" s="4" t="str">
-        <x:v>深信服-X-STAR顶尖人才计划</x:v>
+        <x:v>搜狐畅游</x:v>
       </x:c>
       <x:c r="C30" s="4" t="str">
-        <x:v>网络安全/云计算/软件</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D30" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/互联网</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
+        <x:v>以岗位页面为准</x:v>
       </x:c>
       <x:c r="F30" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>顶尖人才，本硕博按岗位要求</x:v>
+        <x:v>2027届毕业生（部分岗位兼收2026届）</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
+        <x:v>游戏策划、游戏开发、游戏美术、游戏运营、业务支持、平台开发、平台职能、游戏测试8大类岗位</x:v>
       </x:c>
       <x:c r="I30" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
+        <x:v>https://app.mokahr.com/m/campus_apply/cyou-inc/42233?recommendCode=DSRgNQU7#/jobs</x:v>
       </x:c>
       <x:c r="J30" s="4" t="str">
-        <x:v>2026-09-25</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K30" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>非免笔试；提前批未录取可参加后续统一笔试</x:v>
       </x:c>
       <x:c r="L30" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>可信高校就业网公告显示开放；官方投递入口已核验</x:v>
       </x:c>
       <x:c r="M30" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N30" s="4" t="str">
-        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
+        <x:v>深圳北理莫斯科大学就业网公告《搜狐畅游2027届秋季校园招聘提前批正式启动！》发布于2026-07-28；提前批流程快、部分岗位有直通面试机会，未被录取者可参与后续统一笔试，部分热招岗位招满即停。</x:v>
       </x:c>
       <x:c r="O30" s="15" t="str">
-        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
-      </x:c>
-      <x:c r="P30" s="14" t="str">
-        <x:v>A-高校就业网含官方投递链接</x:v>
+        <x:v>https://career.smbu.edu.cn/detail/online?id=3535355</x:v>
+      </x:c>
+      <x:c r="P30" s="16" t="str">
+        <x:v>B-可信高校就业网公告含官方投递链接</x:v>
       </x:c>
       <x:c r="Q30" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="54" customHeight="1">
       <x:c r="A31" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="B31" s="4" t="str">
-        <x:v>希夕智能</x:v>
+        <x:v>我乐家居</x:v>
       </x:c>
       <x:c r="C31" s="4" t="str">
-        <x:v>机器人/智能制造</x:v>
+        <x:v>家居/消费品/智能制造</x:v>
       </x:c>
       <x:c r="D31" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F31" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>2027届本科及以上</x:v>
+        <x:v>2027届本科及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
+        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
       </x:c>
       <x:c r="I31" s="15" t="str">
-        <x:v>https://sunseed.zhiye.com/jobs</x:v>
+        <x:v>https://olo-home.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J31" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2127,104 +2130,104 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L31" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
       </x:c>
       <x:c r="M31" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N31" s="4" t="str">
-        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
+        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
       </x:c>
       <x:c r="O31" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
       </x:c>
       <x:c r="P31" s="16" t="str">
-        <x:v>B-高校就业平台转载企业来源</x:v>
+        <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
       <x:c r="Q31" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="54" customHeight="1">
       <x:c r="A32" s="4" t="str">
-        <x:v>不晚于2026-07-24</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="B32" s="4" t="str">
-        <x:v>中国兵器工业集团</x:v>
+        <x:v>轩宇信息</x:v>
       </x:c>
       <x:c r="C32" s="4" t="str">
-        <x:v>军工/高端装备</x:v>
+        <x:v>航天/军工信息化/软件</x:v>
       </x:c>
       <x:c r="D32" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>央企子公司/高新技术企业</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
-        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
+        <x:v>北京、杭州、西安</x:v>
       </x:c>
       <x:c r="F32" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>AI专项/提前批</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
-        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
+        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
       </x:c>
       <x:c r="I32" s="15" t="str">
-        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
+        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
       </x:c>
       <x:c r="J32" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K32" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L32" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
       </x:c>
       <x:c r="M32" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N32" s="4" t="str">
-        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
+        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
       </x:c>
       <x:c r="O32" s="15" t="str">
-        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
-      </x:c>
-      <x:c r="P32" s="16" t="str">
-        <x:v>B-公开招聘公告/集团入口</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P32" s="14" t="str">
+        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
       </x:c>
       <x:c r="Q32" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="54" customHeight="1">
       <x:c r="A33" s="4" t="str">
-        <x:v>2026-07-23</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B33" s="4" t="str">
-        <x:v>禾迈股份</x:v>
+        <x:v>卡尔动力</x:v>
       </x:c>
       <x:c r="C33" s="4" t="str">
-        <x:v>光伏/电力电子</x:v>
+        <x:v>自动驾驶/智能汽车</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
-        <x:v>杭州等，以岗位页为准</x:v>
+        <x:v>北京、上海、天津等</x:v>
       </x:c>
       <x:c r="F33" s="4" t="str">
-        <x:v>研发类提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
-        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H33" s="4" t="str">
-        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
+        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
       </x:c>
       <x:c r="I33" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
+        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
       </x:c>
       <x:c r="J33" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2233,19 +2236,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L33" s="4" t="str">
-        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
       </x:c>
       <x:c r="M33" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N33" s="4" t="str">
-        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
+        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
       </x:c>
       <x:c r="O33" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
+        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
       </x:c>
       <x:c r="P33" s="16" t="str">
-        <x:v>B-高校就业网转载企业公告</x:v>
+        <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
       <x:c r="Q33" s="4" t="str">
         <x:v>2026-07-27</x:v>
@@ -2253,158 +2256,158 @@
     </x:row>
     <x:row r="34" ht="54" customHeight="1">
       <x:c r="A34" s="4" t="str">
-        <x:v>2026-07-23</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B34" s="4" t="str">
-        <x:v>极客未来</x:v>
+        <x:v>深信服-X-STAR顶尖人才计划</x:v>
       </x:c>
       <x:c r="C34" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>网络安全/云计算/软件</x:v>
       </x:c>
       <x:c r="D34" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
-        <x:v>四川、重庆、广东</x:v>
+        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F34" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G34" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>顶尖人才，本硕博按岗位要求</x:v>
       </x:c>
       <x:c r="H34" s="4" t="str">
-        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
       </x:c>
       <x:c r="I34" s="15" t="str">
-        <x:v>https://geek3.zhiye.com/campus/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
       </x:c>
       <x:c r="J34" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-09-25</x:v>
       </x:c>
       <x:c r="K34" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L34" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M34" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N34" s="4" t="str">
-        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
+        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
       </x:c>
       <x:c r="O34" s="15" t="str">
-        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
-      </x:c>
-      <x:c r="P34" s="16" t="str">
-        <x:v>B-高校就业网公告+公开招聘页面</x:v>
+        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
+      </x:c>
+      <x:c r="P34" s="14" t="str">
+        <x:v>A-高校就业网含官方投递链接</x:v>
       </x:c>
       <x:c r="Q34" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="54" customHeight="1">
       <x:c r="A35" s="4" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B35" s="4" t="str">
-        <x:v>安永EY</x:v>
+        <x:v>希夕智能</x:v>
       </x:c>
       <x:c r="C35" s="4" t="str">
-        <x:v>会计审计/咨询/专业服务</x:v>
+        <x:v>机器人/智能制造</x:v>
       </x:c>
       <x:c r="D35" s="4" t="str">
-        <x:v>外资/专业服务机构</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E35" s="4" t="str">
-        <x:v>中国内地多地，以职位页为准</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F35" s="4" t="str">
-        <x:v>正式批/秋季校园招聘</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
-        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
+        <x:v>2027届本科及以上</x:v>
       </x:c>
       <x:c r="H35" s="4" t="str">
-        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
+        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
       </x:c>
       <x:c r="I35" s="15" t="str">
-        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
+        <x:v>https://sunseed.zhiye.com/jobs</x:v>
       </x:c>
       <x:c r="J35" s="4" t="str">
-        <x:v>2026年10月（具体日期未公布）</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K35" s="4" t="str">
-        <x:v>否；官方流程包含在线测评</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L35" s="4" t="str">
-        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
+        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
       </x:c>
       <x:c r="M35" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N35" s="4" t="str">
-        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
+        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
       </x:c>
       <x:c r="O35" s="15" t="str">
-        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
-      </x:c>
-      <x:c r="P35" s="14" t="str">
-        <x:v>A-企业官方校招网站与职位页已核验</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
+      </x:c>
+      <x:c r="P35" s="16" t="str">
+        <x:v>B-高校就业平台转载企业来源</x:v>
       </x:c>
       <x:c r="Q35" s="4" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="54" customHeight="1">
       <x:c r="A36" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>不晚于2026-07-24</x:v>
       </x:c>
       <x:c r="B36" s="4" t="str">
-        <x:v>阿里巴巴-阿里星计划</x:v>
+        <x:v>中国兵器工业集团</x:v>
       </x:c>
       <x:c r="C36" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>军工/高端装备</x:v>
       </x:c>
       <x:c r="D36" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
-        <x:v>杭州、北京、上海、深圳等</x:v>
+        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
       </x:c>
       <x:c r="F36" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G36" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H36" s="4" t="str">
-        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
+        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
       </x:c>
       <x:c r="I36" s="15" t="str">
-        <x:v>https://talent.alibaba.com/campus/</x:v>
+        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
       </x:c>
       <x:c r="J36" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K36" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L36" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M36" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N36" s="4" t="str">
-        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
+        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
       </x:c>
       <x:c r="O36" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P36" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
+      </x:c>
+      <x:c r="P36" s="16" t="str">
+        <x:v>B-公开招聘公告/集团入口</x:v>
       </x:c>
       <x:c r="Q36" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -2412,82 +2415,84 @@
     </x:row>
     <x:row r="37" ht="54" customHeight="1">
       <x:c r="A37" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B37" s="4" t="str">
-        <x:v>贝恩公司</x:v>
+        <x:v>禾迈股份</x:v>
       </x:c>
       <x:c r="C37" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>光伏/电力电子</x:v>
       </x:c>
       <x:c r="D37" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E37" s="4" t="str">
-        <x:v>北京、上海、香港等</x:v>
+        <x:v>杭州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F37" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>研发类提前批</x:v>
       </x:c>
       <x:c r="G37" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
-        <x:v>助理咨询顾问等</x:v>
+        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
       </x:c>
       <x:c r="I37" s="15" t="str">
-        <x:v>https://www.bain.com/careers/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
       </x:c>
       <x:c r="J37" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K37" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L37" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
       </x:c>
       <x:c r="M37" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N37" s="4" t="str"/>
+      <x:c r="N37" s="4" t="str">
+        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
+      </x:c>
       <x:c r="O37" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P37" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
+      </x:c>
+      <x:c r="P37" s="16" t="str">
+        <x:v>B-高校就业网转载企业公告</x:v>
       </x:c>
       <x:c r="Q37" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="54" customHeight="1">
       <x:c r="A38" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B38" s="4" t="str">
-        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
+        <x:v>极客未来</x:v>
       </x:c>
       <x:c r="C38" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D38" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E38" s="4" t="str">
-        <x:v>上海、北京等</x:v>
+        <x:v>四川、重庆、广东</x:v>
       </x:c>
       <x:c r="F38" s="4" t="str">
-        <x:v>顶尖技术专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H38" s="4" t="str">
-        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
+        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
       <x:c r="I38" s="15" t="str">
-        <x:v>https://jobs.bilibili.com/</x:v>
+        <x:v>https://geek3.zhiye.com/campus/</x:v>
       </x:c>
       <x:c r="J38" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2496,75 +2501,75 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L38" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
       </x:c>
       <x:c r="M38" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N38" s="4" t="str">
-        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
+        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
       </x:c>
       <x:c r="O38" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P38" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
+      </x:c>
+      <x:c r="P38" s="16" t="str">
+        <x:v>B-高校就业网公告+公开招聘页面</x:v>
       </x:c>
       <x:c r="Q38" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="54" customHeight="1">
       <x:c r="A39" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="B39" s="4" t="str">
-        <x:v>东风汽车-全球博士人才</x:v>
+        <x:v>安永EY</x:v>
       </x:c>
       <x:c r="C39" s="4" t="str">
-        <x:v>汽车/央企</x:v>
+        <x:v>会计审计/咨询/专业服务</x:v>
       </x:c>
       <x:c r="D39" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>外资/专业服务机构</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
-        <x:v>武汉、广州、十堰及全国研发基地</x:v>
+        <x:v>中国内地多地，以职位页为准</x:v>
       </x:c>
       <x:c r="F39" s="4" t="str">
-        <x:v>博士专项</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G39" s="4" t="str">
-        <x:v>2026届及以后博士</x:v>
+        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
       </x:c>
       <x:c r="H39" s="4" t="str">
-        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
+        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
       </x:c>
       <x:c r="I39" s="15" t="str">
-        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
       </x:c>
       <x:c r="J39" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026年10月（具体日期未公布）</x:v>
       </x:c>
       <x:c r="K39" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；官方流程包含在线测评</x:v>
       </x:c>
       <x:c r="L39" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
       </x:c>
       <x:c r="M39" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N39" s="4" t="str">
-        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
+        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
       </x:c>
       <x:c r="O39" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P39" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
+      </x:c>
+      <x:c r="P39" s="14" t="str">
+        <x:v>A-企业官方校招网站与职位页已核验</x:v>
       </x:c>
       <x:c r="Q39" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="54" customHeight="1">
@@ -2572,28 +2577,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B40" s="4" t="str">
-        <x:v>度小满-博士后人才招聘</x:v>
+        <x:v>阿里巴巴-阿里星计划</x:v>
       </x:c>
       <x:c r="C40" s="4" t="str">
-        <x:v>金融科技</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D40" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E40" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>杭州、北京、上海、深圳等</x:v>
       </x:c>
       <x:c r="F40" s="4" t="str">
-        <x:v>博士后专项</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G40" s="4" t="str">
-        <x:v>2025/2026/2027届博士</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H40" s="4" t="str">
-        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
+        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
       </x:c>
       <x:c r="I40" s="15" t="str">
-        <x:v>https://campus.duxiaoman.com/</x:v>
+        <x:v>https://talent.alibaba.com/campus/</x:v>
       </x:c>
       <x:c r="J40" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2608,12 +2613,12 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N40" s="4" t="str">
-        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
+        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
       </x:c>
       <x:c r="O40" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P40" s="19" t="str">
+      <x:c r="P40" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q40" s="4" t="str">
@@ -2625,34 +2630,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B41" s="4" t="str">
-        <x:v>多益网络</x:v>
+        <x:v>贝恩公司</x:v>
       </x:c>
       <x:c r="C41" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D41" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E41" s="4" t="str">
-        <x:v>广州、武汉、成都等</x:v>
+        <x:v>北京、上海、香港等</x:v>
       </x:c>
       <x:c r="F41" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G41" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H41" s="4" t="str">
-        <x:v>程序、策划、美术、运营、市场及职能</x:v>
+        <x:v>助理咨询顾问等</x:v>
       </x:c>
       <x:c r="I41" s="15" t="str">
-        <x:v>https://www.duoyi.com/job/</x:v>
+        <x:v>https://www.bain.com/careers/</x:v>
       </x:c>
       <x:c r="J41" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K41" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L41" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2660,13 +2665,11 @@
       <x:c r="M41" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N41" s="4" t="str">
-        <x:v>岗位可能按城市提前关闭。</x:v>
-      </x:c>
+      <x:c r="N41" s="4" t="str"/>
       <x:c r="O41" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P41" s="19" t="str">
+      <x:c r="P41" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q41" s="4" t="str">
@@ -2678,28 +2681,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B42" s="4" t="str">
-        <x:v>海天集团-高潜专项</x:v>
+        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
       </x:c>
       <x:c r="C42" s="4" t="str">
-        <x:v>工业制造</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="D42" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E42" s="4" t="str">
-        <x:v>宁波及全国基地</x:v>
+        <x:v>上海、北京等</x:v>
       </x:c>
       <x:c r="F42" s="4" t="str">
-        <x:v>高潜人才专项/提前批</x:v>
+        <x:v>顶尖技术专项/提前批</x:v>
       </x:c>
       <x:c r="G42" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H42" s="4" t="str">
-        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
+        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
       </x:c>
       <x:c r="I42" s="15" t="str">
-        <x:v>https://www.haitian.com/careers/</x:v>
+        <x:v>https://jobs.bilibili.com/</x:v>
       </x:c>
       <x:c r="J42" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2714,12 +2717,12 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N42" s="4" t="str">
-        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
+        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
       </x:c>
       <x:c r="O42" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P42" s="19" t="str">
+      <x:c r="P42" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q42" s="4" t="str">
@@ -2731,28 +2734,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B43" s="4" t="str">
-        <x:v>赫力昂-销售先锋计划</x:v>
+        <x:v>东风汽车-全球博士人才</x:v>
       </x:c>
       <x:c r="C43" s="4" t="str">
-        <x:v>消费健康/医药</x:v>
+        <x:v>汽车/央企</x:v>
       </x:c>
       <x:c r="D43" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E43" s="4" t="str">
-        <x:v>全国重点城市</x:v>
+        <x:v>武汉、广州、十堰及全国研发基地</x:v>
       </x:c>
       <x:c r="F43" s="4" t="str">
-        <x:v>管培/销售专项</x:v>
+        <x:v>博士专项</x:v>
       </x:c>
       <x:c r="G43" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026届及以后博士</x:v>
       </x:c>
       <x:c r="H43" s="4" t="str">
-        <x:v>医药及消费健康销售、商业运营方向</x:v>
+        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
       </x:c>
       <x:c r="I43" s="15" t="str">
-        <x:v>https://careers.haleon.com/</x:v>
+        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
       </x:c>
       <x:c r="J43" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2766,11 +2769,13 @@
       <x:c r="M43" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N43" s="4" t="str"/>
+      <x:c r="N43" s="4" t="str">
+        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
+      </x:c>
       <x:c r="O43" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P43" s="19" t="str">
+      <x:c r="P43" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q43" s="4" t="str">
@@ -2782,46 +2787,48 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B44" s="4" t="str">
-        <x:v>虹软科技</x:v>
+        <x:v>度小满-博士后人才招聘</x:v>
       </x:c>
       <x:c r="C44" s="4" t="str">
-        <x:v>计算机视觉/软件</x:v>
+        <x:v>金融科技</x:v>
       </x:c>
       <x:c r="D44" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E44" s="4" t="str">
-        <x:v>杭州、上海、南京等</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F44" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>博士后专项</x:v>
       </x:c>
       <x:c r="G44" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2025/2026/2027届博士</x:v>
       </x:c>
       <x:c r="H44" s="4" t="str">
-        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
+        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
       </x:c>
       <x:c r="I44" s="15" t="str">
-        <x:v>https://hr.arcsoft.com.cn/</x:v>
+        <x:v>https://campus.duxiaoman.com/</x:v>
       </x:c>
       <x:c r="J44" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K44" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L44" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M44" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N44" s="4" t="str"/>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N44" s="4" t="str">
+        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
+      </x:c>
       <x:c r="O44" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P44" s="19" t="str">
+      <x:c r="P44" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q44" s="4" t="str">
@@ -2833,34 +2840,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B45" s="4" t="str">
-        <x:v>汇川技术</x:v>
+        <x:v>多益网络</x:v>
       </x:c>
       <x:c r="C45" s="4" t="str">
-        <x:v>工业自动化/新能源</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D45" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E45" s="4" t="str">
-        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
+        <x:v>广州、武汉、成都等</x:v>
       </x:c>
       <x:c r="F45" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G45" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H45" s="4" t="str">
-        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
+        <x:v>程序、策划、美术、运营、市场及职能</x:v>
       </x:c>
       <x:c r="I45" s="15" t="str">
-        <x:v>https://career.inovance.com/</x:v>
+        <x:v>https://www.duoyi.com/job/</x:v>
       </x:c>
       <x:c r="J45" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K45" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L45" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -2868,11 +2875,13 @@
       <x:c r="M45" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N45" s="4" t="str"/>
+      <x:c r="N45" s="4" t="str">
+        <x:v>岗位可能按城市提前关闭。</x:v>
+      </x:c>
       <x:c r="O45" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P45" s="19" t="str">
+      <x:c r="P45" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q45" s="4" t="str">
@@ -2884,28 +2893,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B46" s="4" t="str">
-        <x:v>伽利略-星途星锐计划</x:v>
+        <x:v>海天集团-高潜专项</x:v>
       </x:c>
       <x:c r="C46" s="4" t="str">
-        <x:v>科技/综合</x:v>
+        <x:v>工业制造</x:v>
       </x:c>
       <x:c r="D46" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E46" s="4" t="str">
-        <x:v>以项目职位页为准</x:v>
+        <x:v>宁波及全国基地</x:v>
       </x:c>
       <x:c r="F46" s="4" t="str">
-        <x:v>人才专项</x:v>
+        <x:v>高潜人才专项/提前批</x:v>
       </x:c>
       <x:c r="G46" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H46" s="4" t="str">
-        <x:v>以官方项目页为准</x:v>
-      </x:c>
-      <x:c r="I46" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
+      </x:c>
+      <x:c r="I46" s="15" t="str">
+        <x:v>https://www.haitian.com/careers/</x:v>
       </x:c>
       <x:c r="J46" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2920,13 +2929,13 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N46" s="4" t="str">
-        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
+        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
       </x:c>
       <x:c r="O46" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P46" s="19" t="str">
-        <x:v>C-主体与入口需二次确认</x:v>
+      <x:c r="P46" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q46" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -2937,52 +2946,50 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B47" s="4" t="str">
-        <x:v>京东-TET管理培训生</x:v>
+        <x:v>赫力昂-销售先锋计划</x:v>
       </x:c>
       <x:c r="C47" s="4" t="str">
-        <x:v>互联网/零售</x:v>
+        <x:v>消费健康/医药</x:v>
       </x:c>
       <x:c r="D47" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E47" s="4" t="str">
-        <x:v>北京及业务所在城市</x:v>
+        <x:v>全国重点城市</x:v>
       </x:c>
       <x:c r="F47" s="4" t="str">
-        <x:v>管培生专项/提前批</x:v>
+        <x:v>管培/销售专项</x:v>
       </x:c>
       <x:c r="G47" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H47" s="4" t="str">
-        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
+        <x:v>医药及消费健康销售、商业运营方向</x:v>
       </x:c>
       <x:c r="I47" s="15" t="str">
-        <x:v>https://campus.jd.com/</x:v>
+        <x:v>https://careers.haleon.com/</x:v>
       </x:c>
       <x:c r="J47" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K47" s="4" t="str">
-        <x:v>含测评，笔试以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L47" s="4" t="str">
-        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M47" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
-      </x:c>
-      <x:c r="N47" s="4" t="str">
-        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
-      </x:c>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N47" s="4" t="str"/>
       <x:c r="O47" s="15" t="str">
-        <x:v>https://campus.jd.com/#/</x:v>
-      </x:c>
-      <x:c r="P47" s="14" t="str">
-        <x:v>A-企业官网校招页面已核验</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P47" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q47" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="54" customHeight="1">
@@ -2990,48 +2997,46 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B48" s="4" t="str">
-        <x:v>科大讯飞-飞凡计划</x:v>
+        <x:v>虹软科技</x:v>
       </x:c>
       <x:c r="C48" s="4" t="str">
-        <x:v>AI/软件</x:v>
+        <x:v>计算机视觉/软件</x:v>
       </x:c>
       <x:c r="D48" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E48" s="4" t="str">
-        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
+        <x:v>杭州、上海、南京等</x:v>
       </x:c>
       <x:c r="F48" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G48" s="4" t="str">
-        <x:v>2026/2027届</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H48" s="4" t="str">
-        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
+        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
       </x:c>
       <x:c r="I48" s="15" t="str">
-        <x:v>https://campus.iflytek.com/</x:v>
+        <x:v>https://hr.arcsoft.com.cn/</x:v>
       </x:c>
       <x:c r="J48" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K48" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L48" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M48" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N48" s="4" t="str">
-        <x:v>专项岗位与常规校招可能并行。</x:v>
-      </x:c>
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N48" s="4" t="str"/>
       <x:c r="O48" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P48" s="19" t="str">
+      <x:c r="P48" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q48" s="4" t="str">
@@ -3043,34 +3048,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B49" s="4" t="str">
-        <x:v>理想汽车</x:v>
+        <x:v>汇川技术</x:v>
       </x:c>
       <x:c r="C49" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>工业自动化/新能源</x:v>
       </x:c>
       <x:c r="D49" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E49" s="4" t="str">
-        <x:v>北京、上海、常州等</x:v>
+        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
       </x:c>
       <x:c r="F49" s="4" t="str">
-        <x:v>暑期实习转正通道</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G49" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H49" s="4" t="str">
-        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
+        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
       </x:c>
       <x:c r="I49" s="15" t="str">
-        <x:v>https://career.lixiang.com/campus</x:v>
+        <x:v>https://career.inovance.com/</x:v>
       </x:c>
       <x:c r="J49" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K49" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L49" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3078,13 +3083,11 @@
       <x:c r="M49" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N49" s="4" t="str">
-        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
-      </x:c>
+      <x:c r="N49" s="4" t="str"/>
       <x:c r="O49" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P49" s="19" t="str">
+      <x:c r="P49" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q49" s="4" t="str">
@@ -3096,47 +3099,49 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B50" s="4" t="str">
-        <x:v>莉莉丝游戏</x:v>
+        <x:v>伽利略-星途星锐计划</x:v>
       </x:c>
       <x:c r="C50" s="4" t="str">
-        <x:v>游戏</x:v>
+        <x:v>科技/综合</x:v>
       </x:c>
       <x:c r="D50" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E50" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>以项目职位页为准</x:v>
       </x:c>
       <x:c r="F50" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>人才专项</x:v>
       </x:c>
       <x:c r="G50" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H50" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
-      </x:c>
-      <x:c r="I50" s="15" t="str">
-        <x:v>https://campus.lilith.com/</x:v>
+        <x:v>以官方项目页为准</x:v>
+      </x:c>
+      <x:c r="I50" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J50" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K50" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L50" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M50" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N50" s="4" t="str"/>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N50" s="4" t="str">
+        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
+      </x:c>
       <x:c r="O50" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P50" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P50" s="20" t="str">
+        <x:v>C-主体与入口需二次确认</x:v>
       </x:c>
       <x:c r="Q50" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3147,50 +3152,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B51" s="4" t="str">
-        <x:v>麦肯锡</x:v>
+        <x:v>京东-TET管理培训生</x:v>
       </x:c>
       <x:c r="C51" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>互联网/零售</x:v>
       </x:c>
       <x:c r="D51" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E51" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>北京及业务所在城市</x:v>
       </x:c>
       <x:c r="F51" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>管培生专项/提前批</x:v>
       </x:c>
       <x:c r="G51" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H51" s="4" t="str">
-        <x:v>商业分析师、咨询及专业岗位</x:v>
+        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
       </x:c>
       <x:c r="I51" s="15" t="str">
-        <x:v>https://www.mckinsey.com/careers</x:v>
+        <x:v>https://campus.jd.com/</x:v>
       </x:c>
       <x:c r="J51" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K51" s="4" t="str">
-        <x:v>通常含测评/案例面试；以通知为准</x:v>
+        <x:v>含测评，笔试以通知为准</x:v>
       </x:c>
       <x:c r="L51" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
       </x:c>
       <x:c r="M51" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N51" s="4" t="str"/>
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N51" s="4" t="str">
+        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
+      </x:c>
       <x:c r="O51" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P51" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://campus.jd.com/#/</x:v>
+      </x:c>
+      <x:c r="P51" s="14" t="str">
+        <x:v>A-企业官网校招页面已核验</x:v>
       </x:c>
       <x:c r="Q51" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="54" customHeight="1">
@@ -3198,34 +3205,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B52" s="4" t="str">
-        <x:v>拼多多</x:v>
+        <x:v>科大讯飞-飞凡计划</x:v>
       </x:c>
       <x:c r="C52" s="4" t="str">
-        <x:v>互联网/电商</x:v>
+        <x:v>AI/软件</x:v>
       </x:c>
       <x:c r="D52" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E52" s="4" t="str">
-        <x:v>上海、广州等，以岗位页为准</x:v>
+        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
       </x:c>
       <x:c r="F52" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G52" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026/2027届</x:v>
       </x:c>
       <x:c r="H52" s="4" t="str">
-        <x:v>技术、算法、产品、运营、商业分析等</x:v>
+        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
       </x:c>
       <x:c r="I52" s="15" t="str">
-        <x:v>https://careers.pinduoduo.com/campus/</x:v>
+        <x:v>https://campus.iflytek.com/</x:v>
       </x:c>
       <x:c r="J52" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K52" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L52" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3234,12 +3241,12 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N52" s="4" t="str">
-        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
+        <x:v>专项岗位与常规校招可能并行。</x:v>
       </x:c>
       <x:c r="O52" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P52" s="19" t="str">
+      <x:c r="P52" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q52" s="4" t="str">
@@ -3251,34 +3258,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B53" s="4" t="str">
-        <x:v>启林投资</x:v>
+        <x:v>理想汽车</x:v>
       </x:c>
       <x:c r="C53" s="4" t="str">
-        <x:v>量化金融/资管</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D53" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E53" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>北京、上海、常州等</x:v>
       </x:c>
       <x:c r="F53" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>暑期实习转正通道</x:v>
       </x:c>
       <x:c r="G53" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H53" s="4" t="str">
-        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
+        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
       </x:c>
       <x:c r="I53" s="15" t="str">
-        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
+        <x:v>https://career.lixiang.com/campus</x:v>
       </x:c>
       <x:c r="J53" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K53" s="4" t="str">
-        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L53" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3287,12 +3294,12 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N53" s="4" t="str">
-        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
+        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
       </x:c>
       <x:c r="O53" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P53" s="19" t="str">
+      <x:c r="P53" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q53" s="4" t="str">
@@ -3300,56 +3307,56 @@
       </x:c>
     </x:row>
     <x:row r="54" ht="54" customHeight="1">
-      <x:c r="A54" s="4" t="str">
+      <x:c r="A54" s="16" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B54" s="4" t="str">
-        <x:v>商汤科技-无限原力计划</x:v>
-      </x:c>
-      <x:c r="C54" s="4" t="str">
-        <x:v>AI/计算机视觉</x:v>
-      </x:c>
-      <x:c r="D54" s="4" t="str">
+      <x:c r="B54" s="16" t="str">
+        <x:v>莉莉丝游戏</x:v>
+      </x:c>
+      <x:c r="C54" s="16" t="str">
+        <x:v>游戏</x:v>
+      </x:c>
+      <x:c r="D54" s="16" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E54" s="4" t="str">
-        <x:v>上海、北京、深圳、杭州等</x:v>
-      </x:c>
-      <x:c r="F54" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
-      </x:c>
-      <x:c r="G54" s="4" t="str">
-        <x:v>2027/2028届</x:v>
-      </x:c>
-      <x:c r="H54" s="4" t="str">
-        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
-      </x:c>
-      <x:c r="I54" s="15" t="str">
-        <x:v>https://joinus.sensetime.com/</x:v>
-      </x:c>
-      <x:c r="J54" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K54" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L54" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
-      </x:c>
-      <x:c r="M54" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N54" s="4" t="str">
-        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
-      </x:c>
-      <x:c r="O54" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P54" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q54" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+      <x:c r="E54" s="16" t="str">
+        <x:v>上海等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F54" s="16" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G54" s="16" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H54" s="16" t="str">
+        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
+      </x:c>
+      <x:c r="I54" s="17" t="str">
+        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
+      </x:c>
+      <x:c r="J54" s="16" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+      <x:c r="K54" s="16" t="str">
+        <x:v>按岗位，官方未统一说明</x:v>
+      </x:c>
+      <x:c r="L54" s="16" t="str">
+        <x:v>今日截止；莉莉丝官方校园招聘页当前仍显示27届校招提前批14个职位</x:v>
+      </x:c>
+      <x:c r="M54" s="16" t="str">
+        <x:v>P0-今日截止</x:v>
+      </x:c>
+      <x:c r="N54" s="16" t="str">
+        <x:v>官网当前显示服务器开发、数据分析、战略研究、算法、关卡策划、客户端等27届提前批职位；截止日为2026-08-07，页面仍可投递但可能随时关闭，建议立即完成网申。</x:v>
+      </x:c>
+      <x:c r="O54" s="17" t="str">
+        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
+      </x:c>
+      <x:c r="P54" s="14" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q54" s="16" t="str">
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="54" customHeight="1">
@@ -3357,34 +3364,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B55" s="4" t="str">
-        <x:v>腾讯-青云计划</x:v>
+        <x:v>麦肯锡</x:v>
       </x:c>
       <x:c r="C55" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D55" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E55" s="4" t="str">
-        <x:v>深圳、北京、上海等</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F55" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G55" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H55" s="4" t="str">
-        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
+        <x:v>商业分析师、咨询及专业岗位</x:v>
       </x:c>
       <x:c r="I55" s="15" t="str">
-        <x:v>https://join.qq.com/</x:v>
+        <x:v>https://www.mckinsey.com/careers</x:v>
       </x:c>
       <x:c r="J55" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K55" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常含测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L55" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3392,13 +3399,11 @@
       <x:c r="M55" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N55" s="4" t="str">
-        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
-      </x:c>
+      <x:c r="N55" s="4" t="str"/>
       <x:c r="O55" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P55" s="19" t="str">
+      <x:c r="P55" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q55" s="4" t="str">
@@ -3410,16 +3415,16 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B56" s="4" t="str">
-        <x:v>天锐星通</x:v>
+        <x:v>拼多多</x:v>
       </x:c>
       <x:c r="C56" s="4" t="str">
-        <x:v>卫星通信/相控阵</x:v>
+        <x:v>互联网/电商</x:v>
       </x:c>
       <x:c r="D56" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E56" s="4" t="str">
-        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
+        <x:v>上海、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F56" s="4" t="str">
         <x:v>提前批</x:v>
@@ -3428,16 +3433,16 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H56" s="4" t="str">
-        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
+        <x:v>技术、算法、产品、运营、商业分析等</x:v>
       </x:c>
       <x:c r="I56" s="15" t="str">
-        <x:v>https://www.tianruixing.com/</x:v>
+        <x:v>https://careers.pinduoduo.com/campus/</x:v>
       </x:c>
       <x:c r="J56" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K56" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L56" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3446,12 +3451,12 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N56" s="4" t="str">
-        <x:v>官网入口与具体岗位需投前复核。</x:v>
+        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
       </x:c>
       <x:c r="O56" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P56" s="19" t="str">
+      <x:c r="P56" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q56" s="4" t="str">
@@ -3460,52 +3465,52 @@
     </x:row>
     <x:row r="57" ht="54" customHeight="1">
       <x:c r="A57" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B57" s="4" t="str">
-        <x:v>网易游戏雷火</x:v>
+        <x:v>启林投资</x:v>
       </x:c>
       <x:c r="C57" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>量化金融/资管</x:v>
       </x:c>
       <x:c r="D57" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E57" s="4" t="str">
-        <x:v>杭州、上海等，以岗位页为准</x:v>
+        <x:v>上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F57" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G57" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H57" s="4" t="str">
-        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
+        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
       </x:c>
       <x:c r="I57" s="15" t="str">
-        <x:v>https://leihuo.163.com/campus/#/full</x:v>
+        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
       </x:c>
       <x:c r="J57" s="4" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K57" s="4" t="str">
-        <x:v>部分岗位免笔试；部分可直通面试</x:v>
+        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
       </x:c>
       <x:c r="L57" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M57" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N57" s="4" t="str">
-        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
+        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
       </x:c>
       <x:c r="O57" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P57" s="14" t="str">
-        <x:v>A-官方招聘官网已核验</x:v>
+      <x:c r="P57" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q57" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3516,28 +3521,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B58" s="4" t="str">
-        <x:v>小鹏集团</x:v>
+        <x:v>商汤科技-无限原力计划</x:v>
       </x:c>
       <x:c r="C58" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>AI/计算机视觉</x:v>
       </x:c>
       <x:c r="D58" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E58" s="4" t="str">
-        <x:v>广州、北京、上海、深圳、武汉等</x:v>
+        <x:v>上海、北京、深圳、杭州等</x:v>
       </x:c>
       <x:c r="F58" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G58" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027/2028届</x:v>
       </x:c>
       <x:c r="H58" s="4" t="str">
-        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
+        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
       </x:c>
       <x:c r="I58" s="15" t="str">
-        <x:v>https://join.xiaopeng.com/campus</x:v>
+        <x:v>https://joinus.sensetime.com/</x:v>
       </x:c>
       <x:c r="J58" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3552,12 +3557,12 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N58" s="4" t="str">
-        <x:v>营销服与技术岗位可能分项目发布。</x:v>
+        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
       </x:c>
       <x:c r="O58" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P58" s="19" t="str">
+      <x:c r="P58" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q58" s="4" t="str">
@@ -3569,34 +3574,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B59" s="4" t="str">
-        <x:v>芯动科技</x:v>
+        <x:v>腾讯-青云计划</x:v>
       </x:c>
       <x:c r="C59" s="4" t="str">
-        <x:v>半导体/IP设计</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D59" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E59" s="4" t="str">
-        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
+        <x:v>深圳、北京、上海等</x:v>
       </x:c>
       <x:c r="F59" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G59" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H59" s="4" t="str">
-        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
+        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
       </x:c>
       <x:c r="I59" s="15" t="str">
-        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
+        <x:v>https://join.qq.com/</x:v>
       </x:c>
       <x:c r="J59" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K59" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L59" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3604,11 +3609,13 @@
       <x:c r="M59" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N59" s="4" t="str"/>
+      <x:c r="N59" s="4" t="str">
+        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
+      </x:c>
       <x:c r="O59" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P59" s="19" t="str">
+      <x:c r="P59" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q59" s="4" t="str">
@@ -3617,52 +3624,52 @@
     </x:row>
     <x:row r="60" ht="54" customHeight="1">
       <x:c r="A60" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B60" s="4" t="str">
-        <x:v>芯迈半导体</x:v>
+        <x:v>天锐星通</x:v>
       </x:c>
       <x:c r="C60" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>卫星通信/相控阵</x:v>
       </x:c>
       <x:c r="D60" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E60" s="4" t="str">
-        <x:v>杭州、上海、深圳、成都</x:v>
+        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F60" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G60" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H60" s="4" t="str">
-        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
+        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
       </x:c>
       <x:c r="I60" s="15" t="str">
-        <x:v>https://www.silicon-magic.com/joinus</x:v>
+        <x:v>https://www.tianruixing.com/</x:v>
       </x:c>
       <x:c r="J60" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K60" s="4" t="str">
-        <x:v>官方未说明；公开流程未列笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L60" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M60" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N60" s="4" t="str">
-        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
+        <x:v>官网入口与具体岗位需投前复核。</x:v>
       </x:c>
       <x:c r="O60" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P60" s="14" t="str">
-        <x:v>A-企业官网与公开公告已核验</x:v>
+      <x:c r="P60" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q60" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3670,55 +3677,55 @@
     </x:row>
     <x:row r="61" ht="54" customHeight="1">
       <x:c r="A61" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B61" s="4" t="str">
-        <x:v>新易盛</x:v>
+        <x:v>网易游戏雷火</x:v>
       </x:c>
       <x:c r="C61" s="4" t="str">
-        <x:v>光通信/半导体</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D61" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E61" s="4" t="str">
-        <x:v>成都、苏州等，以岗位页为准</x:v>
+        <x:v>杭州、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F61" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G61" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H61" s="4" t="str">
-        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
+        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
       </x:c>
       <x:c r="I61" s="15" t="str">
-        <x:v>https://www.eoptolink.com/</x:v>
+        <x:v>https://leihuo.163.com/campus/#/full</x:v>
       </x:c>
       <x:c r="J61" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="K61" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>部分岗位免笔试；部分可直通面试</x:v>
       </x:c>
       <x:c r="L61" s="4" t="str">
-        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M61" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N61" s="4" t="str">
-        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
       </x:c>
       <x:c r="O61" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P61" s="16" t="str">
-        <x:v>B-高校/招聘平台转载，投前复核</x:v>
+      <x:c r="P61" s="14" t="str">
+        <x:v>A-官方招聘官网已核验</x:v>
       </x:c>
       <x:c r="Q61" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="54" customHeight="1">
@@ -3726,34 +3733,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B62" s="4" t="str">
-        <x:v>元戎启行</x:v>
+        <x:v>小鹏集团</x:v>
       </x:c>
       <x:c r="C62" s="4" t="str">
-        <x:v>自动驾驶</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D62" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E62" s="4" t="str">
-        <x:v>深圳、北京等</x:v>
+        <x:v>广州、北京、上海、深圳、武汉等</x:v>
       </x:c>
       <x:c r="F62" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G62" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H62" s="4" t="str">
-        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
+        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
       </x:c>
       <x:c r="I62" s="15" t="str">
-        <x:v>https://www.deeproute.ai/join-us</x:v>
+        <x:v>https://join.xiaopeng.com/campus</x:v>
       </x:c>
       <x:c r="J62" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K62" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L62" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3761,11 +3768,13 @@
       <x:c r="M62" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N62" s="4" t="str"/>
+      <x:c r="N62" s="4" t="str">
+        <x:v>营销服与技术岗位可能分项目发布。</x:v>
+      </x:c>
       <x:c r="O62" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P62" s="19" t="str">
+      <x:c r="P62" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q62" s="4" t="str">
@@ -3777,34 +3786,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B63" s="4" t="str">
-        <x:v>圆通速递</x:v>
+        <x:v>芯动科技</x:v>
       </x:c>
       <x:c r="C63" s="4" t="str">
-        <x:v>物流/供应链</x:v>
+        <x:v>半导体/IP设计</x:v>
       </x:c>
       <x:c r="D63" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E63" s="4" t="str">
-        <x:v>上海及全国网络</x:v>
+        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
       </x:c>
       <x:c r="F63" s="4" t="str">
-        <x:v>正式批/校招</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G63" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H63" s="4" t="str">
-        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
+        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
       </x:c>
       <x:c r="I63" s="15" t="str">
-        <x:v>https://hr.yto.net.cn/</x:v>
+        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
       </x:c>
       <x:c r="J63" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K63" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L63" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3816,7 +3825,7 @@
       <x:c r="O63" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P63" s="19" t="str">
+      <x:c r="P63" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q63" s="4" t="str">
@@ -3825,50 +3834,52 @@
     </x:row>
     <x:row r="64" ht="54" customHeight="1">
       <x:c r="A64" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B64" s="4" t="str">
-        <x:v>长亭科技</x:v>
+        <x:v>芯迈半导体</x:v>
       </x:c>
       <x:c r="C64" s="4" t="str">
-        <x:v>网络安全</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D64" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E64" s="4" t="str">
-        <x:v>北京、上海等，以岗位页为准</x:v>
+        <x:v>杭州、上海、深圳、成都</x:v>
       </x:c>
       <x:c r="F64" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G64" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H64" s="4" t="str">
-        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
+        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
       </x:c>
       <x:c r="I64" s="15" t="str">
-        <x:v>https://job.chaitin.cn/</x:v>
+        <x:v>https://www.silicon-magic.com/joinus</x:v>
       </x:c>
       <x:c r="J64" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K64" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明；公开流程未列笔试</x:v>
       </x:c>
       <x:c r="L64" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M64" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N64" s="4" t="str"/>
+      <x:c r="N64" s="4" t="str">
+        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
+      </x:c>
       <x:c r="O64" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P64" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P64" s="14" t="str">
+        <x:v>A-企业官网与公开公告已核验</x:v>
       </x:c>
       <x:c r="Q64" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3879,50 +3890,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B65" s="4" t="str">
-        <x:v>智元机器人-优才计划</x:v>
+        <x:v>新易盛</x:v>
       </x:c>
       <x:c r="C65" s="4" t="str">
-        <x:v>具身智能/机器人</x:v>
+        <x:v>光通信/半导体</x:v>
       </x:c>
       <x:c r="D65" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E65" s="4" t="str">
-        <x:v>上海、北京、深圳等</x:v>
+        <x:v>成都、苏州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F65" s="4" t="str">
-        <x:v>优才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G65" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H65" s="4" t="str">
-        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
+        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
       </x:c>
       <x:c r="I65" s="15" t="str">
-        <x:v>https://www.agibot.com/recruit</x:v>
+        <x:v>https://www.eoptolink.com/</x:v>
       </x:c>
       <x:c r="J65" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K65" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L65" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
       </x:c>
       <x:c r="M65" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N65" s="4" t="str"/>
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N65" s="4" t="str">
+        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+      </x:c>
       <x:c r="O65" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P65" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P65" s="16" t="str">
+        <x:v>B-高校/招聘平台转载，投前复核</x:v>
       </x:c>
       <x:c r="Q65" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="54" customHeight="1">
@@ -3930,34 +3943,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B66" s="4" t="str">
-        <x:v>中国电信天翼云-超级优才</x:v>
+        <x:v>元戎启行</x:v>
       </x:c>
       <x:c r="C66" s="4" t="str">
-        <x:v>云计算/央企</x:v>
+        <x:v>自动驾驶</x:v>
       </x:c>
       <x:c r="D66" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E66" s="4" t="str">
-        <x:v>北京、上海、广州、成都及全国机构</x:v>
+        <x:v>深圳、北京等</x:v>
       </x:c>
       <x:c r="F66" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G66" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H66" s="4" t="str">
-        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
+        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
       </x:c>
       <x:c r="I66" s="15" t="str">
-        <x:v>https://www.ctyun.cn/about/recruit</x:v>
+        <x:v>https://www.deeproute.ai/join-us</x:v>
       </x:c>
       <x:c r="J66" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K66" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L66" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3965,13 +3978,11 @@
       <x:c r="M66" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N66" s="4" t="str">
-        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
-      </x:c>
+      <x:c r="N66" s="4" t="str"/>
       <x:c r="O66" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P66" s="19" t="str">
+      <x:c r="P66" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q66" s="4" t="str">
@@ -3983,31 +3994,31 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B67" s="4" t="str">
-        <x:v>中科光电</x:v>
+        <x:v>圆通速递</x:v>
       </x:c>
       <x:c r="C67" s="4" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>物流/供应链</x:v>
       </x:c>
       <x:c r="D67" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E67" s="4" t="str">
-        <x:v>以职位公告为准</x:v>
+        <x:v>上海及全国网络</x:v>
       </x:c>
       <x:c r="F67" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校招</x:v>
       </x:c>
       <x:c r="G67" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H67" s="4" t="str">
-        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
+        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
       </x:c>
       <x:c r="I67" s="15" t="str">
-        <x:v>https://job.cn-amd.com/</x:v>
+        <x:v>https://hr.yto.net.cn/</x:v>
       </x:c>
       <x:c r="J67" s="4" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K67" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -4016,16 +4027,14 @@
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M67" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N67" s="4" t="str">
-        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
-      </x:c>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N67" s="4" t="str"/>
       <x:c r="O67" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P67" s="19" t="str">
-        <x:v>C-名称需二次确认</x:v>
+      <x:c r="P67" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q67" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4036,34 +4045,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B68" s="4" t="str">
-        <x:v>中兴微电子-未来领军计划</x:v>
+        <x:v>长亭科技</x:v>
       </x:c>
       <x:c r="C68" s="4" t="str">
-        <x:v>半导体/通信</x:v>
+        <x:v>网络安全</x:v>
       </x:c>
       <x:c r="D68" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E68" s="4" t="str">
-        <x:v>深圳、西安、南京、上海等</x:v>
+        <x:v>北京、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F68" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G68" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H68" s="4" t="str">
-        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
+        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
       </x:c>
       <x:c r="I68" s="15" t="str">
-        <x:v>https://job.zte.com.cn/</x:v>
+        <x:v>https://job.chaitin.cn/</x:v>
       </x:c>
       <x:c r="J68" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K68" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L68" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -4071,13 +4080,11 @@
       <x:c r="M68" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N68" s="4" t="str">
-        <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
-      </x:c>
+      <x:c r="N68" s="4" t="str"/>
       <x:c r="O68" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P68" s="19" t="str">
+      <x:c r="P68" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q68" s="4" t="str">
@@ -4085,56 +4092,54 @@
       </x:c>
     </x:row>
     <x:row r="69" ht="54" customHeight="1">
-      <x:c r="A69" s="17" t="str">
+      <x:c r="A69" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B69" s="17" t="str">
-        <x:v>字节跳动-AI产品经理早鸟通道</x:v>
-      </x:c>
-      <x:c r="C69" s="17" t="str">
-        <x:v>互联网/AI</x:v>
-      </x:c>
-      <x:c r="D69" s="17" t="str">
+      <x:c r="B69" s="4" t="str">
+        <x:v>智元机器人-优才计划</x:v>
+      </x:c>
+      <x:c r="C69" s="4" t="str">
+        <x:v>具身智能/机器人</x:v>
+      </x:c>
+      <x:c r="D69" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E69" s="17" t="str">
-        <x:v>北京、上海、深圳</x:v>
-      </x:c>
-      <x:c r="F69" s="17" t="str">
-        <x:v>早鸟专项/提前批</x:v>
-      </x:c>
-      <x:c r="G69" s="17" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H69" s="17" t="str">
-        <x:v>AI产品经理、智能体及大模型产品方向</x:v>
-      </x:c>
-      <x:c r="I69" s="18" t="str">
-        <x:v>https://jobs.bytedance.com/campus/</x:v>
-      </x:c>
-      <x:c r="J69" s="17" t="str">
-        <x:v>2026-08-02</x:v>
-      </x:c>
-      <x:c r="K69" s="17" t="str">
-        <x:v>按岗位，未统一公布</x:v>
-      </x:c>
-      <x:c r="L69" s="17" t="str">
-        <x:v>已截止（2026-08-02）；原公告与官方投递入口保留</x:v>
-      </x:c>
-      <x:c r="M69" s="17" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N69" s="17" t="str">
-        <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
-      </x:c>
-      <x:c r="O69" s="18" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P69" s="16" t="str">
-        <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q69" s="17" t="str">
-        <x:v>2026-08-03</x:v>
+      <x:c r="E69" s="4" t="str">
+        <x:v>上海、北京、深圳等</x:v>
+      </x:c>
+      <x:c r="F69" s="4" t="str">
+        <x:v>优才专项/提前批</x:v>
+      </x:c>
+      <x:c r="G69" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H69" s="4" t="str">
+        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
+      </x:c>
+      <x:c r="I69" s="15" t="str">
+        <x:v>https://www.agibot.com/recruit</x:v>
+      </x:c>
+      <x:c r="J69" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K69" s="4" t="str">
+        <x:v>按岗位，官方未统一说明</x:v>
+      </x:c>
+      <x:c r="L69" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M69" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N69" s="4" t="str"/>
+      <x:c r="O69" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P69" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q69" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="54" customHeight="1">
@@ -4142,46 +4147,48 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B70" s="4" t="str">
-        <x:v>BCG波士顿咨询</x:v>
+        <x:v>中国电信天翼云-超级优才</x:v>
       </x:c>
       <x:c r="C70" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>云计算/央企</x:v>
       </x:c>
       <x:c r="D70" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E70" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>北京、上海、广州、成都及全国机构</x:v>
       </x:c>
       <x:c r="F70" s="4" t="str">
-        <x:v>正式批/中国区校招</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G70" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H70" s="4" t="str">
-        <x:v>咨询顾问及相关专业岗位</x:v>
+        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
       </x:c>
       <x:c r="I70" s="15" t="str">
-        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
+        <x:v>https://www.ctyun.cn/about/recruit</x:v>
       </x:c>
       <x:c r="J70" s="4" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K70" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L70" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M70" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N70" s="4" t="str"/>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N70" s="4" t="str">
+        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
+      </x:c>
       <x:c r="O70" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P70" s="19" t="str">
+      <x:c r="P70" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q70" s="4" t="str">
@@ -4193,31 +4200,31 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B71" s="4" t="str">
-        <x:v>OPPO</x:v>
+        <x:v>中科光电</x:v>
       </x:c>
       <x:c r="C71" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D71" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E71" s="4" t="str">
-        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
+        <x:v>以职位公告为准</x:v>
       </x:c>
       <x:c r="F71" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G71" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H71" s="4" t="str">
-        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
+        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
       </x:c>
       <x:c r="I71" s="15" t="str">
-        <x:v>https://careers.oppo.com/campus</x:v>
+        <x:v>https://job.cn-amd.com/</x:v>
       </x:c>
       <x:c r="J71" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K71" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -4226,16 +4233,16 @@
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M71" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N71" s="4" t="str">
-        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
+        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
       </x:c>
       <x:c r="O71" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P71" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P71" s="20" t="str">
+        <x:v>C-名称需二次确认</x:v>
       </x:c>
       <x:c r="Q71" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4246,28 +4253,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B72" s="4" t="str">
-        <x:v>Tap4Fun</x:v>
+        <x:v>中兴微电子-未来领军计划</x:v>
       </x:c>
       <x:c r="C72" s="4" t="str">
-        <x:v>游戏</x:v>
+        <x:v>半导体/通信</x:v>
       </x:c>
       <x:c r="D72" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E72" s="4" t="str">
-        <x:v>成都等</x:v>
+        <x:v>深圳、西安、南京、上海等</x:v>
       </x:c>
       <x:c r="F72" s="4" t="str">
-        <x:v>实习转正通道</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G72" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H72" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
+        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
       </x:c>
       <x:c r="I72" s="15" t="str">
-        <x:v>https://www.tap4fun.com/careers</x:v>
+        <x:v>https://job.zte.com.cn/</x:v>
       </x:c>
       <x:c r="J72" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4282,12 +4289,12 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N72" s="4" t="str">
-        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
+        <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
       </x:c>
       <x:c r="O72" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P72" s="19" t="str">
+      <x:c r="P72" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q72" s="4" t="str">
@@ -4295,159 +4302,157 @@
       </x:c>
     </x:row>
     <x:row r="73" ht="54" customHeight="1">
-      <x:c r="A73" s="4" t="str">
-        <x:v>2026-07-20</x:v>
-      </x:c>
-      <x:c r="B73" s="4" t="str">
-        <x:v>航天科技集团五院502所</x:v>
-      </x:c>
-      <x:c r="C73" s="4" t="str">
-        <x:v>航天/自动控制</x:v>
-      </x:c>
-      <x:c r="D73" s="4" t="str">
-        <x:v>事业单位/央企院所</x:v>
-      </x:c>
-      <x:c r="E73" s="4" t="str">
-        <x:v>北京</x:v>
-      </x:c>
-      <x:c r="F73" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G73" s="4" t="str">
-        <x:v>硕士/博士为主，以岗位为准</x:v>
-      </x:c>
-      <x:c r="H73" s="4" t="str">
-        <x:v>导航制导与控制、自动化、电子、通信、计算机、软件、机械等</x:v>
-      </x:c>
-      <x:c r="I73" s="15" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
-      </x:c>
-      <x:c r="J73" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K73" s="4" t="str">
-        <x:v>未统一公布</x:v>
-      </x:c>
-      <x:c r="L73" s="4" t="str">
-        <x:v>公开公告显示开放；投前确认</x:v>
-      </x:c>
-      <x:c r="M73" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N73" s="4" t="str">
-        <x:v>研究所岗位通常有专业、学历、政审及保密要求。</x:v>
-      </x:c>
-      <x:c r="O73" s="15" t="str">
-        <x:v>https://www.baidu.com/s?wd=%E4%BA%94%E9%99%A2502%E6%89%802027%E5%B1%8A%E6%A0%A1%E6%8B%9B</x:v>
+      <x:c r="A73" s="18" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B73" s="18" t="str">
+        <x:v>字节跳动-AI产品经理早鸟通道</x:v>
+      </x:c>
+      <x:c r="C73" s="18" t="str">
+        <x:v>互联网/AI</x:v>
+      </x:c>
+      <x:c r="D73" s="18" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E73" s="18" t="str">
+        <x:v>北京、上海、深圳</x:v>
+      </x:c>
+      <x:c r="F73" s="18" t="str">
+        <x:v>早鸟专项/提前批</x:v>
+      </x:c>
+      <x:c r="G73" s="18" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H73" s="18" t="str">
+        <x:v>AI产品经理、智能体及大模型产品方向</x:v>
+      </x:c>
+      <x:c r="I73" s="19" t="str">
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
+      </x:c>
+      <x:c r="J73" s="18" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+      <x:c r="K73" s="18" t="str">
+        <x:v>按岗位，未统一公布</x:v>
+      </x:c>
+      <x:c r="L73" s="18" t="str">
+        <x:v>已截止（2026-08-02）；原公告与官方投递入口保留</x:v>
+      </x:c>
+      <x:c r="M73" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N73" s="18" t="str">
+        <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
+      </x:c>
+      <x:c r="O73" s="19" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
       </x:c>
       <x:c r="P73" s="16" t="str">
-        <x:v>B-高校就业网公开公告</x:v>
-      </x:c>
-      <x:c r="Q73" s="4" t="str">
+        <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q73" s="18" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="54" customHeight="1">
+      <x:c r="A74" s="4" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B74" s="4" t="str">
+        <x:v>BCG波士顿咨询</x:v>
+      </x:c>
+      <x:c r="C74" s="4" t="str">
+        <x:v>管理咨询</x:v>
+      </x:c>
+      <x:c r="D74" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E74" s="4" t="str">
+        <x:v>北京、上海、深圳、香港等</x:v>
+      </x:c>
+      <x:c r="F74" s="4" t="str">
+        <x:v>正式批/中国区校招</x:v>
+      </x:c>
+      <x:c r="G74" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H74" s="4" t="str">
+        <x:v>咨询顾问及相关专业岗位</x:v>
+      </x:c>
+      <x:c r="I74" s="15" t="str">
+        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
+      </x:c>
+      <x:c r="J74" s="4" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="K74" s="4" t="str">
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+      </x:c>
+      <x:c r="L74" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M74" s="4" t="str">
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N74" s="4" t="str"/>
+      <x:c r="O74" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P74" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q74" s="4" t="str">
         <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" ht="54" customHeight="1">
-      <x:c r="A74" s="17" t="str">
-        <x:v>2026-07-17</x:v>
-      </x:c>
-      <x:c r="B74" s="17" t="str">
-        <x:v>鹰角网络</x:v>
-      </x:c>
-      <x:c r="C74" s="17" t="str">
-        <x:v>游戏</x:v>
-      </x:c>
-      <x:c r="D74" s="17" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E74" s="17" t="str">
-        <x:v>上海</x:v>
-      </x:c>
-      <x:c r="F74" s="17" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G74" s="17" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H74" s="17" t="str">
-        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
-      </x:c>
-      <x:c r="I74" s="18" t="str">
-        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
-      </x:c>
-      <x:c r="J74" s="17" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K74" s="17" t="str">
-        <x:v>否；安排笔试/面试</x:v>
-      </x:c>
-      <x:c r="L74" s="17" t="str">
-        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M74" s="17" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N74" s="17" t="str">
-        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
-      </x:c>
-      <x:c r="O74" s="18" t="str">
-        <x:v>https://campus.hypergryph.com/</x:v>
-      </x:c>
-      <x:c r="P74" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q74" s="17" t="str">
-        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="54" customHeight="1">
       <x:c r="A75" s="4" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B75" s="4" t="str">
-        <x:v>联发科技</x:v>
+        <x:v>OPPO</x:v>
       </x:c>
       <x:c r="C75" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D75" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E75" s="4" t="str">
-        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
+        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
       </x:c>
       <x:c r="F75" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G75" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H75" s="4" t="str">
-        <x:v>软件类、通信类、IC类</x:v>
+        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
       </x:c>
       <x:c r="I75" s="15" t="str">
-        <x:v>https://mediatek.zhiye.com/</x:v>
+        <x:v>https://careers.oppo.com/campus</x:v>
       </x:c>
       <x:c r="J75" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K75" s="4" t="str">
-        <x:v>否；明确安排7-8月笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L75" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M75" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N75" s="4" t="str">
-        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
+        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
       </x:c>
       <x:c r="O75" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P75" s="14" t="str">
-        <x:v>A-官方招聘公告已核验</x:v>
+      <x:c r="P75" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q75" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4455,52 +4460,52 @@
     </x:row>
     <x:row r="76" ht="54" customHeight="1">
       <x:c r="A76" s="4" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B76" s="4" t="str">
-        <x:v>DJI大疆</x:v>
+        <x:v>Tap4Fun</x:v>
       </x:c>
       <x:c r="C76" s="4" t="str">
-        <x:v>无人机/智能硬件</x:v>
+        <x:v>游戏</x:v>
       </x:c>
       <x:c r="D76" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E76" s="4" t="str">
-        <x:v>深圳、东莞、上海、北京、西安等</x:v>
+        <x:v>成都等</x:v>
       </x:c>
       <x:c r="F76" s="4" t="str">
-        <x:v>正式批-拓疆者计划</x:v>
+        <x:v>实习转正通道</x:v>
       </x:c>
       <x:c r="G76" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H76" s="4" t="str">
-        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
+        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
       </x:c>
       <x:c r="I76" s="15" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
+        <x:v>https://www.tap4fun.com/careers</x:v>
       </x:c>
       <x:c r="J76" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K76" s="4" t="str">
-        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L76" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M76" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N76" s="4" t="str">
-        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
+        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
       </x:c>
       <x:c r="O76" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P76" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
+      <x:c r="P76" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q76" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4508,158 +4513,158 @@
     </x:row>
     <x:row r="77" ht="54" customHeight="1">
       <x:c r="A77" s="4" t="str">
-        <x:v>2026-07-15</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="B77" s="4" t="str">
-        <x:v>蔚来</x:v>
+        <x:v>航天科技集团五院502所</x:v>
       </x:c>
       <x:c r="C77" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>航天/自动控制</x:v>
       </x:c>
       <x:c r="D77" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>事业单位/央企院所</x:v>
       </x:c>
       <x:c r="E77" s="4" t="str">
-        <x:v>上海、合肥、北京、武汉、南京等</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F77" s="4" t="str">
-        <x:v>技术提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G77" s="4" t="str">
-        <x:v>2024年9月-2027年8月毕业</x:v>
+        <x:v>硕士/博士为主，以岗位为准</x:v>
       </x:c>
       <x:c r="H77" s="4" t="str">
-        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
+        <x:v>导航制导与控制、自动化、电子、通信、计算机、软件、机械等</x:v>
       </x:c>
       <x:c r="I77" s="15" t="str">
-        <x:v>https://campus.nio.com/</x:v>
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J77" s="4" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K77" s="4" t="str">
-        <x:v>否；有笔试/测评</x:v>
+        <x:v>未统一公布</x:v>
       </x:c>
       <x:c r="L77" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>公开公告显示开放；投前确认</x:v>
       </x:c>
       <x:c r="M77" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N77" s="4" t="str">
-        <x:v>最多同时申请3个岗位。</x:v>
+        <x:v>研究所岗位通常有专业、学历、政审及保密要求。</x:v>
       </x:c>
       <x:c r="O77" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P77" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
+        <x:v>https://www.baidu.com/s?wd=%E4%BA%94%E9%99%A2502%E6%89%802027%E5%B1%8A%E6%A0%A1%E6%8B%9B</x:v>
+      </x:c>
+      <x:c r="P77" s="16" t="str">
+        <x:v>B-高校就业网公开公告</x:v>
       </x:c>
       <x:c r="Q77" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="54" customHeight="1">
-      <x:c r="A78" s="4" t="str">
-        <x:v>2026-07-10</x:v>
-      </x:c>
-      <x:c r="B78" s="4" t="str">
-        <x:v>北方华创</x:v>
-      </x:c>
-      <x:c r="C78" s="4" t="str">
-        <x:v>半导体设备</x:v>
-      </x:c>
-      <x:c r="D78" s="4" t="str">
-        <x:v>国企/上市</x:v>
-      </x:c>
-      <x:c r="E78" s="4" t="str">
-        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F78" s="4" t="str">
+      <x:c r="A78" s="18" t="str">
+        <x:v>2026-07-17</x:v>
+      </x:c>
+      <x:c r="B78" s="18" t="str">
+        <x:v>鹰角网络</x:v>
+      </x:c>
+      <x:c r="C78" s="18" t="str">
+        <x:v>游戏</x:v>
+      </x:c>
+      <x:c r="D78" s="18" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E78" s="18" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F78" s="18" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G78" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H78" s="4" t="str">
-        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
-      </x:c>
-      <x:c r="I78" s="15" t="str">
-        <x:v>https://career.naura.com/campus</x:v>
-      </x:c>
-      <x:c r="J78" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K78" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L78" s="4" t="str">
-        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
-      </x:c>
-      <x:c r="M78" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N78" s="4" t="str">
-        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
-      </x:c>
-      <x:c r="O78" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
+      <x:c r="G78" s="18" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H78" s="18" t="str">
+        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
+      </x:c>
+      <x:c r="I78" s="19" t="str">
+        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
+      </x:c>
+      <x:c r="J78" s="18" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K78" s="18" t="str">
+        <x:v>否；安排笔试/面试</x:v>
+      </x:c>
+      <x:c r="L78" s="18" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M78" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N78" s="18" t="str">
+        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
+      </x:c>
+      <x:c r="O78" s="19" t="str">
+        <x:v>https://campus.hypergryph.com/</x:v>
       </x:c>
       <x:c r="P78" s="14" t="str">
-        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
-      </x:c>
-      <x:c r="Q78" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q78" s="18" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="54" customHeight="1">
       <x:c r="A79" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B79" s="4" t="str">
-        <x:v>百度</x:v>
+        <x:v>联发科技</x:v>
       </x:c>
       <x:c r="C79" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D79" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E79" s="4" t="str">
-        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
       </x:c>
       <x:c r="F79" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G79" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H79" s="4" t="str">
-        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+        <x:v>软件类、通信类、IC类</x:v>
       </x:c>
       <x:c r="I79" s="15" t="str">
-        <x:v>https://talent.baidu.com/jobs</x:v>
+        <x:v>https://mediatek.zhiye.com/</x:v>
       </x:c>
       <x:c r="J79" s="4" t="str">
-        <x:v>2027-06-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K79" s="4" t="str">
-        <x:v>部分免；并非所有候选人参加笔试</x:v>
+        <x:v>否；明确安排7-8月笔试</x:v>
       </x:c>
       <x:c r="L79" s="4" t="str">
         <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M79" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N79" s="4" t="str">
-        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
+        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
       </x:c>
       <x:c r="O79" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P79" s="14" t="str">
-        <x:v>A-官方招聘日历/官方来源已核验</x:v>
+        <x:v>A-官方招聘公告已核验</x:v>
       </x:c>
       <x:c r="Q79" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4667,137 +4672,137 @@
     </x:row>
     <x:row r="80" ht="54" customHeight="1">
       <x:c r="A80" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B80" s="4" t="str">
-        <x:v>中国航天科工集团第六研究院</x:v>
+        <x:v>DJI大疆</x:v>
       </x:c>
       <x:c r="C80" s="4" t="str">
-        <x:v>航天/军工/动力系统</x:v>
+        <x:v>无人机/智能硬件</x:v>
       </x:c>
       <x:c r="D80" s="4" t="str">
-        <x:v>央企院所</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E80" s="4" t="str">
-        <x:v>呼和浩特及所属单位</x:v>
+        <x:v>深圳、东莞、上海、北京、西安等</x:v>
       </x:c>
       <x:c r="F80" s="4" t="str">
-        <x:v>提前批+暑期开放日</x:v>
+        <x:v>正式批-拓疆者计划</x:v>
       </x:c>
       <x:c r="G80" s="4" t="str">
-        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H80" s="4" t="str">
-        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
+        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
       </x:c>
       <x:c r="I80" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
+        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
       </x:c>
       <x:c r="J80" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K80" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
       </x:c>
       <x:c r="L80" s="4" t="str">
-        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M80" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N80" s="4" t="str">
-        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
+        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
       </x:c>
       <x:c r="O80" s="15" t="str">
-        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
-      </x:c>
-      <x:c r="P80" s="16" t="str">
-        <x:v>B-高校就业网公开公告</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P80" s="14" t="str">
+        <x:v>A-官方来源公告已核验</x:v>
       </x:c>
       <x:c r="Q80" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="54" customHeight="1">
       <x:c r="A81" s="4" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="B81" s="4" t="str">
-        <x:v>思瑞浦</x:v>
+        <x:v>蔚来</x:v>
       </x:c>
       <x:c r="C81" s="4" t="str">
-        <x:v>半导体/模拟IC</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D81" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E81" s="4" t="str">
-        <x:v>上海、深圳等，以岗位页为准</x:v>
+        <x:v>上海、合肥、北京、武汉、南京等</x:v>
       </x:c>
       <x:c r="F81" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>技术提前批</x:v>
       </x:c>
       <x:c r="G81" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2024年9月-2027年8月毕业</x:v>
       </x:c>
       <x:c r="H81" s="4" t="str">
-        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
+        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
       </x:c>
       <x:c r="I81" s="15" t="str">
-        <x:v>https://www.3peak.cn/careers</x:v>
+        <x:v>https://campus.nio.com/</x:v>
       </x:c>
       <x:c r="J81" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K81" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；有笔试/测评</x:v>
       </x:c>
       <x:c r="L81" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M81" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N81" s="4" t="str">
-        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
+        <x:v>最多同时申请3个岗位。</x:v>
       </x:c>
       <x:c r="O81" s="15" t="str">
-        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
-      </x:c>
-      <x:c r="P81" s="16" t="str">
-        <x:v>B-招聘平台/高校就业转载</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P81" s="14" t="str">
+        <x:v>A-官方来源公告已核验</x:v>
       </x:c>
       <x:c r="Q81" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="54" customHeight="1">
       <x:c r="A82" s="4" t="str">
-        <x:v>不晚于2026-07-07</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="B82" s="4" t="str">
-        <x:v>文远知行WeRide</x:v>
+        <x:v>北方华创</x:v>
       </x:c>
       <x:c r="C82" s="4" t="str">
-        <x:v>自动驾驶/人工智能</x:v>
+        <x:v>半导体设备</x:v>
       </x:c>
       <x:c r="D82" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E82" s="4" t="str">
-        <x:v>广州、深圳、武汉等，以岗位页为准</x:v>
+        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F82" s="4" t="str">
-        <x:v>正式批/校招/可转正实习</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G82" s="4" t="str">
-        <x:v>2027届应届毕业生及可转正实习生，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H82" s="4" t="str">
-        <x:v>感知/预测/规划控制算法、算法测试、测试开发、SRE、云与车端安全、AI Infra、仿真平台等</x:v>
+        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
       </x:c>
       <x:c r="I82" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
+        <x:v>https://career.naura.com/campus</x:v>
       </x:c>
       <x:c r="J82" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4806,357 +4811,357 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L82" s="4" t="str">
-        <x:v>企业官方校招系统在招；已核验137个职位</x:v>
+        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
       </x:c>
       <x:c r="M82" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N82" s="4" t="str">
-        <x:v>官方列表显示2027届校招职位最早发布于7月7日；部分岗位为可转正实习，城市和岗位随招聘系统实时调整。</x:v>
+        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
       </x:c>
       <x:c r="O82" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
       </x:c>
       <x:c r="P82" s="14" t="str">
-        <x:v>A-企业官方校招系统与职位列表已核验</x:v>
+        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
       </x:c>
       <x:c r="Q82" s="4" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="54" customHeight="1">
-      <x:c r="A83" s="17" t="str">
-        <x:v>2026-07-06</x:v>
-      </x:c>
-      <x:c r="B83" s="17" t="str">
-        <x:v>米哈游</x:v>
-      </x:c>
-      <x:c r="C83" s="17" t="str">
-        <x:v>游戏/互联网</x:v>
-      </x:c>
-      <x:c r="D83" s="17" t="str">
+      <x:c r="A83" s="4" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="B83" s="4" t="str">
+        <x:v>百度</x:v>
+      </x:c>
+      <x:c r="C83" s="4" t="str">
+        <x:v>互联网/AI</x:v>
+      </x:c>
+      <x:c r="D83" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E83" s="17" t="str">
-        <x:v>上海、北京</x:v>
-      </x:c>
-      <x:c r="F83" s="17" t="str">
-        <x:v>技术提前批</x:v>
-      </x:c>
-      <x:c r="G83" s="17" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H83" s="17" t="str">
-        <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
-      </x:c>
-      <x:c r="I83" s="18" t="str">
-        <x:v>https://campus.mihoyo.com/</x:v>
-      </x:c>
-      <x:c r="J83" s="17" t="str">
-        <x:v>2026-07-27</x:v>
-      </x:c>
-      <x:c r="K83" s="17" t="str">
-        <x:v>有免笔试直通面试机会</x:v>
-      </x:c>
-      <x:c r="L83" s="17" t="str">
-        <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
-      </x:c>
-      <x:c r="M83" s="17" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N83" s="17" t="str">
-        <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
-      </x:c>
-      <x:c r="O83" s="18" t="str">
+      <x:c r="E83" s="4" t="str">
+        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+      </x:c>
+      <x:c r="F83" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G83" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H83" s="4" t="str">
+        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+      </x:c>
+      <x:c r="I83" s="15" t="str">
+        <x:v>https://talent.baidu.com/jobs</x:v>
+      </x:c>
+      <x:c r="J83" s="4" t="str">
+        <x:v>2027-06-30</x:v>
+      </x:c>
+      <x:c r="K83" s="4" t="str">
+        <x:v>部分免；并非所有候选人参加笔试</x:v>
+      </x:c>
+      <x:c r="L83" s="4" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M83" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N83" s="4" t="str">
+        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
+      </x:c>
+      <x:c r="O83" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P83" s="14" t="str">
-        <x:v>A-官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q83" s="17" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>A-官方招聘日历/官方来源已核验</x:v>
+      </x:c>
+      <x:c r="Q83" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="54" customHeight="1">
       <x:c r="A84" s="4" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B84" s="4" t="str">
-        <x:v>京东方-先锋京英计划</x:v>
+        <x:v>中国航天科工集团第六研究院</x:v>
       </x:c>
       <x:c r="C84" s="4" t="str">
-        <x:v>显示技术/半导体/物联网</x:v>
+        <x:v>航天/军工/动力系统</x:v>
       </x:c>
       <x:c r="D84" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企院所</x:v>
       </x:c>
       <x:c r="E84" s="4" t="str">
-        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
+        <x:v>呼和浩特及所属单位</x:v>
       </x:c>
       <x:c r="F84" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>提前批+暑期开放日</x:v>
       </x:c>
       <x:c r="G84" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
       </x:c>
       <x:c r="H84" s="4" t="str">
-        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
+        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
       </x:c>
       <x:c r="I84" s="15" t="str">
-        <x:v>https://campus.boe.com/</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
       <x:c r="J84" s="4" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K84" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L84" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
       </x:c>
       <x:c r="M84" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N84" s="4" t="str">
-        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
+        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
       </x:c>
       <x:c r="O84" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P84" s="14" t="str">
-        <x:v>A-国家大学生就业平台公告已核验</x:v>
+        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
+      </x:c>
+      <x:c r="P84" s="16" t="str">
+        <x:v>B-高校就业网公开公告</x:v>
       </x:c>
       <x:c r="Q84" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="54" customHeight="1">
       <x:c r="A85" s="4" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="B85" s="4" t="str">
-        <x:v>中国航天科技集团</x:v>
+        <x:v>思瑞浦</x:v>
       </x:c>
       <x:c r="C85" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>半导体/模拟IC</x:v>
       </x:c>
       <x:c r="D85" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E85" s="4" t="str">
-        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
+        <x:v>上海、深圳等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F85" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G85" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H85" s="4" t="str">
-        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
+        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
       </x:c>
       <x:c r="I85" s="15" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
+        <x:v>https://www.3peak.cn/careers</x:v>
       </x:c>
       <x:c r="J85" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K85" s="4" t="str">
-        <x:v>各院所自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L85" s="4" t="str">
-        <x:v>官方公告已确认启动</x:v>
+        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
       </x:c>
       <x:c r="M85" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N85" s="4" t="str">
-        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
+        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
       </x:c>
       <x:c r="O85" s="15" t="str">
-        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
-      </x:c>
-      <x:c r="P85" s="14" t="str">
-        <x:v>A-国务院国资委/集团官方来源</x:v>
+        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
+      </x:c>
+      <x:c r="P85" s="16" t="str">
+        <x:v>B-招聘平台/高校就业转载</x:v>
       </x:c>
       <x:c r="Q85" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="54" customHeight="1">
       <x:c r="A86" s="4" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>不晚于2026-07-07</x:v>
       </x:c>
       <x:c r="B86" s="4" t="str">
-        <x:v>高途</x:v>
+        <x:v>文远知行WeRide</x:v>
       </x:c>
       <x:c r="C86" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>自动驾驶/人工智能</x:v>
       </x:c>
       <x:c r="D86" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E86" s="4" t="str">
+        <x:v>广州、深圳、武汉等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F86" s="4" t="str">
+        <x:v>正式批/校招/可转正实习</x:v>
+      </x:c>
+      <x:c r="G86" s="4" t="str">
+        <x:v>2027届应届毕业生及可转正实习生，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H86" s="4" t="str">
+        <x:v>感知/预测/规划控制算法、算法测试、测试开发、SRE、云与车端安全、AI Infra、仿真平台等</x:v>
+      </x:c>
+      <x:c r="I86" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
+      </x:c>
+      <x:c r="J86" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K86" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L86" s="4" t="str">
+        <x:v>企业官方校招系统在招；已核验137个职位</x:v>
+      </x:c>
+      <x:c r="M86" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N86" s="4" t="str">
+        <x:v>官方列表显示2027届校招职位最早发布于7月7日；部分岗位为可转正实习，城市和岗位随招聘系统实时调整。</x:v>
+      </x:c>
+      <x:c r="O86" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
+      </x:c>
+      <x:c r="P86" s="14" t="str">
+        <x:v>A-企业官方校招系统与职位列表已核验</x:v>
+      </x:c>
+      <x:c r="Q86" s="4" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="54" customHeight="1">
+      <x:c r="A87" s="18" t="str">
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="B87" s="18" t="str">
+        <x:v>米哈游</x:v>
+      </x:c>
+      <x:c r="C87" s="18" t="str">
+        <x:v>游戏/互联网</x:v>
+      </x:c>
+      <x:c r="D87" s="18" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E86" s="4" t="str">
-        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
-      </x:c>
-      <x:c r="F86" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G86" s="4" t="str">
-        <x:v>27届为主，优秀28届也可投</x:v>
-      </x:c>
-      <x:c r="H86" s="4" t="str">
-        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
-      </x:c>
-      <x:c r="I86" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
-      </x:c>
-      <x:c r="J86" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K86" s="4" t="str">
-        <x:v>否；流程包含笔试</x:v>
-      </x:c>
-      <x:c r="L86" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M86" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N86" s="4" t="str">
-        <x:v>滚动发放Offer，截止时间未公布。</x:v>
-      </x:c>
-      <x:c r="O86" s="15" t="str">
+      <x:c r="E87" s="18" t="str">
+        <x:v>上海、北京</x:v>
+      </x:c>
+      <x:c r="F87" s="18" t="str">
+        <x:v>技术提前批</x:v>
+      </x:c>
+      <x:c r="G87" s="18" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H87" s="18" t="str">
+        <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
+      </x:c>
+      <x:c r="I87" s="19" t="str">
+        <x:v>https://campus.mihoyo.com/</x:v>
+      </x:c>
+      <x:c r="J87" s="18" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+      <x:c r="K87" s="18" t="str">
+        <x:v>有免笔试直通面试机会</x:v>
+      </x:c>
+      <x:c r="L87" s="18" t="str">
+        <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
+      </x:c>
+      <x:c r="M87" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N87" s="18" t="str">
+        <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
+      </x:c>
+      <x:c r="O87" s="19" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P86" s="14" t="str">
-        <x:v>A-官方投递平台已核验</x:v>
-      </x:c>
-      <x:c r="Q86" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" ht="54" customHeight="1">
-      <x:c r="A87" s="4" t="str">
-        <x:v>2026-06-27</x:v>
-      </x:c>
-      <x:c r="B87" s="4" t="str">
-        <x:v>中汽中心</x:v>
-      </x:c>
-      <x:c r="C87" s="4" t="str">
-        <x:v>汽车检测/科研</x:v>
-      </x:c>
-      <x:c r="D87" s="4" t="str">
-        <x:v>央企</x:v>
-      </x:c>
-      <x:c r="E87" s="4" t="str">
-        <x:v>天津、武汉、北京、上海等</x:v>
-      </x:c>
-      <x:c r="F87" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G87" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H87" s="4" t="str">
-        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
-      </x:c>
-      <x:c r="I87" s="15" t="str">
-        <x:v>https://www.catarc.ac.cn/</x:v>
-      </x:c>
-      <x:c r="J87" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K87" s="4" t="str">
-        <x:v>官方未统一说明</x:v>
-      </x:c>
-      <x:c r="L87" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
-      </x:c>
-      <x:c r="M87" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N87" s="4" t="str">
-        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
-      </x:c>
-      <x:c r="O87" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
-      </x:c>
-      <x:c r="P87" s="16" t="str">
-        <x:v>B-公开招聘公告</x:v>
-      </x:c>
-      <x:c r="Q87" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+      <x:c r="P87" s="14" t="str">
+        <x:v>A-官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q87" s="18" t="str">
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="54" customHeight="1">
       <x:c r="A88" s="4" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="B88" s="4" t="str">
-        <x:v>中国航天科工集团</x:v>
+        <x:v>京东方-先锋京英计划</x:v>
       </x:c>
       <x:c r="C88" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>显示技术/半导体/物联网</x:v>
       </x:c>
       <x:c r="D88" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E88" s="4" t="str">
-        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
+        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
       </x:c>
       <x:c r="F88" s="4" t="str">
-        <x:v>正式批/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G88" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H88" s="4" t="str">
-        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
+        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
       </x:c>
       <x:c r="I88" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
+        <x:v>https://campus.boe.com/</x:v>
       </x:c>
       <x:c r="J88" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K88" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L88" s="4" t="str">
-        <x:v>官网公告已确认启动</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M88" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N88" s="4" t="str">
-        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
+        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
       </x:c>
       <x:c r="O88" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P88" s="14" t="str">
-        <x:v>A-集团官网公告已核验</x:v>
+        <x:v>A-国家大学生就业平台公告已核验</x:v>
       </x:c>
       <x:c r="Q88" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="54" customHeight="1">
       <x:c r="A89" s="4" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="B89" s="4" t="str">
-        <x:v>禾赛科技</x:v>
+        <x:v>中国航天科技集团</x:v>
       </x:c>
       <x:c r="C89" s="4" t="str">
-        <x:v>激光雷达/机器人</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D89" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E89" s="4" t="str">
-        <x:v>上海、杭州</x:v>
+        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
       </x:c>
       <x:c r="F89" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5165,31 +5170,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H89" s="4" t="str">
-        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
+        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
       </x:c>
       <x:c r="I89" s="15" t="str">
-        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J89" s="4" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K89" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各院所自行组织，未统一</x:v>
       </x:c>
       <x:c r="L89" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>官方公告已确认启动</x:v>
       </x:c>
       <x:c r="M89" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N89" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
       </x:c>
       <x:c r="O89" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P89" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
+      </x:c>
+      <x:c r="P89" s="14" t="str">
+        <x:v>A-国务院国资委/集团官方来源</x:v>
       </x:c>
       <x:c r="Q89" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5197,52 +5202,52 @@
     </x:row>
     <x:row r="90" ht="54" customHeight="1">
       <x:c r="A90" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="B90" s="4" t="str">
-        <x:v>北京国望光学科技有限公司</x:v>
+        <x:v>高途</x:v>
       </x:c>
       <x:c r="C90" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D90" s="4" t="str">
-        <x:v>央国企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E90" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
       </x:c>
       <x:c r="F90" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G90" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>27届为主，优秀28届也可投</x:v>
       </x:c>
       <x:c r="H90" s="4" t="str">
-        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
-      </x:c>
-      <x:c r="I90" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
+      </x:c>
+      <x:c r="I90" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
       </x:c>
       <x:c r="J90" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K90" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；流程包含笔试</x:v>
       </x:c>
       <x:c r="L90" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M90" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N90" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>滚动发放Offer，截止时间未公布。</x:v>
       </x:c>
       <x:c r="O90" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P90" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P90" s="14" t="str">
+        <x:v>A-官方投递平台已核验</x:v>
       </x:c>
       <x:c r="Q90" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5250,19 +5255,19 @@
     </x:row>
     <x:row r="91" ht="54" customHeight="1">
       <x:c r="A91" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="B91" s="4" t="str">
-        <x:v>乐读</x:v>
+        <x:v>中汽中心</x:v>
       </x:c>
       <x:c r="C91" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>汽车检测/科研</x:v>
       </x:c>
       <x:c r="D91" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E91" s="4" t="str">
-        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
+        <x:v>天津、武汉、北京、上海等</x:v>
       </x:c>
       <x:c r="F91" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5271,31 +5276,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H91" s="4" t="str">
-        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
-      </x:c>
-      <x:c r="I91" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
+      </x:c>
+      <x:c r="I91" s="15" t="str">
+        <x:v>https://www.catarc.ac.cn/</x:v>
       </x:c>
       <x:c r="J91" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K91" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L91" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M91" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N91" s="4" t="str">
-        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
+        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
       </x:c>
       <x:c r="O91" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
       </x:c>
       <x:c r="P91" s="16" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
+        <x:v>B-公开招聘公告</x:v>
       </x:c>
       <x:c r="Q91" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5303,72 +5308,72 @@
     </x:row>
     <x:row r="92" ht="54" customHeight="1">
       <x:c r="A92" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="B92" s="4" t="str">
-        <x:v>龙蟠科技</x:v>
+        <x:v>中国航天科工集团</x:v>
       </x:c>
       <x:c r="C92" s="4" t="str">
-        <x:v>新能源材料/化工</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D92" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E92" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
       </x:c>
       <x:c r="F92" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/提前批</x:v>
       </x:c>
       <x:c r="G92" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H92" s="4" t="str">
-        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
+        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
       </x:c>
       <x:c r="I92" s="15" t="str">
-        <x:v>https://www.lopal.com.cn/join</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
       <x:c r="J92" s="4" t="str">
-        <x:v>2027-06-01</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K92" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L92" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>官网公告已确认启动</x:v>
       </x:c>
       <x:c r="M92" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N92" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
       </x:c>
       <x:c r="O92" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P92" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
+      </x:c>
+      <x:c r="P92" s="14" t="str">
+        <x:v>A-集团官网公告已核验</x:v>
       </x:c>
       <x:c r="Q92" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="54" customHeight="1">
       <x:c r="A93" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="B93" s="4" t="str">
-        <x:v>牧原</x:v>
+        <x:v>禾赛科技</x:v>
       </x:c>
       <x:c r="C93" s="4" t="str">
-        <x:v>农业/食品/智能养殖</x:v>
+        <x:v>激光雷达/机器人</x:v>
       </x:c>
       <x:c r="D93" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E93" s="4" t="str">
-        <x:v>河南南阳及全国</x:v>
+        <x:v>上海、杭州</x:v>
       </x:c>
       <x:c r="F93" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5377,13 +5382,13 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H93" s="4" t="str">
-        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
+        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
       </x:c>
       <x:c r="I93" s="15" t="str">
-        <x:v>https://job.muyuanfoods.com/</x:v>
+        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
       </x:c>
       <x:c r="J93" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="K93" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -5392,7 +5397,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M93" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N93" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -5412,28 +5417,28 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B94" s="4" t="str">
-        <x:v>三一集团-小语种校招</x:v>
+        <x:v>北京国望光学科技有限公司</x:v>
       </x:c>
       <x:c r="C94" s="4" t="str">
-        <x:v>工程机械/制造</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D94" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央国企</x:v>
       </x:c>
       <x:c r="E94" s="4" t="str">
-        <x:v>海外多国</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F94" s="4" t="str">
-        <x:v>小语种专项/正式批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G94" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H94" s="4" t="str">
-        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
-      </x:c>
-      <x:c r="I94" s="15" t="str">
-        <x:v>https://sanycampus.zhiye.com/</x:v>
+        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
+      </x:c>
+      <x:c r="I94" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J94" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5465,28 +5470,28 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B95" s="4" t="str">
-        <x:v>上海电气-暑期精英训练营</x:v>
+        <x:v>乐读</x:v>
       </x:c>
       <x:c r="C95" s="4" t="str">
-        <x:v>高端装备/能源</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D95" s="4" t="str">
-        <x:v>地方国企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E95" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
       </x:c>
       <x:c r="F95" s="4" t="str">
-        <x:v>训练营/秋招直通</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G95" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H95" s="4" t="str">
-        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
-      </x:c>
-      <x:c r="I95" s="15" t="str">
-        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
+        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
+      </x:c>
+      <x:c r="I95" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J95" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5495,19 +5500,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L95" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M95" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N95" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
       </x:c>
       <x:c r="O95" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P95" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>B-招聘平台公开汇总</x:v>
       </x:c>
       <x:c r="Q95" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5518,49 +5523,49 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B96" s="4" t="str">
-        <x:v>vivo-蓝极星计划</x:v>
+        <x:v>龙蟠科技</x:v>
       </x:c>
       <x:c r="C96" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>新能源材料/化工</x:v>
       </x:c>
       <x:c r="D96" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E96" s="4" t="str">
-        <x:v>深圳、杭州、东莞、上海</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F96" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G96" s="4" t="str">
-        <x:v>博士为主</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H96" s="4" t="str">
-        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
+        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
       </x:c>
       <x:c r="I96" s="15" t="str">
-        <x:v>https://hr.vivo.com/</x:v>
+        <x:v>https://www.lopal.com.cn/join</x:v>
       </x:c>
       <x:c r="J96" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-01</x:v>
       </x:c>
       <x:c r="K96" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L96" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M96" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N96" s="4" t="str">
-        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O96" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P96" s="16" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q96" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5568,31 +5573,31 @@
     </x:row>
     <x:row r="97" ht="54" customHeight="1">
       <x:c r="A97" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B97" s="4" t="str">
-        <x:v>澜起科技</x:v>
+        <x:v>牧原</x:v>
       </x:c>
       <x:c r="C97" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>农业/食品/智能养殖</x:v>
       </x:c>
       <x:c r="D97" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E97" s="4" t="str">
-        <x:v>昆山、西安、南京</x:v>
+        <x:v>河南南阳及全国</x:v>
       </x:c>
       <x:c r="F97" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G97" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H97" s="4" t="str">
-        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
+        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
       </x:c>
       <x:c r="I97" s="15" t="str">
-        <x:v>https://www.montage-tech.com/cn/careers</x:v>
+        <x:v>https://job.muyuanfoods.com/</x:v>
       </x:c>
       <x:c r="J97" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5621,31 +5626,31 @@
     </x:row>
     <x:row r="98" ht="54" customHeight="1">
       <x:c r="A98" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B98" s="4" t="str">
-        <x:v>上海宇量昇</x:v>
+        <x:v>三一集团-小语种校招</x:v>
       </x:c>
       <x:c r="C98" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>工程机械/制造</x:v>
       </x:c>
       <x:c r="D98" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E98" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>海外多国</x:v>
       </x:c>
       <x:c r="F98" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>小语种专项/正式批</x:v>
       </x:c>
       <x:c r="G98" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H98" s="4" t="str">
-        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
+        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
       </x:c>
       <x:c r="I98" s="15" t="str">
-        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
+        <x:v>https://sanycampus.zhiye.com/</x:v>
       </x:c>
       <x:c r="J98" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5674,31 +5679,31 @@
     </x:row>
     <x:row r="99" ht="54" customHeight="1">
       <x:c r="A99" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B99" s="4" t="str">
-        <x:v>是为科技</x:v>
+        <x:v>上海电气-暑期精英训练营</x:v>
       </x:c>
       <x:c r="C99" s="4" t="str">
-        <x:v>新能源/智能制造</x:v>
+        <x:v>高端装备/能源</x:v>
       </x:c>
       <x:c r="D99" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>地方国企</x:v>
       </x:c>
       <x:c r="E99" s="4" t="str">
-        <x:v>南京、上海、常州</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F99" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>训练营/秋招直通</x:v>
       </x:c>
       <x:c r="G99" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H99" s="4" t="str">
-        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
+        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
       </x:c>
       <x:c r="I99" s="15" t="str">
-        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
+        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
       </x:c>
       <x:c r="J99" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5727,31 +5732,31 @@
     </x:row>
     <x:row r="100" ht="54" customHeight="1">
       <x:c r="A100" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B100" s="4" t="str">
-        <x:v>游族网络</x:v>
+        <x:v>vivo-蓝极星计划</x:v>
       </x:c>
       <x:c r="C100" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D100" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E100" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>深圳、杭州、东莞、上海</x:v>
       </x:c>
       <x:c r="F100" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G100" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>博士为主</x:v>
       </x:c>
       <x:c r="H100" s="4" t="str">
-        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
+        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
       </x:c>
       <x:c r="I100" s="15" t="str">
-        <x:v>https://job.youzu.com/</x:v>
+        <x:v>https://hr.vivo.com/</x:v>
       </x:c>
       <x:c r="J100" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5760,19 +5765,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L100" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M100" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N100" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
       </x:c>
       <x:c r="O100" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P100" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>B-招聘平台公开汇总</x:v>
       </x:c>
       <x:c r="Q100" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5780,19 +5785,19 @@
     </x:row>
     <x:row r="101" ht="54" customHeight="1">
       <x:c r="A101" s="4" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B101" s="4" t="str">
-        <x:v>中铁设计</x:v>
+        <x:v>澜起科技</x:v>
       </x:c>
       <x:c r="C101" s="4" t="str">
-        <x:v>轨道交通/工程设计</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D101" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E101" s="4" t="str">
-        <x:v>北京、济南、郑州、太原</x:v>
+        <x:v>昆山、西安、南京</x:v>
       </x:c>
       <x:c r="F101" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5801,10 +5806,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H101" s="4" t="str">
-        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
+        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
       </x:c>
       <x:c r="I101" s="15" t="str">
-        <x:v>https://www.crdc.com/</x:v>
+        <x:v>https://www.montage-tech.com/cn/careers</x:v>
       </x:c>
       <x:c r="J101" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5833,31 +5838,31 @@
     </x:row>
     <x:row r="102" ht="54" customHeight="1">
       <x:c r="A102" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B102" s="4" t="str">
-        <x:v>迈安德集团-校园大使</x:v>
+        <x:v>上海宇量昇</x:v>
       </x:c>
       <x:c r="C102" s="4" t="str">
-        <x:v>粮油工程/装备</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D102" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E102" s="4" t="str">
-        <x:v>扬州/高校</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F102" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G102" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H102" s="4" t="str">
-        <x:v>校园大使</x:v>
+        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
       </x:c>
       <x:c r="I102" s="15" t="str">
-        <x:v>https://www.myande.com/</x:v>
+        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
       </x:c>
       <x:c r="J102" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5886,19 +5891,19 @@
     </x:row>
     <x:row r="103" ht="54" customHeight="1">
       <x:c r="A103" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B103" s="4" t="str">
-        <x:v>迅仿科技</x:v>
+        <x:v>是为科技</x:v>
       </x:c>
       <x:c r="C103" s="4" t="str">
-        <x:v>工业软件/仿真</x:v>
+        <x:v>新能源/智能制造</x:v>
       </x:c>
       <x:c r="D103" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E103" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>南京、上海、常州</x:v>
       </x:c>
       <x:c r="F103" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5907,10 +5912,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H103" s="4" t="str">
-        <x:v>仿真工程师</x:v>
-      </x:c>
-      <x:c r="I103" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
+      </x:c>
+      <x:c r="I103" s="15" t="str">
+        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
       </x:c>
       <x:c r="J103" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5939,34 +5944,34 @@
     </x:row>
     <x:row r="104" ht="54" customHeight="1">
       <x:c r="A104" s="4" t="str">
-        <x:v>2026-06-12</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B104" s="4" t="str">
-        <x:v>MOVA</x:v>
+        <x:v>游族网络</x:v>
       </x:c>
       <x:c r="C104" s="4" t="str">
-        <x:v>智能家电/机器人</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D104" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E104" s="4" t="str">
-        <x:v>苏州及全国</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F104" s="4" t="str">
-        <x:v>全球校招/正式批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G104" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H104" s="4" t="str">
-        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
       </x:c>
       <x:c r="I104" s="15" t="str">
-        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+        <x:v>https://job.youzu.com/</x:v>
       </x:c>
       <x:c r="J104" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K104" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -5975,7 +5980,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M104" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N104" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -5992,19 +5997,19 @@
     </x:row>
     <x:row r="105" ht="54" customHeight="1">
       <x:c r="A105" s="4" t="str">
-        <x:v>2026-06-11</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="B105" s="4" t="str">
-        <x:v>财通证券</x:v>
+        <x:v>中铁设计</x:v>
       </x:c>
       <x:c r="C105" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>轨道交通/工程设计</x:v>
       </x:c>
       <x:c r="D105" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E105" s="4" t="str">
-        <x:v>杭州、上海、深圳、北京</x:v>
+        <x:v>北京、济南、郑州、太原</x:v>
       </x:c>
       <x:c r="F105" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6013,10 +6018,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H105" s="4" t="str">
-        <x:v>总部、参股公司、分公司岗位</x:v>
+        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
       </x:c>
       <x:c r="I105" s="15" t="str">
-        <x:v>https://www.ctsec.com/joinUs</x:v>
+        <x:v>https://www.crdc.com/</x:v>
       </x:c>
       <x:c r="J105" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6045,31 +6050,31 @@
     </x:row>
     <x:row r="106" ht="54" customHeight="1">
       <x:c r="A106" s="4" t="str">
-        <x:v>2026-06-10</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B106" s="4" t="str">
-        <x:v>歌尔股份</x:v>
+        <x:v>迈安德集团-校园大使</x:v>
       </x:c>
       <x:c r="C106" s="4" t="str">
-        <x:v>消费电子/智能硬件</x:v>
+        <x:v>粮油工程/装备</x:v>
       </x:c>
       <x:c r="D106" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E106" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>扬州/高校</x:v>
       </x:c>
       <x:c r="F106" s="4" t="str">
-        <x:v>实习/校招储备</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G106" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H106" s="4" t="str">
-        <x:v>法务助理</x:v>
+        <x:v>校园大使</x:v>
       </x:c>
       <x:c r="I106" s="15" t="str">
-        <x:v>https://career.goertek.com/</x:v>
+        <x:v>https://www.myande.com/</x:v>
       </x:c>
       <x:c r="J106" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6098,31 +6103,31 @@
     </x:row>
     <x:row r="107" ht="54" customHeight="1">
       <x:c r="A107" s="4" t="str">
-        <x:v>2026-06-09</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B107" s="4" t="str">
-        <x:v>深信服-校园大使</x:v>
+        <x:v>迅仿科技</x:v>
       </x:c>
       <x:c r="C107" s="4" t="str">
-        <x:v>网络安全/云计算</x:v>
+        <x:v>工业软件/仿真</x:v>
       </x:c>
       <x:c r="D107" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E107" s="4" t="str">
-        <x:v>西安</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F107" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G107" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H107" s="4" t="str">
-        <x:v>校园大使</x:v>
-      </x:c>
-      <x:c r="I107" s="15" t="str">
-        <x:v>https://hr.sangfor.com/</x:v>
+        <x:v>仿真工程师</x:v>
+      </x:c>
+      <x:c r="I107" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J107" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6151,34 +6156,34 @@
     </x:row>
     <x:row r="108" ht="54" customHeight="1">
       <x:c r="A108" s="4" t="str">
-        <x:v>2026-06-08</x:v>
+        <x:v>2026-06-12</x:v>
       </x:c>
       <x:c r="B108" s="4" t="str">
-        <x:v>晓禾教育</x:v>
+        <x:v>MOVA</x:v>
       </x:c>
       <x:c r="C108" s="4" t="str">
-        <x:v>教育</x:v>
+        <x:v>智能家电/机器人</x:v>
       </x:c>
       <x:c r="D108" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E108" s="4" t="str">
-        <x:v>武汉、郑州、襄阳、宜昌</x:v>
+        <x:v>苏州及全国</x:v>
       </x:c>
       <x:c r="F108" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>全球校招/正式批</x:v>
       </x:c>
       <x:c r="G108" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H108" s="4" t="str">
-        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
-      </x:c>
-      <x:c r="I108" s="22" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+      </x:c>
+      <x:c r="I108" s="15" t="str">
+        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
       </x:c>
       <x:c r="J108" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K108" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -6187,7 +6192,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M108" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N108" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -6204,31 +6209,31 @@
     </x:row>
     <x:row r="109" ht="54" customHeight="1">
       <x:c r="A109" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-11</x:v>
       </x:c>
       <x:c r="B109" s="4" t="str">
-        <x:v>晖致医药</x:v>
+        <x:v>财通证券</x:v>
       </x:c>
       <x:c r="C109" s="4" t="str">
-        <x:v>医药</x:v>
+        <x:v>证券/金融</x:v>
       </x:c>
       <x:c r="D109" s="4" t="str">
-        <x:v>外资</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E109" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>杭州、上海、深圳、北京</x:v>
       </x:c>
       <x:c r="F109" s="4" t="str">
-        <x:v>实习储备正式岗</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G109" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H109" s="4" t="str">
-        <x:v>医学信息沟通实习生</x:v>
+        <x:v>总部、参股公司、分公司岗位</x:v>
       </x:c>
       <x:c r="I109" s="15" t="str">
-        <x:v>https://careers.viatris.com/</x:v>
+        <x:v>https://www.ctsec.com/joinUs</x:v>
       </x:c>
       <x:c r="J109" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6257,31 +6262,31 @@
     </x:row>
     <x:row r="110" ht="54" customHeight="1">
       <x:c r="A110" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-10</x:v>
       </x:c>
       <x:c r="B110" s="4" t="str">
-        <x:v>苏州鸿凌达电子</x:v>
+        <x:v>歌尔股份</x:v>
       </x:c>
       <x:c r="C110" s="4" t="str">
-        <x:v>电子制造</x:v>
+        <x:v>消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D110" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E110" s="4" t="str">
-        <x:v>苏州</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F110" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>实习/校招储备</x:v>
       </x:c>
       <x:c r="G110" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H110" s="4" t="str">
-        <x:v>财务助理</x:v>
+        <x:v>法务助理</x:v>
       </x:c>
       <x:c r="I110" s="15" t="str">
-        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
+        <x:v>https://career.goertek.com/</x:v>
       </x:c>
       <x:c r="J110" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6310,31 +6315,31 @@
     </x:row>
     <x:row r="111" ht="54" customHeight="1">
       <x:c r="A111" s="4" t="str">
-        <x:v>2026-06-02</x:v>
+        <x:v>2026-06-09</x:v>
       </x:c>
       <x:c r="B111" s="4" t="str">
-        <x:v>万得信息</x:v>
+        <x:v>深信服-校园大使</x:v>
       </x:c>
       <x:c r="C111" s="4" t="str">
-        <x:v>金融数据/软件</x:v>
+        <x:v>网络安全/云计算</x:v>
       </x:c>
       <x:c r="D111" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E111" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>西安</x:v>
       </x:c>
       <x:c r="F111" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G111" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H111" s="4" t="str">
-        <x:v>AI算法工程师等</x:v>
+        <x:v>校园大使</x:v>
       </x:c>
       <x:c r="I111" s="15" t="str">
-        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
+        <x:v>https://hr.sangfor.com/</x:v>
       </x:c>
       <x:c r="J111" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6363,30 +6368,30 @@
     </x:row>
     <x:row r="112" ht="54" customHeight="1">
       <x:c r="A112" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-08</x:v>
       </x:c>
       <x:c r="B112" s="4" t="str">
-        <x:v>淘大集供应链</x:v>
+        <x:v>晓禾教育</x:v>
       </x:c>
       <x:c r="C112" s="4" t="str">
-        <x:v>零售/供应链</x:v>
+        <x:v>教育</x:v>
       </x:c>
       <x:c r="D112" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E112" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>武汉、郑州、襄阳、宜昌</x:v>
       </x:c>
       <x:c r="F112" s="4" t="str">
-        <x:v>管培/实习</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G112" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H112" s="4" t="str">
-        <x:v>巡店管培生、实习生</x:v>
-      </x:c>
-      <x:c r="I112" s="22" t="str">
+        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
+      </x:c>
+      <x:c r="I112" s="23" t="str">
         <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J112" s="4" t="str">
@@ -6416,31 +6421,31 @@
     </x:row>
     <x:row r="113" ht="54" customHeight="1">
       <x:c r="A113" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="B113" s="4" t="str">
-        <x:v>友芝友实业集团</x:v>
+        <x:v>晖致医药</x:v>
       </x:c>
       <x:c r="C113" s="4" t="str">
-        <x:v>综合实业</x:v>
+        <x:v>医药</x:v>
       </x:c>
       <x:c r="D113" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>外资</x:v>
       </x:c>
       <x:c r="E113" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F113" s="4" t="str">
-        <x:v>管培生</x:v>
+        <x:v>实习储备正式岗</x:v>
       </x:c>
       <x:c r="G113" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H113" s="4" t="str">
-        <x:v>青年领军人才管培生</x:v>
+        <x:v>医学信息沟通实习生</x:v>
       </x:c>
       <x:c r="I113" s="15" t="str">
-        <x:v>https://www.yzyqh.com/jrwm</x:v>
+        <x:v>https://careers.viatris.com/</x:v>
       </x:c>
       <x:c r="J113" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6469,19 +6474,19 @@
     </x:row>
     <x:row r="114" ht="54" customHeight="1">
       <x:c r="A114" s="4" t="str">
-        <x:v>2026-05-29</x:v>
+        <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="B114" s="4" t="str">
-        <x:v>银雁科技</x:v>
+        <x:v>苏州鸿凌达电子</x:v>
       </x:c>
       <x:c r="C114" s="4" t="str">
-        <x:v>金融科技服务</x:v>
+        <x:v>电子制造</x:v>
       </x:c>
       <x:c r="D114" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E114" s="4" t="str">
-        <x:v>成都</x:v>
+        <x:v>苏州</x:v>
       </x:c>
       <x:c r="F114" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6490,10 +6495,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H114" s="4" t="str">
-        <x:v>人伤理赔</x:v>
+        <x:v>财务助理</x:v>
       </x:c>
       <x:c r="I114" s="15" t="str">
-        <x:v>https://www.cfss.net.cn/</x:v>
+        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
       </x:c>
       <x:c r="J114" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6522,19 +6527,19 @@
     </x:row>
     <x:row r="115" ht="54" customHeight="1">
       <x:c r="A115" s="4" t="str">
-        <x:v>2026-05-15</x:v>
+        <x:v>2026-06-02</x:v>
       </x:c>
       <x:c r="B115" s="4" t="str">
-        <x:v>知乎</x:v>
+        <x:v>万得信息</x:v>
       </x:c>
       <x:c r="C115" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>金融数据/软件</x:v>
       </x:c>
       <x:c r="D115" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E115" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F115" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6543,10 +6548,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H115" s="4" t="str">
-        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
+        <x:v>AI算法工程师等</x:v>
       </x:c>
       <x:c r="I115" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
+        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
       </x:c>
       <x:c r="J115" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6575,31 +6580,31 @@
     </x:row>
     <x:row r="116" ht="54" customHeight="1">
       <x:c r="A116" s="4" t="str">
-        <x:v>2026-05-08</x:v>
+        <x:v>2026-06-01</x:v>
       </x:c>
       <x:c r="B116" s="4" t="str">
-        <x:v>招商银行长沙分行</x:v>
+        <x:v>淘大集供应链</x:v>
       </x:c>
       <x:c r="C116" s="4" t="str">
-        <x:v>银行/金融</x:v>
+        <x:v>零售/供应链</x:v>
       </x:c>
       <x:c r="D116" s="4" t="str">
-        <x:v>股份制银行</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E116" s="4" t="str">
-        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+        <x:v>武汉</x:v>
       </x:c>
       <x:c r="F116" s="4" t="str">
-        <x:v>暑期实习/秋招直通</x:v>
+        <x:v>管培/实习</x:v>
       </x:c>
       <x:c r="G116" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H116" s="4" t="str">
-        <x:v>2027暑期实习生</x:v>
-      </x:c>
-      <x:c r="I116" s="15" t="str">
-        <x:v>https://career.cmbchina.com/</x:v>
+        <x:v>巡店管培生、实习生</x:v>
+      </x:c>
+      <x:c r="I116" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J116" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6628,31 +6633,31 @@
     </x:row>
     <x:row r="117" ht="54" customHeight="1">
       <x:c r="A117" s="4" t="str">
-        <x:v>2026-04-22</x:v>
+        <x:v>2026-06-01</x:v>
       </x:c>
       <x:c r="B117" s="4" t="str">
-        <x:v>华金证券</x:v>
+        <x:v>友芝友实业集团</x:v>
       </x:c>
       <x:c r="C117" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>综合实业</x:v>
       </x:c>
       <x:c r="D117" s="4" t="str">
-        <x:v>国企</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E117" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>武汉</x:v>
       </x:c>
       <x:c r="F117" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>管培生</x:v>
       </x:c>
       <x:c r="G117" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H117" s="4" t="str">
-        <x:v>战略发展类</x:v>
+        <x:v>青年领军人才管培生</x:v>
       </x:c>
       <x:c r="I117" s="15" t="str">
-        <x:v>https://www.huajinsc.cn/</x:v>
+        <x:v>https://www.yzyqh.com/jrwm</x:v>
       </x:c>
       <x:c r="J117" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6676,6 +6681,271 @@
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q117" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" ht="54" customHeight="1">
+      <x:c r="A118" s="4" t="str">
+        <x:v>2026-05-29</x:v>
+      </x:c>
+      <x:c r="B118" s="4" t="str">
+        <x:v>银雁科技</x:v>
+      </x:c>
+      <x:c r="C118" s="4" t="str">
+        <x:v>金融科技服务</x:v>
+      </x:c>
+      <x:c r="D118" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E118" s="4" t="str">
+        <x:v>成都</x:v>
+      </x:c>
+      <x:c r="F118" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G118" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H118" s="4" t="str">
+        <x:v>人伤理赔</x:v>
+      </x:c>
+      <x:c r="I118" s="15" t="str">
+        <x:v>https://www.cfss.net.cn/</x:v>
+      </x:c>
+      <x:c r="J118" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K118" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L118" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M118" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N118" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O118" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P118" s="16" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q118" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" ht="54" customHeight="1">
+      <x:c r="A119" s="4" t="str">
+        <x:v>不晚于2026-05-19</x:v>
+      </x:c>
+      <x:c r="B119" s="4" t="str">
+        <x:v>宇树科技-2027校园招聘</x:v>
+      </x:c>
+      <x:c r="C119" s="4" t="str">
+        <x:v>机器人/具身智能</x:v>
+      </x:c>
+      <x:c r="D119" s="4" t="str">
+        <x:v>民营/科技企业</x:v>
+      </x:c>
+      <x:c r="E119" s="4" t="str">
+        <x:v>杭州</x:v>
+      </x:c>
+      <x:c r="F119" s="4" t="str">
+        <x:v>正式批/校园招聘</x:v>
+      </x:c>
+      <x:c r="G119" s="4" t="str">
+        <x:v>2027届应届生，以具体岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H119" s="4" t="str">
+        <x:v>算法、嵌入式、软件、硬件、机械、SLAM、C++、AI、数据、前端、测试、销售、技术支持及设计等</x:v>
+      </x:c>
+      <x:c r="I119" s="15" t="str">
+        <x:v>https://www.unitree.com/cn/position</x:v>
+      </x:c>
+      <x:c r="J119" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K119" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L119" s="4" t="str">
+        <x:v>本轮新增；宇树科技官方招贤纳士页面当前显示多项热招岗位</x:v>
+      </x:c>
+      <x:c r="M119" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N119" s="4" t="str">
+        <x:v>官方岗位页当前显示杭州技术类与销售类多个热招职位；校园招聘公告由高校就业平台发布，投递以宇树官网职位详情为准。</x:v>
+      </x:c>
+      <x:c r="O119" s="15" t="str">
+        <x:v>https://www.unitree.com/cn/position</x:v>
+      </x:c>
+      <x:c r="P119" s="14" t="str">
+        <x:v>A-企业官方招贤纳士页面已核验</x:v>
+      </x:c>
+      <x:c r="Q119" s="4" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" ht="54" customHeight="1">
+      <x:c r="A120" s="4" t="str">
+        <x:v>2026-05-15</x:v>
+      </x:c>
+      <x:c r="B120" s="4" t="str">
+        <x:v>知乎</x:v>
+      </x:c>
+      <x:c r="C120" s="4" t="str">
+        <x:v>互联网/内容平台</x:v>
+      </x:c>
+      <x:c r="D120" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E120" s="4" t="str">
+        <x:v>北京</x:v>
+      </x:c>
+      <x:c r="F120" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G120" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H120" s="4" t="str">
+        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
+      </x:c>
+      <x:c r="I120" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
+      </x:c>
+      <x:c r="J120" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K120" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L120" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M120" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N120" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O120" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P120" s="16" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q120" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="54" customHeight="1">
+      <x:c r="A121" s="4" t="str">
+        <x:v>2026-05-08</x:v>
+      </x:c>
+      <x:c r="B121" s="4" t="str">
+        <x:v>招商银行长沙分行</x:v>
+      </x:c>
+      <x:c r="C121" s="4" t="str">
+        <x:v>银行/金融</x:v>
+      </x:c>
+      <x:c r="D121" s="4" t="str">
+        <x:v>股份制银行</x:v>
+      </x:c>
+      <x:c r="E121" s="4" t="str">
+        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+      </x:c>
+      <x:c r="F121" s="4" t="str">
+        <x:v>暑期实习/秋招直通</x:v>
+      </x:c>
+      <x:c r="G121" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H121" s="4" t="str">
+        <x:v>2027暑期实习生</x:v>
+      </x:c>
+      <x:c r="I121" s="15" t="str">
+        <x:v>https://career.cmbchina.com/</x:v>
+      </x:c>
+      <x:c r="J121" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K121" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L121" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M121" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N121" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O121" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P121" s="16" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q121" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" ht="54" customHeight="1">
+      <x:c r="A122" s="4" t="str">
+        <x:v>2026-04-22</x:v>
+      </x:c>
+      <x:c r="B122" s="4" t="str">
+        <x:v>华金证券</x:v>
+      </x:c>
+      <x:c r="C122" s="4" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="D122" s="4" t="str">
+        <x:v>国企</x:v>
+      </x:c>
+      <x:c r="E122" s="4" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F122" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G122" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H122" s="4" t="str">
+        <x:v>战略发展类</x:v>
+      </x:c>
+      <x:c r="I122" s="15" t="str">
+        <x:v>https://www.huajinsc.cn/</x:v>
+      </x:c>
+      <x:c r="J122" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K122" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L122" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M122" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N122" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O122" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P122" s="16" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q122" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -6686,7 +6956,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e1ab9c254a3487a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2abd2ade612244ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6716,7 +6986,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>近期有明确截止时间的项目（截至2026-08-06）</x:v>
+        <x:v>近期有明确截止时间的项目（截至2026-08-07）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -6810,54 +7080,56 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
-      <x:c r="A4" s="4" t="str">
+      <x:c r="A4" s="16" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="str">
+      <x:c r="B4" s="16" t="str">
         <x:v>莉莉丝游戏</x:v>
       </x:c>
-      <x:c r="C4" s="4" t="str">
+      <x:c r="C4" s="16" t="str">
         <x:v>游戏</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="str">
+      <x:c r="D4" s="16" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E4" s="4" t="str">
+      <x:c r="E4" s="16" t="str">
         <x:v>上海等，以岗位页为准</x:v>
       </x:c>
-      <x:c r="F4" s="4" t="str">
+      <x:c r="F4" s="16" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G4" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="str">
+      <x:c r="G4" s="16" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H4" s="16" t="str">
         <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
       </x:c>
-      <x:c r="I4" s="15" t="str">
-        <x:v>https://campus.lilith.com/</x:v>
-      </x:c>
-      <x:c r="J4" s="4" t="str">
+      <x:c r="I4" s="17" t="str">
+        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
+      </x:c>
+      <x:c r="J4" s="16" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
-      <x:c r="K4" s="4" t="str">
+      <x:c r="K4" s="16" t="str">
         <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
-      <x:c r="L4" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
-      </x:c>
-      <x:c r="M4" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N4" s="4" t="str"/>
-      <x:c r="O4" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P4" s="19" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q4" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+      <x:c r="L4" s="16" t="str">
+        <x:v>今日截止；莉莉丝官方校园招聘页当前仍显示27届校招提前批14个职位</x:v>
+      </x:c>
+      <x:c r="M4" s="16" t="str">
+        <x:v>P0-今日截止</x:v>
+      </x:c>
+      <x:c r="N4" s="16" t="str">
+        <x:v>官网当前显示服务器开发、数据分析、战略研究、算法、关卡策划、客户端等27届提前批职位；截止日为2026-08-07，页面仍可投递但可能随时关闭，建议立即完成网申。</x:v>
+      </x:c>
+      <x:c r="O4" s="17" t="str">
+        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
+      </x:c>
+      <x:c r="P4" s="14" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q4" s="16" t="str">
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
@@ -7012,7 +7284,7 @@
       <x:c r="O7" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P7" s="19" t="str">
+      <x:c r="P7" s="20" t="str">
         <x:v>C-名称需二次确认</x:v>
       </x:c>
       <x:c r="Q7" s="4" t="str">
@@ -7063,7 +7335,7 @@
       <x:c r="O8" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P8" s="19" t="str">
+      <x:c r="P8" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q8" s="4" t="str">
@@ -7114,7 +7386,7 @@
       <x:c r="O9" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P9" s="19" t="str">
+      <x:c r="P9" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q9" s="4" t="str">
@@ -7764,7 +8036,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R336494da190147f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43b37ffcbb2b47fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7781,295 +8053,295 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="27" t="str">
-        <x:v>使用说明与统计（截至2026-08-06）</x:v>
-      </x:c>
-      <x:c r="B1" s="27"/>
-      <x:c r="C1" s="27"/>
-      <x:c r="D1" s="27"/>
-      <x:c r="E1" s="27"/>
+      <x:c r="A1" s="28" t="str">
+        <x:v>使用说明与统计（截至2026-08-07）</x:v>
+      </x:c>
+      <x:c r="B1" s="28"/>
+      <x:c r="C1" s="28"/>
+      <x:c r="D1" s="28"/>
+      <x:c r="E1" s="28"/>
       <x:c r="F1"/>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="25"/>
-      <x:c r="B2" s="25"/>
-      <x:c r="C2" s="25"/>
-      <x:c r="D2" s="25"/>
-      <x:c r="E2" s="25"/>
+      <x:c r="A2" s="26"/>
+      <x:c r="B2" s="26"/>
+      <x:c r="C2" s="26"/>
+      <x:c r="D2" s="26"/>
+      <x:c r="E2" s="26"/>
       <x:c r="F2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="28" t="str">
+      <x:c r="A3" s="29" t="str">
         <x:v>核验等级</x:v>
       </x:c>
-      <x:c r="B3" s="28" t="str">
+      <x:c r="B3" s="29" t="str">
         <x:v>含义</x:v>
       </x:c>
-      <x:c r="C3" s="28"/>
-      <x:c r="D3" s="29" t="str">
+      <x:c r="C3" s="29"/>
+      <x:c r="D3" s="30" t="str">
         <x:v>行业分布（前15）</x:v>
       </x:c>
-      <x:c r="E3" s="30"/>
+      <x:c r="E3" s="31"/>
       <x:c r="F3"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="25" t="str">
+      <x:c r="A4" s="26" t="str">
         <x:v>A</x:v>
       </x:c>
-      <x:c r="B4" s="25" t="str">
+      <x:c r="B4" s="26" t="str">
         <x:v>已打开企业官网、官方招聘页、官方来源公告或国资委页面核验。</x:v>
       </x:c>
-      <x:c r="C4" s="25"/>
-      <x:c r="D4" s="31" t="str">
+      <x:c r="C4" s="26"/>
+      <x:c r="D4" s="32" t="str">
         <x:v>半导体/IC设计</x:v>
       </x:c>
-      <x:c r="E4" s="32" t="n">
+      <x:c r="E4" s="33" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F4"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="25" t="str">
+      <x:c r="A5" s="26" t="str">
         <x:v>B</x:v>
       </x:c>
-      <x:c r="B5" s="25" t="str">
+      <x:c r="B5" s="26" t="str">
         <x:v>来自高校就业网、51job校园或官方来源转载；投递前仍需确认岗位是否静默关闭。</x:v>
       </x:c>
-      <x:c r="C5" s="25"/>
-      <x:c r="D5" s="31" t="str">
+      <x:c r="C5" s="26"/>
+      <x:c r="D5" s="32" t="str">
         <x:v>游戏/互联网</x:v>
       </x:c>
-      <x:c r="E5" s="32" t="n">
+      <x:c r="E5" s="33" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F5"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="25" t="str">
+      <x:c r="A6" s="26" t="str">
         <x:v>C</x:v>
       </x:c>
-      <x:c r="B6" s="25" t="str">
+      <x:c r="B6" s="26" t="str">
         <x:v>来自2026-07-21公开汇总；用于扩大覆盖面，必须通过企业官网二次确认。</x:v>
       </x:c>
-      <x:c r="C6" s="25"/>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="C6" s="26"/>
+      <x:c r="D6" s="32" t="str">
         <x:v>互联网/AI</x:v>
       </x:c>
-      <x:c r="E6" s="32" t="n">
+      <x:c r="E6" s="33" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F6"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="25"/>
-      <x:c r="B7" s="25"/>
-      <x:c r="C7" s="25"/>
-      <x:c r="D7" s="31" t="str">
+      <x:c r="A7" s="26"/>
+      <x:c r="B7" s="26"/>
+      <x:c r="C7" s="26"/>
+      <x:c r="D7" s="32" t="str">
         <x:v>教育科技</x:v>
       </x:c>
-      <x:c r="E7" s="32" t="n">
+      <x:c r="E7" s="33" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="F7"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="28" t="str">
+      <x:c r="A8" s="29" t="str">
         <x:v>重要说明</x:v>
       </x:c>
-      <x:c r="B8" s="28"/>
-      <x:c r="C8" s="25"/>
-      <x:c r="D8" s="31" t="str">
+      <x:c r="B8" s="29"/>
+      <x:c r="C8" s="26"/>
+      <x:c r="D8" s="32" t="str">
         <x:v>管理咨询</x:v>
       </x:c>
-      <x:c r="E8" s="32" t="n">
+      <x:c r="E8" s="33" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F8"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="25" t="str">
+      <x:c r="A9" s="26" t="str">
         <x:v>1. ‘官方未说明’不等于免笔试；只有公告明确写明免笔试/部分免笔试时才作肯定标注。</x:v>
       </x:c>
-      <x:c r="B9" s="25"/>
-      <x:c r="C9" s="25"/>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="B9" s="26"/>
+      <x:c r="C9" s="26"/>
+      <x:c r="D9" s="32" t="str">
         <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
-      <x:c r="E9" s="32" t="n">
+      <x:c r="E9" s="33" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F9"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="25" t="str">
+      <x:c r="A10" s="26" t="str">
         <x:v>2. ‘招满即止’岗位可能没有公开截止日，并可能在无通知的情况下关闭。</x:v>
       </x:c>
-      <x:c r="B10" s="25"/>
-      <x:c r="C10" s="25"/>
-      <x:c r="D10" s="31" t="str">
+      <x:c r="B10" s="26"/>
+      <x:c r="C10" s="26"/>
+      <x:c r="D10" s="32" t="str">
         <x:v>游戏</x:v>
       </x:c>
-      <x:c r="E10" s="32" t="n">
+      <x:c r="E10" s="33" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F10"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="25" t="str">
+      <x:c r="A11" s="26" t="str">
         <x:v>3. 实习转正、训练营、校园大使、博士后/博士专项已在招聘类型和注意事项中单独标明。</x:v>
       </x:c>
-      <x:c r="B11" s="25"/>
-      <x:c r="C11" s="25"/>
-      <x:c r="D11" s="31" t="str">
+      <x:c r="B11" s="26"/>
+      <x:c r="C11" s="26"/>
+      <x:c r="D11" s="32" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="E11" s="33" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="26" t="str">
+        <x:v>4. 当前银行和大型央企正式秋招尚未全面启动，本表不使用上一届时间预测冒充已开放信息。</x:v>
+      </x:c>
+      <x:c r="B12" s="26"/>
+      <x:c r="C12" s="26"/>
+      <x:c r="D12" s="32" t="str">
         <x:v>光电/科研</x:v>
       </x:c>
-      <x:c r="E11" s="32" t="n">
+      <x:c r="E12" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F11"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="25" t="str">
-        <x:v>4. 当前银行和大型央企正式秋招尚未全面启动，本表不使用上一届时间预测冒充已开放信息。</x:v>
-      </x:c>
-      <x:c r="B12" s="25"/>
-      <x:c r="C12" s="25"/>
-      <x:c r="D12" s="31" t="str">
+      <x:c r="F12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="26" t="str">
+        <x:v>5. 工作地点与岗位汇总按项目级归纳，最终以具体职位JD为准。</x:v>
+      </x:c>
+      <x:c r="B13" s="26"/>
+      <x:c r="C13" s="26"/>
+      <x:c r="D13" s="32" t="str">
         <x:v>光学/高端装备</x:v>
       </x:c>
-      <x:c r="E12" s="32" t="n">
+      <x:c r="E13" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F12"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="25" t="str">
-        <x:v>5. 工作地点与岗位汇总按项目级归纳，最终以具体职位JD为准。</x:v>
-      </x:c>
-      <x:c r="B13" s="25"/>
-      <x:c r="C13" s="25"/>
-      <x:c r="D13" s="31" t="str">
+      <x:c r="F13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="26"/>
+      <x:c r="B14" s="26"/>
+      <x:c r="C14" s="26"/>
+      <x:c r="D14" s="32" t="str">
         <x:v>航天/军工</x:v>
       </x:c>
-      <x:c r="E13" s="32" t="n">
+      <x:c r="E14" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F13"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="25"/>
-      <x:c r="B14" s="25"/>
-      <x:c r="C14" s="25"/>
-      <x:c r="D14" s="31" t="str">
+      <x:c r="F14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="26"/>
+      <x:c r="B15" s="26"/>
+      <x:c r="C15" s="26"/>
+      <x:c r="D15" s="32" t="str">
         <x:v>互联网/内容平台</x:v>
       </x:c>
-      <x:c r="E14" s="32" t="n">
+      <x:c r="E15" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F14"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="25"/>
-      <x:c r="B15" s="25"/>
-      <x:c r="C15" s="25"/>
-      <x:c r="D15" s="31" t="str">
+      <x:c r="F15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="29" t="str">
+        <x:v>项目总数</x:v>
+      </x:c>
+      <x:c r="B16" s="29" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C16" s="26"/>
+      <x:c r="D16" s="32" t="str">
+        <x:v>会计审计/专业服务</x:v>
+      </x:c>
+      <x:c r="E16" s="33" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="29" t="str">
+        <x:v>有明确截止时间（未截止）</x:v>
+      </x:c>
+      <x:c r="B17" s="29" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C17" s="26"/>
+      <x:c r="D17" s="32" t="str">
         <x:v>消费电子/智能终端</x:v>
       </x:c>
-      <x:c r="E15" s="32" t="n">
+      <x:c r="E17" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F15"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="28" t="str">
-        <x:v>项目总数</x:v>
-      </x:c>
-      <x:c r="B16" s="28" t="n">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="C16" s="25"/>
-      <x:c r="D16" s="31" t="str">
+      <x:c r="F17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="29" t="str">
+        <x:v>A等级</x:v>
+      </x:c>
+      <x:c r="B18" s="29" t="n">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C18" s="26"/>
+      <x:c r="D18" s="32" t="str">
         <x:v>银行/金融</x:v>
       </x:c>
-      <x:c r="E16" s="32" t="n">
+      <x:c r="E18" s="33" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F16"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="28" t="str">
-        <x:v>有明确截止时间（未截止）</x:v>
-      </x:c>
-      <x:c r="B17" s="28" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C17" s="25"/>
-      <x:c r="D17" s="31" t="str">
-        <x:v>证券/金融</x:v>
-      </x:c>
-      <x:c r="E17" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="F17"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="28" t="str">
-        <x:v>A等级</x:v>
-      </x:c>
-      <x:c r="B18" s="28" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C18" s="25"/>
-      <x:c r="D18" s="31" t="str">
-        <x:v>半导体/模拟混合信号IC</x:v>
-      </x:c>
-      <x:c r="E18" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="F18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="28" t="str">
+      <x:c r="A19" s="29" t="str">
         <x:v>B等级</x:v>
       </x:c>
-      <x:c r="B19" s="28" t="n">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C19" s="25"/>
-      <x:c r="D19" s="31"/>
-      <x:c r="E19" s="32"/>
+      <x:c r="B19" s="29" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C19" s="26"/>
+      <x:c r="D19" s="32"/>
+      <x:c r="E19" s="33"/>
       <x:c r="F19"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="28" t="str">
+      <x:c r="A20" s="29" t="str">
         <x:v>C等级</x:v>
       </x:c>
-      <x:c r="B20" s="28" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C20" s="25"/>
-      <x:c r="D20" s="33"/>
-      <x:c r="E20" s="34"/>
+      <x:c r="B20" s="29" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C20" s="26"/>
+      <x:c r="D20" s="34"/>
+      <x:c r="E20" s="35"/>
       <x:c r="F20"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="25"/>
-      <x:c r="B21" s="25"/>
-      <x:c r="C21" s="25"/>
-      <x:c r="D21" s="25"/>
-      <x:c r="E21" s="25"/>
+      <x:c r="A21" s="26"/>
+      <x:c r="B21" s="26"/>
+      <x:c r="C21" s="26"/>
+      <x:c r="D21" s="26"/>
+      <x:c r="E21" s="26"/>
       <x:c r="F21"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="25" t="str">
+      <x:c r="A22" s="26" t="str">
         <x:v>本次更新</x:v>
       </x:c>
-      <x:c r="B22" s="25" t="str">
-        <x:v>新增8项；关闭0项；未来7天内明确截止1项；新增项目来自企业官方校园招聘页，免笔试政策以公告为准。</x:v>
-      </x:c>
-      <x:c r="C22" s="25"/>
-      <x:c r="D22" s="25"/>
-      <x:c r="E22" s="25"/>
+      <x:c r="B22" s="26" t="str">
+        <x:v>新增5项；关闭0项；未来7天内明确截止3项；新增项目来自企业官方校园招聘页，免笔试政策以公告为准。</x:v>
+      </x:c>
+      <x:c r="C22" s="26"/>
+      <x:c r="D22" s="26"/>
+      <x:c r="E22" s="26"/>
       <x:c r="F22"/>
     </x:row>
   </x:sheetData>

--- a/2027届秋招投递信息_2026-07-24.xlsx
+++ b/2027届秋招投递信息_2026-07-24.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R214d8c2d82f44384"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="R30a06d868c944cf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="Ra75e7e4526774c24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R1b68ac3122b14a4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="Ra31780144de547da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="Rd0a130912a414c59"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -83,12 +83,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE2F0D9"/>
+        <x:fgColor rgb="FFFFF2CC"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF2CC"/>
+        <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -241,7 +241,7 @@
     <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -304,8 +304,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q122" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:Q122"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q131" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:Q131"/>
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="开放投递时间"/>
     <x:tableColumn id="2" name="企业名称"/>
@@ -330,8 +330,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DeadlineProjectsTable" displayName="DeadlineProjectsTable" ref="A3:Q21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:Q21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DeadlineProjectsTable" displayName="DeadlineProjectsTable" ref="A3:Q23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:Q23"/>
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="开放投递时间"/>
     <x:tableColumn id="2" name="企业名称"/>
@@ -571,7 +571,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>2027届秋招投递信息（截至2026-08-07）</x:v>
+        <x:v>2027届秋招投递信息（截至2026-08-10）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -592,7 +592,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>每日更新：按开放时间倒序；本轮新增5项官方核验项目，关闭0项；第三方汇总入口不作为立即投递链接。</x:v>
+        <x:v>每日更新：按开放时间倒序；本轮新增9项官方核验项目，关闭1项；第三方汇总入口不作为立即投递链接。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -666,243 +666,243 @@
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="4" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-08</x:v>
       </x:c>
       <x:c r="B4" s="4" t="str">
-        <x:v>德邦快递</x:v>
+        <x:v>浪潮集团-2027校园招聘提前批</x:v>
       </x:c>
       <x:c r="C4" s="4" t="str">
-        <x:v>物流/快递/供应链</x:v>
+        <x:v>计算机/云计算/企业数字化</x:v>
       </x:c>
       <x:c r="D4" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>国有控股/大型科技企业</x:v>
       </x:c>
       <x:c r="E4" s="4" t="str">
-        <x:v>全国各战区，已核验山东、广东、西北、京津、浙沪等区域岗位</x:v>
+        <x:v>济南、北京、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F4" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G4" s="4" t="str">
-        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
+        <x:v>2027届海内外应届毕业生，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H4" s="4" t="str">
-        <x:v>经营方向、运营方向及总部校园岗位</x:v>
+        <x:v>研发、算法、产品、解决方案、市场营销、供应链及职能类岗位</x:v>
       </x:c>
       <x:c r="I4" s="15" t="str">
-        <x:v>http://zhaopin.deppon.com/campus</x:v>
+        <x:v>https://career.inspur.com/campus2026/campus.html</x:v>
       </x:c>
       <x:c r="J4" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K4" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L4" s="4" t="str">
-        <x:v>本轮新增；官方校园岗位于2026-08-06集中发布</x:v>
+        <x:v>本轮新增；可信高校就业公众号发布浪潮招聘官方来源公告</x:v>
       </x:c>
       <x:c r="M4" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N4" s="4" t="str">
-        <x:v>官网分省区和总部两类入口；经营、运营岗位按战区发布，部分岗位可能随需求提前下线，投递前确认工作省份。</x:v>
+        <x:v>本批次为2027届校园招聘提前批；官方投递站部分网络环境可能访问较慢，建议使用电脑端并留意浪潮招聘公众号通知。</x:v>
       </x:c>
       <x:c r="O4" s="15" t="str">
-        <x:v>http://zhaopin.deppon.com/campus_post?p=3%5E21</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MjM5MTE5MTY4Mw==&amp;mid=2651035581&amp;idx=2&amp;sn=c101807295d1ebe05feff789278a1e26&amp;chksm=bc0437e75efa462c3fcfc23cd62a2a73a1fe1a7dda51d57f38951e02cf466402c565be0261ba&amp;scene=27</x:v>
       </x:c>
       <x:c r="P4" s="14" t="str">
-        <x:v>A-企业官方校园招聘岗位页已核验</x:v>
+        <x:v>B-可信高校就业公众号转载浪潮招聘官方公告</x:v>
       </x:c>
       <x:c r="Q4" s="4" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="4" t="str">
-        <x:v>不晚于2026-08-06</x:v>
+        <x:v>2026-08-08</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>亿联网络</x:v>
+        <x:v>龙湖集团-2027届仕官生</x:v>
       </x:c>
       <x:c r="C5" s="4" t="str">
-        <x:v>通信设备/企业协作/软件</x:v>
+        <x:v>房地产/商业运营/物业服务</x:v>
       </x:c>
       <x:c r="D5" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E5" s="4" t="str">
-        <x:v>厦门为主；国内客户及售前岗位覆盖北京、上海、广州、深圳</x:v>
+        <x:v>全国龙湖业务城市，以岗位页为准</x:v>
       </x:c>
       <x:c r="F5" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>正式批/仕官生校园招聘</x:v>
       </x:c>
       <x:c r="G5" s="4" t="str">
         <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
       </x:c>
       <x:c r="H5" s="4" t="str">
-        <x:v>大模型、图像算法、C/C++、Android、Web前端、SRE、硬件、射频、测试、产品、产品市场、客户经理、售前、技术支持、市场宣传及营销管理</x:v>
+        <x:v>地产开发、商业投资、资产管理、物业服务、智慧营造及职能方向仕官生岗位</x:v>
       </x:c>
       <x:c r="I5" s="15" t="str">
-        <x:v>https://yealink.zhiye.com/campus/jobs</x:v>
+        <x:v>https://longfor.career.gllue.com/</x:v>
       </x:c>
       <x:c r="J5" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K5" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L5" s="4" t="str">
-        <x:v>本轮新增；官方校园招聘页当前开放23个岗位</x:v>
+        <x:v>本轮新增；龙湖集团官网招聘入口与可信高校就业公众号已交叉核验</x:v>
       </x:c>
       <x:c r="M5" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N5" s="4" t="str">
-        <x:v>岗位分批开放，城市与专业要求差异较大；海外岗位通常有外语要求，以每个职位详情页为准。</x:v>
+        <x:v>“仕官生”为龙湖集团校园人才项目；各航道和城市岗位分批开放，申请前在官方系统确认业务板块、工作地点及流程。</x:v>
       </x:c>
       <x:c r="O5" s="15" t="str">
-        <x:v>https://yealink.zhiye.com/campus/jobs</x:v>
-      </x:c>
-      <x:c r="P5" s="14" t="str">
-        <x:v>A-企业官方校园招聘岗位页已核验</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3ODQ3NTIzMA==&amp;mid=2651327326&amp;idx=4&amp;sn=f06e3855d8ec62eeb0ee4fdbba72ff18&amp;chksm=8522803a87a4c7c246f2a7caf72729d4c768262d0d9e0b0c062c28f1423525de5b599f018e99&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P5" s="16" t="str">
+        <x:v>A-集团官网招聘入口与可信高校就业公告交叉核验</x:v>
       </x:c>
       <x:c r="Q5" s="4" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="4" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-08</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>菜鸟-2027应届生招聘</x:v>
+        <x:v>去哪儿旅行-2027校园招聘</x:v>
       </x:c>
       <x:c r="C6" s="4" t="str">
-        <x:v>物流科技/供应链</x:v>
+        <x:v>互联网/在线旅游</x:v>
       </x:c>
       <x:c r="D6" s="4" t="str">
-        <x:v>民营/阿里巴巴业务</x:v>
+        <x:v>民营/在线旅游平台</x:v>
       </x:c>
       <x:c r="E6" s="4" t="str">
-        <x:v>以阿里巴巴校园招聘官网岗位页为准</x:v>
+        <x:v>北京、上海</x:v>
       </x:c>
       <x:c r="F6" s="4" t="str">
-        <x:v>正式批/应届生招聘</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G6" s="4" t="str">
-        <x:v>海内外2027届应届生，毕业时间为2026年11月至2027年10月</x:v>
+        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
       </x:c>
       <x:c r="H6" s="4" t="str">
-        <x:v>算法、研发、产品、运营、数据、物流、职能及销售类</x:v>
+        <x:v>技术类8个岗位、产品类2个岗位、运营类7个岗位</x:v>
       </x:c>
       <x:c r="I6" s="15" t="str">
-        <x:v>https://campus-talent.alibaba.com/</x:v>
+        <x:v>https://hf7l9aiqzx.jobs.feishu.cn/704852</x:v>
       </x:c>
       <x:c r="J6" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K6" s="4" t="str">
-        <x:v>否（技术类岗位参加笔试，新增AI Coding题型）</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L6" s="4" t="str">
-        <x:v>本轮新增；可信高校就业网发布企业招聘海报，阿里巴巴官方校招入口已核验</x:v>
+        <x:v>本轮新增；去哪儿旅行官方校园招聘门户与可信高校就业公众号已交叉核验</x:v>
       </x:c>
       <x:c r="M6" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N6" s="4" t="str">
-        <x:v>进入阿里巴巴集团校招官网后选择27届应届生批次和菜鸟业务，最多选择两个意向岗位；技术类岗位笔试，8月中旬起面试，9月下旬起发放Offer。</x:v>
+        <x:v>官方校招门户当前展示技术、产品、运营三类共17个岗位；岗位可能随招聘进度调整，投递前确认城市和职位状态。</x:v>
       </x:c>
       <x:c r="O6" s="15" t="str">
-        <x:v>https://wtu.91wllm.cn/news/view/aid/300685/tag/xxtz</x:v>
+        <x:v>https://hf7l9aiqzx.jobs.feishu.cn/704852</x:v>
       </x:c>
       <x:c r="P6" s="16" t="str">
-        <x:v>B-可信高校就业网公告含企业官方投递入口</x:v>
+        <x:v>A-企业官方校园招聘门户已核验</x:v>
       </x:c>
       <x:c r="Q6" s="4" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="4" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-08</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>电科芯片吉芯科技</x:v>
+        <x:v>中国东方-2027届校园招聘</x:v>
       </x:c>
       <x:c r="C7" s="4" t="str">
-        <x:v>半导体/模拟混合信号IC</x:v>
+        <x:v>金融资产管理/投资</x:v>
       </x:c>
       <x:c r="D7" s="4" t="str">
-        <x:v>国有控股</x:v>
+        <x:v>中央金融企业/国有</x:v>
       </x:c>
       <x:c r="E7" s="4" t="str">
-        <x:v>重庆</x:v>
+        <x:v>北京及系统内机构所在地，以岗位页为准</x:v>
       </x:c>
       <x:c r="F7" s="4" t="str">
         <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G7" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届毕业生，以公告和岗位要求为准</x:v>
       </x:c>
       <x:c r="H7" s="4" t="str">
-        <x:v>IC设计、IC测试、失效分析、IC应用、产品与质量、调测等岗位</x:v>
+        <x:v>总公司及系统内单位校园招聘岗位，具体方向以官方职位列表为准</x:v>
       </x:c>
       <x:c r="I7" s="15" t="str">
-        <x:v>https://campus.51job.com/jxkj2026/</x:v>
+        <x:v>https://coamc.zhiye.com/</x:v>
       </x:c>
       <x:c r="J7" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K7" s="4" t="str">
-        <x:v>否（官方招聘流程明确包含在线测评）</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L7" s="4" t="str">
-        <x:v>本轮新增；可信高校就业网发布企业招聘海报，官方投递站可访问</x:v>
+        <x:v>本轮新增；中国东方官方招聘门户与可信高校就业公众号已交叉核验</x:v>
       </x:c>
       <x:c r="M7" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N7" s="4" t="str">
-        <x:v>招聘流程为简历投递、简历筛选、在线测评、技术面试、综合面试、Offer发放；投递站路径虽含2026字样，但为本次2027届海报公布的电脑端入口。</x:v>
+        <x:v>投递前确认招聘主体是中国东方资产管理股份有限公司或其系统内单位；具体学历、专业和属地要求以官方职位详情为准。</x:v>
       </x:c>
       <x:c r="O7" s="15" t="str">
-        <x:v>https://wtu.91wllm.cn/news/view/aid/300682/tag/xxtz</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MjM5NzUwNDkwMg==&amp;mid=2676624395&amp;idx=5&amp;sn=7c4208eb1d8b355a0d400bce1c6477c0&amp;chksm=bdd166862695f7f67b0b647b0ae8eb79a37e9e0b4892ec1bb32b0591185be4f69c094097f503&amp;scene=27</x:v>
       </x:c>
       <x:c r="P7" s="16" t="str">
-        <x:v>B-可信高校就业网公告含企业官方投递入口</x:v>
+        <x:v>A-企业官方招聘门户与可信高校就业公告交叉核验</x:v>
       </x:c>
       <x:c r="Q7" s="4" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="4" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>科大讯飞-2027秋季校园招聘</x:v>
+        <x:v>创维集团-2027届全球校园招聘</x:v>
       </x:c>
       <x:c r="C8" s="4" t="str">
-        <x:v>AI/软件/智能语音</x:v>
+        <x:v>智能家电/智能系统/新能源</x:v>
       </x:c>
       <x:c r="D8" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/上市集团</x:v>
       </x:c>
       <x:c r="E8" s="4" t="str">
-        <x:v>合肥、北京、上海、武汉、西安、广州、成都、苏州、石家庄、南京等</x:v>
+        <x:v>深圳、广州、南京、武汉等及海外，以岗位页为准</x:v>
       </x:c>
       <x:c r="F8" s="4" t="str">
-        <x:v>正式批/大型秋季校园招聘</x:v>
+        <x:v>正式批/全球校园招聘</x:v>
       </x:c>
       <x:c r="G8" s="4" t="str">
-        <x:v>毕业时间为2025年6月1日至2027年8月31日的学生（官网原文）</x:v>
+        <x:v>2027届海内外应届毕业生，以岗位详情要求为准</x:v>
       </x:c>
       <x:c r="H8" s="4" t="str">
-        <x:v>研究算法、研发、AI研发、测试、大数据、产品、营销、设计、教育、医学、职能、资源、交付及工程类</x:v>
+        <x:v>技术研发、算法、国内营销、海外营销、小语种、智能制造、供应链及管理类</x:v>
       </x:c>
       <x:c r="I8" s="15" t="str">
-        <x:v>https://iflytek.zhiye.com/campus/jobs?sessionid=</x:v>
+        <x:v>https://skyworth.hotjob.cn/SU668b8b251c240e2e76ea71d8/pb/school.html#/</x:v>
       </x:c>
       <x:c r="J8" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -911,104 +911,104 @@
         <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L8" s="4" t="str">
-        <x:v>本轮新增；与飞凡计划区分，官方常规大型秋季校招项目开放100个岗位</x:v>
+        <x:v>本轮新增；创维集团官方校招门户显示2027届全球校招项目</x:v>
       </x:c>
       <x:c r="M8" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N8" s="4" t="str">
-        <x:v>岗位持续上新；官网当前显示100个职位。正式秋招与库内的飞凡人才专项并行，投递时注意选择“常规大型秋季校园招聘项目-2027届”。</x:v>
+        <x:v>创维集团多家品牌公司联合招聘，岗位覆盖智能家电、智能系统技术、新能源和现代服务业；投递时注意选择具体公司和工作城市。</x:v>
       </x:c>
       <x:c r="O8" s="15" t="str">
-        <x:v>https://wtu.91wllm.cn/news/view/aid/300681/tag/xxtz</x:v>
-      </x:c>
-      <x:c r="P8" s="14" t="str">
-        <x:v>A-企业官方校招页与可信高校就业网公告交叉核验</x:v>
+        <x:v>https://skyworth.hotjob.cn/SU668b8b251c240e2e76ea71d8/pb/index.html#/</x:v>
+      </x:c>
+      <x:c r="P8" s="16" t="str">
+        <x:v>A-企业官方校园招聘门户已核验</x:v>
       </x:c>
       <x:c r="Q8" s="4" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="4" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>不晚于2026-08-06</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>联想集团</x:v>
+        <x:v>阿里巴巴集团-2027届应届生招聘</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
-        <x:v>计算机/消费电子/智能硬件</x:v>
+        <x:v>互联网/电商/云计算/AI</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>北京、上海、天津、成都、南京、武汉、深圳、厦门等，以岗位页为准</x:v>
+        <x:v>北京、杭州、上海、深圳、广州、成都等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F9" s="4" t="str">
-        <x:v>正式批/应届生招聘</x:v>
+        <x:v>正式批/集团统一校园招聘</x:v>
       </x:c>
       <x:c r="G9" s="4" t="str">
-        <x:v>2027届海内外毕业生（中国大陆毕业时间为2026年9月1日至2027年8月31日）</x:v>
+        <x:v>毕业时间为2026年11月至2027年10月的海内外应届生</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>AI开发、软件开发、嵌入式、硬件、产品与项目、设计、市场与销售、供应链及职能岗位</x:v>
+        <x:v>算法、研发、芯片、产品、游戏、运营、商务拓展及其他方向，官方职位页当前显示487个职位</x:v>
       </x:c>
       <x:c r="I9" s="15" t="str">
-        <x:v>https://talent.lenovo.com.cn/campus</x:v>
+        <x:v>https://campus-talent.alibaba.com/campus/position?batchId=100000760001</x:v>
       </x:c>
       <x:c r="J9" s="4" t="str">
-        <x:v>2026-11-13</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K9" s="4" t="str">
-        <x:v>否（官方校招日历含在线测评&amp;技术笔试，简历筛选通过发放笔试通知）</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L9" s="4" t="str">
-        <x:v>本轮新增；联想官方应届生招聘页显示热招中</x:v>
+        <x:v>本轮新增；阿里巴巴官方校招平台显示2027届应届生批次及多业务集团在招</x:v>
       </x:c>
       <x:c r="M9" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N9" s="4" t="str">
-        <x:v>联想官方应届生招聘页当前显示“联想2027应届生招聘”，面向2027届海内外毕业生；网申自2026年8月5日开启，官网公布网申截止2026年11月13日。简历完整度需达到100%才能投递，每个校招项目只能投一个岗位（管培生项目和其他项目可各投一个），部分岗位可能因投递人数较多下线；投递时可选择接受岗位调剂，测评通知以邮件、短信和系统提醒为准。</x:v>
+        <x:v>官方平台可按淘天、淘宝闪购、飞猪、阿里国际、阿里云、平头哥、高德、菜鸟、虎鲸文娱、盒马、阿里健康等业务筛选；岗位持续更新，招满可能提前下架。</x:v>
       </x:c>
       <x:c r="O9" s="15" t="str">
-        <x:v>https://talent.lenovo.com.cn/campus</x:v>
-      </x:c>
-      <x:c r="P9" s="14" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
+        <x:v>https://campus-talent.alibaba.com/campus/position?batchId=100000760001</x:v>
+      </x:c>
+      <x:c r="P9" s="16" t="str">
+        <x:v>A-企业官方校园招聘平台已核验</x:v>
       </x:c>
       <x:c r="Q9" s="4" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="4" t="str">
-        <x:v>不晚于2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
       <x:c r="B10" s="4" t="str">
-        <x:v>泉峰科技-2027校园招聘</x:v>
+        <x:v>德邦快递</x:v>
       </x:c>
       <x:c r="C10" s="4" t="str">
-        <x:v>电动工具/智能制造/消费科技</x:v>
+        <x:v>物流/快递/供应链</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>南京、上海及海外岗位，以职位页为准</x:v>
+        <x:v>全国各战区，已核验山东、广东、西北、京津、浙沪等区域岗位</x:v>
       </x:c>
       <x:c r="F10" s="4" t="str">
         <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>产品研发、工程与制造、质量与供应链、销售与市场、行政与综合管理等30个岗位</x:v>
+        <x:v>经营方向、运营方向及总部校园岗位</x:v>
       </x:c>
       <x:c r="I10" s="15" t="str">
-        <x:v>https://wecruit.hotjob.cn/SU6396cdcc0dcad40b2a419d69/pb/school.html#/</x:v>
+        <x:v>http://zhaopin.deppon.com/campus</x:v>
       </x:c>
       <x:c r="J10" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1017,18 +1017,18 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L10" s="4" t="str">
-        <x:v>本轮新增；官方校园招聘页显示30个在招岗位，多项2027届职位于2026-08-05更新</x:v>
+        <x:v>本轮新增；官方校园岗位于2026-08-06集中发布</x:v>
       </x:c>
       <x:c r="M10" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N10" s="4" t="str">
-        <x:v>本次为当前正式校园招聘岗位，不沿用6月提前批的7月3日截止时间；岗位包含销售与市场管培、算法、BMS、系统研发、产品、海外服务、质量、IT及电机开发等。</x:v>
+        <x:v>官网分省区和总部两类入口；经营、运营岗位按战区发布，部分岗位可能随需求提前下线，投递前确认工作省份。</x:v>
       </x:c>
       <x:c r="O10" s="15" t="str">
-        <x:v>https://wecruit.hotjob.cn/SU6396cdcc0dcad40b2a419d69/pb/school.html#/</x:v>
-      </x:c>
-      <x:c r="P10" s="14" t="str">
+        <x:v>http://zhaopin.deppon.com/campus_post?p=3%5E21</x:v>
+      </x:c>
+      <x:c r="P10" s="16" t="str">
         <x:v>A-企业官方校园招聘岗位页已核验</x:v>
       </x:c>
       <x:c r="Q10" s="4" t="str">
@@ -1037,158 +1037,158 @@
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="4" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
       <x:c r="B11" s="4" t="str">
-        <x:v>淘宝闪购-2027应届生招聘</x:v>
+        <x:v>寒武纪-2027届校园招聘</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
-        <x:v>互联网/本地生活/即时零售</x:v>
+        <x:v>人工智能/芯片/计算平台</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>民营/阿里巴巴业务</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>以阿里巴巴校园招聘官网岗位页为准</x:v>
+        <x:v>北京、上海、深圳、合肥、西安、南京</x:v>
       </x:c>
       <x:c r="F11" s="4" t="str">
-        <x:v>正式批/应届生招聘</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G11" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>毕业时间为2026年9月至2027年8月的高校应届毕业生</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>AI应用研发、AI Infra、安全技术、算法、数据科学、AI视觉与体验设计、AI产品、产品运营、用户运营、商品运营、整合营销、风险策略运营及AI商业分析</x:v>
+        <x:v>芯片类、软件类、职能与研发支持类，共48个在招职位</x:v>
       </x:c>
       <x:c r="I11" s="15" t="str">
-        <x:v>https://campus-talent.alibaba.com/</x:v>
+        <x:v>https://app.mokahr.com/campus_apply/cambricon/44201#/</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K11" s="4" t="str">
-        <x:v>否（算法、工程、AI研发、数据研发、数据科学方向共安排11场笔试）</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L11" s="4" t="str">
-        <x:v>本轮新增；可信高校就业网发布企业招聘海报，阿里巴巴官方校招入口已核验</x:v>
+        <x:v>本轮新增；寒武纪官方校园招聘门户显示2027届校园招聘48个职位</x:v>
       </x:c>
       <x:c r="M11" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N11" s="4" t="str">
-        <x:v>电脑端在阿里巴巴集团校园招聘官网选择淘宝闪购业务；手机端可关注“淘宝闪购招聘”公众号并进入校园招聘。具体岗位以淘宝闪购招聘官网发布为准。</x:v>
+        <x:v>官方门户另有2027届实习生招聘项目，投递正式校招时注意选择“2027届校园招聘”；职位数量和城市以实时页面为准。</x:v>
       </x:c>
       <x:c r="O11" s="15" t="str">
-        <x:v>https://wtu.91wllm.cn/news/view/aid/300684/tag/xxtz</x:v>
+        <x:v>https://app.mokahr.com/campus_apply/cambricon/44201#/</x:v>
       </x:c>
       <x:c r="P11" s="16" t="str">
-        <x:v>B-可信高校就业网公告含企业官方投递方式</x:v>
+        <x:v>A-企业官方校园招聘门户已核验</x:v>
       </x:c>
       <x:c r="Q11" s="4" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="4" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>不晚于2026-08-06</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>德勤-2027秋季校园招聘</x:v>
+        <x:v>亿联网络</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
-        <x:v>会计审计/专业服务</x:v>
+        <x:v>通信设备/企业协作/软件</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>外资/专业服务</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>北京、上海、广州、深圳、重庆等，以岗位页为准</x:v>
+        <x:v>厦门为主；国内客户及售前岗位覆盖北京、上海、广州、深圳</x:v>
       </x:c>
       <x:c r="F12" s="4" t="str">
-        <x:v>正式批/秋季校园招聘</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>2027届应届毕业生；另有2027寒假实习生</x:v>
+        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>审计与鉴证、管理咨询、风险咨询、财务咨询、税务及法律、数字化等</x:v>
+        <x:v>大模型、图像算法、C/C++、Android、Web前端、SRE、硬件、射频、测试、产品、产品市场、客户经理、售前、技术支持、市场宣传及营销管理</x:v>
       </x:c>
       <x:c r="I12" s="15" t="str">
-        <x:v>https://www.deloitte.com/cn/zh/careers.html</x:v>
+        <x:v>https://yealink.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="J12" s="4" t="str">
-        <x:v>2026-10-31（部分岗位招满提前关闭）</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K12" s="4" t="str">
-        <x:v>否（网申后通常安排在线笔试，具体以岗位流程为准）</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L12" s="4" t="str">
-        <x:v>本轮新增；可信高校就业公众号发布德勤2027校招信息，官方招聘入口已核验</x:v>
+        <x:v>本轮新增；官方校园招聘页当前开放23个岗位</x:v>
       </x:c>
       <x:c r="M12" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N12" s="4" t="str">
-        <x:v>秋季全职与寒假实习并行；网申完成后通常收到在线笔试邀请，部分岗位招满会提前结束网申；德勤中国不收取招聘费用，谨防第三方收费。</x:v>
+        <x:v>岗位分批开放，城市与专业要求差异较大；海外岗位通常有外语要求，以每个职位详情页为准。</x:v>
       </x:c>
       <x:c r="O12" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3ODQ3NTIzMA==&amp;mid=2651327099&amp;idx=4&amp;sn=465f2aa047b826709fa081aa25e633f5&amp;chksm=85d23ac1f4759b74460c0c675e988bc8434725c02e7a91d66890eb4795c8000b3dbe9fcf4a48&amp;scene=27</x:v>
+        <x:v>https://yealink.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="P12" s="16" t="str">
-        <x:v>B-可信高校就业公众号公告含德勤官方招聘入口</x:v>
+        <x:v>A-企业官方校园招聘岗位页已核验</x:v>
       </x:c>
       <x:c r="Q12" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="4" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="B13" s="4" t="str">
-        <x:v>德州仪器TI</x:v>
+        <x:v>菜鸟-2027应届生招聘</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
-        <x:v>半导体/模拟与嵌入式芯片</x:v>
+        <x:v>物流科技/供应链</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
-        <x:v>外资/上市</x:v>
+        <x:v>民营/阿里巴巴业务</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>上海及中国区岗位，以职位详情页为准</x:v>
+        <x:v>以阿里巴巴校园招聘官网岗位页为准</x:v>
       </x:c>
       <x:c r="F13" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>正式批/应届生招聘</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
+        <x:v>海内外2027届应届生，毕业时间为2026年11月至2027年10月</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>人力资源培训生、税务专员、会计专员、产品市场工程师（模拟/嵌入式方向）及品牌营销专员</x:v>
+        <x:v>算法、研发、产品、运营、数据、物流、职能及销售类</x:v>
       </x:c>
       <x:c r="I13" s="15" t="str">
-        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
+        <x:v>https://campus-talent.alibaba.com/</x:v>
       </x:c>
       <x:c r="J13" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K13" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否（技术类岗位参加笔试，新增AI Coding题型）</x:v>
       </x:c>
       <x:c r="L13" s="4" t="str">
-        <x:v>本轮新增；官方职位页已发布多项中国区2027校园招聘岗位</x:v>
+        <x:v>本轮新增；可信高校就业网发布企业招聘海报，阿里巴巴官方校招入口已核验</x:v>
       </x:c>
       <x:c r="M13" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N13" s="4" t="str">
-        <x:v>岗位分批发布，当前核验到的2027校招岗位发布日期为2026-08-04；投递前按China地区和岗位关键词筛选。</x:v>
+        <x:v>进入阿里巴巴集团校招官网后选择27届应届生批次和菜鸟业务，最多选择两个意向岗位；技术类岗位笔试，8月中旬起面试，9月下旬起发放Offer。</x:v>
       </x:c>
       <x:c r="O13" s="15" t="str">
-        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
+        <x:v>https://wtu.91wllm.cn/news/view/aid/300685/tag/xxtz</x:v>
       </x:c>
       <x:c r="P13" s="14" t="str">
-        <x:v>A-企业官方职位页已核验</x:v>
+        <x:v>B-可信高校就业网公告含企业官方投递入口</x:v>
       </x:c>
       <x:c r="Q13" s="4" t="str">
         <x:v>2026-08-06</x:v>
@@ -1196,349 +1196,349 @@
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="4" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="B14" s="4" t="str">
-        <x:v>哔哩哔哩-2027秋季校园招聘</x:v>
+        <x:v>电科芯片吉芯科技</x:v>
       </x:c>
       <x:c r="C14" s="4" t="str">
-        <x:v>互联网/内容平台/游戏</x:v>
+        <x:v>半导体/模拟混合信号IC</x:v>
       </x:c>
       <x:c r="D14" s="4" t="str">
+        <x:v>国有控股</x:v>
+      </x:c>
+      <x:c r="E14" s="4" t="str">
+        <x:v>重庆</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="str">
+        <x:v>正式批/校园招聘</x:v>
+      </x:c>
+      <x:c r="G14" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H14" s="4" t="str">
+        <x:v>IC设计、IC测试、失效分析、IC应用、产品与质量、调测等岗位</x:v>
+      </x:c>
+      <x:c r="I14" s="15" t="str">
+        <x:v>https://campus.51job.com/jxkj2026/</x:v>
+      </x:c>
+      <x:c r="J14" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K14" s="4" t="str">
+        <x:v>否（官方招聘流程明确包含在线测评）</x:v>
+      </x:c>
+      <x:c r="L14" s="4" t="str">
+        <x:v>本轮新增；可信高校就业网发布企业招聘海报，官方投递站可访问</x:v>
+      </x:c>
+      <x:c r="M14" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N14" s="4" t="str">
+        <x:v>招聘流程为简历投递、简历筛选、在线测评、技术面试、综合面试、Offer发放；投递站路径虽含2026字样，但为本次2027届海报公布的电脑端入口。</x:v>
+      </x:c>
+      <x:c r="O14" s="15" t="str">
+        <x:v>https://wtu.91wllm.cn/news/view/aid/300682/tag/xxtz</x:v>
+      </x:c>
+      <x:c r="P14" s="14" t="str">
+        <x:v>B-可信高校就业网公告含企业官方投递入口</x:v>
+      </x:c>
+      <x:c r="Q14" s="4" t="str">
+        <x:v>2026-08-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="54" customHeight="1">
+      <x:c r="A15" s="4" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+      <x:c r="B15" s="4" t="str">
+        <x:v>科大讯飞-2027秋季校园招聘</x:v>
+      </x:c>
+      <x:c r="C15" s="4" t="str">
+        <x:v>AI/软件/智能语音</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
-      <x:c r="E14" s="4" t="str">
-        <x:v>上海、北京、广州、深圳、杭州等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F14" s="4" t="str">
-        <x:v>正式批/秋季校园招聘</x:v>
-      </x:c>
-      <x:c r="G14" s="4" t="str">
-        <x:v>毕业时间为2026年9月1日至2027年8月31日的海内外2027届应届生</x:v>
-      </x:c>
-      <x:c r="H14" s="4" t="str">
-        <x:v>技术、产品、运营、市场、设计、职能及游戏等全序列岗位；另有B-UP顶尖技术人才项目</x:v>
-      </x:c>
-      <x:c r="I14" s="15" t="str">
-        <x:v>https://jobs.bilibili.com/campus</x:v>
-      </x:c>
-      <x:c r="J14" s="4" t="str">
-        <x:v>未公布/岗位招满即止</x:v>
-      </x:c>
-      <x:c r="K14" s="4" t="str">
+      <x:c r="E15" s="4" t="str">
+        <x:v>合肥、北京、上海、武汉、西安、广州、成都、苏州、石家庄、南京等</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="str">
+        <x:v>正式批/大型秋季校园招聘</x:v>
+      </x:c>
+      <x:c r="G15" s="4" t="str">
+        <x:v>毕业时间为2025年6月1日至2027年8月31日的学生（官网原文）</x:v>
+      </x:c>
+      <x:c r="H15" s="4" t="str">
+        <x:v>研究算法、研发、AI研发、测试、大数据、产品、营销、设计、教育、医学、职能、资源、交付及工程类</x:v>
+      </x:c>
+      <x:c r="I15" s="15" t="str">
+        <x:v>https://iflytek.zhiye.com/campus/jobs?sessionid=</x:v>
+      </x:c>
+      <x:c r="J15" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K15" s="4" t="str">
         <x:v>官方未统一说明</x:v>
       </x:c>
-      <x:c r="L14" s="4" t="str">
-        <x:v>本轮新增；哔哩哔哩官方校园招聘页显示2027届秋季校园招聘正式启动</x:v>
-      </x:c>
-      <x:c r="M14" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N14" s="4" t="str">
-        <x:v>每位同学最多投递2个志愿，按投递先后认定一、二志愿；可在校招官网投递记录或“哔哩哔哩招聘”公众号查询进度，岗位招满可能提前下架。</x:v>
-      </x:c>
-      <x:c r="O14" s="15" t="str">
-        <x:v>https://jobs.bilibili.com/campus</x:v>
-      </x:c>
-      <x:c r="P14" s="14" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="Q14" s="4" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="54" customHeight="1">
-      <x:c r="A15" s="16" t="str">
-        <x:v>2026-08-03</x:v>
-      </x:c>
-      <x:c r="B15" s="16" t="str">
-        <x:v>中泰证券-2027秋季校园招聘</x:v>
-      </x:c>
-      <x:c r="C15" s="16" t="str">
-        <x:v>证券/金融</x:v>
-      </x:c>
-      <x:c r="D15" s="16" t="str">
-        <x:v>国有控股/上市</x:v>
-      </x:c>
-      <x:c r="E15" s="16" t="str">
-        <x:v>济南、北京、上海、深圳、青岛及全国分支机构</x:v>
-      </x:c>
-      <x:c r="F15" s="16" t="str">
-        <x:v>正式批/秋季校园招聘</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="str">
-        <x:v>2027届高校毕业生（择业期内高校毕业生亦可报名）</x:v>
-      </x:c>
-      <x:c r="H15" s="16" t="str">
-        <x:v>投行、投资、研究、机构、金融科技、总部中后台、分支机构及旗下金融子公司岗位，共86个岗位、拟招227人</x:v>
-      </x:c>
-      <x:c r="I15" s="17" t="str">
-        <x:v>https://zts.hotjob.cn/school.html</x:v>
-      </x:c>
-      <x:c r="J15" s="16" t="str">
-        <x:v>2026-08-16 24:00</x:v>
-      </x:c>
-      <x:c r="K15" s="16" t="str">
-        <x:v>否（招聘程序明确包含笔试、面试）</x:v>
-      </x:c>
-      <x:c r="L15" s="16" t="str">
-        <x:v>本轮新增；山东省国资委公告与中泰证券官方招聘网站已交叉核验</x:v>
-      </x:c>
-      <x:c r="M15" s="16" t="str">
-        <x:v>P1-7天内截止</x:v>
-      </x:c>
-      <x:c r="N15" s="16" t="str">
-        <x:v>母公司业务条线、金融科技和总部中后台多要求硕士及以上，分支机构财富管理类岗位本科可报；统一网上报名，可通过中泰证券官方招聘网站或“中泰证券招聘”官方公众号投递，不收取任何费用。</x:v>
-      </x:c>
-      <x:c r="O15" s="17" t="str">
-        <x:v>https://www.selectshandong.com/recruit/company/833895033675845.html</x:v>
-      </x:c>
-      <x:c r="P15" s="14" t="str">
-        <x:v>A-山东省国资委公告与企业官方招聘网站交叉核验</x:v>
-      </x:c>
-      <x:c r="Q15" s="16" t="str">
-        <x:v>2026-08-07</x:v>
+      <x:c r="L15" s="4" t="str">
+        <x:v>本轮新增；与飞凡计划区分，官方常规大型秋季校招项目开放100个岗位</x:v>
+      </x:c>
+      <x:c r="M15" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N15" s="4" t="str">
+        <x:v>岗位持续上新；官网当前显示100个职位。正式秋招与库内的飞凡人才专项并行，投递时注意选择“常规大型秋季校园招聘项目-2027届”。</x:v>
+      </x:c>
+      <x:c r="O15" s="15" t="str">
+        <x:v>https://wtu.91wllm.cn/news/view/aid/300681/tag/xxtz</x:v>
+      </x:c>
+      <x:c r="P15" s="16" t="str">
+        <x:v>A-企业官方校招页与可信高校就业网公告交叉核验</x:v>
+      </x:c>
+      <x:c r="Q15" s="4" t="str">
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="4" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
-        <x:v>字节跳动-2027校园招聘</x:v>
+        <x:v>联想集团</x:v>
       </x:c>
       <x:c r="C16" s="4" t="str">
-        <x:v>互联网/AI/内容平台</x:v>
+        <x:v>计算机/消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>北京、上海、深圳、杭州等，具体以岗位页为准</x:v>
+        <x:v>北京、上海、天津、成都、南京、武汉、深圳、厦门等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F16" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>正式批/应届生招聘</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>毕业时间为2026年9月至2027年8月的应届生</x:v>
+        <x:v>2027届海内外毕业生（中国大陆毕业时间为2026年9月1日至2027年8月31日）</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>研发、产品、运营、设计、市场、职能/支持、销售、游戏策划八大类；新增AI全栈工程师、AI Agent开发等方向</x:v>
+        <x:v>AI开发、软件开发、嵌入式、硬件、产品与项目、设计、市场与销售、供应链及职能岗位</x:v>
       </x:c>
       <x:c r="I16" s="15" t="str">
-        <x:v>https://jobs.bytedance.com/campus/</x:v>
+        <x:v>https://talent.lenovo.com.cn/campus</x:v>
       </x:c>
       <x:c r="J16" s="4" t="str">
-        <x:v>2026-12-31（岗位招满可能提前下架）</x:v>
+        <x:v>2026-11-13</x:v>
       </x:c>
       <x:c r="K16" s="4" t="str">
-        <x:v>官方未统一说明</x:v>
+        <x:v>否（官方校招日历含在线测评&amp;技术笔试，简历筛选通过发放笔试通知）</x:v>
       </x:c>
       <x:c r="L16" s="4" t="str">
-        <x:v>本轮新增；字节跳动官方校园招聘入口已核验，2027届校招于2026-08-03启动</x:v>
+        <x:v>本轮新增；联想官方应届生招聘页显示热招中</x:v>
       </x:c>
       <x:c r="M16" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N16" s="4" t="str">
-        <x:v>普通校招投递机会按阶段刷新：2026-08-03至2026-12-31有两次机会，2027-01-01刷新两次；岗位招满会下架。AI产品早鸟通道、前沿技术人才校招、Seed大模型人才校招等专项不占用普通投递机会。</x:v>
+        <x:v>联想官方应届生招聘页当前显示“联想2027应届生招聘”，面向2027届海内外毕业生；网申自2026年8月5日开启，官网公布网申截止2026年11月13日。简历完整度需达到100%才能投递，每个校招项目只能投一个岗位（管培生项目和其他项目可各投一个），部分岗位可能因投递人数较多下线；投递时可选择接受岗位调剂，测评通知以邮件、短信和系统提醒为准。</x:v>
       </x:c>
       <x:c r="O16" s="15" t="str">
-        <x:v>https://jobs.bytedance.com/campus/</x:v>
-      </x:c>
-      <x:c r="P16" s="14" t="str">
-        <x:v>A-企业官方校园招聘入口已核验</x:v>
+        <x:v>https://talent.lenovo.com.cn/campus</x:v>
+      </x:c>
+      <x:c r="P16" s="16" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="Q16" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="4" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>不晚于2026-08-05</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>影石Insta360</x:v>
+        <x:v>泉峰科技-2027校园招聘</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
-        <x:v>消费电子/智能影像</x:v>
+        <x:v>电动工具/智能制造/消费科技</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>深圳、上海、珠海</x:v>
+        <x:v>南京、上海及海外岗位，以职位页为准</x:v>
       </x:c>
       <x:c r="F17" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+        <x:v>产品研发、工程与制造、质量与供应链、销售与市场、行政与综合管理等30个岗位</x:v>
       </x:c>
       <x:c r="I17" s="15" t="str">
-        <x:v>https://www.insta360.com/cn/jobs</x:v>
+        <x:v>https://wecruit.hotjob.cn/SU6396cdcc0dcad40b2a419d69/pb/school.html#/</x:v>
       </x:c>
       <x:c r="J17" s="4" t="str">
-        <x:v>2026-10-31</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K17" s="4" t="str">
-        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L17" s="4" t="str">
-        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
+        <x:v>本轮新增；官方校园招聘页显示30个在招岗位，多项2027届职位于2026-08-05更新</x:v>
       </x:c>
       <x:c r="M17" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N17" s="4" t="str">
-        <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
+        <x:v>本次为当前正式校园招聘岗位，不沿用6月提前批的7月3日截止时间；岗位包含销售与市场管培、算法、BMS、系统研发、产品、海外服务、质量、IT及电机开发等。</x:v>
       </x:c>
       <x:c r="O17" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P17" s="14" t="str">
-        <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
+        <x:v>https://wecruit.hotjob.cn/SU6396cdcc0dcad40b2a419d69/pb/school.html#/</x:v>
+      </x:c>
+      <x:c r="P17" s="16" t="str">
+        <x:v>A-企业官方校园招聘岗位页已核验</x:v>
       </x:c>
       <x:c r="Q17" s="4" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
-      <x:c r="A18" s="18" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B18" s="18" t="str">
-        <x:v>恒丰银行总行-雏鹰计划</x:v>
-      </x:c>
-      <x:c r="C18" s="18" t="str">
-        <x:v>银行/金融</x:v>
-      </x:c>
-      <x:c r="D18" s="18" t="str">
-        <x:v>股份制商业银行</x:v>
-      </x:c>
-      <x:c r="E18" s="18" t="str">
-        <x:v>总行及相关机构，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F18" s="18" t="str">
-        <x:v>暑期实习/秋招储备</x:v>
-      </x:c>
-      <x:c r="G18" s="18" t="str">
-        <x:v>2027届硕士及以上，以公告要求为准</x:v>
-      </x:c>
-      <x:c r="H18" s="18" t="str">
-        <x:v>总行实习生，具体专业和方向以官方公告为准</x:v>
-      </x:c>
-      <x:c r="I18" s="19" t="str">
-        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
-      </x:c>
-      <x:c r="J18" s="18" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K18" s="18" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L18" s="18" t="str">
-        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M18" s="18" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N18" s="18" t="str">
-        <x:v>官方公告显示7月31日24:00截止，实习期安排和具体岗位以恒丰银行招聘官网为准。</x:v>
-      </x:c>
-      <x:c r="O18" s="19" t="str">
-        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
+      <x:c r="A18" s="4" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+      <x:c r="B18" s="4" t="str">
+        <x:v>淘宝闪购-2027应届生招聘</x:v>
+      </x:c>
+      <x:c r="C18" s="4" t="str">
+        <x:v>互联网/本地生活/即时零售</x:v>
+      </x:c>
+      <x:c r="D18" s="4" t="str">
+        <x:v>民营/阿里巴巴业务</x:v>
+      </x:c>
+      <x:c r="E18" s="4" t="str">
+        <x:v>以阿里巴巴校园招聘官网岗位页为准</x:v>
+      </x:c>
+      <x:c r="F18" s="4" t="str">
+        <x:v>正式批/应届生招聘</x:v>
+      </x:c>
+      <x:c r="G18" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H18" s="4" t="str">
+        <x:v>AI应用研发、AI Infra、安全技术、算法、数据科学、AI视觉与体验设计、AI产品、产品运营、用户运营、商品运营、整合营销、风险策略运营及AI商业分析</x:v>
+      </x:c>
+      <x:c r="I18" s="15" t="str">
+        <x:v>https://campus-talent.alibaba.com/</x:v>
+      </x:c>
+      <x:c r="J18" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K18" s="4" t="str">
+        <x:v>否（算法、工程、AI研发、数据研发、数据科学方向共安排11场笔试）</x:v>
+      </x:c>
+      <x:c r="L18" s="4" t="str">
+        <x:v>本轮新增；可信高校就业网发布企业招聘海报，阿里巴巴官方校招入口已核验</x:v>
+      </x:c>
+      <x:c r="M18" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N18" s="4" t="str">
+        <x:v>电脑端在阿里巴巴集团校园招聘官网选择淘宝闪购业务；手机端可关注“淘宝闪购招聘”公众号并进入校园招聘。具体岗位以淘宝闪购招聘官网发布为准。</x:v>
+      </x:c>
+      <x:c r="O18" s="15" t="str">
+        <x:v>https://wtu.91wllm.cn/news/view/aid/300684/tag/xxtz</x:v>
       </x:c>
       <x:c r="P18" s="14" t="str">
-        <x:v>A-企业官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q18" s="18" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>B-可信高校就业网公告含企业官方投递方式</x:v>
+      </x:c>
+      <x:c r="Q18" s="4" t="str">
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>四方股份</x:v>
+        <x:v>德勤-2027秋季校园招聘</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>电力系统/工业自动化</x:v>
+        <x:v>会计审计/专业服务</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>外资/专业服务</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
+        <x:v>北京、上海、广州、深圳、重庆等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届毕业生；另有2027寒假实习生</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
+        <x:v>审计与鉴证、管理咨询、风险咨询、财务咨询、税务及法律、数字化等</x:v>
       </x:c>
       <x:c r="I19" s="15" t="str">
-        <x:v>https://www.sf-auto.com/campus</x:v>
+        <x:v>https://www.deloitte.com/cn/zh/careers.html</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-31（部分岗位招满提前关闭）</x:v>
       </x:c>
       <x:c r="K19" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否（网申后通常安排在线笔试，具体以岗位流程为准）</x:v>
       </x:c>
       <x:c r="L19" s="4" t="str">
-        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
+        <x:v>本轮新增；可信高校就业公众号发布德勤2027校招信息，官方招聘入口已核验</x:v>
       </x:c>
       <x:c r="M19" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N19" s="4" t="str">
-        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
+        <x:v>秋季全职与寒假实习并行；网申完成后通常收到在线笔试邀请，部分岗位招满会提前结束网申；德勤中国不收取招聘费用，谨防第三方收费。</x:v>
       </x:c>
       <x:c r="O19" s="15" t="str">
-        <x:v>https://www.sf-auto.com/campus</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3ODQ3NTIzMA==&amp;mid=2651327099&amp;idx=4&amp;sn=465f2aa047b826709fa081aa25e633f5&amp;chksm=85d23ac1f4759b74460c0c675e988bc8434725c02e7a91d66890eb4795c8000b3dbe9fcf4a48&amp;scene=27</x:v>
       </x:c>
       <x:c r="P19" s="14" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
+        <x:v>B-可信高校就业公众号公告含德勤官方招聘入口</x:v>
       </x:c>
       <x:c r="Q19" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
-        <x:v>苏纳光电</x:v>
+        <x:v>德州仪器TI</x:v>
       </x:c>
       <x:c r="C20" s="4" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>半导体/模拟与嵌入式芯片</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>外资/上市</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>苏州、上海</x:v>
+        <x:v>上海及中国区岗位，以职位详情页为准</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>提前批/Open Day</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
+        <x:v>人力资源培训生、税务专员、会计专员、产品市场工程师（模拟/嵌入式方向）及品牌营销专员</x:v>
       </x:c>
       <x:c r="I20" s="15" t="str">
-        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1547,287 +1547,287 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L20" s="4" t="str">
-        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
+        <x:v>本轮新增；官方职位页已发布多项中国区2027校园招聘岗位</x:v>
       </x:c>
       <x:c r="M20" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N20" s="4" t="str">
-        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
+        <x:v>岗位分批发布，当前核验到的2027校招岗位发布日期为2026-08-04；投递前按China地区和岗位关键词筛选。</x:v>
       </x:c>
       <x:c r="O20" s="15" t="str">
-        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
-      </x:c>
-      <x:c r="P20" s="14" t="str">
-        <x:v>A-企业官方校园招聘系统已核验</x:v>
+        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
+      </x:c>
+      <x:c r="P20" s="16" t="str">
+        <x:v>A-企业官方职位页已核验</x:v>
       </x:c>
       <x:c r="Q20" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
       <x:c r="B21" s="4" t="str">
-        <x:v>特斯拉中国</x:v>
+        <x:v>哔哩哔哩-2027秋季校园招聘</x:v>
       </x:c>
       <x:c r="C21" s="4" t="str">
-        <x:v>新能源汽车/智能制造</x:v>
+        <x:v>互联网/内容平台/游戏</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>外资/上市</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
+        <x:v>上海、北京、广州、深圳、杭州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F21" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
+        <x:v>毕业时间为2026年9月1日至2027年8月31日的海内外2027届应届生</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
+        <x:v>技术、产品、运营、市场、设计、职能及游戏等全序列岗位；另有B-UP顶尖技术人才项目</x:v>
       </x:c>
       <x:c r="I21" s="15" t="str">
-        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
+        <x:v>https://jobs.bilibili.com/campus</x:v>
       </x:c>
       <x:c r="J21" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>未公布/岗位招满即止</x:v>
       </x:c>
       <x:c r="K21" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L21" s="4" t="str">
-        <x:v>本轮新确认；企业官方职位页已核验</x:v>
+        <x:v>本轮新增；哔哩哔哩官方校园招聘页显示2027届秋季校园招聘正式启动</x:v>
       </x:c>
       <x:c r="M21" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N21" s="4" t="str">
-        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
+        <x:v>每位同学最多投递2个志愿，按投递先后认定一、二志愿；可在校招官网投递记录或“哔哩哔哩招聘”公众号查询进度，岗位招满可能提前下架。</x:v>
       </x:c>
       <x:c r="O21" s="15" t="str">
-        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
-      </x:c>
-      <x:c r="P21" s="14" t="str">
-        <x:v>A-企业官方职位页已核验</x:v>
+        <x:v>https://jobs.bilibili.com/campus</x:v>
+      </x:c>
+      <x:c r="P21" s="16" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="Q21" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
-      <x:c r="A22" s="18" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B22" s="18" t="str">
-        <x:v>天健会计师事务所-暑期实习培训生</x:v>
-      </x:c>
-      <x:c r="C22" s="18" t="str">
-        <x:v>会计审计/专业服务</x:v>
-      </x:c>
-      <x:c r="D22" s="18" t="str">
-        <x:v>会计师事务所</x:v>
-      </x:c>
-      <x:c r="E22" s="18" t="str">
-        <x:v>上海等，以职位页为准</x:v>
-      </x:c>
-      <x:c r="F22" s="18" t="str">
-        <x:v>暑期实习/培训生</x:v>
-      </x:c>
-      <x:c r="G22" s="18" t="str">
-        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H22" s="18" t="str">
-        <x:v>财务审计暑期实习培训生</x:v>
-      </x:c>
-      <x:c r="I22" s="19" t="str">
-        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
-      </x:c>
-      <x:c r="J22" s="18" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K22" s="18" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L22" s="18" t="str">
-        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M22" s="18" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N22" s="18" t="str">
-        <x:v>公开公告显示7月31日截止；具体办公地点、专业要求和实习安排以天健招聘官网为准。</x:v>
-      </x:c>
-      <x:c r="O22" s="19" t="str">
-        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
-      </x:c>
-      <x:c r="P22" s="14" t="str">
-        <x:v>A-企业官方招聘入口已核验</x:v>
-      </x:c>
-      <x:c r="Q22" s="18" t="str">
+      <x:c r="A22" s="14" t="str">
         <x:v>2026-08-03</x:v>
+      </x:c>
+      <x:c r="B22" s="14" t="str">
+        <x:v>中泰证券-2027秋季校园招聘</x:v>
+      </x:c>
+      <x:c r="C22" s="14" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="D22" s="14" t="str">
+        <x:v>国有控股/上市</x:v>
+      </x:c>
+      <x:c r="E22" s="14" t="str">
+        <x:v>济南、北京、上海、深圳、青岛及全国分支机构</x:v>
+      </x:c>
+      <x:c r="F22" s="14" t="str">
+        <x:v>正式批/秋季校园招聘</x:v>
+      </x:c>
+      <x:c r="G22" s="14" t="str">
+        <x:v>2027届高校毕业生（择业期内高校毕业生亦可报名）</x:v>
+      </x:c>
+      <x:c r="H22" s="14" t="str">
+        <x:v>投行、投资、研究、机构、金融科技、总部中后台、分支机构及旗下金融子公司岗位，共86个岗位、拟招227人</x:v>
+      </x:c>
+      <x:c r="I22" s="17" t="str">
+        <x:v>https://zts.hotjob.cn/school.html</x:v>
+      </x:c>
+      <x:c r="J22" s="14" t="str">
+        <x:v>2026-08-16 24:00</x:v>
+      </x:c>
+      <x:c r="K22" s="14" t="str">
+        <x:v>否（招聘程序明确包含笔试、面试）</x:v>
+      </x:c>
+      <x:c r="L22" s="14" t="str">
+        <x:v>本轮新增；山东省国资委公告与中泰证券官方招聘网站已交叉核验</x:v>
+      </x:c>
+      <x:c r="M22" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N22" s="14" t="str">
+        <x:v>母公司业务条线、金融科技和总部中后台多要求硕士及以上，分支机构财富管理类岗位本科可报；统一网上报名，可通过中泰证券官方招聘网站或“中泰证券招聘”官方公众号投递，不收取任何费用。</x:v>
+      </x:c>
+      <x:c r="O22" s="17" t="str">
+        <x:v>https://www.selectshandong.com/recruit/company/833895033675845.html</x:v>
+      </x:c>
+      <x:c r="P22" s="16" t="str">
+        <x:v>A-山东省国资委公告与企业官方招聘网站交叉核验</x:v>
+      </x:c>
+      <x:c r="Q22" s="14" t="str">
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
       <x:c r="B23" s="4" t="str">
-        <x:v>西安紫光国芯半导体</x:v>
+        <x:v>字节跳动-2027校园招聘</x:v>
       </x:c>
       <x:c r="C23" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>互联网/AI/内容平台</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>西安、上海、成都</x:v>
+        <x:v>北京、上海、深圳、杭州等，具体以岗位页为准</x:v>
       </x:c>
       <x:c r="F23" s="4" t="str">
         <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
-        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
+        <x:v>毕业时间为2026年9月至2027年8月的应届生</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
+        <x:v>研发、产品、运营、设计、市场、职能/支持、销售、游戏策划八大类；新增AI全栈工程师、AI Agent开发等方向</x:v>
       </x:c>
       <x:c r="I23" s="15" t="str">
-        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
       </x:c>
       <x:c r="J23" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-12-31（岗位招满可能提前下架）</x:v>
       </x:c>
       <x:c r="K23" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L23" s="4" t="str">
-        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
+        <x:v>本轮新增；字节跳动官方校园招聘入口已核验，2027届校招于2026-08-03启动</x:v>
       </x:c>
       <x:c r="M23" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N23" s="4" t="str">
-        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
+        <x:v>普通校招投递机会按阶段刷新：2026-08-03至2026-12-31有两次机会，2027-01-01刷新两次；岗位招满会下架。AI产品早鸟通道、前沿技术人才校招、Seed大模型人才校招等专项不占用普通投递机会。</x:v>
       </x:c>
       <x:c r="O23" s="15" t="str">
-        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
-      </x:c>
-      <x:c r="P23" s="14" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
+      </x:c>
+      <x:c r="P23" s="16" t="str">
+        <x:v>A-企业官方校园招聘入口已核验</x:v>
       </x:c>
       <x:c r="Q23" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="4" t="str">
+        <x:v>2026-08-01</x:v>
+      </x:c>
+      <x:c r="B24" s="4" t="str">
+        <x:v>影石Insta360</x:v>
+      </x:c>
+      <x:c r="C24" s="4" t="str">
+        <x:v>消费电子/智能影像</x:v>
+      </x:c>
+      <x:c r="D24" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E24" s="4" t="str">
+        <x:v>深圳、上海、珠海</x:v>
+      </x:c>
+      <x:c r="F24" s="4" t="str">
+        <x:v>正式批/秋招</x:v>
+      </x:c>
+      <x:c r="G24" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H24" s="4" t="str">
+        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+      </x:c>
+      <x:c r="I24" s="15" t="str">
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
+      </x:c>
+      <x:c r="J24" s="4" t="str">
+        <x:v>2026-10-31</x:v>
+      </x:c>
+      <x:c r="K24" s="4" t="str">
+        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
+      </x:c>
+      <x:c r="L24" s="4" t="str">
+        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
+      </x:c>
+      <x:c r="M24" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N24" s="4" t="str">
+        <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
+      </x:c>
+      <x:c r="O24" s="15" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P24" s="16" t="str">
+        <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
+      </x:c>
+      <x:c r="Q24" s="4" t="str">
+        <x:v>2026-08-04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="54" customHeight="1">
+      <x:c r="A25" s="18" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
-      <x:c r="B24" s="4" t="str">
-        <x:v>新大陆自动识别</x:v>
-      </x:c>
-      <x:c r="C24" s="4" t="str">
-        <x:v>计算机视觉/智能硬件</x:v>
-      </x:c>
-      <x:c r="D24" s="4" t="str">
-        <x:v>民营/上市公司子公司</x:v>
-      </x:c>
-      <x:c r="E24" s="4" t="str">
-        <x:v>福州总部及全国/海外岗位</x:v>
-      </x:c>
-      <x:c r="F24" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
-      </x:c>
-      <x:c r="G24" s="4" t="str">
-        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
-      </x:c>
-      <x:c r="H24" s="4" t="str">
-        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
-      </x:c>
-      <x:c r="I24" s="15" t="str">
-        <x:v>https://nlscan.zhiye.com/Campus</x:v>
-      </x:c>
-      <x:c r="J24" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K24" s="4" t="str">
+      <x:c r="B25" s="18" t="str">
+        <x:v>恒丰银行总行-雏鹰计划</x:v>
+      </x:c>
+      <x:c r="C25" s="18" t="str">
+        <x:v>银行/金融</x:v>
+      </x:c>
+      <x:c r="D25" s="18" t="str">
+        <x:v>股份制商业银行</x:v>
+      </x:c>
+      <x:c r="E25" s="18" t="str">
+        <x:v>总行及相关机构，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F25" s="18" t="str">
+        <x:v>暑期实习/秋招储备</x:v>
+      </x:c>
+      <x:c r="G25" s="18" t="str">
+        <x:v>2027届硕士及以上，以公告要求为准</x:v>
+      </x:c>
+      <x:c r="H25" s="18" t="str">
+        <x:v>总行实习生，具体专业和方向以官方公告为准</x:v>
+      </x:c>
+      <x:c r="I25" s="19" t="str">
+        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K25" s="18" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
-      <x:c r="L24" s="4" t="str">
-        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
-      </x:c>
-      <x:c r="M24" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N24" s="4" t="str">
-        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
-      </x:c>
-      <x:c r="O24" s="15" t="str">
-        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
-      </x:c>
-      <x:c r="P24" s="14" t="str">
-        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
-      </x:c>
-      <x:c r="Q24" s="4" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="54" customHeight="1">
-      <x:c r="A25" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B25" s="4" t="str">
-        <x:v>兆易创新</x:v>
-      </x:c>
-      <x:c r="C25" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
-      </x:c>
-      <x:c r="D25" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E25" s="4" t="str">
-        <x:v>北京、上海、武汉、合肥等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F25" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G25" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H25" s="4" t="str">
-        <x:v>芯片设计、验证、嵌入式、软件、应用、测试及职能岗位</x:v>
-      </x:c>
-      <x:c r="I25" s="15" t="str">
-        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
-      </x:c>
-      <x:c r="J25" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K25" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L25" s="4" t="str">
-        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
-      </x:c>
-      <x:c r="M25" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N25" s="4" t="str">
-        <x:v>提前批岗位和城市以兆易创新官方加入我们页面为准，投递前确认职位仍开放。</x:v>
-      </x:c>
-      <x:c r="O25" s="15" t="str">
-        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
-      </x:c>
-      <x:c r="P25" s="14" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
-      </x:c>
-      <x:c r="Q25" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+      <x:c r="L25" s="18" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M25" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N25" s="18" t="str">
+        <x:v>官方公告显示7月31日24:00截止，实习期安排和具体岗位以恒丰银行招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O25" s="19" t="str">
+        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
+      </x:c>
+      <x:c r="P25" s="16" t="str">
+        <x:v>A-企业官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q25" s="18" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="54" customHeight="1">
@@ -1835,28 +1835,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B26" s="4" t="str">
-        <x:v>中国航空发动机集团</x:v>
+        <x:v>四方股份</x:v>
       </x:c>
       <x:c r="C26" s="4" t="str">
-        <x:v>航空发动机/军工</x:v>
+        <x:v>电力系统/工业自动化</x:v>
       </x:c>
       <x:c r="D26" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E26" s="4" t="str">
-        <x:v>全国各院所及下属单位</x:v>
+        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
       </x:c>
       <x:c r="F26" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G26" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H26" s="4" t="str">
-        <x:v>研发设计、工艺、试验、制造、材料、控制、软件及管理岗位</x:v>
+        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
       </x:c>
       <x:c r="I26" s="15" t="str">
-        <x:v>https://aecc.iguopin.com/notice2</x:v>
+        <x:v>https://www.sf-auto.com/campus</x:v>
       </x:c>
       <x:c r="J26" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1865,22 +1865,22 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L26" s="4" t="str">
-        <x:v>本轮复核；中国航发官方招聘平台当前显示2027届校园招聘岗位持续开放</x:v>
+        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="M26" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N26" s="4" t="str">
-        <x:v>各单位岗位和截止时间不同，需在中国航发招聘平台按单位和专业筛选；本次复核到159家招聘单位及多项研发、工艺、制造、控制和软件岗位。</x:v>
+        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
       </x:c>
       <x:c r="O26" s="15" t="str">
-        <x:v>https://aecc.iguopin.com/job</x:v>
-      </x:c>
-      <x:c r="P26" s="14" t="str">
-        <x:v>A-中国航发官方招聘平台已核验</x:v>
+        <x:v>https://www.sf-auto.com/campus</x:v>
+      </x:c>
+      <x:c r="P26" s="16" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="Q26" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="54" customHeight="1">
@@ -1888,28 +1888,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B27" s="4" t="str">
-        <x:v>中粮资本-粮曦计划</x:v>
+        <x:v>苏纳光电</x:v>
       </x:c>
       <x:c r="C27" s="4" t="str">
-        <x:v>金融/投资/资管</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D27" s="4" t="str">
-        <x:v>央企/金融控股</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E27" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>苏州、上海</x:v>
       </x:c>
       <x:c r="F27" s="4" t="str">
-        <x:v>培养计划/实习</x:v>
+        <x:v>提前批/Open Day</x:v>
       </x:c>
       <x:c r="G27" s="4" t="str">
-        <x:v>2027-2029届硕士及以上，以公告要求为准</x:v>
+        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H27" s="4" t="str">
-        <x:v>金融、投资、风险、运营、人力资源及综合管理方向</x:v>
+        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
       </x:c>
       <x:c r="I27" s="15" t="str">
-        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="J27" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1918,19 +1918,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L27" s="4" t="str">
-        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
+        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
       </x:c>
       <x:c r="M27" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N27" s="4" t="str">
-        <x:v>粮曦计划具体批次、面向人群和岗位以中粮资本官方加入我们页面及公告为准。</x:v>
+        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
       </x:c>
       <x:c r="O27" s="15" t="str">
-        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
-      </x:c>
-      <x:c r="P27" s="14" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+      </x:c>
+      <x:c r="P27" s="16" t="str">
+        <x:v>A-企业官方校园招聘系统已核验</x:v>
       </x:c>
       <x:c r="Q27" s="4" t="str">
         <x:v>2026-07-31</x:v>
@@ -1941,187 +1941,187 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B28" s="4" t="str">
-        <x:v>中移九天人工智能科技</x:v>
+        <x:v>特斯拉中国</x:v>
       </x:c>
       <x:c r="C28" s="4" t="str">
-        <x:v>AI/软件/云计算</x:v>
+        <x:v>新能源汽车/智能制造</x:v>
       </x:c>
       <x:c r="D28" s="4" t="str">
-        <x:v>央企子公司</x:v>
+        <x:v>外资/上市</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>北京、西安、广州、深圳</x:v>
+        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
       </x:c>
       <x:c r="F28" s="4" t="str">
-        <x:v>正式批/超级实习生</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
+        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
       </x:c>
       <x:c r="I28" s="15" t="str">
-        <x:v>https://job.10086.cn/personal/campus/</x:v>
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
       </x:c>
       <x:c r="J28" s="4" t="str">
-        <x:v>2026-09-27</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K28" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L28" s="4" t="str">
-        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
+        <x:v>本轮新确认；企业官方职位页已核验</x:v>
       </x:c>
       <x:c r="M28" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N28" s="4" t="str">
-        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
+        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
       </x:c>
       <x:c r="O28" s="15" t="str">
-        <x:v>https://job.10086.cn/personal/campus/</x:v>
-      </x:c>
-      <x:c r="P28" s="14" t="str">
-        <x:v>A-中国移动官方招聘平台已核验</x:v>
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
+      </x:c>
+      <x:c r="P28" s="16" t="str">
+        <x:v>A-企业官方职位页已核验</x:v>
       </x:c>
       <x:c r="Q28" s="4" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="54" customHeight="1">
-      <x:c r="A29" s="4" t="str">
-        <x:v>2026-07-28</x:v>
-      </x:c>
-      <x:c r="B29" s="4" t="str">
-        <x:v>广州市卓越教育集团</x:v>
-      </x:c>
-      <x:c r="C29" s="4" t="str">
-        <x:v>教育科技</x:v>
-      </x:c>
-      <x:c r="D29" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E29" s="4" t="str">
-        <x:v>广州等，以职位页为准</x:v>
-      </x:c>
-      <x:c r="F29" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G29" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H29" s="4" t="str">
-        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
-      </x:c>
-      <x:c r="I29" s="15" t="str">
-        <x:v>https://zyjob.hotjob.cn/</x:v>
-      </x:c>
-      <x:c r="J29" s="4" t="str">
-        <x:v>2026-10-26</x:v>
-      </x:c>
-      <x:c r="K29" s="4" t="str">
+      <x:c r="A29" s="18" t="str">
+        <x:v>不晚于2026-07-30</x:v>
+      </x:c>
+      <x:c r="B29" s="18" t="str">
+        <x:v>天健会计师事务所-暑期实习培训生</x:v>
+      </x:c>
+      <x:c r="C29" s="18" t="str">
+        <x:v>会计审计/专业服务</x:v>
+      </x:c>
+      <x:c r="D29" s="18" t="str">
+        <x:v>会计师事务所</x:v>
+      </x:c>
+      <x:c r="E29" s="18" t="str">
+        <x:v>上海等，以职位页为准</x:v>
+      </x:c>
+      <x:c r="F29" s="18" t="str">
+        <x:v>暑期实习/培训生</x:v>
+      </x:c>
+      <x:c r="G29" s="18" t="str">
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H29" s="18" t="str">
+        <x:v>财务审计暑期实习培训生</x:v>
+      </x:c>
+      <x:c r="I29" s="19" t="str">
+        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
+      </x:c>
+      <x:c r="J29" s="18" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K29" s="18" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
-      <x:c r="L29" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
-      </x:c>
-      <x:c r="M29" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
-      </x:c>
-      <x:c r="N29" s="4" t="str">
-        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
-      </x:c>
-      <x:c r="O29" s="15" t="str">
-        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
-      </x:c>
-      <x:c r="P29" s="14" t="str">
-        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
-      </x:c>
-      <x:c r="Q29" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+      <x:c r="L29" s="18" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M29" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N29" s="18" t="str">
+        <x:v>公开公告显示7月31日截止；具体办公地点、专业要求和实习安排以天健招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O29" s="19" t="str">
+        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
+      </x:c>
+      <x:c r="P29" s="16" t="str">
+        <x:v>A-企业官方招聘入口已核验</x:v>
+      </x:c>
+      <x:c r="Q29" s="18" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="54" customHeight="1">
       <x:c r="A30" s="4" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B30" s="4" t="str">
-        <x:v>搜狐畅游</x:v>
+        <x:v>西安紫光国芯半导体</x:v>
       </x:c>
       <x:c r="C30" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D30" s="4" t="str">
-        <x:v>民营/互联网</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>以岗位页面为准</x:v>
+        <x:v>西安、上海、成都</x:v>
       </x:c>
       <x:c r="F30" s="4" t="str">
-        <x:v>提前批/校园招聘</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>2027届毕业生（部分岗位兼收2026届）</x:v>
+        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>游戏策划、游戏开发、游戏美术、游戏运营、业务支持、平台开发、平台职能、游戏测试8大类岗位</x:v>
+        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
       </x:c>
       <x:c r="I30" s="15" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/cyou-inc/42233?recommendCode=DSRgNQU7#/jobs</x:v>
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
       </x:c>
       <x:c r="J30" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K30" s="4" t="str">
-        <x:v>非免笔试；提前批未录取可参加后续统一笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L30" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；官方投递入口已核验</x:v>
+        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
       </x:c>
       <x:c r="M30" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N30" s="4" t="str">
-        <x:v>深圳北理莫斯科大学就业网公告《搜狐畅游2027届秋季校园招聘提前批正式启动！》发布于2026-07-28；提前批流程快、部分岗位有直通面试机会，未被录取者可参与后续统一笔试，部分热招岗位招满即停。</x:v>
+        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
       </x:c>
       <x:c r="O30" s="15" t="str">
-        <x:v>https://career.smbu.edu.cn/detail/online?id=3535355</x:v>
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
       </x:c>
       <x:c r="P30" s="16" t="str">
-        <x:v>B-可信高校就业网公告含官方投递链接</x:v>
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q30" s="4" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="54" customHeight="1">
       <x:c r="A31" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B31" s="4" t="str">
-        <x:v>我乐家居</x:v>
+        <x:v>新大陆自动识别</x:v>
       </x:c>
       <x:c r="C31" s="4" t="str">
-        <x:v>家居/消费品/智能制造</x:v>
+        <x:v>计算机视觉/智能硬件</x:v>
       </x:c>
       <x:c r="D31" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/上市公司子公司</x:v>
       </x:c>
       <x:c r="E31" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>福州总部及全国/海外岗位</x:v>
       </x:c>
       <x:c r="F31" s="4" t="str">
-        <x:v>提前批/校园招聘</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G31" s="4" t="str">
-        <x:v>2027届本科及以上，以岗位要求为准</x:v>
+        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
       </x:c>
       <x:c r="H31" s="4" t="str">
-        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
+        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
       </x:c>
       <x:c r="I31" s="15" t="str">
-        <x:v>https://olo-home.zhiye.com/Campus</x:v>
+        <x:v>https://nlscan.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J31" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2130,51 +2130,51 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L31" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
+        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
       </x:c>
       <x:c r="M31" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N31" s="4" t="str">
-        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
+        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
       </x:c>
       <x:c r="O31" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
+        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
       </x:c>
       <x:c r="P31" s="16" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
+        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
       </x:c>
       <x:c r="Q31" s="4" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="54" customHeight="1">
       <x:c r="A32" s="4" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B32" s="4" t="str">
-        <x:v>轩宇信息</x:v>
+        <x:v>兆易创新</x:v>
       </x:c>
       <x:c r="C32" s="4" t="str">
-        <x:v>航天/军工信息化/软件</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D32" s="4" t="str">
-        <x:v>央企子公司/高新技术企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
-        <x:v>北京、杭州、西安</x:v>
+        <x:v>北京、上海、武汉、合肥等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F32" s="4" t="str">
-        <x:v>AI专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
         <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
-        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
+        <x:v>芯片设计、验证、嵌入式、软件、应用、测试及职能岗位</x:v>
       </x:c>
       <x:c r="I32" s="15" t="str">
-        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
+        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
       </x:c>
       <x:c r="J32" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2183,51 +2183,51 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L32" s="4" t="str">
-        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
+        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="M32" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N32" s="4" t="str">
-        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
+        <x:v>提前批岗位和城市以兆易创新官方加入我们页面为准，投递前确认职位仍开放。</x:v>
       </x:c>
       <x:c r="O32" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P32" s="14" t="str">
-        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
+        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
+      </x:c>
+      <x:c r="P32" s="16" t="str">
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q32" s="4" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="54" customHeight="1">
       <x:c r="A33" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B33" s="4" t="str">
-        <x:v>卡尔动力</x:v>
+        <x:v>中国航空发动机集团</x:v>
       </x:c>
       <x:c r="C33" s="4" t="str">
-        <x:v>自动驾驶/智能汽车</x:v>
+        <x:v>航空发动机/军工</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
-        <x:v>北京、上海、天津等</x:v>
+        <x:v>全国各院所及下属单位</x:v>
       </x:c>
       <x:c r="F33" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
         <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H33" s="4" t="str">
-        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
+        <x:v>研发设计、工艺、试验、制造、材料、控制、软件及管理岗位</x:v>
       </x:c>
       <x:c r="I33" s="15" t="str">
-        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
+        <x:v>https://aecc.iguopin.com/notice2</x:v>
       </x:c>
       <x:c r="J33" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2236,145 +2236,145 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L33" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
+        <x:v>本轮复核；中国航发官方招聘平台当前显示2027届校园招聘岗位持续开放</x:v>
       </x:c>
       <x:c r="M33" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N33" s="4" t="str">
-        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
+        <x:v>各单位岗位和截止时间不同，需在中国航发招聘平台按单位和专业筛选；本次复核到159家招聘单位及多项研发、工艺、制造、控制和软件岗位。</x:v>
       </x:c>
       <x:c r="O33" s="15" t="str">
-        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
+        <x:v>https://aecc.iguopin.com/job</x:v>
       </x:c>
       <x:c r="P33" s="16" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
+        <x:v>A-中国航发官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="Q33" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="54" customHeight="1">
       <x:c r="A34" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B34" s="4" t="str">
-        <x:v>深信服-X-STAR顶尖人才计划</x:v>
+        <x:v>中粮资本-粮曦计划</x:v>
       </x:c>
       <x:c r="C34" s="4" t="str">
-        <x:v>网络安全/云计算/软件</x:v>
+        <x:v>金融/投资/资管</x:v>
       </x:c>
       <x:c r="D34" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企/金融控股</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
-        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F34" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>培养计划/实习</x:v>
       </x:c>
       <x:c r="G34" s="4" t="str">
-        <x:v>顶尖人才，本硕博按岗位要求</x:v>
+        <x:v>2027-2029届硕士及以上，以公告要求为准</x:v>
       </x:c>
       <x:c r="H34" s="4" t="str">
-        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
+        <x:v>金融、投资、风险、运营、人力资源及综合管理方向</x:v>
       </x:c>
       <x:c r="I34" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
+        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
       </x:c>
       <x:c r="J34" s="4" t="str">
-        <x:v>2026-09-25</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K34" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L34" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
       </x:c>
       <x:c r="M34" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N34" s="4" t="str">
-        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
+        <x:v>粮曦计划具体批次、面向人群和岗位以中粮资本官方加入我们页面及公告为准。</x:v>
       </x:c>
       <x:c r="O34" s="15" t="str">
-        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
-      </x:c>
-      <x:c r="P34" s="14" t="str">
-        <x:v>A-高校就业网含官方投递链接</x:v>
+        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+      </x:c>
+      <x:c r="P34" s="16" t="str">
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q34" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="54" customHeight="1">
       <x:c r="A35" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B35" s="4" t="str">
-        <x:v>希夕智能</x:v>
+        <x:v>中移九天人工智能科技</x:v>
       </x:c>
       <x:c r="C35" s="4" t="str">
-        <x:v>机器人/智能制造</x:v>
+        <x:v>AI/软件/云计算</x:v>
       </x:c>
       <x:c r="D35" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>央企子公司</x:v>
       </x:c>
       <x:c r="E35" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京、西安、广州、深圳</x:v>
       </x:c>
       <x:c r="F35" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>正式批/超级实习生</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
-        <x:v>2027届本科及以上</x:v>
+        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
       </x:c>
       <x:c r="H35" s="4" t="str">
-        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
+        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
       </x:c>
       <x:c r="I35" s="15" t="str">
-        <x:v>https://sunseed.zhiye.com/jobs</x:v>
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="J35" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-09-27</x:v>
       </x:c>
       <x:c r="K35" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L35" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
+        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
       </x:c>
       <x:c r="M35" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N35" s="4" t="str">
-        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
+        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
       </x:c>
       <x:c r="O35" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="P35" s="16" t="str">
-        <x:v>B-高校就业平台转载企业来源</x:v>
+        <x:v>A-中国移动官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="Q35" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="54" customHeight="1">
       <x:c r="A36" s="4" t="str">
-        <x:v>不晚于2026-07-24</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B36" s="4" t="str">
-        <x:v>中国兵器工业集团</x:v>
+        <x:v>广州市卓越教育集团</x:v>
       </x:c>
       <x:c r="C36" s="4" t="str">
-        <x:v>军工/高端装备</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D36" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
-        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
+        <x:v>广州等，以职位页为准</x:v>
       </x:c>
       <x:c r="F36" s="4" t="str">
         <x:v>提前批</x:v>
@@ -2383,116 +2383,116 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H36" s="4" t="str">
-        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
+        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
       <x:c r="I36" s="15" t="str">
-        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
+        <x:v>https://zyjob.hotjob.cn/</x:v>
       </x:c>
       <x:c r="J36" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-26</x:v>
       </x:c>
       <x:c r="K36" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L36" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
       </x:c>
       <x:c r="M36" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N36" s="4" t="str">
-        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
+        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
       </x:c>
       <x:c r="O36" s="15" t="str">
-        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
+        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
       </x:c>
       <x:c r="P36" s="16" t="str">
-        <x:v>B-公开招聘公告/集团入口</x:v>
+        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
       </x:c>
       <x:c r="Q36" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="54" customHeight="1">
       <x:c r="A37" s="4" t="str">
-        <x:v>2026-07-23</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B37" s="4" t="str">
-        <x:v>禾迈股份</x:v>
+        <x:v>搜狐畅游</x:v>
       </x:c>
       <x:c r="C37" s="4" t="str">
-        <x:v>光伏/电力电子</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D37" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/互联网</x:v>
       </x:c>
       <x:c r="E37" s="4" t="str">
-        <x:v>杭州等，以岗位页为准</x:v>
+        <x:v>以岗位页面为准</x:v>
       </x:c>
       <x:c r="F37" s="4" t="str">
-        <x:v>研发类提前批</x:v>
+        <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G37" s="4" t="str">
-        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
+        <x:v>2027届毕业生（部分岗位兼收2026届）</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
-        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
+        <x:v>游戏策划、游戏开发、游戏美术、游戏运营、业务支持、平台开发、平台职能、游戏测试8大类岗位</x:v>
       </x:c>
       <x:c r="I37" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
+        <x:v>https://app.mokahr.com/m/campus_apply/cyou-inc/42233?recommendCode=DSRgNQU7#/jobs</x:v>
       </x:c>
       <x:c r="J37" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K37" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>非免笔试；提前批未录取可参加后续统一笔试</x:v>
       </x:c>
       <x:c r="L37" s="4" t="str">
-        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
+        <x:v>可信高校就业网公告显示开放；官方投递入口已核验</x:v>
       </x:c>
       <x:c r="M37" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N37" s="4" t="str">
-        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
+        <x:v>深圳北理莫斯科大学就业网公告《搜狐畅游2027届秋季校园招聘提前批正式启动！》发布于2026-07-28；提前批流程快、部分岗位有直通面试机会，未被录取者可参与后续统一笔试，部分热招岗位招满即停。</x:v>
       </x:c>
       <x:c r="O37" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
-      </x:c>
-      <x:c r="P37" s="16" t="str">
-        <x:v>B-高校就业网转载企业公告</x:v>
+        <x:v>https://career.smbu.edu.cn/detail/online?id=3535355</x:v>
+      </x:c>
+      <x:c r="P37" s="14" t="str">
+        <x:v>B-可信高校就业网公告含官方投递链接</x:v>
       </x:c>
       <x:c r="Q37" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="54" customHeight="1">
       <x:c r="A38" s="4" t="str">
-        <x:v>2026-07-23</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="B38" s="4" t="str">
-        <x:v>极客未来</x:v>
+        <x:v>我乐家居</x:v>
       </x:c>
       <x:c r="C38" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>家居/消费品/智能制造</x:v>
       </x:c>
       <x:c r="D38" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E38" s="4" t="str">
-        <x:v>四川、重庆、广东</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F38" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H38" s="4" t="str">
-        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
       </x:c>
       <x:c r="I38" s="15" t="str">
-        <x:v>https://geek3.zhiye.com/campus/</x:v>
+        <x:v>https://olo-home.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J38" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2501,104 +2501,104 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L38" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
       </x:c>
       <x:c r="M38" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N38" s="4" t="str">
-        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
+        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
       </x:c>
       <x:c r="O38" s="15" t="str">
-        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
-      </x:c>
-      <x:c r="P38" s="16" t="str">
-        <x:v>B-高校就业网公告+公开招聘页面</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P38" s="14" t="str">
+        <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
       <x:c r="Q38" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="54" customHeight="1">
       <x:c r="A39" s="4" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="B39" s="4" t="str">
-        <x:v>安永EY</x:v>
+        <x:v>轩宇信息</x:v>
       </x:c>
       <x:c r="C39" s="4" t="str">
-        <x:v>会计审计/咨询/专业服务</x:v>
+        <x:v>航天/军工信息化/软件</x:v>
       </x:c>
       <x:c r="D39" s="4" t="str">
-        <x:v>外资/专业服务机构</x:v>
+        <x:v>央企子公司/高新技术企业</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
-        <x:v>中国内地多地，以职位页为准</x:v>
+        <x:v>北京、杭州、西安</x:v>
       </x:c>
       <x:c r="F39" s="4" t="str">
-        <x:v>正式批/秋季校园招聘</x:v>
+        <x:v>AI专项/提前批</x:v>
       </x:c>
       <x:c r="G39" s="4" t="str">
-        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H39" s="4" t="str">
-        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
+        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
       </x:c>
       <x:c r="I39" s="15" t="str">
-        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
+        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
       </x:c>
       <x:c r="J39" s="4" t="str">
-        <x:v>2026年10月（具体日期未公布）</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K39" s="4" t="str">
-        <x:v>否；官方流程包含在线测评</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L39" s="4" t="str">
-        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
+        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
       </x:c>
       <x:c r="M39" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N39" s="4" t="str">
-        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
+        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
       </x:c>
       <x:c r="O39" s="15" t="str">
-        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
-      </x:c>
-      <x:c r="P39" s="14" t="str">
-        <x:v>A-企业官方校招网站与职位页已核验</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P39" s="16" t="str">
+        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
       </x:c>
       <x:c r="Q39" s="4" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="54" customHeight="1">
       <x:c r="A40" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B40" s="4" t="str">
-        <x:v>阿里巴巴-阿里星计划</x:v>
+        <x:v>卡尔动力</x:v>
       </x:c>
       <x:c r="C40" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>自动驾驶/智能汽车</x:v>
       </x:c>
       <x:c r="D40" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E40" s="4" t="str">
-        <x:v>杭州、北京、上海、深圳等</x:v>
+        <x:v>北京、上海、天津等</x:v>
       </x:c>
       <x:c r="F40" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G40" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H40" s="4" t="str">
-        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
+        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
       </x:c>
       <x:c r="I40" s="15" t="str">
-        <x:v>https://talent.alibaba.com/campus/</x:v>
+        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
       </x:c>
       <x:c r="J40" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2607,102 +2607,104 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L40" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
       </x:c>
       <x:c r="M40" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N40" s="4" t="str">
-        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
+        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
       </x:c>
       <x:c r="O40" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P40" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
+      </x:c>
+      <x:c r="P40" s="14" t="str">
+        <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
       <x:c r="Q40" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="54" customHeight="1">
       <x:c r="A41" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B41" s="4" t="str">
-        <x:v>贝恩公司</x:v>
+        <x:v>深信服-X-STAR顶尖人才计划</x:v>
       </x:c>
       <x:c r="C41" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>网络安全/云计算/软件</x:v>
       </x:c>
       <x:c r="D41" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E41" s="4" t="str">
-        <x:v>北京、上海、香港等</x:v>
+        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F41" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G41" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>顶尖人才，本硕博按岗位要求</x:v>
       </x:c>
       <x:c r="H41" s="4" t="str">
-        <x:v>助理咨询顾问等</x:v>
+        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
       </x:c>
       <x:c r="I41" s="15" t="str">
-        <x:v>https://www.bain.com/careers/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
       </x:c>
       <x:c r="J41" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-09-25</x:v>
       </x:c>
       <x:c r="K41" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L41" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M41" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N41" s="4" t="str"/>
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N41" s="4" t="str">
+        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
+      </x:c>
       <x:c r="O41" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P41" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
+      </x:c>
+      <x:c r="P41" s="16" t="str">
+        <x:v>A-高校就业网含官方投递链接</x:v>
       </x:c>
       <x:c r="Q41" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="54" customHeight="1">
       <x:c r="A42" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B42" s="4" t="str">
-        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
+        <x:v>希夕智能</x:v>
       </x:c>
       <x:c r="C42" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>机器人/智能制造</x:v>
       </x:c>
       <x:c r="D42" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E42" s="4" t="str">
-        <x:v>上海、北京等</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F42" s="4" t="str">
-        <x:v>顶尖技术专项/提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G42" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科及以上</x:v>
       </x:c>
       <x:c r="H42" s="4" t="str">
-        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
+        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
       </x:c>
       <x:c r="I42" s="15" t="str">
-        <x:v>https://jobs.bilibili.com/</x:v>
+        <x:v>https://sunseed.zhiye.com/jobs</x:v>
       </x:c>
       <x:c r="J42" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2711,72 +2713,72 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L42" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
       </x:c>
       <x:c r="M42" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N42" s="4" t="str">
-        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
+        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
       </x:c>
       <x:c r="O42" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P42" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
+      </x:c>
+      <x:c r="P42" s="14" t="str">
+        <x:v>B-高校就业平台转载企业来源</x:v>
       </x:c>
       <x:c r="Q42" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="54" customHeight="1">
       <x:c r="A43" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>不晚于2026-07-24</x:v>
       </x:c>
       <x:c r="B43" s="4" t="str">
-        <x:v>东风汽车-全球博士人才</x:v>
+        <x:v>中国兵器工业集团</x:v>
       </x:c>
       <x:c r="C43" s="4" t="str">
-        <x:v>汽车/央企</x:v>
+        <x:v>军工/高端装备</x:v>
       </x:c>
       <x:c r="D43" s="4" t="str">
         <x:v>央企</x:v>
       </x:c>
       <x:c r="E43" s="4" t="str">
-        <x:v>武汉、广州、十堰及全国研发基地</x:v>
+        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
       </x:c>
       <x:c r="F43" s="4" t="str">
-        <x:v>博士专项</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G43" s="4" t="str">
-        <x:v>2026届及以后博士</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H43" s="4" t="str">
-        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
+        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
       </x:c>
       <x:c r="I43" s="15" t="str">
-        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
+        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
       </x:c>
       <x:c r="J43" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K43" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L43" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M43" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N43" s="4" t="str">
-        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
+        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
       </x:c>
       <x:c r="O43" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P43" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
+      </x:c>
+      <x:c r="P43" s="14" t="str">
+        <x:v>B-公开招聘公告/集团入口</x:v>
       </x:c>
       <x:c r="Q43" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -2784,31 +2786,31 @@
     </x:row>
     <x:row r="44" ht="54" customHeight="1">
       <x:c r="A44" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B44" s="4" t="str">
-        <x:v>度小满-博士后人才招聘</x:v>
+        <x:v>禾迈股份</x:v>
       </x:c>
       <x:c r="C44" s="4" t="str">
-        <x:v>金融科技</x:v>
+        <x:v>光伏/电力电子</x:v>
       </x:c>
       <x:c r="D44" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E44" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>杭州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F44" s="4" t="str">
-        <x:v>博士后专项</x:v>
+        <x:v>研发类提前批</x:v>
       </x:c>
       <x:c r="G44" s="4" t="str">
-        <x:v>2025/2026/2027届博士</x:v>
+        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H44" s="4" t="str">
-        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
+        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
       </x:c>
       <x:c r="I44" s="15" t="str">
-        <x:v>https://campus.duxiaoman.com/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
       </x:c>
       <x:c r="J44" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2817,39 +2819,39 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L44" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
       </x:c>
       <x:c r="M44" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N44" s="4" t="str">
-        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
+        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
       </x:c>
       <x:c r="O44" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P44" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
+      </x:c>
+      <x:c r="P44" s="14" t="str">
+        <x:v>B-高校就业网转载企业公告</x:v>
       </x:c>
       <x:c r="Q44" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="54" customHeight="1">
       <x:c r="A45" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B45" s="4" t="str">
-        <x:v>多益网络</x:v>
+        <x:v>极客未来</x:v>
       </x:c>
       <x:c r="C45" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D45" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E45" s="4" t="str">
-        <x:v>广州、武汉、成都等</x:v>
+        <x:v>四川、重庆、广东</x:v>
       </x:c>
       <x:c r="F45" s="4" t="str">
         <x:v>提前批</x:v>
@@ -2858,10 +2860,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H45" s="4" t="str">
-        <x:v>程序、策划、美术、运营、市场及职能</x:v>
+        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
       <x:c r="I45" s="15" t="str">
-        <x:v>https://www.duoyi.com/job/</x:v>
+        <x:v>https://geek3.zhiye.com/campus/</x:v>
       </x:c>
       <x:c r="J45" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2870,75 +2872,75 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L45" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
       </x:c>
       <x:c r="M45" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N45" s="4" t="str">
-        <x:v>岗位可能按城市提前关闭。</x:v>
+        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
       </x:c>
       <x:c r="O45" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P45" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
+      </x:c>
+      <x:c r="P45" s="14" t="str">
+        <x:v>B-高校就业网公告+公开招聘页面</x:v>
       </x:c>
       <x:c r="Q45" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="54" customHeight="1">
       <x:c r="A46" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="B46" s="4" t="str">
-        <x:v>海天集团-高潜专项</x:v>
+        <x:v>安永EY</x:v>
       </x:c>
       <x:c r="C46" s="4" t="str">
-        <x:v>工业制造</x:v>
+        <x:v>会计审计/咨询/专业服务</x:v>
       </x:c>
       <x:c r="D46" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>外资/专业服务机构</x:v>
       </x:c>
       <x:c r="E46" s="4" t="str">
-        <x:v>宁波及全国基地</x:v>
+        <x:v>中国内地多地，以职位页为准</x:v>
       </x:c>
       <x:c r="F46" s="4" t="str">
-        <x:v>高潜人才专项/提前批</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G46" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
       </x:c>
       <x:c r="H46" s="4" t="str">
-        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
+        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
       </x:c>
       <x:c r="I46" s="15" t="str">
-        <x:v>https://www.haitian.com/careers/</x:v>
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
       </x:c>
       <x:c r="J46" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026年10月（具体日期未公布）</x:v>
       </x:c>
       <x:c r="K46" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；官方流程包含在线测评</x:v>
       </x:c>
       <x:c r="L46" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
       </x:c>
       <x:c r="M46" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N46" s="4" t="str">
-        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
+        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
       </x:c>
       <x:c r="O46" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P46" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
+      </x:c>
+      <x:c r="P46" s="16" t="str">
+        <x:v>A-企业官方校招网站与职位页已核验</x:v>
       </x:c>
       <x:c r="Q46" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="54" customHeight="1">
@@ -2946,28 +2948,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B47" s="4" t="str">
-        <x:v>赫力昂-销售先锋计划</x:v>
+        <x:v>阿里巴巴-阿里星计划</x:v>
       </x:c>
       <x:c r="C47" s="4" t="str">
-        <x:v>消费健康/医药</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D47" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E47" s="4" t="str">
-        <x:v>全国重点城市</x:v>
+        <x:v>杭州、北京、上海、深圳等</x:v>
       </x:c>
       <x:c r="F47" s="4" t="str">
-        <x:v>管培/销售专项</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G47" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H47" s="4" t="str">
-        <x:v>医药及消费健康销售、商业运营方向</x:v>
+        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
       </x:c>
       <x:c r="I47" s="15" t="str">
-        <x:v>https://careers.haleon.com/</x:v>
+        <x:v>https://talent.alibaba.com/campus/</x:v>
       </x:c>
       <x:c r="J47" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2981,7 +2983,9 @@
       <x:c r="M47" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N47" s="4" t="str"/>
+      <x:c r="N47" s="4" t="str">
+        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
+      </x:c>
       <x:c r="O47" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -2997,40 +3001,40 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B48" s="4" t="str">
-        <x:v>虹软科技</x:v>
+        <x:v>贝恩公司</x:v>
       </x:c>
       <x:c r="C48" s="4" t="str">
-        <x:v>计算机视觉/软件</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D48" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E48" s="4" t="str">
-        <x:v>杭州、上海、南京等</x:v>
+        <x:v>北京、上海、香港等</x:v>
       </x:c>
       <x:c r="F48" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G48" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H48" s="4" t="str">
-        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
+        <x:v>助理咨询顾问等</x:v>
       </x:c>
       <x:c r="I48" s="15" t="str">
-        <x:v>https://hr.arcsoft.com.cn/</x:v>
+        <x:v>https://www.bain.com/careers/</x:v>
       </x:c>
       <x:c r="J48" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K48" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L48" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M48" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N48" s="4" t="str"/>
       <x:c r="O48" s="15" t="str">
@@ -3048,34 +3052,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B49" s="4" t="str">
-        <x:v>汇川技术</x:v>
+        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
       </x:c>
       <x:c r="C49" s="4" t="str">
-        <x:v>工业自动化/新能源</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="D49" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E49" s="4" t="str">
-        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
+        <x:v>上海、北京等</x:v>
       </x:c>
       <x:c r="F49" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>顶尖技术专项/提前批</x:v>
       </x:c>
       <x:c r="G49" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H49" s="4" t="str">
-        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
+        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
       </x:c>
       <x:c r="I49" s="15" t="str">
-        <x:v>https://career.inovance.com/</x:v>
+        <x:v>https://jobs.bilibili.com/</x:v>
       </x:c>
       <x:c r="J49" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K49" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L49" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3083,7 +3087,9 @@
       <x:c r="M49" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N49" s="4" t="str"/>
+      <x:c r="N49" s="4" t="str">
+        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
+      </x:c>
       <x:c r="O49" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3099,28 +3105,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B50" s="4" t="str">
-        <x:v>伽利略-星途星锐计划</x:v>
+        <x:v>东风汽车-全球博士人才</x:v>
       </x:c>
       <x:c r="C50" s="4" t="str">
-        <x:v>科技/综合</x:v>
+        <x:v>汽车/央企</x:v>
       </x:c>
       <x:c r="D50" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E50" s="4" t="str">
-        <x:v>以项目职位页为准</x:v>
+        <x:v>武汉、广州、十堰及全国研发基地</x:v>
       </x:c>
       <x:c r="F50" s="4" t="str">
-        <x:v>人才专项</x:v>
+        <x:v>博士专项</x:v>
       </x:c>
       <x:c r="G50" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026届及以后博士</x:v>
       </x:c>
       <x:c r="H50" s="4" t="str">
-        <x:v>以官方项目页为准</x:v>
-      </x:c>
-      <x:c r="I50" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
+      </x:c>
+      <x:c r="I50" s="15" t="str">
+        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
       </x:c>
       <x:c r="J50" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3135,13 +3141,13 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N50" s="4" t="str">
-        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
+        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
       </x:c>
       <x:c r="O50" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P50" s="20" t="str">
-        <x:v>C-主体与入口需二次确认</x:v>
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q50" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3152,52 +3158,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B51" s="4" t="str">
-        <x:v>京东-TET管理培训生</x:v>
+        <x:v>度小满-博士后人才招聘</x:v>
       </x:c>
       <x:c r="C51" s="4" t="str">
-        <x:v>互联网/零售</x:v>
+        <x:v>金融科技</x:v>
       </x:c>
       <x:c r="D51" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E51" s="4" t="str">
-        <x:v>北京及业务所在城市</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F51" s="4" t="str">
-        <x:v>管培生专项/提前批</x:v>
+        <x:v>博士后专项</x:v>
       </x:c>
       <x:c r="G51" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2025/2026/2027届博士</x:v>
       </x:c>
       <x:c r="H51" s="4" t="str">
-        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
+        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
       </x:c>
       <x:c r="I51" s="15" t="str">
-        <x:v>https://campus.jd.com/</x:v>
+        <x:v>https://campus.duxiaoman.com/</x:v>
       </x:c>
       <x:c r="J51" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K51" s="4" t="str">
-        <x:v>含测评，笔试以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L51" s="4" t="str">
-        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M51" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N51" s="4" t="str">
-        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
+        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
       </x:c>
       <x:c r="O51" s="15" t="str">
-        <x:v>https://campus.jd.com/#/</x:v>
-      </x:c>
-      <x:c r="P51" s="14" t="str">
-        <x:v>A-企业官网校招页面已核验</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P51" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q51" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="54" customHeight="1">
@@ -3205,28 +3211,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B52" s="4" t="str">
-        <x:v>科大讯飞-飞凡计划</x:v>
+        <x:v>多益网络</x:v>
       </x:c>
       <x:c r="C52" s="4" t="str">
-        <x:v>AI/软件</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D52" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E52" s="4" t="str">
-        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
+        <x:v>广州、武汉、成都等</x:v>
       </x:c>
       <x:c r="F52" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G52" s="4" t="str">
-        <x:v>2026/2027届</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H52" s="4" t="str">
-        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
+        <x:v>程序、策划、美术、运营、市场及职能</x:v>
       </x:c>
       <x:c r="I52" s="15" t="str">
-        <x:v>https://campus.iflytek.com/</x:v>
+        <x:v>https://www.duoyi.com/job/</x:v>
       </x:c>
       <x:c r="J52" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3241,7 +3247,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N52" s="4" t="str">
-        <x:v>专项岗位与常规校招可能并行。</x:v>
+        <x:v>岗位可能按城市提前关闭。</x:v>
       </x:c>
       <x:c r="O52" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3258,28 +3264,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B53" s="4" t="str">
-        <x:v>理想汽车</x:v>
+        <x:v>海天集团-高潜专项</x:v>
       </x:c>
       <x:c r="C53" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>工业制造</x:v>
       </x:c>
       <x:c r="D53" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E53" s="4" t="str">
-        <x:v>北京、上海、常州等</x:v>
+        <x:v>宁波及全国基地</x:v>
       </x:c>
       <x:c r="F53" s="4" t="str">
-        <x:v>暑期实习转正通道</x:v>
+        <x:v>高潜人才专项/提前批</x:v>
       </x:c>
       <x:c r="G53" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H53" s="4" t="str">
-        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
+        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
       </x:c>
       <x:c r="I53" s="15" t="str">
-        <x:v>https://career.lixiang.com/campus</x:v>
+        <x:v>https://www.haitian.com/careers/</x:v>
       </x:c>
       <x:c r="J53" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3294,7 +3300,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N53" s="4" t="str">
-        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
+        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
       </x:c>
       <x:c r="O53" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3307,56 +3313,54 @@
       </x:c>
     </x:row>
     <x:row r="54" ht="54" customHeight="1">
-      <x:c r="A54" s="16" t="str">
+      <x:c r="A54" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B54" s="16" t="str">
-        <x:v>莉莉丝游戏</x:v>
-      </x:c>
-      <x:c r="C54" s="16" t="str">
-        <x:v>游戏</x:v>
-      </x:c>
-      <x:c r="D54" s="16" t="str">
+      <x:c r="B54" s="4" t="str">
+        <x:v>赫力昂-销售先锋计划</x:v>
+      </x:c>
+      <x:c r="C54" s="4" t="str">
+        <x:v>消费健康/医药</x:v>
+      </x:c>
+      <x:c r="D54" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E54" s="16" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F54" s="16" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G54" s="16" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H54" s="16" t="str">
-        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
-      </x:c>
-      <x:c r="I54" s="17" t="str">
-        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
-      </x:c>
-      <x:c r="J54" s="16" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
-      <x:c r="K54" s="16" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
-      </x:c>
-      <x:c r="L54" s="16" t="str">
-        <x:v>今日截止；莉莉丝官方校园招聘页当前仍显示27届校招提前批14个职位</x:v>
-      </x:c>
-      <x:c r="M54" s="16" t="str">
-        <x:v>P0-今日截止</x:v>
-      </x:c>
-      <x:c r="N54" s="16" t="str">
-        <x:v>官网当前显示服务器开发、数据分析、战略研究、算法、关卡策划、客户端等27届提前批职位；截止日为2026-08-07，页面仍可投递但可能随时关闭，建议立即完成网申。</x:v>
-      </x:c>
-      <x:c r="O54" s="17" t="str">
-        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
-      </x:c>
-      <x:c r="P54" s="14" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="Q54" s="16" t="str">
-        <x:v>2026-08-07</x:v>
+      <x:c r="E54" s="4" t="str">
+        <x:v>全国重点城市</x:v>
+      </x:c>
+      <x:c r="F54" s="4" t="str">
+        <x:v>管培/销售专项</x:v>
+      </x:c>
+      <x:c r="G54" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H54" s="4" t="str">
+        <x:v>医药及消费健康销售、商业运营方向</x:v>
+      </x:c>
+      <x:c r="I54" s="15" t="str">
+        <x:v>https://careers.haleon.com/</x:v>
+      </x:c>
+      <x:c r="J54" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K54" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L54" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M54" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N54" s="4" t="str"/>
+      <x:c r="O54" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P54" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q54" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="54" customHeight="1">
@@ -3364,40 +3368,40 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B55" s="4" t="str">
-        <x:v>麦肯锡</x:v>
+        <x:v>虹软科技</x:v>
       </x:c>
       <x:c r="C55" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>计算机视觉/软件</x:v>
       </x:c>
       <x:c r="D55" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E55" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>杭州、上海、南京等</x:v>
       </x:c>
       <x:c r="F55" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G55" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H55" s="4" t="str">
-        <x:v>商业分析师、咨询及专业岗位</x:v>
+        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
       </x:c>
       <x:c r="I55" s="15" t="str">
-        <x:v>https://www.mckinsey.com/careers</x:v>
+        <x:v>https://hr.arcsoft.com.cn/</x:v>
       </x:c>
       <x:c r="J55" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K55" s="4" t="str">
-        <x:v>通常含测评/案例面试；以通知为准</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L55" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M55" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N55" s="4" t="str"/>
       <x:c r="O55" s="15" t="str">
@@ -3415,28 +3419,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B56" s="4" t="str">
-        <x:v>拼多多</x:v>
+        <x:v>汇川技术</x:v>
       </x:c>
       <x:c r="C56" s="4" t="str">
-        <x:v>互联网/电商</x:v>
+        <x:v>工业自动化/新能源</x:v>
       </x:c>
       <x:c r="D56" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E56" s="4" t="str">
-        <x:v>上海、广州等，以岗位页为准</x:v>
+        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
       </x:c>
       <x:c r="F56" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G56" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H56" s="4" t="str">
-        <x:v>技术、算法、产品、运营、商业分析等</x:v>
+        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
       </x:c>
       <x:c r="I56" s="15" t="str">
-        <x:v>https://careers.pinduoduo.com/campus/</x:v>
+        <x:v>https://career.inovance.com/</x:v>
       </x:c>
       <x:c r="J56" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3450,9 +3454,7 @@
       <x:c r="M56" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N56" s="4" t="str">
-        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
-      </x:c>
+      <x:c r="N56" s="4" t="str"/>
       <x:c r="O56" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3468,34 +3470,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B57" s="4" t="str">
-        <x:v>启林投资</x:v>
+        <x:v>伽利略-星途星锐计划</x:v>
       </x:c>
       <x:c r="C57" s="4" t="str">
-        <x:v>量化金融/资管</x:v>
+        <x:v>科技/综合</x:v>
       </x:c>
       <x:c r="D57" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E57" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>以项目职位页为准</x:v>
       </x:c>
       <x:c r="F57" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>人才专项</x:v>
       </x:c>
       <x:c r="G57" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H57" s="4" t="str">
-        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
-      </x:c>
-      <x:c r="I57" s="15" t="str">
-        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
+        <x:v>以官方项目页为准</x:v>
+      </x:c>
+      <x:c r="I57" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J57" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K57" s="4" t="str">
-        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L57" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3504,13 +3506,13 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N57" s="4" t="str">
-        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
+        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
       </x:c>
       <x:c r="O57" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P57" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>C-主体与入口需二次确认</x:v>
       </x:c>
       <x:c r="Q57" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3521,52 +3523,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B58" s="4" t="str">
-        <x:v>商汤科技-无限原力计划</x:v>
+        <x:v>京东-TET管理培训生</x:v>
       </x:c>
       <x:c r="C58" s="4" t="str">
-        <x:v>AI/计算机视觉</x:v>
+        <x:v>互联网/零售</x:v>
       </x:c>
       <x:c r="D58" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E58" s="4" t="str">
-        <x:v>上海、北京、深圳、杭州等</x:v>
+        <x:v>北京及业务所在城市</x:v>
       </x:c>
       <x:c r="F58" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>管培生专项/提前批</x:v>
       </x:c>
       <x:c r="G58" s="4" t="str">
-        <x:v>2027/2028届</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H58" s="4" t="str">
-        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
+        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
       </x:c>
       <x:c r="I58" s="15" t="str">
-        <x:v>https://joinus.sensetime.com/</x:v>
+        <x:v>https://campus.jd.com/</x:v>
       </x:c>
       <x:c r="J58" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K58" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>含测评，笔试以通知为准</x:v>
       </x:c>
       <x:c r="L58" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
       </x:c>
       <x:c r="M58" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N58" s="4" t="str">
-        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
+        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
       </x:c>
       <x:c r="O58" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P58" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://campus.jd.com/#/</x:v>
+      </x:c>
+      <x:c r="P58" s="16" t="str">
+        <x:v>A-企业官网校招页面已核验</x:v>
       </x:c>
       <x:c r="Q58" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="54" customHeight="1">
@@ -3574,28 +3576,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B59" s="4" t="str">
-        <x:v>腾讯-青云计划</x:v>
+        <x:v>科大讯飞-飞凡计划</x:v>
       </x:c>
       <x:c r="C59" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>AI/软件</x:v>
       </x:c>
       <x:c r="D59" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E59" s="4" t="str">
-        <x:v>深圳、北京、上海等</x:v>
+        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
       </x:c>
       <x:c r="F59" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G59" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026/2027届</x:v>
       </x:c>
       <x:c r="H59" s="4" t="str">
-        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
+        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
       </x:c>
       <x:c r="I59" s="15" t="str">
-        <x:v>https://join.qq.com/</x:v>
+        <x:v>https://campus.iflytek.com/</x:v>
       </x:c>
       <x:c r="J59" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3610,7 +3612,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N59" s="4" t="str">
-        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
+        <x:v>专项岗位与常规校招可能并行。</x:v>
       </x:c>
       <x:c r="O59" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3627,28 +3629,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B60" s="4" t="str">
-        <x:v>天锐星通</x:v>
+        <x:v>理想汽车</x:v>
       </x:c>
       <x:c r="C60" s="4" t="str">
-        <x:v>卫星通信/相控阵</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D60" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E60" s="4" t="str">
-        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
+        <x:v>北京、上海、常州等</x:v>
       </x:c>
       <x:c r="F60" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>暑期实习转正通道</x:v>
       </x:c>
       <x:c r="G60" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H60" s="4" t="str">
-        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
+        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
       </x:c>
       <x:c r="I60" s="15" t="str">
-        <x:v>https://www.tianruixing.com/</x:v>
+        <x:v>https://career.lixiang.com/campus</x:v>
       </x:c>
       <x:c r="J60" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3663,7 +3665,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N60" s="4" t="str">
-        <x:v>官网入口与具体岗位需投前复核。</x:v>
+        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
       </x:c>
       <x:c r="O60" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3676,56 +3678,56 @@
       </x:c>
     </x:row>
     <x:row r="61" ht="54" customHeight="1">
-      <x:c r="A61" s="4" t="str">
-        <x:v>2026-07-21</x:v>
-      </x:c>
-      <x:c r="B61" s="4" t="str">
-        <x:v>网易游戏雷火</x:v>
-      </x:c>
-      <x:c r="C61" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
-      </x:c>
-      <x:c r="D61" s="4" t="str">
+      <x:c r="A61" s="18" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B61" s="18" t="str">
+        <x:v>莉莉丝游戏</x:v>
+      </x:c>
+      <x:c r="C61" s="18" t="str">
+        <x:v>游戏</x:v>
+      </x:c>
+      <x:c r="D61" s="18" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E61" s="4" t="str">
-        <x:v>杭州、上海等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F61" s="4" t="str">
-        <x:v>正式批</x:v>
-      </x:c>
-      <x:c r="G61" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H61" s="4" t="str">
-        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
-      </x:c>
-      <x:c r="I61" s="15" t="str">
-        <x:v>https://leihuo.163.com/campus/#/full</x:v>
-      </x:c>
-      <x:c r="J61" s="4" t="str">
-        <x:v>2026-10-15</x:v>
-      </x:c>
-      <x:c r="K61" s="4" t="str">
-        <x:v>部分岗位免笔试；部分可直通面试</x:v>
-      </x:c>
-      <x:c r="L61" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M61" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
-      </x:c>
-      <x:c r="N61" s="4" t="str">
-        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
-      </x:c>
-      <x:c r="O61" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P61" s="14" t="str">
-        <x:v>A-官方招聘官网已核验</x:v>
-      </x:c>
-      <x:c r="Q61" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+      <x:c r="E61" s="18" t="str">
+        <x:v>上海等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F61" s="18" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G61" s="18" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H61" s="18" t="str">
+        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
+      </x:c>
+      <x:c r="I61" s="19" t="str">
+        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
+      </x:c>
+      <x:c r="J61" s="18" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+      <x:c r="K61" s="18" t="str">
+        <x:v>按岗位，官方未统一说明</x:v>
+      </x:c>
+      <x:c r="L61" s="18" t="str">
+        <x:v>已截止（2026-08-07）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M61" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N61" s="18" t="str">
+        <x:v>莉莉丝27届校招提前批截止日为2026-08-07；项目已按日期标记截止，官方招聘页和原投递入口保留供查询。</x:v>
+      </x:c>
+      <x:c r="O61" s="19" t="str">
+        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
+      </x:c>
+      <x:c r="P61" s="16" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q61" s="18" t="str">
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="54" customHeight="1">
@@ -3733,34 +3735,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B62" s="4" t="str">
-        <x:v>小鹏集团</x:v>
+        <x:v>麦肯锡</x:v>
       </x:c>
       <x:c r="C62" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D62" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E62" s="4" t="str">
-        <x:v>广州、北京、上海、深圳、武汉等</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F62" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G62" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H62" s="4" t="str">
-        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
+        <x:v>商业分析师、咨询及专业岗位</x:v>
       </x:c>
       <x:c r="I62" s="15" t="str">
-        <x:v>https://join.xiaopeng.com/campus</x:v>
+        <x:v>https://www.mckinsey.com/careers</x:v>
       </x:c>
       <x:c r="J62" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K62" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常含测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L62" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3768,9 +3770,7 @@
       <x:c r="M62" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N62" s="4" t="str">
-        <x:v>营销服与技术岗位可能分项目发布。</x:v>
-      </x:c>
+      <x:c r="N62" s="4" t="str"/>
       <x:c r="O62" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3786,28 +3786,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B63" s="4" t="str">
-        <x:v>芯动科技</x:v>
+        <x:v>拼多多</x:v>
       </x:c>
       <x:c r="C63" s="4" t="str">
-        <x:v>半导体/IP设计</x:v>
+        <x:v>互联网/电商</x:v>
       </x:c>
       <x:c r="D63" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E63" s="4" t="str">
-        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
+        <x:v>上海、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F63" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G63" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H63" s="4" t="str">
-        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
+        <x:v>技术、算法、产品、运营、商业分析等</x:v>
       </x:c>
       <x:c r="I63" s="15" t="str">
-        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
+        <x:v>https://careers.pinduoduo.com/campus/</x:v>
       </x:c>
       <x:c r="J63" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3821,7 +3821,9 @@
       <x:c r="M63" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N63" s="4" t="str"/>
+      <x:c r="N63" s="4" t="str">
+        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
+      </x:c>
       <x:c r="O63" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3834,52 +3836,52 @@
     </x:row>
     <x:row r="64" ht="54" customHeight="1">
       <x:c r="A64" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B64" s="4" t="str">
-        <x:v>芯迈半导体</x:v>
+        <x:v>启林投资</x:v>
       </x:c>
       <x:c r="C64" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>量化金融/资管</x:v>
       </x:c>
       <x:c r="D64" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E64" s="4" t="str">
-        <x:v>杭州、上海、深圳、成都</x:v>
+        <x:v>上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F64" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G64" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H64" s="4" t="str">
-        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
+        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
       </x:c>
       <x:c r="I64" s="15" t="str">
-        <x:v>https://www.silicon-magic.com/joinus</x:v>
+        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
       </x:c>
       <x:c r="J64" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K64" s="4" t="str">
-        <x:v>官方未说明；公开流程未列笔试</x:v>
+        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
       </x:c>
       <x:c r="L64" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M64" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N64" s="4" t="str">
-        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
+        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
       </x:c>
       <x:c r="O64" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P64" s="14" t="str">
-        <x:v>A-企业官网与公开公告已核验</x:v>
+      <x:c r="P64" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q64" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3890,52 +3892,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B65" s="4" t="str">
-        <x:v>新易盛</x:v>
+        <x:v>商汤科技-无限原力计划</x:v>
       </x:c>
       <x:c r="C65" s="4" t="str">
-        <x:v>光通信/半导体</x:v>
+        <x:v>AI/计算机视觉</x:v>
       </x:c>
       <x:c r="D65" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E65" s="4" t="str">
-        <x:v>成都、苏州等，以岗位页为准</x:v>
+        <x:v>上海、北京、深圳、杭州等</x:v>
       </x:c>
       <x:c r="F65" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G65" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027/2028届</x:v>
       </x:c>
       <x:c r="H65" s="4" t="str">
-        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
+        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
       </x:c>
       <x:c r="I65" s="15" t="str">
-        <x:v>https://www.eoptolink.com/</x:v>
+        <x:v>https://joinus.sensetime.com/</x:v>
       </x:c>
       <x:c r="J65" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K65" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L65" s="4" t="str">
-        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M65" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N65" s="4" t="str">
-        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
       </x:c>
       <x:c r="O65" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P65" s="16" t="str">
-        <x:v>B-高校/招聘平台转载，投前复核</x:v>
+      <x:c r="P65" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q65" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="54" customHeight="1">
@@ -3943,34 +3945,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B66" s="4" t="str">
-        <x:v>元戎启行</x:v>
+        <x:v>腾讯-青云计划</x:v>
       </x:c>
       <x:c r="C66" s="4" t="str">
-        <x:v>自动驾驶</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D66" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E66" s="4" t="str">
-        <x:v>深圳、北京等</x:v>
+        <x:v>深圳、北京、上海等</x:v>
       </x:c>
       <x:c r="F66" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G66" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H66" s="4" t="str">
-        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
+        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
       </x:c>
       <x:c r="I66" s="15" t="str">
-        <x:v>https://www.deeproute.ai/join-us</x:v>
+        <x:v>https://join.qq.com/</x:v>
       </x:c>
       <x:c r="J66" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K66" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L66" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3978,7 +3980,9 @@
       <x:c r="M66" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N66" s="4" t="str"/>
+      <x:c r="N66" s="4" t="str">
+        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
+      </x:c>
       <x:c r="O66" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3994,28 +3998,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B67" s="4" t="str">
-        <x:v>圆通速递</x:v>
+        <x:v>天锐星通</x:v>
       </x:c>
       <x:c r="C67" s="4" t="str">
-        <x:v>物流/供应链</x:v>
+        <x:v>卫星通信/相控阵</x:v>
       </x:c>
       <x:c r="D67" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E67" s="4" t="str">
-        <x:v>上海及全国网络</x:v>
+        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F67" s="4" t="str">
-        <x:v>正式批/校招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G67" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H67" s="4" t="str">
-        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
+        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
       </x:c>
       <x:c r="I67" s="15" t="str">
-        <x:v>https://hr.yto.net.cn/</x:v>
+        <x:v>https://www.tianruixing.com/</x:v>
       </x:c>
       <x:c r="J67" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4029,7 +4033,9 @@
       <x:c r="M67" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N67" s="4" t="str"/>
+      <x:c r="N67" s="4" t="str">
+        <x:v>官网入口与具体岗位需投前复核。</x:v>
+      </x:c>
       <x:c r="O67" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -4042,31 +4048,31 @@
     </x:row>
     <x:row r="68" ht="54" customHeight="1">
       <x:c r="A68" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B68" s="4" t="str">
-        <x:v>长亭科技</x:v>
+        <x:v>网易游戏（互娱）-2027届校园招聘</x:v>
       </x:c>
       <x:c r="C68" s="4" t="str">
-        <x:v>网络安全</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D68" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E68" s="4" t="str">
-        <x:v>北京、上海等，以岗位页为准</x:v>
+        <x:v>广州、杭州、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F68" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G68" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
       </x:c>
       <x:c r="H68" s="4" t="str">
-        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
+        <x:v>游戏研发、技术、策划、产品、艺术设计、测试及运营等方向</x:v>
       </x:c>
       <x:c r="I68" s="15" t="str">
-        <x:v>https://job.chaitin.cn/</x:v>
+        <x:v>https://campus.game.163.com/</x:v>
       </x:c>
       <x:c r="J68" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4075,68 +4081,72 @@
         <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L68" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>本轮新增；网易游戏互娱官方校招动态确认2027届校园招聘已启动</x:v>
       </x:c>
       <x:c r="M68" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N68" s="4" t="str"/>
+      <x:c r="N68" s="4" t="str">
+        <x:v>官方招聘动态于2026-07-21发布；应届生招聘与精英实习生项目分开，投递时注意选择对应批次和游戏业务。</x:v>
+      </x:c>
       <x:c r="O68" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P68" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://campus.game.163.com/news/0</x:v>
+      </x:c>
+      <x:c r="P68" s="16" t="str">
+        <x:v>A-企业官方校园招聘公告已核验</x:v>
       </x:c>
       <x:c r="Q68" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="54" customHeight="1">
       <x:c r="A69" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B69" s="4" t="str">
-        <x:v>智元机器人-优才计划</x:v>
+        <x:v>网易游戏雷火</x:v>
       </x:c>
       <x:c r="C69" s="4" t="str">
-        <x:v>具身智能/机器人</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D69" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E69" s="4" t="str">
-        <x:v>上海、北京、深圳等</x:v>
+        <x:v>杭州、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F69" s="4" t="str">
-        <x:v>优才专项/提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G69" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H69" s="4" t="str">
-        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
+        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
       </x:c>
       <x:c r="I69" s="15" t="str">
-        <x:v>https://www.agibot.com/recruit</x:v>
+        <x:v>https://leihuo.163.com/campus/#/full</x:v>
       </x:c>
       <x:c r="J69" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="K69" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>部分岗位免笔试；部分可直通面试</x:v>
       </x:c>
       <x:c r="L69" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M69" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N69" s="4" t="str"/>
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N69" s="4" t="str">
+        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
+      </x:c>
       <x:c r="O69" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P69" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P69" s="16" t="str">
+        <x:v>A-官方招聘官网已核验</x:v>
       </x:c>
       <x:c r="Q69" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4147,28 +4157,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B70" s="4" t="str">
-        <x:v>中国电信天翼云-超级优才</x:v>
+        <x:v>小鹏集团</x:v>
       </x:c>
       <x:c r="C70" s="4" t="str">
-        <x:v>云计算/央企</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D70" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E70" s="4" t="str">
-        <x:v>北京、上海、广州、成都及全国机构</x:v>
+        <x:v>广州、北京、上海、深圳、武汉等</x:v>
       </x:c>
       <x:c r="F70" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G70" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H70" s="4" t="str">
-        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
+        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
       </x:c>
       <x:c r="I70" s="15" t="str">
-        <x:v>https://www.ctyun.cn/about/recruit</x:v>
+        <x:v>https://join.xiaopeng.com/campus</x:v>
       </x:c>
       <x:c r="J70" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4183,7 +4193,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N70" s="4" t="str">
-        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
+        <x:v>营销服与技术岗位可能分项目发布。</x:v>
       </x:c>
       <x:c r="O70" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -4200,49 +4210,47 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B71" s="4" t="str">
-        <x:v>中科光电</x:v>
+        <x:v>芯动科技</x:v>
       </x:c>
       <x:c r="C71" s="4" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>半导体/IP设计</x:v>
       </x:c>
       <x:c r="D71" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E71" s="4" t="str">
-        <x:v>以职位公告为准</x:v>
+        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
       </x:c>
       <x:c r="F71" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G71" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H71" s="4" t="str">
-        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
+        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
       </x:c>
       <x:c r="I71" s="15" t="str">
-        <x:v>https://job.cn-amd.com/</x:v>
+        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
       </x:c>
       <x:c r="J71" s="4" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K71" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L71" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M71" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N71" s="4" t="str">
-        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
-      </x:c>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N71" s="4" t="str"/>
       <x:c r="O71" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P71" s="20" t="str">
-        <x:v>C-名称需二次确认</x:v>
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q71" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4250,108 +4258,108 @@
     </x:row>
     <x:row r="72" ht="54" customHeight="1">
       <x:c r="A72" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B72" s="4" t="str">
-        <x:v>中兴微电子-未来领军计划</x:v>
+        <x:v>芯迈半导体</x:v>
       </x:c>
       <x:c r="C72" s="4" t="str">
-        <x:v>半导体/通信</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D72" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E72" s="4" t="str">
-        <x:v>深圳、西安、南京、上海等</x:v>
+        <x:v>杭州、上海、深圳、成都</x:v>
       </x:c>
       <x:c r="F72" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G72" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H72" s="4" t="str">
-        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
+        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
       </x:c>
       <x:c r="I72" s="15" t="str">
-        <x:v>https://job.zte.com.cn/</x:v>
+        <x:v>https://www.silicon-magic.com/joinus</x:v>
       </x:c>
       <x:c r="J72" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K72" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未说明；公开流程未列笔试</x:v>
       </x:c>
       <x:c r="L72" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M72" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N72" s="4" t="str">
-        <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
+        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
       </x:c>
       <x:c r="O72" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P72" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P72" s="16" t="str">
+        <x:v>A-企业官网与公开公告已核验</x:v>
       </x:c>
       <x:c r="Q72" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="54" customHeight="1">
-      <x:c r="A73" s="18" t="str">
+      <x:c r="A73" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B73" s="18" t="str">
-        <x:v>字节跳动-AI产品经理早鸟通道</x:v>
-      </x:c>
-      <x:c r="C73" s="18" t="str">
-        <x:v>互联网/AI</x:v>
-      </x:c>
-      <x:c r="D73" s="18" t="str">
+      <x:c r="B73" s="4" t="str">
+        <x:v>新易盛</x:v>
+      </x:c>
+      <x:c r="C73" s="4" t="str">
+        <x:v>光通信/半导体</x:v>
+      </x:c>
+      <x:c r="D73" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E73" s="18" t="str">
-        <x:v>北京、上海、深圳</x:v>
-      </x:c>
-      <x:c r="F73" s="18" t="str">
-        <x:v>早鸟专项/提前批</x:v>
-      </x:c>
-      <x:c r="G73" s="18" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H73" s="18" t="str">
-        <x:v>AI产品经理、智能体及大模型产品方向</x:v>
-      </x:c>
-      <x:c r="I73" s="19" t="str">
-        <x:v>https://jobs.bytedance.com/campus/</x:v>
-      </x:c>
-      <x:c r="J73" s="18" t="str">
-        <x:v>2026-08-02</x:v>
-      </x:c>
-      <x:c r="K73" s="18" t="str">
-        <x:v>按岗位，未统一公布</x:v>
-      </x:c>
-      <x:c r="L73" s="18" t="str">
-        <x:v>已截止（2026-08-02）；原公告与官方投递入口保留</x:v>
-      </x:c>
-      <x:c r="M73" s="18" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N73" s="18" t="str">
-        <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
-      </x:c>
-      <x:c r="O73" s="19" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P73" s="16" t="str">
-        <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q73" s="18" t="str">
-        <x:v>2026-08-03</x:v>
+      <x:c r="E73" s="4" t="str">
+        <x:v>成都、苏州等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F73" s="4" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G73" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H73" s="4" t="str">
+        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
+      </x:c>
+      <x:c r="I73" s="15" t="str">
+        <x:v>https://www.eoptolink.com/</x:v>
+      </x:c>
+      <x:c r="J73" s="4" t="str">
+        <x:v>2026-08-20</x:v>
+      </x:c>
+      <x:c r="K73" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L73" s="4" t="str">
+        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
+      </x:c>
+      <x:c r="M73" s="4" t="str">
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N73" s="4" t="str">
+        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+      </x:c>
+      <x:c r="O73" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P73" s="14" t="str">
+        <x:v>B-高校/招聘平台转载，投前复核</x:v>
+      </x:c>
+      <x:c r="Q73" s="4" t="str">
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="54" customHeight="1">
@@ -4359,40 +4367,40 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B74" s="4" t="str">
-        <x:v>BCG波士顿咨询</x:v>
+        <x:v>元戎启行</x:v>
       </x:c>
       <x:c r="C74" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>自动驾驶</x:v>
       </x:c>
       <x:c r="D74" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E74" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>深圳、北京等</x:v>
       </x:c>
       <x:c r="F74" s="4" t="str">
-        <x:v>正式批/中国区校招</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G74" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H74" s="4" t="str">
-        <x:v>咨询顾问及相关专业岗位</x:v>
+        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
       </x:c>
       <x:c r="I74" s="15" t="str">
-        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
+        <x:v>https://www.deeproute.ai/join-us</x:v>
       </x:c>
       <x:c r="J74" s="4" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K74" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L74" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M74" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N74" s="4" t="str"/>
       <x:c r="O74" s="15" t="str">
@@ -4410,28 +4418,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B75" s="4" t="str">
-        <x:v>OPPO</x:v>
+        <x:v>圆通速递</x:v>
       </x:c>
       <x:c r="C75" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>物流/供应链</x:v>
       </x:c>
       <x:c r="D75" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E75" s="4" t="str">
-        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
+        <x:v>上海及全国网络</x:v>
       </x:c>
       <x:c r="F75" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
+        <x:v>正式批/校招</x:v>
       </x:c>
       <x:c r="G75" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H75" s="4" t="str">
-        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
+        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
       </x:c>
       <x:c r="I75" s="15" t="str">
-        <x:v>https://careers.oppo.com/campus</x:v>
+        <x:v>https://hr.yto.net.cn/</x:v>
       </x:c>
       <x:c r="J75" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4445,9 +4453,7 @@
       <x:c r="M75" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N75" s="4" t="str">
-        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
-      </x:c>
+      <x:c r="N75" s="4" t="str"/>
       <x:c r="O75" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -4463,34 +4469,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B76" s="4" t="str">
-        <x:v>Tap4Fun</x:v>
+        <x:v>长亭科技</x:v>
       </x:c>
       <x:c r="C76" s="4" t="str">
-        <x:v>游戏</x:v>
+        <x:v>网络安全</x:v>
       </x:c>
       <x:c r="D76" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E76" s="4" t="str">
-        <x:v>成都等</x:v>
+        <x:v>北京、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F76" s="4" t="str">
-        <x:v>实习转正通道</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G76" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H76" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
+        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
       </x:c>
       <x:c r="I76" s="15" t="str">
-        <x:v>https://www.tap4fun.com/careers</x:v>
+        <x:v>https://job.chaitin.cn/</x:v>
       </x:c>
       <x:c r="J76" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K76" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L76" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -4498,9 +4504,7 @@
       <x:c r="M76" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N76" s="4" t="str">
-        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
-      </x:c>
+      <x:c r="N76" s="4" t="str"/>
       <x:c r="O76" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -4513,370 +4517,366 @@
     </x:row>
     <x:row r="77" ht="54" customHeight="1">
       <x:c r="A77" s="4" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B77" s="4" t="str">
-        <x:v>航天科技集团五院502所</x:v>
+        <x:v>智元机器人-优才计划</x:v>
       </x:c>
       <x:c r="C77" s="4" t="str">
-        <x:v>航天/自动控制</x:v>
+        <x:v>具身智能/机器人</x:v>
       </x:c>
       <x:c r="D77" s="4" t="str">
-        <x:v>事业单位/央企院所</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E77" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>上海、北京、深圳等</x:v>
       </x:c>
       <x:c r="F77" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>优才专项/提前批</x:v>
       </x:c>
       <x:c r="G77" s="4" t="str">
-        <x:v>硕士/博士为主，以岗位为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H77" s="4" t="str">
-        <x:v>导航制导与控制、自动化、电子、通信、计算机、软件、机械等</x:v>
+        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
       </x:c>
       <x:c r="I77" s="15" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
+        <x:v>https://www.agibot.com/recruit</x:v>
       </x:c>
       <x:c r="J77" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K77" s="4" t="str">
-        <x:v>未统一公布</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L77" s="4" t="str">
-        <x:v>公开公告显示开放；投前确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M77" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N77" s="4" t="str">
-        <x:v>研究所岗位通常有专业、学历、政审及保密要求。</x:v>
-      </x:c>
+      <x:c r="N77" s="4" t="str"/>
       <x:c r="O77" s="15" t="str">
-        <x:v>https://www.baidu.com/s?wd=%E4%BA%94%E9%99%A2502%E6%89%802027%E5%B1%8A%E6%A0%A1%E6%8B%9B</x:v>
-      </x:c>
-      <x:c r="P77" s="16" t="str">
-        <x:v>B-高校就业网公开公告</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P77" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q77" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="54" customHeight="1">
-      <x:c r="A78" s="18" t="str">
-        <x:v>2026-07-17</x:v>
-      </x:c>
-      <x:c r="B78" s="18" t="str">
-        <x:v>鹰角网络</x:v>
-      </x:c>
-      <x:c r="C78" s="18" t="str">
-        <x:v>游戏</x:v>
-      </x:c>
-      <x:c r="D78" s="18" t="str">
+      <x:c r="A78" s="4" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B78" s="4" t="str">
+        <x:v>中国电信天翼云-超级优才</x:v>
+      </x:c>
+      <x:c r="C78" s="4" t="str">
+        <x:v>云计算/央企</x:v>
+      </x:c>
+      <x:c r="D78" s="4" t="str">
+        <x:v>央企</x:v>
+      </x:c>
+      <x:c r="E78" s="4" t="str">
+        <x:v>北京、上海、广州、成都及全国机构</x:v>
+      </x:c>
+      <x:c r="F78" s="4" t="str">
+        <x:v>人才专项/提前批</x:v>
+      </x:c>
+      <x:c r="G78" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H78" s="4" t="str">
+        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
+      </x:c>
+      <x:c r="I78" s="15" t="str">
+        <x:v>https://www.ctyun.cn/about/recruit</x:v>
+      </x:c>
+      <x:c r="J78" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K78" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L78" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M78" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N78" s="4" t="str">
+        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
+      </x:c>
+      <x:c r="O78" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P78" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q78" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="54" customHeight="1">
+      <x:c r="A79" s="14" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B79" s="14" t="str">
+        <x:v>中科光电</x:v>
+      </x:c>
+      <x:c r="C79" s="14" t="str">
+        <x:v>光电/科研</x:v>
+      </x:c>
+      <x:c r="D79" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E78" s="18" t="str">
-        <x:v>上海</x:v>
-      </x:c>
-      <x:c r="F78" s="18" t="str">
+      <x:c r="E79" s="14" t="str">
+        <x:v>以职位公告为准</x:v>
+      </x:c>
+      <x:c r="F79" s="14" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G78" s="18" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H78" s="18" t="str">
-        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
-      </x:c>
-      <x:c r="I78" s="19" t="str">
-        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
-      </x:c>
-      <x:c r="J78" s="18" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K78" s="18" t="str">
-        <x:v>否；安排笔试/面试</x:v>
-      </x:c>
-      <x:c r="L78" s="18" t="str">
-        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M78" s="18" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N78" s="18" t="str">
-        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
-      </x:c>
-      <x:c r="O78" s="19" t="str">
-        <x:v>https://campus.hypergryph.com/</x:v>
-      </x:c>
-      <x:c r="P78" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q78" s="18" t="str">
-        <x:v>2026-08-03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" ht="54" customHeight="1">
-      <x:c r="A79" s="4" t="str">
-        <x:v>2026-07-16</x:v>
-      </x:c>
-      <x:c r="B79" s="4" t="str">
-        <x:v>联发科技</x:v>
-      </x:c>
-      <x:c r="C79" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
-      </x:c>
-      <x:c r="D79" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E79" s="4" t="str">
-        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
-      </x:c>
-      <x:c r="F79" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G79" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H79" s="4" t="str">
-        <x:v>软件类、通信类、IC类</x:v>
-      </x:c>
-      <x:c r="I79" s="15" t="str">
-        <x:v>https://mediatek.zhiye.com/</x:v>
-      </x:c>
-      <x:c r="J79" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K79" s="4" t="str">
-        <x:v>否；明确安排7-8月笔试</x:v>
-      </x:c>
-      <x:c r="L79" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M79" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N79" s="4" t="str">
-        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
-      </x:c>
-      <x:c r="O79" s="15" t="str">
+      <x:c r="G79" s="14" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H79" s="14" t="str">
+        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
+      </x:c>
+      <x:c r="I79" s="17" t="str">
+        <x:v>https://job.cn-amd.com/</x:v>
+      </x:c>
+      <x:c r="J79" s="14" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="K79" s="14" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L79" s="14" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M79" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N79" s="14" t="str">
+        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
+      </x:c>
+      <x:c r="O79" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P79" s="14" t="str">
-        <x:v>A-官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q79" s="4" t="str">
+      <x:c r="P79" s="20" t="str">
+        <x:v>C-名称需二次确认</x:v>
+      </x:c>
+      <x:c r="Q79" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="54" customHeight="1">
       <x:c r="A80" s="4" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B80" s="4" t="str">
-        <x:v>DJI大疆</x:v>
+        <x:v>中兴微电子-未来领军计划</x:v>
       </x:c>
       <x:c r="C80" s="4" t="str">
-        <x:v>无人机/智能硬件</x:v>
+        <x:v>半导体/通信</x:v>
       </x:c>
       <x:c r="D80" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E80" s="4" t="str">
-        <x:v>深圳、东莞、上海、北京、西安等</x:v>
+        <x:v>深圳、西安、南京、上海等</x:v>
       </x:c>
       <x:c r="F80" s="4" t="str">
-        <x:v>正式批-拓疆者计划</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G80" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H80" s="4" t="str">
-        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
+        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
       </x:c>
       <x:c r="I80" s="15" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
+        <x:v>https://job.zte.com.cn/</x:v>
       </x:c>
       <x:c r="J80" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K80" s="4" t="str">
-        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L80" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M80" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N80" s="4" t="str">
-        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
+        <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
       </x:c>
       <x:c r="O80" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P80" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
+      <x:c r="P80" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q80" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="54" customHeight="1">
-      <x:c r="A81" s="4" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="B81" s="4" t="str">
-        <x:v>蔚来</x:v>
-      </x:c>
-      <x:c r="C81" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
-      </x:c>
-      <x:c r="D81" s="4" t="str">
+      <x:c r="A81" s="18" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B81" s="18" t="str">
+        <x:v>字节跳动-AI产品经理早鸟通道</x:v>
+      </x:c>
+      <x:c r="C81" s="18" t="str">
+        <x:v>互联网/AI</x:v>
+      </x:c>
+      <x:c r="D81" s="18" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E81" s="4" t="str">
-        <x:v>上海、合肥、北京、武汉、南京等</x:v>
-      </x:c>
-      <x:c r="F81" s="4" t="str">
-        <x:v>技术提前批</x:v>
-      </x:c>
-      <x:c r="G81" s="4" t="str">
-        <x:v>2024年9月-2027年8月毕业</x:v>
-      </x:c>
-      <x:c r="H81" s="4" t="str">
-        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
-      </x:c>
-      <x:c r="I81" s="15" t="str">
-        <x:v>https://campus.nio.com/</x:v>
-      </x:c>
-      <x:c r="J81" s="4" t="str">
-        <x:v>2026-08-14</x:v>
-      </x:c>
-      <x:c r="K81" s="4" t="str">
-        <x:v>否；有笔试/测评</x:v>
-      </x:c>
-      <x:c r="L81" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M81" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N81" s="4" t="str">
-        <x:v>最多同时申请3个岗位。</x:v>
-      </x:c>
-      <x:c r="O81" s="15" t="str">
+      <x:c r="E81" s="18" t="str">
+        <x:v>北京、上海、深圳</x:v>
+      </x:c>
+      <x:c r="F81" s="18" t="str">
+        <x:v>早鸟专项/提前批</x:v>
+      </x:c>
+      <x:c r="G81" s="18" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H81" s="18" t="str">
+        <x:v>AI产品经理、智能体及大模型产品方向</x:v>
+      </x:c>
+      <x:c r="I81" s="19" t="str">
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
+      </x:c>
+      <x:c r="J81" s="18" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+      <x:c r="K81" s="18" t="str">
+        <x:v>按岗位，未统一公布</x:v>
+      </x:c>
+      <x:c r="L81" s="18" t="str">
+        <x:v>已截止（2026-08-02）；原公告与官方投递入口保留</x:v>
+      </x:c>
+      <x:c r="M81" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N81" s="18" t="str">
+        <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
+      </x:c>
+      <x:c r="O81" s="19" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P81" s="14" t="str">
+        <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q81" s="18" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="54" customHeight="1">
+      <x:c r="A82" s="14" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B82" s="14" t="str">
+        <x:v>BCG波士顿咨询</x:v>
+      </x:c>
+      <x:c r="C82" s="14" t="str">
+        <x:v>管理咨询</x:v>
+      </x:c>
+      <x:c r="D82" s="14" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E82" s="14" t="str">
+        <x:v>北京、上海、深圳、香港等</x:v>
+      </x:c>
+      <x:c r="F82" s="14" t="str">
+        <x:v>正式批/中国区校招</x:v>
+      </x:c>
+      <x:c r="G82" s="14" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H82" s="14" t="str">
+        <x:v>咨询顾问及相关专业岗位</x:v>
+      </x:c>
+      <x:c r="I82" s="17" t="str">
+        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
+      </x:c>
+      <x:c r="J82" s="14" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="K82" s="14" t="str">
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+      </x:c>
+      <x:c r="L82" s="14" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M82" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N82" s="14" t="str"/>
+      <x:c r="O82" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P81" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q81" s="4" t="str">
+      <x:c r="P82" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q82" s="14" t="str">
         <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" ht="54" customHeight="1">
-      <x:c r="A82" s="4" t="str">
-        <x:v>2026-07-10</x:v>
-      </x:c>
-      <x:c r="B82" s="4" t="str">
-        <x:v>北方华创</x:v>
-      </x:c>
-      <x:c r="C82" s="4" t="str">
-        <x:v>半导体设备</x:v>
-      </x:c>
-      <x:c r="D82" s="4" t="str">
-        <x:v>国企/上市</x:v>
-      </x:c>
-      <x:c r="E82" s="4" t="str">
-        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F82" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G82" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H82" s="4" t="str">
-        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
-      </x:c>
-      <x:c r="I82" s="15" t="str">
-        <x:v>https://career.naura.com/campus</x:v>
-      </x:c>
-      <x:c r="J82" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K82" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L82" s="4" t="str">
-        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
-      </x:c>
-      <x:c r="M82" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N82" s="4" t="str">
-        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
-      </x:c>
-      <x:c r="O82" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P82" s="14" t="str">
-        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
-      </x:c>
-      <x:c r="Q82" s="4" t="str">
-        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="54" customHeight="1">
       <x:c r="A83" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B83" s="4" t="str">
-        <x:v>百度</x:v>
+        <x:v>OPPO</x:v>
       </x:c>
       <x:c r="C83" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D83" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E83" s="4" t="str">
-        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
       </x:c>
       <x:c r="F83" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G83" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H83" s="4" t="str">
-        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
       </x:c>
       <x:c r="I83" s="15" t="str">
-        <x:v>https://talent.baidu.com/jobs</x:v>
+        <x:v>https://careers.oppo.com/campus</x:v>
       </x:c>
       <x:c r="J83" s="4" t="str">
-        <x:v>2027-06-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K83" s="4" t="str">
-        <x:v>部分免；并非所有候选人参加笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L83" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M83" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N83" s="4" t="str">
-        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
+        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
       </x:c>
       <x:c r="O83" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P83" s="14" t="str">
-        <x:v>A-官方招聘日历/官方来源已核验</x:v>
+      <x:c r="P83" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q83" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4884,423 +4884,423 @@
     </x:row>
     <x:row r="84" ht="54" customHeight="1">
       <x:c r="A84" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B84" s="4" t="str">
-        <x:v>中国航天科工集团第六研究院</x:v>
+        <x:v>Tap4Fun</x:v>
       </x:c>
       <x:c r="C84" s="4" t="str">
-        <x:v>航天/军工/动力系统</x:v>
+        <x:v>游戏</x:v>
       </x:c>
       <x:c r="D84" s="4" t="str">
-        <x:v>央企院所</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E84" s="4" t="str">
-        <x:v>呼和浩特及所属单位</x:v>
+        <x:v>成都等</x:v>
       </x:c>
       <x:c r="F84" s="4" t="str">
-        <x:v>提前批+暑期开放日</x:v>
+        <x:v>实习转正通道</x:v>
       </x:c>
       <x:c r="G84" s="4" t="str">
-        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H84" s="4" t="str">
-        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
+        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
       </x:c>
       <x:c r="I84" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
+        <x:v>https://www.tap4fun.com/careers</x:v>
       </x:c>
       <x:c r="J84" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K84" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L84" s="4" t="str">
-        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M84" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N84" s="4" t="str">
-        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
+        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
       </x:c>
       <x:c r="O84" s="15" t="str">
-        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
-      </x:c>
-      <x:c r="P84" s="16" t="str">
-        <x:v>B-高校就业网公开公告</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P84" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q84" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="54" customHeight="1">
       <x:c r="A85" s="4" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="B85" s="4" t="str">
-        <x:v>思瑞浦</x:v>
+        <x:v>航天科技集团五院502所</x:v>
       </x:c>
       <x:c r="C85" s="4" t="str">
-        <x:v>半导体/模拟IC</x:v>
+        <x:v>航天/自动控制</x:v>
       </x:c>
       <x:c r="D85" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>事业单位/央企院所</x:v>
       </x:c>
       <x:c r="E85" s="4" t="str">
-        <x:v>上海、深圳等，以岗位页为准</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F85" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G85" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>硕士/博士为主，以岗位为准</x:v>
       </x:c>
       <x:c r="H85" s="4" t="str">
-        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
+        <x:v>导航制导与控制、自动化、电子、通信、计算机、软件、机械等</x:v>
       </x:c>
       <x:c r="I85" s="15" t="str">
-        <x:v>https://www.3peak.cn/careers</x:v>
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J85" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K85" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>未统一公布</x:v>
       </x:c>
       <x:c r="L85" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
+        <x:v>公开公告显示开放；投前确认</x:v>
       </x:c>
       <x:c r="M85" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N85" s="4" t="str">
-        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
+        <x:v>研究所岗位通常有专业、学历、政审及保密要求。</x:v>
       </x:c>
       <x:c r="O85" s="15" t="str">
-        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
-      </x:c>
-      <x:c r="P85" s="16" t="str">
-        <x:v>B-招聘平台/高校就业转载</x:v>
+        <x:v>https://www.baidu.com/s?wd=%E4%BA%94%E9%99%A2502%E6%89%802027%E5%B1%8A%E6%A0%A1%E6%8B%9B</x:v>
+      </x:c>
+      <x:c r="P85" s="14" t="str">
+        <x:v>B-高校就业网公开公告</x:v>
       </x:c>
       <x:c r="Q85" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="54" customHeight="1">
-      <x:c r="A86" s="4" t="str">
-        <x:v>不晚于2026-07-07</x:v>
-      </x:c>
-      <x:c r="B86" s="4" t="str">
-        <x:v>文远知行WeRide</x:v>
-      </x:c>
-      <x:c r="C86" s="4" t="str">
-        <x:v>自动驾驶/人工智能</x:v>
-      </x:c>
-      <x:c r="D86" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E86" s="4" t="str">
-        <x:v>广州、深圳、武汉等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F86" s="4" t="str">
-        <x:v>正式批/校招/可转正实习</x:v>
-      </x:c>
-      <x:c r="G86" s="4" t="str">
-        <x:v>2027届应届毕业生及可转正实习生，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H86" s="4" t="str">
-        <x:v>感知/预测/规划控制算法、算法测试、测试开发、SRE、云与车端安全、AI Infra、仿真平台等</x:v>
-      </x:c>
-      <x:c r="I86" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
-      </x:c>
-      <x:c r="J86" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K86" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L86" s="4" t="str">
-        <x:v>企业官方校招系统在招；已核验137个职位</x:v>
-      </x:c>
-      <x:c r="M86" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N86" s="4" t="str">
-        <x:v>官方列表显示2027届校招职位最早发布于7月7日；部分岗位为可转正实习，城市和岗位随招聘系统实时调整。</x:v>
-      </x:c>
-      <x:c r="O86" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
-      </x:c>
-      <x:c r="P86" s="14" t="str">
-        <x:v>A-企业官方校招系统与职位列表已核验</x:v>
-      </x:c>
-      <x:c r="Q86" s="4" t="str">
+      <x:c r="A86" s="18" t="str">
+        <x:v>2026-07-17</x:v>
+      </x:c>
+      <x:c r="B86" s="18" t="str">
+        <x:v>鹰角网络</x:v>
+      </x:c>
+      <x:c r="C86" s="18" t="str">
+        <x:v>游戏</x:v>
+      </x:c>
+      <x:c r="D86" s="18" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E86" s="18" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F86" s="18" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G86" s="18" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H86" s="18" t="str">
+        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
+      </x:c>
+      <x:c r="I86" s="19" t="str">
+        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
+      </x:c>
+      <x:c r="J86" s="18" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K86" s="18" t="str">
+        <x:v>否；安排笔试/面试</x:v>
+      </x:c>
+      <x:c r="L86" s="18" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M86" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N86" s="18" t="str">
+        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
+      </x:c>
+      <x:c r="O86" s="19" t="str">
+        <x:v>https://campus.hypergryph.com/</x:v>
+      </x:c>
+      <x:c r="P86" s="16" t="str">
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q86" s="18" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="54" customHeight="1">
-      <x:c r="A87" s="18" t="str">
-        <x:v>2026-07-06</x:v>
-      </x:c>
-      <x:c r="B87" s="18" t="str">
-        <x:v>米哈游</x:v>
-      </x:c>
-      <x:c r="C87" s="18" t="str">
-        <x:v>游戏/互联网</x:v>
-      </x:c>
-      <x:c r="D87" s="18" t="str">
+      <x:c r="A87" s="4" t="str">
+        <x:v>2026-07-16</x:v>
+      </x:c>
+      <x:c r="B87" s="4" t="str">
+        <x:v>联发科技</x:v>
+      </x:c>
+      <x:c r="C87" s="4" t="str">
+        <x:v>半导体/IC设计</x:v>
+      </x:c>
+      <x:c r="D87" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E87" s="18" t="str">
-        <x:v>上海、北京</x:v>
-      </x:c>
-      <x:c r="F87" s="18" t="str">
-        <x:v>技术提前批</x:v>
-      </x:c>
-      <x:c r="G87" s="18" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H87" s="18" t="str">
-        <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
-      </x:c>
-      <x:c r="I87" s="19" t="str">
-        <x:v>https://campus.mihoyo.com/</x:v>
-      </x:c>
-      <x:c r="J87" s="18" t="str">
-        <x:v>2026-07-27</x:v>
-      </x:c>
-      <x:c r="K87" s="18" t="str">
-        <x:v>有免笔试直通面试机会</x:v>
-      </x:c>
-      <x:c r="L87" s="18" t="str">
-        <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
-      </x:c>
-      <x:c r="M87" s="18" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N87" s="18" t="str">
-        <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
-      </x:c>
-      <x:c r="O87" s="19" t="str">
+      <x:c r="E87" s="4" t="str">
+        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
+      </x:c>
+      <x:c r="F87" s="4" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G87" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H87" s="4" t="str">
+        <x:v>软件类、通信类、IC类</x:v>
+      </x:c>
+      <x:c r="I87" s="15" t="str">
+        <x:v>https://mediatek.zhiye.com/</x:v>
+      </x:c>
+      <x:c r="J87" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K87" s="4" t="str">
+        <x:v>否；明确安排7-8月笔试</x:v>
+      </x:c>
+      <x:c r="L87" s="4" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M87" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N87" s="4" t="str">
+        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
+      </x:c>
+      <x:c r="O87" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P87" s="14" t="str">
+      <x:c r="P87" s="16" t="str">
         <x:v>A-官方招聘公告已核验</x:v>
       </x:c>
-      <x:c r="Q87" s="18" t="str">
-        <x:v>2026-07-30</x:v>
+      <x:c r="Q87" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="54" customHeight="1">
       <x:c r="A88" s="4" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B88" s="4" t="str">
-        <x:v>京东方-先锋京英计划</x:v>
+        <x:v>DJI大疆</x:v>
       </x:c>
       <x:c r="C88" s="4" t="str">
-        <x:v>显示技术/半导体/物联网</x:v>
+        <x:v>无人机/智能硬件</x:v>
       </x:c>
       <x:c r="D88" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E88" s="4" t="str">
-        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
+        <x:v>深圳、东莞、上海、北京、西安等</x:v>
       </x:c>
       <x:c r="F88" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批-拓疆者计划</x:v>
       </x:c>
       <x:c r="G88" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H88" s="4" t="str">
-        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
+        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
       </x:c>
       <x:c r="I88" s="15" t="str">
-        <x:v>https://campus.boe.com/</x:v>
+        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
       </x:c>
       <x:c r="J88" s="4" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K88" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
       </x:c>
       <x:c r="L88" s="4" t="str">
         <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M88" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N88" s="4" t="str">
-        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
+        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
       </x:c>
       <x:c r="O88" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P88" s="14" t="str">
-        <x:v>A-国家大学生就业平台公告已核验</x:v>
+      <x:c r="P88" s="16" t="str">
+        <x:v>A-官方来源公告已核验</x:v>
       </x:c>
       <x:c r="Q88" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="54" customHeight="1">
-      <x:c r="A89" s="4" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="B89" s="4" t="str">
-        <x:v>中国航天科技集团</x:v>
-      </x:c>
-      <x:c r="C89" s="4" t="str">
-        <x:v>航天/军工</x:v>
-      </x:c>
-      <x:c r="D89" s="4" t="str">
-        <x:v>央企</x:v>
-      </x:c>
-      <x:c r="E89" s="4" t="str">
-        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
-      </x:c>
-      <x:c r="F89" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G89" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H89" s="4" t="str">
-        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
-      </x:c>
-      <x:c r="I89" s="15" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
-      </x:c>
-      <x:c r="J89" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K89" s="4" t="str">
-        <x:v>各院所自行组织，未统一</x:v>
-      </x:c>
-      <x:c r="L89" s="4" t="str">
-        <x:v>官方公告已确认启动</x:v>
-      </x:c>
-      <x:c r="M89" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N89" s="4" t="str">
-        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
-      </x:c>
-      <x:c r="O89" s="15" t="str">
-        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
-      </x:c>
-      <x:c r="P89" s="14" t="str">
-        <x:v>A-国务院国资委/集团官方来源</x:v>
-      </x:c>
-      <x:c r="Q89" s="4" t="str">
+      <x:c r="A89" s="14" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="B89" s="14" t="str">
+        <x:v>蔚来</x:v>
+      </x:c>
+      <x:c r="C89" s="14" t="str">
+        <x:v>新能源汽车/智能汽车</x:v>
+      </x:c>
+      <x:c r="D89" s="14" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E89" s="14" t="str">
+        <x:v>上海、合肥、北京、武汉、南京等</x:v>
+      </x:c>
+      <x:c r="F89" s="14" t="str">
+        <x:v>技术提前批</x:v>
+      </x:c>
+      <x:c r="G89" s="14" t="str">
+        <x:v>2024年9月-2027年8月毕业</x:v>
+      </x:c>
+      <x:c r="H89" s="14" t="str">
+        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
+      </x:c>
+      <x:c r="I89" s="17" t="str">
+        <x:v>https://campus.nio.com/</x:v>
+      </x:c>
+      <x:c r="J89" s="14" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="K89" s="14" t="str">
+        <x:v>否；有笔试/测评</x:v>
+      </x:c>
+      <x:c r="L89" s="14" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M89" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N89" s="14" t="str">
+        <x:v>最多同时申请3个岗位。</x:v>
+      </x:c>
+      <x:c r="O89" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P89" s="16" t="str">
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q89" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="54" customHeight="1">
       <x:c r="A90" s="4" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="B90" s="4" t="str">
-        <x:v>高途</x:v>
+        <x:v>北方华创</x:v>
       </x:c>
       <x:c r="C90" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>半导体设备</x:v>
       </x:c>
       <x:c r="D90" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E90" s="4" t="str">
-        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
+        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F90" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G90" s="4" t="str">
-        <x:v>27届为主，优秀28届也可投</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H90" s="4" t="str">
-        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
+        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
       </x:c>
       <x:c r="I90" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
+        <x:v>https://career.naura.com/campus</x:v>
       </x:c>
       <x:c r="J90" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K90" s="4" t="str">
-        <x:v>否；流程包含笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L90" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
       </x:c>
       <x:c r="M90" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N90" s="4" t="str">
-        <x:v>滚动发放Offer，截止时间未公布。</x:v>
+        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
       </x:c>
       <x:c r="O90" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P90" s="14" t="str">
-        <x:v>A-官方投递平台已核验</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P90" s="16" t="str">
+        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
       </x:c>
       <x:c r="Q90" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="54" customHeight="1">
       <x:c r="A91" s="4" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B91" s="4" t="str">
-        <x:v>中汽中心</x:v>
+        <x:v>百度</x:v>
       </x:c>
       <x:c r="C91" s="4" t="str">
-        <x:v>汽车检测/科研</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D91" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E91" s="4" t="str">
-        <x:v>天津、武汉、北京、上海等</x:v>
+        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
       </x:c>
       <x:c r="F91" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G91" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H91" s="4" t="str">
-        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
+        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
       </x:c>
       <x:c r="I91" s="15" t="str">
-        <x:v>https://www.catarc.ac.cn/</x:v>
+        <x:v>https://talent.baidu.com/jobs</x:v>
       </x:c>
       <x:c r="J91" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-30</x:v>
       </x:c>
       <x:c r="K91" s="4" t="str">
-        <x:v>官方未统一说明</x:v>
+        <x:v>部分免；并非所有候选人参加笔试</x:v>
       </x:c>
       <x:c r="L91" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M91" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N91" s="4" t="str">
-        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
+        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
       </x:c>
       <x:c r="O91" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P91" s="16" t="str">
-        <x:v>B-公开招聘公告</x:v>
+        <x:v>A-官方招聘日历/官方来源已核验</x:v>
       </x:c>
       <x:c r="Q91" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5308,28 +5308,28 @@
     </x:row>
     <x:row r="92" ht="54" customHeight="1">
       <x:c r="A92" s="4" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B92" s="4" t="str">
-        <x:v>中国航天科工集团</x:v>
+        <x:v>中国航天科工集团第六研究院</x:v>
       </x:c>
       <x:c r="C92" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>航天/军工/动力系统</x:v>
       </x:c>
       <x:c r="D92" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>央企院所</x:v>
       </x:c>
       <x:c r="E92" s="4" t="str">
-        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
+        <x:v>呼和浩特及所属单位</x:v>
       </x:c>
       <x:c r="F92" s="4" t="str">
-        <x:v>正式批/提前批</x:v>
+        <x:v>提前批+暑期开放日</x:v>
       </x:c>
       <x:c r="G92" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
       </x:c>
       <x:c r="H92" s="4" t="str">
-        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
+        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
       </x:c>
       <x:c r="I92" s="15" t="str">
         <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
@@ -5341,19 +5341,19 @@
         <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L92" s="4" t="str">
-        <x:v>官网公告已确认启动</x:v>
+        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
       </x:c>
       <x:c r="M92" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N92" s="4" t="str">
-        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
+        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
       </x:c>
       <x:c r="O92" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
+        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
       </x:c>
       <x:c r="P92" s="14" t="str">
-        <x:v>A-集团官网公告已核验</x:v>
+        <x:v>B-高校就业网公开公告</x:v>
       </x:c>
       <x:c r="Q92" s="4" t="str">
         <x:v>2026-07-27</x:v>
@@ -5361,84 +5361,84 @@
     </x:row>
     <x:row r="93" ht="54" customHeight="1">
       <x:c r="A93" s="4" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-07-08</x:v>
       </x:c>
       <x:c r="B93" s="4" t="str">
-        <x:v>禾赛科技</x:v>
+        <x:v>思瑞浦</x:v>
       </x:c>
       <x:c r="C93" s="4" t="str">
-        <x:v>激光雷达/机器人</x:v>
+        <x:v>半导体/模拟IC</x:v>
       </x:c>
       <x:c r="D93" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E93" s="4" t="str">
-        <x:v>上海、杭州</x:v>
+        <x:v>上海、深圳等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F93" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G93" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H93" s="4" t="str">
-        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
+        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
       </x:c>
       <x:c r="I93" s="15" t="str">
-        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
+        <x:v>https://www.3peak.cn/careers</x:v>
       </x:c>
       <x:c r="J93" s="4" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K93" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L93" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
       </x:c>
       <x:c r="M93" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N93" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
       </x:c>
       <x:c r="O93" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P93" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
+      </x:c>
+      <x:c r="P93" s="14" t="str">
+        <x:v>B-招聘平台/高校就业转载</x:v>
       </x:c>
       <x:c r="Q93" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="54" customHeight="1">
       <x:c r="A94" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>不晚于2026-07-07</x:v>
       </x:c>
       <x:c r="B94" s="4" t="str">
-        <x:v>北京国望光学科技有限公司</x:v>
+        <x:v>文远知行WeRide</x:v>
       </x:c>
       <x:c r="C94" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>自动驾驶/人工智能</x:v>
       </x:c>
       <x:c r="D94" s="4" t="str">
-        <x:v>央国企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E94" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>广州、深圳、武汉等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F94" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批/校招/可转正实习</x:v>
       </x:c>
       <x:c r="G94" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届毕业生及可转正实习生，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H94" s="4" t="str">
-        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
-      </x:c>
-      <x:c r="I94" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>感知/预测/规划控制算法、算法测试、测试开发、SRE、云与车端安全、AI Infra、仿真平台等</x:v>
+      </x:c>
+      <x:c r="I94" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
       </x:c>
       <x:c r="J94" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5447,145 +5447,145 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L94" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>企业官方校招系统在招；已核验137个职位</x:v>
       </x:c>
       <x:c r="M94" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N94" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>官方列表显示2027届校招职位最早发布于7月7日；部分岗位为可转正实习，城市和岗位随招聘系统实时调整。</x:v>
       </x:c>
       <x:c r="O94" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
       </x:c>
       <x:c r="P94" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>A-企业官方校招系统与职位列表已核验</x:v>
       </x:c>
       <x:c r="Q94" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="54" customHeight="1">
-      <x:c r="A95" s="4" t="str">
-        <x:v>2026-06-17</x:v>
-      </x:c>
-      <x:c r="B95" s="4" t="str">
-        <x:v>乐读</x:v>
-      </x:c>
-      <x:c r="C95" s="4" t="str">
-        <x:v>教育科技</x:v>
-      </x:c>
-      <x:c r="D95" s="4" t="str">
+      <x:c r="A95" s="18" t="str">
+        <x:v>2026-07-06</x:v>
+      </x:c>
+      <x:c r="B95" s="18" t="str">
+        <x:v>米哈游</x:v>
+      </x:c>
+      <x:c r="C95" s="18" t="str">
+        <x:v>游戏/互联网</x:v>
+      </x:c>
+      <x:c r="D95" s="18" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E95" s="4" t="str">
-        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
-      </x:c>
-      <x:c r="F95" s="4" t="str">
+      <x:c r="E95" s="18" t="str">
+        <x:v>上海、北京</x:v>
+      </x:c>
+      <x:c r="F95" s="18" t="str">
+        <x:v>技术提前批</x:v>
+      </x:c>
+      <x:c r="G95" s="18" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H95" s="18" t="str">
+        <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
+      </x:c>
+      <x:c r="I95" s="19" t="str">
+        <x:v>https://campus.mihoyo.com/</x:v>
+      </x:c>
+      <x:c r="J95" s="18" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+      <x:c r="K95" s="18" t="str">
+        <x:v>有免笔试直通面试机会</x:v>
+      </x:c>
+      <x:c r="L95" s="18" t="str">
+        <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
+      </x:c>
+      <x:c r="M95" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N95" s="18" t="str">
+        <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
+      </x:c>
+      <x:c r="O95" s="19" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P95" s="16" t="str">
+        <x:v>A-官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q95" s="18" t="str">
+        <x:v>2026-07-30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="54" customHeight="1">
+      <x:c r="A96" s="14" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="B96" s="14" t="str">
+        <x:v>京东方-先锋京英计划</x:v>
+      </x:c>
+      <x:c r="C96" s="14" t="str">
+        <x:v>显示技术/半导体/物联网</x:v>
+      </x:c>
+      <x:c r="D96" s="14" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E96" s="14" t="str">
+        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
+      </x:c>
+      <x:c r="F96" s="14" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G95" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H95" s="4" t="str">
-        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
-      </x:c>
-      <x:c r="I95" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
-      </x:c>
-      <x:c r="J95" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K95" s="4" t="str">
+      <x:c r="G96" s="14" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H96" s="14" t="str">
+        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
+      </x:c>
+      <x:c r="I96" s="17" t="str">
+        <x:v>https://campus.boe.com/</x:v>
+      </x:c>
+      <x:c r="J96" s="14" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="K96" s="14" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
-      <x:c r="L95" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
-      </x:c>
-      <x:c r="M95" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N95" s="4" t="str">
-        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
-      </x:c>
-      <x:c r="O95" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P95" s="16" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
-      </x:c>
-      <x:c r="Q95" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="54" customHeight="1">
-      <x:c r="A96" s="4" t="str">
-        <x:v>2026-06-17</x:v>
-      </x:c>
-      <x:c r="B96" s="4" t="str">
-        <x:v>龙蟠科技</x:v>
-      </x:c>
-      <x:c r="C96" s="4" t="str">
-        <x:v>新能源材料/化工</x:v>
-      </x:c>
-      <x:c r="D96" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E96" s="4" t="str">
-        <x:v>南京</x:v>
-      </x:c>
-      <x:c r="F96" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G96" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H96" s="4" t="str">
-        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
-      </x:c>
-      <x:c r="I96" s="15" t="str">
-        <x:v>https://www.lopal.com.cn/join</x:v>
-      </x:c>
-      <x:c r="J96" s="4" t="str">
-        <x:v>2027-06-01</x:v>
-      </x:c>
-      <x:c r="K96" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L96" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
-      </x:c>
-      <x:c r="M96" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
-      </x:c>
-      <x:c r="N96" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
-      </x:c>
-      <x:c r="O96" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      <x:c r="L96" s="14" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M96" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N96" s="14" t="str">
+        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
+      </x:c>
+      <x:c r="O96" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P96" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q96" s="4" t="str">
+        <x:v>A-国家大学生就业平台公告已核验</x:v>
+      </x:c>
+      <x:c r="Q96" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="54" customHeight="1">
       <x:c r="A97" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="B97" s="4" t="str">
-        <x:v>牧原</x:v>
+        <x:v>中国航天科技集团</x:v>
       </x:c>
       <x:c r="C97" s="4" t="str">
-        <x:v>农业/食品/智能养殖</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D97" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E97" s="4" t="str">
-        <x:v>河南南阳及全国</x:v>
+        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
       </x:c>
       <x:c r="F97" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5594,31 +5594,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H97" s="4" t="str">
-        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
+        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
       </x:c>
       <x:c r="I97" s="15" t="str">
-        <x:v>https://job.muyuanfoods.com/</x:v>
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J97" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K97" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各院所自行组织，未统一</x:v>
       </x:c>
       <x:c r="L97" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>官方公告已确认启动</x:v>
       </x:c>
       <x:c r="M97" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N97" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
       </x:c>
       <x:c r="O97" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
       </x:c>
       <x:c r="P97" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>A-国务院国资委/集团官方来源</x:v>
       </x:c>
       <x:c r="Q97" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5626,52 +5626,52 @@
     </x:row>
     <x:row r="98" ht="54" customHeight="1">
       <x:c r="A98" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="B98" s="4" t="str">
-        <x:v>三一集团-小语种校招</x:v>
+        <x:v>高途</x:v>
       </x:c>
       <x:c r="C98" s="4" t="str">
-        <x:v>工程机械/制造</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D98" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E98" s="4" t="str">
-        <x:v>海外多国</x:v>
+        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
       </x:c>
       <x:c r="F98" s="4" t="str">
-        <x:v>小语种专项/正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G98" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>27届为主，优秀28届也可投</x:v>
       </x:c>
       <x:c r="H98" s="4" t="str">
-        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
+        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
       </x:c>
       <x:c r="I98" s="15" t="str">
-        <x:v>https://sanycampus.zhiye.com/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
       </x:c>
       <x:c r="J98" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K98" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；流程包含笔试</x:v>
       </x:c>
       <x:c r="L98" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M98" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N98" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>滚动发放Offer，截止时间未公布。</x:v>
       </x:c>
       <x:c r="O98" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P98" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>A-官方投递平台已核验</x:v>
       </x:c>
       <x:c r="Q98" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5679,52 +5679,52 @@
     </x:row>
     <x:row r="99" ht="54" customHeight="1">
       <x:c r="A99" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="B99" s="4" t="str">
-        <x:v>上海电气-暑期精英训练营</x:v>
+        <x:v>中汽中心</x:v>
       </x:c>
       <x:c r="C99" s="4" t="str">
-        <x:v>高端装备/能源</x:v>
+        <x:v>汽车检测/科研</x:v>
       </x:c>
       <x:c r="D99" s="4" t="str">
-        <x:v>地方国企</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E99" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>天津、武汉、北京、上海等</x:v>
       </x:c>
       <x:c r="F99" s="4" t="str">
-        <x:v>训练营/秋招直通</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G99" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H99" s="4" t="str">
-        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
+        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
       </x:c>
       <x:c r="I99" s="15" t="str">
-        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
+        <x:v>https://www.catarc.ac.cn/</x:v>
       </x:c>
       <x:c r="J99" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K99" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L99" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M99" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N99" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
       </x:c>
       <x:c r="O99" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P99" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
+      </x:c>
+      <x:c r="P99" s="14" t="str">
+        <x:v>B-公开招聘公告</x:v>
       </x:c>
       <x:c r="Q99" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5732,87 +5732,87 @@
     </x:row>
     <x:row r="100" ht="54" customHeight="1">
       <x:c r="A100" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="B100" s="4" t="str">
-        <x:v>vivo-蓝极星计划</x:v>
+        <x:v>中国航天科工集团</x:v>
       </x:c>
       <x:c r="C100" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D100" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E100" s="4" t="str">
-        <x:v>深圳、杭州、东莞、上海</x:v>
+        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
       </x:c>
       <x:c r="F100" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批/提前批</x:v>
       </x:c>
       <x:c r="G100" s="4" t="str">
-        <x:v>博士为主</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H100" s="4" t="str">
-        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
+        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
       </x:c>
       <x:c r="I100" s="15" t="str">
-        <x:v>https://hr.vivo.com/</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
       <x:c r="J100" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K100" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L100" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>官网公告已确认启动</x:v>
       </x:c>
       <x:c r="M100" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N100" s="4" t="str">
-        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
+        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
       </x:c>
       <x:c r="O100" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
       </x:c>
       <x:c r="P100" s="16" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
+        <x:v>A-集团官网公告已核验</x:v>
       </x:c>
       <x:c r="Q100" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="54" customHeight="1">
       <x:c r="A101" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="B101" s="4" t="str">
-        <x:v>澜起科技</x:v>
+        <x:v>禾赛科技</x:v>
       </x:c>
       <x:c r="C101" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>激光雷达/机器人</x:v>
       </x:c>
       <x:c r="D101" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E101" s="4" t="str">
-        <x:v>昆山、西安、南京</x:v>
+        <x:v>上海、杭州</x:v>
       </x:c>
       <x:c r="F101" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G101" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H101" s="4" t="str">
-        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
+        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
       </x:c>
       <x:c r="I101" s="15" t="str">
-        <x:v>https://www.montage-tech.com/cn/careers</x:v>
+        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
       </x:c>
       <x:c r="J101" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="K101" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -5821,7 +5821,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M101" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N101" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -5829,7 +5829,7 @@
       <x:c r="O101" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P101" s="16" t="str">
+      <x:c r="P101" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q101" s="4" t="str">
@@ -5838,19 +5838,19 @@
     </x:row>
     <x:row r="102" ht="54" customHeight="1">
       <x:c r="A102" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B102" s="4" t="str">
-        <x:v>上海宇量昇</x:v>
+        <x:v>北京国望光学科技有限公司</x:v>
       </x:c>
       <x:c r="C102" s="4" t="str">
         <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D102" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>央国企</x:v>
       </x:c>
       <x:c r="E102" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F102" s="4" t="str">
         <x:v>正式批</x:v>
@@ -5859,10 +5859,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H102" s="4" t="str">
-        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
-      </x:c>
-      <x:c r="I102" s="15" t="str">
-        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
+        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
+      </x:c>
+      <x:c r="I102" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J102" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5882,7 +5882,7 @@
       <x:c r="O102" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P102" s="16" t="str">
+      <x:c r="P102" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q102" s="4" t="str">
@@ -5891,31 +5891,31 @@
     </x:row>
     <x:row r="103" ht="54" customHeight="1">
       <x:c r="A103" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B103" s="4" t="str">
-        <x:v>是为科技</x:v>
+        <x:v>乐读</x:v>
       </x:c>
       <x:c r="C103" s="4" t="str">
-        <x:v>新能源/智能制造</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D103" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E103" s="4" t="str">
-        <x:v>南京、上海、常州</x:v>
+        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
       </x:c>
       <x:c r="F103" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G103" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H103" s="4" t="str">
-        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
-      </x:c>
-      <x:c r="I103" s="15" t="str">
-        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
+        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
+      </x:c>
+      <x:c r="I103" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J103" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5924,19 +5924,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L103" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M103" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N103" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
       </x:c>
       <x:c r="O103" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P103" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      <x:c r="P103" s="14" t="str">
+        <x:v>B-招聘平台公开汇总</x:v>
       </x:c>
       <x:c r="Q103" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5944,34 +5944,34 @@
     </x:row>
     <x:row r="104" ht="54" customHeight="1">
       <x:c r="A104" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B104" s="4" t="str">
-        <x:v>游族网络</x:v>
+        <x:v>龙蟠科技</x:v>
       </x:c>
       <x:c r="C104" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>新能源材料/化工</x:v>
       </x:c>
       <x:c r="D104" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E104" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F104" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G104" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H104" s="4" t="str">
-        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
+        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
       </x:c>
       <x:c r="I104" s="15" t="str">
-        <x:v>https://job.youzu.com/</x:v>
+        <x:v>https://www.lopal.com.cn/join</x:v>
       </x:c>
       <x:c r="J104" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-01</x:v>
       </x:c>
       <x:c r="K104" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -5980,7 +5980,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M104" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N104" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -5988,7 +5988,7 @@
       <x:c r="O104" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P104" s="16" t="str">
+      <x:c r="P104" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q104" s="4" t="str">
@@ -5997,31 +5997,31 @@
     </x:row>
     <x:row r="105" ht="54" customHeight="1">
       <x:c r="A105" s="4" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B105" s="4" t="str">
-        <x:v>中铁设计</x:v>
+        <x:v>牧原</x:v>
       </x:c>
       <x:c r="C105" s="4" t="str">
-        <x:v>轨道交通/工程设计</x:v>
+        <x:v>农业/食品/智能养殖</x:v>
       </x:c>
       <x:c r="D105" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E105" s="4" t="str">
-        <x:v>北京、济南、郑州、太原</x:v>
+        <x:v>河南南阳及全国</x:v>
       </x:c>
       <x:c r="F105" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G105" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H105" s="4" t="str">
-        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
+        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
       </x:c>
       <x:c r="I105" s="15" t="str">
-        <x:v>https://www.crdc.com/</x:v>
+        <x:v>https://job.muyuanfoods.com/</x:v>
       </x:c>
       <x:c r="J105" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6041,7 +6041,7 @@
       <x:c r="O105" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P105" s="16" t="str">
+      <x:c r="P105" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q105" s="4" t="str">
@@ -6050,31 +6050,31 @@
     </x:row>
     <x:row r="106" ht="54" customHeight="1">
       <x:c r="A106" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B106" s="4" t="str">
-        <x:v>迈安德集团-校园大使</x:v>
+        <x:v>三一集团-小语种校招</x:v>
       </x:c>
       <x:c r="C106" s="4" t="str">
-        <x:v>粮油工程/装备</x:v>
+        <x:v>工程机械/制造</x:v>
       </x:c>
       <x:c r="D106" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E106" s="4" t="str">
-        <x:v>扬州/高校</x:v>
+        <x:v>海外多国</x:v>
       </x:c>
       <x:c r="F106" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>小语种专项/正式批</x:v>
       </x:c>
       <x:c r="G106" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H106" s="4" t="str">
-        <x:v>校园大使</x:v>
+        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
       </x:c>
       <x:c r="I106" s="15" t="str">
-        <x:v>https://www.myande.com/</x:v>
+        <x:v>https://sanycampus.zhiye.com/</x:v>
       </x:c>
       <x:c r="J106" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6094,7 +6094,7 @@
       <x:c r="O106" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P106" s="16" t="str">
+      <x:c r="P106" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q106" s="4" t="str">
@@ -6103,31 +6103,31 @@
     </x:row>
     <x:row r="107" ht="54" customHeight="1">
       <x:c r="A107" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B107" s="4" t="str">
-        <x:v>迅仿科技</x:v>
+        <x:v>上海电气-暑期精英训练营</x:v>
       </x:c>
       <x:c r="C107" s="4" t="str">
-        <x:v>工业软件/仿真</x:v>
+        <x:v>高端装备/能源</x:v>
       </x:c>
       <x:c r="D107" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>地方国企</x:v>
       </x:c>
       <x:c r="E107" s="4" t="str">
         <x:v>上海</x:v>
       </x:c>
       <x:c r="F107" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>训练营/秋招直通</x:v>
       </x:c>
       <x:c r="G107" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H107" s="4" t="str">
-        <x:v>仿真工程师</x:v>
-      </x:c>
-      <x:c r="I107" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
+      </x:c>
+      <x:c r="I107" s="15" t="str">
+        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
       </x:c>
       <x:c r="J107" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6147,7 +6147,7 @@
       <x:c r="O107" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P107" s="16" t="str">
+      <x:c r="P107" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q107" s="4" t="str">
@@ -6156,52 +6156,52 @@
     </x:row>
     <x:row r="108" ht="54" customHeight="1">
       <x:c r="A108" s="4" t="str">
-        <x:v>2026-06-12</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B108" s="4" t="str">
-        <x:v>MOVA</x:v>
+        <x:v>vivo-蓝极星计划</x:v>
       </x:c>
       <x:c r="C108" s="4" t="str">
-        <x:v>智能家电/机器人</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D108" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E108" s="4" t="str">
-        <x:v>苏州及全国</x:v>
+        <x:v>深圳、杭州、东莞、上海</x:v>
       </x:c>
       <x:c r="F108" s="4" t="str">
-        <x:v>全球校招/正式批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G108" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>博士为主</x:v>
       </x:c>
       <x:c r="H108" s="4" t="str">
-        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
       </x:c>
       <x:c r="I108" s="15" t="str">
-        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+        <x:v>https://hr.vivo.com/</x:v>
       </x:c>
       <x:c r="J108" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K108" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L108" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M108" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N108" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
       </x:c>
       <x:c r="O108" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P108" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      <x:c r="P108" s="14" t="str">
+        <x:v>B-招聘平台公开汇总</x:v>
       </x:c>
       <x:c r="Q108" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -6209,19 +6209,19 @@
     </x:row>
     <x:row r="109" ht="54" customHeight="1">
       <x:c r="A109" s="4" t="str">
-        <x:v>2026-06-11</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B109" s="4" t="str">
-        <x:v>财通证券</x:v>
+        <x:v>澜起科技</x:v>
       </x:c>
       <x:c r="C109" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D109" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E109" s="4" t="str">
-        <x:v>杭州、上海、深圳、北京</x:v>
+        <x:v>昆山、西安、南京</x:v>
       </x:c>
       <x:c r="F109" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6230,10 +6230,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H109" s="4" t="str">
-        <x:v>总部、参股公司、分公司岗位</x:v>
+        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
       </x:c>
       <x:c r="I109" s="15" t="str">
-        <x:v>https://www.ctsec.com/joinUs</x:v>
+        <x:v>https://www.montage-tech.com/cn/careers</x:v>
       </x:c>
       <x:c r="J109" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6253,7 +6253,7 @@
       <x:c r="O109" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P109" s="16" t="str">
+      <x:c r="P109" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q109" s="4" t="str">
@@ -6262,31 +6262,31 @@
     </x:row>
     <x:row r="110" ht="54" customHeight="1">
       <x:c r="A110" s="4" t="str">
-        <x:v>2026-06-10</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B110" s="4" t="str">
-        <x:v>歌尔股份</x:v>
+        <x:v>上海宇量昇</x:v>
       </x:c>
       <x:c r="C110" s="4" t="str">
-        <x:v>消费电子/智能硬件</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D110" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E110" s="4" t="str">
         <x:v>上海</x:v>
       </x:c>
       <x:c r="F110" s="4" t="str">
-        <x:v>实习/校招储备</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G110" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H110" s="4" t="str">
-        <x:v>法务助理</x:v>
+        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
       </x:c>
       <x:c r="I110" s="15" t="str">
-        <x:v>https://career.goertek.com/</x:v>
+        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
       </x:c>
       <x:c r="J110" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6306,7 +6306,7 @@
       <x:c r="O110" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P110" s="16" t="str">
+      <x:c r="P110" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q110" s="4" t="str">
@@ -6315,31 +6315,31 @@
     </x:row>
     <x:row r="111" ht="54" customHeight="1">
       <x:c r="A111" s="4" t="str">
-        <x:v>2026-06-09</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B111" s="4" t="str">
-        <x:v>深信服-校园大使</x:v>
+        <x:v>是为科技</x:v>
       </x:c>
       <x:c r="C111" s="4" t="str">
-        <x:v>网络安全/云计算</x:v>
+        <x:v>新能源/智能制造</x:v>
       </x:c>
       <x:c r="D111" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E111" s="4" t="str">
-        <x:v>西安</x:v>
+        <x:v>南京、上海、常州</x:v>
       </x:c>
       <x:c r="F111" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G111" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H111" s="4" t="str">
-        <x:v>校园大使</x:v>
+        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
       </x:c>
       <x:c r="I111" s="15" t="str">
-        <x:v>https://hr.sangfor.com/</x:v>
+        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
       </x:c>
       <x:c r="J111" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6359,7 +6359,7 @@
       <x:c r="O111" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P111" s="16" t="str">
+      <x:c r="P111" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q111" s="4" t="str">
@@ -6368,19 +6368,19 @@
     </x:row>
     <x:row r="112" ht="54" customHeight="1">
       <x:c r="A112" s="4" t="str">
-        <x:v>2026-06-08</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B112" s="4" t="str">
-        <x:v>晓禾教育</x:v>
+        <x:v>游族网络</x:v>
       </x:c>
       <x:c r="C112" s="4" t="str">
-        <x:v>教育</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D112" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E112" s="4" t="str">
-        <x:v>武汉、郑州、襄阳、宜昌</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F112" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6389,10 +6389,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H112" s="4" t="str">
-        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
-      </x:c>
-      <x:c r="I112" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
+      </x:c>
+      <x:c r="I112" s="15" t="str">
+        <x:v>https://job.youzu.com/</x:v>
       </x:c>
       <x:c r="J112" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6412,7 +6412,7 @@
       <x:c r="O112" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P112" s="16" t="str">
+      <x:c r="P112" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q112" s="4" t="str">
@@ -6421,31 +6421,31 @@
     </x:row>
     <x:row r="113" ht="54" customHeight="1">
       <x:c r="A113" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="B113" s="4" t="str">
-        <x:v>晖致医药</x:v>
+        <x:v>中铁设计</x:v>
       </x:c>
       <x:c r="C113" s="4" t="str">
-        <x:v>医药</x:v>
+        <x:v>轨道交通/工程设计</x:v>
       </x:c>
       <x:c r="D113" s="4" t="str">
-        <x:v>外资</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E113" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京、济南、郑州、太原</x:v>
       </x:c>
       <x:c r="F113" s="4" t="str">
-        <x:v>实习储备正式岗</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G113" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H113" s="4" t="str">
-        <x:v>医学信息沟通实习生</x:v>
+        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
       </x:c>
       <x:c r="I113" s="15" t="str">
-        <x:v>https://careers.viatris.com/</x:v>
+        <x:v>https://www.crdc.com/</x:v>
       </x:c>
       <x:c r="J113" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6465,7 +6465,7 @@
       <x:c r="O113" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P113" s="16" t="str">
+      <x:c r="P113" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q113" s="4" t="str">
@@ -6474,31 +6474,31 @@
     </x:row>
     <x:row r="114" ht="54" customHeight="1">
       <x:c r="A114" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B114" s="4" t="str">
-        <x:v>苏州鸿凌达电子</x:v>
+        <x:v>迈安德集团-校园大使</x:v>
       </x:c>
       <x:c r="C114" s="4" t="str">
-        <x:v>电子制造</x:v>
+        <x:v>粮油工程/装备</x:v>
       </x:c>
       <x:c r="D114" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E114" s="4" t="str">
-        <x:v>苏州</x:v>
+        <x:v>扬州/高校</x:v>
       </x:c>
       <x:c r="F114" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G114" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H114" s="4" t="str">
-        <x:v>财务助理</x:v>
+        <x:v>校园大使</x:v>
       </x:c>
       <x:c r="I114" s="15" t="str">
-        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
+        <x:v>https://www.myande.com/</x:v>
       </x:c>
       <x:c r="J114" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6518,7 +6518,7 @@
       <x:c r="O114" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P114" s="16" t="str">
+      <x:c r="P114" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q114" s="4" t="str">
@@ -6527,13 +6527,13 @@
     </x:row>
     <x:row r="115" ht="54" customHeight="1">
       <x:c r="A115" s="4" t="str">
-        <x:v>2026-06-02</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B115" s="4" t="str">
-        <x:v>万得信息</x:v>
+        <x:v>迅仿科技</x:v>
       </x:c>
       <x:c r="C115" s="4" t="str">
-        <x:v>金融数据/软件</x:v>
+        <x:v>工业软件/仿真</x:v>
       </x:c>
       <x:c r="D115" s="4" t="str">
         <x:v>民营</x:v>
@@ -6548,10 +6548,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H115" s="4" t="str">
-        <x:v>AI算法工程师等</x:v>
-      </x:c>
-      <x:c r="I115" s="15" t="str">
-        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
+        <x:v>仿真工程师</x:v>
+      </x:c>
+      <x:c r="I115" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J115" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6571,7 +6571,7 @@
       <x:c r="O115" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P115" s="16" t="str">
+      <x:c r="P115" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q115" s="4" t="str">
@@ -6580,34 +6580,34 @@
     </x:row>
     <x:row r="116" ht="54" customHeight="1">
       <x:c r="A116" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-12</x:v>
       </x:c>
       <x:c r="B116" s="4" t="str">
-        <x:v>淘大集供应链</x:v>
+        <x:v>MOVA</x:v>
       </x:c>
       <x:c r="C116" s="4" t="str">
-        <x:v>零售/供应链</x:v>
+        <x:v>智能家电/机器人</x:v>
       </x:c>
       <x:c r="D116" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E116" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>苏州及全国</x:v>
       </x:c>
       <x:c r="F116" s="4" t="str">
-        <x:v>管培/实习</x:v>
+        <x:v>全球校招/正式批</x:v>
       </x:c>
       <x:c r="G116" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H116" s="4" t="str">
-        <x:v>巡店管培生、实习生</x:v>
-      </x:c>
-      <x:c r="I116" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+      </x:c>
+      <x:c r="I116" s="15" t="str">
+        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
       </x:c>
       <x:c r="J116" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K116" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -6616,7 +6616,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M116" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N116" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -6624,7 +6624,7 @@
       <x:c r="O116" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P116" s="16" t="str">
+      <x:c r="P116" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q116" s="4" t="str">
@@ -6633,31 +6633,31 @@
     </x:row>
     <x:row r="117" ht="54" customHeight="1">
       <x:c r="A117" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-11</x:v>
       </x:c>
       <x:c r="B117" s="4" t="str">
-        <x:v>友芝友实业集团</x:v>
+        <x:v>财通证券</x:v>
       </x:c>
       <x:c r="C117" s="4" t="str">
-        <x:v>综合实业</x:v>
+        <x:v>证券/金融</x:v>
       </x:c>
       <x:c r="D117" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E117" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>杭州、上海、深圳、北京</x:v>
       </x:c>
       <x:c r="F117" s="4" t="str">
-        <x:v>管培生</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G117" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H117" s="4" t="str">
-        <x:v>青年领军人才管培生</x:v>
+        <x:v>总部、参股公司、分公司岗位</x:v>
       </x:c>
       <x:c r="I117" s="15" t="str">
-        <x:v>https://www.yzyqh.com/jrwm</x:v>
+        <x:v>https://www.ctsec.com/joinUs</x:v>
       </x:c>
       <x:c r="J117" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6677,7 +6677,7 @@
       <x:c r="O117" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P117" s="16" t="str">
+      <x:c r="P117" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q117" s="4" t="str">
@@ -6686,84 +6686,84 @@
     </x:row>
     <x:row r="118" ht="54" customHeight="1">
       <x:c r="A118" s="4" t="str">
-        <x:v>2026-05-29</x:v>
+        <x:v>不晚于2026-06-11</x:v>
       </x:c>
       <x:c r="B118" s="4" t="str">
-        <x:v>银雁科技</x:v>
+        <x:v>美团-北斗计划及2027校园招聘</x:v>
       </x:c>
       <x:c r="C118" s="4" t="str">
-        <x:v>金融科技服务</x:v>
+        <x:v>互联网/本地生活/AI</x:v>
       </x:c>
       <x:c r="D118" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E118" s="4" t="str">
-        <x:v>成都</x:v>
+        <x:v>北京、上海、深圳、成都、广州、武汉、杭州、西安等</x:v>
       </x:c>
       <x:c r="F118" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>顶尖人才专项/正式校园招聘</x:v>
       </x:c>
       <x:c r="G118" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>应届毕业生，以具体岗位毕业时间要求为准</x:v>
       </x:c>
       <x:c r="H118" s="4" t="str">
-        <x:v>人伤理赔</x:v>
+        <x:v>北斗计划覆盖大模型、自动驾驶、无人机、机器人和AI Infra等；官方校园职位页当前显示68个岗位</x:v>
       </x:c>
       <x:c r="I118" s="15" t="str">
-        <x:v>https://www.cfss.net.cn/</x:v>
+        <x:v>https://zhaopin.meituan.com/web/position?hiringType=1_1</x:v>
       </x:c>
       <x:c r="J118" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K118" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L118" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>本轮新增；美团官方校园招聘职位页及北斗计划入口均显示开放</x:v>
       </x:c>
       <x:c r="M118" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N118" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>北斗计划为面向顶尖技术人才的专项，普通校园招聘岗位可在同一官方职位页按“应届生”筛选；不同专项的投递规则可能独立。</x:v>
       </x:c>
       <x:c r="O118" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://zhaopin.meituan.com/web/beidouprogram</x:v>
       </x:c>
       <x:c r="P118" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>A-企业官方校园招聘职位页已核验</x:v>
       </x:c>
       <x:c r="Q118" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="54" customHeight="1">
       <x:c r="A119" s="4" t="str">
-        <x:v>不晚于2026-05-19</x:v>
+        <x:v>2026-06-10</x:v>
       </x:c>
       <x:c r="B119" s="4" t="str">
-        <x:v>宇树科技-2027校园招聘</x:v>
+        <x:v>歌尔股份</x:v>
       </x:c>
       <x:c r="C119" s="4" t="str">
-        <x:v>机器人/具身智能</x:v>
+        <x:v>消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D119" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E119" s="4" t="str">
-        <x:v>杭州</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F119" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>实习/校招储备</x:v>
       </x:c>
       <x:c r="G119" s="4" t="str">
-        <x:v>2027届应届生，以具体岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H119" s="4" t="str">
-        <x:v>算法、嵌入式、软件、硬件、机械、SLAM、C++、AI、数据、前端、测试、销售、技术支持及设计等</x:v>
+        <x:v>法务助理</x:v>
       </x:c>
       <x:c r="I119" s="15" t="str">
-        <x:v>https://www.unitree.com/cn/position</x:v>
+        <x:v>https://career.goertek.com/</x:v>
       </x:c>
       <x:c r="J119" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6772,51 +6772,51 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L119" s="4" t="str">
-        <x:v>本轮新增；宇树科技官方招贤纳士页面当前显示多项热招岗位</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M119" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N119" s="4" t="str">
-        <x:v>官方岗位页当前显示杭州技术类与销售类多个热招职位；校园招聘公告由高校就业平台发布，投递以宇树官网职位详情为准。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O119" s="15" t="str">
-        <x:v>https://www.unitree.com/cn/position</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P119" s="14" t="str">
-        <x:v>A-企业官方招贤纳士页面已核验</x:v>
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q119" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="54" customHeight="1">
       <x:c r="A120" s="4" t="str">
-        <x:v>2026-05-15</x:v>
+        <x:v>2026-06-09</x:v>
       </x:c>
       <x:c r="B120" s="4" t="str">
-        <x:v>知乎</x:v>
+        <x:v>深信服-校园大使</x:v>
       </x:c>
       <x:c r="C120" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>网络安全/云计算</x:v>
       </x:c>
       <x:c r="D120" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E120" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>西安</x:v>
       </x:c>
       <x:c r="F120" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G120" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H120" s="4" t="str">
-        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
+        <x:v>校园大使</x:v>
       </x:c>
       <x:c r="I120" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
+        <x:v>https://hr.sangfor.com/</x:v>
       </x:c>
       <x:c r="J120" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6836,7 +6836,7 @@
       <x:c r="O120" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P120" s="16" t="str">
+      <x:c r="P120" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q120" s="4" t="str">
@@ -6845,31 +6845,31 @@
     </x:row>
     <x:row r="121" ht="54" customHeight="1">
       <x:c r="A121" s="4" t="str">
-        <x:v>2026-05-08</x:v>
+        <x:v>2026-06-08</x:v>
       </x:c>
       <x:c r="B121" s="4" t="str">
-        <x:v>招商银行长沙分行</x:v>
+        <x:v>晓禾教育</x:v>
       </x:c>
       <x:c r="C121" s="4" t="str">
-        <x:v>银行/金融</x:v>
+        <x:v>教育</x:v>
       </x:c>
       <x:c r="D121" s="4" t="str">
-        <x:v>股份制银行</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E121" s="4" t="str">
-        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+        <x:v>武汉、郑州、襄阳、宜昌</x:v>
       </x:c>
       <x:c r="F121" s="4" t="str">
-        <x:v>暑期实习/秋招直通</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G121" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H121" s="4" t="str">
-        <x:v>2027暑期实习生</x:v>
-      </x:c>
-      <x:c r="I121" s="15" t="str">
-        <x:v>https://career.cmbchina.com/</x:v>
+        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
+      </x:c>
+      <x:c r="I121" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J121" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6889,7 +6889,7 @@
       <x:c r="O121" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P121" s="16" t="str">
+      <x:c r="P121" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q121" s="4" t="str">
@@ -6898,31 +6898,31 @@
     </x:row>
     <x:row r="122" ht="54" customHeight="1">
       <x:c r="A122" s="4" t="str">
-        <x:v>2026-04-22</x:v>
+        <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="B122" s="4" t="str">
-        <x:v>华金证券</x:v>
+        <x:v>晖致医药</x:v>
       </x:c>
       <x:c r="C122" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>医药</x:v>
       </x:c>
       <x:c r="D122" s="4" t="str">
-        <x:v>国企</x:v>
+        <x:v>外资</x:v>
       </x:c>
       <x:c r="E122" s="4" t="str">
         <x:v>上海</x:v>
       </x:c>
       <x:c r="F122" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>实习储备正式岗</x:v>
       </x:c>
       <x:c r="G122" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H122" s="4" t="str">
-        <x:v>战略发展类</x:v>
+        <x:v>医学信息沟通实习生</x:v>
       </x:c>
       <x:c r="I122" s="15" t="str">
-        <x:v>https://www.huajinsc.cn/</x:v>
+        <x:v>https://careers.viatris.com/</x:v>
       </x:c>
       <x:c r="J122" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6942,10 +6942,487 @@
       <x:c r="O122" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P122" s="16" t="str">
+      <x:c r="P122" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q122" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="54" customHeight="1">
+      <x:c r="A123" s="4" t="str">
+        <x:v>2026-06-04</x:v>
+      </x:c>
+      <x:c r="B123" s="4" t="str">
+        <x:v>苏州鸿凌达电子</x:v>
+      </x:c>
+      <x:c r="C123" s="4" t="str">
+        <x:v>电子制造</x:v>
+      </x:c>
+      <x:c r="D123" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E123" s="4" t="str">
+        <x:v>苏州</x:v>
+      </x:c>
+      <x:c r="F123" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G123" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H123" s="4" t="str">
+        <x:v>财务助理</x:v>
+      </x:c>
+      <x:c r="I123" s="15" t="str">
+        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
+      </x:c>
+      <x:c r="J123" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K123" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L123" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M123" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N123" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O123" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P123" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q123" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" ht="54" customHeight="1">
+      <x:c r="A124" s="4" t="str">
+        <x:v>2026-06-02</x:v>
+      </x:c>
+      <x:c r="B124" s="4" t="str">
+        <x:v>万得信息</x:v>
+      </x:c>
+      <x:c r="C124" s="4" t="str">
+        <x:v>金融数据/软件</x:v>
+      </x:c>
+      <x:c r="D124" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E124" s="4" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F124" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G124" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H124" s="4" t="str">
+        <x:v>AI算法工程师等</x:v>
+      </x:c>
+      <x:c r="I124" s="15" t="str">
+        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
+      </x:c>
+      <x:c r="J124" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K124" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L124" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M124" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N124" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O124" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P124" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q124" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" ht="54" customHeight="1">
+      <x:c r="A125" s="4" t="str">
+        <x:v>2026-06-01</x:v>
+      </x:c>
+      <x:c r="B125" s="4" t="str">
+        <x:v>淘大集供应链</x:v>
+      </x:c>
+      <x:c r="C125" s="4" t="str">
+        <x:v>零售/供应链</x:v>
+      </x:c>
+      <x:c r="D125" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E125" s="4" t="str">
+        <x:v>武汉</x:v>
+      </x:c>
+      <x:c r="F125" s="4" t="str">
+        <x:v>管培/实习</x:v>
+      </x:c>
+      <x:c r="G125" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H125" s="4" t="str">
+        <x:v>巡店管培生、实习生</x:v>
+      </x:c>
+      <x:c r="I125" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
+      </x:c>
+      <x:c r="J125" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K125" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L125" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M125" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N125" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O125" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P125" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q125" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" ht="54" customHeight="1">
+      <x:c r="A126" s="4" t="str">
+        <x:v>2026-06-01</x:v>
+      </x:c>
+      <x:c r="B126" s="4" t="str">
+        <x:v>友芝友实业集团</x:v>
+      </x:c>
+      <x:c r="C126" s="4" t="str">
+        <x:v>综合实业</x:v>
+      </x:c>
+      <x:c r="D126" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E126" s="4" t="str">
+        <x:v>武汉</x:v>
+      </x:c>
+      <x:c r="F126" s="4" t="str">
+        <x:v>管培生</x:v>
+      </x:c>
+      <x:c r="G126" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H126" s="4" t="str">
+        <x:v>青年领军人才管培生</x:v>
+      </x:c>
+      <x:c r="I126" s="15" t="str">
+        <x:v>https://www.yzyqh.com/jrwm</x:v>
+      </x:c>
+      <x:c r="J126" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K126" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L126" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M126" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N126" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O126" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P126" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q126" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" ht="54" customHeight="1">
+      <x:c r="A127" s="4" t="str">
+        <x:v>2026-05-29</x:v>
+      </x:c>
+      <x:c r="B127" s="4" t="str">
+        <x:v>银雁科技</x:v>
+      </x:c>
+      <x:c r="C127" s="4" t="str">
+        <x:v>金融科技服务</x:v>
+      </x:c>
+      <x:c r="D127" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E127" s="4" t="str">
+        <x:v>成都</x:v>
+      </x:c>
+      <x:c r="F127" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G127" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H127" s="4" t="str">
+        <x:v>人伤理赔</x:v>
+      </x:c>
+      <x:c r="I127" s="15" t="str">
+        <x:v>https://www.cfss.net.cn/</x:v>
+      </x:c>
+      <x:c r="J127" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K127" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L127" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M127" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N127" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O127" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P127" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q127" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" ht="54" customHeight="1">
+      <x:c r="A128" s="4" t="str">
+        <x:v>不晚于2026-05-19</x:v>
+      </x:c>
+      <x:c r="B128" s="4" t="str">
+        <x:v>宇树科技-2027校园招聘</x:v>
+      </x:c>
+      <x:c r="C128" s="4" t="str">
+        <x:v>机器人/具身智能</x:v>
+      </x:c>
+      <x:c r="D128" s="4" t="str">
+        <x:v>民营/科技企业</x:v>
+      </x:c>
+      <x:c r="E128" s="4" t="str">
+        <x:v>杭州</x:v>
+      </x:c>
+      <x:c r="F128" s="4" t="str">
+        <x:v>正式批/校园招聘</x:v>
+      </x:c>
+      <x:c r="G128" s="4" t="str">
+        <x:v>2027届应届生，以具体岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H128" s="4" t="str">
+        <x:v>算法、嵌入式、软件、硬件、机械、SLAM、C++、AI、数据、前端、测试、销售、技术支持及设计等</x:v>
+      </x:c>
+      <x:c r="I128" s="15" t="str">
+        <x:v>https://www.unitree.com/cn/position</x:v>
+      </x:c>
+      <x:c r="J128" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K128" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L128" s="4" t="str">
+        <x:v>本轮新增；宇树科技官方招贤纳士页面当前显示多项热招岗位</x:v>
+      </x:c>
+      <x:c r="M128" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N128" s="4" t="str">
+        <x:v>官方岗位页当前显示杭州技术类与销售类多个热招职位；校园招聘公告由高校就业平台发布，投递以宇树官网职位详情为准。</x:v>
+      </x:c>
+      <x:c r="O128" s="15" t="str">
+        <x:v>https://www.unitree.com/cn/position</x:v>
+      </x:c>
+      <x:c r="P128" s="16" t="str">
+        <x:v>A-企业官方招贤纳士页面已核验</x:v>
+      </x:c>
+      <x:c r="Q128" s="4" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" ht="54" customHeight="1">
+      <x:c r="A129" s="4" t="str">
+        <x:v>2026-05-15</x:v>
+      </x:c>
+      <x:c r="B129" s="4" t="str">
+        <x:v>知乎</x:v>
+      </x:c>
+      <x:c r="C129" s="4" t="str">
+        <x:v>互联网/内容平台</x:v>
+      </x:c>
+      <x:c r="D129" s="4" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E129" s="4" t="str">
+        <x:v>北京</x:v>
+      </x:c>
+      <x:c r="F129" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G129" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H129" s="4" t="str">
+        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
+      </x:c>
+      <x:c r="I129" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
+      </x:c>
+      <x:c r="J129" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K129" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L129" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M129" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N129" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O129" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P129" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q129" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" ht="54" customHeight="1">
+      <x:c r="A130" s="4" t="str">
+        <x:v>2026-05-08</x:v>
+      </x:c>
+      <x:c r="B130" s="4" t="str">
+        <x:v>招商银行长沙分行</x:v>
+      </x:c>
+      <x:c r="C130" s="4" t="str">
+        <x:v>银行/金融</x:v>
+      </x:c>
+      <x:c r="D130" s="4" t="str">
+        <x:v>股份制银行</x:v>
+      </x:c>
+      <x:c r="E130" s="4" t="str">
+        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+      </x:c>
+      <x:c r="F130" s="4" t="str">
+        <x:v>暑期实习/秋招直通</x:v>
+      </x:c>
+      <x:c r="G130" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H130" s="4" t="str">
+        <x:v>2027暑期实习生</x:v>
+      </x:c>
+      <x:c r="I130" s="15" t="str">
+        <x:v>https://career.cmbchina.com/</x:v>
+      </x:c>
+      <x:c r="J130" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K130" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L130" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M130" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N130" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O130" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P130" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q130" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="54" customHeight="1">
+      <x:c r="A131" s="4" t="str">
+        <x:v>2026-04-22</x:v>
+      </x:c>
+      <x:c r="B131" s="4" t="str">
+        <x:v>华金证券</x:v>
+      </x:c>
+      <x:c r="C131" s="4" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="D131" s="4" t="str">
+        <x:v>国企</x:v>
+      </x:c>
+      <x:c r="E131" s="4" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F131" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G131" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H131" s="4" t="str">
+        <x:v>战略发展类</x:v>
+      </x:c>
+      <x:c r="I131" s="15" t="str">
+        <x:v>https://www.huajinsc.cn/</x:v>
+      </x:c>
+      <x:c r="J131" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K131" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L131" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M131" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N131" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O131" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P131" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q131" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -6956,7 +7433,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2abd2ade612244ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2852fd9642d34d05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6986,7 +7463,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>近期有明确截止时间的项目（截至2026-08-07）</x:v>
+        <x:v>近期有明确截止时间的项目（截至2026-08-10）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -7080,265 +7557,265 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
-      <x:c r="A4" s="16" t="str">
+      <x:c r="A4" s="14" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="B4" s="14" t="str">
+        <x:v>蔚来</x:v>
+      </x:c>
+      <x:c r="C4" s="14" t="str">
+        <x:v>新能源汽车/智能汽车</x:v>
+      </x:c>
+      <x:c r="D4" s="14" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="str">
+        <x:v>上海、合肥、北京、武汉、南京等</x:v>
+      </x:c>
+      <x:c r="F4" s="14" t="str">
+        <x:v>技术提前批</x:v>
+      </x:c>
+      <x:c r="G4" s="14" t="str">
+        <x:v>2024年9月-2027年8月毕业</x:v>
+      </x:c>
+      <x:c r="H4" s="14" t="str">
+        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
+      </x:c>
+      <x:c r="I4" s="17" t="str">
+        <x:v>https://campus.nio.com/</x:v>
+      </x:c>
+      <x:c r="J4" s="14" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="K4" s="14" t="str">
+        <x:v>否；有笔试/测评</x:v>
+      </x:c>
+      <x:c r="L4" s="14" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M4" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N4" s="14" t="str">
+        <x:v>最多同时申请3个岗位。</x:v>
+      </x:c>
+      <x:c r="O4" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P4" s="16" t="str">
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q4" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="14" t="str">
+        <x:v>2026-07-02</x:v>
+      </x:c>
+      <x:c r="B5" s="14" t="str">
+        <x:v>京东方-先锋京英计划</x:v>
+      </x:c>
+      <x:c r="C5" s="14" t="str">
+        <x:v>显示技术/半导体/物联网</x:v>
+      </x:c>
+      <x:c r="D5" s="14" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="str">
+        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
+      </x:c>
+      <x:c r="F5" s="14" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G5" s="14" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H5" s="14" t="str">
+        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
+      </x:c>
+      <x:c r="I5" s="17" t="str">
+        <x:v>https://campus.boe.com/</x:v>
+      </x:c>
+      <x:c r="J5" s="14" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="K5" s="14" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L5" s="14" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M5" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N5" s="14" t="str">
+        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
+      </x:c>
+      <x:c r="O5" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P5" s="16" t="str">
+        <x:v>A-国家大学生就业平台公告已核验</x:v>
+      </x:c>
+      <x:c r="Q5" s="14" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="14" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>中泰证券-2027秋季校园招聘</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>国有控股/上市</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>济南、北京、上海、深圳、青岛及全国分支机构</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>正式批/秋季校园招聘</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
+        <x:v>2027届高校毕业生（择业期内高校毕业生亦可报名）</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str">
+        <x:v>投行、投资、研究、机构、金融科技、总部中后台、分支机构及旗下金融子公司岗位，共86个岗位、拟招227人</x:v>
+      </x:c>
+      <x:c r="I6" s="17" t="str">
+        <x:v>https://zts.hotjob.cn/school.html</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="str">
+        <x:v>2026-08-16 24:00</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="str">
+        <x:v>否（招聘程序明确包含笔试、面试）</x:v>
+      </x:c>
+      <x:c r="L6" s="14" t="str">
+        <x:v>本轮新增；山东省国资委公告与中泰证券官方招聘网站已交叉核验</x:v>
+      </x:c>
+      <x:c r="M6" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N6" s="14" t="str">
+        <x:v>母公司业务条线、金融科技和总部中后台多要求硕士及以上，分支机构财富管理类岗位本科可报；统一网上报名，可通过中泰证券官方招聘网站或“中泰证券招聘”官方公众号投递，不收取任何费用。</x:v>
+      </x:c>
+      <x:c r="O6" s="17" t="str">
+        <x:v>https://www.selectshandong.com/recruit/company/833895033675845.html</x:v>
+      </x:c>
+      <x:c r="P6" s="16" t="str">
+        <x:v>A-山东省国资委公告与企业官方招聘网站交叉核验</x:v>
+      </x:c>
+      <x:c r="Q6" s="14" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="54" customHeight="1">
+      <x:c r="A7" s="14" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
-        <x:v>莉莉丝游戏</x:v>
-      </x:c>
-      <x:c r="C4" s="16" t="str">
-        <x:v>游戏</x:v>
-      </x:c>
-      <x:c r="D4" s="16" t="str">
+      <x:c r="B7" s="14" t="str">
+        <x:v>中科光电</x:v>
+      </x:c>
+      <x:c r="C7" s="14" t="str">
+        <x:v>光电/科研</x:v>
+      </x:c>
+      <x:c r="D7" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E4" s="16" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F4" s="16" t="str">
+      <x:c r="E7" s="14" t="str">
+        <x:v>以职位公告为准</x:v>
+      </x:c>
+      <x:c r="F7" s="14" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G4" s="16" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H4" s="16" t="str">
-        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
-      </x:c>
-      <x:c r="I4" s="17" t="str">
-        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
-      </x:c>
-      <x:c r="J4" s="16" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
-      <x:c r="K4" s="16" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
-      </x:c>
-      <x:c r="L4" s="16" t="str">
-        <x:v>今日截止；莉莉丝官方校园招聘页当前仍显示27届校招提前批14个职位</x:v>
-      </x:c>
-      <x:c r="M4" s="16" t="str">
-        <x:v>P0-今日截止</x:v>
-      </x:c>
-      <x:c r="N4" s="16" t="str">
-        <x:v>官网当前显示服务器开发、数据分析、战略研究、算法、关卡策划、客户端等27届提前批职位；截止日为2026-08-07，页面仍可投递但可能随时关闭，建议立即完成网申。</x:v>
-      </x:c>
-      <x:c r="O4" s="17" t="str">
-        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
-      </x:c>
-      <x:c r="P4" s="14" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="Q4" s="16" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="54" customHeight="1">
-      <x:c r="A5" s="4" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="B5" s="4" t="str">
-        <x:v>蔚来</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="str">
-        <x:v>上海、合肥、北京、武汉、南京等</x:v>
-      </x:c>
-      <x:c r="F5" s="4" t="str">
-        <x:v>技术提前批</x:v>
-      </x:c>
-      <x:c r="G5" s="4" t="str">
-        <x:v>2024年9月-2027年8月毕业</x:v>
-      </x:c>
-      <x:c r="H5" s="4" t="str">
-        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
-      </x:c>
-      <x:c r="I5" s="15" t="str">
-        <x:v>https://campus.nio.com/</x:v>
-      </x:c>
-      <x:c r="J5" s="4" t="str">
-        <x:v>2026-08-14</x:v>
-      </x:c>
-      <x:c r="K5" s="4" t="str">
-        <x:v>否；有笔试/测评</x:v>
-      </x:c>
-      <x:c r="L5" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M5" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N5" s="4" t="str">
-        <x:v>最多同时申请3个岗位。</x:v>
-      </x:c>
-      <x:c r="O5" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P5" s="14" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q5" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="54" customHeight="1">
-      <x:c r="A6" s="4" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="B6" s="4" t="str">
-        <x:v>京东方-先锋京英计划</x:v>
-      </x:c>
-      <x:c r="C6" s="4" t="str">
-        <x:v>显示技术/半导体/物联网</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E6" s="4" t="str">
-        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
-      </x:c>
-      <x:c r="F6" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G6" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H6" s="4" t="str">
-        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
-      </x:c>
-      <x:c r="I6" s="15" t="str">
-        <x:v>https://campus.boe.com/</x:v>
-      </x:c>
-      <x:c r="J6" s="4" t="str">
-        <x:v>2026-08-14</x:v>
-      </x:c>
-      <x:c r="K6" s="4" t="str">
+      <x:c r="G7" s="14" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H7" s="14" t="str">
+        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
+      </x:c>
+      <x:c r="I7" s="17" t="str">
+        <x:v>https://job.cn-amd.com/</x:v>
+      </x:c>
+      <x:c r="J7" s="14" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="K7" s="14" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
-      <x:c r="L6" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M6" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N6" s="4" t="str">
-        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
-      </x:c>
-      <x:c r="O6" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P6" s="14" t="str">
-        <x:v>A-国家大学生就业平台公告已核验</x:v>
-      </x:c>
-      <x:c r="Q6" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="54" customHeight="1">
-      <x:c r="A7" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
-      </x:c>
-      <x:c r="B7" s="4" t="str">
-        <x:v>中科光电</x:v>
-      </x:c>
-      <x:c r="C7" s="4" t="str">
-        <x:v>光电/科研</x:v>
-      </x:c>
-      <x:c r="D7" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E7" s="4" t="str">
-        <x:v>以职位公告为准</x:v>
-      </x:c>
-      <x:c r="F7" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G7" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H7" s="4" t="str">
-        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
-      </x:c>
-      <x:c r="I7" s="15" t="str">
-        <x:v>https://job.cn-amd.com/</x:v>
-      </x:c>
-      <x:c r="J7" s="4" t="str">
-        <x:v>2026-08-16</x:v>
-      </x:c>
-      <x:c r="K7" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L7" s="4" t="str">
+      <x:c r="L7" s="14" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
-      <x:c r="M7" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N7" s="4" t="str">
+      <x:c r="M7" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N7" s="14" t="str">
         <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
       </x:c>
-      <x:c r="O7" s="15" t="str">
+      <x:c r="O7" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P7" s="20" t="str">
         <x:v>C-名称需二次确认</x:v>
       </x:c>
-      <x:c r="Q7" s="4" t="str">
+      <x:c r="Q7" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="4" t="str">
+      <x:c r="A8" s="14" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B8" s="4" t="str">
+      <x:c r="B8" s="14" t="str">
         <x:v>BCG波士顿咨询</x:v>
       </x:c>
-      <x:c r="C8" s="4" t="str">
+      <x:c r="C8" s="14" t="str">
         <x:v>管理咨询</x:v>
       </x:c>
-      <x:c r="D8" s="4" t="str">
+      <x:c r="D8" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E8" s="4" t="str">
+      <x:c r="E8" s="14" t="str">
         <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
-      <x:c r="F8" s="4" t="str">
+      <x:c r="F8" s="14" t="str">
         <x:v>正式批/中国区校招</x:v>
       </x:c>
-      <x:c r="G8" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H8" s="4" t="str">
+      <x:c r="G8" s="14" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="str">
         <x:v>咨询顾问及相关专业岗位</x:v>
       </x:c>
-      <x:c r="I8" s="15" t="str">
+      <x:c r="I8" s="17" t="str">
         <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
       </x:c>
-      <x:c r="J8" s="4" t="str">
+      <x:c r="J8" s="14" t="str">
         <x:v>2026-08-16</x:v>
       </x:c>
-      <x:c r="K8" s="4" t="str">
+      <x:c r="K8" s="14" t="str">
         <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
-      <x:c r="L8" s="4" t="str">
+      <x:c r="L8" s="14" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
-      <x:c r="M8" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N8" s="4" t="str"/>
-      <x:c r="O8" s="15" t="str">
+      <x:c r="M8" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N8" s="14" t="str"/>
+      <x:c r="O8" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P8" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q8" s="4" t="str">
+      <x:c r="Q8" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -7439,7 +7916,7 @@
       <x:c r="O10" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P10" s="16" t="str">
+      <x:c r="P10" s="14" t="str">
         <x:v>B-高校/招聘平台转载，投前复核</x:v>
       </x:c>
       <x:c r="Q10" s="4" t="str">
@@ -7492,7 +7969,7 @@
       <x:c r="O11" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P11" s="16" t="str">
+      <x:c r="P11" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q11" s="4" t="str">
@@ -7545,7 +8022,7 @@
       <x:c r="O12" s="15" t="str">
         <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
       </x:c>
-      <x:c r="P12" s="14" t="str">
+      <x:c r="P12" s="16" t="str">
         <x:v>A-高校就业网含官方投递链接</x:v>
       </x:c>
       <x:c r="Q12" s="4" t="str">
@@ -7598,7 +8075,7 @@
       <x:c r="O13" s="15" t="str">
         <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
-      <x:c r="P13" s="14" t="str">
+      <x:c r="P13" s="16" t="str">
         <x:v>A-中国移动官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="Q13" s="4" t="str">
@@ -7651,7 +8128,7 @@
       <x:c r="O14" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P14" s="14" t="str">
+      <x:c r="P14" s="16" t="str">
         <x:v>A-官方招聘官网已核验</x:v>
       </x:c>
       <x:c r="Q14" s="4" t="str">
@@ -7704,7 +8181,7 @@
       <x:c r="O15" s="15" t="str">
         <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
       </x:c>
-      <x:c r="P15" s="14" t="str">
+      <x:c r="P15" s="16" t="str">
         <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
       </x:c>
       <x:c r="Q15" s="4" t="str">
@@ -7713,246 +8190,246 @@
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="4" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="B16" s="4" t="str">
-        <x:v>影石Insta360</x:v>
+        <x:v>德勤-2027秋季校园招聘</x:v>
       </x:c>
       <x:c r="C16" s="4" t="str">
-        <x:v>消费电子/智能影像</x:v>
+        <x:v>会计审计/专业服务</x:v>
       </x:c>
       <x:c r="D16" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>外资/专业服务</x:v>
       </x:c>
       <x:c r="E16" s="4" t="str">
-        <x:v>深圳、上海、珠海</x:v>
+        <x:v>北京、上海、广州、深圳、重庆等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F16" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G16" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届毕业生；另有2027寒假实习生</x:v>
       </x:c>
       <x:c r="H16" s="4" t="str">
-        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+        <x:v>审计与鉴证、管理咨询、风险咨询、财务咨询、税务及法律、数字化等</x:v>
       </x:c>
       <x:c r="I16" s="15" t="str">
-        <x:v>https://www.insta360.com/cn/jobs</x:v>
+        <x:v>https://www.deloitte.com/cn/zh/careers.html</x:v>
       </x:c>
       <x:c r="J16" s="4" t="str">
-        <x:v>2026-10-31</x:v>
+        <x:v>2026-10-31（部分岗位招满提前关闭）</x:v>
       </x:c>
       <x:c r="K16" s="4" t="str">
-        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
+        <x:v>否（网申后通常安排在线笔试，具体以岗位流程为准）</x:v>
       </x:c>
       <x:c r="L16" s="4" t="str">
-        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
+        <x:v>本轮新增；可信高校就业公众号发布德勤2027校招信息，官方招聘入口已核验</x:v>
       </x:c>
       <x:c r="M16" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N16" s="4" t="str">
-        <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
+        <x:v>秋季全职与寒假实习并行；网申完成后通常收到在线笔试邀请，部分岗位招满会提前结束网申；德勤中国不收取招聘费用，谨防第三方收费。</x:v>
       </x:c>
       <x:c r="O16" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3ODQ3NTIzMA==&amp;mid=2651327099&amp;idx=4&amp;sn=465f2aa047b826709fa081aa25e633f5&amp;chksm=85d23ac1f4759b74460c0c675e988bc8434725c02e7a91d66890eb4795c8000b3dbe9fcf4a48&amp;scene=27</x:v>
       </x:c>
       <x:c r="P16" s="14" t="str">
-        <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
+        <x:v>B-可信高校就业公众号公告含德勤官方招聘入口</x:v>
       </x:c>
       <x:c r="Q16" s="4" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="4" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-01</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>联想集团</x:v>
+        <x:v>影石Insta360</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
-        <x:v>计算机/消费电子/智能硬件</x:v>
+        <x:v>消费电子/智能影像</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>北京、上海、天津、成都、南京、武汉、深圳、厦门等，以岗位页为准</x:v>
+        <x:v>深圳、上海、珠海</x:v>
       </x:c>
       <x:c r="F17" s="4" t="str">
-        <x:v>正式批/应届生招聘</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
-        <x:v>2027届海内外毕业生（中国大陆毕业时间为2026年9月1日至2027年8月31日）</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>AI开发、软件开发、嵌入式、硬件、产品与项目、设计、市场与销售、供应链及职能岗位</x:v>
+        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
       </x:c>
       <x:c r="I17" s="15" t="str">
-        <x:v>https://talent.lenovo.com.cn/campus</x:v>
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
       </x:c>
       <x:c r="J17" s="4" t="str">
-        <x:v>2026-11-13</x:v>
+        <x:v>2026-10-31</x:v>
       </x:c>
       <x:c r="K17" s="4" t="str">
-        <x:v>否（官方校招日历含在线测评&amp;技术笔试，简历筛选通过发放笔试通知）</x:v>
+        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
       </x:c>
       <x:c r="L17" s="4" t="str">
-        <x:v>本轮新增；联想官方应届生招聘页显示热招中</x:v>
+        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
       </x:c>
       <x:c r="M17" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N17" s="4" t="str">
-        <x:v>联想官方应届生招聘页当前显示“联想2027应届生招聘”，面向2027届海内外毕业生；网申自2026年8月5日开启，官网公布网申截止2026年11月13日。简历完整度需达到100%才能投递，每个校招项目只能投一个岗位（管培生项目和其他项目可各投一个），部分岗位可能因投递人数较多下线；投递时可选择接受岗位调剂，测评通知以邮件、短信和系统提醒为准。</x:v>
+        <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
       </x:c>
       <x:c r="O17" s="15" t="str">
-        <x:v>https://talent.lenovo.com.cn/campus</x:v>
-      </x:c>
-      <x:c r="P17" s="14" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P17" s="16" t="str">
+        <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
       </x:c>
       <x:c r="Q17" s="4" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="B18" s="4" t="str">
-        <x:v>京东-TET管理培训生</x:v>
+        <x:v>联想集团</x:v>
       </x:c>
       <x:c r="C18" s="4" t="str">
-        <x:v>互联网/零售</x:v>
+        <x:v>计算机/消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>北京及业务所在城市</x:v>
+        <x:v>北京、上海、天津、成都、南京、武汉、深圳、厦门等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F18" s="4" t="str">
-        <x:v>管培生专项/提前批</x:v>
+        <x:v>正式批/应届生招聘</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届海内外毕业生（中国大陆毕业时间为2026年9月1日至2027年8月31日）</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
+        <x:v>AI开发、软件开发、嵌入式、硬件、产品与项目、设计、市场与销售、供应链及职能岗位</x:v>
       </x:c>
       <x:c r="I18" s="15" t="str">
-        <x:v>https://campus.jd.com/</x:v>
+        <x:v>https://talent.lenovo.com.cn/campus</x:v>
       </x:c>
       <x:c r="J18" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>2026-11-13</x:v>
       </x:c>
       <x:c r="K18" s="4" t="str">
-        <x:v>含测评，笔试以通知为准</x:v>
+        <x:v>否（官方校招日历含在线测评&amp;技术笔试，简历筛选通过发放笔试通知）</x:v>
       </x:c>
       <x:c r="L18" s="4" t="str">
-        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
+        <x:v>本轮新增；联想官方应届生招聘页显示热招中</x:v>
       </x:c>
       <x:c r="M18" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N18" s="4" t="str">
-        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
+        <x:v>联想官方应届生招聘页当前显示“联想2027应届生招聘”，面向2027届海内外毕业生；网申自2026年8月5日开启，官网公布网申截止2026年11月13日。简历完整度需达到100%才能投递，每个校招项目只能投一个岗位（管培生项目和其他项目可各投一个），部分岗位可能因投递人数较多下线；投递时可选择接受岗位调剂，测评通知以邮件、短信和系统提醒为准。</x:v>
       </x:c>
       <x:c r="O18" s="15" t="str">
-        <x:v>https://campus.jd.com/#/</x:v>
-      </x:c>
-      <x:c r="P18" s="14" t="str">
-        <x:v>A-企业官网校招页面已核验</x:v>
+        <x:v>https://talent.lenovo.com.cn/campus</x:v>
+      </x:c>
+      <x:c r="P18" s="16" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="Q18" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="4" t="str">
-        <x:v>2026-06-12</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>MOVA</x:v>
+        <x:v>京东-TET管理培训生</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>智能家电/机器人</x:v>
+        <x:v>互联网/零售</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>苏州及全国</x:v>
+        <x:v>北京及业务所在城市</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>全球校招/正式批</x:v>
+        <x:v>管培生专项/提前批</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
       </x:c>
       <x:c r="I19" s="15" t="str">
-        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+        <x:v>https://campus.jd.com/</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
         <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K19" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>含测评，笔试以通知为准</x:v>
       </x:c>
       <x:c r="L19" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
       </x:c>
       <x:c r="M19" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N19" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
       </x:c>
       <x:c r="O19" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://campus.jd.com/#/</x:v>
       </x:c>
       <x:c r="P19" s="16" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>A-企业官网校招页面已核验</x:v>
       </x:c>
       <x:c r="Q19" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-12</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
-        <x:v>龙蟠科技</x:v>
+        <x:v>MOVA</x:v>
       </x:c>
       <x:c r="C20" s="4" t="str">
-        <x:v>新能源材料/化工</x:v>
+        <x:v>智能家电/机器人</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>苏州及全国</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>全球校招/正式批</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
+        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
       </x:c>
       <x:c r="I20" s="15" t="str">
-        <x:v>https://www.lopal.com.cn/join</x:v>
+        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
-        <x:v>2027-06-01</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K20" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -7969,7 +8446,7 @@
       <x:c r="O20" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P20" s="16" t="str">
+      <x:c r="P20" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q20" s="4" t="str">
@@ -7978,54 +8455,160 @@
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
       <x:c r="B21" s="4" t="str">
-        <x:v>百度</x:v>
+        <x:v>字节跳动-2027校园招聘</x:v>
       </x:c>
       <x:c r="C21" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>互联网/AI/内容平台</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+        <x:v>北京、上海、深圳、杭州等，具体以岗位页为准</x:v>
       </x:c>
       <x:c r="F21" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>毕业时间为2026年9月至2027年8月的应届生</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+        <x:v>研发、产品、运营、设计、市场、职能/支持、销售、游戏策划八大类；新增AI全栈工程师、AI Agent开发等方向</x:v>
       </x:c>
       <x:c r="I21" s="15" t="str">
-        <x:v>https://talent.baidu.com/jobs</x:v>
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
       </x:c>
       <x:c r="J21" s="4" t="str">
-        <x:v>2027-06-30</x:v>
+        <x:v>2026-12-31（岗位招满可能提前下架）</x:v>
       </x:c>
       <x:c r="K21" s="4" t="str">
-        <x:v>部分免；并非所有候选人参加笔试</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L21" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>本轮新增；字节跳动官方校园招聘入口已核验，2027届校招于2026-08-03启动</x:v>
       </x:c>
       <x:c r="M21" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N21" s="4" t="str">
+        <x:v>普通校招投递机会按阶段刷新：2026-08-03至2026-12-31有两次机会，2027-01-01刷新两次；岗位招满会下架。AI产品早鸟通道、前沿技术人才校招、Seed大模型人才校招等专项不占用普通投递机会。</x:v>
+      </x:c>
+      <x:c r="O21" s="15" t="str">
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
+      </x:c>
+      <x:c r="P21" s="16" t="str">
+        <x:v>A-企业官方校园招聘入口已核验</x:v>
+      </x:c>
+      <x:c r="Q21" s="4" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="54" customHeight="1">
+      <x:c r="A22" s="4" t="str">
+        <x:v>2026-06-17</x:v>
+      </x:c>
+      <x:c r="B22" s="4" t="str">
+        <x:v>龙蟠科技</x:v>
+      </x:c>
+      <x:c r="C22" s="4" t="str">
+        <x:v>新能源材料/化工</x:v>
+      </x:c>
+      <x:c r="D22" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E22" s="4" t="str">
+        <x:v>南京</x:v>
+      </x:c>
+      <x:c r="F22" s="4" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G22" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H22" s="4" t="str">
+        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
+      </x:c>
+      <x:c r="I22" s="15" t="str">
+        <x:v>https://www.lopal.com.cn/join</x:v>
+      </x:c>
+      <x:c r="J22" s="4" t="str">
+        <x:v>2027-06-01</x:v>
+      </x:c>
+      <x:c r="K22" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L22" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M22" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N22" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O22" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P22" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q22" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="54" customHeight="1">
+      <x:c r="A23" s="4" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="B23" s="4" t="str">
+        <x:v>百度</x:v>
+      </x:c>
+      <x:c r="C23" s="4" t="str">
+        <x:v>互联网/AI</x:v>
+      </x:c>
+      <x:c r="D23" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E23" s="4" t="str">
+        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+      </x:c>
+      <x:c r="F23" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G23" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H23" s="4" t="str">
+        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+      </x:c>
+      <x:c r="I23" s="15" t="str">
+        <x:v>https://talent.baidu.com/jobs</x:v>
+      </x:c>
+      <x:c r="J23" s="4" t="str">
+        <x:v>2027-06-30</x:v>
+      </x:c>
+      <x:c r="K23" s="4" t="str">
+        <x:v>部分免；并非所有候选人参加笔试</x:v>
+      </x:c>
+      <x:c r="L23" s="4" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M23" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N23" s="4" t="str">
         <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
       </x:c>
-      <x:c r="O21" s="15" t="str">
+      <x:c r="O23" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P21" s="14" t="str">
+      <x:c r="P23" s="16" t="str">
         <x:v>A-官方招聘日历/官方来源已核验</x:v>
       </x:c>
-      <x:c r="Q21" s="4" t="str">
+      <x:c r="Q23" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -8036,7 +8619,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43b37ffcbb2b47fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a4d48394f6e46bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8054,7 +8637,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="28" t="str">
-        <x:v>使用说明与统计（截至2026-08-07）</x:v>
+        <x:v>使用说明与统计（截至2026-08-10）</x:v>
       </x:c>
       <x:c r="B1" s="28"/>
       <x:c r="C1" s="28"/>
@@ -8093,10 +8676,10 @@
       </x:c>
       <x:c r="C4" s="26"/>
       <x:c r="D4" s="32" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="E4" s="33" t="n">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F4"/>
     </x:row>
@@ -8109,7 +8692,7 @@
       </x:c>
       <x:c r="C5" s="26"/>
       <x:c r="D5" s="32" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="E5" s="33" t="n">
         <x:v>5</x:v>
@@ -8257,7 +8840,7 @@
         <x:v>项目总数</x:v>
       </x:c>
       <x:c r="B16" s="29" t="n">
-        <x:v>119</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C16" s="26"/>
       <x:c r="D16" s="32" t="str">
@@ -8273,7 +8856,7 @@
         <x:v>有明确截止时间（未截止）</x:v>
       </x:c>
       <x:c r="B17" s="29" t="n">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C17" s="26"/>
       <x:c r="D17" s="32" t="str">
@@ -8289,7 +8872,7 @@
         <x:v>A等级</x:v>
       </x:c>
       <x:c r="B18" s="29" t="n">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C18" s="26"/>
       <x:c r="D18" s="32" t="str">
@@ -8305,7 +8888,7 @@
         <x:v>B等级</x:v>
       </x:c>
       <x:c r="B19" s="29" t="n">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C19" s="26"/>
       <x:c r="D19" s="32"/>
@@ -8337,7 +8920,7 @@
         <x:v>本次更新</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>新增5项；关闭0项；未来7天内明确截止3项；新增项目来自企业官方校园招聘页，免笔试政策以公告为准。</x:v>
+        <x:v>新增9项；关闭1项；未来7天内明确截止5项；新增项目来自企业官方校园招聘页，免笔试政策以公告为准。</x:v>
       </x:c>
       <x:c r="C22" s="26"/>
       <x:c r="D22" s="26"/>

--- a/2027届秋招投递信息_2026-07-24.xlsx
+++ b/2027届秋招投递信息_2026-07-24.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R1b68ac3122b14a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="Ra31780144de547da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="Rd0a130912a414c59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R74348679e3bc440f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="R63cde1c2fb524898"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="R4eccbf1c302d44a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -304,8 +304,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q131" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:Q131"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CurrentProjectsTable" displayName="CurrentProjectsTable" ref="A3:Q133" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:Q133"/>
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="开放投递时间"/>
     <x:tableColumn id="2" name="企业名称"/>
@@ -330,8 +330,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DeadlineProjectsTable" displayName="DeadlineProjectsTable" ref="A3:Q23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A3:Q23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="DeadlineProjectsTable" displayName="DeadlineProjectsTable" ref="A3:Q24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A3:Q24"/>
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="开放投递时间"/>
     <x:tableColumn id="2" name="企业名称"/>
@@ -571,7 +571,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>2027届秋招投递信息（截至2026-08-10）</x:v>
+        <x:v>2027届秋招投递信息（截至2026-08-11）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -592,7 +592,7 @@
     </x:row>
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>每日更新：按开放时间倒序；本轮新增9项官方核验项目，关闭1项；第三方汇总入口不作为立即投递链接。</x:v>
+        <x:v>每日更新：按开放时间倒序；本轮新增2项官方核验项目，关闭0项；第三方汇总入口不作为立即投递链接。</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -1461,55 +1461,55 @@
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="4" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>德勤-2027秋季校园招聘</x:v>
+        <x:v>温氏股份-2027届校园招聘</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>会计审计/专业服务</x:v>
+        <x:v>农牧/食品</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>外资/专业服务</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>北京、上海、广州、深圳、重庆等，以岗位页为准</x:v>
+        <x:v>全国20多个省（市、自治区），以岗位页面为准</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>正式批/秋季校园招聘</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>2027届应届毕业生；另有2027寒假实习生</x:v>
+        <x:v>2027届高校毕业生，具体学历、专业要求以岗位页面为准</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>审计与鉴证、管理咨询、风险咨询、财务咨询、税务及法律、数字化等</x:v>
+        <x:v>养殖技术、食品与生产、机电设备、市场营销、研发及综合职能等集团校招岗位</x:v>
       </x:c>
       <x:c r="I19" s="15" t="str">
-        <x:v>https://www.deloitte.com/cn/zh/careers.html</x:v>
+        <x:v>https://mp.weixin.qq.com/s/4r82YEfMv3ADYDAili-30w</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
-        <x:v>2026-10-31（部分岗位招满提前关闭）</x:v>
+        <x:v>未公布/以各岗位为准</x:v>
       </x:c>
       <x:c r="K19" s="4" t="str">
-        <x:v>否（网申后通常安排在线笔试，具体以岗位流程为准）</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L19" s="4" t="str">
-        <x:v>本轮新增；可信高校就业公众号发布德勤2027校招信息，官方招聘入口已核验</x:v>
+        <x:v>本轮新增；温氏股份招聘官方公众号已发布2027届校园招聘启动公告</x:v>
       </x:c>
       <x:c r="M19" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-截止未公布/岗位动态关闭</x:v>
       </x:c>
       <x:c r="N19" s="4" t="str">
-        <x:v>秋季全职与寒假实习并行；网申完成后通常收到在线笔试邀请，部分岗位招满会提前结束网申；德勤中国不收取招聘费用，谨防第三方收费。</x:v>
+        <x:v>官方公众号文章发布于2026-08-05；电脑端可从温氏股份官网“人才招聘-校园招聘”进入，移动端可关注“温氏股份招聘”并选择“加入温氏-校园招聘”。岗位可能分批开放，投递前确认单位、城市和岗位状态。</x:v>
       </x:c>
       <x:c r="O19" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3ODQ3NTIzMA==&amp;mid=2651327099&amp;idx=4&amp;sn=465f2aa047b826709fa081aa25e633f5&amp;chksm=85d23ac1f4759b74460c0c675e988bc8434725c02e7a91d66890eb4795c8000b3dbe9fcf4a48&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P19" s="14" t="str">
-        <x:v>B-可信高校就业公众号公告含德勤官方招聘入口</x:v>
+        <x:v>https://mp.weixin.qq.com/s/4r82YEfMv3ADYDAili-30w</x:v>
+      </x:c>
+      <x:c r="P19" s="16" t="str">
+        <x:v>A-温氏股份招聘官方公众号与集团官网校园招聘入口已核验</x:v>
       </x:c>
       <x:c r="Q19" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
@@ -1517,423 +1517,423 @@
         <x:v>2026-08-04</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
-        <x:v>德州仪器TI</x:v>
+        <x:v>德勤-2027秋季校园招聘</x:v>
       </x:c>
       <x:c r="C20" s="4" t="str">
-        <x:v>半导体/模拟与嵌入式芯片</x:v>
+        <x:v>会计审计/专业服务</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>外资/上市</x:v>
+        <x:v>外资/专业服务</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>上海及中国区岗位，以职位详情页为准</x:v>
+        <x:v>北京、上海、广州、深圳、重庆等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
-        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
+        <x:v>2027届应届毕业生；另有2027寒假实习生</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>人力资源培训生、税务专员、会计专员、产品市场工程师（模拟/嵌入式方向）及品牌营销专员</x:v>
+        <x:v>审计与鉴证、管理咨询、风险咨询、财务咨询、税务及法律、数字化等</x:v>
       </x:c>
       <x:c r="I20" s="15" t="str">
-        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
+        <x:v>https://www.deloitte.com/cn/zh/careers.html</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-31（部分岗位招满提前关闭）</x:v>
       </x:c>
       <x:c r="K20" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否（网申后通常安排在线笔试，具体以岗位流程为准）</x:v>
       </x:c>
       <x:c r="L20" s="4" t="str">
-        <x:v>本轮新增；官方职位页已发布多项中国区2027校园招聘岗位</x:v>
+        <x:v>本轮新增；可信高校就业公众号发布德勤2027校招信息，官方招聘入口已核验</x:v>
       </x:c>
       <x:c r="M20" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N20" s="4" t="str">
-        <x:v>岗位分批发布，当前核验到的2027校招岗位发布日期为2026-08-04；投递前按China地区和岗位关键词筛选。</x:v>
+        <x:v>秋季全职与寒假实习并行；网申完成后通常收到在线笔试邀请，部分岗位招满会提前结束网申；德勤中国不收取招聘费用，谨防第三方收费。</x:v>
       </x:c>
       <x:c r="O20" s="15" t="str">
-        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
-      </x:c>
-      <x:c r="P20" s="16" t="str">
-        <x:v>A-企业官方职位页已核验</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3ODQ3NTIzMA==&amp;mid=2651327099&amp;idx=4&amp;sn=465f2aa047b826709fa081aa25e633f5&amp;chksm=85d23ac1f4759b74460c0c675e988bc8434725c02e7a91d66890eb4795c8000b3dbe9fcf4a48&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P20" s="14" t="str">
+        <x:v>B-可信高校就业公众号公告含德勤官方招聘入口</x:v>
       </x:c>
       <x:c r="Q20" s="4" t="str">
-        <x:v>2026-08-06</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="4" t="str">
+        <x:v>2026-08-04</x:v>
+      </x:c>
+      <x:c r="B21" s="4" t="str">
+        <x:v>德州仪器TI</x:v>
+      </x:c>
+      <x:c r="C21" s="4" t="str">
+        <x:v>半导体/模拟与嵌入式芯片</x:v>
+      </x:c>
+      <x:c r="D21" s="4" t="str">
+        <x:v>外资/上市</x:v>
+      </x:c>
+      <x:c r="E21" s="4" t="str">
+        <x:v>上海及中国区岗位，以职位详情页为准</x:v>
+      </x:c>
+      <x:c r="F21" s="4" t="str">
+        <x:v>正式批/校园招聘</x:v>
+      </x:c>
+      <x:c r="G21" s="4" t="str">
+        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
+      </x:c>
+      <x:c r="H21" s="4" t="str">
+        <x:v>人力资源培训生、税务专员、会计专员、产品市场工程师（模拟/嵌入式方向）及品牌营销专员</x:v>
+      </x:c>
+      <x:c r="I21" s="15" t="str">
+        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
+      </x:c>
+      <x:c r="J21" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K21" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L21" s="4" t="str">
+        <x:v>本轮新增；官方职位页已发布多项中国区2027校园招聘岗位</x:v>
+      </x:c>
+      <x:c r="M21" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N21" s="4" t="str">
+        <x:v>岗位分批发布，当前核验到的2027校招岗位发布日期为2026-08-04；投递前按China地区和岗位关键词筛选。</x:v>
+      </x:c>
+      <x:c r="O21" s="15" t="str">
+        <x:v>https://careers.ti.com/zh-CN/sites/CX/jobs</x:v>
+      </x:c>
+      <x:c r="P21" s="16" t="str">
+        <x:v>A-企业官方职位页已核验</x:v>
+      </x:c>
+      <x:c r="Q21" s="4" t="str">
+        <x:v>2026-08-06</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="54" customHeight="1">
+      <x:c r="A22" s="4" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
-      <x:c r="B21" s="4" t="str">
+      <x:c r="B22" s="4" t="str">
         <x:v>哔哩哔哩-2027秋季校园招聘</x:v>
       </x:c>
-      <x:c r="C21" s="4" t="str">
+      <x:c r="C22" s="4" t="str">
         <x:v>互联网/内容平台/游戏</x:v>
       </x:c>
-      <x:c r="D21" s="4" t="str">
+      <x:c r="D22" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
-      <x:c r="E21" s="4" t="str">
+      <x:c r="E22" s="4" t="str">
         <x:v>上海、北京、广州、深圳、杭州等，以岗位页为准</x:v>
       </x:c>
-      <x:c r="F21" s="4" t="str">
+      <x:c r="F22" s="4" t="str">
         <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
-      <x:c r="G21" s="4" t="str">
+      <x:c r="G22" s="4" t="str">
         <x:v>毕业时间为2026年9月1日至2027年8月31日的海内外2027届应届生</x:v>
       </x:c>
-      <x:c r="H21" s="4" t="str">
+      <x:c r="H22" s="4" t="str">
         <x:v>技术、产品、运营、市场、设计、职能及游戏等全序列岗位；另有B-UP顶尖技术人才项目</x:v>
       </x:c>
-      <x:c r="I21" s="15" t="str">
+      <x:c r="I22" s="15" t="str">
         <x:v>https://jobs.bilibili.com/campus</x:v>
       </x:c>
-      <x:c r="J21" s="4" t="str">
+      <x:c r="J22" s="4" t="str">
         <x:v>未公布/岗位招满即止</x:v>
       </x:c>
-      <x:c r="K21" s="4" t="str">
+      <x:c r="K22" s="4" t="str">
         <x:v>官方未统一说明</x:v>
       </x:c>
-      <x:c r="L21" s="4" t="str">
+      <x:c r="L22" s="4" t="str">
         <x:v>本轮新增；哔哩哔哩官方校园招聘页显示2027届秋季校园招聘正式启动</x:v>
       </x:c>
-      <x:c r="M21" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N21" s="4" t="str">
+      <x:c r="M22" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N22" s="4" t="str">
         <x:v>每位同学最多投递2个志愿，按投递先后认定一、二志愿；可在校招官网投递记录或“哔哩哔哩招聘”公众号查询进度，岗位招满可能提前下架。</x:v>
       </x:c>
-      <x:c r="O21" s="15" t="str">
+      <x:c r="O22" s="15" t="str">
         <x:v>https://jobs.bilibili.com/campus</x:v>
       </x:c>
-      <x:c r="P21" s="16" t="str">
+      <x:c r="P22" s="16" t="str">
         <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
-      <x:c r="Q21" s="4" t="str">
+      <x:c r="Q22" s="4" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="54" customHeight="1">
-      <x:c r="A22" s="14" t="str">
+    <x:row r="23" ht="54" customHeight="1">
+      <x:c r="A23" s="14" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
-      <x:c r="B22" s="14" t="str">
+      <x:c r="B23" s="14" t="str">
         <x:v>中泰证券-2027秋季校园招聘</x:v>
       </x:c>
-      <x:c r="C22" s="14" t="str">
+      <x:c r="C23" s="14" t="str">
         <x:v>证券/金融</x:v>
       </x:c>
-      <x:c r="D22" s="14" t="str">
+      <x:c r="D23" s="14" t="str">
         <x:v>国有控股/上市</x:v>
       </x:c>
-      <x:c r="E22" s="14" t="str">
+      <x:c r="E23" s="14" t="str">
         <x:v>济南、北京、上海、深圳、青岛及全国分支机构</x:v>
       </x:c>
-      <x:c r="F22" s="14" t="str">
+      <x:c r="F23" s="14" t="str">
         <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="str">
+      <x:c r="G23" s="14" t="str">
         <x:v>2027届高校毕业生（择业期内高校毕业生亦可报名）</x:v>
       </x:c>
-      <x:c r="H22" s="14" t="str">
+      <x:c r="H23" s="14" t="str">
         <x:v>投行、投资、研究、机构、金融科技、总部中后台、分支机构及旗下金融子公司岗位，共86个岗位、拟招227人</x:v>
       </x:c>
-      <x:c r="I22" s="17" t="str">
+      <x:c r="I23" s="17" t="str">
         <x:v>https://zts.hotjob.cn/school.html</x:v>
       </x:c>
-      <x:c r="J22" s="14" t="str">
+      <x:c r="J23" s="14" t="str">
         <x:v>2026-08-16 24:00</x:v>
       </x:c>
-      <x:c r="K22" s="14" t="str">
+      <x:c r="K23" s="14" t="str">
         <x:v>否（招聘程序明确包含笔试、面试）</x:v>
       </x:c>
-      <x:c r="L22" s="14" t="str">
+      <x:c r="L23" s="14" t="str">
         <x:v>本轮新增；山东省国资委公告与中泰证券官方招聘网站已交叉核验</x:v>
       </x:c>
-      <x:c r="M22" s="14" t="str">
+      <x:c r="M23" s="14" t="str">
         <x:v>P1-7天内截止</x:v>
       </x:c>
-      <x:c r="N22" s="14" t="str">
+      <x:c r="N23" s="14" t="str">
         <x:v>母公司业务条线、金融科技和总部中后台多要求硕士及以上，分支机构财富管理类岗位本科可报；统一网上报名，可通过中泰证券官方招聘网站或“中泰证券招聘”官方公众号投递，不收取任何费用。</x:v>
       </x:c>
-      <x:c r="O22" s="17" t="str">
+      <x:c r="O23" s="17" t="str">
         <x:v>https://www.selectshandong.com/recruit/company/833895033675845.html</x:v>
       </x:c>
-      <x:c r="P22" s="16" t="str">
+      <x:c r="P23" s="16" t="str">
         <x:v>A-山东省国资委公告与企业官方招聘网站交叉核验</x:v>
       </x:c>
-      <x:c r="Q22" s="14" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="54" customHeight="1">
-      <x:c r="A23" s="4" t="str">
-        <x:v>2026-08-03</x:v>
-      </x:c>
-      <x:c r="B23" s="4" t="str">
-        <x:v>字节跳动-2027校园招聘</x:v>
-      </x:c>
-      <x:c r="C23" s="4" t="str">
-        <x:v>互联网/AI/内容平台</x:v>
-      </x:c>
-      <x:c r="D23" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E23" s="4" t="str">
-        <x:v>北京、上海、深圳、杭州等，具体以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F23" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
-      </x:c>
-      <x:c r="G23" s="4" t="str">
-        <x:v>毕业时间为2026年9月至2027年8月的应届生</x:v>
-      </x:c>
-      <x:c r="H23" s="4" t="str">
-        <x:v>研发、产品、运营、设计、市场、职能/支持、销售、游戏策划八大类；新增AI全栈工程师、AI Agent开发等方向</x:v>
-      </x:c>
-      <x:c r="I23" s="15" t="str">
-        <x:v>https://jobs.bytedance.com/campus/</x:v>
-      </x:c>
-      <x:c r="J23" s="4" t="str">
-        <x:v>2026-12-31（岗位招满可能提前下架）</x:v>
-      </x:c>
-      <x:c r="K23" s="4" t="str">
-        <x:v>官方未统一说明</x:v>
-      </x:c>
-      <x:c r="L23" s="4" t="str">
-        <x:v>本轮新增；字节跳动官方校园招聘入口已核验，2027届校招于2026-08-03启动</x:v>
-      </x:c>
-      <x:c r="M23" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
-      </x:c>
-      <x:c r="N23" s="4" t="str">
-        <x:v>普通校招投递机会按阶段刷新：2026-08-03至2026-12-31有两次机会，2027-01-01刷新两次；岗位招满会下架。AI产品早鸟通道、前沿技术人才校招、Seed大模型人才校招等专项不占用普通投递机会。</x:v>
-      </x:c>
-      <x:c r="O23" s="15" t="str">
-        <x:v>https://jobs.bytedance.com/campus/</x:v>
-      </x:c>
-      <x:c r="P23" s="16" t="str">
-        <x:v>A-企业官方校园招聘入口已核验</x:v>
-      </x:c>
-      <x:c r="Q23" s="4" t="str">
+      <x:c r="Q23" s="14" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="4" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
       <x:c r="B24" s="4" t="str">
-        <x:v>影石Insta360</x:v>
+        <x:v>字节跳动-2027校园招聘</x:v>
       </x:c>
       <x:c r="C24" s="4" t="str">
-        <x:v>消费电子/智能影像</x:v>
+        <x:v>互联网/AI/内容平台</x:v>
       </x:c>
       <x:c r="D24" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>深圳、上海、珠海</x:v>
+        <x:v>北京、上海、深圳、杭州等，具体以岗位页为准</x:v>
       </x:c>
       <x:c r="F24" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>毕业时间为2026年9月至2027年8月的应届生</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+        <x:v>研发、产品、运营、设计、市场、职能/支持、销售、游戏策划八大类；新增AI全栈工程师、AI Agent开发等方向</x:v>
       </x:c>
       <x:c r="I24" s="15" t="str">
-        <x:v>https://www.insta360.com/cn/jobs</x:v>
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
       </x:c>
       <x:c r="J24" s="4" t="str">
-        <x:v>2026-10-31</x:v>
+        <x:v>2026-12-31（岗位招满可能提前下架）</x:v>
       </x:c>
       <x:c r="K24" s="4" t="str">
-        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L24" s="4" t="str">
-        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
+        <x:v>本轮新增；字节跳动官方校园招聘入口已核验，2027届校招于2026-08-03启动</x:v>
       </x:c>
       <x:c r="M24" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N24" s="4" t="str">
+        <x:v>普通校招投递机会按阶段刷新：2026-08-03至2026-12-31有两次机会，2027-01-01刷新两次；岗位招满会下架。AI产品早鸟通道、前沿技术人才校招、Seed大模型人才校招等专项不占用普通投递机会。</x:v>
+      </x:c>
+      <x:c r="O24" s="15" t="str">
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
+      </x:c>
+      <x:c r="P24" s="16" t="str">
+        <x:v>A-企业官方校园招聘入口已核验</x:v>
+      </x:c>
+      <x:c r="Q24" s="4" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="54" customHeight="1">
+      <x:c r="A25" s="4" t="str">
+        <x:v>2026-08-01</x:v>
+      </x:c>
+      <x:c r="B25" s="4" t="str">
+        <x:v>影石Insta360</x:v>
+      </x:c>
+      <x:c r="C25" s="4" t="str">
+        <x:v>消费电子/智能影像</x:v>
+      </x:c>
+      <x:c r="D25" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E25" s="4" t="str">
+        <x:v>深圳、上海、珠海</x:v>
+      </x:c>
+      <x:c r="F25" s="4" t="str">
+        <x:v>正式批/秋招</x:v>
+      </x:c>
+      <x:c r="G25" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H25" s="4" t="str">
+        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+      </x:c>
+      <x:c r="I25" s="15" t="str">
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
+      </x:c>
+      <x:c r="J25" s="4" t="str">
+        <x:v>2026-10-31</x:v>
+      </x:c>
+      <x:c r="K25" s="4" t="str">
+        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
+      </x:c>
+      <x:c r="L25" s="4" t="str">
+        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
+      </x:c>
+      <x:c r="M25" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N25" s="4" t="str">
         <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
       </x:c>
-      <x:c r="O24" s="15" t="str">
+      <x:c r="O25" s="15" t="str">
         <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
       </x:c>
-      <x:c r="P24" s="16" t="str">
+      <x:c r="P25" s="16" t="str">
         <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
       </x:c>
-      <x:c r="Q24" s="4" t="str">
+      <x:c r="Q25" s="4" t="str">
         <x:v>2026-08-04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="54" customHeight="1">
-      <x:c r="A25" s="18" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B25" s="18" t="str">
-        <x:v>恒丰银行总行-雏鹰计划</x:v>
-      </x:c>
-      <x:c r="C25" s="18" t="str">
-        <x:v>银行/金融</x:v>
-      </x:c>
-      <x:c r="D25" s="18" t="str">
-        <x:v>股份制商业银行</x:v>
-      </x:c>
-      <x:c r="E25" s="18" t="str">
-        <x:v>总行及相关机构，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F25" s="18" t="str">
-        <x:v>暑期实习/秋招储备</x:v>
-      </x:c>
-      <x:c r="G25" s="18" t="str">
-        <x:v>2027届硕士及以上，以公告要求为准</x:v>
-      </x:c>
-      <x:c r="H25" s="18" t="str">
-        <x:v>总行实习生，具体专业和方向以官方公告为准</x:v>
-      </x:c>
-      <x:c r="I25" s="19" t="str">
-        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
-      </x:c>
-      <x:c r="J25" s="18" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K25" s="18" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L25" s="18" t="str">
-        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M25" s="18" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N25" s="18" t="str">
-        <x:v>官方公告显示7月31日24:00截止，实习期安排和具体岗位以恒丰银行招聘官网为准。</x:v>
-      </x:c>
-      <x:c r="O25" s="19" t="str">
-        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
-      </x:c>
-      <x:c r="P25" s="16" t="str">
-        <x:v>A-企业官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q25" s="18" t="str">
-        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="54" customHeight="1">
       <x:c r="A26" s="4" t="str">
+        <x:v>2026-08-01</x:v>
+      </x:c>
+      <x:c r="B26" s="4" t="str">
+        <x:v>中国人民保险集团-2027届统筹校园招聘</x:v>
+      </x:c>
+      <x:c r="C26" s="4" t="str">
+        <x:v>保险/金融</x:v>
+      </x:c>
+      <x:c r="D26" s="4" t="str">
+        <x:v>中央金融企业/国有</x:v>
+      </x:c>
+      <x:c r="E26" s="4" t="str">
+        <x:v>全国</x:v>
+      </x:c>
+      <x:c r="F26" s="4" t="str">
+        <x:v>正式批/集团统筹校园招聘</x:v>
+      </x:c>
+      <x:c r="G26" s="4" t="str">
+        <x:v>海内外2027届应届高校毕业生</x:v>
+      </x:c>
+      <x:c r="H26" s="4" t="str">
+        <x:v>集团本级及8家成员公司岗位，涵盖保险、投资、科技、精算、信托、再保险及综合职能等</x:v>
+      </x:c>
+      <x:c r="I26" s="15" t="str">
+        <x:v>https://picc.zhiye.com</x:v>
+      </x:c>
+      <x:c r="J26" s="4" t="str">
+        <x:v>2027-04-25（集团本级约2026年10月中旬截止；各单位总部及部分省级机构约2026年11月中下旬截止）</x:v>
+      </x:c>
+      <x:c r="K26" s="4" t="str">
+        <x:v>否（分批次开展笔试，部分岗位设置差异化笔试）</x:v>
+      </x:c>
+      <x:c r="L26" s="4" t="str">
+        <x:v>本轮新增；高校就业网公告来源为中国人民保险集团，官方招聘海报及官网入口已核验</x:v>
+      </x:c>
+      <x:c r="M26" s="4" t="str">
+        <x:v>P2-分机构截止</x:v>
+      </x:c>
+      <x:c r="N26" s="4" t="str">
+        <x:v>招聘覆盖集团本级及8家成员公司；每人最多可投2个志愿，同一机构限投1个岗位。总通道关闭时间较晚，但各机构有更早截止时间，应按目标单位页面尽早投递。</x:v>
+      </x:c>
+      <x:c r="O26" s="15" t="str">
+        <x:v>https://career.smbu.edu.cn/detail/online?id=3537075</x:v>
+      </x:c>
+      <x:c r="P26" s="16" t="str">
+        <x:v>A-官方招聘海报与中国人民保险招聘官网入口已核验</x:v>
+      </x:c>
+      <x:c r="Q26" s="4" t="str">
+        <x:v>2026-08-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="54" customHeight="1">
+      <x:c r="A27" s="18" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
-      <x:c r="B26" s="4" t="str">
-        <x:v>四方股份</x:v>
-      </x:c>
-      <x:c r="C26" s="4" t="str">
-        <x:v>电力系统/工业自动化</x:v>
-      </x:c>
-      <x:c r="D26" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E26" s="4" t="str">
-        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
-      </x:c>
-      <x:c r="F26" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G26" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H26" s="4" t="str">
-        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
-      </x:c>
-      <x:c r="I26" s="15" t="str">
-        <x:v>https://www.sf-auto.com/campus</x:v>
-      </x:c>
-      <x:c r="J26" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K26" s="4" t="str">
+      <x:c r="B27" s="18" t="str">
+        <x:v>恒丰银行总行-雏鹰计划</x:v>
+      </x:c>
+      <x:c r="C27" s="18" t="str">
+        <x:v>银行/金融</x:v>
+      </x:c>
+      <x:c r="D27" s="18" t="str">
+        <x:v>股份制商业银行</x:v>
+      </x:c>
+      <x:c r="E27" s="18" t="str">
+        <x:v>总行及相关机构，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F27" s="18" t="str">
+        <x:v>暑期实习/秋招储备</x:v>
+      </x:c>
+      <x:c r="G27" s="18" t="str">
+        <x:v>2027届硕士及以上，以公告要求为准</x:v>
+      </x:c>
+      <x:c r="H27" s="18" t="str">
+        <x:v>总行实习生，具体专业和方向以官方公告为准</x:v>
+      </x:c>
+      <x:c r="I27" s="19" t="str">
+        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
+      </x:c>
+      <x:c r="J27" s="18" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K27" s="18" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
-      <x:c r="L26" s="4" t="str">
-        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="M26" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N26" s="4" t="str">
-        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
-      </x:c>
-      <x:c r="O26" s="15" t="str">
-        <x:v>https://www.sf-auto.com/campus</x:v>
-      </x:c>
-      <x:c r="P26" s="16" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="Q26" s="4" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="54" customHeight="1">
-      <x:c r="A27" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
-      </x:c>
-      <x:c r="B27" s="4" t="str">
-        <x:v>苏纳光电</x:v>
-      </x:c>
-      <x:c r="C27" s="4" t="str">
-        <x:v>光电/科研</x:v>
-      </x:c>
-      <x:c r="D27" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
-      </x:c>
-      <x:c r="E27" s="4" t="str">
-        <x:v>苏州、上海</x:v>
-      </x:c>
-      <x:c r="F27" s="4" t="str">
-        <x:v>提前批/Open Day</x:v>
-      </x:c>
-      <x:c r="G27" s="4" t="str">
-        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H27" s="4" t="str">
-        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
-      </x:c>
-      <x:c r="I27" s="15" t="str">
-        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
-      </x:c>
-      <x:c r="J27" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K27" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L27" s="4" t="str">
-        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
-      </x:c>
-      <x:c r="M27" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N27" s="4" t="str">
-        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
-      </x:c>
-      <x:c r="O27" s="15" t="str">
-        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+      <x:c r="L27" s="18" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M27" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N27" s="18" t="str">
+        <x:v>官方公告显示7月31日24:00截止，实习期安排和具体岗位以恒丰银行招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O27" s="19" t="str">
+        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
       </x:c>
       <x:c r="P27" s="16" t="str">
-        <x:v>A-企业官方校园招聘系统已核验</x:v>
-      </x:c>
-      <x:c r="Q27" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>A-企业官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q27" s="18" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="54" customHeight="1">
@@ -1941,28 +1941,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B28" s="4" t="str">
-        <x:v>特斯拉中国</x:v>
+        <x:v>四方股份</x:v>
       </x:c>
       <x:c r="C28" s="4" t="str">
-        <x:v>新能源汽车/智能制造</x:v>
+        <x:v>电力系统/工业自动化</x:v>
       </x:c>
       <x:c r="D28" s="4" t="str">
-        <x:v>外资/上市</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E28" s="4" t="str">
-        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
+        <x:v>北京、保定、南京、湖州、武汉、深圳等</x:v>
       </x:c>
       <x:c r="F28" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G28" s="4" t="str">
-        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H28" s="4" t="str">
-        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
+        <x:v>技术研发、软件、硬件、电气、工程、市场及职能岗位</x:v>
       </x:c>
       <x:c r="I28" s="15" t="str">
-        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
+        <x:v>https://www.sf-auto.com/campus</x:v>
       </x:c>
       <x:c r="J28" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -1971,75 +1971,75 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L28" s="4" t="str">
-        <x:v>本轮新确认；企业官方职位页已核验</x:v>
+        <x:v>本轮新确认；企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="M28" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N28" s="4" t="str">
-        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
+        <x:v>提前批具体岗位、工作城市和选拔流程以四方股份校园招聘官网为准。</x:v>
       </x:c>
       <x:c r="O28" s="15" t="str">
-        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
+        <x:v>https://www.sf-auto.com/campus</x:v>
       </x:c>
       <x:c r="P28" s="16" t="str">
-        <x:v>A-企业官方职位页已核验</x:v>
+        <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
       <x:c r="Q28" s="4" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="54" customHeight="1">
-      <x:c r="A29" s="18" t="str">
+      <x:c r="A29" s="4" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
-      <x:c r="B29" s="18" t="str">
-        <x:v>天健会计师事务所-暑期实习培训生</x:v>
-      </x:c>
-      <x:c r="C29" s="18" t="str">
-        <x:v>会计审计/专业服务</x:v>
-      </x:c>
-      <x:c r="D29" s="18" t="str">
-        <x:v>会计师事务所</x:v>
-      </x:c>
-      <x:c r="E29" s="18" t="str">
-        <x:v>上海等，以职位页为准</x:v>
-      </x:c>
-      <x:c r="F29" s="18" t="str">
-        <x:v>暑期实习/培训生</x:v>
-      </x:c>
-      <x:c r="G29" s="18" t="str">
-        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H29" s="18" t="str">
-        <x:v>财务审计暑期实习培训生</x:v>
-      </x:c>
-      <x:c r="I29" s="19" t="str">
-        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
-      </x:c>
-      <x:c r="J29" s="18" t="str">
+      <x:c r="B29" s="4" t="str">
+        <x:v>苏纳光电</x:v>
+      </x:c>
+      <x:c r="C29" s="4" t="str">
+        <x:v>光电/科研</x:v>
+      </x:c>
+      <x:c r="D29" s="4" t="str">
+        <x:v>民营/科技企业</x:v>
+      </x:c>
+      <x:c r="E29" s="4" t="str">
+        <x:v>苏州、上海</x:v>
+      </x:c>
+      <x:c r="F29" s="4" t="str">
+        <x:v>提前批/Open Day</x:v>
+      </x:c>
+      <x:c r="G29" s="4" t="str">
+        <x:v>2027届硕士/博士，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H29" s="4" t="str">
+        <x:v>光电、激光、研发、工艺、软件、测试及职能岗位</x:v>
+      </x:c>
+      <x:c r="I29" s="15" t="str">
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+      </x:c>
+      <x:c r="J29" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K29" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L29" s="4" t="str">
+        <x:v>本轮新确认；企业官方校园招聘系统已核验</x:v>
+      </x:c>
+      <x:c r="M29" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N29" s="4" t="str">
+        <x:v>Open Day及提前批岗位安排以苏纳SUNA官方校园招聘系统为准。</x:v>
+      </x:c>
+      <x:c r="O29" s="15" t="str">
+        <x:v>https://suna-opto.zhiye.com/campus/jobs</x:v>
+      </x:c>
+      <x:c r="P29" s="16" t="str">
+        <x:v>A-企业官方校园招聘系统已核验</x:v>
+      </x:c>
+      <x:c r="Q29" s="4" t="str">
         <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K29" s="18" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L29" s="18" t="str">
-        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M29" s="18" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N29" s="18" t="str">
-        <x:v>公开公告显示7月31日截止；具体办公地点、专业要求和实习安排以天健招聘官网为准。</x:v>
-      </x:c>
-      <x:c r="O29" s="19" t="str">
-        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
-      </x:c>
-      <x:c r="P29" s="16" t="str">
-        <x:v>A-企业官方招聘入口已核验</x:v>
-      </x:c>
-      <x:c r="Q29" s="18" t="str">
-        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="54" customHeight="1">
@@ -2047,28 +2047,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B30" s="4" t="str">
-        <x:v>西安紫光国芯半导体</x:v>
+        <x:v>特斯拉中国</x:v>
       </x:c>
       <x:c r="C30" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>新能源汽车/智能制造</x:v>
       </x:c>
       <x:c r="D30" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>外资/上市</x:v>
       </x:c>
       <x:c r="E30" s="4" t="str">
-        <x:v>西安、上海、成都</x:v>
+        <x:v>上海及中国大陆招聘城市，以职位页为准</x:v>
       </x:c>
       <x:c r="F30" s="4" t="str">
         <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G30" s="4" t="str">
-        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H30" s="4" t="str">
-        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
+        <x:v>工程、软件、制造、供应链、销售服务及职能岗位</x:v>
       </x:c>
       <x:c r="I30" s="15" t="str">
-        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
       </x:c>
       <x:c r="J30" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2077,75 +2077,75 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L30" s="4" t="str">
-        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
+        <x:v>本轮新确认；企业官方职位页已核验</x:v>
       </x:c>
       <x:c r="M30" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N30" s="4" t="str">
-        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
+        <x:v>岗位分批开放并可能随时关闭，请在特斯拉官方职位搜索页筛选中国及校园岗位。</x:v>
       </x:c>
       <x:c r="O30" s="15" t="str">
-        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
+        <x:v>https://www.tesla.com/careers/search/?country=CN</x:v>
       </x:c>
       <x:c r="P30" s="16" t="str">
-        <x:v>A-企业官方招聘页已核验</x:v>
+        <x:v>A-企业官方职位页已核验</x:v>
       </x:c>
       <x:c r="Q30" s="4" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="54" customHeight="1">
-      <x:c r="A31" s="4" t="str">
+      <x:c r="A31" s="18" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
-      <x:c r="B31" s="4" t="str">
-        <x:v>新大陆自动识别</x:v>
-      </x:c>
-      <x:c r="C31" s="4" t="str">
-        <x:v>计算机视觉/智能硬件</x:v>
-      </x:c>
-      <x:c r="D31" s="4" t="str">
-        <x:v>民营/上市公司子公司</x:v>
-      </x:c>
-      <x:c r="E31" s="4" t="str">
-        <x:v>福州总部及全国/海外岗位</x:v>
-      </x:c>
-      <x:c r="F31" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
-      </x:c>
-      <x:c r="G31" s="4" t="str">
-        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
-      </x:c>
-      <x:c r="H31" s="4" t="str">
-        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
-      </x:c>
-      <x:c r="I31" s="15" t="str">
-        <x:v>https://nlscan.zhiye.com/Campus</x:v>
-      </x:c>
-      <x:c r="J31" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K31" s="4" t="str">
+      <x:c r="B31" s="18" t="str">
+        <x:v>天健会计师事务所-暑期实习培训生</x:v>
+      </x:c>
+      <x:c r="C31" s="18" t="str">
+        <x:v>会计审计/专业服务</x:v>
+      </x:c>
+      <x:c r="D31" s="18" t="str">
+        <x:v>会计师事务所</x:v>
+      </x:c>
+      <x:c r="E31" s="18" t="str">
+        <x:v>上海等，以职位页为准</x:v>
+      </x:c>
+      <x:c r="F31" s="18" t="str">
+        <x:v>暑期实习/培训生</x:v>
+      </x:c>
+      <x:c r="G31" s="18" t="str">
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H31" s="18" t="str">
+        <x:v>财务审计暑期实习培训生</x:v>
+      </x:c>
+      <x:c r="I31" s="19" t="str">
+        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
+      </x:c>
+      <x:c r="J31" s="18" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K31" s="18" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
-      <x:c r="L31" s="4" t="str">
-        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
-      </x:c>
-      <x:c r="M31" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N31" s="4" t="str">
-        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
-      </x:c>
-      <x:c r="O31" s="15" t="str">
-        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
+      <x:c r="L31" s="18" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M31" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N31" s="18" t="str">
+        <x:v>公开公告显示7月31日截止；具体办公地点、专业要求和实习安排以天健招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O31" s="19" t="str">
+        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
       </x:c>
       <x:c r="P31" s="16" t="str">
-        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
-      </x:c>
-      <x:c r="Q31" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>A-企业官方招聘入口已核验</x:v>
+      </x:c>
+      <x:c r="Q31" s="18" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="54" customHeight="1">
@@ -2153,28 +2153,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B32" s="4" t="str">
-        <x:v>兆易创新</x:v>
+        <x:v>西安紫光国芯半导体</x:v>
       </x:c>
       <x:c r="C32" s="4" t="str">
         <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D32" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E32" s="4" t="str">
-        <x:v>北京、上海、武汉、合肥等，以岗位页为准</x:v>
+        <x:v>西安、上海、成都</x:v>
       </x:c>
       <x:c r="F32" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G32" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届硕士及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H32" s="4" t="str">
-        <x:v>芯片设计、验证、嵌入式、软件、应用、测试及职能岗位</x:v>
+        <x:v>ASIC、数字/模拟IC设计、验证、嵌入式、测试及应用岗位</x:v>
       </x:c>
       <x:c r="I32" s="15" t="str">
-        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
       </x:c>
       <x:c r="J32" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2183,16 +2183,16 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L32" s="4" t="str">
-        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
+        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
       </x:c>
       <x:c r="M32" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N32" s="4" t="str">
-        <x:v>提前批岗位和城市以兆易创新官方加入我们页面为准，投递前确认职位仍开放。</x:v>
+        <x:v>不同城市和岗位学历要求不同，投递前以紫光国芯官方招聘页面为准。</x:v>
       </x:c>
       <x:c r="O32" s="15" t="str">
-        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
+        <x:v>https://www.unisemicon.com/index.php?m=content&amp;c=index&amp;a=lists&amp;catid=5</x:v>
       </x:c>
       <x:c r="P32" s="16" t="str">
         <x:v>A-企业官方招聘页已核验</x:v>
@@ -2206,28 +2206,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B33" s="4" t="str">
-        <x:v>中国航空发动机集团</x:v>
+        <x:v>新大陆自动识别</x:v>
       </x:c>
       <x:c r="C33" s="4" t="str">
-        <x:v>航空发动机/军工</x:v>
+        <x:v>计算机视觉/智能硬件</x:v>
       </x:c>
       <x:c r="D33" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/上市公司子公司</x:v>
       </x:c>
       <x:c r="E33" s="4" t="str">
-        <x:v>全国各院所及下属单位</x:v>
+        <x:v>福州总部及全国/海外岗位</x:v>
       </x:c>
       <x:c r="F33" s="4" t="str">
         <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G33" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2026年9月至2027年12月毕业的本科/硕士/博士</x:v>
       </x:c>
       <x:c r="H33" s="4" t="str">
-        <x:v>研发设计、工艺、试验、制造、材料、控制、软件及管理岗位</x:v>
+        <x:v>算法、软件、嵌入式、硬件、产品、营销及职能岗位</x:v>
       </x:c>
       <x:c r="I33" s="15" t="str">
-        <x:v>https://aecc.iguopin.com/notice2</x:v>
+        <x:v>https://nlscan.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J33" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2236,22 +2236,22 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L33" s="4" t="str">
-        <x:v>本轮复核；中国航发官方招聘平台当前显示2027届校园招聘岗位持续开放</x:v>
+        <x:v>本轮新确认；企业官方校招系统已核验</x:v>
       </x:c>
       <x:c r="M33" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N33" s="4" t="str">
-        <x:v>各单位岗位和截止时间不同，需在中国航发招聘平台按单位和专业筛选；本次复核到159家招聘单位及多项研发、工艺、制造、控制和软件岗位。</x:v>
+        <x:v>研发类岗位以福州总部为主，营销岗位覆盖国内外，具体要求以官方职位页为准。</x:v>
       </x:c>
       <x:c r="O33" s="15" t="str">
-        <x:v>https://aecc.iguopin.com/job</x:v>
+        <x:v>https://www.nlscan.com/campusrecruitment.html</x:v>
       </x:c>
       <x:c r="P33" s="16" t="str">
-        <x:v>A-中国航发官方招聘平台已核验</x:v>
+        <x:v>A-企业官网与官方校招系统交叉核验</x:v>
       </x:c>
       <x:c r="Q33" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="54" customHeight="1">
@@ -2259,28 +2259,28 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B34" s="4" t="str">
-        <x:v>中粮资本-粮曦计划</x:v>
+        <x:v>兆易创新</x:v>
       </x:c>
       <x:c r="C34" s="4" t="str">
-        <x:v>金融/投资/资管</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D34" s="4" t="str">
-        <x:v>央企/金融控股</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E34" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>北京、上海、武汉、合肥等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F34" s="4" t="str">
-        <x:v>培养计划/实习</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G34" s="4" t="str">
-        <x:v>2027-2029届硕士及以上，以公告要求为准</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H34" s="4" t="str">
-        <x:v>金融、投资、风险、运营、人力资源及综合管理方向</x:v>
+        <x:v>芯片设计、验证、嵌入式、软件、应用、测试及职能岗位</x:v>
       </x:c>
       <x:c r="I34" s="15" t="str">
-        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
       </x:c>
       <x:c r="J34" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2289,16 +2289,16 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L34" s="4" t="str">
-        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
+        <x:v>本轮新确认；企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="M34" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N34" s="4" t="str">
-        <x:v>粮曦计划具体批次、面向人群和岗位以中粮资本官方加入我们页面及公告为准。</x:v>
+        <x:v>提前批岗位和城市以兆易创新官方加入我们页面为准，投递前确认职位仍开放。</x:v>
       </x:c>
       <x:c r="O34" s="15" t="str">
-        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
+        <x:v>https://www.gigadevice.com.cn/about/career</x:v>
       </x:c>
       <x:c r="P34" s="16" t="str">
         <x:v>A-企业官方招聘页已核验</x:v>
@@ -2312,293 +2312,293 @@
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B35" s="4" t="str">
-        <x:v>中移九天人工智能科技</x:v>
+        <x:v>中国航空发动机集团</x:v>
       </x:c>
       <x:c r="C35" s="4" t="str">
-        <x:v>AI/软件/云计算</x:v>
+        <x:v>航空发动机/军工</x:v>
       </x:c>
       <x:c r="D35" s="4" t="str">
-        <x:v>央企子公司</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E35" s="4" t="str">
-        <x:v>北京、西安、广州、深圳</x:v>
+        <x:v>全国各院所及下属单位</x:v>
       </x:c>
       <x:c r="F35" s="4" t="str">
-        <x:v>正式批/超级实习生</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G35" s="4" t="str">
-        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H35" s="4" t="str">
-        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
+        <x:v>研发设计、工艺、试验、制造、材料、控制、软件及管理岗位</x:v>
       </x:c>
       <x:c r="I35" s="15" t="str">
-        <x:v>https://job.10086.cn/personal/campus/</x:v>
+        <x:v>https://aecc.iguopin.com/notice2</x:v>
       </x:c>
       <x:c r="J35" s="4" t="str">
-        <x:v>2026-09-27</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K35" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L35" s="4" t="str">
-        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
+        <x:v>本轮复核；中国航发官方招聘平台当前显示2027届校园招聘岗位持续开放</x:v>
       </x:c>
       <x:c r="M35" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N35" s="4" t="str">
-        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
+        <x:v>各单位岗位和截止时间不同，需在中国航发招聘平台按单位和专业筛选；本次复核到159家招聘单位及多项研发、工艺、制造、控制和软件岗位。</x:v>
       </x:c>
       <x:c r="O35" s="15" t="str">
-        <x:v>https://job.10086.cn/personal/campus/</x:v>
+        <x:v>https://aecc.iguopin.com/job</x:v>
       </x:c>
       <x:c r="P35" s="16" t="str">
-        <x:v>A-中国移动官方招聘平台已核验</x:v>
+        <x:v>A-中国航发官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="Q35" s="4" t="str">
-        <x:v>2026-07-31</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="54" customHeight="1">
       <x:c r="A36" s="4" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B36" s="4" t="str">
-        <x:v>广州市卓越教育集团</x:v>
+        <x:v>中粮资本-粮曦计划</x:v>
       </x:c>
       <x:c r="C36" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>金融/投资/资管</x:v>
       </x:c>
       <x:c r="D36" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企/金融控股</x:v>
       </x:c>
       <x:c r="E36" s="4" t="str">
-        <x:v>广州等，以职位页为准</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F36" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>培养计划/实习</x:v>
       </x:c>
       <x:c r="G36" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027-2029届硕士及以上，以公告要求为准</x:v>
       </x:c>
       <x:c r="H36" s="4" t="str">
-        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+        <x:v>金融、投资、风险、运营、人力资源及综合管理方向</x:v>
       </x:c>
       <x:c r="I36" s="15" t="str">
-        <x:v>https://zyjob.hotjob.cn/</x:v>
+        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
       </x:c>
       <x:c r="J36" s="4" t="str">
-        <x:v>2026-10-26</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K36" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L36" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
+        <x:v>本轮新确认；企业官方加入我们页面已核验</x:v>
       </x:c>
       <x:c r="M36" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N36" s="4" t="str">
-        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
+        <x:v>粮曦计划具体批次、面向人群和岗位以中粮资本官方加入我们页面及公告为准。</x:v>
       </x:c>
       <x:c r="O36" s="15" t="str">
-        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
+        <x:v>http://www.cofco-capital.com/join_us.html</x:v>
       </x:c>
       <x:c r="P36" s="16" t="str">
-        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
+        <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
       <x:c r="Q36" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="54" customHeight="1">
       <x:c r="A37" s="4" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B37" s="4" t="str">
-        <x:v>搜狐畅游</x:v>
+        <x:v>中移九天人工智能科技</x:v>
       </x:c>
       <x:c r="C37" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>AI/软件/云计算</x:v>
       </x:c>
       <x:c r="D37" s="4" t="str">
-        <x:v>民营/互联网</x:v>
+        <x:v>央企子公司</x:v>
       </x:c>
       <x:c r="E37" s="4" t="str">
-        <x:v>以岗位页面为准</x:v>
+        <x:v>北京、西安、广州、深圳</x:v>
       </x:c>
       <x:c r="F37" s="4" t="str">
-        <x:v>提前批/校园招聘</x:v>
+        <x:v>正式批/超级实习生</x:v>
       </x:c>
       <x:c r="G37" s="4" t="str">
-        <x:v>2027届毕业生（部分岗位兼收2026届）</x:v>
+        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
       </x:c>
       <x:c r="H37" s="4" t="str">
-        <x:v>游戏策划、游戏开发、游戏美术、游戏运营、业务支持、平台开发、平台职能、游戏测试8大类岗位</x:v>
+        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
       </x:c>
       <x:c r="I37" s="15" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/cyou-inc/42233?recommendCode=DSRgNQU7#/jobs</x:v>
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="J37" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-09-27</x:v>
       </x:c>
       <x:c r="K37" s="4" t="str">
-        <x:v>非免笔试；提前批未录取可参加后续统一笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L37" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；官方投递入口已核验</x:v>
+        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
       </x:c>
       <x:c r="M37" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N37" s="4" t="str">
-        <x:v>深圳北理莫斯科大学就业网公告《搜狐畅游2027届秋季校园招聘提前批正式启动！》发布于2026-07-28；提前批流程快、部分岗位有直通面试机会，未被录取者可参与后续统一笔试，部分热招岗位招满即停。</x:v>
+        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
       </x:c>
       <x:c r="O37" s="15" t="str">
-        <x:v>https://career.smbu.edu.cn/detail/online?id=3535355</x:v>
-      </x:c>
-      <x:c r="P37" s="14" t="str">
-        <x:v>B-可信高校就业网公告含官方投递链接</x:v>
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
+      </x:c>
+      <x:c r="P37" s="16" t="str">
+        <x:v>A-中国移动官方招聘平台已核验</x:v>
       </x:c>
       <x:c r="Q37" s="4" t="str">
-        <x:v>2026-08-04</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="54" customHeight="1">
       <x:c r="A38" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B38" s="4" t="str">
-        <x:v>我乐家居</x:v>
+        <x:v>广州市卓越教育集团</x:v>
       </x:c>
       <x:c r="C38" s="4" t="str">
-        <x:v>家居/消费品/智能制造</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D38" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E38" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>广州等，以职位页为准</x:v>
       </x:c>
       <x:c r="F38" s="4" t="str">
-        <x:v>提前批/校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G38" s="4" t="str">
-        <x:v>2027届本科及以上，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H38" s="4" t="str">
-        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
+        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
       <x:c r="I38" s="15" t="str">
-        <x:v>https://olo-home.zhiye.com/Campus</x:v>
+        <x:v>https://zyjob.hotjob.cn/</x:v>
       </x:c>
       <x:c r="J38" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-26</x:v>
       </x:c>
       <x:c r="K38" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L38" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
+        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
       </x:c>
       <x:c r="M38" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N38" s="4" t="str">
-        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
+        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
       </x:c>
       <x:c r="O38" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P38" s="14" t="str">
-        <x:v>B-高校就业网转载企业来源</x:v>
+        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
+      </x:c>
+      <x:c r="P38" s="16" t="str">
+        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
       </x:c>
       <x:c r="Q38" s="4" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="54" customHeight="1">
       <x:c r="A39" s="4" t="str">
-        <x:v>2026-07-26</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B39" s="4" t="str">
-        <x:v>轩宇信息</x:v>
+        <x:v>搜狐畅游</x:v>
       </x:c>
       <x:c r="C39" s="4" t="str">
-        <x:v>航天/军工信息化/软件</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D39" s="4" t="str">
-        <x:v>央企子公司/高新技术企业</x:v>
+        <x:v>民营/互联网</x:v>
       </x:c>
       <x:c r="E39" s="4" t="str">
-        <x:v>北京、杭州、西安</x:v>
+        <x:v>以岗位页面为准</x:v>
       </x:c>
       <x:c r="F39" s="4" t="str">
-        <x:v>AI专项/提前批</x:v>
+        <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G39" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届毕业生（部分岗位兼收2026届）</x:v>
       </x:c>
       <x:c r="H39" s="4" t="str">
-        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
+        <x:v>游戏策划、游戏开发、游戏美术、游戏运营、业务支持、平台开发、平台职能、游戏测试8大类岗位</x:v>
       </x:c>
       <x:c r="I39" s="15" t="str">
-        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
+        <x:v>https://app.mokahr.com/m/campus_apply/cyou-inc/42233?recommendCode=DSRgNQU7#/jobs</x:v>
       </x:c>
       <x:c r="J39" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K39" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>非免笔试；提前批未录取可参加后续统一笔试</x:v>
       </x:c>
       <x:c r="L39" s="4" t="str">
-        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
+        <x:v>可信高校就业网公告显示开放；官方投递入口已核验</x:v>
       </x:c>
       <x:c r="M39" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N39" s="4" t="str">
-        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
+        <x:v>深圳北理莫斯科大学就业网公告《搜狐畅游2027届秋季校园招聘提前批正式启动！》发布于2026-07-28；提前批流程快、部分岗位有直通面试机会，未被录取者可参与后续统一笔试，部分热招岗位招满即停。</x:v>
       </x:c>
       <x:c r="O39" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P39" s="16" t="str">
-        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
+        <x:v>https://career.smbu.edu.cn/detail/online?id=3535355</x:v>
+      </x:c>
+      <x:c r="P39" s="14" t="str">
+        <x:v>B-可信高校就业网公告含官方投递链接</x:v>
       </x:c>
       <x:c r="Q39" s="4" t="str">
-        <x:v>2026-07-29</x:v>
+        <x:v>2026-08-04</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="54" customHeight="1">
       <x:c r="A40" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="B40" s="4" t="str">
-        <x:v>卡尔动力</x:v>
+        <x:v>我乐家居</x:v>
       </x:c>
       <x:c r="C40" s="4" t="str">
-        <x:v>自动驾驶/智能汽车</x:v>
+        <x:v>家居/消费品/智能制造</x:v>
       </x:c>
       <x:c r="D40" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E40" s="4" t="str">
-        <x:v>北京、上海、天津等</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F40" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>提前批/校园招聘</x:v>
       </x:c>
       <x:c r="G40" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届本科及以上，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H40" s="4" t="str">
-        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
+        <x:v>自动化、工业工程、产品设计等，具体以公告二维码岗位为准</x:v>
       </x:c>
       <x:c r="I40" s="15" t="str">
-        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
+        <x:v>https://olo-home.zhiye.com/Campus</x:v>
       </x:c>
       <x:c r="J40" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2607,75 +2607,75 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L40" s="4" t="str">
-        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文/二维码</x:v>
       </x:c>
       <x:c r="M40" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N40" s="4" t="str">
-        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
+        <x:v>公告发布时间为2026-07-27，地域标注江苏南京；岗位详情和投递二维码在公告图片中，投前确认学历、专业与岗位要求。</x:v>
       </x:c>
       <x:c r="O40" s="15" t="str">
-        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894368&amp;idx=8&amp;sn=1c45c0ca7329bca7fd4fa3ec2c5d3bcc&amp;chksm=e8473f9c1207ee3d16dc98bf376084b73ba7a46e5bbf96ce7efad74f251501eea9ffeeadd647&amp;scene=27</x:v>
       </x:c>
       <x:c r="P40" s="14" t="str">
         <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
       <x:c r="Q40" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="54" customHeight="1">
       <x:c r="A41" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-07-26</x:v>
       </x:c>
       <x:c r="B41" s="4" t="str">
-        <x:v>深信服-X-STAR顶尖人才计划</x:v>
+        <x:v>轩宇信息</x:v>
       </x:c>
       <x:c r="C41" s="4" t="str">
-        <x:v>网络安全/云计算/软件</x:v>
+        <x:v>航天/军工信息化/软件</x:v>
       </x:c>
       <x:c r="D41" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企子公司/高新技术企业</x:v>
       </x:c>
       <x:c r="E41" s="4" t="str">
-        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
+        <x:v>北京、杭州、西安</x:v>
       </x:c>
       <x:c r="F41" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>AI专项/提前批</x:v>
       </x:c>
       <x:c r="G41" s="4" t="str">
-        <x:v>顶尖人才，本硕博按岗位要求</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H41" s="4" t="str">
-        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
+        <x:v>AI算法、软件研发、嵌入式软件、系统集成、软件测试/评测、FPGA验证</x:v>
       </x:c>
       <x:c r="I41" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
+        <x:v>https://www.sunwiseinfo.com/zxns</x:v>
       </x:c>
       <x:c r="J41" s="4" t="str">
-        <x:v>2026-09-25</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K41" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L41" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>已核验开放（高校公告与企业官网交叉核验）</x:v>
       </x:c>
       <x:c r="M41" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N41" s="4" t="str">
-        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
+        <x:v>公司为航天科技集团五院502所全资子公司；高校公告发布时间为2026-07-26，具体AI专项岗位与学历要求以公告图片和官网岗位页为准。</x:v>
       </x:c>
       <x:c r="O41" s="15" t="str">
-        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIzODQ0MjEyNw==&amp;mid=2247894337&amp;idx=6&amp;sn=449461c8cd4a310ac4d4ae953d0a16f9&amp;chksm=e845ef01105437310f7fefcb8b62bbf8bb7a81b0a3f2420832f8032e3c48eab47c04487ce2e9&amp;scene=27</x:v>
       </x:c>
       <x:c r="P41" s="16" t="str">
-        <x:v>A-高校就业网含官方投递链接</x:v>
+        <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
       </x:c>
       <x:c r="Q41" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="54" customHeight="1">
@@ -2683,28 +2683,28 @@
         <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B42" s="4" t="str">
-        <x:v>希夕智能</x:v>
+        <x:v>卡尔动力</x:v>
       </x:c>
       <x:c r="C42" s="4" t="str">
-        <x:v>机器人/智能制造</x:v>
+        <x:v>自动驾驶/智能汽车</x:v>
       </x:c>
       <x:c r="D42" s="4" t="str">
         <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E42" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京、上海、天津等</x:v>
       </x:c>
       <x:c r="F42" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G42" s="4" t="str">
-        <x:v>2027届本科及以上</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H42" s="4" t="str">
-        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
+        <x:v>自动驾驶算法、感知/规划/控制、软件、硬件、车辆工程、测试及系统研发</x:v>
       </x:c>
       <x:c r="I42" s="15" t="str">
-        <x:v>https://sunseed.zhiye.com/jobs</x:v>
+        <x:v>https://kargobot.jobs.feishu.cn/267069/</x:v>
       </x:c>
       <x:c r="J42" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2713,19 +2713,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L42" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
+        <x:v>高校就业网转载企业公告显示开放；投递入口见公告原文</x:v>
       </x:c>
       <x:c r="M42" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N42" s="4" t="str">
-        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
+        <x:v>公开信息标注base北京、上海、天津等；卡尔动力岗位详情主要以公告图片/原文为准。</x:v>
       </x:c>
       <x:c r="O42" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
+        <x:v>https://wtu.91wllm.cn/news/view/aid/299821/tag/xxtz</x:v>
       </x:c>
       <x:c r="P42" s="14" t="str">
-        <x:v>B-高校就业平台转载企业来源</x:v>
+        <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
       <x:c r="Q42" s="4" t="str">
         <x:v>2026-07-27</x:v>
@@ -2733,84 +2733,84 @@
     </x:row>
     <x:row r="43" ht="54" customHeight="1">
       <x:c r="A43" s="4" t="str">
-        <x:v>不晚于2026-07-24</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B43" s="4" t="str">
-        <x:v>中国兵器工业集团</x:v>
+        <x:v>深信服-X-STAR顶尖人才计划</x:v>
       </x:c>
       <x:c r="C43" s="4" t="str">
-        <x:v>军工/高端装备</x:v>
+        <x:v>网络安全/云计算/软件</x:v>
       </x:c>
       <x:c r="D43" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E43" s="4" t="str">
-        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
+        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F43" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G43" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>顶尖人才，本硕博按岗位要求</x:v>
       </x:c>
       <x:c r="H43" s="4" t="str">
-        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
+        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
       </x:c>
       <x:c r="I43" s="15" t="str">
-        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
       </x:c>
       <x:c r="J43" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-09-25</x:v>
       </x:c>
       <x:c r="K43" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L43" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M43" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N43" s="4" t="str">
-        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
+        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
       </x:c>
       <x:c r="O43" s="15" t="str">
-        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
-      </x:c>
-      <x:c r="P43" s="14" t="str">
-        <x:v>B-公开招聘公告/集团入口</x:v>
+        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
+      </x:c>
+      <x:c r="P43" s="16" t="str">
+        <x:v>A-高校就业网含官方投递链接</x:v>
       </x:c>
       <x:c r="Q43" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="54" customHeight="1">
       <x:c r="A44" s="4" t="str">
-        <x:v>2026-07-23</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B44" s="4" t="str">
-        <x:v>禾迈股份</x:v>
+        <x:v>希夕智能</x:v>
       </x:c>
       <x:c r="C44" s="4" t="str">
-        <x:v>光伏/电力电子</x:v>
+        <x:v>机器人/智能制造</x:v>
       </x:c>
       <x:c r="D44" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E44" s="4" t="str">
-        <x:v>杭州等，以岗位页为准</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F44" s="4" t="str">
-        <x:v>研发类提前批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G44" s="4" t="str">
-        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
+        <x:v>2027届本科及以上</x:v>
       </x:c>
       <x:c r="H44" s="4" t="str">
-        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
+        <x:v>机器人研发、软件/算法、机械/电气、调试/应用等，具体以公告二维码岗位为准</x:v>
       </x:c>
       <x:c r="I44" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
+        <x:v>https://sunseed.zhiye.com/jobs</x:v>
       </x:c>
       <x:c r="J44" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2819,19 +2819,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L44" s="4" t="str">
-        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
+        <x:v>公开招聘公告显示开放；投递入口为公告原文/二维码</x:v>
       </x:c>
       <x:c r="M44" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N44" s="4" t="str">
-        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
+        <x:v>企业来源为希夕智能，招聘详情主要以图片和原文二维码展示；投递前确认具体岗位与办公城市。</x:v>
       </x:c>
       <x:c r="O44" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3NDUwOTEzNA==&amp;mid=2653230193&amp;idx=3&amp;sn=56fc191e0d65c0794431f870ce759256</x:v>
       </x:c>
       <x:c r="P44" s="14" t="str">
-        <x:v>B-高校就业网转载企业公告</x:v>
+        <x:v>B-高校就业平台转载企业来源</x:v>
       </x:c>
       <x:c r="Q44" s="4" t="str">
         <x:v>2026-07-27</x:v>
@@ -2839,19 +2839,19 @@
     </x:row>
     <x:row r="45" ht="54" customHeight="1">
       <x:c r="A45" s="4" t="str">
-        <x:v>2026-07-23</x:v>
+        <x:v>不晚于2026-07-24</x:v>
       </x:c>
       <x:c r="B45" s="4" t="str">
-        <x:v>极客未来</x:v>
+        <x:v>中国兵器工业集团</x:v>
       </x:c>
       <x:c r="C45" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>军工/高端装备</x:v>
       </x:c>
       <x:c r="D45" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E45" s="4" t="str">
-        <x:v>四川、重庆、广东</x:v>
+        <x:v>北京、西安、南京、内蒙古及全国下属单位</x:v>
       </x:c>
       <x:c r="F45" s="4" t="str">
         <x:v>提前批</x:v>
@@ -2860,116 +2860,116 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H45" s="4" t="str">
-        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+        <x:v>兵器、机械、电子、控制、计算机、材料、化工及管理</x:v>
       </x:c>
       <x:c r="I45" s="15" t="str">
-        <x:v>https://geek3.zhiye.com/campus/</x:v>
+        <x:v>https://zhaopin.norincogroup.com.cn/</x:v>
       </x:c>
       <x:c r="J45" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K45" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L45" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M45" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N45" s="4" t="str">
-        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
+        <x:v>集团下属单位独立筛选，部分岗位有政审及保密要求。</x:v>
       </x:c>
       <x:c r="O45" s="15" t="str">
-        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
+        <x:v>https://www.baidu.com/s?wd=%E4%B8%AD%E5%9B%BD%E5%85%B5%E5%99%A8%E9%9B%86%E5%9B%A22027%E5%B1%8A%E6%8B%9B%E8%81%98%E6%8F%90%E5%89%8D%E6%89%B9</x:v>
       </x:c>
       <x:c r="P45" s="14" t="str">
-        <x:v>B-高校就业网公告+公开招聘页面</x:v>
+        <x:v>B-公开招聘公告/集团入口</x:v>
       </x:c>
       <x:c r="Q45" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="54" customHeight="1">
       <x:c r="A46" s="4" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B46" s="4" t="str">
-        <x:v>安永EY</x:v>
+        <x:v>禾迈股份</x:v>
       </x:c>
       <x:c r="C46" s="4" t="str">
-        <x:v>会计审计/咨询/专业服务</x:v>
+        <x:v>光伏/电力电子</x:v>
       </x:c>
       <x:c r="D46" s="4" t="str">
-        <x:v>外资/专业服务机构</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E46" s="4" t="str">
-        <x:v>中国内地多地，以职位页为准</x:v>
+        <x:v>杭州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F46" s="4" t="str">
-        <x:v>正式批/秋季校园招聘</x:v>
+        <x:v>研发类提前批</x:v>
       </x:c>
       <x:c r="G46" s="4" t="str">
-        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
+        <x:v>2027届本科/硕士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H46" s="4" t="str">
-        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
+        <x:v>电力电子、硬件、嵌入式、软件、结构、测试、控制算法及研发职能等</x:v>
       </x:c>
       <x:c r="I46" s="15" t="str">
-        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/hoymiles/70377#/</x:v>
       </x:c>
       <x:c r="J46" s="4" t="str">
-        <x:v>2026年10月（具体日期未公布）</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K46" s="4" t="str">
-        <x:v>否；官方流程包含在线测评</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L46" s="4" t="str">
-        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
+        <x:v>公开招聘公告显示开放；点击公告原文投递</x:v>
       </x:c>
       <x:c r="M46" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N46" s="4" t="str">
-        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
+        <x:v>研发类提前批，具体岗位和投递二维码在公告图片/原文中；建议同时关注禾迈官方招聘页。</x:v>
       </x:c>
       <x:c r="O46" s="15" t="str">
-        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
-      </x:c>
-      <x:c r="P46" s="16" t="str">
-        <x:v>A-企业官方校招网站与职位页已核验</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3MDAxNzIxNQ==&amp;mid=2651791469&amp;idx=5&amp;sn=65c6b7616b931a76a9a7ffee76f848be</x:v>
+      </x:c>
+      <x:c r="P46" s="14" t="str">
+        <x:v>B-高校就业网转载企业公告</x:v>
       </x:c>
       <x:c r="Q46" s="4" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="54" customHeight="1">
       <x:c r="A47" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-23</x:v>
       </x:c>
       <x:c r="B47" s="4" t="str">
-        <x:v>阿里巴巴-阿里星计划</x:v>
+        <x:v>极客未来</x:v>
       </x:c>
       <x:c r="C47" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D47" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E47" s="4" t="str">
-        <x:v>杭州、北京、上海、深圳等</x:v>
+        <x:v>四川、重庆、广东</x:v>
       </x:c>
       <x:c r="F47" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G47" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H47" s="4" t="str">
-        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
+        <x:v>小学班课主讲教师、初中班课主讲教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
       <x:c r="I47" s="15" t="str">
-        <x:v>https://talent.alibaba.com/campus/</x:v>
+        <x:v>https://geek3.zhiye.com/campus/</x:v>
       </x:c>
       <x:c r="J47" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -2978,73 +2978,75 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L47" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>可信高校就业网公告显示开放；公开投递页已找到</x:v>
       </x:c>
       <x:c r="M47" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N47" s="4" t="str">
-        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
+        <x:v>中国地质大学（北京）就业网发布时间为2026-07-23；公开页面显示岗位地点为四川、重庆、广东，投前确认岗位是否仍开放及具体城市。</x:v>
       </x:c>
       <x:c r="O47" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P47" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://jiuye.cugb.edu.cn/Zhaopin/xiaozhao.html?type=1&amp;id=d3099e36-638c-fe93-2f2e-b7749d914e03</x:v>
+      </x:c>
+      <x:c r="P47" s="14" t="str">
+        <x:v>B-高校就业网公告+公开招聘页面</x:v>
       </x:c>
       <x:c r="Q47" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="54" customHeight="1">
       <x:c r="A48" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="B48" s="4" t="str">
-        <x:v>贝恩公司</x:v>
+        <x:v>安永EY</x:v>
       </x:c>
       <x:c r="C48" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>会计审计/咨询/专业服务</x:v>
       </x:c>
       <x:c r="D48" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>外资/专业服务机构</x:v>
       </x:c>
       <x:c r="E48" s="4" t="str">
-        <x:v>北京、上海、香港等</x:v>
+        <x:v>中国内地多地，以职位页为准</x:v>
       </x:c>
       <x:c r="F48" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G48" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026/2027届本科及以上毕业生，不限专业</x:v>
       </x:c>
       <x:c r="H48" s="4" t="str">
-        <x:v>助理咨询顾问等</x:v>
+        <x:v>审计、咨询、战略、税务与交易等全部业务线</x:v>
       </x:c>
       <x:c r="I48" s="15" t="str">
-        <x:v>https://www.bain.com/careers/</x:v>
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/job/3f07f2cc-f41e-4a61-9203-7ff249953423</x:v>
       </x:c>
       <x:c r="J48" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026年10月（具体日期未公布）</x:v>
       </x:c>
       <x:c r="K48" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>否；官方流程包含在线测评</x:v>
       </x:c>
       <x:c r="L48" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>企业官方秋季校园招聘项目已核验开放</x:v>
       </x:c>
       <x:c r="M48" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N48" s="4" t="str"/>
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N48" s="4" t="str">
+        <x:v>官方说明秋季招聘网申时间为每年8-10月；项目页显示职位发布于7月22日，具体城市和截止日以职位页为准。</x:v>
+      </x:c>
       <x:c r="O48" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P48" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://careers.ey.com.cn/campus-recruitment/ey/166374?locale=zh-CN/#/</x:v>
+      </x:c>
+      <x:c r="P48" s="16" t="str">
+        <x:v>A-企业官方校招网站与职位页已核验</x:v>
       </x:c>
       <x:c r="Q48" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="54" customHeight="1">
@@ -3052,28 +3054,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B49" s="4" t="str">
-        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
+        <x:v>阿里巴巴-阿里星计划</x:v>
       </x:c>
       <x:c r="C49" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D49" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E49" s="4" t="str">
-        <x:v>上海、北京等</x:v>
+        <x:v>杭州、北京、上海、深圳等</x:v>
       </x:c>
       <x:c r="F49" s="4" t="str">
-        <x:v>顶尖技术专项/提前批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G49" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H49" s="4" t="str">
-        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
+        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
       </x:c>
       <x:c r="I49" s="15" t="str">
-        <x:v>https://jobs.bilibili.com/</x:v>
+        <x:v>https://talent.alibaba.com/campus/</x:v>
       </x:c>
       <x:c r="J49" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3088,7 +3090,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N49" s="4" t="str">
-        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
+        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
       </x:c>
       <x:c r="O49" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3105,34 +3107,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B50" s="4" t="str">
-        <x:v>东风汽车-全球博士人才</x:v>
+        <x:v>贝恩公司</x:v>
       </x:c>
       <x:c r="C50" s="4" t="str">
-        <x:v>汽车/央企</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D50" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E50" s="4" t="str">
-        <x:v>武汉、广州、十堰及全国研发基地</x:v>
+        <x:v>北京、上海、香港等</x:v>
       </x:c>
       <x:c r="F50" s="4" t="str">
-        <x:v>博士专项</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G50" s="4" t="str">
-        <x:v>2026届及以后博士</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H50" s="4" t="str">
-        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
+        <x:v>助理咨询顾问等</x:v>
       </x:c>
       <x:c r="I50" s="15" t="str">
-        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
+        <x:v>https://www.bain.com/careers/</x:v>
       </x:c>
       <x:c r="J50" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K50" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L50" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3140,9 +3142,7 @@
       <x:c r="M50" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N50" s="4" t="str">
-        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
-      </x:c>
+      <x:c r="N50" s="4" t="str"/>
       <x:c r="O50" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3158,28 +3158,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B51" s="4" t="str">
-        <x:v>度小满-博士后人才招聘</x:v>
+        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
       </x:c>
       <x:c r="C51" s="4" t="str">
-        <x:v>金融科技</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="D51" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E51" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>上海、北京等</x:v>
       </x:c>
       <x:c r="F51" s="4" t="str">
-        <x:v>博士后专项</x:v>
+        <x:v>顶尖技术专项/提前批</x:v>
       </x:c>
       <x:c r="G51" s="4" t="str">
-        <x:v>2025/2026/2027届博士</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H51" s="4" t="str">
-        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
+        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
       </x:c>
       <x:c r="I51" s="15" t="str">
-        <x:v>https://campus.duxiaoman.com/</x:v>
+        <x:v>https://jobs.bilibili.com/</x:v>
       </x:c>
       <x:c r="J51" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3194,7 +3194,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N51" s="4" t="str">
-        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
+        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
       </x:c>
       <x:c r="O51" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3211,28 +3211,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B52" s="4" t="str">
-        <x:v>多益网络</x:v>
+        <x:v>东风汽车-全球博士人才</x:v>
       </x:c>
       <x:c r="C52" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>汽车/央企</x:v>
       </x:c>
       <x:c r="D52" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E52" s="4" t="str">
-        <x:v>广州、武汉、成都等</x:v>
+        <x:v>武汉、广州、十堰及全国研发基地</x:v>
       </x:c>
       <x:c r="F52" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>博士专项</x:v>
       </x:c>
       <x:c r="G52" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2026届及以后博士</x:v>
       </x:c>
       <x:c r="H52" s="4" t="str">
-        <x:v>程序、策划、美术、运营、市场及职能</x:v>
+        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
       </x:c>
       <x:c r="I52" s="15" t="str">
-        <x:v>https://www.duoyi.com/job/</x:v>
+        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
       </x:c>
       <x:c r="J52" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3247,7 +3247,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N52" s="4" t="str">
-        <x:v>岗位可能按城市提前关闭。</x:v>
+        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
       </x:c>
       <x:c r="O52" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3264,28 +3264,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B53" s="4" t="str">
-        <x:v>海天集团-高潜专项</x:v>
+        <x:v>度小满-博士后人才招聘</x:v>
       </x:c>
       <x:c r="C53" s="4" t="str">
-        <x:v>工业制造</x:v>
+        <x:v>金融科技</x:v>
       </x:c>
       <x:c r="D53" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E53" s="4" t="str">
-        <x:v>宁波及全国基地</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F53" s="4" t="str">
-        <x:v>高潜人才专项/提前批</x:v>
+        <x:v>博士后专项</x:v>
       </x:c>
       <x:c r="G53" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2025/2026/2027届博士</x:v>
       </x:c>
       <x:c r="H53" s="4" t="str">
-        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
+        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
       </x:c>
       <x:c r="I53" s="15" t="str">
-        <x:v>https://www.haitian.com/careers/</x:v>
+        <x:v>https://campus.duxiaoman.com/</x:v>
       </x:c>
       <x:c r="J53" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3300,7 +3300,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N53" s="4" t="str">
-        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
+        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
       </x:c>
       <x:c r="O53" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3317,28 +3317,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B54" s="4" t="str">
-        <x:v>赫力昂-销售先锋计划</x:v>
+        <x:v>多益网络</x:v>
       </x:c>
       <x:c r="C54" s="4" t="str">
-        <x:v>消费健康/医药</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D54" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E54" s="4" t="str">
-        <x:v>全国重点城市</x:v>
+        <x:v>广州、武汉、成都等</x:v>
       </x:c>
       <x:c r="F54" s="4" t="str">
-        <x:v>管培/销售专项</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G54" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H54" s="4" t="str">
-        <x:v>医药及消费健康销售、商业运营方向</x:v>
+        <x:v>程序、策划、美术、运营、市场及职能</x:v>
       </x:c>
       <x:c r="I54" s="15" t="str">
-        <x:v>https://careers.haleon.com/</x:v>
+        <x:v>https://www.duoyi.com/job/</x:v>
       </x:c>
       <x:c r="J54" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3352,7 +3352,9 @@
       <x:c r="M54" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N54" s="4" t="str"/>
+      <x:c r="N54" s="4" t="str">
+        <x:v>岗位可能按城市提前关闭。</x:v>
+      </x:c>
       <x:c r="O54" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3368,42 +3370,44 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B55" s="4" t="str">
-        <x:v>虹软科技</x:v>
+        <x:v>海天集团-高潜专项</x:v>
       </x:c>
       <x:c r="C55" s="4" t="str">
-        <x:v>计算机视觉/软件</x:v>
+        <x:v>工业制造</x:v>
       </x:c>
       <x:c r="D55" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E55" s="4" t="str">
-        <x:v>杭州、上海、南京等</x:v>
+        <x:v>宁波及全国基地</x:v>
       </x:c>
       <x:c r="F55" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>高潜人才专项/提前批</x:v>
       </x:c>
       <x:c r="G55" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H55" s="4" t="str">
-        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
+        <x:v>研发、工程技术、制造、供应链、营销与管理培训</x:v>
       </x:c>
       <x:c r="I55" s="15" t="str">
-        <x:v>https://hr.arcsoft.com.cn/</x:v>
+        <x:v>https://www.haitian.com/careers/</x:v>
       </x:c>
       <x:c r="J55" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K55" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L55" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M55" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N55" s="4" t="str"/>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N55" s="4" t="str">
+        <x:v>请确认招聘主体是海天塑机等具体业务单位。</x:v>
+      </x:c>
       <x:c r="O55" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3419,34 +3423,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B56" s="4" t="str">
-        <x:v>汇川技术</x:v>
+        <x:v>赫力昂-销售先锋计划</x:v>
       </x:c>
       <x:c r="C56" s="4" t="str">
-        <x:v>工业自动化/新能源</x:v>
+        <x:v>消费健康/医药</x:v>
       </x:c>
       <x:c r="D56" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E56" s="4" t="str">
-        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
+        <x:v>全国重点城市</x:v>
       </x:c>
       <x:c r="F56" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>管培/销售专项</x:v>
       </x:c>
       <x:c r="G56" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H56" s="4" t="str">
-        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
+        <x:v>医药及消费健康销售、商业运营方向</x:v>
       </x:c>
       <x:c r="I56" s="15" t="str">
-        <x:v>https://career.inovance.com/</x:v>
+        <x:v>https://careers.haleon.com/</x:v>
       </x:c>
       <x:c r="J56" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K56" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L56" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3470,49 +3474,47 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B57" s="4" t="str">
-        <x:v>伽利略-星途星锐计划</x:v>
+        <x:v>虹软科技</x:v>
       </x:c>
       <x:c r="C57" s="4" t="str">
-        <x:v>科技/综合</x:v>
+        <x:v>计算机视觉/软件</x:v>
       </x:c>
       <x:c r="D57" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E57" s="4" t="str">
-        <x:v>以项目职位页为准</x:v>
+        <x:v>杭州、上海、南京等</x:v>
       </x:c>
       <x:c r="F57" s="4" t="str">
-        <x:v>人才专项</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G57" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H57" s="4" t="str">
-        <x:v>以官方项目页为准</x:v>
-      </x:c>
-      <x:c r="I57" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
+      </x:c>
+      <x:c r="I57" s="15" t="str">
+        <x:v>https://hr.arcsoft.com.cn/</x:v>
       </x:c>
       <x:c r="J57" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K57" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L57" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M57" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N57" s="4" t="str">
-        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
-      </x:c>
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N57" s="4" t="str"/>
       <x:c r="O57" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P57" s="20" t="str">
-        <x:v>C-主体与入口需二次确认</x:v>
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q57" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3523,52 +3525,50 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B58" s="4" t="str">
-        <x:v>京东-TET管理培训生</x:v>
+        <x:v>汇川技术</x:v>
       </x:c>
       <x:c r="C58" s="4" t="str">
-        <x:v>互联网/零售</x:v>
+        <x:v>工业自动化/新能源</x:v>
       </x:c>
       <x:c r="D58" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E58" s="4" t="str">
-        <x:v>北京及业务所在城市</x:v>
+        <x:v>深圳、苏州、上海、南京、长沙等</x:v>
       </x:c>
       <x:c r="F58" s="4" t="str">
-        <x:v>管培生专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G58" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H58" s="4" t="str">
-        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
+        <x:v>电力电子、控制算法、嵌入式、软件、硬件、机械、销售及职能</x:v>
       </x:c>
       <x:c r="I58" s="15" t="str">
-        <x:v>https://campus.jd.com/</x:v>
+        <x:v>https://career.inovance.com/</x:v>
       </x:c>
       <x:c r="J58" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K58" s="4" t="str">
-        <x:v>含测评，笔试以通知为准</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L58" s="4" t="str">
-        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M58" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
-      </x:c>
-      <x:c r="N58" s="4" t="str">
-        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
-      </x:c>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N58" s="4" t="str"/>
       <x:c r="O58" s="15" t="str">
-        <x:v>https://campus.jd.com/#/</x:v>
-      </x:c>
-      <x:c r="P58" s="16" t="str">
-        <x:v>A-企业官网校招页面已核验</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P58" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q58" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="54" customHeight="1">
@@ -3576,28 +3576,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B59" s="4" t="str">
-        <x:v>科大讯飞-飞凡计划</x:v>
+        <x:v>伽利略-星途星锐计划</x:v>
       </x:c>
       <x:c r="C59" s="4" t="str">
-        <x:v>AI/软件</x:v>
+        <x:v>科技/综合</x:v>
       </x:c>
       <x:c r="D59" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E59" s="4" t="str">
-        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
+        <x:v>以项目职位页为准</x:v>
       </x:c>
       <x:c r="F59" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>人才专项</x:v>
       </x:c>
       <x:c r="G59" s="4" t="str">
-        <x:v>2026/2027届</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H59" s="4" t="str">
-        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
-      </x:c>
-      <x:c r="I59" s="15" t="str">
-        <x:v>https://campus.iflytek.com/</x:v>
+        <x:v>以官方项目页为准</x:v>
+      </x:c>
+      <x:c r="I59" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J59" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3612,13 +3612,13 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N59" s="4" t="str">
-        <x:v>专项岗位与常规校招可能并行。</x:v>
+        <x:v>项目主体和投递入口在公开汇总中不够清晰，必须二次核验。</x:v>
       </x:c>
       <x:c r="O59" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P59" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>C-主体与入口需二次确认</x:v>
       </x:c>
       <x:c r="Q59" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -3629,105 +3629,105 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B60" s="4" t="str">
-        <x:v>理想汽车</x:v>
+        <x:v>京东-TET管理培训生</x:v>
       </x:c>
       <x:c r="C60" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>互联网/零售</x:v>
       </x:c>
       <x:c r="D60" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E60" s="4" t="str">
-        <x:v>北京、上海、常州等</x:v>
+        <x:v>北京及业务所在城市</x:v>
       </x:c>
       <x:c r="F60" s="4" t="str">
-        <x:v>暑期实习转正通道</x:v>
+        <x:v>管培生专项/提前批</x:v>
       </x:c>
       <x:c r="G60" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H60" s="4" t="str">
-        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
+        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
       </x:c>
       <x:c r="I60" s="15" t="str">
-        <x:v>https://career.lixiang.com/campus</x:v>
+        <x:v>https://campus.jd.com/</x:v>
       </x:c>
       <x:c r="J60" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K60" s="4" t="str">
+        <x:v>含测评，笔试以通知为准</x:v>
+      </x:c>
+      <x:c r="L60" s="4" t="str">
+        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
+      </x:c>
+      <x:c r="M60" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N60" s="4" t="str">
+        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
+      </x:c>
+      <x:c r="O60" s="15" t="str">
+        <x:v>https://campus.jd.com/#/</x:v>
+      </x:c>
+      <x:c r="P60" s="16" t="str">
+        <x:v>A-企业官网校招页面已核验</x:v>
+      </x:c>
+      <x:c r="Q60" s="4" t="str">
+        <x:v>2026-07-30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="54" customHeight="1">
+      <x:c r="A61" s="4" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B61" s="4" t="str">
+        <x:v>科大讯飞-飞凡计划</x:v>
+      </x:c>
+      <x:c r="C61" s="4" t="str">
+        <x:v>AI/软件</x:v>
+      </x:c>
+      <x:c r="D61" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E61" s="4" t="str">
+        <x:v>合肥、北京、上海、广州、深圳、武汉、西安等</x:v>
+      </x:c>
+      <x:c r="F61" s="4" t="str">
+        <x:v>人才专项/提前批</x:v>
+      </x:c>
+      <x:c r="G61" s="4" t="str">
+        <x:v>2026/2027届</x:v>
+      </x:c>
+      <x:c r="H61" s="4" t="str">
+        <x:v>AI算法、大模型、语音、视觉、软件研发及产品方向</x:v>
+      </x:c>
+      <x:c r="I61" s="15" t="str">
+        <x:v>https://campus.iflytek.com/</x:v>
+      </x:c>
+      <x:c r="J61" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K61" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
-      <x:c r="L60" s="4" t="str">
+      <x:c r="L61" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
-      <x:c r="M60" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N60" s="4" t="str">
-        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
-      </x:c>
-      <x:c r="O60" s="15" t="str">
+      <x:c r="M61" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N61" s="4" t="str">
+        <x:v>专项岗位与常规校招可能并行。</x:v>
+      </x:c>
+      <x:c r="O61" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P60" s="20" t="str">
+      <x:c r="P61" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q60" s="4" t="str">
+      <x:c r="Q61" s="4" t="str">
         <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" ht="54" customHeight="1">
-      <x:c r="A61" s="18" t="str">
-        <x:v>不晚于2026-07-21</x:v>
-      </x:c>
-      <x:c r="B61" s="18" t="str">
-        <x:v>莉莉丝游戏</x:v>
-      </x:c>
-      <x:c r="C61" s="18" t="str">
-        <x:v>游戏</x:v>
-      </x:c>
-      <x:c r="D61" s="18" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E61" s="18" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F61" s="18" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G61" s="18" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H61" s="18" t="str">
-        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
-      </x:c>
-      <x:c r="I61" s="19" t="str">
-        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
-      </x:c>
-      <x:c r="J61" s="18" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
-      <x:c r="K61" s="18" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
-      </x:c>
-      <x:c r="L61" s="18" t="str">
-        <x:v>已截止（2026-08-07）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M61" s="18" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N61" s="18" t="str">
-        <x:v>莉莉丝27届校招提前批截止日为2026-08-07；项目已按日期标记截止，官方招聘页和原投递入口保留供查询。</x:v>
-      </x:c>
-      <x:c r="O61" s="19" t="str">
-        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
-      </x:c>
-      <x:c r="P61" s="16" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="Q61" s="18" t="str">
-        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="54" customHeight="1">
@@ -3735,34 +3735,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B62" s="4" t="str">
-        <x:v>麦肯锡</x:v>
+        <x:v>理想汽车</x:v>
       </x:c>
       <x:c r="C62" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D62" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E62" s="4" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>北京、上海、常州等</x:v>
       </x:c>
       <x:c r="F62" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>暑期实习转正通道</x:v>
       </x:c>
       <x:c r="G62" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H62" s="4" t="str">
-        <x:v>商业分析师、咨询及专业岗位</x:v>
+        <x:v>自动驾驶、算法、软件、硬件、整车、产品及职能</x:v>
       </x:c>
       <x:c r="I62" s="15" t="str">
-        <x:v>https://www.mckinsey.com/careers</x:v>
+        <x:v>https://career.lixiang.com/campus</x:v>
       </x:c>
       <x:c r="J62" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K62" s="4" t="str">
-        <x:v>通常含测评/案例面试；以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L62" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3770,7 +3770,9 @@
       <x:c r="M62" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N62" s="4" t="str"/>
+      <x:c r="N62" s="4" t="str">
+        <x:v>本项为实习项目，转正资格与正式秋招需按岗位确认。</x:v>
+      </x:c>
       <x:c r="O62" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3782,56 +3784,56 @@
       </x:c>
     </x:row>
     <x:row r="63" ht="54" customHeight="1">
-      <x:c r="A63" s="4" t="str">
+      <x:c r="A63" s="18" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B63" s="4" t="str">
-        <x:v>拼多多</x:v>
-      </x:c>
-      <x:c r="C63" s="4" t="str">
-        <x:v>互联网/电商</x:v>
-      </x:c>
-      <x:c r="D63" s="4" t="str">
+      <x:c r="B63" s="18" t="str">
+        <x:v>莉莉丝游戏</x:v>
+      </x:c>
+      <x:c r="C63" s="18" t="str">
+        <x:v>游戏</x:v>
+      </x:c>
+      <x:c r="D63" s="18" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E63" s="4" t="str">
-        <x:v>上海、广州等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F63" s="4" t="str">
+      <x:c r="E63" s="18" t="str">
+        <x:v>上海等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F63" s="18" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G63" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H63" s="4" t="str">
-        <x:v>技术、算法、产品、运营、商业分析等</x:v>
-      </x:c>
-      <x:c r="I63" s="15" t="str">
-        <x:v>https://careers.pinduoduo.com/campus/</x:v>
-      </x:c>
-      <x:c r="J63" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K63" s="4" t="str">
+      <x:c r="G63" s="18" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H63" s="18" t="str">
+        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
+      </x:c>
+      <x:c r="I63" s="19" t="str">
+        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
+      </x:c>
+      <x:c r="J63" s="18" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+      <x:c r="K63" s="18" t="str">
         <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
-      <x:c r="L63" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
-      </x:c>
-      <x:c r="M63" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N63" s="4" t="str">
-        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
-      </x:c>
-      <x:c r="O63" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P63" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q63" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+      <x:c r="L63" s="18" t="str">
+        <x:v>已截止（2026-08-07）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M63" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N63" s="18" t="str">
+        <x:v>莉莉丝27届校招提前批截止日为2026-08-07；项目已按日期标记截止，官方招聘页和原投递入口保留供查询。</x:v>
+      </x:c>
+      <x:c r="O63" s="19" t="str">
+        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
+      </x:c>
+      <x:c r="P63" s="16" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q63" s="18" t="str">
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="54" customHeight="1">
@@ -3839,16 +3841,16 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B64" s="4" t="str">
-        <x:v>启林投资</x:v>
+        <x:v>麦肯锡</x:v>
       </x:c>
       <x:c r="C64" s="4" t="str">
-        <x:v>量化金融/资管</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D64" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E64" s="4" t="str">
-        <x:v>上海等，以岗位页为准</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F64" s="4" t="str">
         <x:v>正式批/秋招</x:v>
@@ -3857,16 +3859,16 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H64" s="4" t="str">
-        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
+        <x:v>商业分析师、咨询及专业岗位</x:v>
       </x:c>
       <x:c r="I64" s="15" t="str">
-        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
+        <x:v>https://www.mckinsey.com/careers</x:v>
       </x:c>
       <x:c r="J64" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K64" s="4" t="str">
-        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
+        <x:v>通常含测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L64" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3874,9 +3876,7 @@
       <x:c r="M64" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N64" s="4" t="str">
-        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
-      </x:c>
+      <x:c r="N64" s="4" t="str"/>
       <x:c r="O64" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -3892,34 +3892,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B65" s="4" t="str">
-        <x:v>商汤科技-无限原力计划</x:v>
+        <x:v>拼多多</x:v>
       </x:c>
       <x:c r="C65" s="4" t="str">
-        <x:v>AI/计算机视觉</x:v>
+        <x:v>互联网/电商</x:v>
       </x:c>
       <x:c r="D65" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E65" s="4" t="str">
-        <x:v>上海、北京、深圳、杭州等</x:v>
+        <x:v>上海、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F65" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G65" s="4" t="str">
-        <x:v>2027/2028届</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H65" s="4" t="str">
-        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
+        <x:v>技术、算法、产品、运营、商业分析等</x:v>
       </x:c>
       <x:c r="I65" s="15" t="str">
-        <x:v>https://joinus.sensetime.com/</x:v>
+        <x:v>https://careers.pinduoduo.com/campus/</x:v>
       </x:c>
       <x:c r="J65" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K65" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L65" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3928,7 +3928,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N65" s="4" t="str">
-        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
+        <x:v>岗位通常滚动筛选、招满关闭。</x:v>
       </x:c>
       <x:c r="O65" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3945,34 +3945,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B66" s="4" t="str">
-        <x:v>腾讯-青云计划</x:v>
+        <x:v>启林投资</x:v>
       </x:c>
       <x:c r="C66" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>量化金融/资管</x:v>
       </x:c>
       <x:c r="D66" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E66" s="4" t="str">
-        <x:v>深圳、北京、上海等</x:v>
+        <x:v>上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F66" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G66" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H66" s="4" t="str">
-        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
+        <x:v>量化研究、策略开发、工程、交易及运营</x:v>
       </x:c>
       <x:c r="I66" s="15" t="str">
-        <x:v>https://join.qq.com/</x:v>
+        <x:v>https://70capital.gllue.com/portal/campusposition/list</x:v>
       </x:c>
       <x:c r="J66" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K66" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常有编程/数理测评；官方未统一说明</x:v>
       </x:c>
       <x:c r="L66" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3981,7 +3981,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N66" s="4" t="str">
-        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
+        <x:v>投递入口需通过企业官方公众号或公告复核。</x:v>
       </x:c>
       <x:c r="O66" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3998,28 +3998,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B67" s="4" t="str">
-        <x:v>天锐星通</x:v>
+        <x:v>商汤科技-无限原力计划</x:v>
       </x:c>
       <x:c r="C67" s="4" t="str">
-        <x:v>卫星通信/相控阵</x:v>
+        <x:v>AI/计算机视觉</x:v>
       </x:c>
       <x:c r="D67" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E67" s="4" t="str">
-        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
+        <x:v>上海、北京、深圳、杭州等</x:v>
       </x:c>
       <x:c r="F67" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G67" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027/2028届</x:v>
       </x:c>
       <x:c r="H67" s="4" t="str">
-        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
+        <x:v>大模型、计算机视觉、算法研究、AI基础设施等</x:v>
       </x:c>
       <x:c r="I67" s="15" t="str">
-        <x:v>https://www.tianruixing.com/</x:v>
+        <x:v>https://joinus.sensetime.com/</x:v>
       </x:c>
       <x:c r="J67" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4034,7 +4034,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N67" s="4" t="str">
-        <x:v>官网入口与具体岗位需投前复核。</x:v>
+        <x:v>专项可能覆盖实习与校招，投递时确认职位性质。</x:v>
       </x:c>
       <x:c r="O67" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -4048,105 +4048,105 @@
     </x:row>
     <x:row r="68" ht="54" customHeight="1">
       <x:c r="A68" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B68" s="4" t="str">
-        <x:v>网易游戏（互娱）-2027届校园招聘</x:v>
+        <x:v>腾讯-青云计划</x:v>
       </x:c>
       <x:c r="C68" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D68" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E68" s="4" t="str">
-        <x:v>广州、杭州、上海等，以岗位页为准</x:v>
+        <x:v>深圳、北京、上海等</x:v>
       </x:c>
       <x:c r="F68" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G68" s="4" t="str">
-        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H68" s="4" t="str">
-        <x:v>游戏研发、技术、策划、产品、艺术设计、测试及运营等方向</x:v>
+        <x:v>AI、大模型、算法、基础研究及核心技术方向</x:v>
       </x:c>
       <x:c r="I68" s="15" t="str">
-        <x:v>https://campus.game.163.com/</x:v>
+        <x:v>https://join.qq.com/</x:v>
       </x:c>
       <x:c r="J68" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K68" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L68" s="4" t="str">
-        <x:v>本轮新增；网易游戏互娱官方校招动态确认2027届校园招聘已启动</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M68" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N68" s="4" t="str">
-        <x:v>官方招聘动态于2026-07-21发布；应届生招聘与精英实习生项目分开，投递时注意选择对应批次和游戏业务。</x:v>
+        <x:v>专项门槛较高；具体岗位与毕业时间按官网项目页。</x:v>
       </x:c>
       <x:c r="O68" s="15" t="str">
-        <x:v>https://campus.game.163.com/news/0</x:v>
-      </x:c>
-      <x:c r="P68" s="16" t="str">
-        <x:v>A-企业官方校园招聘公告已核验</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P68" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q68" s="4" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="54" customHeight="1">
       <x:c r="A69" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B69" s="4" t="str">
-        <x:v>网易游戏雷火</x:v>
+        <x:v>天锐星通</x:v>
       </x:c>
       <x:c r="C69" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>卫星通信/相控阵</x:v>
       </x:c>
       <x:c r="D69" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E69" s="4" t="str">
-        <x:v>杭州、上海等，以岗位页为准</x:v>
+        <x:v>成都、北京、深圳等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F69" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G69" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H69" s="4" t="str">
-        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
+        <x:v>射频、天线、通信算法、硬件、嵌入式、结构及测试</x:v>
       </x:c>
       <x:c r="I69" s="15" t="str">
-        <x:v>https://leihuo.163.com/campus/#/full</x:v>
+        <x:v>https://www.tianruixing.com/</x:v>
       </x:c>
       <x:c r="J69" s="4" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K69" s="4" t="str">
-        <x:v>部分岗位免笔试；部分可直通面试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L69" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M69" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N69" s="4" t="str">
-        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
+        <x:v>官网入口与具体岗位需投前复核。</x:v>
       </x:c>
       <x:c r="O69" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P69" s="16" t="str">
-        <x:v>A-官方招聘官网已核验</x:v>
+      <x:c r="P69" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q69" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4154,103 +4154,105 @@
     </x:row>
     <x:row r="70" ht="54" customHeight="1">
       <x:c r="A70" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B70" s="4" t="str">
-        <x:v>小鹏集团</x:v>
+        <x:v>网易游戏（互娱）-2027届校园招聘</x:v>
       </x:c>
       <x:c r="C70" s="4" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D70" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E70" s="4" t="str">
-        <x:v>广州、北京、上海、深圳、武汉等</x:v>
+        <x:v>广州、杭州、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F70" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G70" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届毕业生，以岗位详情要求为准</x:v>
       </x:c>
       <x:c r="H70" s="4" t="str">
-        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
+        <x:v>游戏研发、技术、策划、产品、艺术设计、测试及运营等方向</x:v>
       </x:c>
       <x:c r="I70" s="15" t="str">
-        <x:v>https://join.xiaopeng.com/campus</x:v>
+        <x:v>https://campus.game.163.com/</x:v>
       </x:c>
       <x:c r="J70" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K70" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L70" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>本轮新增；网易游戏互娱官方校招动态确认2027届校园招聘已启动</x:v>
       </x:c>
       <x:c r="M70" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N70" s="4" t="str">
-        <x:v>营销服与技术岗位可能分项目发布。</x:v>
+        <x:v>官方招聘动态于2026-07-21发布；应届生招聘与精英实习生项目分开，投递时注意选择对应批次和游戏业务。</x:v>
       </x:c>
       <x:c r="O70" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P70" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+        <x:v>https://campus.game.163.com/news/0</x:v>
+      </x:c>
+      <x:c r="P70" s="16" t="str">
+        <x:v>A-企业官方校园招聘公告已核验</x:v>
       </x:c>
       <x:c r="Q70" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="54" customHeight="1">
       <x:c r="A71" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B71" s="4" t="str">
-        <x:v>芯动科技</x:v>
+        <x:v>网易游戏雷火</x:v>
       </x:c>
       <x:c r="C71" s="4" t="str">
-        <x:v>半导体/IP设计</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D71" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E71" s="4" t="str">
-        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
+        <x:v>杭州、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F71" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G71" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H71" s="4" t="str">
-        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
+        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
       </x:c>
       <x:c r="I71" s="15" t="str">
-        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
+        <x:v>https://leihuo.163.com/campus/#/full</x:v>
       </x:c>
       <x:c r="J71" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="K71" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>部分岗位免笔试；部分可直通面试</x:v>
       </x:c>
       <x:c r="L71" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M71" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N71" s="4" t="str"/>
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N71" s="4" t="str">
+        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
+      </x:c>
       <x:c r="O71" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P71" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P71" s="16" t="str">
+        <x:v>A-官方招聘官网已核验</x:v>
       </x:c>
       <x:c r="Q71" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4258,52 +4260,52 @@
     </x:row>
     <x:row r="72" ht="54" customHeight="1">
       <x:c r="A72" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B72" s="4" t="str">
-        <x:v>芯迈半导体</x:v>
+        <x:v>小鹏集团</x:v>
       </x:c>
       <x:c r="C72" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D72" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E72" s="4" t="str">
-        <x:v>杭州、上海、深圳、成都</x:v>
+        <x:v>广州、北京、上海、深圳、武汉等</x:v>
       </x:c>
       <x:c r="F72" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G72" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H72" s="4" t="str">
-        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
+        <x:v>智能驾驶、算法、软件、硬件、整车、营销服务、产品及职能</x:v>
       </x:c>
       <x:c r="I72" s="15" t="str">
-        <x:v>https://www.silicon-magic.com/joinus</x:v>
+        <x:v>https://join.xiaopeng.com/campus</x:v>
       </x:c>
       <x:c r="J72" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K72" s="4" t="str">
-        <x:v>官方未说明；公开流程未列笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L72" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M72" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N72" s="4" t="str">
-        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
+        <x:v>营销服与技术岗位可能分项目发布。</x:v>
       </x:c>
       <x:c r="O72" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P72" s="16" t="str">
-        <x:v>A-企业官网与公开公告已核验</x:v>
+      <x:c r="P72" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q72" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4314,100 +4316,100 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B73" s="4" t="str">
-        <x:v>新易盛</x:v>
+        <x:v>芯动科技</x:v>
       </x:c>
       <x:c r="C73" s="4" t="str">
-        <x:v>光通信/半导体</x:v>
+        <x:v>半导体/IP设计</x:v>
       </x:c>
       <x:c r="D73" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E73" s="4" t="str">
-        <x:v>成都、苏州等，以岗位页为准</x:v>
+        <x:v>武汉、珠海、西安、苏州、深圳等</x:v>
       </x:c>
       <x:c r="F73" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G73" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H73" s="4" t="str">
-        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
+        <x:v>数字/模拟IC、验证、后端、算法、软件、硬件及应用</x:v>
       </x:c>
       <x:c r="I73" s="15" t="str">
-        <x:v>https://www.eoptolink.com/</x:v>
+        <x:v>https://www.innosilicon.com.cn/html/campusRecruit/index.html</x:v>
       </x:c>
       <x:c r="J73" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K73" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L73" s="4" t="str">
-        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M73" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N73" s="4" t="str">
-        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
-      </x:c>
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N73" s="4" t="str"/>
       <x:c r="O73" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P73" s="14" t="str">
-        <x:v>B-高校/招聘平台转载，投前复核</x:v>
+      <x:c r="P73" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q73" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="54" customHeight="1">
       <x:c r="A74" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B74" s="4" t="str">
-        <x:v>元戎启行</x:v>
+        <x:v>芯迈半导体</x:v>
       </x:c>
       <x:c r="C74" s="4" t="str">
-        <x:v>自动驾驶</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D74" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E74" s="4" t="str">
-        <x:v>深圳、北京等</x:v>
+        <x:v>杭州、上海、深圳、成都</x:v>
       </x:c>
       <x:c r="F74" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G74" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H74" s="4" t="str">
-        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
+        <x:v>模拟/数字IC、嵌入式、版图、系统应用、测试、可靠性、产品、封装、工艺、销售、FAE</x:v>
       </x:c>
       <x:c r="I74" s="15" t="str">
-        <x:v>https://www.deeproute.ai/join-us</x:v>
+        <x:v>https://www.silicon-magic.com/joinus</x:v>
       </x:c>
       <x:c r="J74" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K74" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明；公开流程未列笔试</x:v>
       </x:c>
       <x:c r="L74" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M74" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N74" s="4" t="str"/>
+      <x:c r="N74" s="4" t="str">
+        <x:v>官网旧校招专题可能未更新；可同时邮件nhr@silicon-magic.com确认。</x:v>
+      </x:c>
       <x:c r="O74" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P74" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P74" s="16" t="str">
+        <x:v>A-企业官网与公开公告已核验</x:v>
       </x:c>
       <x:c r="Q74" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -4418,50 +4420,52 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B75" s="4" t="str">
-        <x:v>圆通速递</x:v>
+        <x:v>新易盛</x:v>
       </x:c>
       <x:c r="C75" s="4" t="str">
-        <x:v>物流/供应链</x:v>
+        <x:v>光通信/半导体</x:v>
       </x:c>
       <x:c r="D75" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E75" s="4" t="str">
-        <x:v>上海及全国网络</x:v>
+        <x:v>成都、苏州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F75" s="4" t="str">
-        <x:v>正式批/校招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G75" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H75" s="4" t="str">
-        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
+        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
       </x:c>
       <x:c r="I75" s="15" t="str">
-        <x:v>https://hr.yto.net.cn/</x:v>
+        <x:v>https://www.eoptolink.com/</x:v>
       </x:c>
       <x:c r="J75" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K75" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L75" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
       </x:c>
       <x:c r="M75" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N75" s="4" t="str"/>
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N75" s="4" t="str">
+        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+      </x:c>
       <x:c r="O75" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P75" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
+      <x:c r="P75" s="14" t="str">
+        <x:v>B-高校/招聘平台转载，投前复核</x:v>
       </x:c>
       <x:c r="Q75" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="54" customHeight="1">
@@ -4469,16 +4473,16 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B76" s="4" t="str">
-        <x:v>长亭科技</x:v>
+        <x:v>元戎启行</x:v>
       </x:c>
       <x:c r="C76" s="4" t="str">
-        <x:v>网络安全</x:v>
+        <x:v>自动驾驶</x:v>
       </x:c>
       <x:c r="D76" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E76" s="4" t="str">
-        <x:v>北京、上海等，以岗位页为准</x:v>
+        <x:v>深圳、北京等</x:v>
       </x:c>
       <x:c r="F76" s="4" t="str">
         <x:v>正式批/秋招</x:v>
@@ -4487,10 +4491,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H76" s="4" t="str">
-        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
+        <x:v>自动驾驶算法、感知、规划控制、系统、软件、硬件及测试</x:v>
       </x:c>
       <x:c r="I76" s="15" t="str">
-        <x:v>https://job.chaitin.cn/</x:v>
+        <x:v>https://www.deeproute.ai/join-us</x:v>
       </x:c>
       <x:c r="J76" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4520,34 +4524,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B77" s="4" t="str">
-        <x:v>智元机器人-优才计划</x:v>
+        <x:v>圆通速递</x:v>
       </x:c>
       <x:c r="C77" s="4" t="str">
-        <x:v>具身智能/机器人</x:v>
+        <x:v>物流/供应链</x:v>
       </x:c>
       <x:c r="D77" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E77" s="4" t="str">
-        <x:v>上海、北京、深圳等</x:v>
+        <x:v>上海及全国网络</x:v>
       </x:c>
       <x:c r="F77" s="4" t="str">
-        <x:v>优才专项/提前批</x:v>
+        <x:v>正式批/校招</x:v>
       </x:c>
       <x:c r="G77" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H77" s="4" t="str">
-        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
+        <x:v>运营、供应链、物流科技、产品、财务、人力及管培</x:v>
       </x:c>
       <x:c r="I77" s="15" t="str">
-        <x:v>https://www.agibot.com/recruit</x:v>
+        <x:v>https://hr.yto.net.cn/</x:v>
       </x:c>
       <x:c r="J77" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K77" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L77" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -4571,34 +4575,34 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B78" s="4" t="str">
-        <x:v>中国电信天翼云-超级优才</x:v>
+        <x:v>长亭科技</x:v>
       </x:c>
       <x:c r="C78" s="4" t="str">
-        <x:v>云计算/央企</x:v>
+        <x:v>网络安全</x:v>
       </x:c>
       <x:c r="D78" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E78" s="4" t="str">
-        <x:v>北京、上海、广州、成都及全国机构</x:v>
+        <x:v>北京、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F78" s="4" t="str">
-        <x:v>人才专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G78" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H78" s="4" t="str">
-        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
+        <x:v>安全研究、攻防、研发、产品、售前及职能</x:v>
       </x:c>
       <x:c r="I78" s="15" t="str">
-        <x:v>https://www.ctyun.cn/about/recruit</x:v>
+        <x:v>https://job.chaitin.cn/</x:v>
       </x:c>
       <x:c r="J78" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K78" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L78" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -4606,9 +4610,7 @@
       <x:c r="M78" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N78" s="4" t="str">
-        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
-      </x:c>
+      <x:c r="N78" s="4" t="str"/>
       <x:c r="O78" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
@@ -4620,55 +4622,53 @@
       </x:c>
     </x:row>
     <x:row r="79" ht="54" customHeight="1">
-      <x:c r="A79" s="14" t="str">
+      <x:c r="A79" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B79" s="14" t="str">
-        <x:v>中科光电</x:v>
-      </x:c>
-      <x:c r="C79" s="14" t="str">
-        <x:v>光电/科研</x:v>
-      </x:c>
-      <x:c r="D79" s="14" t="str">
+      <x:c r="B79" s="4" t="str">
+        <x:v>智元机器人-优才计划</x:v>
+      </x:c>
+      <x:c r="C79" s="4" t="str">
+        <x:v>具身智能/机器人</x:v>
+      </x:c>
+      <x:c r="D79" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E79" s="14" t="str">
-        <x:v>以职位公告为准</x:v>
-      </x:c>
-      <x:c r="F79" s="14" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G79" s="14" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H79" s="14" t="str">
-        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
-      </x:c>
-      <x:c r="I79" s="17" t="str">
-        <x:v>https://job.cn-amd.com/</x:v>
-      </x:c>
-      <x:c r="J79" s="14" t="str">
-        <x:v>2026-08-16</x:v>
-      </x:c>
-      <x:c r="K79" s="14" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L79" s="14" t="str">
+      <x:c r="E79" s="4" t="str">
+        <x:v>上海、北京、深圳等</x:v>
+      </x:c>
+      <x:c r="F79" s="4" t="str">
+        <x:v>优才专项/提前批</x:v>
+      </x:c>
+      <x:c r="G79" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H79" s="4" t="str">
+        <x:v>具身智能算法、机器人软件、硬件、机械、控制及产品</x:v>
+      </x:c>
+      <x:c r="I79" s="15" t="str">
+        <x:v>https://www.agibot.com/recruit</x:v>
+      </x:c>
+      <x:c r="J79" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K79" s="4" t="str">
+        <x:v>按岗位，官方未统一说明</x:v>
+      </x:c>
+      <x:c r="L79" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
-      <x:c r="M79" s="14" t="str">
-        <x:v>P1-7天内截止</x:v>
-      </x:c>
-      <x:c r="N79" s="14" t="str">
-        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
-      </x:c>
-      <x:c r="O79" s="17" t="str">
+      <x:c r="M79" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N79" s="4" t="str"/>
+      <x:c r="O79" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P79" s="20" t="str">
-        <x:v>C-名称需二次确认</x:v>
-      </x:c>
-      <x:c r="Q79" s="14" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q79" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -4677,28 +4677,28 @@
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B80" s="4" t="str">
-        <x:v>中兴微电子-未来领军计划</x:v>
+        <x:v>中国电信天翼云-超级优才</x:v>
       </x:c>
       <x:c r="C80" s="4" t="str">
-        <x:v>半导体/通信</x:v>
+        <x:v>云计算/央企</x:v>
       </x:c>
       <x:c r="D80" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E80" s="4" t="str">
-        <x:v>深圳、西安、南京、上海等</x:v>
+        <x:v>北京、上海、广州、成都及全国机构</x:v>
       </x:c>
       <x:c r="F80" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>人才专项/提前批</x:v>
       </x:c>
       <x:c r="G80" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H80" s="4" t="str">
-        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
+        <x:v>云计算、AI、大数据、网络安全、研发及解决方案</x:v>
       </x:c>
       <x:c r="I80" s="15" t="str">
-        <x:v>https://job.zte.com.cn/</x:v>
+        <x:v>https://www.ctyun.cn/about/recruit</x:v>
       </x:c>
       <x:c r="J80" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -4713,7 +4713,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N80" s="4" t="str">
-        <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
+        <x:v>超级优才属于专项，普通校招批次可能另行开放。</x:v>
       </x:c>
       <x:c r="O80" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -4726,972 +4726,972 @@
       </x:c>
     </x:row>
     <x:row r="81" ht="54" customHeight="1">
-      <x:c r="A81" s="18" t="str">
+      <x:c r="A81" s="14" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B81" s="18" t="str">
-        <x:v>字节跳动-AI产品经理早鸟通道</x:v>
-      </x:c>
-      <x:c r="C81" s="18" t="str">
-        <x:v>互联网/AI</x:v>
-      </x:c>
-      <x:c r="D81" s="18" t="str">
+      <x:c r="B81" s="14" t="str">
+        <x:v>中科光电</x:v>
+      </x:c>
+      <x:c r="C81" s="14" t="str">
+        <x:v>光电/科研</x:v>
+      </x:c>
+      <x:c r="D81" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E81" s="18" t="str">
-        <x:v>北京、上海、深圳</x:v>
-      </x:c>
-      <x:c r="F81" s="18" t="str">
-        <x:v>早鸟专项/提前批</x:v>
-      </x:c>
-      <x:c r="G81" s="18" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H81" s="18" t="str">
-        <x:v>AI产品经理、智能体及大模型产品方向</x:v>
-      </x:c>
-      <x:c r="I81" s="19" t="str">
-        <x:v>https://jobs.bytedance.com/campus/</x:v>
-      </x:c>
-      <x:c r="J81" s="18" t="str">
-        <x:v>2026-08-02</x:v>
-      </x:c>
-      <x:c r="K81" s="18" t="str">
-        <x:v>按岗位，未统一公布</x:v>
-      </x:c>
-      <x:c r="L81" s="18" t="str">
-        <x:v>已截止（2026-08-02）；原公告与官方投递入口保留</x:v>
-      </x:c>
-      <x:c r="M81" s="18" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N81" s="18" t="str">
-        <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
-      </x:c>
-      <x:c r="O81" s="19" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P81" s="14" t="str">
-        <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q81" s="18" t="str">
-        <x:v>2026-08-03</x:v>
+      <x:c r="E81" s="14" t="str">
+        <x:v>以职位公告为准</x:v>
+      </x:c>
+      <x:c r="F81" s="14" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G81" s="14" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H81" s="14" t="str">
+        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
+      </x:c>
+      <x:c r="I81" s="17" t="str">
+        <x:v>https://job.cn-amd.com/</x:v>
+      </x:c>
+      <x:c r="J81" s="14" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="K81" s="14" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L81" s="14" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M81" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N81" s="14" t="str">
+        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
+      </x:c>
+      <x:c r="O81" s="17" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P81" s="20" t="str">
+        <x:v>C-名称需二次确认</x:v>
+      </x:c>
+      <x:c r="Q81" s="14" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="54" customHeight="1">
-      <x:c r="A82" s="14" t="str">
+      <x:c r="A82" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B82" s="14" t="str">
-        <x:v>BCG波士顿咨询</x:v>
-      </x:c>
-      <x:c r="C82" s="14" t="str">
-        <x:v>管理咨询</x:v>
-      </x:c>
-      <x:c r="D82" s="14" t="str">
+      <x:c r="B82" s="4" t="str">
+        <x:v>中兴微电子-未来领军计划</x:v>
+      </x:c>
+      <x:c r="C82" s="4" t="str">
+        <x:v>半导体/通信</x:v>
+      </x:c>
+      <x:c r="D82" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E82" s="14" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
-      </x:c>
-      <x:c r="F82" s="14" t="str">
-        <x:v>正式批/中国区校招</x:v>
-      </x:c>
-      <x:c r="G82" s="14" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H82" s="14" t="str">
-        <x:v>咨询顾问及相关专业岗位</x:v>
-      </x:c>
-      <x:c r="I82" s="17" t="str">
-        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
-      </x:c>
-      <x:c r="J82" s="14" t="str">
-        <x:v>2026-08-16</x:v>
-      </x:c>
-      <x:c r="K82" s="14" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
-      </x:c>
-      <x:c r="L82" s="14" t="str">
+      <x:c r="E82" s="4" t="str">
+        <x:v>深圳、西安、南京、上海等</x:v>
+      </x:c>
+      <x:c r="F82" s="4" t="str">
+        <x:v>顶尖人才专项/提前批</x:v>
+      </x:c>
+      <x:c r="G82" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H82" s="4" t="str">
+        <x:v>芯片设计、验证、算法、嵌入式、EDA及通信技术</x:v>
+      </x:c>
+      <x:c r="I82" s="15" t="str">
+        <x:v>https://job.zte.com.cn/</x:v>
+      </x:c>
+      <x:c r="J82" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K82" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L82" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
-      <x:c r="M82" s="14" t="str">
-        <x:v>P1-7天内截止</x:v>
-      </x:c>
-      <x:c r="N82" s="14" t="str"/>
-      <x:c r="O82" s="17" t="str">
+      <x:c r="M82" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N82" s="4" t="str">
+        <x:v>属于中兴微电子专项，学历及科研要求按岗位页。</x:v>
+      </x:c>
+      <x:c r="O82" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P82" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q82" s="14" t="str">
+      <x:c r="Q82" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="54" customHeight="1">
-      <x:c r="A83" s="4" t="str">
+      <x:c r="A83" s="18" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
-      <x:c r="B83" s="4" t="str">
-        <x:v>OPPO</x:v>
-      </x:c>
-      <x:c r="C83" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
-      </x:c>
-      <x:c r="D83" s="4" t="str">
+      <x:c r="B83" s="18" t="str">
+        <x:v>字节跳动-AI产品经理早鸟通道</x:v>
+      </x:c>
+      <x:c r="C83" s="18" t="str">
+        <x:v>互联网/AI</x:v>
+      </x:c>
+      <x:c r="D83" s="18" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E83" s="4" t="str">
-        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
-      </x:c>
-      <x:c r="F83" s="4" t="str">
-        <x:v>全球校园招聘/正式批</x:v>
-      </x:c>
-      <x:c r="G83" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H83" s="4" t="str">
-        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
-      </x:c>
-      <x:c r="I83" s="15" t="str">
-        <x:v>https://careers.oppo.com/campus</x:v>
-      </x:c>
-      <x:c r="J83" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K83" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L83" s="4" t="str">
+      <x:c r="E83" s="18" t="str">
+        <x:v>北京、上海、深圳</x:v>
+      </x:c>
+      <x:c r="F83" s="18" t="str">
+        <x:v>早鸟专项/提前批</x:v>
+      </x:c>
+      <x:c r="G83" s="18" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H83" s="18" t="str">
+        <x:v>AI产品经理、智能体及大模型产品方向</x:v>
+      </x:c>
+      <x:c r="I83" s="19" t="str">
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
+      </x:c>
+      <x:c r="J83" s="18" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+      <x:c r="K83" s="18" t="str">
+        <x:v>按岗位，未统一公布</x:v>
+      </x:c>
+      <x:c r="L83" s="18" t="str">
+        <x:v>已截止（2026-08-02）；原公告与官方投递入口保留</x:v>
+      </x:c>
+      <x:c r="M83" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N83" s="18" t="str">
+        <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
+      </x:c>
+      <x:c r="O83" s="19" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P83" s="14" t="str">
+        <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q83" s="18" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="54" customHeight="1">
+      <x:c r="A84" s="14" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B84" s="14" t="str">
+        <x:v>BCG波士顿咨询</x:v>
+      </x:c>
+      <x:c r="C84" s="14" t="str">
+        <x:v>管理咨询</x:v>
+      </x:c>
+      <x:c r="D84" s="14" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E84" s="14" t="str">
+        <x:v>北京、上海、深圳、香港等</x:v>
+      </x:c>
+      <x:c r="F84" s="14" t="str">
+        <x:v>正式批/中国区校招</x:v>
+      </x:c>
+      <x:c r="G84" s="14" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H84" s="14" t="str">
+        <x:v>咨询顾问及相关专业岗位</x:v>
+      </x:c>
+      <x:c r="I84" s="17" t="str">
+        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
+      </x:c>
+      <x:c r="J84" s="14" t="str">
+        <x:v>2026-08-16</x:v>
+      </x:c>
+      <x:c r="K84" s="14" t="str">
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+      </x:c>
+      <x:c r="L84" s="14" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
-      <x:c r="M83" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N83" s="4" t="str">
-        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
-      </x:c>
-      <x:c r="O83" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P83" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q83" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" ht="54" customHeight="1">
-      <x:c r="A84" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
-      </x:c>
-      <x:c r="B84" s="4" t="str">
-        <x:v>Tap4Fun</x:v>
-      </x:c>
-      <x:c r="C84" s="4" t="str">
-        <x:v>游戏</x:v>
-      </x:c>
-      <x:c r="D84" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E84" s="4" t="str">
-        <x:v>成都等</x:v>
-      </x:c>
-      <x:c r="F84" s="4" t="str">
-        <x:v>实习转正通道</x:v>
-      </x:c>
-      <x:c r="G84" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H84" s="4" t="str">
-        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
-      </x:c>
-      <x:c r="I84" s="15" t="str">
-        <x:v>https://www.tap4fun.com/careers</x:v>
-      </x:c>
-      <x:c r="J84" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K84" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L84" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
-      </x:c>
-      <x:c r="M84" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N84" s="4" t="str">
-        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
-      </x:c>
-      <x:c r="O84" s="15" t="str">
+      <x:c r="M84" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N84" s="14" t="str"/>
+      <x:c r="O84" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P84" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q84" s="4" t="str">
+      <x:c r="Q84" s="14" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="54" customHeight="1">
       <x:c r="A85" s="4" t="str">
-        <x:v>2026-07-20</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B85" s="4" t="str">
-        <x:v>航天科技集团五院502所</x:v>
+        <x:v>OPPO</x:v>
       </x:c>
       <x:c r="C85" s="4" t="str">
-        <x:v>航天/自动控制</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D85" s="4" t="str">
-        <x:v>事业单位/央企院所</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E85" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>深圳、东莞、北京、上海、成都、武汉、西安、南京、杭州等</x:v>
       </x:c>
       <x:c r="F85" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>全球校园招聘/正式批</x:v>
       </x:c>
       <x:c r="G85" s="4" t="str">
-        <x:v>硕士/博士为主，以岗位为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H85" s="4" t="str">
-        <x:v>导航制导与控制、自动化、电子、通信、计算机、软件、机械等</x:v>
+        <x:v>软件、算法、硬件、芯片、产品、设计、营销、职能等</x:v>
       </x:c>
       <x:c r="I85" s="15" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
+        <x:v>https://careers.oppo.com/campus</x:v>
       </x:c>
       <x:c r="J85" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K85" s="4" t="str">
-        <x:v>未统一公布</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L85" s="4" t="str">
-        <x:v>公开公告显示开放；投前确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M85" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N85" s="4" t="str">
-        <x:v>研究所岗位通常有专业、学历、政审及保密要求。</x:v>
+        <x:v>不同业务单位会分批开岗，城市和截止时间以职位页为准。</x:v>
       </x:c>
       <x:c r="O85" s="15" t="str">
-        <x:v>https://www.baidu.com/s?wd=%E4%BA%94%E9%99%A2502%E6%89%802027%E5%B1%8A%E6%A0%A1%E6%8B%9B</x:v>
-      </x:c>
-      <x:c r="P85" s="14" t="str">
-        <x:v>B-高校就业网公开公告</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P85" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
       <x:c r="Q85" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="54" customHeight="1">
-      <x:c r="A86" s="18" t="str">
-        <x:v>2026-07-17</x:v>
-      </x:c>
-      <x:c r="B86" s="18" t="str">
-        <x:v>鹰角网络</x:v>
-      </x:c>
-      <x:c r="C86" s="18" t="str">
+      <x:c r="A86" s="4" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B86" s="4" t="str">
+        <x:v>Tap4Fun</x:v>
+      </x:c>
+      <x:c r="C86" s="4" t="str">
         <x:v>游戏</x:v>
       </x:c>
-      <x:c r="D86" s="18" t="str">
+      <x:c r="D86" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E86" s="18" t="str">
-        <x:v>上海</x:v>
-      </x:c>
-      <x:c r="F86" s="18" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G86" s="18" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H86" s="18" t="str">
-        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
-      </x:c>
-      <x:c r="I86" s="19" t="str">
-        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
-      </x:c>
-      <x:c r="J86" s="18" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K86" s="18" t="str">
-        <x:v>否；安排笔试/面试</x:v>
-      </x:c>
-      <x:c r="L86" s="18" t="str">
-        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M86" s="18" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N86" s="18" t="str">
-        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
-      </x:c>
-      <x:c r="O86" s="19" t="str">
-        <x:v>https://campus.hypergryph.com/</x:v>
-      </x:c>
-      <x:c r="P86" s="16" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q86" s="18" t="str">
-        <x:v>2026-08-03</x:v>
+      <x:c r="E86" s="4" t="str">
+        <x:v>成都等</x:v>
+      </x:c>
+      <x:c r="F86" s="4" t="str">
+        <x:v>实习转正通道</x:v>
+      </x:c>
+      <x:c r="G86" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H86" s="4" t="str">
+        <x:v>游戏研发、策划、美术、发行运营等，以官网为准</x:v>
+      </x:c>
+      <x:c r="I86" s="15" t="str">
+        <x:v>https://www.tap4fun.com/careers</x:v>
+      </x:c>
+      <x:c r="J86" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K86" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L86" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M86" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N86" s="4" t="str">
+        <x:v>本项为实习可转正，不等同于直接秋招正式岗。</x:v>
+      </x:c>
+      <x:c r="O86" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P86" s="20" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q86" s="4" t="str">
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="54" customHeight="1">
       <x:c r="A87" s="4" t="str">
-        <x:v>2026-07-16</x:v>
+        <x:v>2026-07-20</x:v>
       </x:c>
       <x:c r="B87" s="4" t="str">
-        <x:v>联发科技</x:v>
+        <x:v>航天科技集团五院502所</x:v>
       </x:c>
       <x:c r="C87" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>航天/自动控制</x:v>
       </x:c>
       <x:c r="D87" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>事业单位/央企院所</x:v>
       </x:c>
       <x:c r="E87" s="4" t="str">
-        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F87" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G87" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>硕士/博士为主，以岗位为准</x:v>
       </x:c>
       <x:c r="H87" s="4" t="str">
-        <x:v>软件类、通信类、IC类</x:v>
+        <x:v>导航制导与控制、自动化、电子、通信、计算机、软件、机械等</x:v>
       </x:c>
       <x:c r="I87" s="15" t="str">
-        <x:v>https://mediatek.zhiye.com/</x:v>
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J87" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K87" s="4" t="str">
-        <x:v>否；明确安排7-8月笔试</x:v>
+        <x:v>未统一公布</x:v>
       </x:c>
       <x:c r="L87" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>公开公告显示开放；投前确认</x:v>
       </x:c>
       <x:c r="M87" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N87" s="4" t="str">
-        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
+        <x:v>研究所岗位通常有专业、学历、政审及保密要求。</x:v>
       </x:c>
       <x:c r="O87" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P87" s="16" t="str">
-        <x:v>A-官方招聘公告已核验</x:v>
+        <x:v>https://www.baidu.com/s?wd=%E4%BA%94%E9%99%A2502%E6%89%802027%E5%B1%8A%E6%A0%A1%E6%8B%9B</x:v>
+      </x:c>
+      <x:c r="P87" s="14" t="str">
+        <x:v>B-高校就业网公开公告</x:v>
       </x:c>
       <x:c r="Q87" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="54" customHeight="1">
-      <x:c r="A88" s="4" t="str">
-        <x:v>2026-07-16</x:v>
-      </x:c>
-      <x:c r="B88" s="4" t="str">
-        <x:v>DJI大疆</x:v>
-      </x:c>
-      <x:c r="C88" s="4" t="str">
-        <x:v>无人机/智能硬件</x:v>
-      </x:c>
-      <x:c r="D88" s="4" t="str">
+      <x:c r="A88" s="18" t="str">
+        <x:v>2026-07-17</x:v>
+      </x:c>
+      <x:c r="B88" s="18" t="str">
+        <x:v>鹰角网络</x:v>
+      </x:c>
+      <x:c r="C88" s="18" t="str">
+        <x:v>游戏</x:v>
+      </x:c>
+      <x:c r="D88" s="18" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E88" s="4" t="str">
-        <x:v>深圳、东莞、上海、北京、西安等</x:v>
-      </x:c>
-      <x:c r="F88" s="4" t="str">
-        <x:v>正式批-拓疆者计划</x:v>
-      </x:c>
-      <x:c r="G88" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H88" s="4" t="str">
-        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
-      </x:c>
-      <x:c r="I88" s="15" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
-      </x:c>
-      <x:c r="J88" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K88" s="4" t="str">
-        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
-      </x:c>
-      <x:c r="L88" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M88" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N88" s="4" t="str">
-        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
-      </x:c>
-      <x:c r="O88" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      <x:c r="E88" s="18" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F88" s="18" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G88" s="18" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H88" s="18" t="str">
+        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
+      </x:c>
+      <x:c r="I88" s="19" t="str">
+        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
+      </x:c>
+      <x:c r="J88" s="18" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K88" s="18" t="str">
+        <x:v>否；安排笔试/面试</x:v>
+      </x:c>
+      <x:c r="L88" s="18" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M88" s="18" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N88" s="18" t="str">
+        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
+      </x:c>
+      <x:c r="O88" s="19" t="str">
+        <x:v>https://campus.hypergryph.com/</x:v>
       </x:c>
       <x:c r="P88" s="16" t="str">
         <x:v>A-官方来源公告已核验</x:v>
       </x:c>
-      <x:c r="Q88" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+      <x:c r="Q88" s="18" t="str">
+        <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="54" customHeight="1">
-      <x:c r="A89" s="14" t="str">
-        <x:v>2026-07-15</x:v>
-      </x:c>
-      <x:c r="B89" s="14" t="str">
-        <x:v>蔚来</x:v>
-      </x:c>
-      <x:c r="C89" s="14" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
-      </x:c>
-      <x:c r="D89" s="14" t="str">
+      <x:c r="A89" s="4" t="str">
+        <x:v>2026-07-16</x:v>
+      </x:c>
+      <x:c r="B89" s="4" t="str">
+        <x:v>联发科技</x:v>
+      </x:c>
+      <x:c r="C89" s="4" t="str">
+        <x:v>半导体/IC设计</x:v>
+      </x:c>
+      <x:c r="D89" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E89" s="14" t="str">
-        <x:v>上海、合肥、北京、武汉、南京等</x:v>
-      </x:c>
-      <x:c r="F89" s="14" t="str">
-        <x:v>技术提前批</x:v>
-      </x:c>
-      <x:c r="G89" s="14" t="str">
-        <x:v>2024年9月-2027年8月毕业</x:v>
-      </x:c>
-      <x:c r="H89" s="14" t="str">
-        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
-      </x:c>
-      <x:c r="I89" s="17" t="str">
-        <x:v>https://campus.nio.com/</x:v>
-      </x:c>
-      <x:c r="J89" s="14" t="str">
-        <x:v>2026-08-14</x:v>
-      </x:c>
-      <x:c r="K89" s="14" t="str">
-        <x:v>否；有笔试/测评</x:v>
-      </x:c>
-      <x:c r="L89" s="14" t="str">
+      <x:c r="E89" s="4" t="str">
+        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
+      </x:c>
+      <x:c r="F89" s="4" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G89" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H89" s="4" t="str">
+        <x:v>软件类、通信类、IC类</x:v>
+      </x:c>
+      <x:c r="I89" s="15" t="str">
+        <x:v>https://mediatek.zhiye.com/</x:v>
+      </x:c>
+      <x:c r="J89" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K89" s="4" t="str">
+        <x:v>否；明确安排7-8月笔试</x:v>
+      </x:c>
+      <x:c r="L89" s="4" t="str">
         <x:v>已核验开放</x:v>
       </x:c>
-      <x:c r="M89" s="14" t="str">
-        <x:v>P1-7天内截止</x:v>
-      </x:c>
-      <x:c r="N89" s="14" t="str">
-        <x:v>最多同时申请3个岗位。</x:v>
-      </x:c>
-      <x:c r="O89" s="17" t="str">
+      <x:c r="M89" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N89" s="4" t="str">
+        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
+      </x:c>
+      <x:c r="O89" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P89" s="16" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q89" s="14" t="str">
+        <x:v>A-官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q89" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="54" customHeight="1">
       <x:c r="A90" s="4" t="str">
-        <x:v>2026-07-10</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B90" s="4" t="str">
-        <x:v>北方华创</x:v>
+        <x:v>DJI大疆</x:v>
       </x:c>
       <x:c r="C90" s="4" t="str">
-        <x:v>半导体设备</x:v>
+        <x:v>无人机/智能硬件</x:v>
       </x:c>
       <x:c r="D90" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E90" s="4" t="str">
-        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
+        <x:v>深圳、东莞、上海、北京、西安等</x:v>
       </x:c>
       <x:c r="F90" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批-拓疆者计划</x:v>
       </x:c>
       <x:c r="G90" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H90" s="4" t="str">
-        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
+        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
       </x:c>
       <x:c r="I90" s="15" t="str">
-        <x:v>https://career.naura.com/campus</x:v>
+        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
       </x:c>
       <x:c r="J90" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K90" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
       </x:c>
       <x:c r="L90" s="4" t="str">
-        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M90" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N90" s="4" t="str">
-        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
+        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
       </x:c>
       <x:c r="O90" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P90" s="16" t="str">
-        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
+        <x:v>A-官方来源公告已核验</x:v>
       </x:c>
       <x:c r="Q90" s="4" t="str">
-        <x:v>2026-07-30</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="54" customHeight="1">
-      <x:c r="A91" s="4" t="str">
-        <x:v>2026-07-09</x:v>
-      </x:c>
-      <x:c r="B91" s="4" t="str">
-        <x:v>百度</x:v>
-      </x:c>
-      <x:c r="C91" s="4" t="str">
-        <x:v>互联网/AI</x:v>
-      </x:c>
-      <x:c r="D91" s="4" t="str">
+      <x:c r="A91" s="14" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="B91" s="14" t="str">
+        <x:v>蔚来</x:v>
+      </x:c>
+      <x:c r="C91" s="14" t="str">
+        <x:v>新能源汽车/智能汽车</x:v>
+      </x:c>
+      <x:c r="D91" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E91" s="4" t="str">
-        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
-      </x:c>
-      <x:c r="F91" s="4" t="str">
-        <x:v>正式批</x:v>
-      </x:c>
-      <x:c r="G91" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H91" s="4" t="str">
-        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
-      </x:c>
-      <x:c r="I91" s="15" t="str">
-        <x:v>https://talent.baidu.com/jobs</x:v>
-      </x:c>
-      <x:c r="J91" s="4" t="str">
-        <x:v>2027-06-30</x:v>
-      </x:c>
-      <x:c r="K91" s="4" t="str">
-        <x:v>部分免；并非所有候选人参加笔试</x:v>
-      </x:c>
-      <x:c r="L91" s="4" t="str">
+      <x:c r="E91" s="14" t="str">
+        <x:v>上海、合肥、北京、武汉、南京等</x:v>
+      </x:c>
+      <x:c r="F91" s="14" t="str">
+        <x:v>技术提前批</x:v>
+      </x:c>
+      <x:c r="G91" s="14" t="str">
+        <x:v>2024年9月-2027年8月毕业</x:v>
+      </x:c>
+      <x:c r="H91" s="14" t="str">
+        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
+      </x:c>
+      <x:c r="I91" s="17" t="str">
+        <x:v>https://campus.nio.com/</x:v>
+      </x:c>
+      <x:c r="J91" s="14" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="K91" s="14" t="str">
+        <x:v>否；有笔试/测评</x:v>
+      </x:c>
+      <x:c r="L91" s="14" t="str">
         <x:v>已核验开放</x:v>
       </x:c>
-      <x:c r="M91" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
-      </x:c>
-      <x:c r="N91" s="4" t="str">
-        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
-      </x:c>
-      <x:c r="O91" s="15" t="str">
+      <x:c r="M91" s="14" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N91" s="14" t="str">
+        <x:v>最多同时申请3个岗位。</x:v>
+      </x:c>
+      <x:c r="O91" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P91" s="16" t="str">
-        <x:v>A-官方招聘日历/官方来源已核验</x:v>
-      </x:c>
-      <x:c r="Q91" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q91" s="14" t="str">
+        <x:v>2026-08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="54" customHeight="1">
       <x:c r="A92" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="B92" s="4" t="str">
-        <x:v>中国航天科工集团第六研究院</x:v>
+        <x:v>北方华创</x:v>
       </x:c>
       <x:c r="C92" s="4" t="str">
-        <x:v>航天/军工/动力系统</x:v>
+        <x:v>半导体设备</x:v>
       </x:c>
       <x:c r="D92" s="4" t="str">
-        <x:v>央企院所</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E92" s="4" t="str">
-        <x:v>呼和浩特及所属单位</x:v>
+        <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F92" s="4" t="str">
-        <x:v>提前批+暑期开放日</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G92" s="4" t="str">
-        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H92" s="4" t="str">
-        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
+        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
       </x:c>
       <x:c r="I92" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
+        <x:v>https://career.naura.com/campus</x:v>
       </x:c>
       <x:c r="J92" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K92" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L92" s="4" t="str">
-        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
+        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
       </x:c>
       <x:c r="M92" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N92" s="4" t="str">
-        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
+        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
       </x:c>
       <x:c r="O92" s="15" t="str">
-        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
-      </x:c>
-      <x:c r="P92" s="14" t="str">
-        <x:v>B-高校就业网公开公告</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P92" s="16" t="str">
+        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
       </x:c>
       <x:c r="Q92" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="54" customHeight="1">
       <x:c r="A93" s="4" t="str">
-        <x:v>2026-07-08</x:v>
+        <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B93" s="4" t="str">
-        <x:v>思瑞浦</x:v>
+        <x:v>百度</x:v>
       </x:c>
       <x:c r="C93" s="4" t="str">
-        <x:v>半导体/模拟IC</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D93" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E93" s="4" t="str">
-        <x:v>上海、深圳等，以岗位页为准</x:v>
+        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
       </x:c>
       <x:c r="F93" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G93" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H93" s="4" t="str">
-        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
+        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
       </x:c>
       <x:c r="I93" s="15" t="str">
-        <x:v>https://www.3peak.cn/careers</x:v>
+        <x:v>https://talent.baidu.com/jobs</x:v>
       </x:c>
       <x:c r="J93" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-30</x:v>
       </x:c>
       <x:c r="K93" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>部分免；并非所有候选人参加笔试</x:v>
       </x:c>
       <x:c r="L93" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M93" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N93" s="4" t="str">
-        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
+        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
       </x:c>
       <x:c r="O93" s="15" t="str">
-        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
-      </x:c>
-      <x:c r="P93" s="14" t="str">
-        <x:v>B-招聘平台/高校就业转载</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P93" s="16" t="str">
+        <x:v>A-官方招聘日历/官方来源已核验</x:v>
       </x:c>
       <x:c r="Q93" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="54" customHeight="1">
       <x:c r="A94" s="4" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="B94" s="4" t="str">
+        <x:v>中国航天科工集团第六研究院</x:v>
+      </x:c>
+      <x:c r="C94" s="4" t="str">
+        <x:v>航天/军工/动力系统</x:v>
+      </x:c>
+      <x:c r="D94" s="4" t="str">
+        <x:v>央企院所</x:v>
+      </x:c>
+      <x:c r="E94" s="4" t="str">
+        <x:v>呼和浩特及所属单位</x:v>
+      </x:c>
+      <x:c r="F94" s="4" t="str">
+        <x:v>提前批+暑期开放日</x:v>
+      </x:c>
+      <x:c r="G94" s="4" t="str">
+        <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
+      </x:c>
+      <x:c r="H94" s="4" t="str">
+        <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
+      </x:c>
+      <x:c r="I94" s="15" t="str">
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
+      </x:c>
+      <x:c r="J94" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K94" s="4" t="str">
+        <x:v>各单位自行组织，未统一</x:v>
+      </x:c>
+      <x:c r="L94" s="4" t="str">
+        <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
+      </x:c>
+      <x:c r="M94" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N94" s="4" t="str">
+        <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
+      </x:c>
+      <x:c r="O94" s="15" t="str">
+        <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
+      </x:c>
+      <x:c r="P94" s="14" t="str">
+        <x:v>B-高校就业网公开公告</x:v>
+      </x:c>
+      <x:c r="Q94" s="4" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="54" customHeight="1">
+      <x:c r="A95" s="4" t="str">
+        <x:v>2026-07-08</x:v>
+      </x:c>
+      <x:c r="B95" s="4" t="str">
+        <x:v>思瑞浦</x:v>
+      </x:c>
+      <x:c r="C95" s="4" t="str">
+        <x:v>半导体/模拟IC</x:v>
+      </x:c>
+      <x:c r="D95" s="4" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E95" s="4" t="str">
+        <x:v>上海、深圳等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F95" s="4" t="str">
+        <x:v>正式批/校园招聘</x:v>
+      </x:c>
+      <x:c r="G95" s="4" t="str">
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H95" s="4" t="str">
+        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
+      </x:c>
+      <x:c r="I95" s="15" t="str">
+        <x:v>https://www.3peak.cn/careers</x:v>
+      </x:c>
+      <x:c r="J95" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K95" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L95" s="4" t="str">
+        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
+      </x:c>
+      <x:c r="M95" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N95" s="4" t="str">
+        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
+      </x:c>
+      <x:c r="O95" s="15" t="str">
+        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
+      </x:c>
+      <x:c r="P95" s="14" t="str">
+        <x:v>B-招聘平台/高校就业转载</x:v>
+      </x:c>
+      <x:c r="Q95" s="4" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="54" customHeight="1">
+      <x:c r="A96" s="4" t="str">
         <x:v>不晚于2026-07-07</x:v>
       </x:c>
-      <x:c r="B94" s="4" t="str">
+      <x:c r="B96" s="4" t="str">
         <x:v>文远知行WeRide</x:v>
       </x:c>
-      <x:c r="C94" s="4" t="str">
+      <x:c r="C96" s="4" t="str">
         <x:v>自动驾驶/人工智能</x:v>
       </x:c>
-      <x:c r="D94" s="4" t="str">
+      <x:c r="D96" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
-      <x:c r="E94" s="4" t="str">
+      <x:c r="E96" s="4" t="str">
         <x:v>广州、深圳、武汉等，以岗位页为准</x:v>
       </x:c>
-      <x:c r="F94" s="4" t="str">
+      <x:c r="F96" s="4" t="str">
         <x:v>正式批/校招/可转正实习</x:v>
       </x:c>
-      <x:c r="G94" s="4" t="str">
+      <x:c r="G96" s="4" t="str">
         <x:v>2027届应届毕业生及可转正实习生，以岗位要求为准</x:v>
       </x:c>
-      <x:c r="H94" s="4" t="str">
+      <x:c r="H96" s="4" t="str">
         <x:v>感知/预测/规划控制算法、算法测试、测试开发、SRE、云与车端安全、AI Infra、仿真平台等</x:v>
       </x:c>
-      <x:c r="I94" s="15" t="str">
+      <x:c r="I96" s="15" t="str">
         <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
       </x:c>
-      <x:c r="J94" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K94" s="4" t="str">
+      <x:c r="J96" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K96" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
-      <x:c r="L94" s="4" t="str">
+      <x:c r="L96" s="4" t="str">
         <x:v>企业官方校招系统在招；已核验137个职位</x:v>
       </x:c>
-      <x:c r="M94" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N94" s="4" t="str">
+      <x:c r="M96" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N96" s="4" t="str">
         <x:v>官方列表显示2027届校招职位最早发布于7月7日；部分岗位为可转正实习，城市和岗位随招聘系统实时调整。</x:v>
       </x:c>
-      <x:c r="O94" s="15" t="str">
+      <x:c r="O96" s="15" t="str">
         <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
       </x:c>
-      <x:c r="P94" s="16" t="str">
+      <x:c r="P96" s="16" t="str">
         <x:v>A-企业官方校招系统与职位列表已核验</x:v>
       </x:c>
-      <x:c r="Q94" s="4" t="str">
+      <x:c r="Q96" s="4" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="54" customHeight="1">
-      <x:c r="A95" s="18" t="str">
+    <x:row r="97" ht="54" customHeight="1">
+      <x:c r="A97" s="18" t="str">
         <x:v>2026-07-06</x:v>
       </x:c>
-      <x:c r="B95" s="18" t="str">
+      <x:c r="B97" s="18" t="str">
         <x:v>米哈游</x:v>
       </x:c>
-      <x:c r="C95" s="18" t="str">
+      <x:c r="C97" s="18" t="str">
         <x:v>游戏/互联网</x:v>
       </x:c>
-      <x:c r="D95" s="18" t="str">
+      <x:c r="D97" s="18" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E95" s="18" t="str">
+      <x:c r="E97" s="18" t="str">
         <x:v>上海、北京</x:v>
       </x:c>
-      <x:c r="F95" s="18" t="str">
+      <x:c r="F97" s="18" t="str">
         <x:v>技术提前批</x:v>
       </x:c>
-      <x:c r="G95" s="18" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H95" s="18" t="str">
+      <x:c r="G97" s="18" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H97" s="18" t="str">
         <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
       </x:c>
-      <x:c r="I95" s="19" t="str">
+      <x:c r="I97" s="19" t="str">
         <x:v>https://campus.mihoyo.com/</x:v>
       </x:c>
-      <x:c r="J95" s="18" t="str">
+      <x:c r="J97" s="18" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
-      <x:c r="K95" s="18" t="str">
+      <x:c r="K97" s="18" t="str">
         <x:v>有免笔试直通面试机会</x:v>
       </x:c>
-      <x:c r="L95" s="18" t="str">
+      <x:c r="L97" s="18" t="str">
         <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
       </x:c>
-      <x:c r="M95" s="18" t="str">
+      <x:c r="M97" s="18" t="str">
         <x:v>已截止</x:v>
       </x:c>
-      <x:c r="N95" s="18" t="str">
+      <x:c r="N97" s="18" t="str">
         <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
       </x:c>
-      <x:c r="O95" s="19" t="str">
+      <x:c r="O97" s="19" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P95" s="16" t="str">
+      <x:c r="P97" s="16" t="str">
         <x:v>A-官方招聘公告已核验</x:v>
       </x:c>
-      <x:c r="Q95" s="18" t="str">
+      <x:c r="Q97" s="18" t="str">
         <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
-    <x:row r="96" ht="54" customHeight="1">
-      <x:c r="A96" s="14" t="str">
+    <x:row r="98" ht="54" customHeight="1">
+      <x:c r="A98" s="14" t="str">
         <x:v>2026-07-02</x:v>
       </x:c>
-      <x:c r="B96" s="14" t="str">
+      <x:c r="B98" s="14" t="str">
         <x:v>京东方-先锋京英计划</x:v>
       </x:c>
-      <x:c r="C96" s="14" t="str">
+      <x:c r="C98" s="14" t="str">
         <x:v>显示技术/半导体/物联网</x:v>
       </x:c>
-      <x:c r="D96" s="14" t="str">
+      <x:c r="D98" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
-      <x:c r="E96" s="14" t="str">
+      <x:c r="E98" s="14" t="str">
         <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
       </x:c>
-      <x:c r="F96" s="14" t="str">
+      <x:c r="F98" s="14" t="str">
         <x:v>提前批</x:v>
       </x:c>
-      <x:c r="G96" s="14" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H96" s="14" t="str">
+      <x:c r="G98" s="14" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H98" s="14" t="str">
         <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
       </x:c>
-      <x:c r="I96" s="17" t="str">
+      <x:c r="I98" s="17" t="str">
         <x:v>https://campus.boe.com/</x:v>
       </x:c>
-      <x:c r="J96" s="14" t="str">
+      <x:c r="J98" s="14" t="str">
         <x:v>2026-08-14</x:v>
       </x:c>
-      <x:c r="K96" s="14" t="str">
+      <x:c r="K98" s="14" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
-      <x:c r="L96" s="14" t="str">
+      <x:c r="L98" s="14" t="str">
         <x:v>已核验开放</x:v>
       </x:c>
-      <x:c r="M96" s="14" t="str">
+      <x:c r="M98" s="14" t="str">
         <x:v>P1-7天内截止</x:v>
       </x:c>
-      <x:c r="N96" s="14" t="str">
+      <x:c r="N98" s="14" t="str">
         <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
       </x:c>
-      <x:c r="O96" s="17" t="str">
+      <x:c r="O98" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P96" s="16" t="str">
+      <x:c r="P98" s="16" t="str">
         <x:v>A-国家大学生就业平台公告已核验</x:v>
       </x:c>
-      <x:c r="Q96" s="14" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" ht="54" customHeight="1">
-      <x:c r="A97" s="4" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="B97" s="4" t="str">
-        <x:v>中国航天科技集团</x:v>
-      </x:c>
-      <x:c r="C97" s="4" t="str">
-        <x:v>航天/军工</x:v>
-      </x:c>
-      <x:c r="D97" s="4" t="str">
-        <x:v>央企</x:v>
-      </x:c>
-      <x:c r="E97" s="4" t="str">
-        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
-      </x:c>
-      <x:c r="F97" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G97" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H97" s="4" t="str">
-        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
-      </x:c>
-      <x:c r="I97" s="15" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
-      </x:c>
-      <x:c r="J97" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K97" s="4" t="str">
-        <x:v>各院所自行组织，未统一</x:v>
-      </x:c>
-      <x:c r="L97" s="4" t="str">
-        <x:v>官方公告已确认启动</x:v>
-      </x:c>
-      <x:c r="M97" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N97" s="4" t="str">
-        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
-      </x:c>
-      <x:c r="O97" s="15" t="str">
-        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
-      </x:c>
-      <x:c r="P97" s="16" t="str">
-        <x:v>A-国务院国资委/集团官方来源</x:v>
-      </x:c>
-      <x:c r="Q97" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" ht="54" customHeight="1">
-      <x:c r="A98" s="4" t="str">
-        <x:v>2026-06-29</x:v>
-      </x:c>
-      <x:c r="B98" s="4" t="str">
-        <x:v>高途</x:v>
-      </x:c>
-      <x:c r="C98" s="4" t="str">
-        <x:v>教育科技</x:v>
-      </x:c>
-      <x:c r="D98" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E98" s="4" t="str">
-        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
-      </x:c>
-      <x:c r="F98" s="4" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G98" s="4" t="str">
-        <x:v>27届为主，优秀28届也可投</x:v>
-      </x:c>
-      <x:c r="H98" s="4" t="str">
-        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
-      </x:c>
-      <x:c r="I98" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
-      </x:c>
-      <x:c r="J98" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K98" s="4" t="str">
-        <x:v>否；流程包含笔试</x:v>
-      </x:c>
-      <x:c r="L98" s="4" t="str">
-        <x:v>已核验开放</x:v>
-      </x:c>
-      <x:c r="M98" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N98" s="4" t="str">
-        <x:v>滚动发放Offer，截止时间未公布。</x:v>
-      </x:c>
-      <x:c r="O98" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P98" s="16" t="str">
-        <x:v>A-官方投递平台已核验</x:v>
-      </x:c>
-      <x:c r="Q98" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+      <x:c r="Q98" s="14" t="str">
+        <x:v>2026-08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="54" customHeight="1">
       <x:c r="A99" s="4" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="B99" s="4" t="str">
-        <x:v>中汽中心</x:v>
+        <x:v>中国航天科技集团</x:v>
       </x:c>
       <x:c r="C99" s="4" t="str">
-        <x:v>汽车检测/科研</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D99" s="4" t="str">
         <x:v>央企</x:v>
       </x:c>
       <x:c r="E99" s="4" t="str">
-        <x:v>天津、武汉、北京、上海等</x:v>
+        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
       </x:c>
       <x:c r="F99" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5700,31 +5700,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H99" s="4" t="str">
-        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
+        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
       </x:c>
       <x:c r="I99" s="15" t="str">
-        <x:v>https://www.catarc.ac.cn/</x:v>
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J99" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K99" s="4" t="str">
-        <x:v>官方未统一说明</x:v>
+        <x:v>各院所自行组织，未统一</x:v>
       </x:c>
       <x:c r="L99" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>官方公告已确认启动</x:v>
       </x:c>
       <x:c r="M99" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N99" s="4" t="str">
-        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
+        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
       </x:c>
       <x:c r="O99" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
-      </x:c>
-      <x:c r="P99" s="14" t="str">
-        <x:v>B-公开招聘公告</x:v>
+        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
+      </x:c>
+      <x:c r="P99" s="16" t="str">
+        <x:v>A-国务院国资委/集团官方来源</x:v>
       </x:c>
       <x:c r="Q99" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5732,72 +5732,72 @@
     </x:row>
     <x:row r="100" ht="54" customHeight="1">
       <x:c r="A100" s="4" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="B100" s="4" t="str">
-        <x:v>中国航天科工集团</x:v>
+        <x:v>高途</x:v>
       </x:c>
       <x:c r="C100" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D100" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E100" s="4" t="str">
-        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
+        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
       </x:c>
       <x:c r="F100" s="4" t="str">
-        <x:v>正式批/提前批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G100" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>27届为主，优秀28届也可投</x:v>
       </x:c>
       <x:c r="H100" s="4" t="str">
-        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
+        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
       </x:c>
       <x:c r="I100" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
       </x:c>
       <x:c r="J100" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K100" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
+        <x:v>否；流程包含笔试</x:v>
       </x:c>
       <x:c r="L100" s="4" t="str">
-        <x:v>官网公告已确认启动</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M100" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N100" s="4" t="str">
-        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
+        <x:v>滚动发放Offer，截止时间未公布。</x:v>
       </x:c>
       <x:c r="O100" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P100" s="16" t="str">
-        <x:v>A-集团官网公告已核验</x:v>
+        <x:v>A-官方投递平台已核验</x:v>
       </x:c>
       <x:c r="Q100" s="4" t="str">
-        <x:v>2026-07-27</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="54" customHeight="1">
       <x:c r="A101" s="4" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-06-27</x:v>
       </x:c>
       <x:c r="B101" s="4" t="str">
-        <x:v>禾赛科技</x:v>
+        <x:v>中汽中心</x:v>
       </x:c>
       <x:c r="C101" s="4" t="str">
-        <x:v>激光雷达/机器人</x:v>
+        <x:v>汽车检测/科研</x:v>
       </x:c>
       <x:c r="D101" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E101" s="4" t="str">
-        <x:v>上海、杭州</x:v>
+        <x:v>天津、武汉、北京、上海等</x:v>
       </x:c>
       <x:c r="F101" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5806,31 +5806,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H101" s="4" t="str">
-        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
+        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
       </x:c>
       <x:c r="I101" s="15" t="str">
-        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
+        <x:v>https://www.catarc.ac.cn/</x:v>
       </x:c>
       <x:c r="J101" s="4" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K101" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L101" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M101" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N101" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
       </x:c>
       <x:c r="O101" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
       </x:c>
       <x:c r="P101" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>B-公开招聘公告</x:v>
       </x:c>
       <x:c r="Q101" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5838,72 +5838,72 @@
     </x:row>
     <x:row r="102" ht="54" customHeight="1">
       <x:c r="A102" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="B102" s="4" t="str">
-        <x:v>北京国望光学科技有限公司</x:v>
+        <x:v>中国航天科工集团</x:v>
       </x:c>
       <x:c r="C102" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D102" s="4" t="str">
-        <x:v>央国企</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E102" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
       </x:c>
       <x:c r="F102" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批/提前批</x:v>
       </x:c>
       <x:c r="G102" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H102" s="4" t="str">
-        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
-      </x:c>
-      <x:c r="I102" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
+      </x:c>
+      <x:c r="I102" s="15" t="str">
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
       <x:c r="J102" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K102" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L102" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>官网公告已确认启动</x:v>
       </x:c>
       <x:c r="M102" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N102" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
       </x:c>
       <x:c r="O102" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P102" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
+      </x:c>
+      <x:c r="P102" s="16" t="str">
+        <x:v>A-集团官网公告已核验</x:v>
       </x:c>
       <x:c r="Q102" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="54" customHeight="1">
       <x:c r="A103" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="B103" s="4" t="str">
-        <x:v>乐读</x:v>
+        <x:v>禾赛科技</x:v>
       </x:c>
       <x:c r="C103" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>激光雷达/机器人</x:v>
       </x:c>
       <x:c r="D103" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E103" s="4" t="str">
-        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
+        <x:v>上海、杭州</x:v>
       </x:c>
       <x:c r="F103" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5912,31 +5912,31 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H103" s="4" t="str">
-        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
-      </x:c>
-      <x:c r="I103" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
+      </x:c>
+      <x:c r="I103" s="15" t="str">
+        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
       </x:c>
       <x:c r="J103" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="K103" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L103" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M103" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N103" s="4" t="str">
-        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O103" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P103" s="14" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q103" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -5947,31 +5947,31 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B104" s="4" t="str">
-        <x:v>龙蟠科技</x:v>
+        <x:v>北京国望光学科技有限公司</x:v>
       </x:c>
       <x:c r="C104" s="4" t="str">
-        <x:v>新能源材料/化工</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D104" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央国企</x:v>
       </x:c>
       <x:c r="E104" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F104" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G104" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H104" s="4" t="str">
-        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
-      </x:c>
-      <x:c r="I104" s="15" t="str">
-        <x:v>https://www.lopal.com.cn/join</x:v>
+        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
+      </x:c>
+      <x:c r="I104" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J104" s="4" t="str">
-        <x:v>2027-06-01</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K104" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -5980,7 +5980,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M104" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N104" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -6000,16 +6000,16 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B105" s="4" t="str">
-        <x:v>牧原</x:v>
+        <x:v>乐读</x:v>
       </x:c>
       <x:c r="C105" s="4" t="str">
-        <x:v>农业/食品/智能养殖</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D105" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E105" s="4" t="str">
-        <x:v>河南南阳及全国</x:v>
+        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
       </x:c>
       <x:c r="F105" s="4" t="str">
         <x:v>提前批</x:v>
@@ -6018,10 +6018,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H105" s="4" t="str">
-        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
-      </x:c>
-      <x:c r="I105" s="15" t="str">
-        <x:v>https://job.muyuanfoods.com/</x:v>
+        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
+      </x:c>
+      <x:c r="I105" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J105" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6030,19 +6030,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L105" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M105" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N105" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
       </x:c>
       <x:c r="O105" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P105" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>B-招聘平台公开汇总</x:v>
       </x:c>
       <x:c r="Q105" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -6053,31 +6053,31 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B106" s="4" t="str">
-        <x:v>三一集团-小语种校招</x:v>
+        <x:v>龙蟠科技</x:v>
       </x:c>
       <x:c r="C106" s="4" t="str">
-        <x:v>工程机械/制造</x:v>
+        <x:v>新能源材料/化工</x:v>
       </x:c>
       <x:c r="D106" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E106" s="4" t="str">
-        <x:v>海外多国</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F106" s="4" t="str">
-        <x:v>小语种专项/正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G106" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H106" s="4" t="str">
-        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
+        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
       </x:c>
       <x:c r="I106" s="15" t="str">
-        <x:v>https://sanycampus.zhiye.com/</x:v>
+        <x:v>https://www.lopal.com.cn/join</x:v>
       </x:c>
       <x:c r="J106" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-01</x:v>
       </x:c>
       <x:c r="K106" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -6086,7 +6086,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M106" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N106" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -6106,28 +6106,28 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B107" s="4" t="str">
-        <x:v>上海电气-暑期精英训练营</x:v>
+        <x:v>牧原</x:v>
       </x:c>
       <x:c r="C107" s="4" t="str">
-        <x:v>高端装备/能源</x:v>
+        <x:v>农业/食品/智能养殖</x:v>
       </x:c>
       <x:c r="D107" s="4" t="str">
-        <x:v>地方国企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E107" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>河南南阳及全国</x:v>
       </x:c>
       <x:c r="F107" s="4" t="str">
-        <x:v>训练营/秋招直通</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G107" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H107" s="4" t="str">
-        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
+        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
       </x:c>
       <x:c r="I107" s="15" t="str">
-        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
+        <x:v>https://job.muyuanfoods.com/</x:v>
       </x:c>
       <x:c r="J107" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6159,28 +6159,28 @@
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B108" s="4" t="str">
-        <x:v>vivo-蓝极星计划</x:v>
+        <x:v>三一集团-小语种校招</x:v>
       </x:c>
       <x:c r="C108" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>工程机械/制造</x:v>
       </x:c>
       <x:c r="D108" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E108" s="4" t="str">
-        <x:v>深圳、杭州、东莞、上海</x:v>
+        <x:v>海外多国</x:v>
       </x:c>
       <x:c r="F108" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>小语种专项/正式批</x:v>
       </x:c>
       <x:c r="G108" s="4" t="str">
-        <x:v>博士为主</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H108" s="4" t="str">
-        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
+        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
       </x:c>
       <x:c r="I108" s="15" t="str">
-        <x:v>https://hr.vivo.com/</x:v>
+        <x:v>https://sanycampus.zhiye.com/</x:v>
       </x:c>
       <x:c r="J108" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6189,19 +6189,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L108" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M108" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N108" s="4" t="str">
-        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O108" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P108" s="14" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q108" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -6209,31 +6209,31 @@
     </x:row>
     <x:row r="109" ht="54" customHeight="1">
       <x:c r="A109" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B109" s="4" t="str">
-        <x:v>澜起科技</x:v>
+        <x:v>上海电气-暑期精英训练营</x:v>
       </x:c>
       <x:c r="C109" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>高端装备/能源</x:v>
       </x:c>
       <x:c r="D109" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>地方国企</x:v>
       </x:c>
       <x:c r="E109" s="4" t="str">
-        <x:v>昆山、西安、南京</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F109" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>训练营/秋招直通</x:v>
       </x:c>
       <x:c r="G109" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H109" s="4" t="str">
-        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
+        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
       </x:c>
       <x:c r="I109" s="15" t="str">
-        <x:v>https://www.montage-tech.com/cn/careers</x:v>
+        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
       </x:c>
       <x:c r="J109" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6262,31 +6262,31 @@
     </x:row>
     <x:row r="110" ht="54" customHeight="1">
       <x:c r="A110" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B110" s="4" t="str">
-        <x:v>上海宇量昇</x:v>
+        <x:v>vivo-蓝极星计划</x:v>
       </x:c>
       <x:c r="C110" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D110" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E110" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>深圳、杭州、东莞、上海</x:v>
       </x:c>
       <x:c r="F110" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G110" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>博士为主</x:v>
       </x:c>
       <x:c r="H110" s="4" t="str">
-        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
+        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
       </x:c>
       <x:c r="I110" s="15" t="str">
-        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
+        <x:v>https://hr.vivo.com/</x:v>
       </x:c>
       <x:c r="J110" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6295,19 +6295,19 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L110" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M110" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N110" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
       </x:c>
       <x:c r="O110" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P110" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>B-招聘平台公开汇总</x:v>
       </x:c>
       <x:c r="Q110" s="4" t="str">
         <x:v>2026-07-24</x:v>
@@ -6318,16 +6318,16 @@
         <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B111" s="4" t="str">
-        <x:v>是为科技</x:v>
+        <x:v>澜起科技</x:v>
       </x:c>
       <x:c r="C111" s="4" t="str">
-        <x:v>新能源/智能制造</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D111" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E111" s="4" t="str">
-        <x:v>南京、上海、常州</x:v>
+        <x:v>昆山、西安、南京</x:v>
       </x:c>
       <x:c r="F111" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6336,10 +6336,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H111" s="4" t="str">
-        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
+        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
       </x:c>
       <x:c r="I111" s="15" t="str">
-        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
+        <x:v>https://www.montage-tech.com/cn/careers</x:v>
       </x:c>
       <x:c r="J111" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6371,13 +6371,13 @@
         <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B112" s="4" t="str">
-        <x:v>游族网络</x:v>
+        <x:v>上海宇量昇</x:v>
       </x:c>
       <x:c r="C112" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D112" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E112" s="4" t="str">
         <x:v>上海</x:v>
@@ -6389,10 +6389,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H112" s="4" t="str">
-        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
+        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
       </x:c>
       <x:c r="I112" s="15" t="str">
-        <x:v>https://job.youzu.com/</x:v>
+        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
       </x:c>
       <x:c r="J112" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6421,19 +6421,19 @@
     </x:row>
     <x:row r="113" ht="54" customHeight="1">
       <x:c r="A113" s="4" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B113" s="4" t="str">
-        <x:v>中铁设计</x:v>
+        <x:v>是为科技</x:v>
       </x:c>
       <x:c r="C113" s="4" t="str">
-        <x:v>轨道交通/工程设计</x:v>
+        <x:v>新能源/智能制造</x:v>
       </x:c>
       <x:c r="D113" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E113" s="4" t="str">
-        <x:v>北京、济南、郑州、太原</x:v>
+        <x:v>南京、上海、常州</x:v>
       </x:c>
       <x:c r="F113" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6442,10 +6442,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H113" s="4" t="str">
-        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
+        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
       </x:c>
       <x:c r="I113" s="15" t="str">
-        <x:v>https://www.crdc.com/</x:v>
+        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
       </x:c>
       <x:c r="J113" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6474,31 +6474,31 @@
     </x:row>
     <x:row r="114" ht="54" customHeight="1">
       <x:c r="A114" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B114" s="4" t="str">
-        <x:v>迈安德集团-校园大使</x:v>
+        <x:v>游族网络</x:v>
       </x:c>
       <x:c r="C114" s="4" t="str">
-        <x:v>粮油工程/装备</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D114" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E114" s="4" t="str">
-        <x:v>扬州/高校</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F114" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G114" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H114" s="4" t="str">
-        <x:v>校园大使</x:v>
+        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
       </x:c>
       <x:c r="I114" s="15" t="str">
-        <x:v>https://www.myande.com/</x:v>
+        <x:v>https://job.youzu.com/</x:v>
       </x:c>
       <x:c r="J114" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6527,19 +6527,19 @@
     </x:row>
     <x:row r="115" ht="54" customHeight="1">
       <x:c r="A115" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="B115" s="4" t="str">
-        <x:v>迅仿科技</x:v>
+        <x:v>中铁设计</x:v>
       </x:c>
       <x:c r="C115" s="4" t="str">
-        <x:v>工业软件/仿真</x:v>
+        <x:v>轨道交通/工程设计</x:v>
       </x:c>
       <x:c r="D115" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E115" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京、济南、郑州、太原</x:v>
       </x:c>
       <x:c r="F115" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6548,10 +6548,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H115" s="4" t="str">
-        <x:v>仿真工程师</x:v>
-      </x:c>
-      <x:c r="I115" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
+      </x:c>
+      <x:c r="I115" s="15" t="str">
+        <x:v>https://www.crdc.com/</x:v>
       </x:c>
       <x:c r="J115" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6580,34 +6580,34 @@
     </x:row>
     <x:row r="116" ht="54" customHeight="1">
       <x:c r="A116" s="4" t="str">
-        <x:v>2026-06-12</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B116" s="4" t="str">
-        <x:v>MOVA</x:v>
+        <x:v>迈安德集团-校园大使</x:v>
       </x:c>
       <x:c r="C116" s="4" t="str">
-        <x:v>智能家电/机器人</x:v>
+        <x:v>粮油工程/装备</x:v>
       </x:c>
       <x:c r="D116" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E116" s="4" t="str">
-        <x:v>苏州及全国</x:v>
+        <x:v>扬州/高校</x:v>
       </x:c>
       <x:c r="F116" s="4" t="str">
-        <x:v>全球校招/正式批</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G116" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H116" s="4" t="str">
-        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+        <x:v>校园大使</x:v>
       </x:c>
       <x:c r="I116" s="15" t="str">
-        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+        <x:v>https://www.myande.com/</x:v>
       </x:c>
       <x:c r="J116" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K116" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -6616,7 +6616,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M116" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N116" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -6633,19 +6633,19 @@
     </x:row>
     <x:row r="117" ht="54" customHeight="1">
       <x:c r="A117" s="4" t="str">
-        <x:v>2026-06-11</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B117" s="4" t="str">
-        <x:v>财通证券</x:v>
+        <x:v>迅仿科技</x:v>
       </x:c>
       <x:c r="C117" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>工业软件/仿真</x:v>
       </x:c>
       <x:c r="D117" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E117" s="4" t="str">
-        <x:v>杭州、上海、深圳、北京</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F117" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6654,10 +6654,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H117" s="4" t="str">
-        <x:v>总部、参股公司、分公司岗位</x:v>
-      </x:c>
-      <x:c r="I117" s="15" t="str">
-        <x:v>https://www.ctsec.com/joinUs</x:v>
+        <x:v>仿真工程师</x:v>
+      </x:c>
+      <x:c r="I117" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J117" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6686,84 +6686,84 @@
     </x:row>
     <x:row r="118" ht="54" customHeight="1">
       <x:c r="A118" s="4" t="str">
-        <x:v>不晚于2026-06-11</x:v>
+        <x:v>2026-06-12</x:v>
       </x:c>
       <x:c r="B118" s="4" t="str">
-        <x:v>美团-北斗计划及2027校园招聘</x:v>
+        <x:v>MOVA</x:v>
       </x:c>
       <x:c r="C118" s="4" t="str">
-        <x:v>互联网/本地生活/AI</x:v>
+        <x:v>智能家电/机器人</x:v>
       </x:c>
       <x:c r="D118" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E118" s="4" t="str">
-        <x:v>北京、上海、深圳、成都、广州、武汉、杭州、西安等</x:v>
+        <x:v>苏州及全国</x:v>
       </x:c>
       <x:c r="F118" s="4" t="str">
-        <x:v>顶尖人才专项/正式校园招聘</x:v>
+        <x:v>全球校招/正式批</x:v>
       </x:c>
       <x:c r="G118" s="4" t="str">
-        <x:v>应届毕业生，以具体岗位毕业时间要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H118" s="4" t="str">
-        <x:v>北斗计划覆盖大模型、自动驾驶、无人机、机器人和AI Infra等；官方校园职位页当前显示68个岗位</x:v>
+        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
       </x:c>
       <x:c r="I118" s="15" t="str">
-        <x:v>https://zhaopin.meituan.com/web/position?hiringType=1_1</x:v>
+        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
       </x:c>
       <x:c r="J118" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K118" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L118" s="4" t="str">
-        <x:v>本轮新增；美团官方校园招聘职位页及北斗计划入口均显示开放</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M118" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N118" s="4" t="str">
-        <x:v>北斗计划为面向顶尖技术人才的专项，普通校园招聘岗位可在同一官方职位页按“应届生”筛选；不同专项的投递规则可能独立。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O118" s="15" t="str">
-        <x:v>https://zhaopin.meituan.com/web/beidouprogram</x:v>
-      </x:c>
-      <x:c r="P118" s="16" t="str">
-        <x:v>A-企业官方校园招聘职位页已核验</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P118" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q118" s="4" t="str">
-        <x:v>2026-08-10</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="54" customHeight="1">
       <x:c r="A119" s="4" t="str">
-        <x:v>2026-06-10</x:v>
+        <x:v>2026-06-11</x:v>
       </x:c>
       <x:c r="B119" s="4" t="str">
-        <x:v>歌尔股份</x:v>
+        <x:v>财通证券</x:v>
       </x:c>
       <x:c r="C119" s="4" t="str">
-        <x:v>消费电子/智能硬件</x:v>
+        <x:v>证券/金融</x:v>
       </x:c>
       <x:c r="D119" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E119" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>杭州、上海、深圳、北京</x:v>
       </x:c>
       <x:c r="F119" s="4" t="str">
-        <x:v>实习/校招储备</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G119" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H119" s="4" t="str">
-        <x:v>法务助理</x:v>
+        <x:v>总部、参股公司、分公司岗位</x:v>
       </x:c>
       <x:c r="I119" s="15" t="str">
-        <x:v>https://career.goertek.com/</x:v>
+        <x:v>https://www.ctsec.com/joinUs</x:v>
       </x:c>
       <x:c r="J119" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6792,84 +6792,84 @@
     </x:row>
     <x:row r="120" ht="54" customHeight="1">
       <x:c r="A120" s="4" t="str">
-        <x:v>2026-06-09</x:v>
+        <x:v>不晚于2026-06-11</x:v>
       </x:c>
       <x:c r="B120" s="4" t="str">
-        <x:v>深信服-校园大使</x:v>
+        <x:v>美团-北斗计划及2027校园招聘</x:v>
       </x:c>
       <x:c r="C120" s="4" t="str">
-        <x:v>网络安全/云计算</x:v>
+        <x:v>互联网/本地生活/AI</x:v>
       </x:c>
       <x:c r="D120" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E120" s="4" t="str">
-        <x:v>西安</x:v>
+        <x:v>北京、上海、深圳、成都、广州、武汉、杭州、西安等</x:v>
       </x:c>
       <x:c r="F120" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>顶尖人才专项/正式校园招聘</x:v>
       </x:c>
       <x:c r="G120" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>应届毕业生，以具体岗位毕业时间要求为准</x:v>
       </x:c>
       <x:c r="H120" s="4" t="str">
-        <x:v>校园大使</x:v>
+        <x:v>北斗计划覆盖大模型、自动驾驶、无人机、机器人和AI Infra等；官方校园职位页当前显示68个岗位</x:v>
       </x:c>
       <x:c r="I120" s="15" t="str">
-        <x:v>https://hr.sangfor.com/</x:v>
+        <x:v>https://zhaopin.meituan.com/web/position?hiringType=1_1</x:v>
       </x:c>
       <x:c r="J120" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K120" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L120" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>本轮新增；美团官方校园招聘职位页及北斗计划入口均显示开放</x:v>
       </x:c>
       <x:c r="M120" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N120" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>北斗计划为面向顶尖技术人才的专项，普通校园招聘岗位可在同一官方职位页按“应届生”筛选；不同专项的投递规则可能独立。</x:v>
       </x:c>
       <x:c r="O120" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P120" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>https://zhaopin.meituan.com/web/beidouprogram</x:v>
+      </x:c>
+      <x:c r="P120" s="16" t="str">
+        <x:v>A-企业官方校园招聘职位页已核验</x:v>
       </x:c>
       <x:c r="Q120" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="54" customHeight="1">
       <x:c r="A121" s="4" t="str">
-        <x:v>2026-06-08</x:v>
+        <x:v>2026-06-10</x:v>
       </x:c>
       <x:c r="B121" s="4" t="str">
-        <x:v>晓禾教育</x:v>
+        <x:v>歌尔股份</x:v>
       </x:c>
       <x:c r="C121" s="4" t="str">
-        <x:v>教育</x:v>
+        <x:v>消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D121" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E121" s="4" t="str">
-        <x:v>武汉、郑州、襄阳、宜昌</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F121" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>实习/校招储备</x:v>
       </x:c>
       <x:c r="G121" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H121" s="4" t="str">
-        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
-      </x:c>
-      <x:c r="I121" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>法务助理</x:v>
+      </x:c>
+      <x:c r="I121" s="15" t="str">
+        <x:v>https://career.goertek.com/</x:v>
       </x:c>
       <x:c r="J121" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6898,31 +6898,31 @@
     </x:row>
     <x:row r="122" ht="54" customHeight="1">
       <x:c r="A122" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-09</x:v>
       </x:c>
       <x:c r="B122" s="4" t="str">
-        <x:v>晖致医药</x:v>
+        <x:v>深信服-校园大使</x:v>
       </x:c>
       <x:c r="C122" s="4" t="str">
-        <x:v>医药</x:v>
+        <x:v>网络安全/云计算</x:v>
       </x:c>
       <x:c r="D122" s="4" t="str">
-        <x:v>外资</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E122" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>西安</x:v>
       </x:c>
       <x:c r="F122" s="4" t="str">
-        <x:v>实习储备正式岗</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G122" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H122" s="4" t="str">
-        <x:v>医学信息沟通实习生</x:v>
+        <x:v>校园大使</x:v>
       </x:c>
       <x:c r="I122" s="15" t="str">
-        <x:v>https://careers.viatris.com/</x:v>
+        <x:v>https://hr.sangfor.com/</x:v>
       </x:c>
       <x:c r="J122" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6951,19 +6951,19 @@
     </x:row>
     <x:row r="123" ht="54" customHeight="1">
       <x:c r="A123" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-08</x:v>
       </x:c>
       <x:c r="B123" s="4" t="str">
-        <x:v>苏州鸿凌达电子</x:v>
+        <x:v>晓禾教育</x:v>
       </x:c>
       <x:c r="C123" s="4" t="str">
-        <x:v>电子制造</x:v>
+        <x:v>教育</x:v>
       </x:c>
       <x:c r="D123" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E123" s="4" t="str">
-        <x:v>苏州</x:v>
+        <x:v>武汉、郑州、襄阳、宜昌</x:v>
       </x:c>
       <x:c r="F123" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6972,10 +6972,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H123" s="4" t="str">
-        <x:v>财务助理</x:v>
-      </x:c>
-      <x:c r="I123" s="15" t="str">
-        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
+        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
+      </x:c>
+      <x:c r="I123" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J123" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7004,31 +7004,31 @@
     </x:row>
     <x:row r="124" ht="54" customHeight="1">
       <x:c r="A124" s="4" t="str">
-        <x:v>2026-06-02</x:v>
+        <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="B124" s="4" t="str">
-        <x:v>万得信息</x:v>
+        <x:v>晖致医药</x:v>
       </x:c>
       <x:c r="C124" s="4" t="str">
-        <x:v>金融数据/软件</x:v>
+        <x:v>医药</x:v>
       </x:c>
       <x:c r="D124" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>外资</x:v>
       </x:c>
       <x:c r="E124" s="4" t="str">
         <x:v>上海</x:v>
       </x:c>
       <x:c r="F124" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>实习储备正式岗</x:v>
       </x:c>
       <x:c r="G124" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H124" s="4" t="str">
-        <x:v>AI算法工程师等</x:v>
+        <x:v>医学信息沟通实习生</x:v>
       </x:c>
       <x:c r="I124" s="15" t="str">
-        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
+        <x:v>https://careers.viatris.com/</x:v>
       </x:c>
       <x:c r="J124" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7057,31 +7057,31 @@
     </x:row>
     <x:row r="125" ht="54" customHeight="1">
       <x:c r="A125" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="B125" s="4" t="str">
-        <x:v>淘大集供应链</x:v>
+        <x:v>苏州鸿凌达电子</x:v>
       </x:c>
       <x:c r="C125" s="4" t="str">
-        <x:v>零售/供应链</x:v>
+        <x:v>电子制造</x:v>
       </x:c>
       <x:c r="D125" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E125" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>苏州</x:v>
       </x:c>
       <x:c r="F125" s="4" t="str">
-        <x:v>管培/实习</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G125" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H125" s="4" t="str">
-        <x:v>巡店管培生、实习生</x:v>
-      </x:c>
-      <x:c r="I125" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>财务助理</x:v>
+      </x:c>
+      <x:c r="I125" s="15" t="str">
+        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
       </x:c>
       <x:c r="J125" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7110,31 +7110,31 @@
     </x:row>
     <x:row r="126" ht="54" customHeight="1">
       <x:c r="A126" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-02</x:v>
       </x:c>
       <x:c r="B126" s="4" t="str">
-        <x:v>友芝友实业集团</x:v>
+        <x:v>万得信息</x:v>
       </x:c>
       <x:c r="C126" s="4" t="str">
-        <x:v>综合实业</x:v>
+        <x:v>金融数据/软件</x:v>
       </x:c>
       <x:c r="D126" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E126" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F126" s="4" t="str">
-        <x:v>管培生</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G126" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H126" s="4" t="str">
-        <x:v>青年领军人才管培生</x:v>
+        <x:v>AI算法工程师等</x:v>
       </x:c>
       <x:c r="I126" s="15" t="str">
-        <x:v>https://www.yzyqh.com/jrwm</x:v>
+        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
       </x:c>
       <x:c r="J126" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7163,31 +7163,31 @@
     </x:row>
     <x:row r="127" ht="54" customHeight="1">
       <x:c r="A127" s="4" t="str">
-        <x:v>2026-05-29</x:v>
+        <x:v>2026-06-01</x:v>
       </x:c>
       <x:c r="B127" s="4" t="str">
-        <x:v>银雁科技</x:v>
+        <x:v>淘大集供应链</x:v>
       </x:c>
       <x:c r="C127" s="4" t="str">
-        <x:v>金融科技服务</x:v>
+        <x:v>零售/供应链</x:v>
       </x:c>
       <x:c r="D127" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E127" s="4" t="str">
-        <x:v>成都</x:v>
+        <x:v>武汉</x:v>
       </x:c>
       <x:c r="F127" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>管培/实习</x:v>
       </x:c>
       <x:c r="G127" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H127" s="4" t="str">
-        <x:v>人伤理赔</x:v>
-      </x:c>
-      <x:c r="I127" s="15" t="str">
-        <x:v>https://www.cfss.net.cn/</x:v>
+        <x:v>巡店管培生、实习生</x:v>
+      </x:c>
+      <x:c r="I127" s="23" t="str">
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J127" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7216,31 +7216,31 @@
     </x:row>
     <x:row r="128" ht="54" customHeight="1">
       <x:c r="A128" s="4" t="str">
-        <x:v>不晚于2026-05-19</x:v>
+        <x:v>2026-06-01</x:v>
       </x:c>
       <x:c r="B128" s="4" t="str">
-        <x:v>宇树科技-2027校园招聘</x:v>
+        <x:v>友芝友实业集团</x:v>
       </x:c>
       <x:c r="C128" s="4" t="str">
-        <x:v>机器人/具身智能</x:v>
+        <x:v>综合实业</x:v>
       </x:c>
       <x:c r="D128" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E128" s="4" t="str">
-        <x:v>杭州</x:v>
+        <x:v>武汉</x:v>
       </x:c>
       <x:c r="F128" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>管培生</x:v>
       </x:c>
       <x:c r="G128" s="4" t="str">
-        <x:v>2027届应届生，以具体岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H128" s="4" t="str">
-        <x:v>算法、嵌入式、软件、硬件、机械、SLAM、C++、AI、数据、前端、测试、销售、技术支持及设计等</x:v>
+        <x:v>青年领军人才管培生</x:v>
       </x:c>
       <x:c r="I128" s="15" t="str">
-        <x:v>https://www.unitree.com/cn/position</x:v>
+        <x:v>https://www.yzyqh.com/jrwm</x:v>
       </x:c>
       <x:c r="J128" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7249,39 +7249,39 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L128" s="4" t="str">
-        <x:v>本轮新增；宇树科技官方招贤纳士页面当前显示多项热招岗位</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M128" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N128" s="4" t="str">
-        <x:v>官方岗位页当前显示杭州技术类与销售类多个热招职位；校园招聘公告由高校就业平台发布，投递以宇树官网职位详情为准。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O128" s="15" t="str">
-        <x:v>https://www.unitree.com/cn/position</x:v>
-      </x:c>
-      <x:c r="P128" s="16" t="str">
-        <x:v>A-企业官方招贤纳士页面已核验</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P128" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q128" s="4" t="str">
-        <x:v>2026-08-07</x:v>
+        <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="54" customHeight="1">
       <x:c r="A129" s="4" t="str">
-        <x:v>2026-05-15</x:v>
+        <x:v>2026-05-29</x:v>
       </x:c>
       <x:c r="B129" s="4" t="str">
-        <x:v>知乎</x:v>
+        <x:v>银雁科技</x:v>
       </x:c>
       <x:c r="C129" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>金融科技服务</x:v>
       </x:c>
       <x:c r="D129" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E129" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>成都</x:v>
       </x:c>
       <x:c r="F129" s="4" t="str">
         <x:v>正式批</x:v>
@@ -7290,10 +7290,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H129" s="4" t="str">
-        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
+        <x:v>人伤理赔</x:v>
       </x:c>
       <x:c r="I129" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
+        <x:v>https://www.cfss.net.cn/</x:v>
       </x:c>
       <x:c r="J129" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7322,31 +7322,31 @@
     </x:row>
     <x:row r="130" ht="54" customHeight="1">
       <x:c r="A130" s="4" t="str">
-        <x:v>2026-05-08</x:v>
+        <x:v>不晚于2026-05-19</x:v>
       </x:c>
       <x:c r="B130" s="4" t="str">
-        <x:v>招商银行长沙分行</x:v>
+        <x:v>宇树科技-2027校园招聘</x:v>
       </x:c>
       <x:c r="C130" s="4" t="str">
-        <x:v>银行/金融</x:v>
+        <x:v>机器人/具身智能</x:v>
       </x:c>
       <x:c r="D130" s="4" t="str">
-        <x:v>股份制银行</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E130" s="4" t="str">
-        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+        <x:v>杭州</x:v>
       </x:c>
       <x:c r="F130" s="4" t="str">
-        <x:v>暑期实习/秋招直通</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G130" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届生，以具体岗位要求为准</x:v>
       </x:c>
       <x:c r="H130" s="4" t="str">
-        <x:v>2027暑期实习生</x:v>
+        <x:v>算法、嵌入式、软件、硬件、机械、SLAM、C++、AI、数据、前端、测试、销售、技术支持及设计等</x:v>
       </x:c>
       <x:c r="I130" s="15" t="str">
-        <x:v>https://career.cmbchina.com/</x:v>
+        <x:v>https://www.unitree.com/cn/position</x:v>
       </x:c>
       <x:c r="J130" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7355,39 +7355,39 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L130" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>本轮新增；宇树科技官方招贤纳士页面当前显示多项热招岗位</x:v>
       </x:c>
       <x:c r="M130" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N130" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>官方岗位页当前显示杭州技术类与销售类多个热招职位；校园招聘公告由高校就业平台发布，投递以宇树官网职位详情为准。</x:v>
       </x:c>
       <x:c r="O130" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P130" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>https://www.unitree.com/cn/position</x:v>
+      </x:c>
+      <x:c r="P130" s="16" t="str">
+        <x:v>A-企业官方招贤纳士页面已核验</x:v>
       </x:c>
       <x:c r="Q130" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="54" customHeight="1">
       <x:c r="A131" s="4" t="str">
-        <x:v>2026-04-22</x:v>
+        <x:v>2026-05-15</x:v>
       </x:c>
       <x:c r="B131" s="4" t="str">
-        <x:v>华金证券</x:v>
+        <x:v>知乎</x:v>
       </x:c>
       <x:c r="C131" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="D131" s="4" t="str">
-        <x:v>国企</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E131" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F131" s="4" t="str">
         <x:v>正式批</x:v>
@@ -7396,10 +7396,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H131" s="4" t="str">
-        <x:v>战略发展类</x:v>
+        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
       </x:c>
       <x:c r="I131" s="15" t="str">
-        <x:v>https://www.huajinsc.cn/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
       </x:c>
       <x:c r="J131" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7423,6 +7423,112 @@
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
       <x:c r="Q131" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" ht="54" customHeight="1">
+      <x:c r="A132" s="4" t="str">
+        <x:v>2026-05-08</x:v>
+      </x:c>
+      <x:c r="B132" s="4" t="str">
+        <x:v>招商银行长沙分行</x:v>
+      </x:c>
+      <x:c r="C132" s="4" t="str">
+        <x:v>银行/金融</x:v>
+      </x:c>
+      <x:c r="D132" s="4" t="str">
+        <x:v>股份制银行</x:v>
+      </x:c>
+      <x:c r="E132" s="4" t="str">
+        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+      </x:c>
+      <x:c r="F132" s="4" t="str">
+        <x:v>暑期实习/秋招直通</x:v>
+      </x:c>
+      <x:c r="G132" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H132" s="4" t="str">
+        <x:v>2027暑期实习生</x:v>
+      </x:c>
+      <x:c r="I132" s="15" t="str">
+        <x:v>https://career.cmbchina.com/</x:v>
+      </x:c>
+      <x:c r="J132" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K132" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L132" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M132" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N132" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O132" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P132" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q132" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="54" customHeight="1">
+      <x:c r="A133" s="4" t="str">
+        <x:v>2026-04-22</x:v>
+      </x:c>
+      <x:c r="B133" s="4" t="str">
+        <x:v>华金证券</x:v>
+      </x:c>
+      <x:c r="C133" s="4" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="D133" s="4" t="str">
+        <x:v>国企</x:v>
+      </x:c>
+      <x:c r="E133" s="4" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F133" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G133" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H133" s="4" t="str">
+        <x:v>战略发展类</x:v>
+      </x:c>
+      <x:c r="I133" s="15" t="str">
+        <x:v>https://www.huajinsc.cn/</x:v>
+      </x:c>
+      <x:c r="J133" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K133" s="4" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L133" s="4" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M133" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N133" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O133" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P133" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q133" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -7433,7 +7539,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2852fd9642d34d05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcb991abd75441ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7463,7 +7569,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>近期有明确截止时间的项目（截至2026-08-10）</x:v>
+        <x:v>近期有明确截止时间的项目（截至2026-08-11）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -7606,7 +7712,7 @@
         <x:v>A-官方来源公告已核验</x:v>
       </x:c>
       <x:c r="Q4" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
@@ -7659,7 +7765,7 @@
         <x:v>A-国家大学生就业平台公告已核验</x:v>
       </x:c>
       <x:c r="Q5" s="14" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
@@ -8508,107 +8614,160 @@
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-08-01</x:v>
       </x:c>
       <x:c r="B22" s="4" t="str">
-        <x:v>龙蟠科技</x:v>
+        <x:v>中国人民保险集团-2027届统筹校园招聘</x:v>
       </x:c>
       <x:c r="C22" s="4" t="str">
-        <x:v>新能源材料/化工</x:v>
+        <x:v>保险/金融</x:v>
       </x:c>
       <x:c r="D22" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>中央金融企业/国有</x:v>
       </x:c>
       <x:c r="E22" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>全国</x:v>
       </x:c>
       <x:c r="F22" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/集团统筹校园招聘</x:v>
       </x:c>
       <x:c r="G22" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>海内外2027届应届高校毕业生</x:v>
       </x:c>
       <x:c r="H22" s="4" t="str">
-        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
+        <x:v>集团本级及8家成员公司岗位，涵盖保险、投资、科技、精算、信托、再保险及综合职能等</x:v>
       </x:c>
       <x:c r="I22" s="15" t="str">
-        <x:v>https://www.lopal.com.cn/join</x:v>
+        <x:v>https://picc.zhiye.com</x:v>
       </x:c>
       <x:c r="J22" s="4" t="str">
-        <x:v>2027-06-01</x:v>
+        <x:v>2027-04-25（集团本级约2026年10月中旬截止；各单位总部及部分省级机构约2026年11月中下旬截止）</x:v>
       </x:c>
       <x:c r="K22" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否（分批次开展笔试，部分岗位设置差异化笔试）</x:v>
       </x:c>
       <x:c r="L22" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>本轮新增；高校就业网公告来源为中国人民保险集团，官方招聘海报及官网入口已核验</x:v>
       </x:c>
       <x:c r="M22" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P2-分机构截止</x:v>
       </x:c>
       <x:c r="N22" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>招聘覆盖集团本级及8家成员公司；每人最多可投2个志愿，同一机构限投1个岗位。总通道关闭时间较晚，但各机构有更早截止时间，应按目标单位页面尽早投递。</x:v>
       </x:c>
       <x:c r="O22" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P22" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+        <x:v>https://career.smbu.edu.cn/detail/online?id=3537075</x:v>
+      </x:c>
+      <x:c r="P22" s="16" t="str">
+        <x:v>A-官方招聘海报与中国人民保险招聘官网入口已核验</x:v>
       </x:c>
       <x:c r="Q22" s="4" t="str">
-        <x:v>2026-07-24</x:v>
+        <x:v>2026-08-11</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B23" s="4" t="str">
-        <x:v>百度</x:v>
+        <x:v>龙蟠科技</x:v>
       </x:c>
       <x:c r="C23" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>新能源材料/化工</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F23" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
       </x:c>
       <x:c r="I23" s="15" t="str">
-        <x:v>https://talent.baidu.com/jobs</x:v>
+        <x:v>https://www.lopal.com.cn/join</x:v>
       </x:c>
       <x:c r="J23" s="4" t="str">
-        <x:v>2027-06-30</x:v>
+        <x:v>2027-06-01</x:v>
       </x:c>
       <x:c r="K23" s="4" t="str">
-        <x:v>部分免；并非所有候选人参加笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L23" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M23" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N23" s="4" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O23" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P23" s="14" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q23" s="4" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="54" customHeight="1">
+      <x:c r="A24" s="4" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="B24" s="4" t="str">
+        <x:v>百度</x:v>
+      </x:c>
+      <x:c r="C24" s="4" t="str">
+        <x:v>互联网/AI</x:v>
+      </x:c>
+      <x:c r="D24" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E24" s="4" t="str">
+        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+      </x:c>
+      <x:c r="F24" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G24" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H24" s="4" t="str">
+        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+      </x:c>
+      <x:c r="I24" s="15" t="str">
+        <x:v>https://talent.baidu.com/jobs</x:v>
+      </x:c>
+      <x:c r="J24" s="4" t="str">
+        <x:v>2027-06-30</x:v>
+      </x:c>
+      <x:c r="K24" s="4" t="str">
+        <x:v>部分免；并非所有候选人参加笔试</x:v>
+      </x:c>
+      <x:c r="L24" s="4" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M24" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N24" s="4" t="str">
         <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
       </x:c>
-      <x:c r="O23" s="15" t="str">
+      <x:c r="O24" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P23" s="16" t="str">
+      <x:c r="P24" s="16" t="str">
         <x:v>A-官方招聘日历/官方来源已核验</x:v>
       </x:c>
-      <x:c r="Q23" s="4" t="str">
+      <x:c r="Q24" s="4" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -8619,7 +8778,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a4d48394f6e46bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d0b695393124d4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8637,7 +8796,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="28" t="str">
-        <x:v>使用说明与统计（截至2026-08-10）</x:v>
+        <x:v>使用说明与统计（截至2026-08-11）</x:v>
       </x:c>
       <x:c r="B1" s="28"/>
       <x:c r="C1" s="28"/>
@@ -8840,7 +8999,7 @@
         <x:v>项目总数</x:v>
       </x:c>
       <x:c r="B16" s="29" t="n">
-        <x:v>128</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C16" s="26"/>
       <x:c r="D16" s="32" t="str">
@@ -8856,7 +9015,7 @@
         <x:v>有明确截止时间（未截止）</x:v>
       </x:c>
       <x:c r="B17" s="29" t="n">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C17" s="26"/>
       <x:c r="D17" s="32" t="str">
@@ -8872,7 +9031,7 @@
         <x:v>A等级</x:v>
       </x:c>
       <x:c r="B18" s="29" t="n">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C18" s="26"/>
       <x:c r="D18" s="32" t="str">
@@ -8920,7 +9079,7 @@
         <x:v>本次更新</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>新增9项；关闭1项；未来7天内明确截止5项；新增项目来自企业官方校园招聘页，免笔试政策以公告为准。</x:v>
+        <x:v>新增2项；关闭0项；未来7天内明确截止5项；新增项目来自企业官方校园招聘页，免笔试政策以公告为准。</x:v>
       </x:c>
       <x:c r="C22" s="26"/>
       <x:c r="D22" s="26"/>

--- a/2027届秋招投递信息_2026-07-24.xlsx
+++ b/2027届秋招投递信息_2026-07-24.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R74348679e3bc440f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="R63cde1c2fb524898"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="R4eccbf1c302d44a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="当前开放项目" sheetId="1" r:id="R485c00ed921a4750"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="近期明确截止" sheetId="2" r:id="R75b742f632754ef8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="3" r:id="R25b22718fc194feb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
@@ -195,7 +198,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="36">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -296,6 +299,16 @@
     <x:xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -550,28 +563,28 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="23" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="42" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="42" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="25" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="25" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="25" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="37" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="42" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="44" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="27" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="22" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="34" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="34" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="34" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>2027届秋招投递信息（截至2026-08-11）</x:v>
+        <x:v>2027届秋招投递信息（截至2026-08-12）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -664,7 +677,7 @@
         <x:v>核验日期</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="54" customHeight="1">
+    <x:row r="4" ht="66" customHeight="1">
       <x:c r="A4" s="4" t="str">
         <x:v>2026-08-08</x:v>
       </x:c>
@@ -713,11 +726,11 @@
       <x:c r="P4" s="14" t="str">
         <x:v>B-可信高校就业公众号转载浪潮招聘官方公告</x:v>
       </x:c>
-      <x:c r="Q4" s="4" t="str">
+      <x:c r="Q4" s="36" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="54" customHeight="1">
+    <x:row r="5" ht="66" customHeight="1">
       <x:c r="A5" s="4" t="str">
         <x:v>2026-08-08</x:v>
       </x:c>
@@ -766,11 +779,11 @@
       <x:c r="P5" s="16" t="str">
         <x:v>A-集团官网招聘入口与可信高校就业公告交叉核验</x:v>
       </x:c>
-      <x:c r="Q5" s="4" t="str">
+      <x:c r="Q5" s="36" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="54" customHeight="1">
+    <x:row r="6" ht="66" customHeight="1">
       <x:c r="A6" s="4" t="str">
         <x:v>2026-08-08</x:v>
       </x:c>
@@ -819,11 +832,11 @@
       <x:c r="P6" s="16" t="str">
         <x:v>A-企业官方校园招聘门户已核验</x:v>
       </x:c>
-      <x:c r="Q6" s="4" t="str">
+      <x:c r="Q6" s="36" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="54" customHeight="1">
+    <x:row r="7" ht="66" customHeight="1">
       <x:c r="A7" s="4" t="str">
         <x:v>2026-08-08</x:v>
       </x:c>
@@ -872,11 +885,11 @@
       <x:c r="P7" s="16" t="str">
         <x:v>A-企业官方招聘门户与可信高校就业公告交叉核验</x:v>
       </x:c>
-      <x:c r="Q7" s="4" t="str">
+      <x:c r="Q7" s="36" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="54" customHeight="1">
+    <x:row r="8" ht="66" customHeight="1">
       <x:c r="A8" s="4" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
@@ -925,11 +938,11 @@
       <x:c r="P8" s="16" t="str">
         <x:v>A-企业官方校园招聘门户已核验</x:v>
       </x:c>
-      <x:c r="Q8" s="4" t="str">
+      <x:c r="Q8" s="36" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="54" customHeight="1">
+    <x:row r="9" ht="66" customHeight="1">
       <x:c r="A9" s="4" t="str">
         <x:v>不晚于2026-08-06</x:v>
       </x:c>
@@ -978,11 +991,11 @@
       <x:c r="P9" s="16" t="str">
         <x:v>A-企业官方校园招聘平台已核验</x:v>
       </x:c>
-      <x:c r="Q9" s="4" t="str">
+      <x:c r="Q9" s="36" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="54" customHeight="1">
+    <x:row r="10" ht="66" customHeight="1">
       <x:c r="A10" s="4" t="str">
         <x:v>2026-08-06</x:v>
       </x:c>
@@ -1031,11 +1044,11 @@
       <x:c r="P10" s="16" t="str">
         <x:v>A-企业官方校园招聘岗位页已核验</x:v>
       </x:c>
-      <x:c r="Q10" s="4" t="str">
+      <x:c r="Q10" s="36" t="str">
         <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="54" customHeight="1">
+    <x:row r="11" ht="66" customHeight="1">
       <x:c r="A11" s="4" t="str">
         <x:v>2026-08-06</x:v>
       </x:c>
@@ -1084,11 +1097,11 @@
       <x:c r="P11" s="16" t="str">
         <x:v>A-企业官方校园招聘门户已核验</x:v>
       </x:c>
-      <x:c r="Q11" s="4" t="str">
+      <x:c r="Q11" s="36" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="54" customHeight="1">
+    <x:row r="12" ht="66" customHeight="1">
       <x:c r="A12" s="4" t="str">
         <x:v>不晚于2026-08-06</x:v>
       </x:c>
@@ -1137,11 +1150,11 @@
       <x:c r="P12" s="16" t="str">
         <x:v>A-企业官方校园招聘岗位页已核验</x:v>
       </x:c>
-      <x:c r="Q12" s="4" t="str">
+      <x:c r="Q12" s="36" t="str">
         <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="54" customHeight="1">
+    <x:row r="13" ht="66" customHeight="1">
       <x:c r="A13" s="4" t="str">
         <x:v>2026-08-05</x:v>
       </x:c>
@@ -1190,11 +1203,11 @@
       <x:c r="P13" s="14" t="str">
         <x:v>B-可信高校就业网公告含企业官方投递入口</x:v>
       </x:c>
-      <x:c r="Q13" s="4" t="str">
+      <x:c r="Q13" s="36" t="str">
         <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="54" customHeight="1">
+    <x:row r="14" ht="66" customHeight="1">
       <x:c r="A14" s="4" t="str">
         <x:v>2026-08-05</x:v>
       </x:c>
@@ -1243,11 +1256,11 @@
       <x:c r="P14" s="14" t="str">
         <x:v>B-可信高校就业网公告含企业官方投递入口</x:v>
       </x:c>
-      <x:c r="Q14" s="4" t="str">
+      <x:c r="Q14" s="36" t="str">
         <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="54" customHeight="1">
+    <x:row r="15" ht="66" customHeight="1">
       <x:c r="A15" s="4" t="str">
         <x:v>2026-08-05</x:v>
       </x:c>
@@ -1296,11 +1309,11 @@
       <x:c r="P15" s="16" t="str">
         <x:v>A-企业官方校招页与可信高校就业网公告交叉核验</x:v>
       </x:c>
-      <x:c r="Q15" s="4" t="str">
+      <x:c r="Q15" s="36" t="str">
         <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="54" customHeight="1">
+    <x:row r="16" ht="66" customHeight="1">
       <x:c r="A16" s="4" t="str">
         <x:v>2026-08-05</x:v>
       </x:c>
@@ -1349,11 +1362,11 @@
       <x:c r="P16" s="16" t="str">
         <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
-      <x:c r="Q16" s="4" t="str">
+      <x:c r="Q16" s="36" t="str">
         <x:v>2026-08-05</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="54" customHeight="1">
+    <x:row r="17" ht="66" customHeight="1">
       <x:c r="A17" s="4" t="str">
         <x:v>不晚于2026-08-05</x:v>
       </x:c>
@@ -1402,11 +1415,11 @@
       <x:c r="P17" s="16" t="str">
         <x:v>A-企业官方校园招聘岗位页已核验</x:v>
       </x:c>
-      <x:c r="Q17" s="4" t="str">
+      <x:c r="Q17" s="36" t="str">
         <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="54" customHeight="1">
+    <x:row r="18" ht="66" customHeight="1">
       <x:c r="A18" s="4" t="str">
         <x:v>2026-08-05</x:v>
       </x:c>
@@ -1455,11 +1468,11 @@
       <x:c r="P18" s="14" t="str">
         <x:v>B-可信高校就业网公告含企业官方投递方式</x:v>
       </x:c>
-      <x:c r="Q18" s="4" t="str">
+      <x:c r="Q18" s="36" t="str">
         <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="54" customHeight="1">
+    <x:row r="19" ht="66" customHeight="1">
       <x:c r="A19" s="4" t="str">
         <x:v>2026-08-05</x:v>
       </x:c>
@@ -1508,11 +1521,11 @@
       <x:c r="P19" s="16" t="str">
         <x:v>A-温氏股份招聘官方公众号与集团官网校园招聘入口已核验</x:v>
       </x:c>
-      <x:c r="Q19" s="4" t="str">
+      <x:c r="Q19" s="36" t="str">
         <x:v>2026-08-11</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="54" customHeight="1">
+    <x:row r="20" ht="66" customHeight="1">
       <x:c r="A20" s="4" t="str">
         <x:v>2026-08-04</x:v>
       </x:c>
@@ -1561,11 +1574,11 @@
       <x:c r="P20" s="14" t="str">
         <x:v>B-可信高校就业公众号公告含德勤官方招聘入口</x:v>
       </x:c>
-      <x:c r="Q20" s="4" t="str">
+      <x:c r="Q20" s="36" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="54" customHeight="1">
+    <x:row r="21" ht="66" customHeight="1">
       <x:c r="A21" s="4" t="str">
         <x:v>2026-08-04</x:v>
       </x:c>
@@ -1614,11 +1627,11 @@
       <x:c r="P21" s="16" t="str">
         <x:v>A-企业官方职位页已核验</x:v>
       </x:c>
-      <x:c r="Q21" s="4" t="str">
+      <x:c r="Q21" s="36" t="str">
         <x:v>2026-08-06</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="54" customHeight="1">
+    <x:row r="22" ht="66" customHeight="1">
       <x:c r="A22" s="4" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
@@ -1667,11 +1680,11 @@
       <x:c r="P22" s="16" t="str">
         <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
-      <x:c r="Q22" s="4" t="str">
+      <x:c r="Q22" s="36" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="54" customHeight="1">
+    <x:row r="23" ht="66" customHeight="1">
       <x:c r="A23" s="14" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
@@ -1720,11 +1733,11 @@
       <x:c r="P23" s="16" t="str">
         <x:v>A-山东省国资委公告与企业官方招聘网站交叉核验</x:v>
       </x:c>
-      <x:c r="Q23" s="14" t="str">
+      <x:c r="Q23" s="37" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="54" customHeight="1">
+    <x:row r="24" ht="66" customHeight="1">
       <x:c r="A24" s="4" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
@@ -1773,11 +1786,11 @@
       <x:c r="P24" s="16" t="str">
         <x:v>A-企业官方校园招聘入口已核验</x:v>
       </x:c>
-      <x:c r="Q24" s="4" t="str">
+      <x:c r="Q24" s="36" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="54" customHeight="1">
+    <x:row r="25" ht="66" customHeight="1">
       <x:c r="A25" s="4" t="str">
         <x:v>2026-08-01</x:v>
       </x:c>
@@ -1826,11 +1839,11 @@
       <x:c r="P25" s="16" t="str">
         <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
       </x:c>
-      <x:c r="Q25" s="4" t="str">
+      <x:c r="Q25" s="36" t="str">
         <x:v>2026-08-04</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="54" customHeight="1">
+    <x:row r="26" ht="66" customHeight="1">
       <x:c r="A26" s="4" t="str">
         <x:v>2026-08-01</x:v>
       </x:c>
@@ -1879,11 +1892,11 @@
       <x:c r="P26" s="16" t="str">
         <x:v>A-官方招聘海报与中国人民保险招聘官网入口已核验</x:v>
       </x:c>
-      <x:c r="Q26" s="4" t="str">
+      <x:c r="Q26" s="36" t="str">
         <x:v>2026-08-11</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="54" customHeight="1">
+    <x:row r="27" ht="66" customHeight="1">
       <x:c r="A27" s="18" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
@@ -1932,11 +1945,11 @@
       <x:c r="P27" s="16" t="str">
         <x:v>A-企业官方招聘公告已核验</x:v>
       </x:c>
-      <x:c r="Q27" s="18" t="str">
+      <x:c r="Q27" s="38" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="54" customHeight="1">
+    <x:row r="28" ht="66" customHeight="1">
       <x:c r="A28" s="4" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
@@ -1985,11 +1998,11 @@
       <x:c r="P28" s="16" t="str">
         <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
-      <x:c r="Q28" s="4" t="str">
+      <x:c r="Q28" s="36" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="54" customHeight="1">
+    <x:row r="29" ht="66" customHeight="1">
       <x:c r="A29" s="4" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
@@ -2038,11 +2051,11 @@
       <x:c r="P29" s="16" t="str">
         <x:v>A-企业官方校园招聘系统已核验</x:v>
       </x:c>
-      <x:c r="Q29" s="4" t="str">
+      <x:c r="Q29" s="36" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="54" customHeight="1">
+    <x:row r="30" ht="66" customHeight="1">
       <x:c r="A30" s="4" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
@@ -2091,11 +2104,11 @@
       <x:c r="P30" s="16" t="str">
         <x:v>A-企业官方职位页已核验</x:v>
       </x:c>
-      <x:c r="Q30" s="4" t="str">
+      <x:c r="Q30" s="36" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="54" customHeight="1">
+    <x:row r="31" ht="66" customHeight="1">
       <x:c r="A31" s="18" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
@@ -2144,11 +2157,11 @@
       <x:c r="P31" s="16" t="str">
         <x:v>A-企业官方招聘入口已核验</x:v>
       </x:c>
-      <x:c r="Q31" s="18" t="str">
+      <x:c r="Q31" s="38" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="54" customHeight="1">
+    <x:row r="32" ht="66" customHeight="1">
       <x:c r="A32" s="4" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
@@ -2197,11 +2210,11 @@
       <x:c r="P32" s="16" t="str">
         <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
-      <x:c r="Q32" s="4" t="str">
+      <x:c r="Q32" s="36" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="54" customHeight="1">
+    <x:row r="33" ht="66" customHeight="1">
       <x:c r="A33" s="4" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
@@ -2250,11 +2263,11 @@
       <x:c r="P33" s="16" t="str">
         <x:v>A-企业官网与官方校招系统交叉核验</x:v>
       </x:c>
-      <x:c r="Q33" s="4" t="str">
+      <x:c r="Q33" s="36" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="54" customHeight="1">
+    <x:row r="34" ht="66" customHeight="1">
       <x:c r="A34" s="4" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
@@ -2303,11 +2316,11 @@
       <x:c r="P34" s="16" t="str">
         <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
-      <x:c r="Q34" s="4" t="str">
+      <x:c r="Q34" s="36" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="54" customHeight="1">
+    <x:row r="35" ht="66" customHeight="1">
       <x:c r="A35" s="4" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
@@ -2356,11 +2369,11 @@
       <x:c r="P35" s="16" t="str">
         <x:v>A-中国航发官方招聘平台已核验</x:v>
       </x:c>
-      <x:c r="Q35" s="4" t="str">
+      <x:c r="Q35" s="36" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="54" customHeight="1">
+    <x:row r="36" ht="66" customHeight="1">
       <x:c r="A36" s="4" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
@@ -2409,11 +2422,11 @@
       <x:c r="P36" s="16" t="str">
         <x:v>A-企业官方招聘页已核验</x:v>
       </x:c>
-      <x:c r="Q36" s="4" t="str">
+      <x:c r="Q36" s="36" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="54" customHeight="1">
+    <x:row r="37" ht="66" customHeight="1">
       <x:c r="A37" s="4" t="str">
         <x:v>不晚于2026-07-30</x:v>
       </x:c>
@@ -2462,11 +2475,11 @@
       <x:c r="P37" s="16" t="str">
         <x:v>A-中国移动官方招聘平台已核验</x:v>
       </x:c>
-      <x:c r="Q37" s="4" t="str">
+      <x:c r="Q37" s="36" t="str">
         <x:v>2026-07-31</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="54" customHeight="1">
+    <x:row r="38" ht="66" customHeight="1">
       <x:c r="A38" s="4" t="str">
         <x:v>2026-07-28</x:v>
       </x:c>
@@ -2515,11 +2528,11 @@
       <x:c r="P38" s="16" t="str">
         <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
       </x:c>
-      <x:c r="Q38" s="4" t="str">
+      <x:c r="Q38" s="36" t="str">
         <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="54" customHeight="1">
+    <x:row r="39" ht="66" customHeight="1">
       <x:c r="A39" s="4" t="str">
         <x:v>2026-07-28</x:v>
       </x:c>
@@ -2568,11 +2581,11 @@
       <x:c r="P39" s="14" t="str">
         <x:v>B-可信高校就业网公告含官方投递链接</x:v>
       </x:c>
-      <x:c r="Q39" s="4" t="str">
+      <x:c r="Q39" s="36" t="str">
         <x:v>2026-08-04</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="54" customHeight="1">
+    <x:row r="40" ht="66" customHeight="1">
       <x:c r="A40" s="4" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
@@ -2621,11 +2634,11 @@
       <x:c r="P40" s="14" t="str">
         <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
-      <x:c r="Q40" s="4" t="str">
+      <x:c r="Q40" s="36" t="str">
         <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="54" customHeight="1">
+    <x:row r="41" ht="66" customHeight="1">
       <x:c r="A41" s="4" t="str">
         <x:v>2026-07-26</x:v>
       </x:c>
@@ -2674,11 +2687,11 @@
       <x:c r="P41" s="16" t="str">
         <x:v>A-企业官网招聘页与高校公告交叉核验</x:v>
       </x:c>
-      <x:c r="Q41" s="4" t="str">
+      <x:c r="Q41" s="36" t="str">
         <x:v>2026-07-29</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="54" customHeight="1">
+    <x:row r="42" ht="66" customHeight="1">
       <x:c r="A42" s="4" t="str">
         <x:v>2026-07-25</x:v>
       </x:c>
@@ -2727,11 +2740,11 @@
       <x:c r="P42" s="14" t="str">
         <x:v>B-高校就业网转载企业来源</x:v>
       </x:c>
-      <x:c r="Q42" s="4" t="str">
+      <x:c r="Q42" s="36" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="54" customHeight="1">
+    <x:row r="43" ht="66" customHeight="1">
       <x:c r="A43" s="4" t="str">
         <x:v>2026-07-25</x:v>
       </x:c>
@@ -2780,11 +2793,11 @@
       <x:c r="P43" s="16" t="str">
         <x:v>A-高校就业网含官方投递链接</x:v>
       </x:c>
-      <x:c r="Q43" s="4" t="str">
+      <x:c r="Q43" s="36" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="54" customHeight="1">
+    <x:row r="44" ht="66" customHeight="1">
       <x:c r="A44" s="4" t="str">
         <x:v>2026-07-25</x:v>
       </x:c>
@@ -2833,11 +2846,11 @@
       <x:c r="P44" s="14" t="str">
         <x:v>B-高校就业平台转载企业来源</x:v>
       </x:c>
-      <x:c r="Q44" s="4" t="str">
+      <x:c r="Q44" s="36" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="54" customHeight="1">
+    <x:row r="45" ht="66" customHeight="1">
       <x:c r="A45" s="4" t="str">
         <x:v>不晚于2026-07-24</x:v>
       </x:c>
@@ -2886,11 +2899,11 @@
       <x:c r="P45" s="14" t="str">
         <x:v>B-公开招聘公告/集团入口</x:v>
       </x:c>
-      <x:c r="Q45" s="4" t="str">
+      <x:c r="Q45" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="54" customHeight="1">
+    <x:row r="46" ht="66" customHeight="1">
       <x:c r="A46" s="4" t="str">
         <x:v>2026-07-23</x:v>
       </x:c>
@@ -2939,11 +2952,11 @@
       <x:c r="P46" s="14" t="str">
         <x:v>B-高校就业网转载企业公告</x:v>
       </x:c>
-      <x:c r="Q46" s="4" t="str">
+      <x:c r="Q46" s="36" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="54" customHeight="1">
+    <x:row r="47" ht="66" customHeight="1">
       <x:c r="A47" s="4" t="str">
         <x:v>2026-07-23</x:v>
       </x:c>
@@ -2992,11 +3005,11 @@
       <x:c r="P47" s="14" t="str">
         <x:v>B-高校就业网公告+公开招聘页面</x:v>
       </x:c>
-      <x:c r="Q47" s="4" t="str">
+      <x:c r="Q47" s="36" t="str">
         <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="54" customHeight="1">
+    <x:row r="48" ht="66" customHeight="1">
       <x:c r="A48" s="4" t="str">
         <x:v>2026-07-22</x:v>
       </x:c>
@@ -3045,37 +3058,37 @@
       <x:c r="P48" s="16" t="str">
         <x:v>A-企业官方校招网站与职位页已核验</x:v>
       </x:c>
-      <x:c r="Q48" s="4" t="str">
+      <x:c r="Q48" s="36" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="54" customHeight="1">
+    <x:row r="49" ht="66" customHeight="1">
       <x:c r="A49" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-22</x:v>
       </x:c>
       <x:c r="B49" s="4" t="str">
-        <x:v>阿里巴巴-阿里星计划</x:v>
+        <x:v>恒玄科技-2027届校园招聘</x:v>
       </x:c>
       <x:c r="C49" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>半导体/芯片</x:v>
       </x:c>
       <x:c r="D49" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E49" s="4" t="str">
-        <x:v>杭州、北京、上海、深圳等</x:v>
+        <x:v>上海、北京、成都、深圳、杭州、武汉、西安</x:v>
       </x:c>
       <x:c r="F49" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G49" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届毕业生，以岗位资格要求为准</x:v>
       </x:c>
       <x:c r="H49" s="4" t="str">
-        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
+        <x:v>52个校招职位，含数字/模拟/射频IC设计、芯片验证、算法、嵌入式软件、硬件、产品、测试、封装、CAD等</x:v>
       </x:c>
       <x:c r="I49" s="15" t="str">
-        <x:v>https://talent.alibaba.com/campus/</x:v>
+        <x:v>https://bestechnic.zhiye.com/campus/jobs</x:v>
       </x:c>
       <x:c r="J49" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3084,57 +3097,57 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L49" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>本轮补录；企业官方校园招聘页当前开放52个2027届校招职位</x:v>
       </x:c>
       <x:c r="M49" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N49" s="4" t="str">
-        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
+        <x:v>岗位按城市和专业方向分批开放；投递前查看职位资格要求与当前状态。</x:v>
       </x:c>
       <x:c r="O49" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://job.lzu.edu.cn/html/74/article/2026/90323.html</x:v>
       </x:c>
       <x:c r="P49" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q49" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="54" customHeight="1">
+        <x:v>A-企业官方校园招聘岗位页已核验；高校就业网公告交叉确认</x:v>
+      </x:c>
+      <x:c r="Q49" s="36" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="66" customHeight="1">
       <x:c r="A50" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B50" s="4" t="str">
-        <x:v>贝恩公司</x:v>
+        <x:v>阿里巴巴-阿里星计划</x:v>
       </x:c>
       <x:c r="C50" s="4" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D50" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E50" s="4" t="str">
-        <x:v>北京、上海、香港等</x:v>
+        <x:v>杭州、北京、上海、深圳等</x:v>
       </x:c>
       <x:c r="F50" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G50" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H50" s="4" t="str">
-        <x:v>助理咨询顾问等</x:v>
+        <x:v>AI、算法、基础研究、数据库及核心技术</x:v>
       </x:c>
       <x:c r="I50" s="15" t="str">
-        <x:v>https://www.bain.com/careers/</x:v>
+        <x:v>https://talent.alibaba.com/campus/</x:v>
       </x:c>
       <x:c r="J50" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K50" s="4" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L50" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3142,50 +3155,52 @@
       <x:c r="M50" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N50" s="4" t="str"/>
+      <x:c r="N50" s="4" t="str">
+        <x:v>顶尖人才专项，不等同于阿里全部正式批岗位。</x:v>
+      </x:c>
       <x:c r="O50" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P50" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q50" s="4" t="str">
+      <x:c r="Q50" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="54" customHeight="1">
+    <x:row r="51" ht="66" customHeight="1">
       <x:c r="A51" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B51" s="4" t="str">
-        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
+        <x:v>贝恩公司</x:v>
       </x:c>
       <x:c r="C51" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D51" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E51" s="4" t="str">
-        <x:v>上海、北京等</x:v>
+        <x:v>北京、上海、香港等</x:v>
       </x:c>
       <x:c r="F51" s="4" t="str">
-        <x:v>顶尖技术专项/提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G51" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H51" s="4" t="str">
-        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
+        <x:v>助理咨询顾问等</x:v>
       </x:c>
       <x:c r="I51" s="15" t="str">
-        <x:v>https://jobs.bilibili.com/</x:v>
+        <x:v>https://www.bain.com/careers/</x:v>
       </x:c>
       <x:c r="J51" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K51" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L51" s="4" t="str">
         <x:v>汇总源显示开放；投递前需官网复核</x:v>
@@ -3193,46 +3208,44 @@
       <x:c r="M51" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
-      <x:c r="N51" s="4" t="str">
-        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
-      </x:c>
+      <x:c r="N51" s="4" t="str"/>
       <x:c r="O51" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P51" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q51" s="4" t="str">
+      <x:c r="Q51" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="54" customHeight="1">
+    <x:row r="52" ht="66" customHeight="1">
       <x:c r="A52" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B52" s="4" t="str">
-        <x:v>东风汽车-全球博士人才</x:v>
+        <x:v>哔哩哔哩-顶尖技术人才项目</x:v>
       </x:c>
       <x:c r="C52" s="4" t="str">
-        <x:v>汽车/央企</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="D52" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E52" s="4" t="str">
-        <x:v>武汉、广州、十堰及全国研发基地</x:v>
+        <x:v>上海、北京等</x:v>
       </x:c>
       <x:c r="F52" s="4" t="str">
-        <x:v>博士专项</x:v>
+        <x:v>顶尖技术专项/提前批</x:v>
       </x:c>
       <x:c r="G52" s="4" t="str">
-        <x:v>2026届及以后博士</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H52" s="4" t="str">
-        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
+        <x:v>算法、AI、音视频、基础架构等核心技术</x:v>
       </x:c>
       <x:c r="I52" s="15" t="str">
-        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
+        <x:v>https://jobs.bilibili.com/</x:v>
       </x:c>
       <x:c r="J52" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3247,7 +3260,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N52" s="4" t="str">
-        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
+        <x:v>专项门槛与普通校招不同，具体资格以官网为准。</x:v>
       </x:c>
       <x:c r="O52" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3255,37 +3268,37 @@
       <x:c r="P52" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q52" s="4" t="str">
+      <x:c r="Q52" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="54" customHeight="1">
+    <x:row r="53" ht="66" customHeight="1">
       <x:c r="A53" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B53" s="4" t="str">
-        <x:v>度小满-博士后人才招聘</x:v>
+        <x:v>东风汽车-全球博士人才</x:v>
       </x:c>
       <x:c r="C53" s="4" t="str">
-        <x:v>金融科技</x:v>
+        <x:v>汽车/央企</x:v>
       </x:c>
       <x:c r="D53" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E53" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>武汉、广州、十堰及全国研发基地</x:v>
       </x:c>
       <x:c r="F53" s="4" t="str">
-        <x:v>博士后专项</x:v>
+        <x:v>博士专项</x:v>
       </x:c>
       <x:c r="G53" s="4" t="str">
-        <x:v>2025/2026/2027届博士</x:v>
+        <x:v>2026届及以后博士</x:v>
       </x:c>
       <x:c r="H53" s="4" t="str">
-        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
+        <x:v>汽车工程、新能源、智能驾驶、材料、机械、软件算法等</x:v>
       </x:c>
       <x:c r="I53" s="15" t="str">
-        <x:v>https://campus.duxiaoman.com/</x:v>
+        <x:v>https://zhaopin.dongfengmotor.com/</x:v>
       </x:c>
       <x:c r="J53" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3300,7 +3313,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N53" s="4" t="str">
-        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
+        <x:v>博士专项，不等同于本科/硕士正式秋招。</x:v>
       </x:c>
       <x:c r="O53" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3308,37 +3321,37 @@
       <x:c r="P53" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q53" s="4" t="str">
+      <x:c r="Q53" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="54" customHeight="1">
+    <x:row r="54" ht="66" customHeight="1">
       <x:c r="A54" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B54" s="4" t="str">
-        <x:v>多益网络</x:v>
+        <x:v>度小满-博士后人才招聘</x:v>
       </x:c>
       <x:c r="C54" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>金融科技</x:v>
       </x:c>
       <x:c r="D54" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E54" s="4" t="str">
-        <x:v>广州、武汉、成都等</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F54" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>博士后专项</x:v>
       </x:c>
       <x:c r="G54" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2025/2026/2027届博士</x:v>
       </x:c>
       <x:c r="H54" s="4" t="str">
-        <x:v>程序、策划、美术、运营、市场及职能</x:v>
+        <x:v>金融科技、AI、大模型、风控及经济金融研究</x:v>
       </x:c>
       <x:c r="I54" s="15" t="str">
-        <x:v>https://www.duoyi.com/job/</x:v>
+        <x:v>https://campus.duxiaoman.com/</x:v>
       </x:c>
       <x:c r="J54" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -3353,7 +3366,7 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N54" s="4" t="str">
-        <x:v>岗位可能按城市提前关闭。</x:v>
+        <x:v>博士后项目，不适用于普通本科/硕士校招。</x:v>
       </x:c>
       <x:c r="O54" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -3361,11 +3374,11 @@
       <x:c r="P54" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q54" s="4" t="str">
+      <x:c r="Q54" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="54" customHeight="1">
+    <x:row r="55" ht="66" customHeight="1">
       <x:c r="A55" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -3414,11 +3427,11 @@
       <x:c r="P55" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q55" s="4" t="str">
+      <x:c r="Q55" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="54" customHeight="1">
+    <x:row r="56" ht="66" customHeight="1">
       <x:c r="A56" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -3465,11 +3478,11 @@
       <x:c r="P56" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q56" s="4" t="str">
+      <x:c r="Q56" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="54" customHeight="1">
+    <x:row r="57" ht="66" customHeight="1">
       <x:c r="A57" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -3516,11 +3529,11 @@
       <x:c r="P57" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q57" s="4" t="str">
+      <x:c r="Q57" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="54" customHeight="1">
+    <x:row r="58" ht="66" customHeight="1">
       <x:c r="A58" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -3567,11 +3580,11 @@
       <x:c r="P58" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q58" s="4" t="str">
+      <x:c r="Q58" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="54" customHeight="1">
+    <x:row r="59" ht="66" customHeight="1">
       <x:c r="A59" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -3620,11 +3633,11 @@
       <x:c r="P59" s="20" t="str">
         <x:v>C-主体与入口需二次确认</x:v>
       </x:c>
-      <x:c r="Q59" s="4" t="str">
+      <x:c r="Q59" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="54" customHeight="1">
+    <x:row r="60" ht="66" customHeight="1">
       <x:c r="A60" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -3673,11 +3686,11 @@
       <x:c r="P60" s="16" t="str">
         <x:v>A-企业官网校招页面已核验</x:v>
       </x:c>
-      <x:c r="Q60" s="4" t="str">
+      <x:c r="Q60" s="36" t="str">
         <x:v>2026-07-30</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="54" customHeight="1">
+    <x:row r="61" ht="66" customHeight="1">
       <x:c r="A61" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -3726,11 +3739,11 @@
       <x:c r="P61" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q61" s="4" t="str">
+      <x:c r="Q61" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="54" customHeight="1">
+    <x:row r="62" ht="66" customHeight="1">
       <x:c r="A62" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -3779,11 +3792,11 @@
       <x:c r="P62" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q62" s="4" t="str">
+      <x:c r="Q62" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="54" customHeight="1">
+    <x:row r="63" ht="66" customHeight="1">
       <x:c r="A63" s="18" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -3832,11 +3845,11 @@
       <x:c r="P63" s="16" t="str">
         <x:v>A-企业官方校园招聘页已核验</x:v>
       </x:c>
-      <x:c r="Q63" s="18" t="str">
+      <x:c r="Q63" s="38" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
-    <x:row r="64" ht="54" customHeight="1">
+    <x:row r="64" ht="66" customHeight="1">
       <x:c r="A64" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -3883,11 +3896,11 @@
       <x:c r="P64" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q64" s="4" t="str">
+      <x:c r="Q64" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="65" ht="54" customHeight="1">
+    <x:row r="65" ht="66" customHeight="1">
       <x:c r="A65" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -3936,11 +3949,11 @@
       <x:c r="P65" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q65" s="4" t="str">
+      <x:c r="Q65" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="66" ht="54" customHeight="1">
+    <x:row r="66" ht="66" customHeight="1">
       <x:c r="A66" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -3989,11 +4002,11 @@
       <x:c r="P66" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q66" s="4" t="str">
+      <x:c r="Q66" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="67" ht="54" customHeight="1">
+    <x:row r="67" ht="66" customHeight="1">
       <x:c r="A67" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4042,11 +4055,11 @@
       <x:c r="P67" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q67" s="4" t="str">
+      <x:c r="Q67" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="68" ht="54" customHeight="1">
+    <x:row r="68" ht="66" customHeight="1">
       <x:c r="A68" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4095,11 +4108,11 @@
       <x:c r="P68" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q68" s="4" t="str">
+      <x:c r="Q68" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="69" ht="54" customHeight="1">
+    <x:row r="69" ht="66" customHeight="1">
       <x:c r="A69" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4148,11 +4161,11 @@
       <x:c r="P69" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q69" s="4" t="str">
+      <x:c r="Q69" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="70" ht="54" customHeight="1">
+    <x:row r="70" ht="66" customHeight="1">
       <x:c r="A70" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
@@ -4201,11 +4214,11 @@
       <x:c r="P70" s="16" t="str">
         <x:v>A-企业官方校园招聘公告已核验</x:v>
       </x:c>
-      <x:c r="Q70" s="4" t="str">
+      <x:c r="Q70" s="36" t="str">
         <x:v>2026-08-10</x:v>
       </x:c>
     </x:row>
-    <x:row r="71" ht="54" customHeight="1">
+    <x:row r="71" ht="66" customHeight="1">
       <x:c r="A71" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
@@ -4254,11 +4267,11 @@
       <x:c r="P71" s="16" t="str">
         <x:v>A-官方招聘官网已核验</x:v>
       </x:c>
-      <x:c r="Q71" s="4" t="str">
+      <x:c r="Q71" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="72" ht="54" customHeight="1">
+    <x:row r="72" ht="66" customHeight="1">
       <x:c r="A72" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4307,11 +4320,11 @@
       <x:c r="P72" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q72" s="4" t="str">
+      <x:c r="Q72" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="73" ht="54" customHeight="1">
+    <x:row r="73" ht="66" customHeight="1">
       <x:c r="A73" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4358,11 +4371,11 @@
       <x:c r="P73" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q73" s="4" t="str">
+      <x:c r="Q73" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="74" ht="54" customHeight="1">
+    <x:row r="74" ht="66" customHeight="1">
       <x:c r="A74" s="4" t="str">
         <x:v>2026-07-21</x:v>
       </x:c>
@@ -4411,11 +4424,11 @@
       <x:c r="P74" s="16" t="str">
         <x:v>A-企业官网与公开公告已核验</x:v>
       </x:c>
-      <x:c r="Q74" s="4" t="str">
+      <x:c r="Q74" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="75" ht="54" customHeight="1">
+    <x:row r="75" ht="66" customHeight="1">
       <x:c r="A75" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4464,11 +4477,11 @@
       <x:c r="P75" s="14" t="str">
         <x:v>B-高校/招聘平台转载，投前复核</x:v>
       </x:c>
-      <x:c r="Q75" s="4" t="str">
+      <x:c r="Q75" s="36" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
-    <x:row r="76" ht="54" customHeight="1">
+    <x:row r="76" ht="66" customHeight="1">
       <x:c r="A76" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4515,11 +4528,11 @@
       <x:c r="P76" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q76" s="4" t="str">
+      <x:c r="Q76" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="77" ht="54" customHeight="1">
+    <x:row r="77" ht="66" customHeight="1">
       <x:c r="A77" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4566,11 +4579,11 @@
       <x:c r="P77" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q77" s="4" t="str">
+      <x:c r="Q77" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="78" ht="54" customHeight="1">
+    <x:row r="78" ht="66" customHeight="1">
       <x:c r="A78" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4617,11 +4630,11 @@
       <x:c r="P78" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q78" s="4" t="str">
+      <x:c r="Q78" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="79" ht="54" customHeight="1">
+    <x:row r="79" ht="66" customHeight="1">
       <x:c r="A79" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4668,11 +4681,11 @@
       <x:c r="P79" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q79" s="4" t="str">
+      <x:c r="Q79" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="80" ht="54" customHeight="1">
+    <x:row r="80" ht="66" customHeight="1">
       <x:c r="A80" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4721,11 +4734,11 @@
       <x:c r="P80" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q80" s="4" t="str">
+      <x:c r="Q80" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="81" ht="54" customHeight="1">
+    <x:row r="81" ht="66" customHeight="1">
       <x:c r="A81" s="14" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4774,11 +4787,11 @@
       <x:c r="P81" s="20" t="str">
         <x:v>C-名称需二次确认</x:v>
       </x:c>
-      <x:c r="Q81" s="14" t="str">
+      <x:c r="Q81" s="37" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="82" ht="54" customHeight="1">
+    <x:row r="82" ht="66" customHeight="1">
       <x:c r="A82" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4827,11 +4840,11 @@
       <x:c r="P82" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q82" s="4" t="str">
+      <x:c r="Q82" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="83" ht="54" customHeight="1">
+    <x:row r="83" ht="66" customHeight="1">
       <x:c r="A83" s="18" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4880,11 +4893,11 @@
       <x:c r="P83" s="14" t="str">
         <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q83" s="18" t="str">
+      <x:c r="Q83" s="38" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
-    <x:row r="84" ht="54" customHeight="1">
+    <x:row r="84" ht="66" customHeight="1">
       <x:c r="A84" s="14" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4931,11 +4944,11 @@
       <x:c r="P84" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q84" s="14" t="str">
+      <x:c r="Q84" s="37" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="85" ht="54" customHeight="1">
+    <x:row r="85" ht="66" customHeight="1">
       <x:c r="A85" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -4984,11 +4997,11 @@
       <x:c r="P85" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q85" s="4" t="str">
+      <x:c r="Q85" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="86" ht="54" customHeight="1">
+    <x:row r="86" ht="66" customHeight="1">
       <x:c r="A86" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
@@ -5037,11 +5050,11 @@
       <x:c r="P86" s="20" t="str">
         <x:v>C-公开汇总，投前需官网复核</x:v>
       </x:c>
-      <x:c r="Q86" s="4" t="str">
+      <x:c r="Q86" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="87" ht="54" customHeight="1">
+    <x:row r="87" ht="66" customHeight="1">
       <x:c r="A87" s="4" t="str">
         <x:v>2026-07-20</x:v>
       </x:c>
@@ -5090,78 +5103,78 @@
       <x:c r="P87" s="14" t="str">
         <x:v>B-高校就业网公开公告</x:v>
       </x:c>
-      <x:c r="Q87" s="4" t="str">
+      <x:c r="Q87" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="88" ht="54" customHeight="1">
+    <x:row r="88" ht="66" customHeight="1">
       <x:c r="A88" s="18" t="str">
+        <x:v>不晚于2026-07-18</x:v>
+      </x:c>
+      <x:c r="B88" s="18" t="str">
+        <x:v>南芯科技-2027届校园招聘</x:v>
+      </x:c>
+      <x:c r="C88" s="18" t="str">
+        <x:v>半导体/芯片</x:v>
+      </x:c>
+      <x:c r="D88" s="18" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E88" s="18" t="str">
+        <x:v>上海、北京、成都、深圳、珠海、南京、西安等</x:v>
+      </x:c>
+      <x:c r="F88" s="18" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G88" s="18" t="str">
+        <x:v>2027届应届毕业生，以岗位资格要求为准</x:v>
+      </x:c>
+      <x:c r="H88" s="18" t="str">
+        <x:v>49个校招职位，含模拟/数字IC设计、系统/现场应用、嵌入式软件、算法、工艺、PDK、质量、器件开发、销售管理等</x:v>
+      </x:c>
+      <x:c r="I88" s="19" t="str">
+        <x:v>https://nanxin.zhiye.com/campus/jobs</x:v>
+      </x:c>
+      <x:c r="J88" s="18" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K88" s="18" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L88" s="18" t="str">
+        <x:v>本轮补录；企业官方校园招聘页当前开放49个2027届校招职位</x:v>
+      </x:c>
+      <x:c r="M88" s="18" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N88" s="18" t="str">
+        <x:v>同一岗位可能覆盖多个城市，资格要求与招聘进度以职位详情页为准。</x:v>
+      </x:c>
+      <x:c r="O88" s="19" t="str">
+        <x:v>https://nanxin.zhiye.com/campus/jobs</x:v>
+      </x:c>
+      <x:c r="P88" s="16" t="str">
+        <x:v>A-企业官方校园招聘岗位页已核验</x:v>
+      </x:c>
+      <x:c r="Q88" s="38" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="66" customHeight="1">
+      <x:c r="A89" s="4" t="str">
         <x:v>2026-07-17</x:v>
       </x:c>
-      <x:c r="B88" s="18" t="str">
+      <x:c r="B89" s="4" t="str">
         <x:v>鹰角网络</x:v>
       </x:c>
-      <x:c r="C88" s="18" t="str">
+      <x:c r="C89" s="4" t="str">
         <x:v>游戏</x:v>
-      </x:c>
-      <x:c r="D88" s="18" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E88" s="18" t="str">
-        <x:v>上海</x:v>
-      </x:c>
-      <x:c r="F88" s="18" t="str">
-        <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G88" s="18" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H88" s="18" t="str">
-        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
-      </x:c>
-      <x:c r="I88" s="19" t="str">
-        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
-      </x:c>
-      <x:c r="J88" s="18" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-      <x:c r="K88" s="18" t="str">
-        <x:v>否；安排笔试/面试</x:v>
-      </x:c>
-      <x:c r="L88" s="18" t="str">
-        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
-      </x:c>
-      <x:c r="M88" s="18" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N88" s="18" t="str">
-        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
-      </x:c>
-      <x:c r="O88" s="19" t="str">
-        <x:v>https://campus.hypergryph.com/</x:v>
-      </x:c>
-      <x:c r="P88" s="16" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q88" s="18" t="str">
-        <x:v>2026-08-03</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" ht="54" customHeight="1">
-      <x:c r="A89" s="4" t="str">
-        <x:v>2026-07-16</x:v>
-      </x:c>
-      <x:c r="B89" s="4" t="str">
-        <x:v>联发科技</x:v>
-      </x:c>
-      <x:c r="C89" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D89" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E89" s="4" t="str">
-        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F89" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5170,69 +5183,69 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H89" s="4" t="str">
-        <x:v>软件类、通信类、IC类</x:v>
+        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
       </x:c>
       <x:c r="I89" s="15" t="str">
-        <x:v>https://mediatek.zhiye.com/</x:v>
+        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
       </x:c>
       <x:c r="J89" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
       <x:c r="K89" s="4" t="str">
-        <x:v>否；明确安排7-8月笔试</x:v>
+        <x:v>否；安排笔试/面试</x:v>
       </x:c>
       <x:c r="L89" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
       </x:c>
       <x:c r="M89" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>已截止</x:v>
       </x:c>
       <x:c r="N89" s="4" t="str">
-        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
+        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
       </x:c>
       <x:c r="O89" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://campus.hypergryph.com/</x:v>
       </x:c>
       <x:c r="P89" s="16" t="str">
-        <x:v>A-官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q89" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" ht="54" customHeight="1">
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q89" s="36" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="66" customHeight="1">
       <x:c r="A90" s="4" t="str">
         <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B90" s="4" t="str">
-        <x:v>DJI大疆</x:v>
+        <x:v>联发科技</x:v>
       </x:c>
       <x:c r="C90" s="4" t="str">
-        <x:v>无人机/智能硬件</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D90" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E90" s="4" t="str">
-        <x:v>深圳、东莞、上海、北京、西安等</x:v>
+        <x:v>北京、上海、深圳、成都、合肥、武汉</x:v>
       </x:c>
       <x:c r="F90" s="4" t="str">
-        <x:v>正式批-拓疆者计划</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G90" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H90" s="4" t="str">
-        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
+        <x:v>软件类、通信类、IC类</x:v>
       </x:c>
       <x:c r="I90" s="15" t="str">
-        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
+        <x:v>https://mediatek.zhiye.com/</x:v>
       </x:c>
       <x:c r="J90" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K90" s="4" t="str">
-        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
+        <x:v>否；明确安排7-8月笔试</x:v>
       </x:c>
       <x:c r="L90" s="4" t="str">
         <x:v>已核验开放</x:v>
@@ -5241,60 +5254,60 @@
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N90" s="4" t="str">
-        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
+        <x:v>主要面向微电子、计算机、通信、软件、自动化等专业本科/硕士。</x:v>
       </x:c>
       <x:c r="O90" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P90" s="16" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q90" s="4" t="str">
+        <x:v>A-官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q90" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="91" ht="54" customHeight="1">
+    <x:row r="91" ht="66" customHeight="1">
       <x:c r="A91" s="14" t="str">
-        <x:v>2026-07-15</x:v>
+        <x:v>2026-07-16</x:v>
       </x:c>
       <x:c r="B91" s="14" t="str">
-        <x:v>蔚来</x:v>
+        <x:v>DJI大疆</x:v>
       </x:c>
       <x:c r="C91" s="14" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>无人机/智能硬件</x:v>
       </x:c>
       <x:c r="D91" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E91" s="14" t="str">
-        <x:v>上海、合肥、北京、武汉、南京等</x:v>
+        <x:v>深圳、东莞、上海、北京、西安等</x:v>
       </x:c>
       <x:c r="F91" s="14" t="str">
-        <x:v>技术提前批</x:v>
+        <x:v>正式批-拓疆者计划</x:v>
       </x:c>
       <x:c r="G91" s="14" t="str">
-        <x:v>2024年9月-2027年8月毕业</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H91" s="14" t="str">
-        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
+        <x:v>算法、软件、嵌入式、芯片、硬件、光学、机械、工业设计、产品、供应链、营销及职能等</x:v>
       </x:c>
       <x:c r="I91" s="17" t="str">
-        <x:v>https://campus.nio.com/</x:v>
+        <x:v>https://app.mokahr.com/m/campus_apply/dji/143359#/jobs</x:v>
       </x:c>
       <x:c r="J91" s="14" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K91" s="14" t="str">
-        <x:v>否；有笔试/测评</x:v>
+        <x:v>部分岗位不设笔试；通过初筛通常有测评</x:v>
       </x:c>
       <x:c r="L91" s="14" t="str">
         <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M91" s="14" t="str">
-        <x:v>P1-7天内截止</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N91" s="14" t="str">
-        <x:v>最多同时申请3个岗位。</x:v>
+        <x:v>首批约138岗；部分终面线下，岗位招满会关闭。</x:v>
       </x:c>
       <x:c r="O91" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
@@ -5302,249 +5315,249 @@
       <x:c r="P91" s="16" t="str">
         <x:v>A-官方来源公告已核验</x:v>
       </x:c>
-      <x:c r="Q91" s="14" t="str">
+      <x:c r="Q91" s="37" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="66" customHeight="1">
+      <x:c r="A92" s="4" t="str">
+        <x:v>2026-07-15</x:v>
+      </x:c>
+      <x:c r="B92" s="4" t="str">
+        <x:v>蔚来</x:v>
+      </x:c>
+      <x:c r="C92" s="4" t="str">
+        <x:v>新能源汽车/智能汽车</x:v>
+      </x:c>
+      <x:c r="D92" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E92" s="4" t="str">
+        <x:v>上海、合肥、北京、武汉、南京等</x:v>
+      </x:c>
+      <x:c r="F92" s="4" t="str">
+        <x:v>技术提前批</x:v>
+      </x:c>
+      <x:c r="G92" s="4" t="str">
+        <x:v>2024年9月-2027年8月毕业</x:v>
+      </x:c>
+      <x:c r="H92" s="4" t="str">
+        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
+      </x:c>
+      <x:c r="I92" s="15" t="str">
+        <x:v>https://campus.nio.com/</x:v>
+      </x:c>
+      <x:c r="J92" s="4" t="str">
+        <x:v>2026-08-14</x:v>
+      </x:c>
+      <x:c r="K92" s="4" t="str">
+        <x:v>否；有笔试/测评</x:v>
+      </x:c>
+      <x:c r="L92" s="4" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M92" s="4" t="str">
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N92" s="4" t="str">
+        <x:v>最多同时申请3个岗位。</x:v>
+      </x:c>
+      <x:c r="O92" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P92" s="16" t="str">
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q92" s="36" t="str">
         <x:v>2026-08-11</x:v>
       </x:c>
     </x:row>
-    <x:row r="92" ht="54" customHeight="1">
-      <x:c r="A92" s="4" t="str">
+    <x:row r="93" ht="66" customHeight="1">
+      <x:c r="A93" s="4" t="str">
         <x:v>2026-07-10</x:v>
       </x:c>
-      <x:c r="B92" s="4" t="str">
+      <x:c r="B93" s="4" t="str">
         <x:v>北方华创</x:v>
       </x:c>
-      <x:c r="C92" s="4" t="str">
+      <x:c r="C93" s="4" t="str">
         <x:v>半导体设备</x:v>
       </x:c>
-      <x:c r="D92" s="4" t="str">
+      <x:c r="D93" s="4" t="str">
         <x:v>国企/上市</x:v>
       </x:c>
-      <x:c r="E92" s="4" t="str">
+      <x:c r="E93" s="4" t="str">
         <x:v>北京、上海、深圳、广州等，以岗位页为准</x:v>
       </x:c>
-      <x:c r="F92" s="4" t="str">
+      <x:c r="F93" s="4" t="str">
         <x:v>提前批</x:v>
-      </x:c>
-      <x:c r="G92" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H92" s="4" t="str">
-        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
-      </x:c>
-      <x:c r="I92" s="15" t="str">
-        <x:v>https://career.naura.com/campus</x:v>
-      </x:c>
-      <x:c r="J92" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K92" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L92" s="4" t="str">
-        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
-      </x:c>
-      <x:c r="M92" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N92" s="4" t="str">
-        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
-      </x:c>
-      <x:c r="O92" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
-      </x:c>
-      <x:c r="P92" s="16" t="str">
-        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
-      </x:c>
-      <x:c r="Q92" s="4" t="str">
-        <x:v>2026-07-30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" ht="54" customHeight="1">
-      <x:c r="A93" s="4" t="str">
-        <x:v>2026-07-09</x:v>
-      </x:c>
-      <x:c r="B93" s="4" t="str">
-        <x:v>百度</x:v>
-      </x:c>
-      <x:c r="C93" s="4" t="str">
-        <x:v>互联网/AI</x:v>
-      </x:c>
-      <x:c r="D93" s="4" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E93" s="4" t="str">
-        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
-      </x:c>
-      <x:c r="F93" s="4" t="str">
-        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G93" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H93" s="4" t="str">
-        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+        <x:v>机械、电气、软件、工艺、射频、质量流程、财务、人力、法务合规、内控审计、供应商管理、销售、市场及商务等</x:v>
       </x:c>
       <x:c r="I93" s="15" t="str">
-        <x:v>https://talent.baidu.com/jobs</x:v>
+        <x:v>https://career.naura.com/campus</x:v>
       </x:c>
       <x:c r="J93" s="4" t="str">
-        <x:v>2027-06-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K93" s="4" t="str">
-        <x:v>部分免；并非所有候选人参加笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L93" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>已核验开放（企业官网校园招聘入口已确认）</x:v>
       </x:c>
       <x:c r="M93" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N93" s="4" t="str">
-        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
+        <x:v>具体子公司、城市和岗位要求需在官方职位页筛选；转载公告未公开统一截止日，可能招满即止。</x:v>
       </x:c>
       <x:c r="O93" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzIyOTIyNzAwMg==&amp;mid=2652731142&amp;idx=8&amp;sn=5ec53ae45d8be7b28b12acc7c9f66ddb&amp;chksm=f2975ec0b516445747eee3bec1d1d4a17042beb68f568890b314fe8cf203f7ceaf0b650f135e&amp;scene=27</x:v>
       </x:c>
       <x:c r="P93" s="16" t="str">
-        <x:v>A-官方招聘日历/官方来源已核验</x:v>
-      </x:c>
-      <x:c r="Q93" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" ht="54" customHeight="1">
+        <x:v>A-企业官网招聘入口与高校公告交叉核验</x:v>
+      </x:c>
+      <x:c r="Q93" s="36" t="str">
+        <x:v>2026-07-30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="66" customHeight="1">
       <x:c r="A94" s="4" t="str">
         <x:v>2026-07-09</x:v>
       </x:c>
       <x:c r="B94" s="4" t="str">
+        <x:v>百度</x:v>
+      </x:c>
+      <x:c r="C94" s="4" t="str">
+        <x:v>互联网/AI</x:v>
+      </x:c>
+      <x:c r="D94" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E94" s="4" t="str">
+        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+      </x:c>
+      <x:c r="F94" s="4" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G94" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H94" s="4" t="str">
+        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+      </x:c>
+      <x:c r="I94" s="15" t="str">
+        <x:v>https://talent.baidu.com/jobs</x:v>
+      </x:c>
+      <x:c r="J94" s="4" t="str">
+        <x:v>2027-06-30</x:v>
+      </x:c>
+      <x:c r="K94" s="4" t="str">
+        <x:v>部分免；并非所有候选人参加笔试</x:v>
+      </x:c>
+      <x:c r="L94" s="4" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M94" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N94" s="4" t="str">
+        <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
+      </x:c>
+      <x:c r="O94" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P94" s="14" t="str">
+        <x:v>A-官方招聘日历/官方来源已核验</x:v>
+      </x:c>
+      <x:c r="Q94" s="36" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="66" customHeight="1">
+      <x:c r="A95" s="4" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="B95" s="4" t="str">
         <x:v>中国航天科工集团第六研究院</x:v>
       </x:c>
-      <x:c r="C94" s="4" t="str">
+      <x:c r="C95" s="4" t="str">
         <x:v>航天/军工/动力系统</x:v>
       </x:c>
-      <x:c r="D94" s="4" t="str">
+      <x:c r="D95" s="4" t="str">
         <x:v>央企院所</x:v>
       </x:c>
-      <x:c r="E94" s="4" t="str">
+      <x:c r="E95" s="4" t="str">
         <x:v>呼和浩特及所属单位</x:v>
       </x:c>
-      <x:c r="F94" s="4" t="str">
+      <x:c r="F95" s="4" t="str">
         <x:v>提前批+暑期开放日</x:v>
       </x:c>
-      <x:c r="G94" s="4" t="str">
+      <x:c r="G95" s="4" t="str">
         <x:v>2027届毕业生，硕士/博士岗位为主，以公告为准</x:v>
       </x:c>
-      <x:c r="H94" s="4" t="str">
+      <x:c r="H95" s="4" t="str">
         <x:v>发动机、动力系统、控制、机械、材料、电子、软件及测试方向</x:v>
       </x:c>
-      <x:c r="I94" s="15" t="str">
+      <x:c r="I95" s="15" t="str">
         <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
-      <x:c r="J94" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K94" s="4" t="str">
+      <x:c r="J95" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K95" s="4" t="str">
         <x:v>各单位自行组织，未统一</x:v>
       </x:c>
-      <x:c r="L94" s="4" t="str">
+      <x:c r="L95" s="4" t="str">
         <x:v>公开高校就业公告显示项目启动；投前确认院所岗位</x:v>
       </x:c>
-      <x:c r="M94" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N94" s="4" t="str">
+      <x:c r="M95" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N95" s="4" t="str">
         <x:v>涉及军工保密、政审和专业限制；六院项目与集团普通校招需分开查看。</x:v>
       </x:c>
-      <x:c r="O94" s="15" t="str">
+      <x:c r="O95" s="15" t="str">
         <x:v>https://sse.ustc.edu.cn/2026/0709/c27935a746910/pagem.htm</x:v>
       </x:c>
-      <x:c r="P94" s="14" t="str">
+      <x:c r="P95" s="14" t="str">
         <x:v>B-高校就业网公开公告</x:v>
       </x:c>
-      <x:c r="Q94" s="4" t="str">
+      <x:c r="Q95" s="36" t="str">
         <x:v>2026-07-27</x:v>
       </x:c>
     </x:row>
-    <x:row r="95" ht="54" customHeight="1">
-      <x:c r="A95" s="4" t="str">
+    <x:row r="96" ht="66" customHeight="1">
+      <x:c r="A96" s="4" t="str">
         <x:v>2026-07-08</x:v>
       </x:c>
-      <x:c r="B95" s="4" t="str">
+      <x:c r="B96" s="4" t="str">
         <x:v>思瑞浦</x:v>
       </x:c>
-      <x:c r="C95" s="4" t="str">
+      <x:c r="C96" s="4" t="str">
         <x:v>半导体/模拟IC</x:v>
-      </x:c>
-      <x:c r="D95" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
-      <x:c r="E95" s="4" t="str">
-        <x:v>上海、深圳等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F95" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
-      </x:c>
-      <x:c r="G95" s="4" t="str">
-        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
-      </x:c>
-      <x:c r="H95" s="4" t="str">
-        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
-      </x:c>
-      <x:c r="I95" s="15" t="str">
-        <x:v>https://www.3peak.cn/careers</x:v>
-      </x:c>
-      <x:c r="J95" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K95" s="4" t="str">
-        <x:v>官方未说明</x:v>
-      </x:c>
-      <x:c r="L95" s="4" t="str">
-        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
-      </x:c>
-      <x:c r="M95" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N95" s="4" t="str">
-        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
-      </x:c>
-      <x:c r="O95" s="15" t="str">
-        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
-      </x:c>
-      <x:c r="P95" s="14" t="str">
-        <x:v>B-招聘平台/高校就业转载</x:v>
-      </x:c>
-      <x:c r="Q95" s="4" t="str">
-        <x:v>2026-07-27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="54" customHeight="1">
-      <x:c r="A96" s="4" t="str">
-        <x:v>不晚于2026-07-07</x:v>
-      </x:c>
-      <x:c r="B96" s="4" t="str">
-        <x:v>文远知行WeRide</x:v>
-      </x:c>
-      <x:c r="C96" s="4" t="str">
-        <x:v>自动驾驶/人工智能</x:v>
       </x:c>
       <x:c r="D96" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E96" s="4" t="str">
-        <x:v>广州、深圳、武汉等，以岗位页为准</x:v>
+        <x:v>上海、深圳等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F96" s="4" t="str">
-        <x:v>正式批/校招/可转正实习</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G96" s="4" t="str">
-        <x:v>2027届应届毕业生及可转正实习生，以岗位要求为准</x:v>
+        <x:v>2027届本科/硕士/博士，以岗位要求为准</x:v>
       </x:c>
       <x:c r="H96" s="4" t="str">
-        <x:v>感知/预测/规划控制算法、算法测试、测试开发、SRE、云与车端安全、AI Infra、仿真平台等</x:v>
+        <x:v>模拟/数字IC设计、验证、应用工程、产品、测试、软件及职能岗位</x:v>
       </x:c>
       <x:c r="I96" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
+        <x:v>https://www.3peak.cn/careers</x:v>
       </x:c>
       <x:c r="J96" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -5553,251 +5566,251 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L96" s="4" t="str">
+        <x:v>公开招聘公告显示开放；投递入口以公告原文为准</x:v>
+      </x:c>
+      <x:c r="M96" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N96" s="4" t="str">
+        <x:v>模拟IC岗位专业匹配要求较强；工作地点和具体岗位以思瑞浦招聘页/公告原文为准。</x:v>
+      </x:c>
+      <x:c r="O96" s="15" t="str">
+        <x:v>https://sh.bendibao.com/job/202678/307448.shtm</x:v>
+      </x:c>
+      <x:c r="P96" s="16" t="str">
+        <x:v>B-招聘平台/高校就业转载</x:v>
+      </x:c>
+      <x:c r="Q96" s="36" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="66" customHeight="1">
+      <x:c r="A97" s="18" t="str">
+        <x:v>不晚于2026-07-07</x:v>
+      </x:c>
+      <x:c r="B97" s="18" t="str">
+        <x:v>文远知行WeRide</x:v>
+      </x:c>
+      <x:c r="C97" s="18" t="str">
+        <x:v>自动驾驶/人工智能</x:v>
+      </x:c>
+      <x:c r="D97" s="18" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E97" s="18" t="str">
+        <x:v>广州、深圳、武汉等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F97" s="18" t="str">
+        <x:v>正式批/校招/可转正实习</x:v>
+      </x:c>
+      <x:c r="G97" s="18" t="str">
+        <x:v>2027届应届毕业生及可转正实习生，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H97" s="18" t="str">
+        <x:v>感知/预测/规划控制算法、算法测试、测试开发、SRE、云与车端安全、AI Infra、仿真平台等</x:v>
+      </x:c>
+      <x:c r="I97" s="19" t="str">
+        <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
+      </x:c>
+      <x:c r="J97" s="18" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K97" s="18" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L97" s="18" t="str">
         <x:v>企业官方校招系统在招；已核验137个职位</x:v>
       </x:c>
-      <x:c r="M96" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N96" s="4" t="str">
+      <x:c r="M97" s="18" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N97" s="18" t="str">
         <x:v>官方列表显示2027届校招职位最早发布于7月7日；部分岗位为可转正实习，城市和岗位随招聘系统实时调整。</x:v>
       </x:c>
-      <x:c r="O96" s="15" t="str">
+      <x:c r="O97" s="19" t="str">
         <x:v>https://app.mokahr.com/campus_apply/jingchi/2137#/jobs</x:v>
       </x:c>
-      <x:c r="P96" s="16" t="str">
+      <x:c r="P97" s="16" t="str">
         <x:v>A-企业官方校招系统与职位列表已核验</x:v>
       </x:c>
-      <x:c r="Q96" s="4" t="str">
+      <x:c r="Q97" s="38" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
     </x:row>
-    <x:row r="97" ht="54" customHeight="1">
-      <x:c r="A97" s="18" t="str">
+    <x:row r="98" ht="66" customHeight="1">
+      <x:c r="A98" s="14" t="str">
         <x:v>2026-07-06</x:v>
       </x:c>
-      <x:c r="B97" s="18" t="str">
+      <x:c r="B98" s="14" t="str">
         <x:v>米哈游</x:v>
       </x:c>
-      <x:c r="C97" s="18" t="str">
+      <x:c r="C98" s="14" t="str">
         <x:v>游戏/互联网</x:v>
-      </x:c>
-      <x:c r="D97" s="18" t="str">
-        <x:v>未注明</x:v>
-      </x:c>
-      <x:c r="E97" s="18" t="str">
-        <x:v>上海、北京</x:v>
-      </x:c>
-      <x:c r="F97" s="18" t="str">
-        <x:v>技术提前批</x:v>
-      </x:c>
-      <x:c r="G97" s="18" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H97" s="18" t="str">
-        <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
-      </x:c>
-      <x:c r="I97" s="19" t="str">
-        <x:v>https://campus.mihoyo.com/</x:v>
-      </x:c>
-      <x:c r="J97" s="18" t="str">
-        <x:v>2026-07-27</x:v>
-      </x:c>
-      <x:c r="K97" s="18" t="str">
-        <x:v>有免笔试直通面试机会</x:v>
-      </x:c>
-      <x:c r="L97" s="18" t="str">
-        <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
-      </x:c>
-      <x:c r="M97" s="18" t="str">
-        <x:v>已截止</x:v>
-      </x:c>
-      <x:c r="N97" s="18" t="str">
-        <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
-      </x:c>
-      <x:c r="O97" s="19" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
-      </x:c>
-      <x:c r="P97" s="16" t="str">
-        <x:v>A-官方招聘公告已核验</x:v>
-      </x:c>
-      <x:c r="Q97" s="18" t="str">
-        <x:v>2026-07-30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" ht="54" customHeight="1">
-      <x:c r="A98" s="14" t="str">
-        <x:v>2026-07-02</x:v>
-      </x:c>
-      <x:c r="B98" s="14" t="str">
-        <x:v>京东方-先锋京英计划</x:v>
-      </x:c>
-      <x:c r="C98" s="14" t="str">
-        <x:v>显示技术/半导体/物联网</x:v>
       </x:c>
       <x:c r="D98" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E98" s="14" t="str">
-        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
+        <x:v>上海、北京</x:v>
       </x:c>
       <x:c r="F98" s="14" t="str">
-        <x:v>提前批</x:v>
+        <x:v>技术提前批</x:v>
       </x:c>
       <x:c r="G98" s="14" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H98" s="14" t="str">
-        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
+        <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
       </x:c>
       <x:c r="I98" s="17" t="str">
-        <x:v>https://campus.boe.com/</x:v>
+        <x:v>https://campus.mihoyo.com/</x:v>
       </x:c>
       <x:c r="J98" s="14" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="K98" s="14" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>有免笔试直通面试机会</x:v>
       </x:c>
       <x:c r="L98" s="14" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
       </x:c>
       <x:c r="M98" s="14" t="str">
-        <x:v>P1-7天内截止</x:v>
+        <x:v>已截止</x:v>
       </x:c>
       <x:c r="N98" s="14" t="str">
-        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
+        <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
       </x:c>
       <x:c r="O98" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P98" s="16" t="str">
-        <x:v>A-国家大学生就业平台公告已核验</x:v>
-      </x:c>
-      <x:c r="Q98" s="14" t="str">
-        <x:v>2026-08-11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" ht="54" customHeight="1">
+        <x:v>A-官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q98" s="37" t="str">
+        <x:v>2026-07-30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="66" customHeight="1">
       <x:c r="A99" s="4" t="str">
-        <x:v>2026-06-30</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="B99" s="4" t="str">
-        <x:v>中国航天科技集团</x:v>
+        <x:v>多益网络</x:v>
       </x:c>
       <x:c r="C99" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D99" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E99" s="4" t="str">
-        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
+        <x:v>广州、武汉、杭州</x:v>
       </x:c>
       <x:c r="F99" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G99" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届毕业生（毕业时间为2026年8月-2027年7月）</x:v>
       </x:c>
       <x:c r="H99" s="4" t="str">
-        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
+        <x:v>程序、策划、美术、运营、市场及职能类岗位，具体以官网职位列表为准</x:v>
       </x:c>
       <x:c r="I99" s="15" t="str">
-        <x:v>https://www.spacetalent.com.cn/</x:v>
+        <x:v>https://xz.duoyi.com/v40/#/news/detail?id=2071944996369465344</x:v>
       </x:c>
       <x:c r="J99" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K99" s="4" t="str">
-        <x:v>各院所自行组织，未统一</x:v>
+        <x:v>否/官方流程含在线笔试（开放题及专业笔试）</x:v>
       </x:c>
       <x:c r="L99" s="4" t="str">
-        <x:v>官方公告已确认启动</x:v>
+        <x:v>企业官方2027届校园招聘秋季提前批开放中</x:v>
       </x:c>
       <x:c r="M99" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N99" s="4" t="str">
-        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
+        <x:v>网申含在线测评，后续为在线笔试和1-2轮在线面试；岗位及工作地点以官网实时列表为准。</x:v>
       </x:c>
       <x:c r="O99" s="15" t="str">
-        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
+        <x:v>https://xz.duoyi.com/v40/#/news/detail?id=2071944996369465344</x:v>
       </x:c>
       <x:c r="P99" s="16" t="str">
-        <x:v>A-国务院国资委/集团官方来源</x:v>
-      </x:c>
-      <x:c r="Q99" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" ht="54" customHeight="1">
+        <x:v>A-企业官方校招公告已核验</x:v>
+      </x:c>
+      <x:c r="Q99" s="36" t="str">
+        <x:v>2026-08-12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="66" customHeight="1">
       <x:c r="A100" s="4" t="str">
-        <x:v>2026-06-29</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="B100" s="4" t="str">
-        <x:v>高途</x:v>
+        <x:v>京东方-先锋京英计划</x:v>
       </x:c>
       <x:c r="C100" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>显示技术/半导体/物联网</x:v>
       </x:c>
       <x:c r="D100" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E100" s="4" t="str">
-        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
+        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
       </x:c>
       <x:c r="F100" s="4" t="str">
         <x:v>提前批</x:v>
       </x:c>
       <x:c r="G100" s="4" t="str">
-        <x:v>27届为主，优秀28届也可投</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H100" s="4" t="str">
-        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
+        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
       </x:c>
       <x:c r="I100" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
+        <x:v>https://campus.boe.com/</x:v>
       </x:c>
       <x:c r="J100" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K100" s="4" t="str">
-        <x:v>否；流程包含笔试</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L100" s="4" t="str">
         <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M100" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P1-7天内截止</x:v>
       </x:c>
       <x:c r="N100" s="4" t="str">
-        <x:v>滚动发放Offer，截止时间未公布。</x:v>
+        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
       </x:c>
       <x:c r="O100" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P100" s="16" t="str">
-        <x:v>A-官方投递平台已核验</x:v>
-      </x:c>
-      <x:c r="Q100" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" ht="54" customHeight="1">
+        <x:v>A-国家大学生就业平台公告已核验</x:v>
+      </x:c>
+      <x:c r="Q100" s="36" t="str">
+        <x:v>2026-08-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="66" customHeight="1">
       <x:c r="A101" s="4" t="str">
-        <x:v>2026-06-27</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="B101" s="4" t="str">
-        <x:v>中汽中心</x:v>
+        <x:v>中国航天科技集团</x:v>
       </x:c>
       <x:c r="C101" s="4" t="str">
-        <x:v>汽车检测/科研</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D101" s="4" t="str">
         <x:v>央企</x:v>
       </x:c>
       <x:c r="E101" s="4" t="str">
-        <x:v>天津、武汉、北京、上海等</x:v>
+        <x:v>北京、上海、西安、成都、天津等各院所</x:v>
       </x:c>
       <x:c r="F101" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5806,104 +5819,104 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H101" s="4" t="str">
-        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
+        <x:v>飞行器、控制、力学、机械、电子、通信、计算机、材料、能源及管理</x:v>
       </x:c>
       <x:c r="I101" s="15" t="str">
-        <x:v>https://www.catarc.ac.cn/</x:v>
+        <x:v>https://www.spacetalent.com.cn/</x:v>
       </x:c>
       <x:c r="J101" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K101" s="4" t="str">
-        <x:v>官方未统一说明</x:v>
+        <x:v>各院所自行组织，未统一</x:v>
       </x:c>
       <x:c r="L101" s="4" t="str">
-        <x:v>公开公告显示启动；投前确认</x:v>
+        <x:v>官方公告已确认启动</x:v>
       </x:c>
       <x:c r="M101" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N101" s="4" t="str">
-        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
+        <x:v>各院所分别招聘，学历和保密要求差异大。</x:v>
       </x:c>
       <x:c r="O101" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
+        <x:v>http://www.sasac.gov.cn/n2588035/n2588325/c35517299/content.html</x:v>
       </x:c>
       <x:c r="P101" s="14" t="str">
-        <x:v>B-公开招聘公告</x:v>
-      </x:c>
-      <x:c r="Q101" s="4" t="str">
+        <x:v>A-国务院国资委/集团官方来源</x:v>
+      </x:c>
+      <x:c r="Q101" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="102" ht="54" customHeight="1">
+    <x:row r="102" ht="66" customHeight="1">
       <x:c r="A102" s="4" t="str">
-        <x:v>2026-06-24</x:v>
+        <x:v>2026-06-29</x:v>
       </x:c>
       <x:c r="B102" s="4" t="str">
-        <x:v>中国航天科工集团</x:v>
+        <x:v>高途</x:v>
       </x:c>
       <x:c r="C102" s="4" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D102" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E102" s="4" t="str">
+        <x:v>北京、郑州、武汉、成都、西安、太原、上海、深圳、广州、苏州、杭州、重庆、南京等</x:v>
+      </x:c>
+      <x:c r="F102" s="4" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G102" s="4" t="str">
+        <x:v>27届为主，优秀28届也可投</x:v>
+      </x:c>
+      <x:c r="H102" s="4" t="str">
+        <x:v>主讲老师、国际教育、顾问、二讲、运营、主播、职能</x:v>
+      </x:c>
+      <x:c r="I102" s="15" t="str">
+        <x:v>https://app.mokahr.com/campus-recruitment/bjhl/102145#/</x:v>
+      </x:c>
+      <x:c r="J102" s="4" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K102" s="4" t="str">
+        <x:v>否；流程包含笔试</x:v>
+      </x:c>
+      <x:c r="L102" s="4" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M102" s="4" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N102" s="4" t="str">
+        <x:v>滚动发放Offer，截止时间未公布。</x:v>
+      </x:c>
+      <x:c r="O102" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P102" s="16" t="str">
+        <x:v>A-官方投递平台已核验</x:v>
+      </x:c>
+      <x:c r="Q102" s="36" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" ht="66" customHeight="1">
+      <x:c r="A103" s="4" t="str">
+        <x:v>2026-06-27</x:v>
+      </x:c>
+      <x:c r="B103" s="4" t="str">
+        <x:v>中汽中心</x:v>
+      </x:c>
+      <x:c r="C103" s="4" t="str">
+        <x:v>汽车检测/科研</x:v>
+      </x:c>
+      <x:c r="D103" s="4" t="str">
         <x:v>央企</x:v>
       </x:c>
-      <x:c r="E102" s="4" t="str">
-        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
-      </x:c>
-      <x:c r="F102" s="4" t="str">
-        <x:v>正式批/提前批</x:v>
-      </x:c>
-      <x:c r="G102" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
-      </x:c>
-      <x:c r="H102" s="4" t="str">
-        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
-      </x:c>
-      <x:c r="I102" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
-      </x:c>
-      <x:c r="J102" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
-      </x:c>
-      <x:c r="K102" s="4" t="str">
-        <x:v>各单位自行组织，未统一</x:v>
-      </x:c>
-      <x:c r="L102" s="4" t="str">
-        <x:v>官网公告已确认启动</x:v>
-      </x:c>
-      <x:c r="M102" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
-      </x:c>
-      <x:c r="N102" s="4" t="str">
-        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
-      </x:c>
-      <x:c r="O102" s="15" t="str">
-        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
-      </x:c>
-      <x:c r="P102" s="16" t="str">
-        <x:v>A-集团官网公告已核验</x:v>
-      </x:c>
-      <x:c r="Q102" s="4" t="str">
-        <x:v>2026-07-27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" ht="54" customHeight="1">
-      <x:c r="A103" s="4" t="str">
-        <x:v>2026-06-18</x:v>
-      </x:c>
-      <x:c r="B103" s="4" t="str">
-        <x:v>禾赛科技</x:v>
-      </x:c>
-      <x:c r="C103" s="4" t="str">
-        <x:v>激光雷达/机器人</x:v>
-      </x:c>
-      <x:c r="D103" s="4" t="str">
-        <x:v>民营/上市</x:v>
-      </x:c>
       <x:c r="E103" s="4" t="str">
-        <x:v>上海、杭州</x:v>
+        <x:v>天津、武汉、北京、上海等</x:v>
       </x:c>
       <x:c r="F103" s="4" t="str">
         <x:v>提前批</x:v>
@@ -5912,104 +5925,104 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H103" s="4" t="str">
-        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
+        <x:v>汽车工程、新能源、智能网联、检测认证、材料、软件算法及管理</x:v>
       </x:c>
       <x:c r="I103" s="15" t="str">
-        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
+        <x:v>https://www.catarc.ac.cn/</x:v>
       </x:c>
       <x:c r="J103" s="4" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K103" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>官方未统一说明</x:v>
       </x:c>
       <x:c r="L103" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>公开公告显示启动；投前确认</x:v>
       </x:c>
       <x:c r="M103" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N103" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>具体招聘单位和入口以中汽中心官网招聘栏目为准。</x:v>
       </x:c>
       <x:c r="O103" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA4Njk5ODI5NQ==&amp;mid=2651694598&amp;idx=1&amp;sn=66575f3946dcae16a875013bd78f0f81</x:v>
       </x:c>
       <x:c r="P103" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q103" s="4" t="str">
+        <x:v>B-公开招聘公告</x:v>
+      </x:c>
+      <x:c r="Q103" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="104" ht="54" customHeight="1">
+    <x:row r="104" ht="66" customHeight="1">
       <x:c r="A104" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-24</x:v>
       </x:c>
       <x:c r="B104" s="4" t="str">
-        <x:v>北京国望光学科技有限公司</x:v>
+        <x:v>中国航天科工集团</x:v>
       </x:c>
       <x:c r="C104" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="D104" s="4" t="str">
-        <x:v>央国企</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E104" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>北京、南京、武汉、成都、西安等各院所</x:v>
       </x:c>
       <x:c r="F104" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批/提前批</x:v>
       </x:c>
       <x:c r="G104" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H104" s="4" t="str">
-        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
+        <x:v>控制、电子、通信、计算机、机械、材料、能源及管理</x:v>
       </x:c>
       <x:c r="I104" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/index.html</x:v>
       </x:c>
       <x:c r="J104" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K104" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>各单位自行组织，未统一</x:v>
       </x:c>
       <x:c r="L104" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>官网公告已确认启动</x:v>
       </x:c>
       <x:c r="M104" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N104" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>各二级单位独立招聘；学历、政审、保密要求和截止时间按具体岗位执行。</x:v>
       </x:c>
       <x:c r="O104" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>http://www.casic.com.cn/n27219851/n27219940/c31882489/content.html</x:v>
       </x:c>
       <x:c r="P104" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q104" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" ht="54" customHeight="1">
+        <x:v>A-集团官网公告已核验</x:v>
+      </x:c>
+      <x:c r="Q104" s="36" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" ht="66" customHeight="1">
       <x:c r="A105" s="4" t="str">
-        <x:v>2026-06-17</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="B105" s="4" t="str">
-        <x:v>乐读</x:v>
+        <x:v>禾赛科技</x:v>
       </x:c>
       <x:c r="C105" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>激光雷达/机器人</x:v>
       </x:c>
       <x:c r="D105" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E105" s="4" t="str">
-        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
+        <x:v>上海、杭州</x:v>
       </x:c>
       <x:c r="F105" s="4" t="str">
         <x:v>提前批</x:v>
@@ -6018,66 +6031,66 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H105" s="4" t="str">
-        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
+        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
       </x:c>
       <x:c r="I105" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
       </x:c>
       <x:c r="J105" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="K105" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L105" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M105" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N105" s="4" t="str">
-        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O105" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P105" s="14" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
-      </x:c>
-      <x:c r="Q105" s="4" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q105" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="106" ht="54" customHeight="1">
+    <x:row r="106" ht="66" customHeight="1">
       <x:c r="A106" s="4" t="str">
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B106" s="4" t="str">
-        <x:v>龙蟠科技</x:v>
+        <x:v>北京国望光学科技有限公司</x:v>
       </x:c>
       <x:c r="C106" s="4" t="str">
-        <x:v>新能源材料/化工</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D106" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>央国企</x:v>
       </x:c>
       <x:c r="E106" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F106" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G106" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H106" s="4" t="str">
-        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
+        <x:v>机械机电、光学光电、制造、环境控制、电子电气、软件算法、集成工艺</x:v>
       </x:c>
       <x:c r="I106" s="15" t="str">
-        <x:v>https://www.lopal.com.cn/join</x:v>
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J106" s="4" t="str">
-        <x:v>2027-06-01</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K106" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -6086,7 +6099,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M106" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N106" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -6097,25 +6110,25 @@
       <x:c r="P106" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q106" s="4" t="str">
+      <x:c r="Q106" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="107" ht="54" customHeight="1">
+    <x:row r="107" ht="66" customHeight="1">
       <x:c r="A107" s="4" t="str">
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B107" s="4" t="str">
-        <x:v>牧原</x:v>
+        <x:v>乐读</x:v>
       </x:c>
       <x:c r="C107" s="4" t="str">
-        <x:v>农业/食品/智能养殖</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D107" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E107" s="4" t="str">
-        <x:v>河南南阳及全国</x:v>
+        <x:v>西安、重庆、沈阳、成都、武汉、北京、上海、广州、深圳、南京、杭州、天津</x:v>
       </x:c>
       <x:c r="F107" s="4" t="str">
         <x:v>提前批</x:v>
@@ -6124,10 +6137,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H107" s="4" t="str">
-        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
+        <x:v>专职授课教师、业务+授课、高端竞赛教练</x:v>
       </x:c>
       <x:c r="I107" s="15" t="str">
-        <x:v>https://job.muyuanfoods.com/</x:v>
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J107" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6136,54 +6149,54 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L107" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M107" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N107" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>官方投递多通过公众号/公告二维码；投前确认城市是否仍开岗。</x:v>
       </x:c>
       <x:c r="O107" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P107" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q107" s="4" t="str">
+        <x:v>B-招聘平台公开汇总</x:v>
+      </x:c>
+      <x:c r="Q107" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="108" ht="54" customHeight="1">
+    <x:row r="108" ht="66" customHeight="1">
       <x:c r="A108" s="4" t="str">
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B108" s="4" t="str">
-        <x:v>三一集团-小语种校招</x:v>
+        <x:v>龙蟠科技</x:v>
       </x:c>
       <x:c r="C108" s="4" t="str">
-        <x:v>工程机械/制造</x:v>
+        <x:v>新能源材料/化工</x:v>
       </x:c>
       <x:c r="D108" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E108" s="4" t="str">
-        <x:v>海外多国</x:v>
+        <x:v>南京</x:v>
       </x:c>
       <x:c r="F108" s="4" t="str">
-        <x:v>小语种专项/正式批</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G108" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H108" s="4" t="str">
-        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
+        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
       </x:c>
       <x:c r="I108" s="15" t="str">
-        <x:v>https://sanycampus.zhiye.com/</x:v>
+        <x:v>https://www.lopal.com.cn/join</x:v>
       </x:c>
       <x:c r="J108" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2027-06-01</x:v>
       </x:c>
       <x:c r="K108" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -6192,7 +6205,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M108" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N108" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -6203,37 +6216,37 @@
       <x:c r="P108" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q108" s="4" t="str">
+      <x:c r="Q108" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="109" ht="54" customHeight="1">
+    <x:row r="109" ht="66" customHeight="1">
       <x:c r="A109" s="4" t="str">
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B109" s="4" t="str">
-        <x:v>上海电气-暑期精英训练营</x:v>
+        <x:v>牧原</x:v>
       </x:c>
       <x:c r="C109" s="4" t="str">
-        <x:v>高端装备/能源</x:v>
+        <x:v>农业/食品/智能养殖</x:v>
       </x:c>
       <x:c r="D109" s="4" t="str">
-        <x:v>地方国企</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E109" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>河南南阳及全国</x:v>
       </x:c>
       <x:c r="F109" s="4" t="str">
-        <x:v>训练营/秋招直通</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G109" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H109" s="4" t="str">
-        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
+        <x:v>智能技术、职能、养殖、屠宰、饲料</x:v>
       </x:c>
       <x:c r="I109" s="15" t="str">
-        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
+        <x:v>https://job.muyuanfoods.com/</x:v>
       </x:c>
       <x:c r="J109" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6256,37 +6269,37 @@
       <x:c r="P109" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q109" s="4" t="str">
+      <x:c r="Q109" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="110" ht="54" customHeight="1">
+    <x:row r="110" ht="66" customHeight="1">
       <x:c r="A110" s="4" t="str">
         <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B110" s="4" t="str">
-        <x:v>vivo-蓝极星计划</x:v>
+        <x:v>三一集团-小语种校招</x:v>
       </x:c>
       <x:c r="C110" s="4" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>工程机械/制造</x:v>
       </x:c>
       <x:c r="D110" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E110" s="4" t="str">
-        <x:v>深圳、杭州、东莞、上海</x:v>
+        <x:v>海外多国</x:v>
       </x:c>
       <x:c r="F110" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>小语种专项/正式批</x:v>
       </x:c>
       <x:c r="G110" s="4" t="str">
-        <x:v>博士为主</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H110" s="4" t="str">
-        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
+        <x:v>国际服务、国际营销、配件、物流、财务、人力、行政运营</x:v>
       </x:c>
       <x:c r="I110" s="15" t="str">
-        <x:v>https://hr.vivo.com/</x:v>
+        <x:v>https://sanycampus.zhiye.com/</x:v>
       </x:c>
       <x:c r="J110" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6295,51 +6308,51 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L110" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M110" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N110" s="4" t="str">
-        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O110" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P110" s="14" t="str">
-        <x:v>B-招聘平台公开汇总</x:v>
-      </x:c>
-      <x:c r="Q110" s="4" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q110" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="111" ht="54" customHeight="1">
+    <x:row r="111" ht="66" customHeight="1">
       <x:c r="A111" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B111" s="4" t="str">
-        <x:v>澜起科技</x:v>
+        <x:v>上海电气-暑期精英训练营</x:v>
       </x:c>
       <x:c r="C111" s="4" t="str">
-        <x:v>半导体/IC设计</x:v>
+        <x:v>高端装备/能源</x:v>
       </x:c>
       <x:c r="D111" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>地方国企</x:v>
       </x:c>
       <x:c r="E111" s="4" t="str">
-        <x:v>昆山、西安、南京</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F111" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>训练营/秋招直通</x:v>
       </x:c>
       <x:c r="G111" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H111" s="4" t="str">
-        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
+        <x:v>能源、机械、电气、自动化、计算机、材料、数理化、AI</x:v>
       </x:c>
       <x:c r="I111" s="15" t="str">
-        <x:v>https://www.montage-tech.com/cn/careers</x:v>
+        <x:v>https://www.shanghai-electric.com/group/c/197/</x:v>
       </x:c>
       <x:c r="J111" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6362,37 +6375,37 @@
       <x:c r="P111" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q111" s="4" t="str">
+      <x:c r="Q111" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="112" ht="54" customHeight="1">
+    <x:row r="112" ht="66" customHeight="1">
       <x:c r="A112" s="4" t="str">
-        <x:v>2026-06-16</x:v>
+        <x:v>2026-06-17</x:v>
       </x:c>
       <x:c r="B112" s="4" t="str">
-        <x:v>上海宇量昇</x:v>
+        <x:v>vivo-蓝极星计划</x:v>
       </x:c>
       <x:c r="C112" s="4" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="D112" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E112" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>深圳、杭州、东莞、上海</x:v>
       </x:c>
       <x:c r="F112" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G112" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>博士为主</x:v>
       </x:c>
       <x:c r="H112" s="4" t="str">
-        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
+        <x:v>影像与计算机视觉、AI与大模型、具身智能、系统软件与嵌入式、核心器件</x:v>
       </x:c>
       <x:c r="I112" s="15" t="str">
-        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
+        <x:v>https://hr.vivo.com/</x:v>
       </x:c>
       <x:c r="J112" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6401,39 +6414,39 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L112" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M112" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N112" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>蓝极星为顶尖博士专项；普通校招需另行关注。</x:v>
       </x:c>
       <x:c r="O112" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P112" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q112" s="4" t="str">
+        <x:v>B-招聘平台公开汇总</x:v>
+      </x:c>
+      <x:c r="Q112" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="113" ht="54" customHeight="1">
+    <x:row r="113" ht="66" customHeight="1">
       <x:c r="A113" s="4" t="str">
         <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B113" s="4" t="str">
-        <x:v>是为科技</x:v>
+        <x:v>澜起科技</x:v>
       </x:c>
       <x:c r="C113" s="4" t="str">
-        <x:v>新能源/智能制造</x:v>
+        <x:v>半导体/IC设计</x:v>
       </x:c>
       <x:c r="D113" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E113" s="4" t="str">
-        <x:v>南京、上海、常州</x:v>
+        <x:v>昆山、西安、南京</x:v>
       </x:c>
       <x:c r="F113" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6442,10 +6455,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H113" s="4" t="str">
-        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
+        <x:v>模拟设计、数字设计、数字验证、产品工程师</x:v>
       </x:c>
       <x:c r="I113" s="15" t="str">
-        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
+        <x:v>https://www.montage-tech.com/cn/careers</x:v>
       </x:c>
       <x:c r="J113" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6468,22 +6481,22 @@
       <x:c r="P113" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q113" s="4" t="str">
+      <x:c r="Q113" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="114" ht="54" customHeight="1">
+    <x:row r="114" ht="66" customHeight="1">
       <x:c r="A114" s="4" t="str">
         <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B114" s="4" t="str">
-        <x:v>游族网络</x:v>
+        <x:v>上海宇量昇</x:v>
       </x:c>
       <x:c r="C114" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="D114" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E114" s="4" t="str">
         <x:v>上海</x:v>
@@ -6495,10 +6508,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H114" s="4" t="str">
-        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
+        <x:v>光学光电、机械机电、软件算法、电子电气、环境控制、集成工艺与材料、制造、职能</x:v>
       </x:c>
       <x:c r="I114" s="15" t="str">
-        <x:v>https://job.youzu.com/</x:v>
+        <x:v>https://wecruit.hotjob.cn/SU63847447bef57c649c3505b5/mc/position/campus</x:v>
       </x:c>
       <x:c r="J114" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6521,25 +6534,25 @@
       <x:c r="P114" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q114" s="4" t="str">
+      <x:c r="Q114" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="115" ht="54" customHeight="1">
+    <x:row r="115" ht="66" customHeight="1">
       <x:c r="A115" s="4" t="str">
-        <x:v>2026-06-15</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B115" s="4" t="str">
-        <x:v>中铁设计</x:v>
+        <x:v>是为科技</x:v>
       </x:c>
       <x:c r="C115" s="4" t="str">
-        <x:v>轨道交通/工程设计</x:v>
+        <x:v>新能源/智能制造</x:v>
       </x:c>
       <x:c r="D115" s="4" t="str">
-        <x:v>央企</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E115" s="4" t="str">
-        <x:v>北京、济南、郑州、太原</x:v>
+        <x:v>南京、上海、常州</x:v>
       </x:c>
       <x:c r="F115" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6548,10 +6561,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H115" s="4" t="str">
-        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
+        <x:v>硬件、软件、EMC、结构、工艺设备、管培、物流计划、质量、采购、项目运营</x:v>
       </x:c>
       <x:c r="I115" s="15" t="str">
-        <x:v>https://www.crdc.com/</x:v>
+        <x:v>https://www.soarwhale.com/Home/JobList</x:v>
       </x:c>
       <x:c r="J115" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6574,37 +6587,37 @@
       <x:c r="P115" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q115" s="4" t="str">
+      <x:c r="Q115" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="116" ht="54" customHeight="1">
+    <x:row r="116" ht="66" customHeight="1">
       <x:c r="A116" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-16</x:v>
       </x:c>
       <x:c r="B116" s="4" t="str">
-        <x:v>迈安德集团-校园大使</x:v>
+        <x:v>游族网络</x:v>
       </x:c>
       <x:c r="C116" s="4" t="str">
-        <x:v>粮油工程/装备</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D116" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E116" s="4" t="str">
-        <x:v>扬州/高校</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F116" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G116" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H116" s="4" t="str">
-        <x:v>校园大使</x:v>
+        <x:v>产品策划、程序技术、美术表现、发行运营</x:v>
       </x:c>
       <x:c r="I116" s="15" t="str">
-        <x:v>https://www.myande.com/</x:v>
+        <x:v>https://job.youzu.com/</x:v>
       </x:c>
       <x:c r="J116" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6627,25 +6640,25 @@
       <x:c r="P116" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q116" s="4" t="str">
+      <x:c r="Q116" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="117" ht="54" customHeight="1">
+    <x:row r="117" ht="66" customHeight="1">
       <x:c r="A117" s="4" t="str">
-        <x:v>2026-06-13</x:v>
+        <x:v>2026-06-15</x:v>
       </x:c>
       <x:c r="B117" s="4" t="str">
-        <x:v>迅仿科技</x:v>
+        <x:v>中铁设计</x:v>
       </x:c>
       <x:c r="C117" s="4" t="str">
-        <x:v>工业软件/仿真</x:v>
+        <x:v>轨道交通/工程设计</x:v>
       </x:c>
       <x:c r="D117" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>央企</x:v>
       </x:c>
       <x:c r="E117" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京、济南、郑州、太原</x:v>
       </x:c>
       <x:c r="F117" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6654,10 +6667,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H117" s="4" t="str">
-        <x:v>仿真工程师</x:v>
+        <x:v>交通运输、测绘、土木建筑、电气通信、机械、工程管理</x:v>
       </x:c>
       <x:c r="I117" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>https://www.crdc.com/</x:v>
       </x:c>
       <x:c r="J117" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6680,40 +6693,40 @@
       <x:c r="P117" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q117" s="4" t="str">
+      <x:c r="Q117" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="118" ht="54" customHeight="1">
+    <x:row r="118" ht="66" customHeight="1">
       <x:c r="A118" s="4" t="str">
-        <x:v>2026-06-12</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B118" s="4" t="str">
-        <x:v>MOVA</x:v>
+        <x:v>迈安德集团-校园大使</x:v>
       </x:c>
       <x:c r="C118" s="4" t="str">
-        <x:v>智能家电/机器人</x:v>
+        <x:v>粮油工程/装备</x:v>
       </x:c>
       <x:c r="D118" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E118" s="4" t="str">
-        <x:v>苏州及全国</x:v>
+        <x:v>扬州/高校</x:v>
       </x:c>
       <x:c r="F118" s="4" t="str">
-        <x:v>全球校招/正式批</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G118" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H118" s="4" t="str">
-        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+        <x:v>校园大使</x:v>
       </x:c>
       <x:c r="I118" s="15" t="str">
-        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+        <x:v>https://www.myande.com/</x:v>
       </x:c>
       <x:c r="J118" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K118" s="4" t="str">
         <x:v>官方未说明</x:v>
@@ -6722,7 +6735,7 @@
         <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M118" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N118" s="4" t="str">
         <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
@@ -6733,25 +6746,25 @@
       <x:c r="P118" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q118" s="4" t="str">
+      <x:c r="Q118" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="119" ht="54" customHeight="1">
+    <x:row r="119" ht="66" customHeight="1">
       <x:c r="A119" s="4" t="str">
-        <x:v>2026-06-11</x:v>
+        <x:v>2026-06-13</x:v>
       </x:c>
       <x:c r="B119" s="4" t="str">
-        <x:v>财通证券</x:v>
+        <x:v>迅仿科技</x:v>
       </x:c>
       <x:c r="C119" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>工业软件/仿真</x:v>
       </x:c>
       <x:c r="D119" s="4" t="str">
-        <x:v>国企/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E119" s="4" t="str">
-        <x:v>杭州、上海、深圳、北京</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F119" s="4" t="str">
         <x:v>正式批</x:v>
@@ -6760,10 +6773,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H119" s="4" t="str">
-        <x:v>总部、参股公司、分公司岗位</x:v>
+        <x:v>仿真工程师</x:v>
       </x:c>
       <x:c r="I119" s="15" t="str">
-        <x:v>https://www.ctsec.com/joinUs</x:v>
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J119" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6786,90 +6799,90 @@
       <x:c r="P119" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q119" s="4" t="str">
+      <x:c r="Q119" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="120" ht="54" customHeight="1">
+    <x:row r="120" ht="66" customHeight="1">
       <x:c r="A120" s="4" t="str">
-        <x:v>不晚于2026-06-11</x:v>
+        <x:v>2026-06-12</x:v>
       </x:c>
       <x:c r="B120" s="4" t="str">
-        <x:v>美团-北斗计划及2027校园招聘</x:v>
+        <x:v>MOVA</x:v>
       </x:c>
       <x:c r="C120" s="4" t="str">
-        <x:v>互联网/本地生活/AI</x:v>
+        <x:v>智能家电/机器人</x:v>
       </x:c>
       <x:c r="D120" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E120" s="4" t="str">
-        <x:v>北京、上海、深圳、成都、广州、武汉、杭州、西安等</x:v>
+        <x:v>苏州及全国</x:v>
       </x:c>
       <x:c r="F120" s="4" t="str">
-        <x:v>顶尖人才专项/正式校园招聘</x:v>
+        <x:v>全球校招/正式批</x:v>
       </x:c>
       <x:c r="G120" s="4" t="str">
-        <x:v>应届毕业生，以具体岗位毕业时间要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H120" s="4" t="str">
-        <x:v>北斗计划覆盖大模型、自动驾驶、无人机、机器人和AI Infra等；官方校园职位页当前显示68个岗位</x:v>
+        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
       </x:c>
       <x:c r="I120" s="15" t="str">
-        <x:v>https://zhaopin.meituan.com/web/position?hiringType=1_1</x:v>
+        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
       </x:c>
       <x:c r="J120" s="4" t="str">
-        <x:v>未公布/招满即止</x:v>
+        <x:v>2026-11-30</x:v>
       </x:c>
       <x:c r="K120" s="4" t="str">
-        <x:v>按岗位，官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L120" s="4" t="str">
-        <x:v>本轮新增；美团官方校园招聘职位页及北斗计划入口均显示开放</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M120" s="4" t="str">
-        <x:v>P1-招满即止/截止未公布</x:v>
+        <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N120" s="4" t="str">
-        <x:v>北斗计划为面向顶尖技术人才的专项，普通校园招聘岗位可在同一官方职位页按“应届生”筛选；不同专项的投递规则可能独立。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O120" s="15" t="str">
-        <x:v>https://zhaopin.meituan.com/web/beidouprogram</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P120" s="16" t="str">
-        <x:v>A-企业官方校园招聘职位页已核验</x:v>
-      </x:c>
-      <x:c r="Q120" s="4" t="str">
-        <x:v>2026-08-10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" ht="54" customHeight="1">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q120" s="36" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" ht="66" customHeight="1">
       <x:c r="A121" s="4" t="str">
-        <x:v>2026-06-10</x:v>
+        <x:v>2026-06-11</x:v>
       </x:c>
       <x:c r="B121" s="4" t="str">
-        <x:v>歌尔股份</x:v>
+        <x:v>财通证券</x:v>
       </x:c>
       <x:c r="C121" s="4" t="str">
-        <x:v>消费电子/智能硬件</x:v>
+        <x:v>证券/金融</x:v>
       </x:c>
       <x:c r="D121" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>国企/上市</x:v>
       </x:c>
       <x:c r="E121" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>杭州、上海、深圳、北京</x:v>
       </x:c>
       <x:c r="F121" s="4" t="str">
-        <x:v>实习/校招储备</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G121" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H121" s="4" t="str">
-        <x:v>法务助理</x:v>
+        <x:v>总部、参股公司、分公司岗位</x:v>
       </x:c>
       <x:c r="I121" s="15" t="str">
-        <x:v>https://career.goertek.com/</x:v>
+        <x:v>https://www.ctsec.com/joinUs</x:v>
       </x:c>
       <x:c r="J121" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6892,90 +6905,90 @@
       <x:c r="P121" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q121" s="4" t="str">
+      <x:c r="Q121" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="122" ht="54" customHeight="1">
+    <x:row r="122" ht="66" customHeight="1">
       <x:c r="A122" s="4" t="str">
-        <x:v>2026-06-09</x:v>
+        <x:v>不晚于2026-06-11</x:v>
       </x:c>
       <x:c r="B122" s="4" t="str">
-        <x:v>深信服-校园大使</x:v>
+        <x:v>美团-北斗计划及2027校园招聘</x:v>
       </x:c>
       <x:c r="C122" s="4" t="str">
-        <x:v>网络安全/云计算</x:v>
+        <x:v>互联网/本地生活/AI</x:v>
       </x:c>
       <x:c r="D122" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E122" s="4" t="str">
-        <x:v>西安</x:v>
+        <x:v>北京、上海、深圳、成都、广州、武汉、杭州、西安等</x:v>
       </x:c>
       <x:c r="F122" s="4" t="str">
-        <x:v>校园大使/非正式全职</x:v>
+        <x:v>顶尖人才专项/正式校园招聘</x:v>
       </x:c>
       <x:c r="G122" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>应届毕业生，以具体岗位毕业时间要求为准</x:v>
       </x:c>
       <x:c r="H122" s="4" t="str">
-        <x:v>校园大使</x:v>
+        <x:v>北斗计划覆盖大模型、自动驾驶、无人机、机器人和AI Infra等；官方校园职位页当前显示68个岗位</x:v>
       </x:c>
       <x:c r="I122" s="15" t="str">
-        <x:v>https://hr.sangfor.com/</x:v>
+        <x:v>https://zhaopin.meituan.com/web/position?hiringType=1_1</x:v>
       </x:c>
       <x:c r="J122" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
       </x:c>
       <x:c r="K122" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L122" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>本轮新增；美团官方校园招聘职位页及北斗计划入口均显示开放</x:v>
       </x:c>
       <x:c r="M122" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N122" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>北斗计划为面向顶尖技术人才的专项，普通校园招聘岗位可在同一官方职位页按“应届生”筛选；不同专项的投递规则可能独立。</x:v>
       </x:c>
       <x:c r="O122" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://zhaopin.meituan.com/web/beidouprogram</x:v>
       </x:c>
       <x:c r="P122" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q122" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" ht="54" customHeight="1">
+        <x:v>A-企业官方校园招聘职位页已核验</x:v>
+      </x:c>
+      <x:c r="Q122" s="36" t="str">
+        <x:v>2026-08-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" ht="66" customHeight="1">
       <x:c r="A123" s="4" t="str">
-        <x:v>2026-06-08</x:v>
+        <x:v>2026-06-10</x:v>
       </x:c>
       <x:c r="B123" s="4" t="str">
-        <x:v>晓禾教育</x:v>
+        <x:v>歌尔股份</x:v>
       </x:c>
       <x:c r="C123" s="4" t="str">
-        <x:v>教育</x:v>
+        <x:v>消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D123" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E123" s="4" t="str">
-        <x:v>武汉、郑州、襄阳、宜昌</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F123" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>实习/校招储备</x:v>
       </x:c>
       <x:c r="G123" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H123" s="4" t="str">
-        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
+        <x:v>法务助理</x:v>
       </x:c>
       <x:c r="I123" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>https://career.goertek.com/</x:v>
       </x:c>
       <x:c r="J123" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -6998,37 +7011,37 @@
       <x:c r="P123" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q123" s="4" t="str">
+      <x:c r="Q123" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="124" ht="54" customHeight="1">
+    <x:row r="124" ht="66" customHeight="1">
       <x:c r="A124" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-09</x:v>
       </x:c>
       <x:c r="B124" s="4" t="str">
-        <x:v>晖致医药</x:v>
+        <x:v>深信服-校园大使</x:v>
       </x:c>
       <x:c r="C124" s="4" t="str">
-        <x:v>医药</x:v>
+        <x:v>网络安全/云计算</x:v>
       </x:c>
       <x:c r="D124" s="4" t="str">
-        <x:v>外资</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E124" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>西安</x:v>
       </x:c>
       <x:c r="F124" s="4" t="str">
-        <x:v>实习储备正式岗</x:v>
+        <x:v>校园大使/非正式全职</x:v>
       </x:c>
       <x:c r="G124" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H124" s="4" t="str">
-        <x:v>医学信息沟通实习生</x:v>
+        <x:v>校园大使</x:v>
       </x:c>
       <x:c r="I124" s="15" t="str">
-        <x:v>https://careers.viatris.com/</x:v>
+        <x:v>https://hr.sangfor.com/</x:v>
       </x:c>
       <x:c r="J124" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7051,25 +7064,25 @@
       <x:c r="P124" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q124" s="4" t="str">
+      <x:c r="Q124" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="125" ht="54" customHeight="1">
+    <x:row r="125" ht="66" customHeight="1">
       <x:c r="A125" s="4" t="str">
-        <x:v>2026-06-04</x:v>
+        <x:v>2026-06-08</x:v>
       </x:c>
       <x:c r="B125" s="4" t="str">
-        <x:v>苏州鸿凌达电子</x:v>
+        <x:v>晓禾教育</x:v>
       </x:c>
       <x:c r="C125" s="4" t="str">
-        <x:v>电子制造</x:v>
+        <x:v>教育</x:v>
       </x:c>
       <x:c r="D125" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E125" s="4" t="str">
-        <x:v>苏州</x:v>
+        <x:v>武汉、郑州、襄阳、宜昌</x:v>
       </x:c>
       <x:c r="F125" s="4" t="str">
         <x:v>正式批</x:v>
@@ -7078,10 +7091,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H125" s="4" t="str">
-        <x:v>财务助理</x:v>
+        <x:v>小初英语教师、竞赛教练、高中数理化教师</x:v>
       </x:c>
       <x:c r="I125" s="15" t="str">
-        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J125" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7104,37 +7117,37 @@
       <x:c r="P125" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q125" s="4" t="str">
+      <x:c r="Q125" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="126" ht="54" customHeight="1">
+    <x:row r="126" ht="66" customHeight="1">
       <x:c r="A126" s="4" t="str">
-        <x:v>2026-06-02</x:v>
+        <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="B126" s="4" t="str">
-        <x:v>万得信息</x:v>
+        <x:v>晖致医药</x:v>
       </x:c>
       <x:c r="C126" s="4" t="str">
-        <x:v>金融数据/软件</x:v>
+        <x:v>医药</x:v>
       </x:c>
       <x:c r="D126" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>外资</x:v>
       </x:c>
       <x:c r="E126" s="4" t="str">
         <x:v>上海</x:v>
       </x:c>
       <x:c r="F126" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>实习储备正式岗</x:v>
       </x:c>
       <x:c r="G126" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H126" s="4" t="str">
-        <x:v>AI算法工程师等</x:v>
+        <x:v>医学信息沟通实习生</x:v>
       </x:c>
       <x:c r="I126" s="15" t="str">
-        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
+        <x:v>https://careers.viatris.com/</x:v>
       </x:c>
       <x:c r="J126" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7157,37 +7170,37 @@
       <x:c r="P126" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q126" s="4" t="str">
+      <x:c r="Q126" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="127" ht="54" customHeight="1">
+    <x:row r="127" ht="66" customHeight="1">
       <x:c r="A127" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-04</x:v>
       </x:c>
       <x:c r="B127" s="4" t="str">
-        <x:v>淘大集供应链</x:v>
+        <x:v>苏州鸿凌达电子</x:v>
       </x:c>
       <x:c r="C127" s="4" t="str">
-        <x:v>零售/供应链</x:v>
+        <x:v>电子制造</x:v>
       </x:c>
       <x:c r="D127" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E127" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>苏州</x:v>
       </x:c>
       <x:c r="F127" s="4" t="str">
-        <x:v>管培/实习</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G127" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H127" s="4" t="str">
-        <x:v>巡店管培生、实习生</x:v>
+        <x:v>财务助理</x:v>
       </x:c>
       <x:c r="I127" s="23" t="str">
-        <x:v>官方入口待核验</x:v>
+        <x:v>http://en.szkanronics.com/list/?171_1.html</x:v>
       </x:c>
       <x:c r="J127" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7210,37 +7223,37 @@
       <x:c r="P127" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q127" s="4" t="str">
+      <x:c r="Q127" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="128" ht="54" customHeight="1">
+    <x:row r="128" ht="66" customHeight="1">
       <x:c r="A128" s="4" t="str">
-        <x:v>2026-06-01</x:v>
+        <x:v>2026-06-02</x:v>
       </x:c>
       <x:c r="B128" s="4" t="str">
-        <x:v>友芝友实业集团</x:v>
+        <x:v>万得信息</x:v>
       </x:c>
       <x:c r="C128" s="4" t="str">
-        <x:v>综合实业</x:v>
+        <x:v>金融数据/软件</x:v>
       </x:c>
       <x:c r="D128" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E128" s="4" t="str">
-        <x:v>武汉</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F128" s="4" t="str">
-        <x:v>管培生</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G128" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H128" s="4" t="str">
-        <x:v>青年领军人才管培生</x:v>
+        <x:v>AI算法工程师等</x:v>
       </x:c>
       <x:c r="I128" s="15" t="str">
-        <x:v>https://www.yzyqh.com/jrwm</x:v>
+        <x:v>https://www.wind.com.cn/portal/zh/JoinUs/index.html</x:v>
       </x:c>
       <x:c r="J128" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7263,37 +7276,37 @@
       <x:c r="P128" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q128" s="4" t="str">
+      <x:c r="Q128" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="129" ht="54" customHeight="1">
+    <x:row r="129" ht="66" customHeight="1">
       <x:c r="A129" s="4" t="str">
-        <x:v>2026-05-29</x:v>
+        <x:v>2026-06-01</x:v>
       </x:c>
       <x:c r="B129" s="4" t="str">
-        <x:v>银雁科技</x:v>
+        <x:v>淘大集供应链</x:v>
       </x:c>
       <x:c r="C129" s="4" t="str">
-        <x:v>金融科技服务</x:v>
+        <x:v>零售/供应链</x:v>
       </x:c>
       <x:c r="D129" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E129" s="4" t="str">
-        <x:v>成都</x:v>
+        <x:v>武汉</x:v>
       </x:c>
       <x:c r="F129" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>管培/实习</x:v>
       </x:c>
       <x:c r="G129" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H129" s="4" t="str">
-        <x:v>人伤理赔</x:v>
+        <x:v>巡店管培生、实习生</x:v>
       </x:c>
       <x:c r="I129" s="15" t="str">
-        <x:v>https://www.cfss.net.cn/</x:v>
+        <x:v>官方入口待核验</x:v>
       </x:c>
       <x:c r="J129" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7316,37 +7329,37 @@
       <x:c r="P129" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q129" s="4" t="str">
+      <x:c r="Q129" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="130" ht="54" customHeight="1">
+    <x:row r="130" ht="66" customHeight="1">
       <x:c r="A130" s="4" t="str">
-        <x:v>不晚于2026-05-19</x:v>
+        <x:v>2026-06-01</x:v>
       </x:c>
       <x:c r="B130" s="4" t="str">
-        <x:v>宇树科技-2027校园招聘</x:v>
+        <x:v>友芝友实业集团</x:v>
       </x:c>
       <x:c r="C130" s="4" t="str">
-        <x:v>机器人/具身智能</x:v>
+        <x:v>综合实业</x:v>
       </x:c>
       <x:c r="D130" s="4" t="str">
-        <x:v>民营/科技企业</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E130" s="4" t="str">
-        <x:v>杭州</x:v>
+        <x:v>武汉</x:v>
       </x:c>
       <x:c r="F130" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>管培生</x:v>
       </x:c>
       <x:c r="G130" s="4" t="str">
-        <x:v>2027届应届生，以具体岗位要求为准</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H130" s="4" t="str">
-        <x:v>算法、嵌入式、软件、硬件、机械、SLAM、C++、AI、数据、前端、测试、销售、技术支持及设计等</x:v>
+        <x:v>青年领军人才管培生</x:v>
       </x:c>
       <x:c r="I130" s="15" t="str">
-        <x:v>https://www.unitree.com/cn/position</x:v>
+        <x:v>https://www.yzyqh.com/jrwm</x:v>
       </x:c>
       <x:c r="J130" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7355,39 +7368,39 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L130" s="4" t="str">
-        <x:v>本轮新增；宇树科技官方招贤纳士页面当前显示多项热招岗位</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M130" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N130" s="4" t="str">
-        <x:v>官方岗位页当前显示杭州技术类与销售类多个热招职位；校园招聘公告由高校就业平台发布，投递以宇树官网职位详情为准。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O130" s="15" t="str">
-        <x:v>https://www.unitree.com/cn/position</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P130" s="16" t="str">
-        <x:v>A-企业官方招贤纳士页面已核验</x:v>
-      </x:c>
-      <x:c r="Q130" s="4" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" ht="54" customHeight="1">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q130" s="36" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" ht="66" customHeight="1">
       <x:c r="A131" s="4" t="str">
-        <x:v>2026-05-15</x:v>
+        <x:v>2026-05-29</x:v>
       </x:c>
       <x:c r="B131" s="4" t="str">
-        <x:v>知乎</x:v>
+        <x:v>银雁科技</x:v>
       </x:c>
       <x:c r="C131" s="4" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>金融科技服务</x:v>
       </x:c>
       <x:c r="D131" s="4" t="str">
         <x:v>民营</x:v>
       </x:c>
       <x:c r="E131" s="4" t="str">
-        <x:v>北京</x:v>
+        <x:v>成都</x:v>
       </x:c>
       <x:c r="F131" s="4" t="str">
         <x:v>正式批</x:v>
@@ -7396,10 +7409,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H131" s="4" t="str">
-        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
+        <x:v>人伤理赔</x:v>
       </x:c>
       <x:c r="I131" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
+        <x:v>https://www.cfss.net.cn/</x:v>
       </x:c>
       <x:c r="J131" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7422,37 +7435,37 @@
       <x:c r="P131" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q131" s="4" t="str">
+      <x:c r="Q131" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="132" ht="54" customHeight="1">
+    <x:row r="132" ht="66" customHeight="1">
       <x:c r="A132" s="4" t="str">
-        <x:v>2026-05-08</x:v>
+        <x:v>不晚于2026-05-19</x:v>
       </x:c>
       <x:c r="B132" s="4" t="str">
-        <x:v>招商银行长沙分行</x:v>
+        <x:v>宇树科技-2027校园招聘</x:v>
       </x:c>
       <x:c r="C132" s="4" t="str">
-        <x:v>银行/金融</x:v>
+        <x:v>机器人/具身智能</x:v>
       </x:c>
       <x:c r="D132" s="4" t="str">
-        <x:v>股份制银行</x:v>
+        <x:v>民营/科技企业</x:v>
       </x:c>
       <x:c r="E132" s="4" t="str">
-        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+        <x:v>杭州</x:v>
       </x:c>
       <x:c r="F132" s="4" t="str">
-        <x:v>暑期实习/秋招直通</x:v>
+        <x:v>正式批/校园招聘</x:v>
       </x:c>
       <x:c r="G132" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届应届生，以具体岗位要求为准</x:v>
       </x:c>
       <x:c r="H132" s="4" t="str">
-        <x:v>2027暑期实习生</x:v>
+        <x:v>算法、嵌入式、软件、硬件、机械、SLAM、C++、AI、数据、前端、测试、销售、技术支持及设计等</x:v>
       </x:c>
       <x:c r="I132" s="15" t="str">
-        <x:v>https://career.cmbchina.com/</x:v>
+        <x:v>https://www.unitree.com/cn/position</x:v>
       </x:c>
       <x:c r="J132" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7461,39 +7474,39 @@
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L132" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>本轮新增；宇树科技官方招贤纳士页面当前显示多项热招岗位</x:v>
       </x:c>
       <x:c r="M132" s="4" t="str">
         <x:v>P1-招满即止/截止未公布</x:v>
       </x:c>
       <x:c r="N132" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>官方岗位页当前显示杭州技术类与销售类多个热招职位；校园招聘公告由高校就业平台发布，投递以宇树官网职位详情为准。</x:v>
       </x:c>
       <x:c r="O132" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://www.unitree.com/cn/position</x:v>
       </x:c>
       <x:c r="P132" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q132" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" ht="54" customHeight="1">
+        <x:v>A-企业官方招贤纳士页面已核验</x:v>
+      </x:c>
+      <x:c r="Q132" s="36" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" ht="66" customHeight="1">
       <x:c r="A133" s="4" t="str">
-        <x:v>2026-04-22</x:v>
+        <x:v>2026-05-15</x:v>
       </x:c>
       <x:c r="B133" s="4" t="str">
-        <x:v>华金证券</x:v>
+        <x:v>知乎</x:v>
       </x:c>
       <x:c r="C133" s="4" t="str">
-        <x:v>证券/金融</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="D133" s="4" t="str">
-        <x:v>国企</x:v>
+        <x:v>民营</x:v>
       </x:c>
       <x:c r="E133" s="4" t="str">
-        <x:v>上海</x:v>
+        <x:v>北京</x:v>
       </x:c>
       <x:c r="F133" s="4" t="str">
         <x:v>正式批</x:v>
@@ -7502,10 +7515,10 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H133" s="4" t="str">
-        <x:v>战略发展类</x:v>
+        <x:v>技术研发、算法/数据科学、产品运营、市场商务</x:v>
       </x:c>
       <x:c r="I133" s="15" t="str">
-        <x:v>https://www.huajinsc.cn/</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/zhihu/</x:v>
       </x:c>
       <x:c r="J133" s="4" t="str">
         <x:v>未公布/招满即止</x:v>
@@ -7528,7 +7541,113 @@
       <x:c r="P133" s="14" t="str">
         <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
       </x:c>
-      <x:c r="Q133" s="4" t="str">
+      <x:c r="Q133" s="36" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" ht="66" customHeight="1">
+      <x:c r="A134" t="str">
+        <x:v>2026-05-08</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>招商银行长沙分行</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>银行/金融</x:v>
+      </x:c>
+      <x:c r="D134" t="str">
+        <x:v>股份制银行</x:v>
+      </x:c>
+      <x:c r="E134" t="str">
+        <x:v>长沙、株洲、湘潭、衡阳、娄底</x:v>
+      </x:c>
+      <x:c r="F134" t="str">
+        <x:v>暑期实习/秋招直通</x:v>
+      </x:c>
+      <x:c r="G134" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H134" t="str">
+        <x:v>2027暑期实习生</x:v>
+      </x:c>
+      <x:c r="I134" t="str">
+        <x:v>https://career.cmbchina.com/</x:v>
+      </x:c>
+      <x:c r="J134" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K134" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L134" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M134" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N134" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O134" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P134" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q134" s="39" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" ht="66" customHeight="1">
+      <x:c r="A135" t="str">
+        <x:v>2026-04-22</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>华金证券</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>证券/金融</x:v>
+      </x:c>
+      <x:c r="D135" t="str">
+        <x:v>国企</x:v>
+      </x:c>
+      <x:c r="E135" t="str">
+        <x:v>上海</x:v>
+      </x:c>
+      <x:c r="F135" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G135" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H135" t="str">
+        <x:v>战略发展类</x:v>
+      </x:c>
+      <x:c r="I135" t="str">
+        <x:v>https://www.huajinsc.cn/</x:v>
+      </x:c>
+      <x:c r="J135" t="str">
+        <x:v>未公布/招满即止</x:v>
+      </x:c>
+      <x:c r="K135" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L135" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M135" t="str">
+        <x:v>P1-招满即止/截止未公布</x:v>
+      </x:c>
+      <x:c r="N135" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O135" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P135" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q135" s="39" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -7539,7 +7658,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbcb991abd75441ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7116c2ec4dbf471a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7569,7 +7688,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>近期有明确截止时间的项目（截至2026-08-11）</x:v>
+        <x:v>近期有明确截止时间的项目（截至2026-08-12）</x:v>
       </x:c>
       <x:c r="B1" s="7"/>
       <x:c r="C1" s="7"/>
@@ -7662,180 +7781,180 @@
         <x:v>核验日期</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="54" customHeight="1">
+    <x:row r="4" ht="66" customHeight="1">
       <x:c r="A4" s="14" t="str">
-        <x:v>2026-07-15</x:v>
+        <x:v>2026-07-06</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>蔚来</x:v>
+        <x:v>米哈游</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
-        <x:v>新能源汽车/智能汽车</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E4" s="14" t="str">
-        <x:v>上海、合肥、北京、武汉、南京等</x:v>
+        <x:v>上海、北京</x:v>
       </x:c>
       <x:c r="F4" s="14" t="str">
         <x:v>技术提前批</x:v>
       </x:c>
       <x:c r="G4" s="14" t="str">
-        <x:v>2024年9月-2027年8月毕业</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H4" s="14" t="str">
-        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
+        <x:v>程序与技术、质量管理、技术美术、技术策划</x:v>
       </x:c>
       <x:c r="I4" s="17" t="str">
-        <x:v>https://campus.nio.com/</x:v>
+        <x:v>https://campus.mihoyo.com/</x:v>
       </x:c>
       <x:c r="J4" s="14" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-07-27</x:v>
       </x:c>
       <x:c r="K4" s="14" t="str">
-        <x:v>否；有笔试/测评</x:v>
+        <x:v>有免笔试直通面试机会</x:v>
       </x:c>
       <x:c r="L4" s="14" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>已截止（公开截止日：2026-07-27；保留原来源）</x:v>
       </x:c>
       <x:c r="M4" s="14" t="str">
-        <x:v>P1-7天内截止</x:v>
+        <x:v>已截止</x:v>
       </x:c>
       <x:c r="N4" s="14" t="str">
-        <x:v>最多同时申请3个岗位。</x:v>
+        <x:v>整个秋招只能投1次、1岗；未获直通仍可能进入正式批再次评估。公开截止日已过，若官网重新开放岗位，以官网按钮状态为准。</x:v>
       </x:c>
       <x:c r="O4" s="17" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P4" s="16" t="str">
-        <x:v>A-官方来源公告已核验</x:v>
-      </x:c>
-      <x:c r="Q4" s="14" t="str">
-        <x:v>2026-08-11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="54" customHeight="1">
+        <x:v>A-官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q4" s="37" t="str">
+        <x:v>2026-07-30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="66" customHeight="1">
       <x:c r="A5" s="14" t="str">
-        <x:v>2026-07-02</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>京东方-先锋京英计划</x:v>
+        <x:v>恒丰银行总行-雏鹰计划</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>显示技术/半导体/物联网</x:v>
+        <x:v>银行/金融</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>未注明</x:v>
+        <x:v>股份制商业银行</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
-        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
+        <x:v>总行及相关机构，以岗位页为准</x:v>
       </x:c>
       <x:c r="F5" s="14" t="str">
-        <x:v>提前批</x:v>
+        <x:v>暑期实习/秋招储备</x:v>
       </x:c>
       <x:c r="G5" s="14" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届硕士及以上，以公告要求为准</x:v>
       </x:c>
       <x:c r="H5" s="14" t="str">
-        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
+        <x:v>总行实习生，具体专业和方向以官方公告为准</x:v>
       </x:c>
       <x:c r="I5" s="17" t="str">
-        <x:v>https://campus.boe.com/</x:v>
+        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
       </x:c>
       <x:c r="J5" s="14" t="str">
-        <x:v>2026-08-14</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
       <x:c r="K5" s="14" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L5" s="14" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
       </x:c>
       <x:c r="M5" s="14" t="str">
-        <x:v>P1-7天内截止</x:v>
+        <x:v>已截止</x:v>
       </x:c>
       <x:c r="N5" s="14" t="str">
-        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
+        <x:v>官方公告显示7月31日24:00截止，实习期安排和具体岗位以恒丰银行招聘官网为准。</x:v>
       </x:c>
       <x:c r="O5" s="17" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://career.hfbank.com.cn/zpgg/316289.shtml</x:v>
       </x:c>
       <x:c r="P5" s="16" t="str">
-        <x:v>A-国家大学生就业平台公告已核验</x:v>
-      </x:c>
-      <x:c r="Q5" s="14" t="str">
-        <x:v>2026-08-11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="54" customHeight="1">
+        <x:v>A-企业官方招聘公告已核验</x:v>
+      </x:c>
+      <x:c r="Q5" s="37" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="66" customHeight="1">
       <x:c r="A6" s="14" t="str">
+        <x:v>不晚于2026-07-30</x:v>
+      </x:c>
+      <x:c r="B6" s="14" t="str">
+        <x:v>天健会计师事务所-暑期实习培训生</x:v>
+      </x:c>
+      <x:c r="C6" s="14" t="str">
+        <x:v>会计审计/专业服务</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>会计师事务所</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>上海等，以职位页为准</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>暑期实习/培训生</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
+        <x:v>2027届应届毕业生，以岗位要求为准</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str">
+        <x:v>财务审计暑期实习培训生</x:v>
+      </x:c>
+      <x:c r="I6" s="17" t="str">
+        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
+      </x:c>
+      <x:c r="J6" s="14" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+      <x:c r="K6" s="14" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L6" s="14" t="str">
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
+      </x:c>
+      <x:c r="M6" s="14" t="str">
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N6" s="14" t="str">
+        <x:v>公开公告显示7月31日截止；具体办公地点、专业要求和实习安排以天健招聘官网为准。</x:v>
+      </x:c>
+      <x:c r="O6" s="17" t="str">
+        <x:v>https://zhaopin.pccpa.cn/hr/recruit/internship</x:v>
+      </x:c>
+      <x:c r="P6" s="16" t="str">
+        <x:v>A-企业官方招聘入口已核验</x:v>
+      </x:c>
+      <x:c r="Q6" s="37" t="str">
         <x:v>2026-08-03</x:v>
       </x:c>
-      <x:c r="B6" s="14" t="str">
-        <x:v>中泰证券-2027秋季校园招聘</x:v>
-      </x:c>
-      <x:c r="C6" s="14" t="str">
-        <x:v>证券/金融</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="str">
-        <x:v>国有控股/上市</x:v>
-      </x:c>
-      <x:c r="E6" s="14" t="str">
-        <x:v>济南、北京、上海、深圳、青岛及全国分支机构</x:v>
-      </x:c>
-      <x:c r="F6" s="14" t="str">
-        <x:v>正式批/秋季校园招聘</x:v>
-      </x:c>
-      <x:c r="G6" s="14" t="str">
-        <x:v>2027届高校毕业生（择业期内高校毕业生亦可报名）</x:v>
-      </x:c>
-      <x:c r="H6" s="14" t="str">
-        <x:v>投行、投资、研究、机构、金融科技、总部中后台、分支机构及旗下金融子公司岗位，共86个岗位、拟招227人</x:v>
-      </x:c>
-      <x:c r="I6" s="17" t="str">
-        <x:v>https://zts.hotjob.cn/school.html</x:v>
-      </x:c>
-      <x:c r="J6" s="14" t="str">
-        <x:v>2026-08-16 24:00</x:v>
-      </x:c>
-      <x:c r="K6" s="14" t="str">
-        <x:v>否（招聘程序明确包含笔试、面试）</x:v>
-      </x:c>
-      <x:c r="L6" s="14" t="str">
-        <x:v>本轮新增；山东省国资委公告与中泰证券官方招聘网站已交叉核验</x:v>
-      </x:c>
-      <x:c r="M6" s="14" t="str">
-        <x:v>P1-7天内截止</x:v>
-      </x:c>
-      <x:c r="N6" s="14" t="str">
-        <x:v>母公司业务条线、金融科技和总部中后台多要求硕士及以上，分支机构财富管理类岗位本科可报；统一网上报名，可通过中泰证券官方招聘网站或“中泰证券招聘”官方公众号投递，不收取任何费用。</x:v>
-      </x:c>
-      <x:c r="O6" s="17" t="str">
-        <x:v>https://www.selectshandong.com/recruit/company/833895033675845.html</x:v>
-      </x:c>
-      <x:c r="P6" s="16" t="str">
-        <x:v>A-山东省国资委公告与企业官方招聘网站交叉核验</x:v>
-      </x:c>
-      <x:c r="Q6" s="14" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="54" customHeight="1">
+    </x:row>
+    <x:row r="7" ht="66" customHeight="1">
       <x:c r="A7" s="14" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-17</x:v>
       </x:c>
       <x:c r="B7" s="14" t="str">
-        <x:v>中科光电</x:v>
+        <x:v>鹰角网络</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>游戏</x:v>
       </x:c>
       <x:c r="D7" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E7" s="14" t="str">
-        <x:v>以职位公告为准</x:v>
+        <x:v>上海</x:v>
       </x:c>
       <x:c r="F7" s="14" t="str">
         <x:v>提前批</x:v>
@@ -7844,102 +7963,104 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H7" s="14" t="str">
-        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
+        <x:v>游戏引擎开发、游戏客户端、角色模型、场景模型</x:v>
       </x:c>
       <x:c r="I7" s="17" t="str">
-        <x:v>https://job.cn-amd.com/</x:v>
+        <x:v>https://app.mokahr.com/su/1aeAwq</x:v>
       </x:c>
       <x:c r="J7" s="14" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-07-31</x:v>
       </x:c>
       <x:c r="K7" s="14" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；安排笔试/面试</x:v>
       </x:c>
       <x:c r="L7" s="14" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已截止（2026-07-31）；原官方来源保留</x:v>
       </x:c>
       <x:c r="M7" s="14" t="str">
-        <x:v>P1-7天内截止</x:v>
+        <x:v>已截止</x:v>
       </x:c>
       <x:c r="N7" s="14" t="str">
-        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
+        <x:v>只能投1岗；内推码不可补填；提前批未通过仍可参加正式批；7月31日截止且可能提前招满。</x:v>
       </x:c>
       <x:c r="O7" s="17" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://campus.hypergryph.com/</x:v>
       </x:c>
       <x:c r="P7" s="20" t="str">
-        <x:v>C-名称需二次确认</x:v>
-      </x:c>
-      <x:c r="Q7" s="14" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="54" customHeight="1">
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q7" s="37" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="66" customHeight="1">
       <x:c r="A8" s="14" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B8" s="14" t="str">
-        <x:v>BCG波士顿咨询</x:v>
+        <x:v>字节跳动-AI产品经理早鸟通道</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
-        <x:v>管理咨询</x:v>
+        <x:v>互联网/AI</x:v>
       </x:c>
       <x:c r="D8" s="14" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E8" s="14" t="str">
-        <x:v>北京、上海、深圳、香港等</x:v>
+        <x:v>北京、上海、深圳</x:v>
       </x:c>
       <x:c r="F8" s="14" t="str">
-        <x:v>正式批/中国区校招</x:v>
+        <x:v>早鸟专项/提前批</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H8" s="14" t="str">
-        <x:v>咨询顾问及相关专业岗位</x:v>
+        <x:v>AI产品经理、智能体及大模型产品方向</x:v>
       </x:c>
       <x:c r="I8" s="17" t="str">
-        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
       </x:c>
       <x:c r="J8" s="14" t="str">
-        <x:v>2026-08-16</x:v>
+        <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="K8" s="14" t="str">
-        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
+        <x:v>按岗位，未统一公布</x:v>
       </x:c>
       <x:c r="L8" s="14" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已截止（2026-08-02）；原公告与官方投递入口保留</x:v>
       </x:c>
       <x:c r="M8" s="14" t="str">
-        <x:v>P1-7天内截止</x:v>
-      </x:c>
-      <x:c r="N8" s="14" t="str"/>
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N8" s="14" t="str">
+        <x:v>公开文章发布时间为2026-07-16，岗位为AI产品经理，地点为北京、上海、深圳；文章引导通过公众号获取投递方式，实际投递请以字节官网及官方渠道为准。</x:v>
+      </x:c>
       <x:c r="O8" s="17" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzU2OTE0NzQ5OA==&amp;mid=2248459890&amp;idx=2&amp;sn=247ffb04c677f90340e0e47603b3f148&amp;chksm=fec08e8aad908558980561e338d3451da23b3da429122a4cebe82d47301bb04ac4d904c97015&amp;scene=27</x:v>
       </x:c>
       <x:c r="P8" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q8" s="14" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="54" customHeight="1">
+        <x:v>B-招聘公众号公开公告，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q8" s="37" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="66" customHeight="1">
       <x:c r="A9" s="4" t="str">
         <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>虹软科技</x:v>
+        <x:v>莉莉丝游戏</x:v>
       </x:c>
       <x:c r="C9" s="4" t="str">
-        <x:v>计算机视觉/软件</x:v>
+        <x:v>游戏</x:v>
       </x:c>
       <x:c r="D9" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E9" s="4" t="str">
-        <x:v>杭州、上海、南京等</x:v>
+        <x:v>上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F9" s="4" t="str">
         <x:v>提前批</x:v>
@@ -7948,102 +8069,104 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
-        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
+        <x:v>游戏研发、策划、美术、发行运营及职能</x:v>
       </x:c>
       <x:c r="I9" s="15" t="str">
-        <x:v>https://hr.arcsoft.com.cn/</x:v>
+        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
       </x:c>
       <x:c r="J9" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-07</x:v>
       </x:c>
       <x:c r="K9" s="4" t="str">
         <x:v>按岗位，官方未统一说明</x:v>
       </x:c>
       <x:c r="L9" s="4" t="str">
-        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+        <x:v>已截止（2026-08-07）；原官方来源保留</x:v>
       </x:c>
       <x:c r="M9" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
-      </x:c>
-      <x:c r="N9" s="4" t="str"/>
+        <x:v>已截止</x:v>
+      </x:c>
+      <x:c r="N9" s="4" t="str">
+        <x:v>莉莉丝27届校招提前批截止日为2026-08-07；项目已按日期标记截止，官方招聘页和原投递入口保留供查询。</x:v>
+      </x:c>
       <x:c r="O9" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://lilithgames.jobs.feishu.cn/campus</x:v>
       </x:c>
       <x:c r="P9" s="20" t="str">
-        <x:v>C-公开汇总，投前需官网复核</x:v>
-      </x:c>
-      <x:c r="Q9" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="54" customHeight="1">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q9" s="36" t="str">
+        <x:v>2026-08-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="66" customHeight="1">
       <x:c r="A10" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>2026-07-15</x:v>
       </x:c>
       <x:c r="B10" s="4" t="str">
-        <x:v>新易盛</x:v>
+        <x:v>蔚来</x:v>
       </x:c>
       <x:c r="C10" s="4" t="str">
-        <x:v>光通信/半导体</x:v>
+        <x:v>新能源汽车/智能汽车</x:v>
       </x:c>
       <x:c r="D10" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E10" s="4" t="str">
-        <x:v>成都、苏州等，以岗位页为准</x:v>
+        <x:v>上海、合肥、北京、武汉、南京等</x:v>
       </x:c>
       <x:c r="F10" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>技术提前批</x:v>
       </x:c>
       <x:c r="G10" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2024年9月-2027年8月毕业</x:v>
       </x:c>
       <x:c r="H10" s="4" t="str">
-        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
+        <x:v>算法、软件/芯片研发、智能硬件、整车、电池、产品、设计、项目管理、数据分析等</x:v>
       </x:c>
       <x:c r="I10" s="15" t="str">
-        <x:v>https://www.eoptolink.com/</x:v>
+        <x:v>https://campus.nio.com/</x:v>
       </x:c>
       <x:c r="J10" s="4" t="str">
-        <x:v>2026-08-20</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K10" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否；有笔试/测评</x:v>
       </x:c>
       <x:c r="L10" s="4" t="str">
-        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M10" s="4" t="str">
-        <x:v>P1-30天内截止</x:v>
+        <x:v>P1-7天内截止</x:v>
       </x:c>
       <x:c r="N10" s="4" t="str">
-        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
+        <x:v>最多同时申请3个岗位。</x:v>
       </x:c>
       <x:c r="O10" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P10" s="14" t="str">
-        <x:v>B-高校/招聘平台转载，投前复核</x:v>
-      </x:c>
-      <x:c r="Q10" s="4" t="str">
-        <x:v>2026-07-27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="54" customHeight="1">
+        <x:v>A-官方来源公告已核验</x:v>
+      </x:c>
+      <x:c r="Q10" s="36" t="str">
+        <x:v>2026-08-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="66" customHeight="1">
       <x:c r="A11" s="4" t="str">
-        <x:v>2026-06-18</x:v>
+        <x:v>2026-07-02</x:v>
       </x:c>
       <x:c r="B11" s="4" t="str">
-        <x:v>禾赛科技</x:v>
+        <x:v>京东方-先锋京英计划</x:v>
       </x:c>
       <x:c r="C11" s="4" t="str">
-        <x:v>激光雷达/机器人</x:v>
+        <x:v>显示技术/半导体/物联网</x:v>
       </x:c>
       <x:c r="D11" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E11" s="4" t="str">
-        <x:v>上海、杭州</x:v>
+        <x:v>北京、成都、重庆、合肥、武汉、苏州、南京、青岛等</x:v>
       </x:c>
       <x:c r="F11" s="4" t="str">
         <x:v>提前批</x:v>
@@ -8052,210 +8175,208 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H11" s="4" t="str">
-        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
+        <x:v>新型显示、智能制造、物联网算法、前沿技术、新医科五大赛道</x:v>
       </x:c>
       <x:c r="I11" s="15" t="str">
-        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
+        <x:v>https://campus.boe.com/</x:v>
       </x:c>
       <x:c r="J11" s="4" t="str">
-        <x:v>2026-08-31</x:v>
+        <x:v>2026-08-14</x:v>
       </x:c>
       <x:c r="K11" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L11" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M11" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-7天内截止</x:v>
       </x:c>
       <x:c r="N11" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>毕业时间须为2026年9月-2027年8月；投递时选择提前批。</x:v>
       </x:c>
       <x:c r="O11" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P11" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q11" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="54" customHeight="1">
+        <x:v>A-国家大学生就业平台公告已核验</x:v>
+      </x:c>
+      <x:c r="Q11" s="36" t="str">
+        <x:v>2026-08-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="66" customHeight="1">
       <x:c r="A12" s="4" t="str">
-        <x:v>2026-07-25</x:v>
+        <x:v>2026-08-03</x:v>
       </x:c>
       <x:c r="B12" s="4" t="str">
-        <x:v>深信服-X-STAR顶尖人才计划</x:v>
+        <x:v>中泰证券-2027秋季校园招聘</x:v>
       </x:c>
       <x:c r="C12" s="4" t="str">
-        <x:v>网络安全/云计算/软件</x:v>
+        <x:v>证券/金融</x:v>
       </x:c>
       <x:c r="D12" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>国有控股/上市</x:v>
       </x:c>
       <x:c r="E12" s="4" t="str">
-        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
+        <x:v>济南、北京、上海、深圳、青岛及全国分支机构</x:v>
       </x:c>
       <x:c r="F12" s="4" t="str">
-        <x:v>顶尖人才专项/提前批</x:v>
+        <x:v>正式批/秋季校园招聘</x:v>
       </x:c>
       <x:c r="G12" s="4" t="str">
-        <x:v>顶尖人才，本硕博按岗位要求</x:v>
+        <x:v>2027届高校毕业生（择业期内高校毕业生亦可报名）</x:v>
       </x:c>
       <x:c r="H12" s="4" t="str">
-        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
+        <x:v>投行、投资、研究、机构、金融科技、总部中后台、分支机构及旗下金融子公司岗位，共86个岗位、拟招227人</x:v>
       </x:c>
       <x:c r="I12" s="15" t="str">
-        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
+        <x:v>https://zts.hotjob.cn/school.html</x:v>
       </x:c>
       <x:c r="J12" s="4" t="str">
-        <x:v>2026-09-25</x:v>
+        <x:v>2026-08-16 24:00</x:v>
       </x:c>
       <x:c r="K12" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>否（招聘程序明确包含笔试、面试）</x:v>
       </x:c>
       <x:c r="L12" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>本轮新增；山东省国资委公告与中泰证券官方招聘网站已交叉核验</x:v>
       </x:c>
       <x:c r="M12" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-7天内截止</x:v>
       </x:c>
       <x:c r="N12" s="4" t="str">
-        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
+        <x:v>母公司业务条线、金融科技和总部中后台多要求硕士及以上，分支机构财富管理类岗位本科可报；统一网上报名，可通过中泰证券官方招聘网站或“中泰证券招聘”官方公众号投递，不收取任何费用。</x:v>
       </x:c>
       <x:c r="O12" s="15" t="str">
-        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
+        <x:v>https://www.selectshandong.com/recruit/company/833895033675845.html</x:v>
       </x:c>
       <x:c r="P12" s="16" t="str">
-        <x:v>A-高校就业网含官方投递链接</x:v>
-      </x:c>
-      <x:c r="Q12" s="4" t="str">
-        <x:v>2026-07-27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="54" customHeight="1">
+        <x:v>A-山东省国资委公告与企业官方招聘网站交叉核验</x:v>
+      </x:c>
+      <x:c r="Q12" s="36" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="66" customHeight="1">
       <x:c r="A13" s="4" t="str">
-        <x:v>不晚于2026-07-30</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B13" s="4" t="str">
-        <x:v>中移九天人工智能科技</x:v>
+        <x:v>中科光电</x:v>
       </x:c>
       <x:c r="C13" s="4" t="str">
-        <x:v>AI/软件/云计算</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="D13" s="4" t="str">
-        <x:v>央企子公司</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E13" s="4" t="str">
-        <x:v>北京、西安、广州、深圳</x:v>
+        <x:v>以职位公告为准</x:v>
       </x:c>
       <x:c r="F13" s="4" t="str">
-        <x:v>正式批/超级实习生</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G13" s="4" t="str">
-        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H13" s="4" t="str">
-        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
+        <x:v>光学、光电、电子、软件算法、机械及工艺方向</x:v>
       </x:c>
       <x:c r="I13" s="15" t="str">
-        <x:v>https://job.10086.cn/personal/campus/</x:v>
+        <x:v>https://job.cn-amd.com/</x:v>
       </x:c>
       <x:c r="J13" s="4" t="str">
-        <x:v>2026-09-27</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K13" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L13" s="4" t="str">
-        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M13" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-7天内截止</x:v>
       </x:c>
       <x:c r="N13" s="4" t="str">
-        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
+        <x:v>同名机构较多，必须通过原公告确认招聘主体与入口。</x:v>
       </x:c>
       <x:c r="O13" s="15" t="str">
-        <x:v>https://job.10086.cn/personal/campus/</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P13" s="16" t="str">
-        <x:v>A-中国移动官方招聘平台已核验</x:v>
-      </x:c>
-      <x:c r="Q13" s="4" t="str">
-        <x:v>2026-07-31</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="54" customHeight="1">
+        <x:v>C-名称需二次确认</x:v>
+      </x:c>
+      <x:c r="Q13" s="36" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="66" customHeight="1">
       <x:c r="A14" s="4" t="str">
-        <x:v>2026-07-21</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B14" s="4" t="str">
-        <x:v>网易游戏雷火</x:v>
+        <x:v>BCG波士顿咨询</x:v>
       </x:c>
       <x:c r="C14" s="4" t="str">
-        <x:v>游戏/互联网</x:v>
+        <x:v>管理咨询</x:v>
       </x:c>
       <x:c r="D14" s="4" t="str">
         <x:v>未注明</x:v>
       </x:c>
       <x:c r="E14" s="4" t="str">
-        <x:v>杭州、上海等，以岗位页为准</x:v>
+        <x:v>北京、上海、深圳、香港等</x:v>
       </x:c>
       <x:c r="F14" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批/中国区校招</x:v>
       </x:c>
       <x:c r="G14" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H14" s="4" t="str">
-        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
+        <x:v>咨询顾问及相关专业岗位</x:v>
       </x:c>
       <x:c r="I14" s="15" t="str">
-        <x:v>https://leihuo.163.com/campus/#/full</x:v>
+        <x:v>https://careers.bcg.com/global/en/locations/china</x:v>
       </x:c>
       <x:c r="J14" s="4" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>2026-08-16</x:v>
       </x:c>
       <x:c r="K14" s="4" t="str">
-        <x:v>部分岗位免笔试；部分可直通面试</x:v>
+        <x:v>通常含在线测评/案例面试；以通知为准</x:v>
       </x:c>
       <x:c r="L14" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
       </x:c>
       <x:c r="M14" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
-      </x:c>
-      <x:c r="N14" s="4" t="str">
-        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
-      </x:c>
+        <x:v>P1-7天内截止</x:v>
+      </x:c>
+      <x:c r="N14" s="4" t="str"/>
       <x:c r="O14" s="15" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P14" s="16" t="str">
-        <x:v>A-官方招聘官网已核验</x:v>
-      </x:c>
-      <x:c r="Q14" s="4" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q14" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="54" customHeight="1">
+    <x:row r="15" ht="66" customHeight="1">
       <x:c r="A15" s="4" t="str">
-        <x:v>2026-07-28</x:v>
+        <x:v>不晚于2026-07-21</x:v>
       </x:c>
       <x:c r="B15" s="4" t="str">
-        <x:v>广州市卓越教育集团</x:v>
+        <x:v>虹软科技</x:v>
       </x:c>
       <x:c r="C15" s="4" t="str">
-        <x:v>教育科技</x:v>
+        <x:v>计算机视觉/软件</x:v>
       </x:c>
       <x:c r="D15" s="4" t="str">
-        <x:v>民营/上市</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E15" s="4" t="str">
-        <x:v>广州等，以职位页为准</x:v>
+        <x:v>杭州、上海、南京等</x:v>
       </x:c>
       <x:c r="F15" s="4" t="str">
         <x:v>提前批</x:v>
@@ -8264,510 +8385,826 @@
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H15" s="4" t="str">
-        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
+        <x:v>计算机视觉、图像算法、深度学习、软件研发、测试等</x:v>
       </x:c>
       <x:c r="I15" s="15" t="str">
-        <x:v>https://zyjob.hotjob.cn/</x:v>
+        <x:v>https://hr.arcsoft.com.cn/</x:v>
       </x:c>
       <x:c r="J15" s="4" t="str">
-        <x:v>2026-10-26</x:v>
+        <x:v>2026-08-20</x:v>
       </x:c>
       <x:c r="K15" s="4" t="str">
+        <x:v>按岗位，官方未统一说明</x:v>
+      </x:c>
+      <x:c r="L15" s="4" t="str">
+        <x:v>汇总源显示开放；投递前需官网复核</x:v>
+      </x:c>
+      <x:c r="M15" s="4" t="str">
+        <x:v>P1-30天内截止</x:v>
+      </x:c>
+      <x:c r="N15" s="4" t="str"/>
+      <x:c r="O15" s="15" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P15" s="16" t="str">
+        <x:v>C-公开汇总，投前需官网复核</x:v>
+      </x:c>
+      <x:c r="Q15" s="36" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="66" customHeight="1">
+      <x:c r="A16" s="4" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B16" s="4" t="str">
+        <x:v>新易盛</x:v>
+      </x:c>
+      <x:c r="C16" s="4" t="str">
+        <x:v>光通信/半导体</x:v>
+      </x:c>
+      <x:c r="D16" s="4" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E16" s="4" t="str">
+        <x:v>成都、苏州等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F16" s="4" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G16" s="4" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H16" s="4" t="str">
+        <x:v>光模块研发、硬件、软件、测试、工艺、质量及职能</x:v>
+      </x:c>
+      <x:c r="I16" s="15" t="str">
+        <x:v>https://www.eoptolink.com/</x:v>
+      </x:c>
+      <x:c r="J16" s="4" t="str">
+        <x:v>2026-08-20</x:v>
+      </x:c>
+      <x:c r="K16" s="4" t="str">
         <x:v>官方未说明</x:v>
       </x:c>
-      <x:c r="L15" s="4" t="str">
-        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
-      </x:c>
-      <x:c r="M15" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
-      </x:c>
-      <x:c r="N15" s="4" t="str">
-        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
-      </x:c>
-      <x:c r="O15" s="15" t="str">
-        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
-      </x:c>
-      <x:c r="P15" s="16" t="str">
-        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
-      </x:c>
-      <x:c r="Q15" s="4" t="str">
-        <x:v>2026-07-30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="54" customHeight="1">
-      <x:c r="A16" s="4" t="str">
-        <x:v>2026-08-04</x:v>
-      </x:c>
-      <x:c r="B16" s="4" t="str">
-        <x:v>德勤-2027秋季校园招聘</x:v>
-      </x:c>
-      <x:c r="C16" s="4" t="str">
-        <x:v>会计审计/专业服务</x:v>
-      </x:c>
-      <x:c r="D16" s="4" t="str">
-        <x:v>外资/专业服务</x:v>
-      </x:c>
-      <x:c r="E16" s="4" t="str">
-        <x:v>北京、上海、广州、深圳、重庆等，以岗位页为准</x:v>
-      </x:c>
-      <x:c r="F16" s="4" t="str">
-        <x:v>正式批/秋季校园招聘</x:v>
-      </x:c>
-      <x:c r="G16" s="4" t="str">
-        <x:v>2027届应届毕业生；另有2027寒假实习生</x:v>
-      </x:c>
-      <x:c r="H16" s="4" t="str">
-        <x:v>审计与鉴证、管理咨询、风险咨询、财务咨询、税务及法律、数字化等</x:v>
-      </x:c>
-      <x:c r="I16" s="15" t="str">
-        <x:v>https://www.deloitte.com/cn/zh/careers.html</x:v>
-      </x:c>
-      <x:c r="J16" s="4" t="str">
-        <x:v>2026-10-31（部分岗位招满提前关闭）</x:v>
-      </x:c>
-      <x:c r="K16" s="4" t="str">
-        <x:v>否（网申后通常安排在线笔试，具体以岗位流程为准）</x:v>
-      </x:c>
       <x:c r="L16" s="4" t="str">
-        <x:v>本轮新增；可信高校就业公众号发布德勤2027校招信息，官方招聘入口已核验</x:v>
+        <x:v>7月下旬再次出现提前批/开放日公告，投前复核官网</x:v>
       </x:c>
       <x:c r="M16" s="4" t="str">
-        <x:v>P2-正常关注</x:v>
+        <x:v>P1-30天内截止</x:v>
       </x:c>
       <x:c r="N16" s="4" t="str">
-        <x:v>秋季全职与寒假实习并行；网申完成后通常收到在线笔试邀请，部分岗位招满会提前结束网申；德勤中国不收取招聘费用，谨防第三方收费。</x:v>
+        <x:v>公开汇总截止日为8月20日；7月下旬出现新的提前批/开放日公告，建议直接进入企业招聘页确认。</x:v>
       </x:c>
       <x:c r="O16" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3ODQ3NTIzMA==&amp;mid=2651327099&amp;idx=4&amp;sn=465f2aa047b826709fa081aa25e633f5&amp;chksm=85d23ac1f4759b74460c0c675e988bc8434725c02e7a91d66890eb4795c8000b3dbe9fcf4a48&amp;scene=27</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P16" s="14" t="str">
-        <x:v>B-可信高校就业公众号公告含德勤官方招聘入口</x:v>
-      </x:c>
-      <x:c r="Q16" s="4" t="str">
-        <x:v>2026-08-07</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="54" customHeight="1">
+        <x:v>B-高校/招聘平台转载，投前复核</x:v>
+      </x:c>
+      <x:c r="Q16" s="36" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="66" customHeight="1">
       <x:c r="A17" s="4" t="str">
-        <x:v>2026-08-01</x:v>
+        <x:v>2026-06-18</x:v>
       </x:c>
       <x:c r="B17" s="4" t="str">
-        <x:v>影石Insta360</x:v>
+        <x:v>禾赛科技</x:v>
       </x:c>
       <x:c r="C17" s="4" t="str">
-        <x:v>消费电子/智能影像</x:v>
+        <x:v>激光雷达/机器人</x:v>
       </x:c>
       <x:c r="D17" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E17" s="4" t="str">
-        <x:v>深圳、上海、珠海</x:v>
+        <x:v>上海、杭州</x:v>
       </x:c>
       <x:c r="F17" s="4" t="str">
-        <x:v>正式批/秋招</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G17" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H17" s="4" t="str">
-        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
+        <x:v>空间智能、机器人动力模组、雷达研发、智能制造与质量</x:v>
       </x:c>
       <x:c r="I17" s="15" t="str">
-        <x:v>https://www.insta360.com/cn/jobs</x:v>
+        <x:v>https://www.hesaitech.com/cn/careers/</x:v>
       </x:c>
       <x:c r="J17" s="4" t="str">
-        <x:v>2026-10-31</x:v>
+        <x:v>2026-08-31</x:v>
       </x:c>
       <x:c r="K17" s="4" t="str">
-        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L17" s="4" t="str">
-        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
       </x:c>
       <x:c r="M17" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N17" s="4" t="str">
-        <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
       </x:c>
       <x:c r="O17" s="15" t="str">
-        <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P17" s="16" t="str">
-        <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
-      </x:c>
-      <x:c r="Q17" s="4" t="str">
-        <x:v>2026-08-04</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="54" customHeight="1">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q17" s="36" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="66" customHeight="1">
       <x:c r="A18" s="4" t="str">
-        <x:v>2026-08-05</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="B18" s="4" t="str">
-        <x:v>联想集团</x:v>
+        <x:v>深信服-X-STAR顶尖人才计划</x:v>
       </x:c>
       <x:c r="C18" s="4" t="str">
-        <x:v>计算机/消费电子/智能硬件</x:v>
+        <x:v>网络安全/云计算/软件</x:v>
       </x:c>
       <x:c r="D18" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E18" s="4" t="str">
-        <x:v>北京、上海、天津、成都、南京、武汉、深圳、厦门等，以岗位页为准</x:v>
+        <x:v>深圳、北京、西安、长沙等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F18" s="4" t="str">
-        <x:v>正式批/应届生招聘</x:v>
+        <x:v>顶尖人才专项/提前批</x:v>
       </x:c>
       <x:c r="G18" s="4" t="str">
-        <x:v>2027届海内外毕业生（中国大陆毕业时间为2026年9月1日至2027年8月31日）</x:v>
+        <x:v>顶尖人才，本硕博按岗位要求</x:v>
       </x:c>
       <x:c r="H18" s="4" t="str">
-        <x:v>AI开发、软件开发、嵌入式、硬件、产品与项目、设计、市场与销售、供应链及职能岗位</x:v>
+        <x:v>网络安全、云计算、软件研发、算法、基础架构、产品及技术研究方向</x:v>
       </x:c>
       <x:c r="I18" s="15" t="str">
-        <x:v>https://talent.lenovo.com.cn/campus</x:v>
+        <x:v>https://app.mokahr.com/campus-recruitment/sangfor/27944?locale=zh-CN</x:v>
       </x:c>
       <x:c r="J18" s="4" t="str">
-        <x:v>2026-11-13</x:v>
+        <x:v>2026-09-25</x:v>
       </x:c>
       <x:c r="K18" s="4" t="str">
-        <x:v>否（官方校招日历含在线测评&amp;技术笔试，简历筛选通过发放笔试通知）</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L18" s="4" t="str">
-        <x:v>本轮新增；联想官方应届生招聘页显示热招中</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M18" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N18" s="4" t="str">
-        <x:v>联想官方应届生招聘页当前显示“联想2027应届生招聘”，面向2027届海内外毕业生；网申自2026年8月5日开启，官网公布网申截止2026年11月13日。简历完整度需达到100%才能投递，每个校招项目只能投一个岗位（管培生项目和其他项目可各投一个），部分岗位可能因投递人数较多下线；投递时可选择接受岗位调剂，测评通知以邮件、短信和系统提醒为准。</x:v>
+        <x:v>X-STAR为顶尖人才专项，不等同于深信服普通校招；公开过期时间为9月25日，具体岗位按官网筛选。</x:v>
       </x:c>
       <x:c r="O18" s="15" t="str">
-        <x:v>https://talent.lenovo.com.cn/campus</x:v>
+        <x:v>https://cqu.cqbys.com/campus/view/id/731760</x:v>
       </x:c>
       <x:c r="P18" s="16" t="str">
-        <x:v>A-企业官方校园招聘页已核验</x:v>
-      </x:c>
-      <x:c r="Q18" s="4" t="str">
-        <x:v>2026-08-05</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="54" customHeight="1">
+        <x:v>A-高校就业网含官方投递链接</x:v>
+      </x:c>
+      <x:c r="Q18" s="36" t="str">
+        <x:v>2026-07-27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="66" customHeight="1">
       <x:c r="A19" s="4" t="str">
-        <x:v>不晚于2026-07-21</x:v>
+        <x:v>不晚于2026-07-30</x:v>
       </x:c>
       <x:c r="B19" s="4" t="str">
-        <x:v>京东-TET管理培训生</x:v>
+        <x:v>中移九天人工智能科技</x:v>
       </x:c>
       <x:c r="C19" s="4" t="str">
-        <x:v>互联网/零售</x:v>
+        <x:v>AI/软件/云计算</x:v>
       </x:c>
       <x:c r="D19" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>央企子公司</x:v>
       </x:c>
       <x:c r="E19" s="4" t="str">
-        <x:v>北京及业务所在城市</x:v>
+        <x:v>北京、西安、广州、深圳</x:v>
       </x:c>
       <x:c r="F19" s="4" t="str">
-        <x:v>管培生专项/提前批</x:v>
+        <x:v>正式批/超级实习生</x:v>
       </x:c>
       <x:c r="G19" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届及在校博士优先，优秀硕士可放宽</x:v>
       </x:c>
       <x:c r="H19" s="4" t="str">
-        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
+        <x:v>算法、人工智能、软件研发、产品及解决方案岗位</x:v>
       </x:c>
       <x:c r="I19" s="15" t="str">
-        <x:v>https://campus.jd.com/</x:v>
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="J19" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>2026-09-27</x:v>
       </x:c>
       <x:c r="K19" s="4" t="str">
-        <x:v>含测评，笔试以通知为准</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L19" s="4" t="str">
-        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
+        <x:v>本轮新确认；中国移动官方校园招聘入口已核验</x:v>
       </x:c>
       <x:c r="M19" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N19" s="4" t="str">
-        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
+        <x:v>在中国移动招聘网站筛选中移九天相关岗位；公开信息标注9月27日截止，投递前以岗位页为准。</x:v>
       </x:c>
       <x:c r="O19" s="15" t="str">
-        <x:v>https://campus.jd.com/#/</x:v>
+        <x:v>https://job.10086.cn/personal/campus/</x:v>
       </x:c>
       <x:c r="P19" s="16" t="str">
-        <x:v>A-企业官网校招页面已核验</x:v>
-      </x:c>
-      <x:c r="Q19" s="4" t="str">
-        <x:v>2026-07-30</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="54" customHeight="1">
+        <x:v>A-中国移动官方招聘平台已核验</x:v>
+      </x:c>
+      <x:c r="Q19" s="36" t="str">
+        <x:v>2026-07-31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="66" customHeight="1">
       <x:c r="A20" s="4" t="str">
-        <x:v>2026-06-12</x:v>
+        <x:v>2026-07-21</x:v>
       </x:c>
       <x:c r="B20" s="4" t="str">
-        <x:v>MOVA</x:v>
+        <x:v>网易游戏雷火</x:v>
       </x:c>
       <x:c r="C20" s="4" t="str">
-        <x:v>智能家电/机器人</x:v>
+        <x:v>游戏/互联网</x:v>
       </x:c>
       <x:c r="D20" s="4" t="str">
-        <x:v>民营</x:v>
+        <x:v>未注明</x:v>
       </x:c>
       <x:c r="E20" s="4" t="str">
-        <x:v>苏州及全国</x:v>
+        <x:v>杭州、上海等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F20" s="4" t="str">
-        <x:v>全球校招/正式批</x:v>
+        <x:v>正式批</x:v>
       </x:c>
       <x:c r="G20" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H20" s="4" t="str">
-        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+        <x:v>游戏研发、策划、艺术设计、产品运营、市场及职能等</x:v>
       </x:c>
       <x:c r="I20" s="15" t="str">
-        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+        <x:v>https://leihuo.163.com/campus/#/full</x:v>
       </x:c>
       <x:c r="J20" s="4" t="str">
-        <x:v>2026-11-30</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="K20" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>部分岗位免笔试；部分可直通面试</x:v>
       </x:c>
       <x:c r="L20" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>已核验开放</x:v>
       </x:c>
       <x:c r="M20" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N20" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>岗位招满即止；笔试/测试8-10月分批进行。</x:v>
       </x:c>
       <x:c r="O20" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
       <x:c r="P20" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q20" s="4" t="str">
+        <x:v>A-官方招聘官网已核验</x:v>
+      </x:c>
+      <x:c r="Q20" s="36" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="54" customHeight="1">
+    <x:row r="21" ht="66" customHeight="1">
       <x:c r="A21" s="4" t="str">
-        <x:v>2026-08-03</x:v>
+        <x:v>2026-07-28</x:v>
       </x:c>
       <x:c r="B21" s="4" t="str">
-        <x:v>字节跳动-2027校园招聘</x:v>
+        <x:v>广州市卓越教育集团</x:v>
       </x:c>
       <x:c r="C21" s="4" t="str">
-        <x:v>互联网/AI/内容平台</x:v>
+        <x:v>教育科技</x:v>
       </x:c>
       <x:c r="D21" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E21" s="4" t="str">
-        <x:v>北京、上海、深圳、杭州等，具体以岗位页为准</x:v>
+        <x:v>广州等，以职位页为准</x:v>
       </x:c>
       <x:c r="F21" s="4" t="str">
-        <x:v>正式批/校园招聘</x:v>
+        <x:v>提前批</x:v>
       </x:c>
       <x:c r="G21" s="4" t="str">
-        <x:v>毕业时间为2026年9月至2027年8月的应届生</x:v>
+        <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H21" s="4" t="str">
-        <x:v>研发、产品、运营、设计、市场、职能/支持、销售、游戏策划八大类；新增AI全栈工程师、AI Agent开发等方向</x:v>
+        <x:v>专职教师、学科校长管培生（教学方向）、运营校长管培生（销售方向）</x:v>
       </x:c>
       <x:c r="I21" s="15" t="str">
-        <x:v>https://jobs.bytedance.com/campus/</x:v>
+        <x:v>https://zyjob.hotjob.cn/</x:v>
       </x:c>
       <x:c r="J21" s="4" t="str">
-        <x:v>2026-12-31（岗位招满可能提前下架）</x:v>
+        <x:v>2026-10-26</x:v>
       </x:c>
       <x:c r="K21" s="4" t="str">
-        <x:v>官方未统一说明</x:v>
+        <x:v>官方未说明</x:v>
       </x:c>
       <x:c r="L21" s="4" t="str">
-        <x:v>本轮新增；字节跳动官方校园招聘入口已核验，2027届校招于2026-08-03启动</x:v>
+        <x:v>可信高校就业网公告显示开放；企业招聘官网入口已核验</x:v>
       </x:c>
       <x:c r="M21" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N21" s="4" t="str">
-        <x:v>普通校招投递机会按阶段刷新：2026-08-03至2026-12-31有两次机会，2027-01-01刷新两次；岗位招满会下架。AI产品早鸟通道、前沿技术人才校招、Seed大模型人才校招等专项不占用普通投递机会。</x:v>
+        <x:v>郑州大学就业网发布时间为2026-07-28 16:41，公告标题为校园招聘提前批；投递时按企业招聘官网岗位页面要求提交，具体城市和岗位以职位页为准。</x:v>
       </x:c>
       <x:c r="O21" s="15" t="str">
-        <x:v>https://jobs.bytedance.com/campus/</x:v>
+        <x:v>https://job.zzu.edu.cn/campus/view/id/1018654</x:v>
       </x:c>
       <x:c r="P21" s="16" t="str">
-        <x:v>A-企业官方校园招聘入口已核验</x:v>
-      </x:c>
-      <x:c r="Q21" s="4" t="str">
+        <x:v>A-可信高校就业网与企业招聘官网交叉核验</x:v>
+      </x:c>
+      <x:c r="Q21" s="36" t="str">
+        <x:v>2026-07-30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="66" customHeight="1">
+      <x:c r="A22" s="4" t="str">
+        <x:v>2026-08-04</x:v>
+      </x:c>
+      <x:c r="B22" s="4" t="str">
+        <x:v>德勤-2027秋季校园招聘</x:v>
+      </x:c>
+      <x:c r="C22" s="4" t="str">
+        <x:v>会计审计/专业服务</x:v>
+      </x:c>
+      <x:c r="D22" s="4" t="str">
+        <x:v>外资/专业服务</x:v>
+      </x:c>
+      <x:c r="E22" s="4" t="str">
+        <x:v>北京、上海、广州、深圳、重庆等，以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F22" s="4" t="str">
+        <x:v>正式批/秋季校园招聘</x:v>
+      </x:c>
+      <x:c r="G22" s="4" t="str">
+        <x:v>2027届应届毕业生；另有2027寒假实习生</x:v>
+      </x:c>
+      <x:c r="H22" s="4" t="str">
+        <x:v>审计与鉴证、管理咨询、风险咨询、财务咨询、税务及法律、数字化等</x:v>
+      </x:c>
+      <x:c r="I22" s="15" t="str">
+        <x:v>https://www.deloitte.com/cn/zh/careers.html</x:v>
+      </x:c>
+      <x:c r="J22" s="4" t="str">
+        <x:v>2026-10-31（部分岗位招满提前关闭）</x:v>
+      </x:c>
+      <x:c r="K22" s="4" t="str">
+        <x:v>否（网申后通常安排在线笔试，具体以岗位流程为准）</x:v>
+      </x:c>
+      <x:c r="L22" s="4" t="str">
+        <x:v>本轮新增；可信高校就业公众号发布德勤2027校招信息，官方招聘入口已核验</x:v>
+      </x:c>
+      <x:c r="M22" s="4" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N22" s="4" t="str">
+        <x:v>秋季全职与寒假实习并行；网申完成后通常收到在线笔试邀请，部分岗位招满会提前结束网申；德勤中国不收取招聘费用，谨防第三方收费。</x:v>
+      </x:c>
+      <x:c r="O22" s="15" t="str">
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzA3ODQ3NTIzMA==&amp;mid=2651327099&amp;idx=4&amp;sn=465f2aa047b826709fa081aa25e633f5&amp;chksm=85d23ac1f4759b74460c0c675e988bc8434725c02e7a91d66890eb4795c8000b3dbe9fcf4a48&amp;scene=27</x:v>
+      </x:c>
+      <x:c r="P22" s="16" t="str">
+        <x:v>B-可信高校就业公众号公告含德勤官方招聘入口</x:v>
+      </x:c>
+      <x:c r="Q22" s="36" t="str">
         <x:v>2026-08-07</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="54" customHeight="1">
-      <x:c r="A22" s="4" t="str">
+    <x:row r="23" ht="66" customHeight="1">
+      <x:c r="A23" s="4" t="str">
         <x:v>2026-08-01</x:v>
       </x:c>
-      <x:c r="B22" s="4" t="str">
-        <x:v>中国人民保险集团-2027届统筹校园招聘</x:v>
-      </x:c>
-      <x:c r="C22" s="4" t="str">
-        <x:v>保险/金融</x:v>
-      </x:c>
-      <x:c r="D22" s="4" t="str">
-        <x:v>中央金融企业/国有</x:v>
-      </x:c>
-      <x:c r="E22" s="4" t="str">
-        <x:v>全国</x:v>
-      </x:c>
-      <x:c r="F22" s="4" t="str">
-        <x:v>正式批/集团统筹校园招聘</x:v>
-      </x:c>
-      <x:c r="G22" s="4" t="str">
-        <x:v>海内外2027届应届高校毕业生</x:v>
-      </x:c>
-      <x:c r="H22" s="4" t="str">
-        <x:v>集团本级及8家成员公司岗位，涵盖保险、投资、科技、精算、信托、再保险及综合职能等</x:v>
-      </x:c>
-      <x:c r="I22" s="15" t="str">
-        <x:v>https://picc.zhiye.com</x:v>
-      </x:c>
-      <x:c r="J22" s="4" t="str">
-        <x:v>2027-04-25（集团本级约2026年10月中旬截止；各单位总部及部分省级机构约2026年11月中下旬截止）</x:v>
-      </x:c>
-      <x:c r="K22" s="4" t="str">
-        <x:v>否（分批次开展笔试，部分岗位设置差异化笔试）</x:v>
-      </x:c>
-      <x:c r="L22" s="4" t="str">
-        <x:v>本轮新增；高校就业网公告来源为中国人民保险集团，官方招聘海报及官网入口已核验</x:v>
-      </x:c>
-      <x:c r="M22" s="4" t="str">
-        <x:v>P2-分机构截止</x:v>
-      </x:c>
-      <x:c r="N22" s="4" t="str">
-        <x:v>招聘覆盖集团本级及8家成员公司；每人最多可投2个志愿，同一机构限投1个岗位。总通道关闭时间较晚，但各机构有更早截止时间，应按目标单位页面尽早投递。</x:v>
-      </x:c>
-      <x:c r="O22" s="15" t="str">
-        <x:v>https://career.smbu.edu.cn/detail/online?id=3537075</x:v>
-      </x:c>
-      <x:c r="P22" s="16" t="str">
-        <x:v>A-官方招聘海报与中国人民保险招聘官网入口已核验</x:v>
-      </x:c>
-      <x:c r="Q22" s="4" t="str">
-        <x:v>2026-08-11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="54" customHeight="1">
-      <x:c r="A23" s="4" t="str">
-        <x:v>2026-06-17</x:v>
-      </x:c>
       <x:c r="B23" s="4" t="str">
-        <x:v>龙蟠科技</x:v>
+        <x:v>影石Insta360</x:v>
       </x:c>
       <x:c r="C23" s="4" t="str">
-        <x:v>新能源材料/化工</x:v>
+        <x:v>消费电子/智能影像</x:v>
       </x:c>
       <x:c r="D23" s="4" t="str">
         <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E23" s="4" t="str">
-        <x:v>南京</x:v>
+        <x:v>深圳、上海、珠海</x:v>
       </x:c>
       <x:c r="F23" s="4" t="str">
-        <x:v>提前批</x:v>
+        <x:v>正式批/秋招</x:v>
       </x:c>
       <x:c r="G23" s="4" t="str">
         <x:v>2027届应届毕业生</x:v>
       </x:c>
       <x:c r="H23" s="4" t="str">
-        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
+        <x:v>软件、算法、硬件、产品、设计、营销及职能岗位</x:v>
       </x:c>
       <x:c r="I23" s="15" t="str">
-        <x:v>https://www.lopal.com.cn/join</x:v>
+        <x:v>https://www.insta360.com/cn/jobs</x:v>
       </x:c>
       <x:c r="J23" s="4" t="str">
-        <x:v>2027-06-01</x:v>
+        <x:v>2026-10-31</x:v>
       </x:c>
       <x:c r="K23" s="4" t="str">
-        <x:v>官方未说明</x:v>
+        <x:v>非免笔试（官方日程含8-11月笔面试）</x:v>
       </x:c>
       <x:c r="L23" s="4" t="str">
-        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+        <x:v>官方公众号文章与企业招聘页已交叉核验</x:v>
       </x:c>
       <x:c r="M23" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N23" s="4" t="str">
-        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+        <x:v>南大就业公众号文章发布于2026-08-01，面向2027届毕业生（毕业时间为2026年9月至2027年8月），工作地点为深圳、上海、珠海；简历投递截止2026-10-31 19:00，8-11月安排笔面试、10月起沟通Offer。岗位城市和具体职位以影石Insta360官方招聘页为准。</x:v>
       </x:c>
       <x:c r="O23" s="15" t="str">
-        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+        <x:v>https://mp.weixin.qq.com/s?__biz=MzAxMDA3MjIwMw==&amp;mid=2652174609&amp;idx=1&amp;sn=341a17d61257a145a21e44df7633757a&amp;chksm=81427f5412a5949a05987cdd3b7c4a6d9bea8bd715ad941339cf4c6373e216476c4fc00456a7&amp;scene=27</x:v>
       </x:c>
       <x:c r="P23" s="14" t="str">
-        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
-      </x:c>
-      <x:c r="Q23" s="4" t="str">
-        <x:v>2026-07-24</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="54" customHeight="1">
+        <x:v>A-企业官方招聘页与官方公众号文章交叉核验</x:v>
+      </x:c>
+      <x:c r="Q23" s="36" t="str">
+        <x:v>2026-08-04</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="66" customHeight="1">
       <x:c r="A24" s="4" t="str">
-        <x:v>2026-07-09</x:v>
+        <x:v>2026-08-05</x:v>
       </x:c>
       <x:c r="B24" s="4" t="str">
-        <x:v>百度</x:v>
+        <x:v>联想集团</x:v>
       </x:c>
       <x:c r="C24" s="4" t="str">
-        <x:v>互联网/AI</x:v>
+        <x:v>计算机/消费电子/智能硬件</x:v>
       </x:c>
       <x:c r="D24" s="4" t="str">
-        <x:v>未注明</x:v>
+        <x:v>民营/上市</x:v>
       </x:c>
       <x:c r="E24" s="4" t="str">
-        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+        <x:v>北京、上海、天津、成都、南京、武汉、深圳、厦门等，以岗位页为准</x:v>
       </x:c>
       <x:c r="F24" s="4" t="str">
-        <x:v>正式批</x:v>
+        <x:v>正式批/应届生招聘</x:v>
       </x:c>
       <x:c r="G24" s="4" t="str">
-        <x:v>2027届应届毕业生</x:v>
+        <x:v>2027届海内外毕业生（中国大陆毕业时间为2026年9月1日至2027年8月31日）</x:v>
       </x:c>
       <x:c r="H24" s="4" t="str">
-        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+        <x:v>AI开发、软件开发、嵌入式、硬件、产品与项目、设计、市场与销售、供应链及职能岗位</x:v>
       </x:c>
       <x:c r="I24" s="15" t="str">
-        <x:v>https://talent.baidu.com/jobs</x:v>
+        <x:v>https://talent.lenovo.com.cn/campus</x:v>
       </x:c>
       <x:c r="J24" s="4" t="str">
-        <x:v>2027-06-30</x:v>
+        <x:v>2026-11-13</x:v>
       </x:c>
       <x:c r="K24" s="4" t="str">
-        <x:v>部分免；并非所有候选人参加笔试</x:v>
+        <x:v>否（官方校招日历含在线测评&amp;技术笔试，简历筛选通过发放笔试通知）</x:v>
       </x:c>
       <x:c r="L24" s="4" t="str">
-        <x:v>已核验开放</x:v>
+        <x:v>本轮新增；联想官方应届生招聘页显示热招中</x:v>
       </x:c>
       <x:c r="M24" s="4" t="str">
         <x:v>P2-正常关注</x:v>
       </x:c>
       <x:c r="N24" s="4" t="str">
+        <x:v>联想官方应届生招聘页当前显示“联想2027应届生招聘”，面向2027届海内外毕业生；网申自2026年8月5日开启，官网公布网申截止2026年11月13日。简历完整度需达到100%才能投递，每个校招项目只能投一个岗位（管培生项目和其他项目可各投一个），部分岗位可能因投递人数较多下线；投递时可选择接受岗位调剂，测评通知以邮件、短信和系统提醒为准。</x:v>
+      </x:c>
+      <x:c r="O24" s="15" t="str">
+        <x:v>https://talent.lenovo.com.cn/campus</x:v>
+      </x:c>
+      <x:c r="P24" s="16" t="str">
+        <x:v>A-企业官方校园招聘页已核验</x:v>
+      </x:c>
+      <x:c r="Q24" s="36" t="str">
+        <x:v>2026-08-05</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="66" customHeight="1">
+      <x:c r="A25" t="str">
+        <x:v>不晚于2026-07-21</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>京东-TET管理培训生</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>互联网/零售</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>北京及业务所在城市</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>管培生专项/提前批</x:v>
+      </x:c>
+      <x:c r="G25" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>技术、产品、供应链、零售及综合管理方向</x:v>
+      </x:c>
+      <x:c r="I25" t="str">
+        <x:v>https://campus.jd.com/</x:v>
+      </x:c>
+      <x:c r="J25" t="str">
+        <x:v>2026-11-30</x:v>
+      </x:c>
+      <x:c r="K25" t="str">
+        <x:v>含测评，笔试以通知为准</x:v>
+      </x:c>
+      <x:c r="L25" t="str">
+        <x:v>已核验开放（官网简历接收至2026-11-30）</x:v>
+      </x:c>
+      <x:c r="M25" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N25" t="str">
+        <x:v>京东官网页面显示 TET 简历接收时间为7月1日-11月30日；测评/笔试/AI面试在简历筛选通过后发送。此前公开汇总标注7月31日，已按官网更正。</x:v>
+      </x:c>
+      <x:c r="O25" t="str">
+        <x:v>https://campus.jd.com/#/</x:v>
+      </x:c>
+      <x:c r="P25" t="str">
+        <x:v>A-企业官网校招页面已核验</x:v>
+      </x:c>
+      <x:c r="Q25" s="39" t="str">
+        <x:v>2026-07-30</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="66" customHeight="1">
+      <x:c r="A26" t="str">
+        <x:v>2026-06-12</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>MOVA</x:v>
+      </x:c>
+      <x:c r="C26" t="str">
+        <x:v>智能家电/机器人</x:v>
+      </x:c>
+      <x:c r="D26" t="str">
+        <x:v>民营</x:v>
+      </x:c>
+      <x:c r="E26" t="str">
+        <x:v>苏州及全国</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>全球校招/正式批</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H26" t="str">
+        <x:v>研产、全球营销、设计、职能、制造供应</x:v>
+      </x:c>
+      <x:c r="I26" t="str">
+        <x:v>https://mova.zhiye.com/Campus/jobs?activityGuid=d17b6348-1714-42cd-a04c-1ebf0555819a&amp;ActivityJumpPage=PortalPage</x:v>
+      </x:c>
+      <x:c r="J26" t="str">
+        <x:v>2026-11-30</x:v>
+      </x:c>
+      <x:c r="K26" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L26" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M26" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N26" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O26" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P26" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q26" s="39" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="66" customHeight="1">
+      <x:c r="A27" t="str">
+        <x:v>2026-08-03</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>字节跳动-2027校园招聘</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>互联网/AI/内容平台</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>北京、上海、深圳、杭州等，具体以岗位页为准</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>正式批/校园招聘</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>毕业时间为2026年9月至2027年8月的应届生</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>研发、产品、运营、设计、市场、职能/支持、销售、游戏策划八大类；新增AI全栈工程师、AI Agent开发等方向</x:v>
+      </x:c>
+      <x:c r="I27" t="str">
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
+      </x:c>
+      <x:c r="J27" t="str">
+        <x:v>2026-12-31（岗位招满可能提前下架）</x:v>
+      </x:c>
+      <x:c r="K27" t="str">
+        <x:v>官方未统一说明</x:v>
+      </x:c>
+      <x:c r="L27" t="str">
+        <x:v>本轮新增；字节跳动官方校园招聘入口已核验，2027届校招于2026-08-03启动</x:v>
+      </x:c>
+      <x:c r="M27" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N27" t="str">
+        <x:v>普通校招投递机会按阶段刷新：2026-08-03至2026-12-31有两次机会，2027-01-01刷新两次；岗位招满会下架。AI产品早鸟通道、前沿技术人才校招、Seed大模型人才校招等专项不占用普通投递机会。</x:v>
+      </x:c>
+      <x:c r="O27" t="str">
+        <x:v>https://jobs.bytedance.com/campus/</x:v>
+      </x:c>
+      <x:c r="P27" t="str">
+        <x:v>A-企业官方校园招聘入口已核验</x:v>
+      </x:c>
+      <x:c r="Q27" s="39" t="str">
+        <x:v>2026-08-07</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="66" customHeight="1">
+      <x:c r="A28" t="str">
+        <x:v>2026-08-01</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>中国人民保险集团-2027届统筹校园招聘</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>保险/金融</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>中央金融企业/国有</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>全国</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>正式批/集团统筹校园招聘</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>海内外2027届应届高校毕业生</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>集团本级及8家成员公司岗位，涵盖保险、投资、科技、精算、信托、再保险及综合职能等</x:v>
+      </x:c>
+      <x:c r="I28" t="str">
+        <x:v>https://picc.zhiye.com</x:v>
+      </x:c>
+      <x:c r="J28" t="str">
+        <x:v>2027-04-25（集团本级约2026年10月中旬截止；各单位总部及部分省级机构约2026年11月中下旬截止）</x:v>
+      </x:c>
+      <x:c r="K28" t="str">
+        <x:v>否（分批次开展笔试，部分岗位设置差异化笔试）</x:v>
+      </x:c>
+      <x:c r="L28" t="str">
+        <x:v>本轮新增；高校就业网公告来源为中国人民保险集团，官方招聘海报及官网入口已核验</x:v>
+      </x:c>
+      <x:c r="M28" t="str">
+        <x:v>P2-分机构截止</x:v>
+      </x:c>
+      <x:c r="N28" t="str">
+        <x:v>招聘覆盖集团本级及8家成员公司；每人最多可投2个志愿，同一机构限投1个岗位。总通道关闭时间较晚，但各机构有更早截止时间，应按目标单位页面尽早投递。</x:v>
+      </x:c>
+      <x:c r="O28" t="str">
+        <x:v>https://career.smbu.edu.cn/detail/online?id=3537075</x:v>
+      </x:c>
+      <x:c r="P28" t="str">
+        <x:v>A-官方招聘海报与中国人民保险招聘官网入口已核验</x:v>
+      </x:c>
+      <x:c r="Q28" s="39" t="str">
+        <x:v>2026-08-11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="66" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>2026-06-17</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>龙蟠科技</x:v>
+      </x:c>
+      <x:c r="C29" t="str">
+        <x:v>新能源材料/化工</x:v>
+      </x:c>
+      <x:c r="D29" t="str">
+        <x:v>民营/上市</x:v>
+      </x:c>
+      <x:c r="E29" t="str">
+        <x:v>南京</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>提前批</x:v>
+      </x:c>
+      <x:c r="G29" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H29" t="str">
+        <x:v>博士专项、研发技术、AI与数字化、职能</x:v>
+      </x:c>
+      <x:c r="I29" t="str">
+        <x:v>https://www.lopal.com.cn/join</x:v>
+      </x:c>
+      <x:c r="J29" t="str">
+        <x:v>2027-06-01</x:v>
+      </x:c>
+      <x:c r="K29" t="str">
+        <x:v>官方未说明</x:v>
+      </x:c>
+      <x:c r="L29" t="str">
+        <x:v>公开招聘平台显示开放；招满即止需确认</x:v>
+      </x:c>
+      <x:c r="M29" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N29" t="str">
+        <x:v>公开信息标注招满即止；若入口仅为企业主页或来源页，需通过官网招聘栏目/公众号投递。</x:v>
+      </x:c>
+      <x:c r="O29" t="str">
+        <x:v>https://baijiahao.baidu.com/s?id=1868689819659985123&amp;wfr=spider&amp;for=pc</x:v>
+      </x:c>
+      <x:c r="P29" t="str">
+        <x:v>B-51job校园公开汇总，投前需确认岗位仍开放</x:v>
+      </x:c>
+      <x:c r="Q29" s="39" t="str">
+        <x:v>2026-07-24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="66" customHeight="1">
+      <x:c r="A30" t="str">
+        <x:v>2026-07-09</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>百度</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>互联网/AI</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>未注明</x:v>
+      </x:c>
+      <x:c r="E30" t="str">
+        <x:v>北京、南京、上海、苏州、深圳、郑州、广州、大连、杭州、保定、成都等</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>正式批</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>2027届应届毕业生</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>技术、产品、政企、销售、综合五大方向，约74个细分职位</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>https://talent.baidu.com/jobs</x:v>
+      </x:c>
+      <x:c r="J30" t="str">
+        <x:v>2027-06-30</x:v>
+      </x:c>
+      <x:c r="K30" t="str">
+        <x:v>部分免；并非所有候选人参加笔试</x:v>
+      </x:c>
+      <x:c r="L30" t="str">
+        <x:v>已核验开放</x:v>
+      </x:c>
+      <x:c r="M30" t="str">
+        <x:v>P2-正常关注</x:v>
+      </x:c>
+      <x:c r="N30" t="str">
         <x:v>同一时间只能投1岗；淘汰后可重新投递，次数不限。</x:v>
       </x:c>
-      <x:c r="O24" s="15" t="str">
+      <x:c r="O30" t="str">
         <x:v>https://baijiahao.baidu.com/s?id=1871311310412318517&amp;wfr=spider&amp;for=pc</x:v>
       </x:c>
-      <x:c r="P24" s="16" t="str">
+      <x:c r="P30" t="str">
         <x:v>A-官方招聘日历/官方来源已核验</x:v>
       </x:c>
-      <x:c r="Q24" s="4" t="str">
+      <x:c r="Q30" s="39" t="str">
         <x:v>2026-07-24</x:v>
       </x:c>
     </x:row>
@@ -8778,7 +9215,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d0b695393124d4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32f019867e04453b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8796,7 +9233,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="28" t="str">
-        <x:v>使用说明与统计（截至2026-08-11）</x:v>
+        <x:v>使用说明与统计（截至2026-08-12）</x:v>
       </x:c>
       <x:c r="B1" s="28"/>
       <x:c r="C1" s="28"/>
@@ -8949,7 +9386,7 @@
       <x:c r="B12" s="26"/>
       <x:c r="C12" s="26"/>
       <x:c r="D12" s="32" t="str">
-        <x:v>光电/科研</x:v>
+        <x:v>半导体/芯片</x:v>
       </x:c>
       <x:c r="E12" s="33" t="n">
         <x:v>2</x:v>
@@ -8963,7 +9400,7 @@
       <x:c r="B13" s="26"/>
       <x:c r="C13" s="26"/>
       <x:c r="D13" s="32" t="str">
-        <x:v>光学/高端装备</x:v>
+        <x:v>光电/科研</x:v>
       </x:c>
       <x:c r="E13" s="33" t="n">
         <x:v>2</x:v>
@@ -8975,7 +9412,7 @@
       <x:c r="B14" s="26"/>
       <x:c r="C14" s="26"/>
       <x:c r="D14" s="32" t="str">
-        <x:v>航天/军工</x:v>
+        <x:v>光学/高端装备</x:v>
       </x:c>
       <x:c r="E14" s="33" t="n">
         <x:v>2</x:v>
@@ -8987,7 +9424,7 @@
       <x:c r="B15" s="26"/>
       <x:c r="C15" s="26"/>
       <x:c r="D15" s="32" t="str">
-        <x:v>互联网/内容平台</x:v>
+        <x:v>航天/军工</x:v>
       </x:c>
       <x:c r="E15" s="33" t="n">
         <x:v>2</x:v>
@@ -8999,11 +9436,11 @@
         <x:v>项目总数</x:v>
       </x:c>
       <x:c r="B16" s="29" t="n">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C16" s="26"/>
       <x:c r="D16" s="32" t="str">
-        <x:v>会计审计/专业服务</x:v>
+        <x:v>互联网/内容平台</x:v>
       </x:c>
       <x:c r="E16" s="33" t="n">
         <x:v>2</x:v>
@@ -9012,14 +9449,14 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="29" t="str">
-        <x:v>有明确截止时间（未截止）</x:v>
+        <x:v>明确截止日期</x:v>
       </x:c>
       <x:c r="B17" s="29" t="n">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C17" s="26"/>
       <x:c r="D17" s="32" t="str">
-        <x:v>消费电子/智能终端</x:v>
+        <x:v>会计审计/专业服务</x:v>
       </x:c>
       <x:c r="E17" s="33" t="n">
         <x:v>2</x:v>
@@ -9031,11 +9468,11 @@
         <x:v>A等级</x:v>
       </x:c>
       <x:c r="B18" s="29" t="n">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C18" s="26"/>
       <x:c r="D18" s="32" t="str">
-        <x:v>银行/金融</x:v>
+        <x:v>消费电子/智能终端</x:v>
       </x:c>
       <x:c r="E18" s="33" t="n">
         <x:v>2</x:v>
@@ -9059,7 +9496,7 @@
         <x:v>C等级</x:v>
       </x:c>
       <x:c r="B20" s="29" t="n">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C20" s="26"/>
       <x:c r="D20" s="34"/>
@@ -9079,7 +9516,7 @@
         <x:v>本次更新</x:v>
       </x:c>
       <x:c r="B22" s="26" t="str">
-        <x:v>新增2项；关闭0项；未来7天内明确截止5项；新增项目来自企业官方校园招聘页，免笔试政策以公告为准。</x:v>
+        <x:v>新增2项；关闭0项；未来7天内明确截止5项；补录恒玄科技、南芯科技官方校招项目，多益网络升级为企业官方A等级核验。</x:v>
       </x:c>
       <x:c r="C22" s="26"/>
       <x:c r="D22" s="26"/>
